--- a/WeiJingShuZhi/属性表.xlsx
+++ b/WeiJingShuZhi/属性表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\WeiJingShuZhi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19FACCAB-EA86-43C0-81D6-C501D8B20C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F006511-A447-4C24-B5E6-CD410D4BFE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -29,17 +29,18 @@
     <sheet name="宝石" sheetId="14" r:id="rId14"/>
     <sheet name="宠物" sheetId="15" r:id="rId15"/>
     <sheet name="宠物属性" sheetId="16" r:id="rId16"/>
-    <sheet name="宠物爬塔" sheetId="17" r:id="rId17"/>
-    <sheet name="宠物之核" sheetId="18" r:id="rId18"/>
-    <sheet name="装备" sheetId="19" r:id="rId19"/>
-    <sheet name="怪物属性" sheetId="20" r:id="rId20"/>
-    <sheet name="boss技能" sheetId="21" r:id="rId21"/>
-    <sheet name="称号" sheetId="22" r:id="rId22"/>
-    <sheet name="生命之盾" sheetId="23" r:id="rId23"/>
+    <sheet name="宠物装备" sheetId="24" r:id="rId17"/>
+    <sheet name="宠物爬塔" sheetId="17" r:id="rId18"/>
+    <sheet name="宠物之核" sheetId="18" r:id="rId19"/>
+    <sheet name="装备" sheetId="19" r:id="rId20"/>
+    <sheet name="怪物属性" sheetId="20" r:id="rId21"/>
+    <sheet name="boss技能" sheetId="21" r:id="rId22"/>
+    <sheet name="称号" sheetId="22" r:id="rId23"/>
+    <sheet name="生命之盾" sheetId="23" r:id="rId24"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId24"/>
     <externalReference r:id="rId25"/>
+    <externalReference r:id="rId26"/>
   </externalReferences>
   <calcPr calcId="191029"/>
 </workbook>
@@ -89,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5182" uniqueCount="2896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5290" uniqueCount="2950">
   <si>
     <t>人物属性</t>
   </si>
@@ -9107,6 +9108,177 @@
   </si>
   <si>
     <t>万能鉴定符</t>
+  </si>
+  <si>
+    <t>生命+1500\n生命+1%\n对怪攻击提升300点</t>
+  </si>
+  <si>
+    <t>生命+2625\n生命+2%\n对怪攻击提升525点</t>
+  </si>
+  <si>
+    <t>生命+3750\n生命+3%\n对怪攻击提升750点</t>
+  </si>
+  <si>
+    <t>生命+4875\n生命+4%\n对怪攻击提升975点</t>
+  </si>
+  <si>
+    <t>生命+6000\n生命+5%\n对怪攻击提升1200点</t>
+  </si>
+  <si>
+    <t>生命+7500\n生命+6%\n对怪攻击提升1500点</t>
+  </si>
+  <si>
+    <t>生命+9000\n生命+7%\n对怪攻击提升1800点</t>
+  </si>
+  <si>
+    <t>生命+10500\n生命+8%\n对怪攻击提升2100点</t>
+  </si>
+  <si>
+    <t>生命+12750\n生命+9%\n对怪攻击提升2550点</t>
+  </si>
+  <si>
+    <t>生命+15000\n生命+10%\n对怪攻击提升3000点</t>
+  </si>
+  <si>
+    <t>生命+18000\n生命+11%\n对怪攻击提升3500点</t>
+  </si>
+  <si>
+    <t>生命+21000\n生命+12%\n对怪攻击提升4000点</t>
+  </si>
+  <si>
+    <t>生命+24000\n生命+13%\n对怪攻击提升4500点</t>
+  </si>
+  <si>
+    <t>生命+27000\n生命+14%\n对怪攻击提升5000点</t>
+  </si>
+  <si>
+    <t>生命+30000\n生命+15%\n对怪攻击提升5500点</t>
+  </si>
+  <si>
+    <t>攻击+200\n攻击+1%\n对怪攻击提升300点</t>
+  </si>
+  <si>
+    <t>攻击+350\n攻击+2%\n对怪攻击提升525点</t>
+  </si>
+  <si>
+    <t>攻击+500\n攻击+3%\n对怪攻击提升750点</t>
+  </si>
+  <si>
+    <t>攻击+650\n攻击+4%\n对怪攻击提升975点</t>
+  </si>
+  <si>
+    <t>攻击+800\n攻击+5%\n对怪攻击提升1200点</t>
+  </si>
+  <si>
+    <t>攻击+1000\n攻击+6%\n对怪攻击提升1500点</t>
+  </si>
+  <si>
+    <t>攻击+1200\n攻击+7%\n对怪攻击提升1800点</t>
+  </si>
+  <si>
+    <t>攻击+1400\n攻击+8%\n对怪攻击提升2100点</t>
+  </si>
+  <si>
+    <t>攻击+1700\n攻击+9%\n对怪攻击提升2550点</t>
+  </si>
+  <si>
+    <t>攻击+2000\n攻击+10%\n对怪攻击提升3000点</t>
+  </si>
+  <si>
+    <t>攻击+2300\n攻击+11%\n对怪攻击提升3500点</t>
+  </si>
+  <si>
+    <t>攻击+2600\n攻击+12%\n对怪攻击提升4000点</t>
+  </si>
+  <si>
+    <t>攻击+2900\n攻击+13%\n对怪攻击提升4500点</t>
+  </si>
+  <si>
+    <t>攻击+3200\n攻击+14%\n对怪攻击提升5000点</t>
+  </si>
+  <si>
+    <t>攻击+3500\n攻击+15%\n对怪攻击提升5500点</t>
+  </si>
+  <si>
+    <t>物防+200\n物防+1%\n对怪攻击提升300点</t>
+  </si>
+  <si>
+    <t>物防+350\n物防+2%\n对怪攻击提升525点</t>
+  </si>
+  <si>
+    <t>物防+500\n物防+3%\n对怪攻击提升750点</t>
+  </si>
+  <si>
+    <t>物防+650\n物防+4%\n对怪攻击提升975点</t>
+  </si>
+  <si>
+    <t>物防+800\n物防+5%\n对怪攻击提升1200点</t>
+  </si>
+  <si>
+    <t>物防+1000\n物防+6%\n对怪攻击提升1500点</t>
+  </si>
+  <si>
+    <t>物防+1200\n物防+7%\n对怪攻击提升1800点</t>
+  </si>
+  <si>
+    <t>物防+1400\n物防+8%\n对怪攻击提升2100点</t>
+  </si>
+  <si>
+    <t>物防+1700\n物防+9%\n对怪攻击提升2550点</t>
+  </si>
+  <si>
+    <t>物防+2000\n物防+10%\n对怪攻击提升3000点</t>
+  </si>
+  <si>
+    <t>物防+2300\n物防+11%\n对怪攻击提升3500点</t>
+  </si>
+  <si>
+    <t>物防+2600\n物防+12%\n对怪攻击提升4000点</t>
+  </si>
+  <si>
+    <t>物防+2900\n物防+13%\n对怪攻击提升4500点</t>
+  </si>
+  <si>
+    <t>物防+3200\n物防+14%\n对怪攻击提升5000点</t>
+  </si>
+  <si>
+    <t>物防+3500\n物防+15%\n对怪攻击提升5500点</t>
+  </si>
+  <si>
+    <t>项圈</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>体质</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>力量</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>智力</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐力</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>头饰</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>手腕</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物装备打造属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
+    <phoneticPr fontId="35" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -9387,7 +9559,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9508,6 +9680,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14865565965758232"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -9619,7 +9797,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9944,6 +10122,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="20" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -10621,2519 +10802,2491 @@
       <sheetData sheetId="0">
         <row r="856">
           <cell r="C856">
-            <v>13002103</v>
+            <v>10302006</v>
           </cell>
         </row>
         <row r="857">
           <cell r="C857">
-            <v>13002104</v>
+            <v>10303001</v>
           </cell>
         </row>
         <row r="858">
           <cell r="C858">
-            <v>13002105</v>
+            <v>10303002</v>
           </cell>
         </row>
         <row r="859">
           <cell r="C859">
-            <v>13003001</v>
+            <v>10303003</v>
           </cell>
         </row>
         <row r="860">
           <cell r="C860">
-            <v>13003002</v>
+            <v>10303004</v>
           </cell>
         </row>
         <row r="861">
           <cell r="C861">
-            <v>13003003</v>
+            <v>10303005</v>
           </cell>
         </row>
         <row r="862">
           <cell r="C862">
-            <v>13003004</v>
+            <v>10303006</v>
           </cell>
         </row>
         <row r="863">
           <cell r="C863">
-            <v>13003005</v>
+            <v>11200000</v>
           </cell>
         </row>
         <row r="864">
           <cell r="C864">
-            <v>13003006</v>
+            <v>11200001</v>
           </cell>
         </row>
         <row r="865">
           <cell r="C865">
-            <v>13003101</v>
+            <v>11200002</v>
           </cell>
         </row>
         <row r="866">
           <cell r="C866">
-            <v>13003102</v>
+            <v>11200003</v>
           </cell>
         </row>
         <row r="867">
           <cell r="C867">
-            <v>13003103</v>
+            <v>11200010</v>
           </cell>
         </row>
         <row r="868">
           <cell r="C868">
-            <v>13003104</v>
+            <v>11300001</v>
           </cell>
         </row>
         <row r="869">
           <cell r="C869">
-            <v>13003105</v>
+            <v>11300002</v>
           </cell>
         </row>
         <row r="870">
           <cell r="C870">
-            <v>13004001</v>
+            <v>11300003</v>
           </cell>
         </row>
         <row r="871">
           <cell r="C871">
-            <v>13004002</v>
+            <v>11300004</v>
           </cell>
         </row>
         <row r="872">
           <cell r="C872">
-            <v>13004003</v>
+            <v>11300005</v>
           </cell>
         </row>
         <row r="873">
           <cell r="C873">
-            <v>13004004</v>
+            <v>11300006</v>
           </cell>
         </row>
         <row r="874">
           <cell r="C874">
-            <v>13004005</v>
+            <v>11300007</v>
           </cell>
         </row>
         <row r="875">
           <cell r="C875">
-            <v>13004006</v>
+            <v>11300008</v>
           </cell>
         </row>
         <row r="876">
           <cell r="C876">
-            <v>13004101</v>
+            <v>11300009</v>
           </cell>
         </row>
         <row r="877">
           <cell r="C877">
-            <v>13004102</v>
+            <v>11300101</v>
           </cell>
         </row>
         <row r="878">
           <cell r="C878">
-            <v>13004103</v>
+            <v>11300102</v>
           </cell>
         </row>
         <row r="879">
           <cell r="C879">
-            <v>13004104</v>
+            <v>11300103</v>
           </cell>
         </row>
         <row r="880">
           <cell r="C880">
-            <v>13004105</v>
+            <v>11300104</v>
           </cell>
         </row>
         <row r="881">
           <cell r="C881">
-            <v>13005001</v>
+            <v>11300105</v>
           </cell>
         </row>
         <row r="882">
           <cell r="C882">
-            <v>13005002</v>
+            <v>11300201</v>
           </cell>
         </row>
         <row r="883">
           <cell r="C883">
-            <v>13005003</v>
+            <v>11300202</v>
           </cell>
         </row>
         <row r="884">
           <cell r="C884">
-            <v>13005004</v>
+            <v>11300203</v>
           </cell>
         </row>
         <row r="885">
           <cell r="C885">
-            <v>13005005</v>
+            <v>11300204</v>
           </cell>
         </row>
         <row r="886">
           <cell r="C886">
-            <v>13005006</v>
+            <v>11300205</v>
           </cell>
         </row>
         <row r="887">
           <cell r="C887">
-            <v>13005101</v>
+            <v>11300301</v>
           </cell>
         </row>
         <row r="888">
           <cell r="C888">
-            <v>13005102</v>
+            <v>11300302</v>
           </cell>
         </row>
         <row r="889">
           <cell r="C889">
-            <v>13005103</v>
+            <v>11300303</v>
           </cell>
         </row>
         <row r="890">
           <cell r="C890">
-            <v>13005104</v>
+            <v>11300304</v>
           </cell>
         </row>
         <row r="891">
           <cell r="C891">
-            <v>13005105</v>
+            <v>11300305</v>
           </cell>
         </row>
         <row r="892">
           <cell r="C892">
-            <v>13006001</v>
+            <v>11300401</v>
           </cell>
         </row>
         <row r="893">
           <cell r="C893">
-            <v>13006002</v>
+            <v>11300402</v>
           </cell>
         </row>
         <row r="894">
           <cell r="C894">
-            <v>13006003</v>
-          </cell>
-          <cell r="S894">
-            <v>0</v>
+            <v>11300403</v>
           </cell>
         </row>
         <row r="895">
           <cell r="C895">
-            <v>13006004</v>
-          </cell>
-          <cell r="S895">
-            <v>0</v>
+            <v>11300404</v>
           </cell>
         </row>
         <row r="896">
           <cell r="C896">
-            <v>13009001</v>
+            <v>11300405</v>
           </cell>
         </row>
         <row r="897">
           <cell r="C897">
-            <v>13009002</v>
+            <v>11300501</v>
           </cell>
         </row>
         <row r="898">
           <cell r="C898">
-            <v>14000001</v>
+            <v>11300502</v>
           </cell>
         </row>
         <row r="899">
           <cell r="C899">
-            <v>14000002</v>
+            <v>11300503</v>
           </cell>
         </row>
         <row r="900">
           <cell r="C900">
-            <v>14000003</v>
-          </cell>
-          <cell r="S900">
-            <v>69000011</v>
+            <v>11300504</v>
           </cell>
         </row>
         <row r="901">
           <cell r="C901">
-            <v>14000004</v>
+            <v>11300505</v>
           </cell>
         </row>
         <row r="902">
           <cell r="C902">
-            <v>14000005</v>
+            <v>11300601</v>
           </cell>
         </row>
         <row r="903">
           <cell r="C903">
-            <v>14010001</v>
+            <v>11300602</v>
           </cell>
         </row>
         <row r="904">
           <cell r="C904">
-            <v>14010002</v>
+            <v>11300603</v>
           </cell>
         </row>
         <row r="905">
           <cell r="C905">
-            <v>14010003</v>
+            <v>11300604</v>
           </cell>
         </row>
         <row r="906">
           <cell r="C906">
-            <v>14010004</v>
+            <v>11300605</v>
           </cell>
         </row>
         <row r="907">
           <cell r="C907">
-            <v>14010005</v>
+            <v>11400101</v>
           </cell>
         </row>
         <row r="908">
           <cell r="C908">
-            <v>14010006</v>
+            <v>11400102</v>
           </cell>
         </row>
         <row r="909">
           <cell r="C909">
-            <v>14010007</v>
+            <v>11400103</v>
           </cell>
         </row>
         <row r="910">
           <cell r="C910">
-            <v>14010008</v>
+            <v>11500101</v>
           </cell>
         </row>
         <row r="911">
           <cell r="C911">
-            <v>14010009</v>
+            <v>11500102</v>
           </cell>
         </row>
         <row r="912">
           <cell r="C912">
-            <v>14010010</v>
+            <v>11500103</v>
           </cell>
         </row>
         <row r="913">
           <cell r="C913">
-            <v>14010011</v>
+            <v>11500201</v>
           </cell>
         </row>
         <row r="914">
           <cell r="C914">
-            <v>14010012</v>
+            <v>11500202</v>
           </cell>
         </row>
         <row r="915">
           <cell r="C915">
-            <v>14020001</v>
+            <v>11500203</v>
           </cell>
         </row>
         <row r="916">
           <cell r="C916">
-            <v>14020002</v>
+            <v>11500301</v>
           </cell>
         </row>
         <row r="917">
           <cell r="C917">
-            <v>14020003</v>
+            <v>11500302</v>
           </cell>
         </row>
         <row r="918">
           <cell r="C918">
-            <v>14020004</v>
+            <v>11500303</v>
           </cell>
         </row>
         <row r="919">
           <cell r="C919">
-            <v>14020005</v>
+            <v>11500401</v>
           </cell>
         </row>
         <row r="920">
           <cell r="C920">
-            <v>14020006</v>
+            <v>11500402</v>
           </cell>
         </row>
         <row r="921">
           <cell r="C921">
-            <v>14020007</v>
+            <v>11500403</v>
           </cell>
         </row>
         <row r="922">
           <cell r="C922">
-            <v>14020008</v>
+            <v>11500501</v>
           </cell>
         </row>
         <row r="923">
           <cell r="C923">
-            <v>14020009</v>
+            <v>11500502</v>
           </cell>
         </row>
         <row r="924">
           <cell r="C924">
-            <v>14020010</v>
+            <v>11500503</v>
           </cell>
         </row>
         <row r="925">
           <cell r="C925">
-            <v>14020011</v>
+            <v>13001001</v>
           </cell>
         </row>
         <row r="926">
           <cell r="C926">
-            <v>14020012</v>
+            <v>13001002</v>
           </cell>
         </row>
         <row r="927">
           <cell r="C927">
-            <v>14020013</v>
+            <v>13001003</v>
           </cell>
         </row>
         <row r="928">
           <cell r="C928">
-            <v>14030001</v>
+            <v>13001004</v>
           </cell>
         </row>
         <row r="929">
           <cell r="C929">
-            <v>14030002</v>
+            <v>13001005</v>
           </cell>
         </row>
         <row r="930">
           <cell r="C930">
-            <v>14030003</v>
+            <v>13001006</v>
           </cell>
         </row>
         <row r="931">
           <cell r="C931">
-            <v>14030004</v>
+            <v>13001101</v>
           </cell>
         </row>
         <row r="932">
           <cell r="C932">
-            <v>14030005</v>
+            <v>13001102</v>
           </cell>
         </row>
         <row r="933">
           <cell r="C933">
-            <v>14030006</v>
+            <v>13001103</v>
           </cell>
         </row>
         <row r="934">
           <cell r="C934">
-            <v>14030007</v>
+            <v>13001104</v>
           </cell>
         </row>
         <row r="935">
           <cell r="C935">
-            <v>14030008</v>
+            <v>13001105</v>
           </cell>
         </row>
         <row r="936">
           <cell r="C936">
-            <v>14030009</v>
+            <v>13002001</v>
           </cell>
         </row>
         <row r="937">
           <cell r="C937">
-            <v>14030010</v>
+            <v>13002002</v>
           </cell>
         </row>
         <row r="938">
           <cell r="C938">
-            <v>14030011</v>
+            <v>13002003</v>
           </cell>
         </row>
         <row r="939">
           <cell r="C939">
-            <v>14030012</v>
+            <v>13002004</v>
           </cell>
         </row>
         <row r="940">
           <cell r="C940">
-            <v>14030013</v>
+            <v>13002005</v>
           </cell>
         </row>
         <row r="941">
           <cell r="C941">
-            <v>14040001</v>
+            <v>13002006</v>
           </cell>
         </row>
         <row r="942">
           <cell r="C942">
-            <v>14040002</v>
+            <v>13002101</v>
           </cell>
         </row>
         <row r="943">
           <cell r="C943">
-            <v>14040003</v>
+            <v>13002102</v>
           </cell>
         </row>
         <row r="944">
           <cell r="C944">
-            <v>14040004</v>
+            <v>13002103</v>
           </cell>
         </row>
         <row r="945">
           <cell r="C945">
-            <v>14040005</v>
+            <v>13002104</v>
           </cell>
         </row>
         <row r="946">
           <cell r="C946">
-            <v>14040006</v>
+            <v>13002105</v>
           </cell>
         </row>
         <row r="947">
           <cell r="C947">
-            <v>14040007</v>
+            <v>13003001</v>
           </cell>
         </row>
         <row r="948">
           <cell r="C948">
-            <v>14040008</v>
+            <v>13003002</v>
           </cell>
         </row>
         <row r="949">
           <cell r="C949">
-            <v>14040009</v>
+            <v>13003003</v>
           </cell>
         </row>
         <row r="950">
           <cell r="C950">
-            <v>14040010</v>
+            <v>13003004</v>
           </cell>
         </row>
         <row r="951">
           <cell r="C951">
-            <v>14040011</v>
+            <v>13003005</v>
           </cell>
         </row>
         <row r="952">
           <cell r="C952">
-            <v>14040012</v>
+            <v>13003006</v>
           </cell>
         </row>
         <row r="953">
           <cell r="C953">
-            <v>14050001</v>
+            <v>13003101</v>
           </cell>
         </row>
         <row r="954">
           <cell r="C954">
-            <v>14050002</v>
+            <v>13003102</v>
           </cell>
         </row>
         <row r="955">
           <cell r="C955">
-            <v>14050003</v>
+            <v>13003103</v>
           </cell>
         </row>
         <row r="956">
           <cell r="C956">
-            <v>14050004</v>
+            <v>13003104</v>
           </cell>
         </row>
         <row r="957">
           <cell r="C957">
-            <v>14050005</v>
+            <v>13003105</v>
           </cell>
         </row>
         <row r="958">
           <cell r="C958">
-            <v>14050006</v>
+            <v>13004001</v>
           </cell>
         </row>
         <row r="959">
           <cell r="C959">
-            <v>14050007</v>
+            <v>13004002</v>
           </cell>
         </row>
         <row r="960">
           <cell r="C960">
-            <v>14050008</v>
+            <v>13004003</v>
           </cell>
         </row>
         <row r="961">
           <cell r="C961">
-            <v>14050009</v>
+            <v>13004004</v>
           </cell>
         </row>
         <row r="962">
           <cell r="C962">
-            <v>14050010</v>
+            <v>13004005</v>
           </cell>
         </row>
         <row r="963">
           <cell r="C963">
-            <v>14050011</v>
+            <v>13004006</v>
           </cell>
         </row>
         <row r="964">
           <cell r="C964">
-            <v>14050012</v>
+            <v>13004101</v>
           </cell>
         </row>
         <row r="965">
           <cell r="C965">
-            <v>14060001</v>
+            <v>13004102</v>
           </cell>
         </row>
         <row r="966">
           <cell r="C966">
-            <v>14060002</v>
+            <v>13004103</v>
           </cell>
         </row>
         <row r="967">
           <cell r="C967">
-            <v>14060003</v>
+            <v>13004104</v>
           </cell>
         </row>
         <row r="968">
           <cell r="C968">
-            <v>14060004</v>
+            <v>13004105</v>
           </cell>
         </row>
         <row r="969">
           <cell r="C969">
-            <v>14060005</v>
+            <v>13005001</v>
           </cell>
         </row>
         <row r="970">
           <cell r="C970">
-            <v>14060006</v>
-          </cell>
-          <cell r="S970">
-            <v>68000018</v>
+            <v>13005002</v>
           </cell>
         </row>
         <row r="971">
           <cell r="C971">
-            <v>14070001</v>
+            <v>13005003</v>
           </cell>
         </row>
         <row r="972">
           <cell r="C972">
-            <v>14070002</v>
+            <v>13005004</v>
           </cell>
         </row>
         <row r="973">
           <cell r="C973">
-            <v>14070003</v>
+            <v>13005005</v>
           </cell>
         </row>
         <row r="974">
           <cell r="C974">
-            <v>14070004</v>
+            <v>13005006</v>
           </cell>
         </row>
         <row r="975">
           <cell r="C975">
-            <v>14080001</v>
-          </cell>
-          <cell r="S975">
-            <v>66001001</v>
+            <v>13005101</v>
           </cell>
         </row>
         <row r="976">
           <cell r="C976">
-            <v>14080002</v>
-          </cell>
-          <cell r="S976">
-            <v>66001002</v>
+            <v>13005102</v>
           </cell>
         </row>
         <row r="977">
           <cell r="C977">
-            <v>14080003</v>
-          </cell>
-          <cell r="S977">
-            <v>66001003</v>
+            <v>13005103</v>
           </cell>
         </row>
         <row r="978">
           <cell r="C978">
-            <v>14080004</v>
-          </cell>
-          <cell r="S978">
-            <v>66001012</v>
+            <v>13005104</v>
           </cell>
         </row>
         <row r="979">
           <cell r="C979">
-            <v>14090001</v>
+            <v>13005105</v>
           </cell>
         </row>
         <row r="980">
           <cell r="C980">
-            <v>14090002</v>
+            <v>13006001</v>
           </cell>
         </row>
         <row r="981">
           <cell r="C981">
-            <v>14090003</v>
+            <v>13006002</v>
           </cell>
         </row>
         <row r="982">
           <cell r="C982">
-            <v>14090004</v>
+            <v>13006003</v>
+          </cell>
+          <cell r="S982">
+            <v>0</v>
           </cell>
         </row>
         <row r="983">
           <cell r="C983">
-            <v>14100001</v>
+            <v>13006004</v>
+          </cell>
+          <cell r="S983">
+            <v>0</v>
           </cell>
         </row>
         <row r="984">
           <cell r="C984">
-            <v>14100002</v>
+            <v>13009001</v>
           </cell>
         </row>
         <row r="985">
           <cell r="C985">
-            <v>14100003</v>
+            <v>13009002</v>
           </cell>
         </row>
         <row r="986">
           <cell r="C986">
-            <v>14100004</v>
+            <v>14000001</v>
           </cell>
         </row>
         <row r="987">
           <cell r="C987">
-            <v>14100005</v>
+            <v>14000002</v>
           </cell>
         </row>
         <row r="988">
           <cell r="C988">
-            <v>14100006</v>
+            <v>14000003</v>
+          </cell>
+          <cell r="S988">
+            <v>69000011</v>
           </cell>
         </row>
         <row r="989">
           <cell r="C989">
-            <v>14100007</v>
+            <v>14000004</v>
           </cell>
         </row>
         <row r="990">
           <cell r="C990">
-            <v>14100008</v>
+            <v>14000005</v>
           </cell>
         </row>
         <row r="991">
           <cell r="C991">
-            <v>14100011</v>
-          </cell>
-          <cell r="S991">
-            <v>69000001</v>
+            <v>14010001</v>
           </cell>
         </row>
         <row r="992">
           <cell r="C992">
-            <v>14100012</v>
+            <v>14010002</v>
           </cell>
         </row>
         <row r="993">
           <cell r="C993">
-            <v>14100021</v>
+            <v>14010003</v>
           </cell>
         </row>
         <row r="994">
           <cell r="C994">
-            <v>14100022</v>
+            <v>14010004</v>
           </cell>
         </row>
         <row r="995">
           <cell r="C995">
-            <v>14100101</v>
+            <v>14010005</v>
           </cell>
         </row>
         <row r="996">
           <cell r="C996">
-            <v>14100102</v>
+            <v>14010006</v>
           </cell>
         </row>
         <row r="997">
           <cell r="C997">
-            <v>14100103</v>
+            <v>14010007</v>
           </cell>
         </row>
         <row r="998">
           <cell r="C998">
-            <v>14100104</v>
+            <v>14010008</v>
           </cell>
         </row>
         <row r="999">
           <cell r="C999">
-            <v>14100105</v>
+            <v>14010009</v>
           </cell>
         </row>
         <row r="1000">
           <cell r="C1000">
-            <v>14100106</v>
+            <v>14010010</v>
           </cell>
         </row>
         <row r="1001">
           <cell r="C1001">
-            <v>14100107</v>
+            <v>14010011</v>
           </cell>
         </row>
         <row r="1002">
           <cell r="C1002">
-            <v>14100108</v>
+            <v>14010012</v>
           </cell>
         </row>
         <row r="1003">
           <cell r="C1003">
-            <v>14100111</v>
-          </cell>
-          <cell r="S1003">
-            <v>69000002</v>
+            <v>14020001</v>
           </cell>
         </row>
         <row r="1004">
           <cell r="C1004">
-            <v>14100112</v>
-          </cell>
-          <cell r="S1004">
-            <v>69000003</v>
+            <v>14020002</v>
           </cell>
         </row>
         <row r="1005">
           <cell r="C1005">
-            <v>14100121</v>
+            <v>14020003</v>
           </cell>
         </row>
         <row r="1006">
           <cell r="C1006">
-            <v>14100122</v>
+            <v>14020004</v>
           </cell>
         </row>
         <row r="1007">
           <cell r="C1007">
-            <v>14100201</v>
+            <v>14020005</v>
           </cell>
         </row>
         <row r="1008">
           <cell r="C1008">
-            <v>14100202</v>
+            <v>14020006</v>
           </cell>
         </row>
         <row r="1009">
           <cell r="C1009">
-            <v>14100203</v>
+            <v>14020007</v>
           </cell>
         </row>
         <row r="1010">
           <cell r="C1010">
-            <v>14100204</v>
+            <v>14020008</v>
           </cell>
         </row>
         <row r="1011">
           <cell r="C1011">
-            <v>14100211</v>
-          </cell>
-          <cell r="S1011">
-            <v>69000002</v>
+            <v>14020009</v>
           </cell>
         </row>
         <row r="1012">
           <cell r="C1012">
-            <v>14100221</v>
+            <v>14020010</v>
           </cell>
         </row>
         <row r="1013">
           <cell r="C1013">
-            <v>14110001</v>
+            <v>14020011</v>
           </cell>
         </row>
         <row r="1014">
           <cell r="C1014">
-            <v>14110002</v>
+            <v>14020012</v>
           </cell>
         </row>
         <row r="1015">
           <cell r="C1015">
-            <v>14110003</v>
+            <v>14020013</v>
           </cell>
         </row>
         <row r="1016">
           <cell r="C1016">
-            <v>14110004</v>
+            <v>14030001</v>
           </cell>
         </row>
         <row r="1017">
           <cell r="C1017">
-            <v>14110005</v>
+            <v>14030002</v>
           </cell>
         </row>
         <row r="1018">
           <cell r="C1018">
-            <v>14110006</v>
+            <v>14030003</v>
           </cell>
         </row>
         <row r="1019">
           <cell r="C1019">
-            <v>14110007</v>
+            <v>14030004</v>
           </cell>
         </row>
         <row r="1020">
           <cell r="C1020">
-            <v>14110008</v>
+            <v>14030005</v>
           </cell>
         </row>
         <row r="1021">
           <cell r="C1021">
-            <v>14110009</v>
+            <v>14030006</v>
           </cell>
         </row>
         <row r="1022">
           <cell r="C1022">
-            <v>14110010</v>
+            <v>14030007</v>
           </cell>
         </row>
         <row r="1023">
           <cell r="C1023">
-            <v>14110011</v>
+            <v>14030008</v>
           </cell>
         </row>
         <row r="1024">
           <cell r="C1024">
-            <v>14110012</v>
+            <v>14030009</v>
           </cell>
         </row>
         <row r="1025">
           <cell r="C1025">
-            <v>14110021</v>
+            <v>14030010</v>
           </cell>
         </row>
         <row r="1026">
           <cell r="C1026">
-            <v>14110022</v>
+            <v>14030011</v>
           </cell>
         </row>
         <row r="1027">
           <cell r="C1027">
-            <v>14110023</v>
+            <v>14030012</v>
           </cell>
         </row>
         <row r="1028">
           <cell r="C1028">
-            <v>15201001</v>
+            <v>14030013</v>
           </cell>
         </row>
         <row r="1029">
           <cell r="C1029">
-            <v>15201002</v>
+            <v>14040001</v>
           </cell>
         </row>
         <row r="1030">
           <cell r="C1030">
-            <v>15201003</v>
+            <v>14040002</v>
           </cell>
         </row>
         <row r="1031">
           <cell r="C1031">
-            <v>15201004</v>
+            <v>14040003</v>
           </cell>
         </row>
         <row r="1032">
           <cell r="C1032">
-            <v>15201005</v>
+            <v>14040004</v>
           </cell>
         </row>
         <row r="1033">
           <cell r="C1033">
-            <v>15201006</v>
+            <v>14040005</v>
           </cell>
         </row>
         <row r="1034">
           <cell r="C1034">
-            <v>15202001</v>
+            <v>14040006</v>
           </cell>
         </row>
         <row r="1035">
           <cell r="C1035">
-            <v>15202002</v>
+            <v>14040007</v>
           </cell>
         </row>
         <row r="1036">
           <cell r="C1036">
-            <v>15202003</v>
+            <v>14040008</v>
           </cell>
         </row>
         <row r="1037">
           <cell r="C1037">
-            <v>15202004</v>
+            <v>14040009</v>
           </cell>
         </row>
         <row r="1038">
           <cell r="C1038">
-            <v>15202005</v>
+            <v>14040010</v>
           </cell>
         </row>
         <row r="1039">
           <cell r="C1039">
-            <v>15202006</v>
+            <v>14040011</v>
           </cell>
         </row>
         <row r="1040">
           <cell r="C1040">
-            <v>15203001</v>
+            <v>14040012</v>
           </cell>
         </row>
         <row r="1041">
           <cell r="C1041">
-            <v>15203002</v>
+            <v>14050001</v>
           </cell>
         </row>
         <row r="1042">
           <cell r="C1042">
-            <v>15203003</v>
+            <v>14050002</v>
           </cell>
         </row>
         <row r="1043">
           <cell r="C1043">
-            <v>15203004</v>
+            <v>14050003</v>
           </cell>
         </row>
         <row r="1044">
           <cell r="C1044">
-            <v>15203005</v>
+            <v>14050004</v>
           </cell>
         </row>
         <row r="1045">
           <cell r="C1045">
-            <v>15203006</v>
+            <v>14050005</v>
           </cell>
         </row>
         <row r="1046">
           <cell r="C1046">
-            <v>15204001</v>
+            <v>14050006</v>
           </cell>
         </row>
         <row r="1047">
           <cell r="C1047">
-            <v>15204002</v>
+            <v>14050007</v>
           </cell>
         </row>
         <row r="1048">
           <cell r="C1048">
-            <v>15204003</v>
+            <v>14050008</v>
           </cell>
         </row>
         <row r="1049">
           <cell r="C1049">
-            <v>15204004</v>
+            <v>14050009</v>
           </cell>
         </row>
         <row r="1050">
           <cell r="C1050">
-            <v>15204005</v>
+            <v>14050010</v>
           </cell>
         </row>
         <row r="1051">
           <cell r="C1051">
-            <v>15204006</v>
+            <v>14050011</v>
           </cell>
         </row>
         <row r="1052">
           <cell r="C1052">
-            <v>15205001</v>
+            <v>14050012</v>
           </cell>
         </row>
         <row r="1053">
           <cell r="C1053">
-            <v>15205002</v>
+            <v>14060001</v>
           </cell>
         </row>
         <row r="1054">
           <cell r="C1054">
-            <v>15205003</v>
+            <v>14060002</v>
           </cell>
         </row>
         <row r="1055">
           <cell r="C1055">
-            <v>15205004</v>
+            <v>14060003</v>
           </cell>
         </row>
         <row r="1056">
           <cell r="C1056">
-            <v>15205005</v>
+            <v>14060004</v>
           </cell>
         </row>
         <row r="1057">
           <cell r="C1057">
-            <v>15205006</v>
+            <v>14060005</v>
           </cell>
         </row>
         <row r="1058">
           <cell r="C1058">
-            <v>15205007</v>
+            <v>14060006</v>
+          </cell>
+          <cell r="S1058">
+            <v>68000018</v>
           </cell>
         </row>
         <row r="1059">
           <cell r="C1059">
-            <v>15206001</v>
+            <v>14070001</v>
           </cell>
         </row>
         <row r="1060">
           <cell r="C1060">
-            <v>15206002</v>
+            <v>14070002</v>
           </cell>
         </row>
         <row r="1061">
           <cell r="C1061">
-            <v>15206003</v>
+            <v>14070003</v>
           </cell>
         </row>
         <row r="1062">
           <cell r="C1062">
-            <v>15207001</v>
+            <v>14070004</v>
           </cell>
         </row>
         <row r="1063">
           <cell r="C1063">
-            <v>15207002</v>
+            <v>14080001</v>
+          </cell>
+          <cell r="S1063">
+            <v>66001001</v>
           </cell>
         </row>
         <row r="1064">
           <cell r="C1064">
-            <v>15207003</v>
+            <v>14080002</v>
+          </cell>
+          <cell r="S1064">
+            <v>66001002</v>
           </cell>
         </row>
         <row r="1065">
           <cell r="C1065">
-            <v>15208001</v>
+            <v>14080003</v>
           </cell>
           <cell r="S1065">
-            <v>66001004</v>
+            <v>66001003</v>
           </cell>
         </row>
         <row r="1066">
           <cell r="C1066">
-            <v>15208002</v>
+            <v>14080004</v>
           </cell>
           <cell r="S1066">
-            <v>66001005</v>
+            <v>66001012</v>
           </cell>
         </row>
         <row r="1067">
           <cell r="C1067">
-            <v>15208003</v>
-          </cell>
-          <cell r="S1067">
-            <v>66001013</v>
+            <v>14090001</v>
           </cell>
         </row>
         <row r="1068">
           <cell r="C1068">
-            <v>15209001</v>
+            <v>14090002</v>
           </cell>
         </row>
         <row r="1069">
           <cell r="C1069">
-            <v>15209002</v>
+            <v>14090003</v>
           </cell>
         </row>
         <row r="1070">
           <cell r="C1070">
-            <v>15210001</v>
+            <v>14090004</v>
           </cell>
         </row>
         <row r="1071">
           <cell r="C1071">
-            <v>15210002</v>
+            <v>14100001</v>
           </cell>
         </row>
         <row r="1072">
           <cell r="C1072">
-            <v>15210003</v>
+            <v>14100002</v>
           </cell>
         </row>
         <row r="1073">
           <cell r="C1073">
-            <v>15210004</v>
+            <v>14100003</v>
           </cell>
         </row>
         <row r="1074">
           <cell r="C1074">
-            <v>15210011</v>
-          </cell>
-          <cell r="S1074">
-            <v>69000016</v>
+            <v>14100004</v>
           </cell>
         </row>
         <row r="1075">
           <cell r="C1075">
-            <v>15210012</v>
+            <v>14100005</v>
           </cell>
         </row>
         <row r="1076">
           <cell r="C1076">
-            <v>15210101</v>
+            <v>14100006</v>
           </cell>
         </row>
         <row r="1077">
           <cell r="C1077">
-            <v>15210102</v>
+            <v>14100007</v>
           </cell>
         </row>
         <row r="1078">
           <cell r="C1078">
-            <v>15210103</v>
+            <v>14100008</v>
           </cell>
         </row>
         <row r="1079">
           <cell r="C1079">
-            <v>15210104</v>
+            <v>14100011</v>
+          </cell>
+          <cell r="S1079">
+            <v>69000001</v>
           </cell>
         </row>
         <row r="1080">
           <cell r="C1080">
-            <v>15210111</v>
+            <v>14100012</v>
           </cell>
         </row>
         <row r="1081">
           <cell r="C1081">
-            <v>15210112</v>
+            <v>14100021</v>
           </cell>
         </row>
         <row r="1082">
           <cell r="C1082">
-            <v>15210201</v>
+            <v>14100022</v>
           </cell>
         </row>
         <row r="1083">
           <cell r="C1083">
-            <v>15210202</v>
+            <v>14100101</v>
           </cell>
         </row>
         <row r="1084">
           <cell r="C1084">
-            <v>15210211</v>
-          </cell>
-          <cell r="S1084">
-            <v>69000014</v>
+            <v>14100102</v>
           </cell>
         </row>
         <row r="1085">
           <cell r="C1085">
-            <v>15211001</v>
+            <v>14100103</v>
           </cell>
         </row>
         <row r="1086">
           <cell r="C1086">
-            <v>15211002</v>
+            <v>14100104</v>
           </cell>
         </row>
         <row r="1087">
           <cell r="C1087">
-            <v>15211003</v>
+            <v>14100105</v>
           </cell>
         </row>
         <row r="1088">
           <cell r="C1088">
-            <v>15211004</v>
+            <v>14100106</v>
           </cell>
         </row>
         <row r="1089">
           <cell r="C1089">
-            <v>15211005</v>
+            <v>14100107</v>
           </cell>
         </row>
         <row r="1090">
           <cell r="C1090">
-            <v>15211006</v>
+            <v>14100108</v>
           </cell>
         </row>
         <row r="1091">
           <cell r="C1091">
-            <v>15211011</v>
+            <v>14100111</v>
+          </cell>
+          <cell r="S1091">
+            <v>69000002</v>
           </cell>
         </row>
         <row r="1092">
           <cell r="C1092">
-            <v>15211012</v>
+            <v>14100112</v>
+          </cell>
+          <cell r="S1092">
+            <v>69000003</v>
           </cell>
         </row>
         <row r="1093">
           <cell r="C1093">
-            <v>15211013</v>
-          </cell>
-          <cell r="S1093">
-            <v>69000004</v>
+            <v>14100121</v>
           </cell>
         </row>
         <row r="1094">
           <cell r="C1094">
-            <v>15301001</v>
+            <v>14100122</v>
           </cell>
         </row>
         <row r="1095">
           <cell r="C1095">
-            <v>15301002</v>
+            <v>14100201</v>
           </cell>
         </row>
         <row r="1096">
           <cell r="C1096">
-            <v>15301003</v>
+            <v>14100202</v>
           </cell>
         </row>
         <row r="1097">
           <cell r="C1097">
-            <v>15301004</v>
+            <v>14100203</v>
           </cell>
         </row>
         <row r="1098">
           <cell r="C1098">
-            <v>15301005</v>
+            <v>14100204</v>
           </cell>
         </row>
         <row r="1099">
           <cell r="C1099">
-            <v>15301006</v>
+            <v>14100211</v>
+          </cell>
+          <cell r="S1099">
+            <v>69000002</v>
           </cell>
         </row>
         <row r="1100">
           <cell r="C1100">
-            <v>15302001</v>
+            <v>14100221</v>
           </cell>
         </row>
         <row r="1101">
           <cell r="C1101">
-            <v>15302002</v>
+            <v>14110001</v>
           </cell>
         </row>
         <row r="1102">
           <cell r="C1102">
-            <v>15302003</v>
+            <v>14110002</v>
           </cell>
         </row>
         <row r="1103">
           <cell r="C1103">
-            <v>15302004</v>
+            <v>14110003</v>
           </cell>
         </row>
         <row r="1104">
           <cell r="C1104">
-            <v>15302005</v>
+            <v>14110004</v>
           </cell>
         </row>
         <row r="1105">
           <cell r="C1105">
-            <v>15302006</v>
+            <v>14110005</v>
           </cell>
         </row>
         <row r="1106">
           <cell r="C1106">
-            <v>15302007</v>
+            <v>14110006</v>
           </cell>
         </row>
         <row r="1107">
           <cell r="C1107">
-            <v>15303001</v>
+            <v>14110007</v>
           </cell>
         </row>
         <row r="1108">
           <cell r="C1108">
-            <v>15303002</v>
+            <v>14110008</v>
           </cell>
         </row>
         <row r="1109">
           <cell r="C1109">
-            <v>15303003</v>
+            <v>14110009</v>
           </cell>
         </row>
         <row r="1110">
           <cell r="C1110">
-            <v>15303004</v>
+            <v>14110010</v>
           </cell>
         </row>
         <row r="1111">
           <cell r="C1111">
-            <v>15303005</v>
+            <v>14110011</v>
           </cell>
         </row>
         <row r="1112">
           <cell r="C1112">
-            <v>15303006</v>
+            <v>14110012</v>
           </cell>
         </row>
         <row r="1113">
           <cell r="C1113">
-            <v>15304001</v>
+            <v>14110021</v>
           </cell>
         </row>
         <row r="1114">
           <cell r="C1114">
-            <v>15304002</v>
+            <v>14110022</v>
           </cell>
         </row>
         <row r="1115">
           <cell r="C1115">
-            <v>15304003</v>
+            <v>14110023</v>
           </cell>
         </row>
         <row r="1116">
           <cell r="C1116">
-            <v>15304004</v>
+            <v>15201001</v>
           </cell>
         </row>
         <row r="1117">
           <cell r="C1117">
-            <v>15304005</v>
+            <v>15201002</v>
           </cell>
         </row>
         <row r="1118">
           <cell r="C1118">
-            <v>15304006</v>
+            <v>15201003</v>
           </cell>
         </row>
         <row r="1119">
           <cell r="C1119">
-            <v>15305001</v>
+            <v>15201004</v>
           </cell>
         </row>
         <row r="1120">
           <cell r="C1120">
-            <v>15305002</v>
+            <v>15201005</v>
           </cell>
         </row>
         <row r="1121">
           <cell r="C1121">
-            <v>15305003</v>
+            <v>15201006</v>
           </cell>
         </row>
         <row r="1122">
           <cell r="C1122">
-            <v>15305004</v>
+            <v>15202001</v>
           </cell>
         </row>
         <row r="1123">
           <cell r="C1123">
-            <v>15305005</v>
+            <v>15202002</v>
           </cell>
         </row>
         <row r="1124">
           <cell r="C1124">
-            <v>15305006</v>
+            <v>15202003</v>
           </cell>
         </row>
         <row r="1125">
           <cell r="C1125">
-            <v>15306001</v>
+            <v>15202004</v>
           </cell>
         </row>
         <row r="1126">
           <cell r="C1126">
-            <v>15306002</v>
+            <v>15202005</v>
           </cell>
         </row>
         <row r="1127">
           <cell r="C1127">
-            <v>15306003</v>
+            <v>15202006</v>
           </cell>
         </row>
         <row r="1128">
           <cell r="C1128">
-            <v>15307001</v>
+            <v>15203001</v>
           </cell>
         </row>
         <row r="1129">
           <cell r="C1129">
-            <v>15307002</v>
+            <v>15203002</v>
           </cell>
         </row>
         <row r="1130">
           <cell r="C1130">
-            <v>15308001</v>
-          </cell>
-          <cell r="S1130">
-            <v>66001006</v>
+            <v>15203003</v>
           </cell>
         </row>
         <row r="1131">
           <cell r="C1131">
-            <v>15308002</v>
-          </cell>
-          <cell r="S1131">
-            <v>66001007</v>
+            <v>15203004</v>
           </cell>
         </row>
         <row r="1132">
           <cell r="C1132">
-            <v>15308003</v>
-          </cell>
-          <cell r="S1132">
-            <v>66001014</v>
+            <v>15203005</v>
           </cell>
         </row>
         <row r="1133">
           <cell r="C1133">
-            <v>15308004</v>
-          </cell>
-          <cell r="S1133">
-            <v>66001017</v>
+            <v>15203006</v>
           </cell>
         </row>
         <row r="1134">
           <cell r="C1134">
-            <v>15309001</v>
+            <v>15204001</v>
           </cell>
         </row>
         <row r="1135">
           <cell r="C1135">
-            <v>15309002</v>
+            <v>15204002</v>
           </cell>
         </row>
         <row r="1136">
           <cell r="C1136">
-            <v>15309003</v>
+            <v>15204003</v>
           </cell>
         </row>
         <row r="1137">
           <cell r="C1137">
-            <v>15310001</v>
+            <v>15204004</v>
           </cell>
         </row>
         <row r="1138">
           <cell r="C1138">
-            <v>15310002</v>
+            <v>15204005</v>
           </cell>
         </row>
         <row r="1139">
           <cell r="C1139">
-            <v>15310003</v>
+            <v>15204006</v>
           </cell>
         </row>
         <row r="1140">
           <cell r="C1140">
-            <v>15310004</v>
+            <v>15205001</v>
           </cell>
         </row>
         <row r="1141">
           <cell r="C1141">
-            <v>15310011</v>
-          </cell>
-          <cell r="S1141">
-            <v>69000016</v>
+            <v>15205002</v>
           </cell>
         </row>
         <row r="1142">
           <cell r="C1142">
-            <v>15310012</v>
+            <v>15205003</v>
           </cell>
         </row>
         <row r="1143">
           <cell r="C1143">
-            <v>15310101</v>
+            <v>15205004</v>
           </cell>
         </row>
         <row r="1144">
           <cell r="C1144">
-            <v>15310102</v>
+            <v>15205005</v>
           </cell>
         </row>
         <row r="1145">
           <cell r="C1145">
-            <v>15310103</v>
+            <v>15205006</v>
           </cell>
         </row>
         <row r="1146">
           <cell r="C1146">
-            <v>15310104</v>
+            <v>15205007</v>
           </cell>
         </row>
         <row r="1147">
           <cell r="C1147">
-            <v>15310111</v>
-          </cell>
-          <cell r="S1147">
-            <v>69000018</v>
+            <v>15206001</v>
           </cell>
         </row>
         <row r="1148">
           <cell r="C1148">
-            <v>15310112</v>
+            <v>15206002</v>
           </cell>
         </row>
         <row r="1149">
           <cell r="C1149">
-            <v>15310201</v>
+            <v>15206003</v>
           </cell>
         </row>
         <row r="1150">
           <cell r="C1150">
-            <v>15310202</v>
+            <v>15207001</v>
           </cell>
         </row>
         <row r="1151">
           <cell r="C1151">
-            <v>15310211</v>
-          </cell>
-          <cell r="S1151">
-            <v>69000002</v>
+            <v>15207002</v>
           </cell>
         </row>
         <row r="1152">
           <cell r="C1152">
-            <v>15311001</v>
+            <v>15207003</v>
           </cell>
         </row>
         <row r="1153">
           <cell r="C1153">
-            <v>15311002</v>
+            <v>15208001</v>
+          </cell>
+          <cell r="S1153">
+            <v>66001004</v>
           </cell>
         </row>
         <row r="1154">
           <cell r="C1154">
-            <v>15311003</v>
+            <v>15208002</v>
+          </cell>
+          <cell r="S1154">
+            <v>66001005</v>
           </cell>
         </row>
         <row r="1155">
           <cell r="C1155">
-            <v>15311004</v>
+            <v>15208003</v>
+          </cell>
+          <cell r="S1155">
+            <v>66001013</v>
           </cell>
         </row>
         <row r="1156">
           <cell r="C1156">
-            <v>15311005</v>
+            <v>15209001</v>
           </cell>
         </row>
         <row r="1157">
           <cell r="C1157">
-            <v>15311006</v>
+            <v>15209002</v>
           </cell>
         </row>
         <row r="1158">
           <cell r="C1158">
-            <v>15311011</v>
+            <v>15210001</v>
           </cell>
         </row>
         <row r="1159">
           <cell r="C1159">
-            <v>15311012</v>
+            <v>15210002</v>
           </cell>
         </row>
         <row r="1160">
           <cell r="C1160">
-            <v>15311013</v>
-          </cell>
-          <cell r="S1160">
-            <v>69000006</v>
+            <v>15210003</v>
           </cell>
         </row>
         <row r="1161">
           <cell r="C1161">
-            <v>15401001</v>
+            <v>15210004</v>
           </cell>
         </row>
         <row r="1162">
           <cell r="C1162">
-            <v>15401002</v>
+            <v>15210011</v>
+          </cell>
+          <cell r="S1162">
+            <v>69000016</v>
           </cell>
         </row>
         <row r="1163">
           <cell r="C1163">
-            <v>15401003</v>
+            <v>15210012</v>
           </cell>
         </row>
         <row r="1164">
           <cell r="C1164">
-            <v>15401004</v>
+            <v>15210101</v>
           </cell>
         </row>
         <row r="1165">
           <cell r="C1165">
-            <v>15401005</v>
+            <v>15210102</v>
           </cell>
         </row>
         <row r="1166">
           <cell r="C1166">
-            <v>15401006</v>
+            <v>15210103</v>
           </cell>
         </row>
         <row r="1167">
           <cell r="C1167">
-            <v>15401007</v>
+            <v>15210104</v>
           </cell>
         </row>
         <row r="1168">
           <cell r="C1168">
-            <v>15402001</v>
+            <v>15210111</v>
           </cell>
         </row>
         <row r="1169">
           <cell r="C1169">
-            <v>15402002</v>
+            <v>15210112</v>
           </cell>
         </row>
         <row r="1170">
           <cell r="C1170">
-            <v>15402003</v>
+            <v>15210201</v>
           </cell>
         </row>
         <row r="1171">
           <cell r="C1171">
-            <v>15402004</v>
+            <v>15210202</v>
           </cell>
         </row>
         <row r="1172">
           <cell r="C1172">
-            <v>15402005</v>
+            <v>15210211</v>
+          </cell>
+          <cell r="S1172">
+            <v>69000014</v>
           </cell>
         </row>
         <row r="1173">
           <cell r="C1173">
-            <v>15402006</v>
+            <v>15211001</v>
           </cell>
         </row>
         <row r="1174">
           <cell r="C1174">
-            <v>15403001</v>
+            <v>15211002</v>
           </cell>
         </row>
         <row r="1175">
           <cell r="C1175">
-            <v>15403002</v>
+            <v>15211003</v>
           </cell>
         </row>
         <row r="1176">
           <cell r="C1176">
-            <v>15403003</v>
+            <v>15211004</v>
           </cell>
         </row>
         <row r="1177">
           <cell r="C1177">
-            <v>15403004</v>
+            <v>15211005</v>
           </cell>
         </row>
         <row r="1178">
           <cell r="C1178">
-            <v>15403005</v>
+            <v>15211006</v>
           </cell>
         </row>
         <row r="1179">
           <cell r="C1179">
-            <v>15403006</v>
+            <v>15211011</v>
           </cell>
         </row>
         <row r="1180">
           <cell r="C1180">
-            <v>15404001</v>
+            <v>15211012</v>
           </cell>
         </row>
         <row r="1181">
           <cell r="C1181">
-            <v>15404002</v>
+            <v>15211013</v>
+          </cell>
+          <cell r="S1181">
+            <v>69000004</v>
           </cell>
         </row>
         <row r="1182">
           <cell r="C1182">
-            <v>15404003</v>
+            <v>15301001</v>
           </cell>
         </row>
         <row r="1183">
           <cell r="C1183">
-            <v>15404004</v>
+            <v>15301002</v>
           </cell>
         </row>
         <row r="1184">
           <cell r="C1184">
-            <v>15404005</v>
+            <v>15301003</v>
           </cell>
         </row>
         <row r="1185">
           <cell r="C1185">
-            <v>15404006</v>
+            <v>15301004</v>
           </cell>
         </row>
         <row r="1186">
           <cell r="C1186">
-            <v>15405001</v>
+            <v>15301005</v>
           </cell>
         </row>
         <row r="1187">
           <cell r="C1187">
-            <v>15405002</v>
+            <v>15301006</v>
           </cell>
         </row>
         <row r="1188">
           <cell r="C1188">
-            <v>15405003</v>
+            <v>15302001</v>
           </cell>
         </row>
         <row r="1189">
           <cell r="C1189">
-            <v>15405004</v>
+            <v>15302002</v>
           </cell>
         </row>
         <row r="1190">
           <cell r="C1190">
-            <v>15405005</v>
+            <v>15302003</v>
           </cell>
         </row>
         <row r="1191">
           <cell r="C1191">
-            <v>15405006</v>
+            <v>15302004</v>
           </cell>
         </row>
         <row r="1192">
           <cell r="C1192">
-            <v>15406001</v>
+            <v>15302005</v>
           </cell>
         </row>
         <row r="1193">
           <cell r="C1193">
-            <v>15406002</v>
+            <v>15302006</v>
           </cell>
         </row>
         <row r="1194">
           <cell r="C1194">
-            <v>15406003</v>
-          </cell>
-          <cell r="S1194">
-            <v>69000007</v>
+            <v>15302007</v>
           </cell>
         </row>
         <row r="1195">
           <cell r="C1195">
-            <v>15407001</v>
+            <v>15303001</v>
           </cell>
         </row>
         <row r="1196">
           <cell r="C1196">
-            <v>15407002</v>
+            <v>15303002</v>
           </cell>
         </row>
         <row r="1197">
           <cell r="C1197">
-            <v>15407003</v>
+            <v>15303003</v>
           </cell>
         </row>
         <row r="1198">
           <cell r="C1198">
-            <v>15408001</v>
-          </cell>
-          <cell r="S1198">
-            <v>66001008</v>
+            <v>15303004</v>
           </cell>
         </row>
         <row r="1199">
           <cell r="C1199">
-            <v>15408002</v>
-          </cell>
-          <cell r="S1199">
-            <v>66001009</v>
+            <v>15303005</v>
           </cell>
         </row>
         <row r="1200">
           <cell r="C1200">
-            <v>15408003</v>
-          </cell>
-          <cell r="S1200">
-            <v>66001015</v>
+            <v>15303006</v>
           </cell>
         </row>
         <row r="1201">
           <cell r="C1201">
-            <v>15409001</v>
+            <v>15304001</v>
           </cell>
         </row>
         <row r="1202">
           <cell r="C1202">
-            <v>15409002</v>
+            <v>15304002</v>
           </cell>
         </row>
         <row r="1203">
           <cell r="C1203">
-            <v>15410001</v>
+            <v>15304003</v>
           </cell>
         </row>
         <row r="1204">
           <cell r="C1204">
-            <v>15410002</v>
+            <v>15304004</v>
           </cell>
         </row>
         <row r="1205">
           <cell r="C1205">
-            <v>15410003</v>
+            <v>15304005</v>
           </cell>
         </row>
         <row r="1206">
           <cell r="C1206">
-            <v>15410004</v>
+            <v>15304006</v>
           </cell>
         </row>
         <row r="1207">
           <cell r="C1207">
-            <v>15410011</v>
-          </cell>
-          <cell r="S1207" t="str">
-            <v>69000013;69000017</v>
+            <v>15305001</v>
           </cell>
         </row>
         <row r="1208">
           <cell r="C1208">
-            <v>15410012</v>
+            <v>15305002</v>
           </cell>
         </row>
         <row r="1209">
           <cell r="C1209">
-            <v>15410101</v>
+            <v>15305003</v>
           </cell>
         </row>
         <row r="1210">
           <cell r="C1210">
-            <v>15410102</v>
+            <v>15305004</v>
           </cell>
         </row>
         <row r="1211">
           <cell r="C1211">
-            <v>15410103</v>
+            <v>15305005</v>
           </cell>
         </row>
         <row r="1212">
           <cell r="C1212">
-            <v>15410104</v>
+            <v>15305006</v>
           </cell>
         </row>
         <row r="1213">
           <cell r="C1213">
-            <v>15410111</v>
+            <v>15306001</v>
           </cell>
         </row>
         <row r="1214">
           <cell r="C1214">
-            <v>15410112</v>
-          </cell>
-          <cell r="S1214">
-            <v>69000009</v>
+            <v>15306002</v>
           </cell>
         </row>
         <row r="1215">
           <cell r="C1215">
-            <v>15410201</v>
+            <v>15306003</v>
           </cell>
         </row>
         <row r="1216">
           <cell r="C1216">
-            <v>15410202</v>
+            <v>15307001</v>
           </cell>
         </row>
         <row r="1217">
           <cell r="C1217">
-            <v>15410211</v>
+            <v>15307002</v>
           </cell>
         </row>
         <row r="1218">
           <cell r="C1218">
-            <v>15411001</v>
+            <v>15308001</v>
+          </cell>
+          <cell r="S1218">
+            <v>66001006</v>
           </cell>
         </row>
         <row r="1219">
           <cell r="C1219">
-            <v>15411002</v>
+            <v>15308002</v>
+          </cell>
+          <cell r="S1219">
+            <v>66001007</v>
           </cell>
         </row>
         <row r="1220">
           <cell r="C1220">
-            <v>15411003</v>
+            <v>15308003</v>
+          </cell>
+          <cell r="S1220">
+            <v>66001014</v>
           </cell>
         </row>
         <row r="1221">
           <cell r="C1221">
-            <v>15411004</v>
+            <v>15308004</v>
+          </cell>
+          <cell r="S1221">
+            <v>66001017</v>
           </cell>
         </row>
         <row r="1222">
           <cell r="C1222">
-            <v>15411005</v>
+            <v>15309001</v>
           </cell>
         </row>
         <row r="1223">
           <cell r="C1223">
-            <v>15411006</v>
+            <v>15309002</v>
           </cell>
         </row>
         <row r="1224">
           <cell r="C1224">
-            <v>15411011</v>
-          </cell>
-          <cell r="S1224">
-            <v>69000010</v>
+            <v>15309003</v>
           </cell>
         </row>
         <row r="1225">
           <cell r="C1225">
-            <v>15411012</v>
+            <v>15310001</v>
           </cell>
         </row>
         <row r="1226">
           <cell r="C1226">
-            <v>15411013</v>
+            <v>15310002</v>
           </cell>
         </row>
         <row r="1227">
           <cell r="C1227">
-            <v>15501001</v>
+            <v>15310003</v>
           </cell>
         </row>
         <row r="1228">
           <cell r="C1228">
-            <v>15501002</v>
+            <v>15310004</v>
           </cell>
         </row>
         <row r="1229">
           <cell r="C1229">
-            <v>15501003</v>
+            <v>15310011</v>
+          </cell>
+          <cell r="S1229">
+            <v>69000016</v>
           </cell>
         </row>
         <row r="1230">
           <cell r="C1230">
-            <v>15501004</v>
+            <v>15310012</v>
           </cell>
         </row>
         <row r="1231">
           <cell r="C1231">
-            <v>15501005</v>
+            <v>15310101</v>
           </cell>
         </row>
         <row r="1232">
           <cell r="C1232">
-            <v>15501006</v>
+            <v>15310102</v>
           </cell>
         </row>
         <row r="1233">
           <cell r="C1233">
-            <v>15502001</v>
+            <v>15310103</v>
           </cell>
         </row>
         <row r="1234">
           <cell r="C1234">
-            <v>15502002</v>
+            <v>15310104</v>
           </cell>
         </row>
         <row r="1235">
           <cell r="C1235">
-            <v>15502003</v>
+            <v>15310111</v>
+          </cell>
+          <cell r="S1235">
+            <v>69000018</v>
           </cell>
         </row>
         <row r="1236">
           <cell r="C1236">
-            <v>15502004</v>
+            <v>15310112</v>
           </cell>
         </row>
         <row r="1237">
           <cell r="C1237">
-            <v>15502005</v>
+            <v>15310201</v>
           </cell>
         </row>
         <row r="1238">
           <cell r="C1238">
-            <v>15502006</v>
+            <v>15310202</v>
           </cell>
         </row>
         <row r="1239">
           <cell r="C1239">
-            <v>15503001</v>
+            <v>15310211</v>
+          </cell>
+          <cell r="S1239">
+            <v>69000002</v>
           </cell>
         </row>
         <row r="1240">
           <cell r="C1240">
-            <v>15503002</v>
+            <v>15311001</v>
           </cell>
         </row>
         <row r="1241">
           <cell r="C1241">
-            <v>15503003</v>
+            <v>15311002</v>
           </cell>
         </row>
         <row r="1242">
           <cell r="C1242">
-            <v>15503004</v>
+            <v>15311003</v>
           </cell>
         </row>
         <row r="1243">
           <cell r="C1243">
-            <v>15503005</v>
+            <v>15311004</v>
           </cell>
         </row>
         <row r="1244">
           <cell r="C1244">
-            <v>15503006</v>
+            <v>15311005</v>
           </cell>
         </row>
         <row r="1245">
           <cell r="C1245">
-            <v>15503007</v>
+            <v>15311006</v>
           </cell>
         </row>
         <row r="1246">
           <cell r="C1246">
-            <v>15504001</v>
+            <v>15311011</v>
           </cell>
         </row>
         <row r="1247">
           <cell r="C1247">
-            <v>15504002</v>
+            <v>15311012</v>
           </cell>
         </row>
         <row r="1248">
           <cell r="C1248">
-            <v>15504003</v>
+            <v>15311013</v>
+          </cell>
+          <cell r="S1248">
+            <v>69000006</v>
           </cell>
         </row>
         <row r="1249">
           <cell r="C1249">
-            <v>15504004</v>
+            <v>15401001</v>
           </cell>
         </row>
         <row r="1250">
           <cell r="C1250">
-            <v>15504005</v>
+            <v>15401002</v>
           </cell>
         </row>
         <row r="1251">
           <cell r="C1251">
-            <v>15504006</v>
+            <v>15401003</v>
           </cell>
         </row>
         <row r="1252">
           <cell r="C1252">
-            <v>15505001</v>
+            <v>15401004</v>
           </cell>
         </row>
         <row r="1253">
           <cell r="C1253">
-            <v>15505002</v>
+            <v>15401005</v>
           </cell>
         </row>
         <row r="1254">
           <cell r="C1254">
-            <v>15505003</v>
+            <v>15401006</v>
           </cell>
         </row>
         <row r="1255">
           <cell r="C1255">
-            <v>15505004</v>
+            <v>15401007</v>
           </cell>
         </row>
         <row r="1256">
           <cell r="C1256">
-            <v>15505005</v>
+            <v>15402001</v>
           </cell>
         </row>
         <row r="1257">
           <cell r="C1257">
-            <v>15505006</v>
+            <v>15402002</v>
           </cell>
         </row>
         <row r="1258">
           <cell r="C1258">
-            <v>15506001</v>
+            <v>15402003</v>
           </cell>
         </row>
         <row r="1259">
           <cell r="C1259">
-            <v>15506002</v>
+            <v>15402004</v>
           </cell>
         </row>
         <row r="1260">
           <cell r="C1260">
-            <v>15506003</v>
+            <v>15402005</v>
           </cell>
         </row>
         <row r="1261">
           <cell r="C1261">
-            <v>15507001</v>
+            <v>15402006</v>
           </cell>
         </row>
         <row r="1262">
           <cell r="C1262">
-            <v>15507002</v>
+            <v>15403001</v>
           </cell>
         </row>
         <row r="1263">
           <cell r="C1263">
-            <v>15507003</v>
+            <v>15403002</v>
           </cell>
         </row>
         <row r="1264">
           <cell r="C1264">
-            <v>15508001</v>
-          </cell>
-          <cell r="S1264">
-            <v>66001010</v>
+            <v>15403003</v>
           </cell>
         </row>
         <row r="1265">
           <cell r="C1265">
-            <v>15508002</v>
-          </cell>
-          <cell r="S1265">
-            <v>66001011</v>
+            <v>15403004</v>
           </cell>
         </row>
         <row r="1266">
           <cell r="C1266">
-            <v>15508003</v>
-          </cell>
-          <cell r="S1266">
-            <v>66001016</v>
+            <v>15403005</v>
           </cell>
         </row>
         <row r="1267">
           <cell r="C1267">
-            <v>15509001</v>
+            <v>15403006</v>
           </cell>
         </row>
         <row r="1268">
           <cell r="C1268">
-            <v>15509002</v>
+            <v>15404001</v>
           </cell>
         </row>
         <row r="1269">
           <cell r="C1269">
-            <v>15509003</v>
+            <v>15404002</v>
           </cell>
         </row>
         <row r="1270">
           <cell r="C1270">
-            <v>15510001</v>
+            <v>15404003</v>
           </cell>
         </row>
         <row r="1271">
           <cell r="C1271">
-            <v>15510002</v>
+            <v>15404004</v>
           </cell>
         </row>
         <row r="1272">
           <cell r="C1272">
-            <v>15510003</v>
+            <v>15404005</v>
           </cell>
         </row>
         <row r="1273">
           <cell r="C1273">
-            <v>15510004</v>
+            <v>15404006</v>
           </cell>
         </row>
         <row r="1274">
           <cell r="C1274">
-            <v>15510011</v>
+            <v>15405001</v>
           </cell>
         </row>
         <row r="1275">
           <cell r="C1275">
-            <v>15510012</v>
+            <v>15405002</v>
           </cell>
         </row>
         <row r="1276">
           <cell r="C1276">
-            <v>15510101</v>
+            <v>15405003</v>
           </cell>
         </row>
         <row r="1277">
           <cell r="C1277">
-            <v>15510102</v>
+            <v>15405004</v>
           </cell>
         </row>
         <row r="1278">
           <cell r="C1278">
-            <v>15510103</v>
+            <v>15405005</v>
           </cell>
         </row>
         <row r="1279">
           <cell r="C1279">
-            <v>15510104</v>
+            <v>15405006</v>
           </cell>
         </row>
         <row r="1280">
           <cell r="C1280">
-            <v>15510121</v>
-          </cell>
-          <cell r="S1280">
-            <v>69000011</v>
+            <v>15406001</v>
           </cell>
         </row>
         <row r="1281">
           <cell r="C1281">
-            <v>15510122</v>
+            <v>15406002</v>
           </cell>
         </row>
         <row r="1282">
           <cell r="C1282">
-            <v>15510201</v>
+            <v>15406003</v>
+          </cell>
+          <cell r="S1282">
+            <v>69000007</v>
           </cell>
         </row>
         <row r="1283">
           <cell r="C1283">
-            <v>15510202</v>
+            <v>15407001</v>
           </cell>
         </row>
         <row r="1284">
           <cell r="C1284">
-            <v>15510211</v>
+            <v>15407002</v>
           </cell>
         </row>
         <row r="1285">
           <cell r="C1285">
-            <v>15511001</v>
+            <v>15407003</v>
           </cell>
         </row>
         <row r="1286">
           <cell r="C1286">
-            <v>15511002</v>
+            <v>15408001</v>
+          </cell>
+          <cell r="S1286">
+            <v>66001008</v>
           </cell>
         </row>
         <row r="1287">
           <cell r="C1287">
-            <v>15511003</v>
+            <v>15408002</v>
+          </cell>
+          <cell r="S1287">
+            <v>66001009</v>
           </cell>
         </row>
         <row r="1288">
           <cell r="C1288">
-            <v>15511004</v>
+            <v>15408003</v>
+          </cell>
+          <cell r="S1288">
+            <v>66001015</v>
           </cell>
         </row>
         <row r="1289">
           <cell r="C1289">
-            <v>15511005</v>
+            <v>15409001</v>
           </cell>
         </row>
         <row r="1290">
           <cell r="C1290">
-            <v>15511006</v>
+            <v>15409002</v>
           </cell>
         </row>
         <row r="1291">
           <cell r="C1291">
-            <v>15511011</v>
-          </cell>
-          <cell r="S1291">
-            <v>69000012</v>
+            <v>15410001</v>
           </cell>
         </row>
         <row r="1292">
           <cell r="C1292">
-            <v>15511012</v>
+            <v>15410002</v>
           </cell>
         </row>
         <row r="1293">
           <cell r="C1293">
-            <v>15511013</v>
+            <v>15410003</v>
           </cell>
         </row>
         <row r="1294">
           <cell r="C1294">
-            <v>15601001</v>
+            <v>15410004</v>
           </cell>
         </row>
         <row r="1295">
           <cell r="C1295">
-            <v>15601002</v>
+            <v>15410011</v>
+          </cell>
+          <cell r="S1295" t="str">
+            <v>69000013;69000017</v>
           </cell>
         </row>
         <row r="1296">
           <cell r="C1296">
-            <v>15601003</v>
+            <v>15410012</v>
           </cell>
         </row>
         <row r="1297">
           <cell r="C1297">
-            <v>15602001</v>
+            <v>15410101</v>
           </cell>
         </row>
         <row r="1298">
           <cell r="C1298">
-            <v>15602002</v>
+            <v>15410102</v>
           </cell>
         </row>
         <row r="1299">
           <cell r="C1299">
-            <v>15602003</v>
+            <v>15410103</v>
           </cell>
         </row>
         <row r="1300">
           <cell r="C1300">
-            <v>15603001</v>
+            <v>15410104</v>
           </cell>
         </row>
         <row r="1301">
           <cell r="C1301">
-            <v>15603002</v>
+            <v>15410111</v>
           </cell>
         </row>
         <row r="1302">
           <cell r="C1302">
-            <v>15603003</v>
+            <v>15410112</v>
+          </cell>
+          <cell r="S1302">
+            <v>69000009</v>
           </cell>
         </row>
         <row r="1303">
           <cell r="C1303">
-            <v>15604001</v>
+            <v>15410201</v>
           </cell>
         </row>
         <row r="1304">
           <cell r="C1304">
-            <v>15604002</v>
+            <v>15410202</v>
           </cell>
         </row>
         <row r="1305">
           <cell r="C1305">
-            <v>15604003</v>
+            <v>15410211</v>
           </cell>
         </row>
         <row r="1306">
           <cell r="C1306">
-            <v>15605001</v>
+            <v>15411001</v>
           </cell>
         </row>
         <row r="1307">
           <cell r="C1307">
-            <v>15605002</v>
+            <v>15411002</v>
           </cell>
         </row>
         <row r="1308">
           <cell r="C1308">
-            <v>15605003</v>
+            <v>15411003</v>
           </cell>
         </row>
         <row r="1309">
           <cell r="C1309">
-            <v>15606001</v>
+            <v>15411004</v>
           </cell>
         </row>
         <row r="1310">
           <cell r="C1310">
-            <v>15607001</v>
+            <v>15411005</v>
           </cell>
         </row>
         <row r="1311">
           <cell r="C1311">
-            <v>15608001</v>
-          </cell>
-          <cell r="S1311">
-            <v>66001011</v>
+            <v>15411006</v>
           </cell>
         </row>
         <row r="1312">
           <cell r="C1312">
-            <v>15609001</v>
+            <v>15411011</v>
+          </cell>
+          <cell r="S1312">
+            <v>69000010</v>
           </cell>
         </row>
         <row r="1313">
           <cell r="C1313">
-            <v>15610001</v>
+            <v>15411012</v>
           </cell>
         </row>
         <row r="1314">
           <cell r="C1314">
-            <v>15610002</v>
+            <v>15411013</v>
           </cell>
         </row>
         <row r="1315">
           <cell r="C1315">
-            <v>15610101</v>
+            <v>15501001</v>
           </cell>
         </row>
         <row r="1316">
           <cell r="C1316">
-            <v>15610102</v>
+            <v>15501002</v>
           </cell>
         </row>
         <row r="1317">
           <cell r="C1317">
-            <v>15610201</v>
+            <v>15501003</v>
           </cell>
         </row>
         <row r="1318">
           <cell r="C1318">
-            <v>15611001</v>
+            <v>15501004</v>
           </cell>
         </row>
         <row r="1319">
           <cell r="C1319">
-            <v>15611002</v>
+            <v>15501005</v>
           </cell>
         </row>
         <row r="1320">
           <cell r="C1320">
-            <v>15611003</v>
+            <v>15501006</v>
           </cell>
         </row>
         <row r="1321">
           <cell r="C1321">
-            <v>15701001</v>
+            <v>15502001</v>
           </cell>
         </row>
         <row r="1322">
           <cell r="C1322">
-            <v>15701002</v>
+            <v>15502002</v>
           </cell>
         </row>
         <row r="1323">
           <cell r="C1323">
-            <v>15701003</v>
+            <v>15502003</v>
           </cell>
         </row>
         <row r="1324">
           <cell r="C1324">
-            <v>15702001</v>
+            <v>15502004</v>
           </cell>
         </row>
         <row r="1325">
           <cell r="C1325">
-            <v>15702002</v>
+            <v>15502005</v>
           </cell>
         </row>
         <row r="1326">
           <cell r="C1326">
-            <v>15702003</v>
+            <v>15502006</v>
           </cell>
         </row>
         <row r="1327">
           <cell r="C1327">
-            <v>15703001</v>
+            <v>15503001</v>
           </cell>
         </row>
         <row r="1328">
           <cell r="C1328">
-            <v>15703002</v>
+            <v>15503002</v>
           </cell>
         </row>
         <row r="1329">
           <cell r="C1329">
-            <v>15703003</v>
+            <v>15503003</v>
           </cell>
         </row>
         <row r="1330">
           <cell r="C1330">
-            <v>15704001</v>
+            <v>15503004</v>
           </cell>
         </row>
         <row r="1331">
           <cell r="C1331">
-            <v>15704002</v>
+            <v>15503005</v>
           </cell>
         </row>
         <row r="1332">
           <cell r="C1332">
-            <v>15704003</v>
+            <v>15503006</v>
           </cell>
         </row>
         <row r="1333">
           <cell r="C1333">
-            <v>15705001</v>
-          </cell>
-        </row>
-        <row r="1334">
-          <cell r="C1334">
-            <v>15705002</v>
-          </cell>
-        </row>
-        <row r="1335">
-          <cell r="C1335">
-            <v>15705003</v>
+            <v>15503007</v>
           </cell>
         </row>
       </sheetData>
@@ -34337,6 +34490,1342 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B442FB8B-835F-4FE6-873D-08A9F0AA61FD}">
+  <dimension ref="A1:V45"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1">
+        <f>H2*7.5</f>
+        <v>1500</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1">
+        <f>$C2*总表!E$4</f>
+        <v>200</v>
+      </c>
+      <c r="I2" s="1">
+        <f>H2</f>
+        <v>200</v>
+      </c>
+      <c r="J2" s="1">
+        <f>H2</f>
+        <v>200</v>
+      </c>
+      <c r="K2" s="1">
+        <f>H2*3</f>
+        <v>600</v>
+      </c>
+      <c r="N2" s="116" t="s">
+        <v>2896</v>
+      </c>
+      <c r="R2" s="116" t="s">
+        <v>2911</v>
+      </c>
+      <c r="V2" s="116" t="s">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D11" si="0">H3*7.5</f>
+        <v>2625</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1">
+        <f>$C3*总表!E$4</f>
+        <v>350</v>
+      </c>
+      <c r="I3" s="1">
+        <f t="shared" ref="I3:I11" si="1">H3</f>
+        <v>350</v>
+      </c>
+      <c r="J3" s="1">
+        <f t="shared" ref="J3:J11" si="2">H3</f>
+        <v>350</v>
+      </c>
+      <c r="K3" s="1">
+        <f t="shared" ref="K3:K11" si="3">H3*3</f>
+        <v>1050</v>
+      </c>
+      <c r="N3" s="116" t="s">
+        <v>2897</v>
+      </c>
+      <c r="R3" s="116" t="s">
+        <v>2912</v>
+      </c>
+      <c r="V3" s="116" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="C4" s="1">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>3750</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1">
+        <f>$C4*总表!E$4</f>
+        <v>500</v>
+      </c>
+      <c r="I4" s="1">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J4" s="1">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="K4" s="1">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+      <c r="N4" s="116" t="s">
+        <v>2898</v>
+      </c>
+      <c r="R4" s="116" t="s">
+        <v>2913</v>
+      </c>
+      <c r="V4" s="116" t="s">
+        <v>2928</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>4875</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1">
+        <f>$C5*总表!E$4</f>
+        <v>650</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" si="1"/>
+        <v>650</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" si="2"/>
+        <v>650</v>
+      </c>
+      <c r="K5" s="1">
+        <f t="shared" si="3"/>
+        <v>1950</v>
+      </c>
+      <c r="N5" s="116" t="s">
+        <v>2899</v>
+      </c>
+      <c r="R5" s="116" t="s">
+        <v>2914</v>
+      </c>
+      <c r="V5" s="116" t="s">
+        <v>2929</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3.75</v>
+      </c>
+      <c r="C6" s="1">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1">
+        <f>$C6*总表!E$4</f>
+        <v>800</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" si="2"/>
+        <v>800</v>
+      </c>
+      <c r="K6" s="1">
+        <f t="shared" si="3"/>
+        <v>2400</v>
+      </c>
+      <c r="N6" s="116" t="s">
+        <v>2900</v>
+      </c>
+      <c r="R6" s="116" t="s">
+        <v>2915</v>
+      </c>
+      <c r="V6" s="116" t="s">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
+        <v>7500</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1">
+        <f>$C7*总表!E$4</f>
+        <v>1000</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="K7" s="1">
+        <f t="shared" si="3"/>
+        <v>3000</v>
+      </c>
+      <c r="N7" s="116" t="s">
+        <v>2901</v>
+      </c>
+      <c r="R7" s="116" t="s">
+        <v>2916</v>
+      </c>
+      <c r="V7" s="116" t="s">
+        <v>2931</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="C8" s="1">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>9000</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
+        <f>$C8*总表!E$4</f>
+        <v>1200</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="1"/>
+        <v>1200</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="2"/>
+        <v>1200</v>
+      </c>
+      <c r="K8" s="1">
+        <f t="shared" si="3"/>
+        <v>3600</v>
+      </c>
+      <c r="N8" s="116" t="s">
+        <v>2902</v>
+      </c>
+      <c r="R8" s="116" t="s">
+        <v>2917</v>
+      </c>
+      <c r="V8" s="116" t="s">
+        <v>2932</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>10500</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
+        <f>$C9*总表!E$4</f>
+        <v>1400</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="1"/>
+        <v>1400</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="2"/>
+        <v>1400</v>
+      </c>
+      <c r="K9" s="1">
+        <f t="shared" si="3"/>
+        <v>4200</v>
+      </c>
+      <c r="N9" s="116" t="s">
+        <v>2903</v>
+      </c>
+      <c r="R9" s="116" t="s">
+        <v>2918</v>
+      </c>
+      <c r="V9" s="116" t="s">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>6.75</v>
+      </c>
+      <c r="C10" s="1">
+        <v>17</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>12750</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
+        <f>$C10*总表!E$4</f>
+        <v>1700</v>
+      </c>
+      <c r="I10" s="1">
+        <f t="shared" si="1"/>
+        <v>1700</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="2"/>
+        <v>1700</v>
+      </c>
+      <c r="K10" s="1">
+        <f t="shared" si="3"/>
+        <v>5100</v>
+      </c>
+      <c r="N10" s="116" t="s">
+        <v>2904</v>
+      </c>
+      <c r="R10" s="116" t="s">
+        <v>2919</v>
+      </c>
+      <c r="V10" s="116" t="s">
+        <v>2934</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1">
+        <f>$C11*总表!E$4</f>
+        <v>2000</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="2"/>
+        <v>2000</v>
+      </c>
+      <c r="K11" s="1">
+        <f t="shared" si="3"/>
+        <v>6000</v>
+      </c>
+      <c r="N11" s="116" t="s">
+        <v>2905</v>
+      </c>
+      <c r="R11" s="116" t="s">
+        <v>2920</v>
+      </c>
+      <c r="V11" s="116" t="s">
+        <v>2935</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="N12" s="51" t="s">
+        <v>2906</v>
+      </c>
+      <c r="R12" s="51" t="s">
+        <v>2921</v>
+      </c>
+      <c r="V12" s="51" t="s">
+        <v>2936</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="N13" s="51" t="s">
+        <v>2907</v>
+      </c>
+      <c r="R13" s="51" t="s">
+        <v>2922</v>
+      </c>
+      <c r="V13" s="51" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="N14" s="51" t="s">
+        <v>2908</v>
+      </c>
+      <c r="R14" s="51" t="s">
+        <v>2923</v>
+      </c>
+      <c r="V14" s="51" t="s">
+        <v>2938</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="N15" s="51" t="s">
+        <v>2909</v>
+      </c>
+      <c r="R15" s="51" t="s">
+        <v>2924</v>
+      </c>
+      <c r="V15" s="51" t="s">
+        <v>2939</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="20.100000000000001" customHeight="1">
+      <c r="N16" s="51" t="s">
+        <v>2910</v>
+      </c>
+      <c r="R16" s="51" t="s">
+        <v>2925</v>
+      </c>
+      <c r="V16" s="51" t="s">
+        <v>2940</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1"/>
+    <row r="18" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1"/>
+    <row r="19" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B19" s="1" t="s">
+        <v>2946</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>2943</v>
+      </c>
+      <c r="J19" s="1">
+        <v>60</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>2948</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B20" s="1" t="s">
+        <v>2941</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="1" t="s">
+        <v>2947</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>2945</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="J22" s="1">
+        <f>5*70</f>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="J23" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="E24" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="1">
+        <f>C25*0.3</f>
+        <v>36</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1">
+        <v>120</v>
+      </c>
+      <c r="D25" s="1">
+        <f>C25/4</f>
+        <v>30</v>
+      </c>
+      <c r="E25" s="1">
+        <f>D25/3</f>
+        <v>10</v>
+      </c>
+      <c r="F25" s="1">
+        <f>D25*$F$24</f>
+        <v>7.5</v>
+      </c>
+      <c r="G25" s="1">
+        <f>D25*$G$24</f>
+        <v>15</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>2949</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A26" s="1">
+        <f t="shared" ref="A26:A29" si="4">C26*0.3</f>
+        <v>54</v>
+      </c>
+      <c r="B26" s="1">
+        <v>2</v>
+      </c>
+      <c r="C26" s="1">
+        <f>C25+60</f>
+        <v>180</v>
+      </c>
+      <c r="D26" s="1">
+        <f t="shared" ref="D26:D29" si="5">C26/4</f>
+        <v>45</v>
+      </c>
+      <c r="E26" s="1">
+        <f t="shared" ref="E26:E29" si="6">D26/3</f>
+        <v>15</v>
+      </c>
+      <c r="F26" s="1">
+        <f t="shared" ref="F26:F29" si="7">D26*$F$24</f>
+        <v>11.25</v>
+      </c>
+      <c r="G26" s="1">
+        <f t="shared" ref="G26:G29" si="8">D26*$G$24</f>
+        <v>22.5</v>
+      </c>
+      <c r="H26" s="1">
+        <v>10</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>2946</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L26" s="1">
+        <v>8</v>
+      </c>
+      <c r="M26" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>2943</v>
+      </c>
+      <c r="O26" s="1">
+        <v>30</v>
+      </c>
+      <c r="P26" s="1">
+        <v>105103</v>
+      </c>
+      <c r="R26" s="1" t="str">
+        <f>M26&amp;","&amp;P26</f>
+        <v>105503,105103</v>
+      </c>
+      <c r="T26" s="1" t="str">
+        <f>L26&amp;","&amp;O26</f>
+        <v>8,30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A27" s="1">
+        <f t="shared" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="B27" s="1">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1">
+        <f t="shared" ref="C27:C29" si="9">C26+60</f>
+        <v>240</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" si="5"/>
+        <v>60</v>
+      </c>
+      <c r="E27" s="1">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="G27" s="1">
+        <f t="shared" si="8"/>
+        <v>30</v>
+      </c>
+      <c r="I27" s="1">
+        <v>2</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>2941</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L27" s="1">
+        <v>8</v>
+      </c>
+      <c r="M27" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>2944</v>
+      </c>
+      <c r="O27" s="1">
+        <v>30</v>
+      </c>
+      <c r="P27" s="1">
+        <v>105303</v>
+      </c>
+      <c r="R27" s="1" t="str">
+        <f t="shared" ref="R27:R40" si="10">M27&amp;","&amp;P27</f>
+        <v>105503,105303</v>
+      </c>
+      <c r="T27" s="1" t="str">
+        <f t="shared" ref="T27:T40" si="11">L27&amp;","&amp;O27</f>
+        <v>8,30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A28" s="1">
+        <f t="shared" si="4"/>
+        <v>90</v>
+      </c>
+      <c r="B28" s="1">
+        <v>4</v>
+      </c>
+      <c r="C28" s="1">
+        <f t="shared" si="9"/>
+        <v>300</v>
+      </c>
+      <c r="D28" s="1">
+        <f t="shared" si="5"/>
+        <v>75</v>
+      </c>
+      <c r="E28" s="1">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+      <c r="F28" s="1">
+        <f t="shared" si="7"/>
+        <v>18.75</v>
+      </c>
+      <c r="G28" s="1">
+        <f t="shared" si="8"/>
+        <v>37.5</v>
+      </c>
+      <c r="I28" s="1">
+        <v>3</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>2947</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L28" s="1">
+        <v>16</v>
+      </c>
+      <c r="M28" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>2945</v>
+      </c>
+      <c r="O28" s="1">
+        <v>30</v>
+      </c>
+      <c r="P28" s="1">
+        <v>105403</v>
+      </c>
+      <c r="R28" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>105503,105403</v>
+      </c>
+      <c r="T28" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>16,30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A29" s="1">
+        <f t="shared" si="4"/>
+        <v>108</v>
+      </c>
+      <c r="B29" s="1">
+        <v>5</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="shared" si="9"/>
+        <v>360</v>
+      </c>
+      <c r="D29" s="1">
+        <f t="shared" si="5"/>
+        <v>90</v>
+      </c>
+      <c r="E29" s="1">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+      <c r="F29" s="1">
+        <f t="shared" si="7"/>
+        <v>22.5</v>
+      </c>
+      <c r="G29" s="1">
+        <f t="shared" si="8"/>
+        <v>45</v>
+      </c>
+      <c r="H29" s="1">
+        <v>30</v>
+      </c>
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>2946</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L29" s="1">
+        <v>12</v>
+      </c>
+      <c r="M29" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>2943</v>
+      </c>
+      <c r="O29" s="1">
+        <v>45</v>
+      </c>
+      <c r="P29" s="1">
+        <v>105103</v>
+      </c>
+      <c r="R29" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>105503,105103</v>
+      </c>
+      <c r="T29" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>12,45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I30" s="1">
+        <v>2</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>2941</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L30" s="1">
+        <v>12</v>
+      </c>
+      <c r="M30" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>2944</v>
+      </c>
+      <c r="O30" s="1">
+        <v>45</v>
+      </c>
+      <c r="P30" s="1">
+        <v>105303</v>
+      </c>
+      <c r="R30" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>105503,105303</v>
+      </c>
+      <c r="T30" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>12,45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A31" s="1">
+        <f>A25/4</f>
+        <v>9</v>
+      </c>
+      <c r="B31" s="1">
+        <v>12</v>
+      </c>
+      <c r="C31" s="1">
+        <f>B31/A31</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E31" s="1">
+        <v>10</v>
+      </c>
+      <c r="I31" s="1">
+        <v>3</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>2947</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L31" s="1">
+        <v>24</v>
+      </c>
+      <c r="M31" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>2945</v>
+      </c>
+      <c r="O31" s="1">
+        <v>45</v>
+      </c>
+      <c r="P31" s="1">
+        <v>105403</v>
+      </c>
+      <c r="R31" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>105503,105403</v>
+      </c>
+      <c r="T31" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>24,45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A32" s="1">
+        <f t="shared" ref="A32:A35" si="12">A26/4</f>
+        <v>13.5</v>
+      </c>
+      <c r="B32" s="1">
+        <v>30</v>
+      </c>
+      <c r="C32" s="1">
+        <f>B32/A32</f>
+        <v>2.2222222222222223</v>
+      </c>
+      <c r="E32" s="1">
+        <v>15</v>
+      </c>
+      <c r="H32" s="1">
+        <v>40</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>2946</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L32" s="1">
+        <v>16</v>
+      </c>
+      <c r="M32" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>2943</v>
+      </c>
+      <c r="O32" s="1">
+        <v>60</v>
+      </c>
+      <c r="P32" s="1">
+        <v>105103</v>
+      </c>
+      <c r="R32" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>105503,105103</v>
+      </c>
+      <c r="T32" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>16,60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A33" s="1">
+        <f t="shared" si="12"/>
+        <v>18</v>
+      </c>
+      <c r="B33" s="1">
+        <v>40</v>
+      </c>
+      <c r="C33" s="1">
+        <f>B33/A33</f>
+        <v>2.2222222222222223</v>
+      </c>
+      <c r="E33" s="1">
+        <v>20</v>
+      </c>
+      <c r="I33" s="1">
+        <v>2</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>2941</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L33" s="1">
+        <v>16</v>
+      </c>
+      <c r="M33" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>2944</v>
+      </c>
+      <c r="O33" s="1">
+        <v>60</v>
+      </c>
+      <c r="P33" s="1">
+        <v>105303</v>
+      </c>
+      <c r="R33" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>105503,105303</v>
+      </c>
+      <c r="T33" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>16,60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A34" s="1">
+        <f t="shared" si="12"/>
+        <v>22.5</v>
+      </c>
+      <c r="B34" s="1">
+        <v>50</v>
+      </c>
+      <c r="C34" s="1">
+        <f>B34/A34</f>
+        <v>2.2222222222222223</v>
+      </c>
+      <c r="E34" s="1">
+        <v>25</v>
+      </c>
+      <c r="I34" s="1">
+        <v>3</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>2947</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L34" s="1">
+        <v>32</v>
+      </c>
+      <c r="M34" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>2945</v>
+      </c>
+      <c r="O34" s="1">
+        <v>60</v>
+      </c>
+      <c r="P34" s="1">
+        <v>105403</v>
+      </c>
+      <c r="R34" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>105503,105403</v>
+      </c>
+      <c r="T34" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>32,60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A35" s="1">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="B35" s="1">
+        <v>55</v>
+      </c>
+      <c r="C35" s="1">
+        <f>B35/A35</f>
+        <v>2.0370370370370372</v>
+      </c>
+      <c r="E35" s="1">
+        <v>30</v>
+      </c>
+      <c r="H35" s="1">
+        <v>50</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>2946</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L35" s="1">
+        <v>20</v>
+      </c>
+      <c r="M35" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>2943</v>
+      </c>
+      <c r="O35" s="1">
+        <v>75</v>
+      </c>
+      <c r="P35" s="1">
+        <v>105103</v>
+      </c>
+      <c r="R35" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>105503,105103</v>
+      </c>
+      <c r="T35" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>20,75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I36" s="1">
+        <v>2</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>2941</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L36" s="1">
+        <v>20</v>
+      </c>
+      <c r="M36" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>2944</v>
+      </c>
+      <c r="O36" s="1">
+        <v>75</v>
+      </c>
+      <c r="P36" s="1">
+        <v>105303</v>
+      </c>
+      <c r="R36" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>105503,105303</v>
+      </c>
+      <c r="T36" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>20,75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I37" s="1">
+        <v>3</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>2947</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L37" s="1">
+        <v>40</v>
+      </c>
+      <c r="M37" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>2945</v>
+      </c>
+      <c r="O37" s="1">
+        <v>75</v>
+      </c>
+      <c r="P37" s="1">
+        <v>105403</v>
+      </c>
+      <c r="R37" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>105503,105403</v>
+      </c>
+      <c r="T37" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>40,75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="H38" s="1">
+        <v>55</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>2946</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L38" s="1">
+        <v>25</v>
+      </c>
+      <c r="M38" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>2943</v>
+      </c>
+      <c r="O38" s="1">
+        <v>90</v>
+      </c>
+      <c r="P38" s="1">
+        <v>105103</v>
+      </c>
+      <c r="R38" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>105503,105103</v>
+      </c>
+      <c r="T38" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>25,90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I39" s="1">
+        <v>2</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>2941</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L39" s="1">
+        <v>25</v>
+      </c>
+      <c r="M39" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>2944</v>
+      </c>
+      <c r="O39" s="1">
+        <v>90</v>
+      </c>
+      <c r="P39" s="1">
+        <v>105303</v>
+      </c>
+      <c r="R39" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>105503,105303</v>
+      </c>
+      <c r="T39" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>25,90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I40" s="1">
+        <v>3</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>2947</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>2942</v>
+      </c>
+      <c r="L40" s="1">
+        <v>50</v>
+      </c>
+      <c r="M40" s="1">
+        <v>105503</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>2945</v>
+      </c>
+      <c r="O40" s="1">
+        <v>90</v>
+      </c>
+      <c r="P40" s="1">
+        <v>105403</v>
+      </c>
+      <c r="R40" s="1" t="str">
+        <f t="shared" si="10"/>
+        <v>105503,105403</v>
+      </c>
+      <c r="T40" s="1" t="str">
+        <f t="shared" si="11"/>
+        <v>50,90</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1"/>
+    <row r="42" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1"/>
+    <row r="43" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1"/>
+    <row r="44" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1"/>
+    <row r="45" spans="1:20" s="1" customFormat="1" ht="20.100000000000001" customHeight="1"/>
+  </sheetData>
+  <phoneticPr fontId="35" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:AV200"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -44642,7 +46131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:U54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -46535,7 +48024,2078 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H71"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="7" width="9" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1">
+        <f>B2*[1]属性总表!$E$5</f>
+        <v>5250</v>
+      </c>
+      <c r="E2" s="1">
+        <f>ROUND([1]等级属性!C2*[1]属性总表!$F$5,0)</f>
+        <v>500</v>
+      </c>
+      <c r="F2" s="1">
+        <f>ROUND(C2*[1]属性总表!$G$5,0)</f>
+        <v>150</v>
+      </c>
+      <c r="G2" s="1">
+        <f>ROUND(C2*[1]属性总表!$H$5,0)</f>
+        <v>150</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <f>B2+0.25</f>
+        <v>5.25</v>
+      </c>
+      <c r="C3" s="1">
+        <f>C2+0.12</f>
+        <v>5.12</v>
+      </c>
+      <c r="D3" s="1">
+        <f>B3*[1]属性总表!$E$5</f>
+        <v>5512.5</v>
+      </c>
+      <c r="E3" s="1">
+        <f>ROUND([1]等级属性!C3*[1]属性总表!$F$5,0)</f>
+        <v>512</v>
+      </c>
+      <c r="F3" s="1">
+        <f>ROUND(C3*[1]属性总表!$G$5,0)</f>
+        <v>154</v>
+      </c>
+      <c r="G3" s="1">
+        <f>ROUND(C3*[1]属性总表!$H$5,0)</f>
+        <v>154</v>
+      </c>
+      <c r="H3" s="1">
+        <f>D3-D2</f>
+        <v>262.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <f t="shared" ref="B4:B67" si="0">B3+0.25</f>
+        <v>5.5</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" ref="C4:C67" si="1">C3+0.12</f>
+        <v>5.24</v>
+      </c>
+      <c r="D4" s="1">
+        <f>B4*[1]属性总表!$E$5</f>
+        <v>5775</v>
+      </c>
+      <c r="E4" s="1">
+        <f>ROUND([1]等级属性!C4*[1]属性总表!$F$5,0)</f>
+        <v>524</v>
+      </c>
+      <c r="F4" s="1">
+        <f>ROUND(C4*[1]属性总表!$G$5,0)</f>
+        <v>157</v>
+      </c>
+      <c r="G4" s="1">
+        <f>ROUND(C4*[1]属性总表!$H$5,0)</f>
+        <v>157</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <f t="shared" si="0"/>
+        <v>5.75</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="1"/>
+        <v>5.36</v>
+      </c>
+      <c r="D5" s="1">
+        <f>B5*[1]属性总表!$E$5</f>
+        <v>6037.5</v>
+      </c>
+      <c r="E5" s="1">
+        <f>ROUND([1]等级属性!C5*[1]属性总表!$F$5,0)</f>
+        <v>536</v>
+      </c>
+      <c r="F5" s="1">
+        <f>ROUND(C5*[1]属性总表!$G$5,0)</f>
+        <v>161</v>
+      </c>
+      <c r="G5" s="1">
+        <f>ROUND(C5*[1]属性总表!$H$5,0)</f>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="1"/>
+        <v>5.48</v>
+      </c>
+      <c r="D6" s="1">
+        <f>B6*[1]属性总表!$E$5</f>
+        <v>6300</v>
+      </c>
+      <c r="E6" s="1">
+        <f>ROUND([1]等级属性!C6*[1]属性总表!$F$5,0)</f>
+        <v>548</v>
+      </c>
+      <c r="F6" s="1">
+        <f>ROUND(C6*[1]属性总表!$G$5,0)</f>
+        <v>164</v>
+      </c>
+      <c r="G6" s="1">
+        <f>ROUND(C6*[1]属性总表!$H$5,0)</f>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <f t="shared" si="0"/>
+        <v>6.25</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
+      </c>
+      <c r="D7" s="1">
+        <f>B7*[1]属性总表!$E$5</f>
+        <v>6562.5</v>
+      </c>
+      <c r="E7" s="1">
+        <f>ROUND([1]等级属性!C7*[1]属性总表!$F$5,0)</f>
+        <v>560</v>
+      </c>
+      <c r="F7" s="1">
+        <f>ROUND(C7*[1]属性总表!$G$5,0)</f>
+        <v>168</v>
+      </c>
+      <c r="G7" s="1">
+        <f>ROUND(C7*[1]属性总表!$H$5,0)</f>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="1"/>
+        <v>5.7200000000000006</v>
+      </c>
+      <c r="D8" s="1">
+        <f>B8*[1]属性总表!$E$5</f>
+        <v>6825</v>
+      </c>
+      <c r="E8" s="1">
+        <f>ROUND([1]等级属性!C8*[1]属性总表!$F$5,0)</f>
+        <v>572</v>
+      </c>
+      <c r="F8" s="1">
+        <f>ROUND(C8*[1]属性总表!$G$5,0)</f>
+        <v>172</v>
+      </c>
+      <c r="G8" s="1">
+        <f>ROUND(C8*[1]属性总表!$H$5,0)</f>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <f t="shared" si="0"/>
+        <v>6.75</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="1"/>
+        <v>5.8400000000000007</v>
+      </c>
+      <c r="D9" s="1">
+        <f>B9*[1]属性总表!$E$5</f>
+        <v>7087.5</v>
+      </c>
+      <c r="E9" s="1">
+        <f>ROUND([1]等级属性!C9*[1]属性总表!$F$5,0)</f>
+        <v>584</v>
+      </c>
+      <c r="F9" s="1">
+        <f>ROUND(C9*[1]属性总表!$G$5,0)</f>
+        <v>175</v>
+      </c>
+      <c r="G9" s="1">
+        <f>ROUND(C9*[1]属性总表!$H$5,0)</f>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" si="1"/>
+        <v>5.9600000000000009</v>
+      </c>
+      <c r="D10" s="1">
+        <f>B10*[1]属性总表!$E$5</f>
+        <v>7350</v>
+      </c>
+      <c r="E10" s="1">
+        <f>ROUND([1]等级属性!C10*[1]属性总表!$F$5,0)</f>
+        <v>596</v>
+      </c>
+      <c r="F10" s="1">
+        <f>ROUND(C10*[1]属性总表!$G$5,0)</f>
+        <v>179</v>
+      </c>
+      <c r="G10" s="1">
+        <f>ROUND(C10*[1]属性总表!$H$5,0)</f>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <f t="shared" si="0"/>
+        <v>7.25</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" si="1"/>
+        <v>6.080000000000001</v>
+      </c>
+      <c r="D11" s="1">
+        <f>B11*[1]属性总表!$E$5</f>
+        <v>7612.5</v>
+      </c>
+      <c r="E11" s="1">
+        <f>ROUND([1]等级属性!C11*[1]属性总表!$F$5,0)</f>
+        <v>608</v>
+      </c>
+      <c r="F11" s="1">
+        <f>ROUND(C11*[1]属性总表!$G$5,0)</f>
+        <v>182</v>
+      </c>
+      <c r="G11" s="1">
+        <f>ROUND(C11*[1]属性总表!$H$5,0)</f>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" si="1"/>
+        <v>6.2000000000000011</v>
+      </c>
+      <c r="D12" s="1">
+        <f>B12*[1]属性总表!$E$5</f>
+        <v>7875</v>
+      </c>
+      <c r="E12" s="1">
+        <f>ROUND([1]等级属性!C12*[1]属性总表!$F$5,0)</f>
+        <v>620</v>
+      </c>
+      <c r="F12" s="1">
+        <f>ROUND(C12*[1]属性总表!$G$5,0)</f>
+        <v>186</v>
+      </c>
+      <c r="G12" s="1">
+        <f>ROUND(C12*[1]属性总表!$H$5,0)</f>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <f t="shared" si="0"/>
+        <v>7.75</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" si="1"/>
+        <v>6.3200000000000012</v>
+      </c>
+      <c r="D13" s="1">
+        <f>B13*[1]属性总表!$E$5</f>
+        <v>8137.5</v>
+      </c>
+      <c r="E13" s="1">
+        <f>ROUND([1]等级属性!C13*[1]属性总表!$F$5,0)</f>
+        <v>632</v>
+      </c>
+      <c r="F13" s="1">
+        <f>ROUND(C13*[1]属性总表!$G$5,0)</f>
+        <v>190</v>
+      </c>
+      <c r="G13" s="1">
+        <f>ROUND(C13*[1]属性总表!$H$5,0)</f>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="1">
+        <f t="shared" si="1"/>
+        <v>6.4400000000000013</v>
+      </c>
+      <c r="D14" s="1">
+        <f>B14*[1]属性总表!$E$5</f>
+        <v>8400</v>
+      </c>
+      <c r="E14" s="1">
+        <f>ROUND([1]等级属性!C14*[1]属性总表!$F$5,0)</f>
+        <v>644</v>
+      </c>
+      <c r="F14" s="1">
+        <f>ROUND(C14*[1]属性总表!$G$5,0)</f>
+        <v>193</v>
+      </c>
+      <c r="G14" s="1">
+        <f>ROUND(C14*[1]属性总表!$H$5,0)</f>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <f t="shared" si="0"/>
+        <v>8.25</v>
+      </c>
+      <c r="C15" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5600000000000014</v>
+      </c>
+      <c r="D15" s="1">
+        <f>B15*[1]属性总表!$E$5</f>
+        <v>8662.5</v>
+      </c>
+      <c r="E15" s="1">
+        <f>ROUND([1]等级属性!C15*[1]属性总表!$F$5,0)</f>
+        <v>656</v>
+      </c>
+      <c r="F15" s="1">
+        <f>ROUND(C15*[1]属性总表!$G$5,0)</f>
+        <v>197</v>
+      </c>
+      <c r="G15" s="1">
+        <f>ROUND(C15*[1]属性总表!$H$5,0)</f>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+      <c r="C16" s="1">
+        <f t="shared" si="1"/>
+        <v>6.6800000000000015</v>
+      </c>
+      <c r="D16" s="1">
+        <f>B16*[1]属性总表!$E$5</f>
+        <v>8925</v>
+      </c>
+      <c r="E16" s="1">
+        <f>ROUND([1]等级属性!C16*[1]属性总表!$F$5,0)</f>
+        <v>668</v>
+      </c>
+      <c r="F16" s="1">
+        <f>ROUND(C16*[1]属性总表!$G$5,0)</f>
+        <v>200</v>
+      </c>
+      <c r="G16" s="1">
+        <f>ROUND(C16*[1]属性总表!$H$5,0)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <f t="shared" si="0"/>
+        <v>8.75</v>
+      </c>
+      <c r="C17" s="1">
+        <f t="shared" si="1"/>
+        <v>6.8000000000000016</v>
+      </c>
+      <c r="D17" s="1">
+        <f>B17*[1]属性总表!$E$5</f>
+        <v>9187.5</v>
+      </c>
+      <c r="E17" s="1">
+        <f>ROUND([1]等级属性!C17*[1]属性总表!$F$5,0)</f>
+        <v>680</v>
+      </c>
+      <c r="F17" s="1">
+        <f>ROUND(C17*[1]属性总表!$G$5,0)</f>
+        <v>204</v>
+      </c>
+      <c r="G17" s="1">
+        <f>ROUND(C17*[1]属性总表!$H$5,0)</f>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" si="1"/>
+        <v>6.9200000000000017</v>
+      </c>
+      <c r="D18" s="1">
+        <f>B18*[1]属性总表!$E$5</f>
+        <v>9450</v>
+      </c>
+      <c r="E18" s="1">
+        <f>ROUND([1]等级属性!C18*[1]属性总表!$F$5,0)</f>
+        <v>692</v>
+      </c>
+      <c r="F18" s="1">
+        <f>ROUND(C18*[1]属性总表!$G$5,0)</f>
+        <v>208</v>
+      </c>
+      <c r="G18" s="1">
+        <f>ROUND(C18*[1]属性总表!$H$5,0)</f>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <f t="shared" si="0"/>
+        <v>9.25</v>
+      </c>
+      <c r="C19" s="1">
+        <f t="shared" si="1"/>
+        <v>7.0400000000000018</v>
+      </c>
+      <c r="D19" s="1">
+        <f>B19*[1]属性总表!$E$5</f>
+        <v>9712.5</v>
+      </c>
+      <c r="E19" s="1">
+        <f>ROUND([1]等级属性!C19*[1]属性总表!$F$5,0)</f>
+        <v>704</v>
+      </c>
+      <c r="F19" s="1">
+        <f>ROUND(C19*[1]属性总表!$G$5,0)</f>
+        <v>211</v>
+      </c>
+      <c r="G19" s="1">
+        <f>ROUND(C19*[1]属性总表!$H$5,0)</f>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" si="1"/>
+        <v>7.1600000000000019</v>
+      </c>
+      <c r="D20" s="1">
+        <f>B20*[1]属性总表!$E$5</f>
+        <v>9975</v>
+      </c>
+      <c r="E20" s="1">
+        <f>ROUND([1]等级属性!C20*[1]属性总表!$F$5,0)</f>
+        <v>716</v>
+      </c>
+      <c r="F20" s="1">
+        <f>ROUND(C20*[1]属性总表!$G$5,0)</f>
+        <v>215</v>
+      </c>
+      <c r="G20" s="1">
+        <f>ROUND(C20*[1]属性总表!$H$5,0)</f>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <f t="shared" si="0"/>
+        <v>9.75</v>
+      </c>
+      <c r="C21" s="1">
+        <f t="shared" si="1"/>
+        <v>7.280000000000002</v>
+      </c>
+      <c r="D21" s="1">
+        <f>B21*[1]属性总表!$E$5</f>
+        <v>10237.5</v>
+      </c>
+      <c r="E21" s="1">
+        <f>ROUND([1]等级属性!C21*[1]属性总表!$F$5,0)</f>
+        <v>728</v>
+      </c>
+      <c r="F21" s="1">
+        <f>ROUND(C21*[1]属性总表!$G$5,0)</f>
+        <v>218</v>
+      </c>
+      <c r="G21" s="1">
+        <f>ROUND(C21*[1]属性总表!$H$5,0)</f>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" si="1"/>
+        <v>7.4000000000000021</v>
+      </c>
+      <c r="D22" s="1">
+        <f>B22*[1]属性总表!$E$5</f>
+        <v>10500</v>
+      </c>
+      <c r="E22" s="1">
+        <f>ROUND([1]等级属性!C22*[1]属性总表!$F$5,0)</f>
+        <v>740</v>
+      </c>
+      <c r="F22" s="1">
+        <f>ROUND(C22*[1]属性总表!$G$5,0)</f>
+        <v>222</v>
+      </c>
+      <c r="G22" s="1">
+        <f>ROUND(C22*[1]属性总表!$H$5,0)</f>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <f t="shared" si="0"/>
+        <v>10.25</v>
+      </c>
+      <c r="C23" s="1">
+        <f t="shared" si="1"/>
+        <v>7.5200000000000022</v>
+      </c>
+      <c r="D23" s="1">
+        <f>B23*[1]属性总表!$E$5</f>
+        <v>10762.5</v>
+      </c>
+      <c r="E23" s="1">
+        <f>ROUND([1]等级属性!C23*[1]属性总表!$F$5,0)</f>
+        <v>752</v>
+      </c>
+      <c r="F23" s="1">
+        <f>ROUND(C23*[1]属性总表!$G$5,0)</f>
+        <v>226</v>
+      </c>
+      <c r="G23" s="1">
+        <f>ROUND(C23*[1]属性总表!$H$5,0)</f>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" si="1"/>
+        <v>7.6400000000000023</v>
+      </c>
+      <c r="D24" s="1">
+        <f>B24*[1]属性总表!$E$5</f>
+        <v>11025</v>
+      </c>
+      <c r="E24" s="1">
+        <f>ROUND([1]等级属性!C24*[1]属性总表!$F$5,0)</f>
+        <v>764</v>
+      </c>
+      <c r="F24" s="1">
+        <f>ROUND(C24*[1]属性总表!$G$5,0)</f>
+        <v>229</v>
+      </c>
+      <c r="G24" s="1">
+        <f>ROUND(C24*[1]属性总表!$H$5,0)</f>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
+        <f t="shared" si="0"/>
+        <v>10.75</v>
+      </c>
+      <c r="C25" s="1">
+        <f t="shared" si="1"/>
+        <v>7.7600000000000025</v>
+      </c>
+      <c r="D25" s="1">
+        <f>B25*[1]属性总表!$E$5</f>
+        <v>11287.5</v>
+      </c>
+      <c r="E25" s="1">
+        <f>ROUND([1]等级属性!C25*[1]属性总表!$F$5,0)</f>
+        <v>776</v>
+      </c>
+      <c r="F25" s="1">
+        <f>ROUND(C25*[1]属性总表!$G$5,0)</f>
+        <v>233</v>
+      </c>
+      <c r="G25" s="1">
+        <f>ROUND(C25*[1]属性总表!$H$5,0)</f>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C26" s="1">
+        <f t="shared" si="1"/>
+        <v>7.8800000000000026</v>
+      </c>
+      <c r="D26" s="1">
+        <f>B26*[1]属性总表!$E$5</f>
+        <v>11550</v>
+      </c>
+      <c r="E26" s="1">
+        <f>ROUND([1]等级属性!C26*[1]属性总表!$F$5,0)</f>
+        <v>788</v>
+      </c>
+      <c r="F26" s="1">
+        <f>ROUND(C26*[1]属性总表!$G$5,0)</f>
+        <v>236</v>
+      </c>
+      <c r="G26" s="1">
+        <f>ROUND(C26*[1]属性总表!$H$5,0)</f>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
+        <f t="shared" si="0"/>
+        <v>11.25</v>
+      </c>
+      <c r="C27" s="1">
+        <f t="shared" si="1"/>
+        <v>8.0000000000000018</v>
+      </c>
+      <c r="D27" s="1">
+        <f>B27*[1]属性总表!$E$5</f>
+        <v>11812.5</v>
+      </c>
+      <c r="E27" s="1">
+        <f>ROUND([1]等级属性!C27*[1]属性总表!$F$5,0)</f>
+        <v>800</v>
+      </c>
+      <c r="F27" s="1">
+        <f>ROUND(C27*[1]属性总表!$G$5,0)</f>
+        <v>240</v>
+      </c>
+      <c r="G27" s="1">
+        <f>ROUND(C27*[1]属性总表!$H$5,0)</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="C28" s="1">
+        <f t="shared" si="1"/>
+        <v>8.120000000000001</v>
+      </c>
+      <c r="D28" s="1">
+        <f>B28*[1]属性总表!$E$5</f>
+        <v>12075</v>
+      </c>
+      <c r="E28" s="1">
+        <f>ROUND([1]等级属性!C28*[1]属性总表!$F$5,0)</f>
+        <v>812</v>
+      </c>
+      <c r="F28" s="1">
+        <f>ROUND(C28*[1]属性总表!$G$5,0)</f>
+        <v>244</v>
+      </c>
+      <c r="G28" s="1">
+        <f>ROUND(C28*[1]属性总表!$H$5,0)</f>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <f t="shared" si="0"/>
+        <v>11.75</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="shared" si="1"/>
+        <v>8.24</v>
+      </c>
+      <c r="D29" s="1">
+        <f>B29*[1]属性总表!$E$5</f>
+        <v>12337.5</v>
+      </c>
+      <c r="E29" s="1">
+        <f>ROUND([1]等级属性!C29*[1]属性总表!$F$5,0)</f>
+        <v>824</v>
+      </c>
+      <c r="F29" s="1">
+        <f>ROUND(C29*[1]属性总表!$G$5,0)</f>
+        <v>247</v>
+      </c>
+      <c r="G29" s="1">
+        <f>ROUND(C29*[1]属性总表!$H$5,0)</f>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C30" s="1">
+        <f t="shared" si="1"/>
+        <v>8.36</v>
+      </c>
+      <c r="D30" s="1">
+        <f>B30*[1]属性总表!$E$5</f>
+        <v>12600</v>
+      </c>
+      <c r="E30" s="1">
+        <f>ROUND([1]等级属性!C30*[1]属性总表!$F$5,0)</f>
+        <v>836</v>
+      </c>
+      <c r="F30" s="1">
+        <f>ROUND(C30*[1]属性总表!$G$5,0)</f>
+        <v>251</v>
+      </c>
+      <c r="G30" s="1">
+        <f>ROUND(C30*[1]属性总表!$H$5,0)</f>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1">
+        <f t="shared" si="0"/>
+        <v>12.25</v>
+      </c>
+      <c r="C31" s="1">
+        <f t="shared" si="1"/>
+        <v>8.4799999999999986</v>
+      </c>
+      <c r="D31" s="1">
+        <f>B31*[1]属性总表!$E$5</f>
+        <v>12862.5</v>
+      </c>
+      <c r="E31" s="1">
+        <f>ROUND([1]等级属性!C31*[1]属性总表!$F$5,0)</f>
+        <v>848</v>
+      </c>
+      <c r="F31" s="1">
+        <f>ROUND(C31*[1]属性总表!$G$5,0)</f>
+        <v>254</v>
+      </c>
+      <c r="G31" s="1">
+        <f>ROUND(C31*[1]属性总表!$H$5,0)</f>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="C32" s="1">
+        <f t="shared" si="1"/>
+        <v>8.5999999999999979</v>
+      </c>
+      <c r="D32" s="1">
+        <f>B32*[1]属性总表!$E$5</f>
+        <v>13125</v>
+      </c>
+      <c r="E32" s="1">
+        <f>ROUND([1]等级属性!C32*[1]属性总表!$F$5,0)</f>
+        <v>860</v>
+      </c>
+      <c r="F32" s="1">
+        <f>ROUND(C32*[1]属性总表!$G$5,0)</f>
+        <v>258</v>
+      </c>
+      <c r="G32" s="1">
+        <f>ROUND(C32*[1]属性总表!$H$5,0)</f>
+        <v>258</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
+        <f t="shared" si="0"/>
+        <v>12.75</v>
+      </c>
+      <c r="C33" s="1">
+        <f t="shared" si="1"/>
+        <v>8.7199999999999971</v>
+      </c>
+      <c r="D33" s="1">
+        <f>B33*[1]属性总表!$E$5</f>
+        <v>13387.5</v>
+      </c>
+      <c r="E33" s="1">
+        <f>ROUND([1]等级属性!C33*[1]属性总表!$F$5,0)</f>
+        <v>872</v>
+      </c>
+      <c r="F33" s="1">
+        <f>ROUND(C33*[1]属性总表!$G$5,0)</f>
+        <v>262</v>
+      </c>
+      <c r="G33" s="1">
+        <f>ROUND(C33*[1]属性总表!$H$5,0)</f>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C34" s="1">
+        <f t="shared" si="1"/>
+        <v>8.8399999999999963</v>
+      </c>
+      <c r="D34" s="1">
+        <f>B34*[1]属性总表!$E$5</f>
+        <v>13650</v>
+      </c>
+      <c r="E34" s="1">
+        <f>ROUND([1]等级属性!C34*[1]属性总表!$F$5,0)</f>
+        <v>884</v>
+      </c>
+      <c r="F34" s="1">
+        <f>ROUND(C34*[1]属性总表!$G$5,0)</f>
+        <v>265</v>
+      </c>
+      <c r="G34" s="1">
+        <f>ROUND(C34*[1]属性总表!$H$5,0)</f>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <f t="shared" si="0"/>
+        <v>13.25</v>
+      </c>
+      <c r="C35" s="1">
+        <f t="shared" si="1"/>
+        <v>8.9599999999999955</v>
+      </c>
+      <c r="D35" s="1">
+        <f>B35*[1]属性总表!$E$5</f>
+        <v>13912.5</v>
+      </c>
+      <c r="E35" s="1">
+        <f>ROUND([1]等级属性!C35*[1]属性总表!$F$5,0)</f>
+        <v>896</v>
+      </c>
+      <c r="F35" s="1">
+        <f>ROUND(C35*[1]属性总表!$G$5,0)</f>
+        <v>269</v>
+      </c>
+      <c r="G35" s="1">
+        <f>ROUND(C35*[1]属性总表!$H$5,0)</f>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="C36" s="1">
+        <f t="shared" si="1"/>
+        <v>9.0799999999999947</v>
+      </c>
+      <c r="D36" s="1">
+        <f>B36*[1]属性总表!$E$5</f>
+        <v>14175</v>
+      </c>
+      <c r="E36" s="1">
+        <f>ROUND([1]等级属性!C36*[1]属性总表!$F$5,0)</f>
+        <v>908</v>
+      </c>
+      <c r="F36" s="1">
+        <f>ROUND(C36*[1]属性总表!$G$5,0)</f>
+        <v>272</v>
+      </c>
+      <c r="G36" s="1">
+        <f>ROUND(C36*[1]属性总表!$H$5,0)</f>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1">
+        <f t="shared" si="0"/>
+        <v>13.75</v>
+      </c>
+      <c r="C37" s="1">
+        <f t="shared" si="1"/>
+        <v>9.199999999999994</v>
+      </c>
+      <c r="D37" s="1">
+        <f>B37*[1]属性总表!$E$5</f>
+        <v>14437.5</v>
+      </c>
+      <c r="E37" s="1">
+        <f>ROUND([1]等级属性!C37*[1]属性总表!$F$5,0)</f>
+        <v>920</v>
+      </c>
+      <c r="F37" s="1">
+        <f>ROUND(C37*[1]属性总表!$G$5,0)</f>
+        <v>276</v>
+      </c>
+      <c r="G37" s="1">
+        <f>ROUND(C37*[1]属性总表!$H$5,0)</f>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C38" s="1">
+        <f t="shared" si="1"/>
+        <v>9.3199999999999932</v>
+      </c>
+      <c r="D38" s="1">
+        <f>B38*[1]属性总表!$E$5</f>
+        <v>14700</v>
+      </c>
+      <c r="E38" s="1">
+        <f>ROUND([1]等级属性!C38*[1]属性总表!$F$5,0)</f>
+        <v>932</v>
+      </c>
+      <c r="F38" s="1">
+        <f>ROUND(C38*[1]属性总表!$G$5,0)</f>
+        <v>280</v>
+      </c>
+      <c r="G38" s="1">
+        <f>ROUND(C38*[1]属性总表!$H$5,0)</f>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1">
+        <f t="shared" si="0"/>
+        <v>14.25</v>
+      </c>
+      <c r="C39" s="1">
+        <f t="shared" si="1"/>
+        <v>9.4399999999999924</v>
+      </c>
+      <c r="D39" s="1">
+        <f>B39*[1]属性总表!$E$5</f>
+        <v>14962.5</v>
+      </c>
+      <c r="E39" s="1">
+        <f>ROUND([1]等级属性!C39*[1]属性总表!$F$5,0)</f>
+        <v>944</v>
+      </c>
+      <c r="F39" s="1">
+        <f>ROUND(C39*[1]属性总表!$G$5,0)</f>
+        <v>283</v>
+      </c>
+      <c r="G39" s="1">
+        <f>ROUND(C39*[1]属性总表!$H$5,0)</f>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+      <c r="C40" s="1">
+        <f t="shared" si="1"/>
+        <v>9.5599999999999916</v>
+      </c>
+      <c r="D40" s="1">
+        <f>B40*[1]属性总表!$E$5</f>
+        <v>15225</v>
+      </c>
+      <c r="E40" s="1">
+        <f>ROUND([1]等级属性!C40*[1]属性总表!$F$5,0)</f>
+        <v>956</v>
+      </c>
+      <c r="F40" s="1">
+        <f>ROUND(C40*[1]属性总表!$G$5,0)</f>
+        <v>287</v>
+      </c>
+      <c r="G40" s="1">
+        <f>ROUND(C40*[1]属性总表!$H$5,0)</f>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1">
+        <f t="shared" si="0"/>
+        <v>14.75</v>
+      </c>
+      <c r="C41" s="1">
+        <f t="shared" si="1"/>
+        <v>9.6799999999999908</v>
+      </c>
+      <c r="D41" s="1">
+        <f>B41*[1]属性总表!$E$5</f>
+        <v>15487.5</v>
+      </c>
+      <c r="E41" s="1">
+        <f>ROUND([1]等级属性!C41*[1]属性总表!$F$5,0)</f>
+        <v>968</v>
+      </c>
+      <c r="F41" s="1">
+        <f>ROUND(C41*[1]属性总表!$G$5,0)</f>
+        <v>290</v>
+      </c>
+      <c r="G41" s="1">
+        <f>ROUND(C41*[1]属性总表!$H$5,0)</f>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C42" s="1">
+        <f t="shared" si="1"/>
+        <v>9.7999999999999901</v>
+      </c>
+      <c r="D42" s="1">
+        <f>B42*[1]属性总表!$E$5</f>
+        <v>15750</v>
+      </c>
+      <c r="E42" s="1">
+        <f>ROUND([1]等级属性!C42*[1]属性总表!$F$5,0)</f>
+        <v>980</v>
+      </c>
+      <c r="F42" s="1">
+        <f>ROUND(C42*[1]属性总表!$G$5,0)</f>
+        <v>294</v>
+      </c>
+      <c r="G42" s="1">
+        <f>ROUND(C42*[1]属性总表!$H$5,0)</f>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <f t="shared" si="0"/>
+        <v>15.25</v>
+      </c>
+      <c r="C43" s="1">
+        <f t="shared" si="1"/>
+        <v>9.9199999999999893</v>
+      </c>
+      <c r="D43" s="1">
+        <f>B43*[1]属性总表!$E$5</f>
+        <v>16012.5</v>
+      </c>
+      <c r="E43" s="1">
+        <f>ROUND([1]等级属性!C43*[1]属性总表!$F$5,0)</f>
+        <v>992</v>
+      </c>
+      <c r="F43" s="1">
+        <f>ROUND(C43*[1]属性总表!$G$5,0)</f>
+        <v>298</v>
+      </c>
+      <c r="G43" s="1">
+        <f>ROUND(C43*[1]属性总表!$H$5,0)</f>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="C44" s="1">
+        <f t="shared" si="1"/>
+        <v>10.039999999999988</v>
+      </c>
+      <c r="D44" s="1">
+        <f>B44*[1]属性总表!$E$5</f>
+        <v>16275</v>
+      </c>
+      <c r="E44" s="1">
+        <f>ROUND([1]等级属性!C44*[1]属性总表!$F$5,0)</f>
+        <v>1004</v>
+      </c>
+      <c r="F44" s="1">
+        <f>ROUND(C44*[1]属性总表!$G$5,0)</f>
+        <v>301</v>
+      </c>
+      <c r="G44" s="1">
+        <f>ROUND(C44*[1]属性总表!$H$5,0)</f>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1">
+        <f t="shared" si="0"/>
+        <v>15.75</v>
+      </c>
+      <c r="C45" s="1">
+        <f t="shared" si="1"/>
+        <v>10.159999999999988</v>
+      </c>
+      <c r="D45" s="1">
+        <f>B45*[1]属性总表!$E$5</f>
+        <v>16537.5</v>
+      </c>
+      <c r="E45" s="1">
+        <f>ROUND([1]等级属性!C45*[1]属性总表!$F$5,0)</f>
+        <v>1016</v>
+      </c>
+      <c r="F45" s="1">
+        <f>ROUND(C45*[1]属性总表!$G$5,0)</f>
+        <v>305</v>
+      </c>
+      <c r="G45" s="1">
+        <f>ROUND(C45*[1]属性总表!$H$5,0)</f>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C46" s="1">
+        <f t="shared" si="1"/>
+        <v>10.279999999999987</v>
+      </c>
+      <c r="D46" s="1">
+        <f>B46*[1]属性总表!$E$5</f>
+        <v>16800</v>
+      </c>
+      <c r="E46" s="1">
+        <f>ROUND([1]等级属性!C46*[1]属性总表!$F$5,0)</f>
+        <v>1028</v>
+      </c>
+      <c r="F46" s="1">
+        <f>ROUND(C46*[1]属性总表!$G$5,0)</f>
+        <v>308</v>
+      </c>
+      <c r="G46" s="1">
+        <f>ROUND(C46*[1]属性总表!$H$5,0)</f>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1">
+        <f t="shared" si="0"/>
+        <v>16.25</v>
+      </c>
+      <c r="C47" s="1">
+        <f t="shared" si="1"/>
+        <v>10.399999999999986</v>
+      </c>
+      <c r="D47" s="1">
+        <f>B47*[1]属性总表!$E$5</f>
+        <v>17062.5</v>
+      </c>
+      <c r="E47" s="1">
+        <f>ROUND([1]等级属性!C47*[1]属性总表!$F$5,0)</f>
+        <v>1040</v>
+      </c>
+      <c r="F47" s="1">
+        <f>ROUND(C47*[1]属性总表!$G$5,0)</f>
+        <v>312</v>
+      </c>
+      <c r="G47" s="1">
+        <f>ROUND(C47*[1]属性总表!$H$5,0)</f>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="C48" s="1">
+        <f t="shared" si="1"/>
+        <v>10.519999999999985</v>
+      </c>
+      <c r="D48" s="1">
+        <f>B48*[1]属性总表!$E$5</f>
+        <v>17325</v>
+      </c>
+      <c r="E48" s="1">
+        <f>ROUND([1]等级属性!C48*[1]属性总表!$F$5,0)</f>
+        <v>1052</v>
+      </c>
+      <c r="F48" s="1">
+        <f>ROUND(C48*[1]属性总表!$G$5,0)</f>
+        <v>316</v>
+      </c>
+      <c r="G48" s="1">
+        <f>ROUND(C48*[1]属性总表!$H$5,0)</f>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1">
+        <f t="shared" si="0"/>
+        <v>16.75</v>
+      </c>
+      <c r="C49" s="1">
+        <f t="shared" si="1"/>
+        <v>10.639999999999985</v>
+      </c>
+      <c r="D49" s="1">
+        <f>B49*[1]属性总表!$E$5</f>
+        <v>17587.5</v>
+      </c>
+      <c r="E49" s="1">
+        <f>ROUND([1]等级属性!C49*[1]属性总表!$F$5,0)</f>
+        <v>1064</v>
+      </c>
+      <c r="F49" s="1">
+        <f>ROUND(C49*[1]属性总表!$G$5,0)</f>
+        <v>319</v>
+      </c>
+      <c r="G49" s="1">
+        <f>ROUND(C49*[1]属性总表!$H$5,0)</f>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C50" s="1">
+        <f t="shared" si="1"/>
+        <v>10.759999999999984</v>
+      </c>
+      <c r="D50" s="1">
+        <f>B50*[1]属性总表!$E$5</f>
+        <v>17850</v>
+      </c>
+      <c r="E50" s="1">
+        <f>ROUND([1]等级属性!C50*[1]属性总表!$F$5,0)</f>
+        <v>1076</v>
+      </c>
+      <c r="F50" s="1">
+        <f>ROUND(C50*[1]属性总表!$G$5,0)</f>
+        <v>323</v>
+      </c>
+      <c r="G50" s="1">
+        <f>ROUND(C50*[1]属性总表!$H$5,0)</f>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1">
+        <f t="shared" si="0"/>
+        <v>17.25</v>
+      </c>
+      <c r="C51" s="1">
+        <f t="shared" si="1"/>
+        <v>10.879999999999983</v>
+      </c>
+      <c r="D51" s="1">
+        <f>B51*[1]属性总表!$E$5</f>
+        <v>18112.5</v>
+      </c>
+      <c r="E51" s="1">
+        <f>ROUND([1]等级属性!C51*[1]属性总表!$F$5,0)</f>
+        <v>1088</v>
+      </c>
+      <c r="F51" s="1">
+        <f>ROUND(C51*[1]属性总表!$G$5,0)</f>
+        <v>326</v>
+      </c>
+      <c r="G51" s="1">
+        <f>ROUND(C51*[1]属性总表!$H$5,0)</f>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+      <c r="C52" s="1">
+        <f t="shared" si="1"/>
+        <v>10.999999999999982</v>
+      </c>
+      <c r="D52" s="1">
+        <f>B52*[1]属性总表!$E$5</f>
+        <v>18375</v>
+      </c>
+      <c r="E52" s="1">
+        <f>ROUND([1]等级属性!C52*[1]属性总表!$F$5,0)</f>
+        <v>1100</v>
+      </c>
+      <c r="F52" s="1">
+        <f>ROUND(C52*[1]属性总表!$G$5,0)</f>
+        <v>330</v>
+      </c>
+      <c r="G52" s="1">
+        <f>ROUND(C52*[1]属性总表!$H$5,0)</f>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1">
+        <f t="shared" si="0"/>
+        <v>17.75</v>
+      </c>
+      <c r="C53" s="1">
+        <f t="shared" si="1"/>
+        <v>11.119999999999981</v>
+      </c>
+      <c r="D53" s="1">
+        <f>B53*[1]属性总表!$E$5</f>
+        <v>18637.5</v>
+      </c>
+      <c r="E53" s="1">
+        <f>ROUND([1]等级属性!C53*[1]属性总表!$F$5,0)</f>
+        <v>1112</v>
+      </c>
+      <c r="F53" s="1">
+        <f>ROUND(C53*[1]属性总表!$G$5,0)</f>
+        <v>334</v>
+      </c>
+      <c r="G53" s="1">
+        <f>ROUND(C53*[1]属性总表!$H$5,0)</f>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C54" s="1">
+        <f t="shared" si="1"/>
+        <v>11.239999999999981</v>
+      </c>
+      <c r="D54" s="1">
+        <f>B54*[1]属性总表!$E$5</f>
+        <v>18900</v>
+      </c>
+      <c r="E54" s="1">
+        <f>ROUND([1]等级属性!C54*[1]属性总表!$F$5,0)</f>
+        <v>1124</v>
+      </c>
+      <c r="F54" s="1">
+        <f>ROUND(C54*[1]属性总表!$G$5,0)</f>
+        <v>337</v>
+      </c>
+      <c r="G54" s="1">
+        <f>ROUND(C54*[1]属性总表!$H$5,0)</f>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1">
+        <f t="shared" si="0"/>
+        <v>18.25</v>
+      </c>
+      <c r="C55" s="1">
+        <f t="shared" si="1"/>
+        <v>11.35999999999998</v>
+      </c>
+      <c r="D55" s="1">
+        <f>B55*[1]属性总表!$E$5</f>
+        <v>19162.5</v>
+      </c>
+      <c r="E55" s="1">
+        <f>ROUND([1]等级属性!C55*[1]属性总表!$F$5,0)</f>
+        <v>1136</v>
+      </c>
+      <c r="F55" s="1">
+        <f>ROUND(C55*[1]属性总表!$G$5,0)</f>
+        <v>341</v>
+      </c>
+      <c r="G55" s="1">
+        <f>ROUND(C55*[1]属性总表!$H$5,0)</f>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1">
+        <f t="shared" si="0"/>
+        <v>18.5</v>
+      </c>
+      <c r="C56" s="1">
+        <f t="shared" si="1"/>
+        <v>11.479999999999979</v>
+      </c>
+      <c r="D56" s="1">
+        <f>B56*[1]属性总表!$E$5</f>
+        <v>19425</v>
+      </c>
+      <c r="E56" s="1">
+        <f>ROUND([1]等级属性!C56*[1]属性总表!$F$5,0)</f>
+        <v>1148</v>
+      </c>
+      <c r="F56" s="1">
+        <f>ROUND(C56*[1]属性总表!$G$5,0)</f>
+        <v>344</v>
+      </c>
+      <c r="G56" s="1">
+        <f>ROUND(C56*[1]属性总表!$H$5,0)</f>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1">
+        <f t="shared" si="0"/>
+        <v>18.75</v>
+      </c>
+      <c r="C57" s="1">
+        <f t="shared" si="1"/>
+        <v>11.599999999999978</v>
+      </c>
+      <c r="D57" s="1">
+        <f>B57*[1]属性总表!$E$5</f>
+        <v>19687.5</v>
+      </c>
+      <c r="E57" s="1">
+        <f>ROUND([1]等级属性!C57*[1]属性总表!$F$5,0)</f>
+        <v>1160</v>
+      </c>
+      <c r="F57" s="1">
+        <f>ROUND(C57*[1]属性总表!$G$5,0)</f>
+        <v>348</v>
+      </c>
+      <c r="G57" s="1">
+        <f>ROUND(C57*[1]属性总表!$H$5,0)</f>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C58" s="1">
+        <f t="shared" si="1"/>
+        <v>11.719999999999978</v>
+      </c>
+      <c r="D58" s="1">
+        <f>B58*[1]属性总表!$E$5</f>
+        <v>19950</v>
+      </c>
+      <c r="E58" s="1">
+        <f>ROUND([1]等级属性!C58*[1]属性总表!$F$5,0)</f>
+        <v>1172</v>
+      </c>
+      <c r="F58" s="1">
+        <f>ROUND(C58*[1]属性总表!$G$5,0)</f>
+        <v>352</v>
+      </c>
+      <c r="G58" s="1">
+        <f>ROUND(C58*[1]属性总表!$H$5,0)</f>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1">
+        <f t="shared" si="0"/>
+        <v>19.25</v>
+      </c>
+      <c r="C59" s="1">
+        <f t="shared" si="1"/>
+        <v>11.839999999999977</v>
+      </c>
+      <c r="D59" s="1">
+        <f>B59*[1]属性总表!$E$5</f>
+        <v>20212.5</v>
+      </c>
+      <c r="E59" s="1">
+        <f>ROUND([1]等级属性!C59*[1]属性总表!$F$5,0)</f>
+        <v>1184</v>
+      </c>
+      <c r="F59" s="1">
+        <f>ROUND(C59*[1]属性总表!$G$5,0)</f>
+        <v>355</v>
+      </c>
+      <c r="G59" s="1">
+        <f>ROUND(C59*[1]属性总表!$H$5,0)</f>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1">
+        <f t="shared" si="0"/>
+        <v>19.5</v>
+      </c>
+      <c r="C60" s="1">
+        <f t="shared" si="1"/>
+        <v>11.959999999999976</v>
+      </c>
+      <c r="D60" s="1">
+        <f>B60*[1]属性总表!$E$5</f>
+        <v>20475</v>
+      </c>
+      <c r="E60" s="1">
+        <f>ROUND([1]等级属性!C60*[1]属性总表!$F$5,0)</f>
+        <v>1196</v>
+      </c>
+      <c r="F60" s="1">
+        <f>ROUND(C60*[1]属性总表!$G$5,0)</f>
+        <v>359</v>
+      </c>
+      <c r="G60" s="1">
+        <f>ROUND(C60*[1]属性总表!$H$5,0)</f>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1">
+        <f t="shared" si="0"/>
+        <v>19.75</v>
+      </c>
+      <c r="C61" s="1">
+        <f t="shared" si="1"/>
+        <v>12.079999999999975</v>
+      </c>
+      <c r="D61" s="1">
+        <f>B61*[1]属性总表!$E$5</f>
+        <v>20737.5</v>
+      </c>
+      <c r="E61" s="1">
+        <f>ROUND([1]等级属性!C61*[1]属性总表!$F$5,0)</f>
+        <v>1208</v>
+      </c>
+      <c r="F61" s="1">
+        <f>ROUND(C61*[1]属性总表!$G$5,0)</f>
+        <v>362</v>
+      </c>
+      <c r="G61" s="1">
+        <f>ROUND(C61*[1]属性总表!$H$5,0)</f>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C62" s="1">
+        <f t="shared" si="1"/>
+        <v>12.199999999999974</v>
+      </c>
+      <c r="D62" s="1">
+        <f>B62*[1]属性总表!$E$5</f>
+        <v>21000</v>
+      </c>
+      <c r="E62" s="1">
+        <f>ROUND([1]等级属性!C62*[1]属性总表!$F$5,0)</f>
+        <v>1220</v>
+      </c>
+      <c r="F62" s="1">
+        <f>ROUND(C62*[1]属性总表!$G$5,0)</f>
+        <v>366</v>
+      </c>
+      <c r="G62" s="1">
+        <f>ROUND(C62*[1]属性总表!$H$5,0)</f>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1">
+        <f t="shared" si="0"/>
+        <v>20.25</v>
+      </c>
+      <c r="C63" s="1">
+        <f t="shared" si="1"/>
+        <v>12.319999999999974</v>
+      </c>
+      <c r="D63" s="1">
+        <f>B63*[1]属性总表!$E$5</f>
+        <v>21262.5</v>
+      </c>
+      <c r="E63" s="1">
+        <f>ROUND([1]等级属性!C63*[1]属性总表!$F$5,0)</f>
+        <v>1232</v>
+      </c>
+      <c r="F63" s="1">
+        <f>ROUND(C63*[1]属性总表!$G$5,0)</f>
+        <v>370</v>
+      </c>
+      <c r="G63" s="1">
+        <f>ROUND(C63*[1]属性总表!$H$5,0)</f>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1">
+        <f t="shared" si="0"/>
+        <v>20.5</v>
+      </c>
+      <c r="C64" s="1">
+        <f t="shared" si="1"/>
+        <v>12.439999999999973</v>
+      </c>
+      <c r="D64" s="1">
+        <f>B64*[1]属性总表!$E$5</f>
+        <v>21525</v>
+      </c>
+      <c r="E64" s="1">
+        <f>ROUND([1]等级属性!C64*[1]属性总表!$F$5,0)</f>
+        <v>1244</v>
+      </c>
+      <c r="F64" s="1">
+        <f>ROUND(C64*[1]属性总表!$G$5,0)</f>
+        <v>373</v>
+      </c>
+      <c r="G64" s="1">
+        <f>ROUND(C64*[1]属性总表!$H$5,0)</f>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1">
+        <f t="shared" si="0"/>
+        <v>20.75</v>
+      </c>
+      <c r="C65" s="1">
+        <f t="shared" si="1"/>
+        <v>12.559999999999972</v>
+      </c>
+      <c r="D65" s="1">
+        <f>B65*[1]属性总表!$E$5</f>
+        <v>21787.5</v>
+      </c>
+      <c r="E65" s="1">
+        <f>ROUND([1]等级属性!C65*[1]属性总表!$F$5,0)</f>
+        <v>1256</v>
+      </c>
+      <c r="F65" s="1">
+        <f>ROUND(C65*[1]属性总表!$G$5,0)</f>
+        <v>377</v>
+      </c>
+      <c r="G65" s="1">
+        <f>ROUND(C65*[1]属性总表!$H$5,0)</f>
+        <v>377</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C66" s="1">
+        <f t="shared" si="1"/>
+        <v>12.679999999999971</v>
+      </c>
+      <c r="D66" s="1">
+        <f>B66*[1]属性总表!$E$5</f>
+        <v>22050</v>
+      </c>
+      <c r="E66" s="1">
+        <f>ROUND([1]等级属性!C66*[1]属性总表!$F$5,0)</f>
+        <v>1268</v>
+      </c>
+      <c r="F66" s="1">
+        <f>ROUND(C66*[1]属性总表!$G$5,0)</f>
+        <v>380</v>
+      </c>
+      <c r="G66" s="1">
+        <f>ROUND(C66*[1]属性总表!$H$5,0)</f>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1">
+        <f t="shared" si="0"/>
+        <v>21.25</v>
+      </c>
+      <c r="C67" s="1">
+        <f t="shared" si="1"/>
+        <v>12.799999999999971</v>
+      </c>
+      <c r="D67" s="1">
+        <f>B67*[1]属性总表!$E$5</f>
+        <v>22312.5</v>
+      </c>
+      <c r="E67" s="1">
+        <f>ROUND([1]等级属性!C67*[1]属性总表!$F$5,0)</f>
+        <v>1280</v>
+      </c>
+      <c r="F67" s="1">
+        <f>ROUND(C67*[1]属性总表!$G$5,0)</f>
+        <v>384</v>
+      </c>
+      <c r="G67" s="1">
+        <f>ROUND(C67*[1]属性总表!$H$5,0)</f>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1">
+        <f t="shared" ref="B68:B71" si="2">B67+0.25</f>
+        <v>21.5</v>
+      </c>
+      <c r="C68" s="1">
+        <f t="shared" ref="C68:C71" si="3">C67+0.12</f>
+        <v>12.91999999999997</v>
+      </c>
+      <c r="D68" s="1">
+        <f>B68*[1]属性总表!$E$5</f>
+        <v>22575</v>
+      </c>
+      <c r="E68" s="1">
+        <f>ROUND([1]等级属性!C68*[1]属性总表!$F$5,0)</f>
+        <v>1292</v>
+      </c>
+      <c r="F68" s="1">
+        <f>ROUND(C68*[1]属性总表!$G$5,0)</f>
+        <v>388</v>
+      </c>
+      <c r="G68" s="1">
+        <f>ROUND(C68*[1]属性总表!$H$5,0)</f>
+        <v>388</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1">
+        <f t="shared" si="2"/>
+        <v>21.75</v>
+      </c>
+      <c r="C69" s="1">
+        <f t="shared" si="3"/>
+        <v>13.039999999999969</v>
+      </c>
+      <c r="D69" s="1">
+        <f>B69*[1]属性总表!$E$5</f>
+        <v>22837.5</v>
+      </c>
+      <c r="E69" s="1">
+        <f>ROUND([1]等级属性!C69*[1]属性总表!$F$5,0)</f>
+        <v>1304</v>
+      </c>
+      <c r="F69" s="1">
+        <f>ROUND(C69*[1]属性总表!$G$5,0)</f>
+        <v>391</v>
+      </c>
+      <c r="G69" s="1">
+        <f>ROUND(C69*[1]属性总表!$H$5,0)</f>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="C70" s="1">
+        <f t="shared" si="3"/>
+        <v>13.159999999999968</v>
+      </c>
+      <c r="D70" s="1">
+        <f>B70*[1]属性总表!$E$5</f>
+        <v>23100</v>
+      </c>
+      <c r="E70" s="1">
+        <f>ROUND([1]等级属性!C70*[1]属性总表!$F$5,0)</f>
+        <v>1316</v>
+      </c>
+      <c r="F70" s="1">
+        <f>ROUND(C70*[1]属性总表!$G$5,0)</f>
+        <v>395</v>
+      </c>
+      <c r="G70" s="1">
+        <f>ROUND(C70*[1]属性总表!$H$5,0)</f>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1">
+        <f t="shared" si="2"/>
+        <v>22.25</v>
+      </c>
+      <c r="C71" s="1">
+        <f t="shared" si="3"/>
+        <v>13.279999999999967</v>
+      </c>
+      <c r="D71" s="1">
+        <f>B71*[1]属性总表!$E$5</f>
+        <v>23362.5</v>
+      </c>
+      <c r="E71" s="1">
+        <f>ROUND([1]等级属性!C71*[1]属性总表!$F$5,0)</f>
+        <v>1328</v>
+      </c>
+      <c r="F71" s="1">
+        <f>ROUND(C71*[1]属性总表!$G$5,0)</f>
+        <v>398</v>
+      </c>
+      <c r="G71" s="1">
+        <f>ROUND(C71*[1]属性总表!$H$5,0)</f>
+        <v>398</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="35" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="C1:P41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -46727,2078 +50287,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="7" width="9" style="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1">
-        <f>B2*[1]属性总表!$E$5</f>
-        <v>5250</v>
-      </c>
-      <c r="E2" s="1">
-        <f>ROUND([1]等级属性!C2*[1]属性总表!$F$5,0)</f>
-        <v>500</v>
-      </c>
-      <c r="F2" s="1">
-        <f>ROUND(C2*[1]属性总表!$G$5,0)</f>
-        <v>150</v>
-      </c>
-      <c r="G2" s="1">
-        <f>ROUND(C2*[1]属性总表!$H$5,0)</f>
-        <v>150</v>
-      </c>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <f>B2+0.25</f>
-        <v>5.25</v>
-      </c>
-      <c r="C3" s="1">
-        <f>C2+0.12</f>
-        <v>5.12</v>
-      </c>
-      <c r="D3" s="1">
-        <f>B3*[1]属性总表!$E$5</f>
-        <v>5512.5</v>
-      </c>
-      <c r="E3" s="1">
-        <f>ROUND([1]等级属性!C3*[1]属性总表!$F$5,0)</f>
-        <v>512</v>
-      </c>
-      <c r="F3" s="1">
-        <f>ROUND(C3*[1]属性总表!$G$5,0)</f>
-        <v>154</v>
-      </c>
-      <c r="G3" s="1">
-        <f>ROUND(C3*[1]属性总表!$H$5,0)</f>
-        <v>154</v>
-      </c>
-      <c r="H3" s="1">
-        <f>D3-D2</f>
-        <v>262.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1">
-        <f t="shared" ref="B4:B67" si="0">B3+0.25</f>
-        <v>5.5</v>
-      </c>
-      <c r="C4" s="1">
-        <f t="shared" ref="C4:C67" si="1">C3+0.12</f>
-        <v>5.24</v>
-      </c>
-      <c r="D4" s="1">
-        <f>B4*[1]属性总表!$E$5</f>
-        <v>5775</v>
-      </c>
-      <c r="E4" s="1">
-        <f>ROUND([1]等级属性!C4*[1]属性总表!$F$5,0)</f>
-        <v>524</v>
-      </c>
-      <c r="F4" s="1">
-        <f>ROUND(C4*[1]属性总表!$G$5,0)</f>
-        <v>157</v>
-      </c>
-      <c r="G4" s="1">
-        <f>ROUND(C4*[1]属性总表!$H$5,0)</f>
-        <v>157</v>
-      </c>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
-        <f t="shared" si="0"/>
-        <v>5.75</v>
-      </c>
-      <c r="C5" s="1">
-        <f t="shared" si="1"/>
-        <v>5.36</v>
-      </c>
-      <c r="D5" s="1">
-        <f>B5*[1]属性总表!$E$5</f>
-        <v>6037.5</v>
-      </c>
-      <c r="E5" s="1">
-        <f>ROUND([1]等级属性!C5*[1]属性总表!$F$5,0)</f>
-        <v>536</v>
-      </c>
-      <c r="F5" s="1">
-        <f>ROUND(C5*[1]属性总表!$G$5,0)</f>
-        <v>161</v>
-      </c>
-      <c r="G5" s="1">
-        <f>ROUND(C5*[1]属性总表!$H$5,0)</f>
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C6" s="1">
-        <f t="shared" si="1"/>
-        <v>5.48</v>
-      </c>
-      <c r="D6" s="1">
-        <f>B6*[1]属性总表!$E$5</f>
-        <v>6300</v>
-      </c>
-      <c r="E6" s="1">
-        <f>ROUND([1]等级属性!C6*[1]属性总表!$F$5,0)</f>
-        <v>548</v>
-      </c>
-      <c r="F6" s="1">
-        <f>ROUND(C6*[1]属性总表!$G$5,0)</f>
-        <v>164</v>
-      </c>
-      <c r="G6" s="1">
-        <f>ROUND(C6*[1]属性总表!$H$5,0)</f>
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1">
-        <f t="shared" si="0"/>
-        <v>6.25</v>
-      </c>
-      <c r="C7" s="1">
-        <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
-      </c>
-      <c r="D7" s="1">
-        <f>B7*[1]属性总表!$E$5</f>
-        <v>6562.5</v>
-      </c>
-      <c r="E7" s="1">
-        <f>ROUND([1]等级属性!C7*[1]属性总表!$F$5,0)</f>
-        <v>560</v>
-      </c>
-      <c r="F7" s="1">
-        <f>ROUND(C7*[1]属性总表!$G$5,0)</f>
-        <v>168</v>
-      </c>
-      <c r="G7" s="1">
-        <f>ROUND(C7*[1]属性总表!$H$5,0)</f>
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>6.5</v>
-      </c>
-      <c r="C8" s="1">
-        <f t="shared" si="1"/>
-        <v>5.7200000000000006</v>
-      </c>
-      <c r="D8" s="1">
-        <f>B8*[1]属性总表!$E$5</f>
-        <v>6825</v>
-      </c>
-      <c r="E8" s="1">
-        <f>ROUND([1]等级属性!C8*[1]属性总表!$F$5,0)</f>
-        <v>572</v>
-      </c>
-      <c r="F8" s="1">
-        <f>ROUND(C8*[1]属性总表!$G$5,0)</f>
-        <v>172</v>
-      </c>
-      <c r="G8" s="1">
-        <f>ROUND(C8*[1]属性总表!$H$5,0)</f>
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1">
-        <f t="shared" si="0"/>
-        <v>6.75</v>
-      </c>
-      <c r="C9" s="1">
-        <f t="shared" si="1"/>
-        <v>5.8400000000000007</v>
-      </c>
-      <c r="D9" s="1">
-        <f>B9*[1]属性总表!$E$5</f>
-        <v>7087.5</v>
-      </c>
-      <c r="E9" s="1">
-        <f>ROUND([1]等级属性!C9*[1]属性总表!$F$5,0)</f>
-        <v>584</v>
-      </c>
-      <c r="F9" s="1">
-        <f>ROUND(C9*[1]属性总表!$G$5,0)</f>
-        <v>175</v>
-      </c>
-      <c r="G9" s="1">
-        <f>ROUND(C9*[1]属性总表!$H$5,0)</f>
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C10" s="1">
-        <f t="shared" si="1"/>
-        <v>5.9600000000000009</v>
-      </c>
-      <c r="D10" s="1">
-        <f>B10*[1]属性总表!$E$5</f>
-        <v>7350</v>
-      </c>
-      <c r="E10" s="1">
-        <f>ROUND([1]等级属性!C10*[1]属性总表!$F$5,0)</f>
-        <v>596</v>
-      </c>
-      <c r="F10" s="1">
-        <f>ROUND(C10*[1]属性总表!$G$5,0)</f>
-        <v>179</v>
-      </c>
-      <c r="G10" s="1">
-        <f>ROUND(C10*[1]属性总表!$H$5,0)</f>
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1">
-        <f t="shared" si="0"/>
-        <v>7.25</v>
-      </c>
-      <c r="C11" s="1">
-        <f t="shared" si="1"/>
-        <v>6.080000000000001</v>
-      </c>
-      <c r="D11" s="1">
-        <f>B11*[1]属性总表!$E$5</f>
-        <v>7612.5</v>
-      </c>
-      <c r="E11" s="1">
-        <f>ROUND([1]等级属性!C11*[1]属性总表!$F$5,0)</f>
-        <v>608</v>
-      </c>
-      <c r="F11" s="1">
-        <f>ROUND(C11*[1]属性总表!$G$5,0)</f>
-        <v>182</v>
-      </c>
-      <c r="G11" s="1">
-        <f>ROUND(C11*[1]属性总表!$H$5,0)</f>
-        <v>182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1">
-        <f t="shared" si="0"/>
-        <v>7.5</v>
-      </c>
-      <c r="C12" s="1">
-        <f t="shared" si="1"/>
-        <v>6.2000000000000011</v>
-      </c>
-      <c r="D12" s="1">
-        <f>B12*[1]属性总表!$E$5</f>
-        <v>7875</v>
-      </c>
-      <c r="E12" s="1">
-        <f>ROUND([1]等级属性!C12*[1]属性总表!$F$5,0)</f>
-        <v>620</v>
-      </c>
-      <c r="F12" s="1">
-        <f>ROUND(C12*[1]属性总表!$G$5,0)</f>
-        <v>186</v>
-      </c>
-      <c r="G12" s="1">
-        <f>ROUND(C12*[1]属性总表!$H$5,0)</f>
-        <v>186</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1">
-        <f t="shared" si="0"/>
-        <v>7.75</v>
-      </c>
-      <c r="C13" s="1">
-        <f t="shared" si="1"/>
-        <v>6.3200000000000012</v>
-      </c>
-      <c r="D13" s="1">
-        <f>B13*[1]属性总表!$E$5</f>
-        <v>8137.5</v>
-      </c>
-      <c r="E13" s="1">
-        <f>ROUND([1]等级属性!C13*[1]属性总表!$F$5,0)</f>
-        <v>632</v>
-      </c>
-      <c r="F13" s="1">
-        <f>ROUND(C13*[1]属性总表!$G$5,0)</f>
-        <v>190</v>
-      </c>
-      <c r="G13" s="1">
-        <f>ROUND(C13*[1]属性总表!$H$5,0)</f>
-        <v>190</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C14" s="1">
-        <f t="shared" si="1"/>
-        <v>6.4400000000000013</v>
-      </c>
-      <c r="D14" s="1">
-        <f>B14*[1]属性总表!$E$5</f>
-        <v>8400</v>
-      </c>
-      <c r="E14" s="1">
-        <f>ROUND([1]等级属性!C14*[1]属性总表!$F$5,0)</f>
-        <v>644</v>
-      </c>
-      <c r="F14" s="1">
-        <f>ROUND(C14*[1]属性总表!$G$5,0)</f>
-        <v>193</v>
-      </c>
-      <c r="G14" s="1">
-        <f>ROUND(C14*[1]属性总表!$H$5,0)</f>
-        <v>193</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1">
-        <f t="shared" si="0"/>
-        <v>8.25</v>
-      </c>
-      <c r="C15" s="1">
-        <f t="shared" si="1"/>
-        <v>6.5600000000000014</v>
-      </c>
-      <c r="D15" s="1">
-        <f>B15*[1]属性总表!$E$5</f>
-        <v>8662.5</v>
-      </c>
-      <c r="E15" s="1">
-        <f>ROUND([1]等级属性!C15*[1]属性总表!$F$5,0)</f>
-        <v>656</v>
-      </c>
-      <c r="F15" s="1">
-        <f>ROUND(C15*[1]属性总表!$G$5,0)</f>
-        <v>197</v>
-      </c>
-      <c r="G15" s="1">
-        <f>ROUND(C15*[1]属性总表!$H$5,0)</f>
-        <v>197</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1">
-        <f t="shared" si="0"/>
-        <v>8.5</v>
-      </c>
-      <c r="C16" s="1">
-        <f t="shared" si="1"/>
-        <v>6.6800000000000015</v>
-      </c>
-      <c r="D16" s="1">
-        <f>B16*[1]属性总表!$E$5</f>
-        <v>8925</v>
-      </c>
-      <c r="E16" s="1">
-        <f>ROUND([1]等级属性!C16*[1]属性总表!$F$5,0)</f>
-        <v>668</v>
-      </c>
-      <c r="F16" s="1">
-        <f>ROUND(C16*[1]属性总表!$G$5,0)</f>
-        <v>200</v>
-      </c>
-      <c r="G16" s="1">
-        <f>ROUND(C16*[1]属性总表!$H$5,0)</f>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1">
-        <f t="shared" si="0"/>
-        <v>8.75</v>
-      </c>
-      <c r="C17" s="1">
-        <f t="shared" si="1"/>
-        <v>6.8000000000000016</v>
-      </c>
-      <c r="D17" s="1">
-        <f>B17*[1]属性总表!$E$5</f>
-        <v>9187.5</v>
-      </c>
-      <c r="E17" s="1">
-        <f>ROUND([1]等级属性!C17*[1]属性总表!$F$5,0)</f>
-        <v>680</v>
-      </c>
-      <c r="F17" s="1">
-        <f>ROUND(C17*[1]属性总表!$G$5,0)</f>
-        <v>204</v>
-      </c>
-      <c r="G17" s="1">
-        <f>ROUND(C17*[1]属性总表!$H$5,0)</f>
-        <v>204</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C18" s="1">
-        <f t="shared" si="1"/>
-        <v>6.9200000000000017</v>
-      </c>
-      <c r="D18" s="1">
-        <f>B18*[1]属性总表!$E$5</f>
-        <v>9450</v>
-      </c>
-      <c r="E18" s="1">
-        <f>ROUND([1]等级属性!C18*[1]属性总表!$F$5,0)</f>
-        <v>692</v>
-      </c>
-      <c r="F18" s="1">
-        <f>ROUND(C18*[1]属性总表!$G$5,0)</f>
-        <v>208</v>
-      </c>
-      <c r="G18" s="1">
-        <f>ROUND(C18*[1]属性总表!$H$5,0)</f>
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1">
-        <f t="shared" si="0"/>
-        <v>9.25</v>
-      </c>
-      <c r="C19" s="1">
-        <f t="shared" si="1"/>
-        <v>7.0400000000000018</v>
-      </c>
-      <c r="D19" s="1">
-        <f>B19*[1]属性总表!$E$5</f>
-        <v>9712.5</v>
-      </c>
-      <c r="E19" s="1">
-        <f>ROUND([1]等级属性!C19*[1]属性总表!$F$5,0)</f>
-        <v>704</v>
-      </c>
-      <c r="F19" s="1">
-        <f>ROUND(C19*[1]属性总表!$G$5,0)</f>
-        <v>211</v>
-      </c>
-      <c r="G19" s="1">
-        <f>ROUND(C19*[1]属性总表!$H$5,0)</f>
-        <v>211</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>9.5</v>
-      </c>
-      <c r="C20" s="1">
-        <f t="shared" si="1"/>
-        <v>7.1600000000000019</v>
-      </c>
-      <c r="D20" s="1">
-        <f>B20*[1]属性总表!$E$5</f>
-        <v>9975</v>
-      </c>
-      <c r="E20" s="1">
-        <f>ROUND([1]等级属性!C20*[1]属性总表!$F$5,0)</f>
-        <v>716</v>
-      </c>
-      <c r="F20" s="1">
-        <f>ROUND(C20*[1]属性总表!$G$5,0)</f>
-        <v>215</v>
-      </c>
-      <c r="G20" s="1">
-        <f>ROUND(C20*[1]属性总表!$H$5,0)</f>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1">
-        <f t="shared" si="0"/>
-        <v>9.75</v>
-      </c>
-      <c r="C21" s="1">
-        <f t="shared" si="1"/>
-        <v>7.280000000000002</v>
-      </c>
-      <c r="D21" s="1">
-        <f>B21*[1]属性总表!$E$5</f>
-        <v>10237.5</v>
-      </c>
-      <c r="E21" s="1">
-        <f>ROUND([1]等级属性!C21*[1]属性总表!$F$5,0)</f>
-        <v>728</v>
-      </c>
-      <c r="F21" s="1">
-        <f>ROUND(C21*[1]属性总表!$G$5,0)</f>
-        <v>218</v>
-      </c>
-      <c r="G21" s="1">
-        <f>ROUND(C21*[1]属性总表!$H$5,0)</f>
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C22" s="1">
-        <f t="shared" si="1"/>
-        <v>7.4000000000000021</v>
-      </c>
-      <c r="D22" s="1">
-        <f>B22*[1]属性总表!$E$5</f>
-        <v>10500</v>
-      </c>
-      <c r="E22" s="1">
-        <f>ROUND([1]等级属性!C22*[1]属性总表!$F$5,0)</f>
-        <v>740</v>
-      </c>
-      <c r="F22" s="1">
-        <f>ROUND(C22*[1]属性总表!$G$5,0)</f>
-        <v>222</v>
-      </c>
-      <c r="G22" s="1">
-        <f>ROUND(C22*[1]属性总表!$H$5,0)</f>
-        <v>222</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="1">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1">
-        <f t="shared" si="0"/>
-        <v>10.25</v>
-      </c>
-      <c r="C23" s="1">
-        <f t="shared" si="1"/>
-        <v>7.5200000000000022</v>
-      </c>
-      <c r="D23" s="1">
-        <f>B23*[1]属性总表!$E$5</f>
-        <v>10762.5</v>
-      </c>
-      <c r="E23" s="1">
-        <f>ROUND([1]等级属性!C23*[1]属性总表!$F$5,0)</f>
-        <v>752</v>
-      </c>
-      <c r="F23" s="1">
-        <f>ROUND(C23*[1]属性总表!$G$5,0)</f>
-        <v>226</v>
-      </c>
-      <c r="G23" s="1">
-        <f>ROUND(C23*[1]属性总表!$H$5,0)</f>
-        <v>226</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="1">
-        <v>23</v>
-      </c>
-      <c r="B24" s="1">
-        <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="C24" s="1">
-        <f t="shared" si="1"/>
-        <v>7.6400000000000023</v>
-      </c>
-      <c r="D24" s="1">
-        <f>B24*[1]属性总表!$E$5</f>
-        <v>11025</v>
-      </c>
-      <c r="E24" s="1">
-        <f>ROUND([1]等级属性!C24*[1]属性总表!$F$5,0)</f>
-        <v>764</v>
-      </c>
-      <c r="F24" s="1">
-        <f>ROUND(C24*[1]属性总表!$G$5,0)</f>
-        <v>229</v>
-      </c>
-      <c r="G24" s="1">
-        <f>ROUND(C24*[1]属性总表!$H$5,0)</f>
-        <v>229</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1">
-        <f t="shared" si="0"/>
-        <v>10.75</v>
-      </c>
-      <c r="C25" s="1">
-        <f t="shared" si="1"/>
-        <v>7.7600000000000025</v>
-      </c>
-      <c r="D25" s="1">
-        <f>B25*[1]属性总表!$E$5</f>
-        <v>11287.5</v>
-      </c>
-      <c r="E25" s="1">
-        <f>ROUND([1]等级属性!C25*[1]属性总表!$F$5,0)</f>
-        <v>776</v>
-      </c>
-      <c r="F25" s="1">
-        <f>ROUND(C25*[1]属性总表!$G$5,0)</f>
-        <v>233</v>
-      </c>
-      <c r="G25" s="1">
-        <f>ROUND(C25*[1]属性总表!$H$5,0)</f>
-        <v>233</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="1">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C26" s="1">
-        <f t="shared" si="1"/>
-        <v>7.8800000000000026</v>
-      </c>
-      <c r="D26" s="1">
-        <f>B26*[1]属性总表!$E$5</f>
-        <v>11550</v>
-      </c>
-      <c r="E26" s="1">
-        <f>ROUND([1]等级属性!C26*[1]属性总表!$F$5,0)</f>
-        <v>788</v>
-      </c>
-      <c r="F26" s="1">
-        <f>ROUND(C26*[1]属性总表!$G$5,0)</f>
-        <v>236</v>
-      </c>
-      <c r="G26" s="1">
-        <f>ROUND(C26*[1]属性总表!$H$5,0)</f>
-        <v>236</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="1">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1">
-        <f t="shared" si="0"/>
-        <v>11.25</v>
-      </c>
-      <c r="C27" s="1">
-        <f t="shared" si="1"/>
-        <v>8.0000000000000018</v>
-      </c>
-      <c r="D27" s="1">
-        <f>B27*[1]属性总表!$E$5</f>
-        <v>11812.5</v>
-      </c>
-      <c r="E27" s="1">
-        <f>ROUND([1]等级属性!C27*[1]属性总表!$F$5,0)</f>
-        <v>800</v>
-      </c>
-      <c r="F27" s="1">
-        <f>ROUND(C27*[1]属性总表!$G$5,0)</f>
-        <v>240</v>
-      </c>
-      <c r="G27" s="1">
-        <f>ROUND(C27*[1]属性总表!$H$5,0)</f>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="1">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1">
-        <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="C28" s="1">
-        <f t="shared" si="1"/>
-        <v>8.120000000000001</v>
-      </c>
-      <c r="D28" s="1">
-        <f>B28*[1]属性总表!$E$5</f>
-        <v>12075</v>
-      </c>
-      <c r="E28" s="1">
-        <f>ROUND([1]等级属性!C28*[1]属性总表!$F$5,0)</f>
-        <v>812</v>
-      </c>
-      <c r="F28" s="1">
-        <f>ROUND(C28*[1]属性总表!$G$5,0)</f>
-        <v>244</v>
-      </c>
-      <c r="G28" s="1">
-        <f>ROUND(C28*[1]属性总表!$H$5,0)</f>
-        <v>244</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="1">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1">
-        <f t="shared" si="0"/>
-        <v>11.75</v>
-      </c>
-      <c r="C29" s="1">
-        <f t="shared" si="1"/>
-        <v>8.24</v>
-      </c>
-      <c r="D29" s="1">
-        <f>B29*[1]属性总表!$E$5</f>
-        <v>12337.5</v>
-      </c>
-      <c r="E29" s="1">
-        <f>ROUND([1]等级属性!C29*[1]属性总表!$F$5,0)</f>
-        <v>824</v>
-      </c>
-      <c r="F29" s="1">
-        <f>ROUND(C29*[1]属性总表!$G$5,0)</f>
-        <v>247</v>
-      </c>
-      <c r="G29" s="1">
-        <f>ROUND(C29*[1]属性总表!$H$5,0)</f>
-        <v>247</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="1">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C30" s="1">
-        <f t="shared" si="1"/>
-        <v>8.36</v>
-      </c>
-      <c r="D30" s="1">
-        <f>B30*[1]属性总表!$E$5</f>
-        <v>12600</v>
-      </c>
-      <c r="E30" s="1">
-        <f>ROUND([1]等级属性!C30*[1]属性总表!$F$5,0)</f>
-        <v>836</v>
-      </c>
-      <c r="F30" s="1">
-        <f>ROUND(C30*[1]属性总表!$G$5,0)</f>
-        <v>251</v>
-      </c>
-      <c r="G30" s="1">
-        <f>ROUND(C30*[1]属性总表!$H$5,0)</f>
-        <v>251</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="1">
-        <v>30</v>
-      </c>
-      <c r="B31" s="1">
-        <f t="shared" si="0"/>
-        <v>12.25</v>
-      </c>
-      <c r="C31" s="1">
-        <f t="shared" si="1"/>
-        <v>8.4799999999999986</v>
-      </c>
-      <c r="D31" s="1">
-        <f>B31*[1]属性总表!$E$5</f>
-        <v>12862.5</v>
-      </c>
-      <c r="E31" s="1">
-        <f>ROUND([1]等级属性!C31*[1]属性总表!$F$5,0)</f>
-        <v>848</v>
-      </c>
-      <c r="F31" s="1">
-        <f>ROUND(C31*[1]属性总表!$G$5,0)</f>
-        <v>254</v>
-      </c>
-      <c r="G31" s="1">
-        <f>ROUND(C31*[1]属性总表!$H$5,0)</f>
-        <v>254</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="1">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1">
-        <f t="shared" si="0"/>
-        <v>12.5</v>
-      </c>
-      <c r="C32" s="1">
-        <f t="shared" si="1"/>
-        <v>8.5999999999999979</v>
-      </c>
-      <c r="D32" s="1">
-        <f>B32*[1]属性总表!$E$5</f>
-        <v>13125</v>
-      </c>
-      <c r="E32" s="1">
-        <f>ROUND([1]等级属性!C32*[1]属性总表!$F$5,0)</f>
-        <v>860</v>
-      </c>
-      <c r="F32" s="1">
-        <f>ROUND(C32*[1]属性总表!$G$5,0)</f>
-        <v>258</v>
-      </c>
-      <c r="G32" s="1">
-        <f>ROUND(C32*[1]属性总表!$H$5,0)</f>
-        <v>258</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="1">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1">
-        <f t="shared" si="0"/>
-        <v>12.75</v>
-      </c>
-      <c r="C33" s="1">
-        <f t="shared" si="1"/>
-        <v>8.7199999999999971</v>
-      </c>
-      <c r="D33" s="1">
-        <f>B33*[1]属性总表!$E$5</f>
-        <v>13387.5</v>
-      </c>
-      <c r="E33" s="1">
-        <f>ROUND([1]等级属性!C33*[1]属性总表!$F$5,0)</f>
-        <v>872</v>
-      </c>
-      <c r="F33" s="1">
-        <f>ROUND(C33*[1]属性总表!$G$5,0)</f>
-        <v>262</v>
-      </c>
-      <c r="G33" s="1">
-        <f>ROUND(C33*[1]属性总表!$H$5,0)</f>
-        <v>262</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="1">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="C34" s="1">
-        <f t="shared" si="1"/>
-        <v>8.8399999999999963</v>
-      </c>
-      <c r="D34" s="1">
-        <f>B34*[1]属性总表!$E$5</f>
-        <v>13650</v>
-      </c>
-      <c r="E34" s="1">
-        <f>ROUND([1]等级属性!C34*[1]属性总表!$F$5,0)</f>
-        <v>884</v>
-      </c>
-      <c r="F34" s="1">
-        <f>ROUND(C34*[1]属性总表!$G$5,0)</f>
-        <v>265</v>
-      </c>
-      <c r="G34" s="1">
-        <f>ROUND(C34*[1]属性总表!$H$5,0)</f>
-        <v>265</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="1">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1">
-        <f t="shared" si="0"/>
-        <v>13.25</v>
-      </c>
-      <c r="C35" s="1">
-        <f t="shared" si="1"/>
-        <v>8.9599999999999955</v>
-      </c>
-      <c r="D35" s="1">
-        <f>B35*[1]属性总表!$E$5</f>
-        <v>13912.5</v>
-      </c>
-      <c r="E35" s="1">
-        <f>ROUND([1]等级属性!C35*[1]属性总表!$F$5,0)</f>
-        <v>896</v>
-      </c>
-      <c r="F35" s="1">
-        <f>ROUND(C35*[1]属性总表!$G$5,0)</f>
-        <v>269</v>
-      </c>
-      <c r="G35" s="1">
-        <f>ROUND(C35*[1]属性总表!$H$5,0)</f>
-        <v>269</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="1">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1">
-        <f t="shared" si="0"/>
-        <v>13.5</v>
-      </c>
-      <c r="C36" s="1">
-        <f t="shared" si="1"/>
-        <v>9.0799999999999947</v>
-      </c>
-      <c r="D36" s="1">
-        <f>B36*[1]属性总表!$E$5</f>
-        <v>14175</v>
-      </c>
-      <c r="E36" s="1">
-        <f>ROUND([1]等级属性!C36*[1]属性总表!$F$5,0)</f>
-        <v>908</v>
-      </c>
-      <c r="F36" s="1">
-        <f>ROUND(C36*[1]属性总表!$G$5,0)</f>
-        <v>272</v>
-      </c>
-      <c r="G36" s="1">
-        <f>ROUND(C36*[1]属性总表!$H$5,0)</f>
-        <v>272</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="1">
-        <v>36</v>
-      </c>
-      <c r="B37" s="1">
-        <f t="shared" si="0"/>
-        <v>13.75</v>
-      </c>
-      <c r="C37" s="1">
-        <f t="shared" si="1"/>
-        <v>9.199999999999994</v>
-      </c>
-      <c r="D37" s="1">
-        <f>B37*[1]属性总表!$E$5</f>
-        <v>14437.5</v>
-      </c>
-      <c r="E37" s="1">
-        <f>ROUND([1]等级属性!C37*[1]属性总表!$F$5,0)</f>
-        <v>920</v>
-      </c>
-      <c r="F37" s="1">
-        <f>ROUND(C37*[1]属性总表!$G$5,0)</f>
-        <v>276</v>
-      </c>
-      <c r="G37" s="1">
-        <f>ROUND(C37*[1]属性总表!$H$5,0)</f>
-        <v>276</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="1">
-        <v>37</v>
-      </c>
-      <c r="B38" s="1">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C38" s="1">
-        <f t="shared" si="1"/>
-        <v>9.3199999999999932</v>
-      </c>
-      <c r="D38" s="1">
-        <f>B38*[1]属性总表!$E$5</f>
-        <v>14700</v>
-      </c>
-      <c r="E38" s="1">
-        <f>ROUND([1]等级属性!C38*[1]属性总表!$F$5,0)</f>
-        <v>932</v>
-      </c>
-      <c r="F38" s="1">
-        <f>ROUND(C38*[1]属性总表!$G$5,0)</f>
-        <v>280</v>
-      </c>
-      <c r="G38" s="1">
-        <f>ROUND(C38*[1]属性总表!$H$5,0)</f>
-        <v>280</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="1">
-        <v>38</v>
-      </c>
-      <c r="B39" s="1">
-        <f t="shared" si="0"/>
-        <v>14.25</v>
-      </c>
-      <c r="C39" s="1">
-        <f t="shared" si="1"/>
-        <v>9.4399999999999924</v>
-      </c>
-      <c r="D39" s="1">
-        <f>B39*[1]属性总表!$E$5</f>
-        <v>14962.5</v>
-      </c>
-      <c r="E39" s="1">
-        <f>ROUND([1]等级属性!C39*[1]属性总表!$F$5,0)</f>
-        <v>944</v>
-      </c>
-      <c r="F39" s="1">
-        <f>ROUND(C39*[1]属性总表!$G$5,0)</f>
-        <v>283</v>
-      </c>
-      <c r="G39" s="1">
-        <f>ROUND(C39*[1]属性总表!$H$5,0)</f>
-        <v>283</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="1">
-        <v>39</v>
-      </c>
-      <c r="B40" s="1">
-        <f t="shared" si="0"/>
-        <v>14.5</v>
-      </c>
-      <c r="C40" s="1">
-        <f t="shared" si="1"/>
-        <v>9.5599999999999916</v>
-      </c>
-      <c r="D40" s="1">
-        <f>B40*[1]属性总表!$E$5</f>
-        <v>15225</v>
-      </c>
-      <c r="E40" s="1">
-        <f>ROUND([1]等级属性!C40*[1]属性总表!$F$5,0)</f>
-        <v>956</v>
-      </c>
-      <c r="F40" s="1">
-        <f>ROUND(C40*[1]属性总表!$G$5,0)</f>
-        <v>287</v>
-      </c>
-      <c r="G40" s="1">
-        <f>ROUND(C40*[1]属性总表!$H$5,0)</f>
-        <v>287</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="1">
-        <v>40</v>
-      </c>
-      <c r="B41" s="1">
-        <f t="shared" si="0"/>
-        <v>14.75</v>
-      </c>
-      <c r="C41" s="1">
-        <f t="shared" si="1"/>
-        <v>9.6799999999999908</v>
-      </c>
-      <c r="D41" s="1">
-        <f>B41*[1]属性总表!$E$5</f>
-        <v>15487.5</v>
-      </c>
-      <c r="E41" s="1">
-        <f>ROUND([1]等级属性!C41*[1]属性总表!$F$5,0)</f>
-        <v>968</v>
-      </c>
-      <c r="F41" s="1">
-        <f>ROUND(C41*[1]属性总表!$G$5,0)</f>
-        <v>290</v>
-      </c>
-      <c r="G41" s="1">
-        <f>ROUND(C41*[1]属性总表!$H$5,0)</f>
-        <v>290</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="1">
-        <v>41</v>
-      </c>
-      <c r="B42" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C42" s="1">
-        <f t="shared" si="1"/>
-        <v>9.7999999999999901</v>
-      </c>
-      <c r="D42" s="1">
-        <f>B42*[1]属性总表!$E$5</f>
-        <v>15750</v>
-      </c>
-      <c r="E42" s="1">
-        <f>ROUND([1]等级属性!C42*[1]属性总表!$F$5,0)</f>
-        <v>980</v>
-      </c>
-      <c r="F42" s="1">
-        <f>ROUND(C42*[1]属性总表!$G$5,0)</f>
-        <v>294</v>
-      </c>
-      <c r="G42" s="1">
-        <f>ROUND(C42*[1]属性总表!$H$5,0)</f>
-        <v>294</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="1">
-        <v>42</v>
-      </c>
-      <c r="B43" s="1">
-        <f t="shared" si="0"/>
-        <v>15.25</v>
-      </c>
-      <c r="C43" s="1">
-        <f t="shared" si="1"/>
-        <v>9.9199999999999893</v>
-      </c>
-      <c r="D43" s="1">
-        <f>B43*[1]属性总表!$E$5</f>
-        <v>16012.5</v>
-      </c>
-      <c r="E43" s="1">
-        <f>ROUND([1]等级属性!C43*[1]属性总表!$F$5,0)</f>
-        <v>992</v>
-      </c>
-      <c r="F43" s="1">
-        <f>ROUND(C43*[1]属性总表!$G$5,0)</f>
-        <v>298</v>
-      </c>
-      <c r="G43" s="1">
-        <f>ROUND(C43*[1]属性总表!$H$5,0)</f>
-        <v>298</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="1">
-        <v>43</v>
-      </c>
-      <c r="B44" s="1">
-        <f t="shared" si="0"/>
-        <v>15.5</v>
-      </c>
-      <c r="C44" s="1">
-        <f t="shared" si="1"/>
-        <v>10.039999999999988</v>
-      </c>
-      <c r="D44" s="1">
-        <f>B44*[1]属性总表!$E$5</f>
-        <v>16275</v>
-      </c>
-      <c r="E44" s="1">
-        <f>ROUND([1]等级属性!C44*[1]属性总表!$F$5,0)</f>
-        <v>1004</v>
-      </c>
-      <c r="F44" s="1">
-        <f>ROUND(C44*[1]属性总表!$G$5,0)</f>
-        <v>301</v>
-      </c>
-      <c r="G44" s="1">
-        <f>ROUND(C44*[1]属性总表!$H$5,0)</f>
-        <v>301</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="1">
-        <v>44</v>
-      </c>
-      <c r="B45" s="1">
-        <f t="shared" si="0"/>
-        <v>15.75</v>
-      </c>
-      <c r="C45" s="1">
-        <f t="shared" si="1"/>
-        <v>10.159999999999988</v>
-      </c>
-      <c r="D45" s="1">
-        <f>B45*[1]属性总表!$E$5</f>
-        <v>16537.5</v>
-      </c>
-      <c r="E45" s="1">
-        <f>ROUND([1]等级属性!C45*[1]属性总表!$F$5,0)</f>
-        <v>1016</v>
-      </c>
-      <c r="F45" s="1">
-        <f>ROUND(C45*[1]属性总表!$G$5,0)</f>
-        <v>305</v>
-      </c>
-      <c r="G45" s="1">
-        <f>ROUND(C45*[1]属性总表!$H$5,0)</f>
-        <v>305</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="1">
-        <v>45</v>
-      </c>
-      <c r="B46" s="1">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C46" s="1">
-        <f t="shared" si="1"/>
-        <v>10.279999999999987</v>
-      </c>
-      <c r="D46" s="1">
-        <f>B46*[1]属性总表!$E$5</f>
-        <v>16800</v>
-      </c>
-      <c r="E46" s="1">
-        <f>ROUND([1]等级属性!C46*[1]属性总表!$F$5,0)</f>
-        <v>1028</v>
-      </c>
-      <c r="F46" s="1">
-        <f>ROUND(C46*[1]属性总表!$G$5,0)</f>
-        <v>308</v>
-      </c>
-      <c r="G46" s="1">
-        <f>ROUND(C46*[1]属性总表!$H$5,0)</f>
-        <v>308</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="1">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1">
-        <f t="shared" si="0"/>
-        <v>16.25</v>
-      </c>
-      <c r="C47" s="1">
-        <f t="shared" si="1"/>
-        <v>10.399999999999986</v>
-      </c>
-      <c r="D47" s="1">
-        <f>B47*[1]属性总表!$E$5</f>
-        <v>17062.5</v>
-      </c>
-      <c r="E47" s="1">
-        <f>ROUND([1]等级属性!C47*[1]属性总表!$F$5,0)</f>
-        <v>1040</v>
-      </c>
-      <c r="F47" s="1">
-        <f>ROUND(C47*[1]属性总表!$G$5,0)</f>
-        <v>312</v>
-      </c>
-      <c r="G47" s="1">
-        <f>ROUND(C47*[1]属性总表!$H$5,0)</f>
-        <v>312</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="1">
-        <v>47</v>
-      </c>
-      <c r="B48" s="1">
-        <f t="shared" si="0"/>
-        <v>16.5</v>
-      </c>
-      <c r="C48" s="1">
-        <f t="shared" si="1"/>
-        <v>10.519999999999985</v>
-      </c>
-      <c r="D48" s="1">
-        <f>B48*[1]属性总表!$E$5</f>
-        <v>17325</v>
-      </c>
-      <c r="E48" s="1">
-        <f>ROUND([1]等级属性!C48*[1]属性总表!$F$5,0)</f>
-        <v>1052</v>
-      </c>
-      <c r="F48" s="1">
-        <f>ROUND(C48*[1]属性总表!$G$5,0)</f>
-        <v>316</v>
-      </c>
-      <c r="G48" s="1">
-        <f>ROUND(C48*[1]属性总表!$H$5,0)</f>
-        <v>316</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="1">
-        <v>48</v>
-      </c>
-      <c r="B49" s="1">
-        <f t="shared" si="0"/>
-        <v>16.75</v>
-      </c>
-      <c r="C49" s="1">
-        <f t="shared" si="1"/>
-        <v>10.639999999999985</v>
-      </c>
-      <c r="D49" s="1">
-        <f>B49*[1]属性总表!$E$5</f>
-        <v>17587.5</v>
-      </c>
-      <c r="E49" s="1">
-        <f>ROUND([1]等级属性!C49*[1]属性总表!$F$5,0)</f>
-        <v>1064</v>
-      </c>
-      <c r="F49" s="1">
-        <f>ROUND(C49*[1]属性总表!$G$5,0)</f>
-        <v>319</v>
-      </c>
-      <c r="G49" s="1">
-        <f>ROUND(C49*[1]属性总表!$H$5,0)</f>
-        <v>319</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="1">
-        <v>49</v>
-      </c>
-      <c r="B50" s="1">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C50" s="1">
-        <f t="shared" si="1"/>
-        <v>10.759999999999984</v>
-      </c>
-      <c r="D50" s="1">
-        <f>B50*[1]属性总表!$E$5</f>
-        <v>17850</v>
-      </c>
-      <c r="E50" s="1">
-        <f>ROUND([1]等级属性!C50*[1]属性总表!$F$5,0)</f>
-        <v>1076</v>
-      </c>
-      <c r="F50" s="1">
-        <f>ROUND(C50*[1]属性总表!$G$5,0)</f>
-        <v>323</v>
-      </c>
-      <c r="G50" s="1">
-        <f>ROUND(C50*[1]属性总表!$H$5,0)</f>
-        <v>323</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="1">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1">
-        <f t="shared" si="0"/>
-        <v>17.25</v>
-      </c>
-      <c r="C51" s="1">
-        <f t="shared" si="1"/>
-        <v>10.879999999999983</v>
-      </c>
-      <c r="D51" s="1">
-        <f>B51*[1]属性总表!$E$5</f>
-        <v>18112.5</v>
-      </c>
-      <c r="E51" s="1">
-        <f>ROUND([1]等级属性!C51*[1]属性总表!$F$5,0)</f>
-        <v>1088</v>
-      </c>
-      <c r="F51" s="1">
-        <f>ROUND(C51*[1]属性总表!$G$5,0)</f>
-        <v>326</v>
-      </c>
-      <c r="G51" s="1">
-        <f>ROUND(C51*[1]属性总表!$H$5,0)</f>
-        <v>326</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="1">
-        <v>51</v>
-      </c>
-      <c r="B52" s="1">
-        <f t="shared" si="0"/>
-        <v>17.5</v>
-      </c>
-      <c r="C52" s="1">
-        <f t="shared" si="1"/>
-        <v>10.999999999999982</v>
-      </c>
-      <c r="D52" s="1">
-        <f>B52*[1]属性总表!$E$5</f>
-        <v>18375</v>
-      </c>
-      <c r="E52" s="1">
-        <f>ROUND([1]等级属性!C52*[1]属性总表!$F$5,0)</f>
-        <v>1100</v>
-      </c>
-      <c r="F52" s="1">
-        <f>ROUND(C52*[1]属性总表!$G$5,0)</f>
-        <v>330</v>
-      </c>
-      <c r="G52" s="1">
-        <f>ROUND(C52*[1]属性总表!$H$5,0)</f>
-        <v>330</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="1">
-        <v>52</v>
-      </c>
-      <c r="B53" s="1">
-        <f t="shared" si="0"/>
-        <v>17.75</v>
-      </c>
-      <c r="C53" s="1">
-        <f t="shared" si="1"/>
-        <v>11.119999999999981</v>
-      </c>
-      <c r="D53" s="1">
-        <f>B53*[1]属性总表!$E$5</f>
-        <v>18637.5</v>
-      </c>
-      <c r="E53" s="1">
-        <f>ROUND([1]等级属性!C53*[1]属性总表!$F$5,0)</f>
-        <v>1112</v>
-      </c>
-      <c r="F53" s="1">
-        <f>ROUND(C53*[1]属性总表!$G$5,0)</f>
-        <v>334</v>
-      </c>
-      <c r="G53" s="1">
-        <f>ROUND(C53*[1]属性总表!$H$5,0)</f>
-        <v>334</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="1">
-        <v>53</v>
-      </c>
-      <c r="B54" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="C54" s="1">
-        <f t="shared" si="1"/>
-        <v>11.239999999999981</v>
-      </c>
-      <c r="D54" s="1">
-        <f>B54*[1]属性总表!$E$5</f>
-        <v>18900</v>
-      </c>
-      <c r="E54" s="1">
-        <f>ROUND([1]等级属性!C54*[1]属性总表!$F$5,0)</f>
-        <v>1124</v>
-      </c>
-      <c r="F54" s="1">
-        <f>ROUND(C54*[1]属性总表!$G$5,0)</f>
-        <v>337</v>
-      </c>
-      <c r="G54" s="1">
-        <f>ROUND(C54*[1]属性总表!$H$5,0)</f>
-        <v>337</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="1">
-        <v>54</v>
-      </c>
-      <c r="B55" s="1">
-        <f t="shared" si="0"/>
-        <v>18.25</v>
-      </c>
-      <c r="C55" s="1">
-        <f t="shared" si="1"/>
-        <v>11.35999999999998</v>
-      </c>
-      <c r="D55" s="1">
-        <f>B55*[1]属性总表!$E$5</f>
-        <v>19162.5</v>
-      </c>
-      <c r="E55" s="1">
-        <f>ROUND([1]等级属性!C55*[1]属性总表!$F$5,0)</f>
-        <v>1136</v>
-      </c>
-      <c r="F55" s="1">
-        <f>ROUND(C55*[1]属性总表!$G$5,0)</f>
-        <v>341</v>
-      </c>
-      <c r="G55" s="1">
-        <f>ROUND(C55*[1]属性总表!$H$5,0)</f>
-        <v>341</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="1">
-        <v>55</v>
-      </c>
-      <c r="B56" s="1">
-        <f t="shared" si="0"/>
-        <v>18.5</v>
-      </c>
-      <c r="C56" s="1">
-        <f t="shared" si="1"/>
-        <v>11.479999999999979</v>
-      </c>
-      <c r="D56" s="1">
-        <f>B56*[1]属性总表!$E$5</f>
-        <v>19425</v>
-      </c>
-      <c r="E56" s="1">
-        <f>ROUND([1]等级属性!C56*[1]属性总表!$F$5,0)</f>
-        <v>1148</v>
-      </c>
-      <c r="F56" s="1">
-        <f>ROUND(C56*[1]属性总表!$G$5,0)</f>
-        <v>344</v>
-      </c>
-      <c r="G56" s="1">
-        <f>ROUND(C56*[1]属性总表!$H$5,0)</f>
-        <v>344</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="1">
-        <v>56</v>
-      </c>
-      <c r="B57" s="1">
-        <f t="shared" si="0"/>
-        <v>18.75</v>
-      </c>
-      <c r="C57" s="1">
-        <f t="shared" si="1"/>
-        <v>11.599999999999978</v>
-      </c>
-      <c r="D57" s="1">
-        <f>B57*[1]属性总表!$E$5</f>
-        <v>19687.5</v>
-      </c>
-      <c r="E57" s="1">
-        <f>ROUND([1]等级属性!C57*[1]属性总表!$F$5,0)</f>
-        <v>1160</v>
-      </c>
-      <c r="F57" s="1">
-        <f>ROUND(C57*[1]属性总表!$G$5,0)</f>
-        <v>348</v>
-      </c>
-      <c r="G57" s="1">
-        <f>ROUND(C57*[1]属性总表!$H$5,0)</f>
-        <v>348</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="1">
-        <v>57</v>
-      </c>
-      <c r="B58" s="1">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C58" s="1">
-        <f t="shared" si="1"/>
-        <v>11.719999999999978</v>
-      </c>
-      <c r="D58" s="1">
-        <f>B58*[1]属性总表!$E$5</f>
-        <v>19950</v>
-      </c>
-      <c r="E58" s="1">
-        <f>ROUND([1]等级属性!C58*[1]属性总表!$F$5,0)</f>
-        <v>1172</v>
-      </c>
-      <c r="F58" s="1">
-        <f>ROUND(C58*[1]属性总表!$G$5,0)</f>
-        <v>352</v>
-      </c>
-      <c r="G58" s="1">
-        <f>ROUND(C58*[1]属性总表!$H$5,0)</f>
-        <v>352</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="1">
-        <v>58</v>
-      </c>
-      <c r="B59" s="1">
-        <f t="shared" si="0"/>
-        <v>19.25</v>
-      </c>
-      <c r="C59" s="1">
-        <f t="shared" si="1"/>
-        <v>11.839999999999977</v>
-      </c>
-      <c r="D59" s="1">
-        <f>B59*[1]属性总表!$E$5</f>
-        <v>20212.5</v>
-      </c>
-      <c r="E59" s="1">
-        <f>ROUND([1]等级属性!C59*[1]属性总表!$F$5,0)</f>
-        <v>1184</v>
-      </c>
-      <c r="F59" s="1">
-        <f>ROUND(C59*[1]属性总表!$G$5,0)</f>
-        <v>355</v>
-      </c>
-      <c r="G59" s="1">
-        <f>ROUND(C59*[1]属性总表!$H$5,0)</f>
-        <v>355</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="1">
-        <v>59</v>
-      </c>
-      <c r="B60" s="1">
-        <f t="shared" si="0"/>
-        <v>19.5</v>
-      </c>
-      <c r="C60" s="1">
-        <f t="shared" si="1"/>
-        <v>11.959999999999976</v>
-      </c>
-      <c r="D60" s="1">
-        <f>B60*[1]属性总表!$E$5</f>
-        <v>20475</v>
-      </c>
-      <c r="E60" s="1">
-        <f>ROUND([1]等级属性!C60*[1]属性总表!$F$5,0)</f>
-        <v>1196</v>
-      </c>
-      <c r="F60" s="1">
-        <f>ROUND(C60*[1]属性总表!$G$5,0)</f>
-        <v>359</v>
-      </c>
-      <c r="G60" s="1">
-        <f>ROUND(C60*[1]属性总表!$H$5,0)</f>
-        <v>359</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="1">
-        <v>60</v>
-      </c>
-      <c r="B61" s="1">
-        <f t="shared" si="0"/>
-        <v>19.75</v>
-      </c>
-      <c r="C61" s="1">
-        <f t="shared" si="1"/>
-        <v>12.079999999999975</v>
-      </c>
-      <c r="D61" s="1">
-        <f>B61*[1]属性总表!$E$5</f>
-        <v>20737.5</v>
-      </c>
-      <c r="E61" s="1">
-        <f>ROUND([1]等级属性!C61*[1]属性总表!$F$5,0)</f>
-        <v>1208</v>
-      </c>
-      <c r="F61" s="1">
-        <f>ROUND(C61*[1]属性总表!$G$5,0)</f>
-        <v>362</v>
-      </c>
-      <c r="G61" s="1">
-        <f>ROUND(C61*[1]属性总表!$H$5,0)</f>
-        <v>362</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="1">
-        <v>61</v>
-      </c>
-      <c r="B62" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="C62" s="1">
-        <f t="shared" si="1"/>
-        <v>12.199999999999974</v>
-      </c>
-      <c r="D62" s="1">
-        <f>B62*[1]属性总表!$E$5</f>
-        <v>21000</v>
-      </c>
-      <c r="E62" s="1">
-        <f>ROUND([1]等级属性!C62*[1]属性总表!$F$5,0)</f>
-        <v>1220</v>
-      </c>
-      <c r="F62" s="1">
-        <f>ROUND(C62*[1]属性总表!$G$5,0)</f>
-        <v>366</v>
-      </c>
-      <c r="G62" s="1">
-        <f>ROUND(C62*[1]属性总表!$H$5,0)</f>
-        <v>366</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="1">
-        <v>62</v>
-      </c>
-      <c r="B63" s="1">
-        <f t="shared" si="0"/>
-        <v>20.25</v>
-      </c>
-      <c r="C63" s="1">
-        <f t="shared" si="1"/>
-        <v>12.319999999999974</v>
-      </c>
-      <c r="D63" s="1">
-        <f>B63*[1]属性总表!$E$5</f>
-        <v>21262.5</v>
-      </c>
-      <c r="E63" s="1">
-        <f>ROUND([1]等级属性!C63*[1]属性总表!$F$5,0)</f>
-        <v>1232</v>
-      </c>
-      <c r="F63" s="1">
-        <f>ROUND(C63*[1]属性总表!$G$5,0)</f>
-        <v>370</v>
-      </c>
-      <c r="G63" s="1">
-        <f>ROUND(C63*[1]属性总表!$H$5,0)</f>
-        <v>370</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="1">
-        <v>63</v>
-      </c>
-      <c r="B64" s="1">
-        <f t="shared" si="0"/>
-        <v>20.5</v>
-      </c>
-      <c r="C64" s="1">
-        <f t="shared" si="1"/>
-        <v>12.439999999999973</v>
-      </c>
-      <c r="D64" s="1">
-        <f>B64*[1]属性总表!$E$5</f>
-        <v>21525</v>
-      </c>
-      <c r="E64" s="1">
-        <f>ROUND([1]等级属性!C64*[1]属性总表!$F$5,0)</f>
-        <v>1244</v>
-      </c>
-      <c r="F64" s="1">
-        <f>ROUND(C64*[1]属性总表!$G$5,0)</f>
-        <v>373</v>
-      </c>
-      <c r="G64" s="1">
-        <f>ROUND(C64*[1]属性总表!$H$5,0)</f>
-        <v>373</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="1">
-        <v>64</v>
-      </c>
-      <c r="B65" s="1">
-        <f t="shared" si="0"/>
-        <v>20.75</v>
-      </c>
-      <c r="C65" s="1">
-        <f t="shared" si="1"/>
-        <v>12.559999999999972</v>
-      </c>
-      <c r="D65" s="1">
-        <f>B65*[1]属性总表!$E$5</f>
-        <v>21787.5</v>
-      </c>
-      <c r="E65" s="1">
-        <f>ROUND([1]等级属性!C65*[1]属性总表!$F$5,0)</f>
-        <v>1256</v>
-      </c>
-      <c r="F65" s="1">
-        <f>ROUND(C65*[1]属性总表!$G$5,0)</f>
-        <v>377</v>
-      </c>
-      <c r="G65" s="1">
-        <f>ROUND(C65*[1]属性总表!$H$5,0)</f>
-        <v>377</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="1">
-        <v>65</v>
-      </c>
-      <c r="B66" s="1">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C66" s="1">
-        <f t="shared" si="1"/>
-        <v>12.679999999999971</v>
-      </c>
-      <c r="D66" s="1">
-        <f>B66*[1]属性总表!$E$5</f>
-        <v>22050</v>
-      </c>
-      <c r="E66" s="1">
-        <f>ROUND([1]等级属性!C66*[1]属性总表!$F$5,0)</f>
-        <v>1268</v>
-      </c>
-      <c r="F66" s="1">
-        <f>ROUND(C66*[1]属性总表!$G$5,0)</f>
-        <v>380</v>
-      </c>
-      <c r="G66" s="1">
-        <f>ROUND(C66*[1]属性总表!$H$5,0)</f>
-        <v>380</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="1">
-        <v>66</v>
-      </c>
-      <c r="B67" s="1">
-        <f t="shared" si="0"/>
-        <v>21.25</v>
-      </c>
-      <c r="C67" s="1">
-        <f t="shared" si="1"/>
-        <v>12.799999999999971</v>
-      </c>
-      <c r="D67" s="1">
-        <f>B67*[1]属性总表!$E$5</f>
-        <v>22312.5</v>
-      </c>
-      <c r="E67" s="1">
-        <f>ROUND([1]等级属性!C67*[1]属性总表!$F$5,0)</f>
-        <v>1280</v>
-      </c>
-      <c r="F67" s="1">
-        <f>ROUND(C67*[1]属性总表!$G$5,0)</f>
-        <v>384</v>
-      </c>
-      <c r="G67" s="1">
-        <f>ROUND(C67*[1]属性总表!$H$5,0)</f>
-        <v>384</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="1">
-        <v>67</v>
-      </c>
-      <c r="B68" s="1">
-        <f t="shared" ref="B68:B71" si="2">B67+0.25</f>
-        <v>21.5</v>
-      </c>
-      <c r="C68" s="1">
-        <f t="shared" ref="C68:C71" si="3">C67+0.12</f>
-        <v>12.91999999999997</v>
-      </c>
-      <c r="D68" s="1">
-        <f>B68*[1]属性总表!$E$5</f>
-        <v>22575</v>
-      </c>
-      <c r="E68" s="1">
-        <f>ROUND([1]等级属性!C68*[1]属性总表!$F$5,0)</f>
-        <v>1292</v>
-      </c>
-      <c r="F68" s="1">
-        <f>ROUND(C68*[1]属性总表!$G$5,0)</f>
-        <v>388</v>
-      </c>
-      <c r="G68" s="1">
-        <f>ROUND(C68*[1]属性总表!$H$5,0)</f>
-        <v>388</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="1">
-        <v>68</v>
-      </c>
-      <c r="B69" s="1">
-        <f t="shared" si="2"/>
-        <v>21.75</v>
-      </c>
-      <c r="C69" s="1">
-        <f t="shared" si="3"/>
-        <v>13.039999999999969</v>
-      </c>
-      <c r="D69" s="1">
-        <f>B69*[1]属性总表!$E$5</f>
-        <v>22837.5</v>
-      </c>
-      <c r="E69" s="1">
-        <f>ROUND([1]等级属性!C69*[1]属性总表!$F$5,0)</f>
-        <v>1304</v>
-      </c>
-      <c r="F69" s="1">
-        <f>ROUND(C69*[1]属性总表!$G$5,0)</f>
-        <v>391</v>
-      </c>
-      <c r="G69" s="1">
-        <f>ROUND(C69*[1]属性总表!$H$5,0)</f>
-        <v>391</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="1">
-        <v>69</v>
-      </c>
-      <c r="B70" s="1">
-        <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="C70" s="1">
-        <f t="shared" si="3"/>
-        <v>13.159999999999968</v>
-      </c>
-      <c r="D70" s="1">
-        <f>B70*[1]属性总表!$E$5</f>
-        <v>23100</v>
-      </c>
-      <c r="E70" s="1">
-        <f>ROUND([1]等级属性!C70*[1]属性总表!$F$5,0)</f>
-        <v>1316</v>
-      </c>
-      <c r="F70" s="1">
-        <f>ROUND(C70*[1]属性总表!$G$5,0)</f>
-        <v>395</v>
-      </c>
-      <c r="G70" s="1">
-        <f>ROUND(C70*[1]属性总表!$H$5,0)</f>
-        <v>395</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="1">
-        <v>70</v>
-      </c>
-      <c r="B71" s="1">
-        <f t="shared" si="2"/>
-        <v>22.25</v>
-      </c>
-      <c r="C71" s="1">
-        <f t="shared" si="3"/>
-        <v>13.279999999999967</v>
-      </c>
-      <c r="D71" s="1">
-        <f>B71*[1]属性总表!$E$5</f>
-        <v>23362.5</v>
-      </c>
-      <c r="E71" s="1">
-        <f>ROUND([1]等级属性!C71*[1]属性总表!$F$5,0)</f>
-        <v>1328</v>
-      </c>
-      <c r="F71" s="1">
-        <f>ROUND(C71*[1]属性总表!$G$5,0)</f>
-        <v>398</v>
-      </c>
-      <c r="G71" s="1">
-        <f>ROUND(C71*[1]属性总表!$H$5,0)</f>
-        <v>398</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="35" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:AL154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -59091,7 +60580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="B1:X50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -59434,7 +60923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A3:J34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -59647,7 +61136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="C1:R30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -60529,7 +62018,7 @@
       <c r="J3" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="116" t="s">
+      <c r="K3" s="117" t="s">
         <v>50</v>
       </c>
       <c r="L3" s="68" t="s">
@@ -60611,7 +62100,7 @@
       <c r="I4" s="78">
         <v>10002</v>
       </c>
-      <c r="K4" s="116"/>
+      <c r="K4" s="117"/>
       <c r="L4" s="68" t="s">
         <v>61</v>
       </c>
@@ -60666,7 +62155,7 @@
       <c r="AW4" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="AX4" s="116" t="s">
+      <c r="AX4" s="117" t="s">
         <v>50</v>
       </c>
       <c r="AY4" s="68" t="s">
@@ -60722,7 +62211,7 @@
       <c r="I5" s="78">
         <v>10003</v>
       </c>
-      <c r="K5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="L5" s="68" t="s">
         <v>81</v>
       </c>
@@ -60774,7 +62263,7 @@
       <c r="AV5" s="68">
         <v>10002</v>
       </c>
-      <c r="AX5" s="116"/>
+      <c r="AX5" s="117"/>
       <c r="AY5" s="68" t="s">
         <v>61</v>
       </c>
@@ -60820,7 +62309,7 @@
       <c r="I6" s="78">
         <v>10011</v>
       </c>
-      <c r="K6" s="116" t="s">
+      <c r="K6" s="117" t="s">
         <v>101</v>
       </c>
       <c r="L6" s="68" t="s">
@@ -60850,7 +62339,7 @@
       <c r="AV6" s="68">
         <v>10003</v>
       </c>
-      <c r="AX6" s="116"/>
+      <c r="AX6" s="117"/>
       <c r="AY6" s="68" t="s">
         <v>81</v>
       </c>
@@ -60880,7 +62369,7 @@
       <c r="I7" s="78">
         <v>10012</v>
       </c>
-      <c r="K7" s="116"/>
+      <c r="K7" s="117"/>
       <c r="L7" s="68" t="s">
         <v>61</v>
       </c>
@@ -60926,7 +62415,7 @@
       <c r="AV7" s="68">
         <v>10011</v>
       </c>
-      <c r="AX7" s="116" t="s">
+      <c r="AX7" s="117" t="s">
         <v>101</v>
       </c>
       <c r="AY7" s="68" t="s">
@@ -60973,7 +62462,7 @@
       <c r="I8" s="78">
         <v>10013</v>
       </c>
-      <c r="K8" s="116"/>
+      <c r="K8" s="117"/>
       <c r="L8" s="68" t="s">
         <v>81</v>
       </c>
@@ -61013,7 +62502,7 @@
       <c r="AV8" s="68">
         <v>10012</v>
       </c>
-      <c r="AX8" s="116"/>
+      <c r="AX8" s="117"/>
       <c r="AY8" s="68" t="s">
         <v>61</v>
       </c>
@@ -61047,7 +62536,7 @@
       <c r="CO8" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="CP8" s="116" t="s">
+      <c r="CP8" s="117" t="s">
         <v>50</v>
       </c>
       <c r="CQ8" s="68" t="s">
@@ -61066,7 +62555,7 @@
       <c r="I9" s="78">
         <v>10021</v>
       </c>
-      <c r="K9" s="116" t="s">
+      <c r="K9" s="117" t="s">
         <v>142</v>
       </c>
       <c r="L9" s="68" t="s">
@@ -61090,7 +62579,7 @@
       <c r="AV9" s="68">
         <v>10013</v>
       </c>
-      <c r="AX9" s="116"/>
+      <c r="AX9" s="117"/>
       <c r="AY9" s="68" t="s">
         <v>81</v>
       </c>
@@ -61109,7 +62598,7 @@
       <c r="CN9" s="78">
         <v>10002</v>
       </c>
-      <c r="CP9" s="116"/>
+      <c r="CP9" s="117"/>
       <c r="CQ9" s="68" t="s">
         <v>61</v>
       </c>
@@ -61137,7 +62626,7 @@
       <c r="I10" s="78">
         <v>10022</v>
       </c>
-      <c r="K10" s="116"/>
+      <c r="K10" s="117"/>
       <c r="L10" s="68" t="s">
         <v>61</v>
       </c>
@@ -61181,7 +62670,7 @@
       <c r="AV10" s="68">
         <v>10021</v>
       </c>
-      <c r="AX10" s="116" t="s">
+      <c r="AX10" s="117" t="s">
         <v>142</v>
       </c>
       <c r="AY10" s="68" t="s">
@@ -61197,7 +62686,7 @@
       <c r="CN10" s="78">
         <v>10003</v>
       </c>
-      <c r="CP10" s="116"/>
+      <c r="CP10" s="117"/>
       <c r="CQ10" s="68" t="s">
         <v>81</v>
       </c>
@@ -61224,7 +62713,7 @@
       <c r="I11" s="78">
         <v>10023</v>
       </c>
-      <c r="K11" s="116"/>
+      <c r="K11" s="117"/>
       <c r="L11" s="68" t="s">
         <v>81</v>
       </c>
@@ -61276,7 +62765,7 @@
       <c r="AV11" s="68">
         <v>10022</v>
       </c>
-      <c r="AX11" s="116"/>
+      <c r="AX11" s="117"/>
       <c r="AY11" s="68" t="s">
         <v>61</v>
       </c>
@@ -61314,7 +62803,7 @@
       <c r="CN11" s="78">
         <v>10011</v>
       </c>
-      <c r="CP11" s="116" t="s">
+      <c r="CP11" s="117" t="s">
         <v>101</v>
       </c>
       <c r="CQ11" s="68" t="s">
@@ -61334,7 +62823,7 @@
       <c r="I12" s="78">
         <v>10031</v>
       </c>
-      <c r="K12" s="116" t="s">
+      <c r="K12" s="117" t="s">
         <v>186</v>
       </c>
       <c r="L12" s="68" t="s">
@@ -61367,7 +62856,7 @@
       <c r="AV12" s="68">
         <v>10023</v>
       </c>
-      <c r="AX12" s="116"/>
+      <c r="AX12" s="117"/>
       <c r="AY12" s="68" t="s">
         <v>81</v>
       </c>
@@ -61416,7 +62905,7 @@
       <c r="CN12" s="78">
         <v>10012</v>
       </c>
-      <c r="CP12" s="116"/>
+      <c r="CP12" s="117"/>
       <c r="CQ12" s="68" t="s">
         <v>61</v>
       </c>
@@ -61437,7 +62926,7 @@
       <c r="I13" s="78">
         <v>10032</v>
       </c>
-      <c r="K13" s="116"/>
+      <c r="K13" s="117"/>
       <c r="L13" s="68" t="s">
         <v>61</v>
       </c>
@@ -61465,7 +62954,7 @@
       <c r="AV13" s="68">
         <v>10031</v>
       </c>
-      <c r="AX13" s="116" t="s">
+      <c r="AX13" s="117" t="s">
         <v>186</v>
       </c>
       <c r="AY13" s="68" t="s">
@@ -61501,7 +62990,7 @@
       <c r="CN13" s="78">
         <v>10013</v>
       </c>
-      <c r="CP13" s="116"/>
+      <c r="CP13" s="117"/>
       <c r="CQ13" s="68" t="s">
         <v>81</v>
       </c>
@@ -61533,7 +63022,7 @@
       <c r="I14" s="78">
         <v>10033</v>
       </c>
-      <c r="K14" s="116"/>
+      <c r="K14" s="117"/>
       <c r="L14" s="68" t="s">
         <v>81</v>
       </c>
@@ -61564,7 +63053,7 @@
       <c r="AV14" s="68">
         <v>10032</v>
       </c>
-      <c r="AX14" s="116"/>
+      <c r="AX14" s="117"/>
       <c r="AY14" s="68" t="s">
         <v>61</v>
       </c>
@@ -61599,7 +63088,7 @@
       <c r="CN14" s="78">
         <v>10021</v>
       </c>
-      <c r="CP14" s="116" t="s">
+      <c r="CP14" s="117" t="s">
         <v>142</v>
       </c>
       <c r="CQ14" s="68" t="s">
@@ -61627,7 +63116,7 @@
       <c r="I15" s="78">
         <v>10041</v>
       </c>
-      <c r="K15" s="116" t="s">
+      <c r="K15" s="117" t="s">
         <v>241</v>
       </c>
       <c r="L15" s="68" t="s">
@@ -61657,7 +63146,7 @@
       <c r="AV15" s="68">
         <v>10033</v>
       </c>
-      <c r="AX15" s="116"/>
+      <c r="AX15" s="117"/>
       <c r="AY15" s="68" t="s">
         <v>81</v>
       </c>
@@ -61682,7 +63171,7 @@
       <c r="CN15" s="78">
         <v>10022</v>
       </c>
-      <c r="CP15" s="116"/>
+      <c r="CP15" s="117"/>
       <c r="CQ15" s="68" t="s">
         <v>61</v>
       </c>
@@ -61708,7 +63197,7 @@
       <c r="I16" s="78">
         <v>10042</v>
       </c>
-      <c r="K16" s="116"/>
+      <c r="K16" s="117"/>
       <c r="L16" s="68" t="s">
         <v>61</v>
       </c>
@@ -61736,7 +63225,7 @@
       <c r="AV16" s="68">
         <v>10041</v>
       </c>
-      <c r="AX16" s="116" t="s">
+      <c r="AX16" s="117" t="s">
         <v>241</v>
       </c>
       <c r="AY16" s="68" t="s">
@@ -61754,7 +63243,7 @@
       <c r="CN16" s="78">
         <v>10023</v>
       </c>
-      <c r="CP16" s="116"/>
+      <c r="CP16" s="117"/>
       <c r="CQ16" s="68" t="s">
         <v>81</v>
       </c>
@@ -61780,7 +63269,7 @@
       <c r="I17" s="78">
         <v>10043</v>
       </c>
-      <c r="K17" s="116"/>
+      <c r="K17" s="117"/>
       <c r="L17" s="68" t="s">
         <v>81</v>
       </c>
@@ -61803,7 +63292,7 @@
       <c r="AV17" s="68">
         <v>10042</v>
       </c>
-      <c r="AX17" s="116"/>
+      <c r="AX17" s="117"/>
       <c r="AY17" s="68" t="s">
         <v>61</v>
       </c>
@@ -61828,7 +63317,7 @@
       <c r="CN17" s="78">
         <v>10031</v>
       </c>
-      <c r="CP17" s="116" t="s">
+      <c r="CP17" s="117" t="s">
         <v>186</v>
       </c>
       <c r="CQ17" s="68" t="s">
@@ -61856,7 +63345,7 @@
       <c r="I18" s="68">
         <v>10051</v>
       </c>
-      <c r="K18" s="116" t="s">
+      <c r="K18" s="117" t="s">
         <v>275</v>
       </c>
       <c r="L18" s="68" t="s">
@@ -61892,7 +63381,7 @@
       <c r="AV18" s="68">
         <v>10043</v>
       </c>
-      <c r="AX18" s="116"/>
+      <c r="AX18" s="117"/>
       <c r="AY18" s="68" t="s">
         <v>81</v>
       </c>
@@ -61908,7 +63397,7 @@
       <c r="CN18" s="78">
         <v>10032</v>
       </c>
-      <c r="CP18" s="116"/>
+      <c r="CP18" s="117"/>
       <c r="CQ18" s="68" t="s">
         <v>61</v>
       </c>
@@ -61931,7 +63420,7 @@
       <c r="I19" s="68">
         <v>10052</v>
       </c>
-      <c r="K19" s="116"/>
+      <c r="K19" s="117"/>
       <c r="L19" s="68" t="s">
         <v>61</v>
       </c>
@@ -61965,7 +63454,7 @@
       <c r="AV19" s="68">
         <v>10051</v>
       </c>
-      <c r="AX19" s="116" t="s">
+      <c r="AX19" s="117" t="s">
         <v>275</v>
       </c>
       <c r="AY19" s="68" t="s">
@@ -61989,7 +63478,7 @@
       <c r="CN19" s="78">
         <v>10033</v>
       </c>
-      <c r="CP19" s="116"/>
+      <c r="CP19" s="117"/>
       <c r="CQ19" s="68" t="s">
         <v>81</v>
       </c>
@@ -62005,7 +63494,7 @@
       <c r="I20" s="68">
         <v>10053</v>
       </c>
-      <c r="K20" s="116"/>
+      <c r="K20" s="117"/>
       <c r="L20" s="68" t="s">
         <v>81</v>
       </c>
@@ -62036,7 +63525,7 @@
       <c r="AV20" s="68">
         <v>10052</v>
       </c>
-      <c r="AX20" s="116"/>
+      <c r="AX20" s="117"/>
       <c r="AY20" s="68" t="s">
         <v>61</v>
       </c>
@@ -62061,7 +63550,7 @@
       <c r="CN20" s="78">
         <v>10041</v>
       </c>
-      <c r="CP20" s="116" t="s">
+      <c r="CP20" s="117" t="s">
         <v>241</v>
       </c>
       <c r="CQ20" s="68" t="s">
@@ -62093,7 +63582,7 @@
         <v>10051</v>
       </c>
       <c r="J21" s="70"/>
-      <c r="K21" s="117" t="s">
+      <c r="K21" s="118" t="s">
         <v>315</v>
       </c>
       <c r="L21" s="70" t="s">
@@ -62120,7 +63609,7 @@
       <c r="AV21" s="68">
         <v>10053</v>
       </c>
-      <c r="AX21" s="116"/>
+      <c r="AX21" s="117"/>
       <c r="AY21" s="68" t="s">
         <v>81</v>
       </c>
@@ -62136,7 +63625,7 @@
       <c r="CN21" s="78">
         <v>10042</v>
       </c>
-      <c r="CP21" s="116"/>
+      <c r="CP21" s="117"/>
       <c r="CQ21" s="68" t="s">
         <v>61</v>
       </c>
@@ -62163,7 +63652,7 @@
         <v>10052</v>
       </c>
       <c r="J22" s="70"/>
-      <c r="K22" s="117"/>
+      <c r="K22" s="118"/>
       <c r="L22" s="70" t="s">
         <v>61</v>
       </c>
@@ -62187,7 +63676,7 @@
         <v>10051</v>
       </c>
       <c r="AW22" s="70"/>
-      <c r="AX22" s="117" t="s">
+      <c r="AX22" s="118" t="s">
         <v>315</v>
       </c>
       <c r="AY22" s="70" t="s">
@@ -62212,7 +63701,7 @@
       <c r="CN22" s="78">
         <v>10043</v>
       </c>
-      <c r="CP22" s="116"/>
+      <c r="CP22" s="117"/>
       <c r="CQ22" s="68" t="s">
         <v>81</v>
       </c>
@@ -62239,7 +63728,7 @@
         <v>10053</v>
       </c>
       <c r="J23" s="70"/>
-      <c r="K23" s="117"/>
+      <c r="K23" s="118"/>
       <c r="L23" s="70" t="s">
         <v>81</v>
       </c>
@@ -62273,7 +63762,7 @@
         <v>10052</v>
       </c>
       <c r="AW23" s="70"/>
-      <c r="AX23" s="117"/>
+      <c r="AX23" s="118"/>
       <c r="AY23" s="70" t="s">
         <v>61</v>
       </c>
@@ -62296,7 +63785,7 @@
       <c r="CN23" s="68">
         <v>10051</v>
       </c>
-      <c r="CP23" s="116" t="s">
+      <c r="CP23" s="117" t="s">
         <v>275</v>
       </c>
       <c r="CQ23" s="68" t="s">
@@ -62362,7 +63851,7 @@
         <v>10053</v>
       </c>
       <c r="AW24" s="70"/>
-      <c r="AX24" s="117"/>
+      <c r="AX24" s="118"/>
       <c r="AY24" s="70" t="s">
         <v>81</v>
       </c>
@@ -62398,7 +63887,7 @@
       <c r="CN24" s="68">
         <v>10052</v>
       </c>
-      <c r="CP24" s="116"/>
+      <c r="CP24" s="117"/>
       <c r="CQ24" s="68" t="s">
         <v>61</v>
       </c>
@@ -62488,7 +63977,7 @@
       <c r="CN25" s="68">
         <v>10053</v>
       </c>
-      <c r="CP25" s="116"/>
+      <c r="CP25" s="117"/>
       <c r="CQ25" s="68" t="s">
         <v>81</v>
       </c>
@@ -62589,7 +64078,7 @@
         <v>10051</v>
       </c>
       <c r="CO26" s="70"/>
-      <c r="CP26" s="117" t="s">
+      <c r="CP26" s="118" t="s">
         <v>315</v>
       </c>
       <c r="CQ26" s="70" t="s">
@@ -62692,7 +64181,7 @@
         <v>10052</v>
       </c>
       <c r="CO27" s="70"/>
-      <c r="CP27" s="117"/>
+      <c r="CP27" s="118"/>
       <c r="CQ27" s="70" t="s">
         <v>61</v>
       </c>
@@ -62795,7 +64284,7 @@
         <v>10053</v>
       </c>
       <c r="CO28" s="70"/>
-      <c r="CP28" s="117"/>
+      <c r="CP28" s="118"/>
       <c r="CQ28" s="70" t="s">
         <v>81</v>
       </c>
@@ -64611,13 +66100,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="CP23:CP25"/>
-    <mergeCell ref="CP26:CP28"/>
-    <mergeCell ref="CP8:CP10"/>
-    <mergeCell ref="CP11:CP13"/>
-    <mergeCell ref="CP14:CP16"/>
-    <mergeCell ref="CP17:CP19"/>
-    <mergeCell ref="CP20:CP22"/>
     <mergeCell ref="K18:K20"/>
     <mergeCell ref="K21:K23"/>
     <mergeCell ref="AX4:AX6"/>
@@ -64632,6 +66114,13 @@
     <mergeCell ref="K9:K11"/>
     <mergeCell ref="K12:K14"/>
     <mergeCell ref="K15:K17"/>
+    <mergeCell ref="CP23:CP25"/>
+    <mergeCell ref="CP26:CP28"/>
+    <mergeCell ref="CP8:CP10"/>
+    <mergeCell ref="CP11:CP13"/>
+    <mergeCell ref="CP14:CP16"/>
+    <mergeCell ref="CP17:CP19"/>
+    <mergeCell ref="CP20:CP22"/>
   </mergeCells>
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -79354,7 +80843,7 @@
         <v>1200</v>
       </c>
       <c r="P96" s="1">
-        <f>LOOKUP(Q96,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(Q96,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>69000002</v>
       </c>
       <c r="Q96" s="1">
@@ -79369,7 +80858,7 @@
       <c r="T96" s="3"/>
       <c r="U96" s="3"/>
       <c r="V96" s="3">
-        <f>LOOKUP(W96,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(W96,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>0</v>
       </c>
       <c r="W96" s="1">
@@ -79384,7 +80873,7 @@
       <c r="Z96" s="3"/>
       <c r="AA96" s="3"/>
       <c r="AB96" s="3">
-        <f>LOOKUP(AC96,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(AC96,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>0</v>
       </c>
       <c r="AC96" s="1">
@@ -79433,7 +80922,7 @@
       </c>
       <c r="N97" s="5"/>
       <c r="P97" s="1">
-        <f>LOOKUP(Q97,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(Q97,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>0</v>
       </c>
       <c r="Q97" s="1">
@@ -79448,7 +80937,7 @@
       <c r="T97" s="3"/>
       <c r="U97" s="3"/>
       <c r="V97" s="3">
-        <f>LOOKUP(W97,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(W97,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>0</v>
       </c>
       <c r="W97" s="1">
@@ -79463,7 +80952,7 @@
       <c r="Z97" s="3"/>
       <c r="AA97" s="3"/>
       <c r="AB97" s="3">
-        <f>LOOKUP(AC97,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(AC97,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>69000016</v>
       </c>
       <c r="AC97" s="1">
@@ -79508,7 +80997,7 @@
       </c>
       <c r="N98" s="5"/>
       <c r="P98" s="1" t="e">
-        <f>LOOKUP(Q98,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(Q98,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>#N/A</v>
       </c>
       <c r="R98" s="1" t="s">
@@ -79520,7 +81009,7 @@
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
       <c r="V98" s="3">
-        <f>LOOKUP(W98,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(W98,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>0</v>
       </c>
       <c r="W98" s="1">
@@ -79535,7 +81024,7 @@
       <c r="Z98" s="3"/>
       <c r="AA98" s="3"/>
       <c r="AB98" s="3">
-        <f>LOOKUP(AC98,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(AC98,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>0</v>
       </c>
       <c r="AC98" s="1">
@@ -79584,7 +81073,7 @@
       </c>
       <c r="N99" s="5"/>
       <c r="P99" s="1">
-        <f>LOOKUP(Q99,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(Q99,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>0</v>
       </c>
       <c r="Q99" s="1">
@@ -79599,7 +81088,7 @@
       <c r="T99" s="3"/>
       <c r="U99" s="3"/>
       <c r="V99" s="3">
-        <f>LOOKUP(W99,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(W99,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>69000010</v>
       </c>
       <c r="W99" s="1">
@@ -79614,7 +81103,7 @@
       <c r="Z99" s="3"/>
       <c r="AA99" s="3"/>
       <c r="AB99" s="3" t="str">
-        <f>LOOKUP(AC99,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(AC99,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>69000013;69000017</v>
       </c>
       <c r="AC99" s="1">
@@ -79642,8 +81131,8 @@
       </c>
       <c r="N100" s="5"/>
       <c r="P100" s="1">
-        <f>LOOKUP(Q100,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
-        <v>69000011</v>
+        <f>LOOKUP(Q100,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <v>0</v>
       </c>
       <c r="Q100" s="1">
         <v>15510121</v>
@@ -79657,8 +81146,8 @@
       <c r="T100" s="3"/>
       <c r="U100" s="3"/>
       <c r="V100" s="3">
-        <f>LOOKUP(W100,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
-        <v>69000012</v>
+        <f>LOOKUP(W100,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <v>0</v>
       </c>
       <c r="W100" s="1">
         <v>15511011</v>
@@ -79672,7 +81161,7 @@
       <c r="Z100" s="3"/>
       <c r="AA100" s="3"/>
       <c r="AB100" s="3">
-        <f>LOOKUP(AC100,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(AC100,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>0</v>
       </c>
       <c r="AC100" s="1">
@@ -79718,7 +81207,7 @@
       <c r="Z101" s="3"/>
       <c r="AA101" s="3"/>
       <c r="AB101" s="3">
-        <f>LOOKUP(AC101,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(AC101,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>0</v>
       </c>
       <c r="AC101" s="1">
@@ -79875,7 +81364,7 @@
         <v>1307</v>
       </c>
       <c r="AB105" s="3">
-        <f>LOOKUP(AC105,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(AC105,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>0</v>
       </c>
       <c r="AC105" s="1">
@@ -79910,7 +81399,7 @@
       <c r="N106" s="5"/>
       <c r="R106" s="1"/>
       <c r="AB106" s="3">
-        <f>LOOKUP(AC106,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(AC106,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>0</v>
       </c>
       <c r="AC106" s="1">
@@ -79944,7 +81433,7 @@
       </c>
       <c r="N107" s="5"/>
       <c r="AB107" s="3">
-        <f>LOOKUP(AC107,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(AC107,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>0</v>
       </c>
       <c r="AC107" s="1">
@@ -79982,7 +81471,7 @@
       </c>
       <c r="N108" s="5"/>
       <c r="AB108" s="3">
-        <f>LOOKUP(AC108,[2]ItemProto!$C$856:$C$1335,[2]ItemProto!$S$856:$S$1335)</f>
+        <f>LOOKUP(AC108,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
         <v>0</v>
       </c>
       <c r="AC108" s="1">

--- a/WeiJingShuZhi/属性表.xlsx
+++ b/WeiJingShuZhi/属性表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\WeiJingShuZhi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F006511-A447-4C24-B5E6-CD410D4BFE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99650F50-E752-4DA2-B9C2-5B917F011D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="10" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -30,17 +30,18 @@
     <sheet name="宠物" sheetId="15" r:id="rId15"/>
     <sheet name="宠物属性" sheetId="16" r:id="rId16"/>
     <sheet name="宠物装备" sheetId="24" r:id="rId17"/>
-    <sheet name="宠物爬塔" sheetId="17" r:id="rId18"/>
-    <sheet name="宠物之核" sheetId="18" r:id="rId19"/>
-    <sheet name="装备" sheetId="19" r:id="rId20"/>
-    <sheet name="怪物属性" sheetId="20" r:id="rId21"/>
-    <sheet name="boss技能" sheetId="21" r:id="rId22"/>
-    <sheet name="称号" sheetId="22" r:id="rId23"/>
-    <sheet name="生命之盾" sheetId="23" r:id="rId24"/>
+    <sheet name="魔能" sheetId="25" r:id="rId18"/>
+    <sheet name="宠物爬塔" sheetId="17" r:id="rId19"/>
+    <sheet name="宠物之核" sheetId="18" r:id="rId20"/>
+    <sheet name="装备" sheetId="19" r:id="rId21"/>
+    <sheet name="怪物属性" sheetId="20" r:id="rId22"/>
+    <sheet name="boss技能" sheetId="21" r:id="rId23"/>
+    <sheet name="称号" sheetId="22" r:id="rId24"/>
+    <sheet name="生命之盾" sheetId="23" r:id="rId25"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId25"/>
     <externalReference r:id="rId26"/>
+    <externalReference r:id="rId27"/>
   </externalReferences>
   <calcPr calcId="191029"/>
 </workbook>
@@ -90,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5290" uniqueCount="2950">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5467" uniqueCount="3070">
   <si>
     <t>人物属性</t>
   </si>
@@ -9278,6 +9279,484 @@
   </si>
   <si>
     <t>等级</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击时有概率触发天崩地裂,造成100%伤害+X点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放时有概率对目标额外造成一次100%伤害+X点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击有概率立即恢复自身1%生命值+X点生命值</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发</t>
+  </si>
+  <si>
+    <t>技能触发</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受击触发</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>间隔触发</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚空</t>
+  </si>
+  <si>
+    <t>轮回</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>沧澜</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>烈焰</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击加成</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能加成</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵消</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次受到技能伤害可以抵消当前伤害X点</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊轮回</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>重置获得</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入战斗后，每秒额外恢复100点生命值</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发暴击后有概率对目标造成2次暴击伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次释放技能有概率提升自身10%伤害+X点攻击,持续5秒</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到伤害可以立即对攻击者造成X点伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次受到伤害有概率触发保护,提升自身防御10%</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到眩晕和置空技能后,自身免伤立即提升30%,持续3秒</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放技能有概率触发天崩地裂,造成100%伤害+X点固定伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次释放技能可恢复100点生命值</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次普通攻击有概率回复100点生命值</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>产出</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>兑换?</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二版</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能伤害额外提升100点</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击额外提升100点</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到普通攻击额外抵消100点</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到技能伤害额外抵消100点</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>引入次数概念?  充能？</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>紫色</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可升级</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>橙色</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>升3级</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉色</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔能之晶</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>升栏位等级</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>某些技能需要达到对应等级的栏位等级才能装备.</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>栏位属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+物防</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+魔防</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+血量</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>物防+魔防+血量</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>开启消耗</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊材料</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>孔位位置</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>收到控制类技能，有20%概率抵消此效果。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击性技能</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次释放技能有概率提升自身10%伤害,持续3秒</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次释放技能有概率提升自身15%伤害,持续3秒</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次释放技能有概率提升自身20%伤害,持续3秒</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨力</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>免疫</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到控制类的技能效果,有20%概率抵消此控制效果。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到控制类的技能效果,有10%概率抵消此控制效果。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到控制类的技能效果,有15%概率抵消此控制效果。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>辅助性技能</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>保护</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>愈合</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到技能伤害有3%概率抵消当前受到的技能伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到技能伤害有4%概率抵消当前受到的技能伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到技能伤害有5%概率抵消当前受到的技能伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到普通攻击有5%概率抵消当前受到的普通攻击伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到普通攻击有7.5%概率抵消当前受到的普通攻击伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到普通攻击有10%概率抵消当前受到的普通攻击伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>格挡</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>增量</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炸</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>引燃</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发暴击后</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放技能有概率使目标额外承受伤害提升10%,持续3秒</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放技能有概率使目标额外承受伤害提升15%,持续3秒</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放技能有概率使目标额外承受伤害提升20%,持续3秒</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>降幅</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发暴击后有5%概率对目标在额外造成一次暴击伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发暴击后有7.5%概率对目标在额外造成一次暴击伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发暴击后有10%概率对目标在额外造成一次暴击伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>使自己的普通攻击对目标时额外附加5%暴击属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>使自己的普通攻击对目标时额外附加7.5%暴击属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>使自己的普通攻击对目标时额外附加10%暴击属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>地裂</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击有一定概率触发爆炸,立即对自身范围触发爆炸，造成100%伤害+500点固定伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击有一定概率触发爆炸,立即对自身范围触发爆炸，造成100%伤害+1000点固定伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击时有概率触发地裂,造成100%伤害+500点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击时有概率触发地裂,造成150%伤害+1000点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击时有概率触发地裂,造成200%伤害+1500点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放技时有一定概率触发烈焰,造成100%伤害+500点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放技时有一定概率触发烈焰造成150%伤害+1000点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放技时有一定概率触发烈焰,造成200%伤害+1500点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击有一定概率触发爆炸,立即对自身范围触发爆炸，造成100%伤害+1500点固定伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击有一定概率在施法者目标处触发爆炸，造成100%伤害+500点固定伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击有一定概率在施法者目标处触发爆炸，造成100%伤害+1000点固定伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击有一定概率在施法者目标处触发爆炸，造成100%伤害+1500点固定伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>抗暴</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>使自己的普通攻击对目标时额外附加10%命中属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>使自己的普通攻击对目标时额外附加15%命中属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>使自己的普通攻击对目标时额外附加20%命中属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入战斗后每秒恢复200点生命值。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入战斗后每秒恢复300点生命值。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>进入战斗后每秒恢复400点生命值。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次受到伤害有概率触发保护,提升自身免伤10%,持续3秒。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次受到伤害有概率触发保护,提升自身免伤15%,持续3秒。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次受到伤害有概率触发保护,提升自身免伤20%,持续3秒。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次普通攻击有概率回复自身3%+3000点生命值。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次普通攻击有概率回复自身4%+4500点生命值。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次普通攻击有概率回复自身5%+6000点生命值。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用恢复药剂,恢复效果额外提升20%。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用恢复药剂,恢复效果额外提升30%。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用恢复药剂,恢复效果额外提升40%。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴伤</t>
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
 </sst>
@@ -10802,2491 +11281,2743 @@
       <sheetData sheetId="0">
         <row r="856">
           <cell r="C856">
-            <v>10302006</v>
+            <v>10302004</v>
+          </cell>
+          <cell r="S856">
+            <v>6204004</v>
           </cell>
         </row>
         <row r="857">
           <cell r="C857">
-            <v>10303001</v>
+            <v>10302005</v>
+          </cell>
+          <cell r="S857">
+            <v>6205004</v>
           </cell>
         </row>
         <row r="858">
           <cell r="C858">
-            <v>10303002</v>
+            <v>10302006</v>
+          </cell>
+          <cell r="S858">
+            <v>6206003</v>
           </cell>
         </row>
         <row r="859">
           <cell r="C859">
-            <v>10303003</v>
+            <v>10303001</v>
+          </cell>
+          <cell r="S859">
+            <v>6301003</v>
           </cell>
         </row>
         <row r="860">
           <cell r="C860">
-            <v>10303004</v>
+            <v>10303002</v>
+          </cell>
+          <cell r="S860">
+            <v>6302003</v>
           </cell>
         </row>
         <row r="861">
           <cell r="C861">
-            <v>10303005</v>
+            <v>10303003</v>
+          </cell>
+          <cell r="S861">
+            <v>6303003</v>
           </cell>
         </row>
         <row r="862">
           <cell r="C862">
-            <v>10303006</v>
+            <v>10303004</v>
+          </cell>
+          <cell r="S862">
+            <v>6304004</v>
           </cell>
         </row>
         <row r="863">
           <cell r="C863">
-            <v>11200000</v>
+            <v>10303005</v>
+          </cell>
+          <cell r="S863">
+            <v>6305004</v>
           </cell>
         </row>
         <row r="864">
           <cell r="C864">
-            <v>11200001</v>
+            <v>10303006</v>
+          </cell>
+          <cell r="S864">
+            <v>6306003</v>
           </cell>
         </row>
         <row r="865">
           <cell r="C865">
-            <v>11200002</v>
+            <v>11200000</v>
+          </cell>
+          <cell r="S865">
+            <v>500</v>
           </cell>
         </row>
         <row r="866">
           <cell r="C866">
-            <v>11200003</v>
+            <v>11200001</v>
+          </cell>
+          <cell r="S866">
+            <v>500</v>
           </cell>
         </row>
         <row r="867">
           <cell r="C867">
-            <v>11200010</v>
+            <v>11200002</v>
+          </cell>
+          <cell r="S867">
+            <v>500</v>
           </cell>
         </row>
         <row r="868">
           <cell r="C868">
-            <v>11300001</v>
+            <v>11200003</v>
+          </cell>
+          <cell r="S868">
+            <v>500</v>
           </cell>
         </row>
         <row r="869">
           <cell r="C869">
-            <v>11300002</v>
+            <v>11200010</v>
+          </cell>
+          <cell r="S869">
+            <v>500</v>
           </cell>
         </row>
         <row r="870">
           <cell r="C870">
-            <v>11300003</v>
+            <v>11300001</v>
+          </cell>
+          <cell r="S870" t="str">
+            <v>1;3901</v>
           </cell>
         </row>
         <row r="871">
           <cell r="C871">
-            <v>11300004</v>
+            <v>11300002</v>
+          </cell>
+          <cell r="S871" t="str">
+            <v>1;3906</v>
           </cell>
         </row>
         <row r="872">
           <cell r="C872">
-            <v>11300005</v>
+            <v>11300003</v>
+          </cell>
+          <cell r="S872" t="str">
+            <v>1;3907</v>
           </cell>
         </row>
         <row r="873">
           <cell r="C873">
-            <v>11300006</v>
+            <v>11300004</v>
+          </cell>
+          <cell r="S873" t="str">
+            <v>1;3908</v>
           </cell>
         </row>
         <row r="874">
           <cell r="C874">
-            <v>11300007</v>
+            <v>11300005</v>
+          </cell>
+          <cell r="S874" t="str">
+            <v>1;3909</v>
           </cell>
         </row>
         <row r="875">
           <cell r="C875">
-            <v>11300008</v>
+            <v>11300006</v>
+          </cell>
+          <cell r="S875" t="str">
+            <v>1;3910</v>
           </cell>
         </row>
         <row r="876">
           <cell r="C876">
-            <v>11300009</v>
+            <v>11300007</v>
+          </cell>
+          <cell r="S876" t="str">
+            <v>2;3902</v>
           </cell>
         </row>
         <row r="877">
           <cell r="C877">
-            <v>11300101</v>
+            <v>11300008</v>
+          </cell>
+          <cell r="S877" t="str">
+            <v>2;3903</v>
           </cell>
         </row>
         <row r="878">
           <cell r="C878">
-            <v>11300102</v>
+            <v>11300009</v>
+          </cell>
+          <cell r="S878" t="str">
+            <v>2;3904</v>
           </cell>
         </row>
         <row r="879">
           <cell r="C879">
-            <v>11300103</v>
+            <v>11300101</v>
+          </cell>
+          <cell r="S879" t="str">
+            <v>1;3101</v>
           </cell>
         </row>
         <row r="880">
           <cell r="C880">
-            <v>11300104</v>
+            <v>11300102</v>
+          </cell>
+          <cell r="S880" t="str">
+            <v>1;3102</v>
           </cell>
         </row>
         <row r="881">
           <cell r="C881">
-            <v>11300105</v>
+            <v>11300103</v>
+          </cell>
+          <cell r="S881" t="str">
+            <v>1;3103</v>
           </cell>
         </row>
         <row r="882">
           <cell r="C882">
-            <v>11300201</v>
+            <v>11300104</v>
+          </cell>
+          <cell r="S882" t="str">
+            <v>1;3104</v>
           </cell>
         </row>
         <row r="883">
           <cell r="C883">
-            <v>11300202</v>
+            <v>11300105</v>
+          </cell>
+          <cell r="S883" t="str">
+            <v>1;3105</v>
           </cell>
         </row>
         <row r="884">
           <cell r="C884">
-            <v>11300203</v>
+            <v>11300201</v>
+          </cell>
+          <cell r="S884" t="str">
+            <v>1;3201</v>
           </cell>
         </row>
         <row r="885">
           <cell r="C885">
-            <v>11300204</v>
+            <v>11300202</v>
+          </cell>
+          <cell r="S885" t="str">
+            <v>1;3202</v>
           </cell>
         </row>
         <row r="886">
           <cell r="C886">
-            <v>11300205</v>
+            <v>11300203</v>
+          </cell>
+          <cell r="S886" t="str">
+            <v>1;3203</v>
           </cell>
         </row>
         <row r="887">
           <cell r="C887">
-            <v>11300301</v>
+            <v>11300204</v>
+          </cell>
+          <cell r="S887" t="str">
+            <v>1;3204</v>
           </cell>
         </row>
         <row r="888">
           <cell r="C888">
-            <v>11300302</v>
+            <v>11300205</v>
+          </cell>
+          <cell r="S888" t="str">
+            <v>1;3205</v>
           </cell>
         </row>
         <row r="889">
           <cell r="C889">
-            <v>11300303</v>
+            <v>11300301</v>
+          </cell>
+          <cell r="S889" t="str">
+            <v>1;3301</v>
           </cell>
         </row>
         <row r="890">
           <cell r="C890">
-            <v>11300304</v>
+            <v>11300302</v>
+          </cell>
+          <cell r="S890" t="str">
+            <v>1;3302</v>
           </cell>
         </row>
         <row r="891">
           <cell r="C891">
-            <v>11300305</v>
+            <v>11300303</v>
+          </cell>
+          <cell r="S891" t="str">
+            <v>1;3303</v>
           </cell>
         </row>
         <row r="892">
           <cell r="C892">
-            <v>11300401</v>
+            <v>11300304</v>
+          </cell>
+          <cell r="S892" t="str">
+            <v>1;3304</v>
           </cell>
         </row>
         <row r="893">
           <cell r="C893">
-            <v>11300402</v>
+            <v>11300305</v>
+          </cell>
+          <cell r="S893" t="str">
+            <v>1;3305</v>
           </cell>
         </row>
         <row r="894">
           <cell r="C894">
-            <v>11300403</v>
+            <v>11300401</v>
+          </cell>
+          <cell r="S894" t="str">
+            <v>1;3401</v>
           </cell>
         </row>
         <row r="895">
           <cell r="C895">
-            <v>11300404</v>
+            <v>11300402</v>
+          </cell>
+          <cell r="S895" t="str">
+            <v>1;3402</v>
           </cell>
         </row>
         <row r="896">
           <cell r="C896">
-            <v>11300405</v>
+            <v>11300403</v>
+          </cell>
+          <cell r="S896" t="str">
+            <v>1;3403</v>
           </cell>
         </row>
         <row r="897">
           <cell r="C897">
-            <v>11300501</v>
+            <v>11300404</v>
+          </cell>
+          <cell r="S897" t="str">
+            <v>1;3404</v>
           </cell>
         </row>
         <row r="898">
           <cell r="C898">
-            <v>11300502</v>
+            <v>11300405</v>
+          </cell>
+          <cell r="S898" t="str">
+            <v>1;3405</v>
           </cell>
         </row>
         <row r="899">
           <cell r="C899">
-            <v>11300503</v>
+            <v>11300501</v>
+          </cell>
+          <cell r="S899" t="str">
+            <v>1;3501</v>
           </cell>
         </row>
         <row r="900">
           <cell r="C900">
-            <v>11300504</v>
+            <v>11300502</v>
+          </cell>
+          <cell r="S900" t="str">
+            <v>1;3502</v>
           </cell>
         </row>
         <row r="901">
           <cell r="C901">
-            <v>11300505</v>
+            <v>11300503</v>
+          </cell>
+          <cell r="S901" t="str">
+            <v>1;3503</v>
           </cell>
         </row>
         <row r="902">
           <cell r="C902">
-            <v>11300601</v>
+            <v>11300504</v>
+          </cell>
+          <cell r="S902" t="str">
+            <v>1;3504</v>
           </cell>
         </row>
         <row r="903">
           <cell r="C903">
-            <v>11300602</v>
+            <v>11300505</v>
+          </cell>
+          <cell r="S903" t="str">
+            <v>1;3505</v>
           </cell>
         </row>
         <row r="904">
           <cell r="C904">
-            <v>11300603</v>
+            <v>11300601</v>
+          </cell>
+          <cell r="S904" t="str">
+            <v>1;3601</v>
           </cell>
         </row>
         <row r="905">
           <cell r="C905">
-            <v>11300604</v>
+            <v>11300602</v>
+          </cell>
+          <cell r="S905" t="str">
+            <v>1;3602</v>
           </cell>
         </row>
         <row r="906">
           <cell r="C906">
-            <v>11300605</v>
+            <v>11300603</v>
+          </cell>
+          <cell r="S906" t="str">
+            <v>1;3603</v>
           </cell>
         </row>
         <row r="907">
           <cell r="C907">
-            <v>11400101</v>
+            <v>11300604</v>
+          </cell>
+          <cell r="S907" t="str">
+            <v>1;3604</v>
           </cell>
         </row>
         <row r="908">
           <cell r="C908">
-            <v>11400102</v>
+            <v>11300605</v>
+          </cell>
+          <cell r="S908" t="str">
+            <v>1;3605</v>
           </cell>
         </row>
         <row r="909">
           <cell r="C909">
-            <v>11400103</v>
+            <v>11400101</v>
+          </cell>
+          <cell r="S909" t="str">
+            <v>1,30@1;202103,0.01,0.03</v>
           </cell>
         </row>
         <row r="910">
           <cell r="C910">
-            <v>11500101</v>
+            <v>11400102</v>
+          </cell>
+          <cell r="S910" t="str">
+            <v>1,30@1;100203,100,200</v>
           </cell>
         </row>
         <row r="911">
           <cell r="C911">
-            <v>11500102</v>
+            <v>11400103</v>
+          </cell>
+          <cell r="S911" t="str">
+            <v>1,30@2;62000001</v>
           </cell>
         </row>
         <row r="912">
           <cell r="C912">
-            <v>11500103</v>
+            <v>11500101</v>
           </cell>
         </row>
         <row r="913">
           <cell r="C913">
-            <v>11500201</v>
+            <v>11500102</v>
           </cell>
         </row>
         <row r="914">
           <cell r="C914">
-            <v>11500202</v>
+            <v>11500103</v>
           </cell>
         </row>
         <row r="915">
           <cell r="C915">
-            <v>11500203</v>
+            <v>11500201</v>
           </cell>
         </row>
         <row r="916">
           <cell r="C916">
-            <v>11500301</v>
+            <v>11500202</v>
           </cell>
         </row>
         <row r="917">
           <cell r="C917">
-            <v>11500302</v>
+            <v>11500203</v>
           </cell>
         </row>
         <row r="918">
           <cell r="C918">
-            <v>11500303</v>
+            <v>11500301</v>
           </cell>
         </row>
         <row r="919">
           <cell r="C919">
-            <v>11500401</v>
+            <v>11500302</v>
           </cell>
         </row>
         <row r="920">
           <cell r="C920">
-            <v>11500402</v>
+            <v>11500303</v>
           </cell>
         </row>
         <row r="921">
           <cell r="C921">
-            <v>11500403</v>
+            <v>11500401</v>
           </cell>
         </row>
         <row r="922">
           <cell r="C922">
-            <v>11500501</v>
+            <v>11500402</v>
           </cell>
         </row>
         <row r="923">
           <cell r="C923">
-            <v>11500502</v>
+            <v>11500403</v>
           </cell>
         </row>
         <row r="924">
           <cell r="C924">
-            <v>11500503</v>
+            <v>11500501</v>
           </cell>
         </row>
         <row r="925">
           <cell r="C925">
-            <v>13001001</v>
+            <v>11500502</v>
           </cell>
         </row>
         <row r="926">
           <cell r="C926">
-            <v>13001002</v>
+            <v>11500503</v>
           </cell>
         </row>
         <row r="927">
           <cell r="C927">
-            <v>13001003</v>
+            <v>13001001</v>
+          </cell>
+          <cell r="S927">
+            <v>65001001</v>
           </cell>
         </row>
         <row r="928">
           <cell r="C928">
-            <v>13001004</v>
+            <v>13001002</v>
+          </cell>
+          <cell r="S928">
+            <v>65001002</v>
           </cell>
         </row>
         <row r="929">
           <cell r="C929">
-            <v>13001005</v>
+            <v>13001003</v>
+          </cell>
+          <cell r="S929">
+            <v>65001003</v>
           </cell>
         </row>
         <row r="930">
           <cell r="C930">
-            <v>13001006</v>
+            <v>13001004</v>
+          </cell>
+          <cell r="S930">
+            <v>65001004</v>
           </cell>
         </row>
         <row r="931">
           <cell r="C931">
-            <v>13001101</v>
+            <v>13001005</v>
+          </cell>
+          <cell r="S931">
+            <v>65001005</v>
           </cell>
         </row>
         <row r="932">
           <cell r="C932">
-            <v>13001102</v>
+            <v>13001006</v>
+          </cell>
+          <cell r="S932">
+            <v>65001006</v>
           </cell>
         </row>
         <row r="933">
           <cell r="C933">
-            <v>13001103</v>
+            <v>13001101</v>
+          </cell>
+          <cell r="S933">
+            <v>65001101</v>
           </cell>
         </row>
         <row r="934">
           <cell r="C934">
-            <v>13001104</v>
+            <v>13001102</v>
+          </cell>
+          <cell r="S934">
+            <v>65001102</v>
           </cell>
         </row>
         <row r="935">
           <cell r="C935">
-            <v>13001105</v>
+            <v>13001103</v>
+          </cell>
+          <cell r="S935">
+            <v>65001103</v>
           </cell>
         </row>
         <row r="936">
           <cell r="C936">
-            <v>13002001</v>
+            <v>13001104</v>
+          </cell>
+          <cell r="S936">
+            <v>65001104</v>
           </cell>
         </row>
         <row r="937">
           <cell r="C937">
-            <v>13002002</v>
+            <v>13001105</v>
+          </cell>
+          <cell r="S937">
+            <v>65001105</v>
           </cell>
         </row>
         <row r="938">
           <cell r="C938">
-            <v>13002003</v>
+            <v>13002001</v>
+          </cell>
+          <cell r="S938">
+            <v>65002001</v>
           </cell>
         </row>
         <row r="939">
           <cell r="C939">
-            <v>13002004</v>
+            <v>13002002</v>
+          </cell>
+          <cell r="S939">
+            <v>65002002</v>
           </cell>
         </row>
         <row r="940">
           <cell r="C940">
-            <v>13002005</v>
+            <v>13002003</v>
+          </cell>
+          <cell r="S940">
+            <v>65002003</v>
           </cell>
         </row>
         <row r="941">
           <cell r="C941">
-            <v>13002006</v>
+            <v>13002004</v>
+          </cell>
+          <cell r="S941">
+            <v>65002004</v>
           </cell>
         </row>
         <row r="942">
           <cell r="C942">
-            <v>13002101</v>
+            <v>13002005</v>
+          </cell>
+          <cell r="S942">
+            <v>65002005</v>
           </cell>
         </row>
         <row r="943">
           <cell r="C943">
-            <v>13002102</v>
+            <v>13002006</v>
+          </cell>
+          <cell r="S943">
+            <v>65002006</v>
           </cell>
         </row>
         <row r="944">
           <cell r="C944">
-            <v>13002103</v>
+            <v>13002101</v>
+          </cell>
+          <cell r="S944">
+            <v>65002101</v>
           </cell>
         </row>
         <row r="945">
           <cell r="C945">
-            <v>13002104</v>
+            <v>13002102</v>
+          </cell>
+          <cell r="S945">
+            <v>65002102</v>
           </cell>
         </row>
         <row r="946">
           <cell r="C946">
-            <v>13002105</v>
+            <v>13002103</v>
+          </cell>
+          <cell r="S946">
+            <v>65002103</v>
           </cell>
         </row>
         <row r="947">
           <cell r="C947">
-            <v>13003001</v>
+            <v>13002104</v>
+          </cell>
+          <cell r="S947">
+            <v>65002104</v>
           </cell>
         </row>
         <row r="948">
           <cell r="C948">
-            <v>13003002</v>
+            <v>13002105</v>
+          </cell>
+          <cell r="S948">
+            <v>65002105</v>
           </cell>
         </row>
         <row r="949">
           <cell r="C949">
-            <v>13003003</v>
+            <v>13003001</v>
+          </cell>
+          <cell r="S949">
+            <v>65003001</v>
           </cell>
         </row>
         <row r="950">
           <cell r="C950">
-            <v>13003004</v>
+            <v>13003002</v>
+          </cell>
+          <cell r="S950">
+            <v>65003002</v>
           </cell>
         </row>
         <row r="951">
           <cell r="C951">
-            <v>13003005</v>
+            <v>13003003</v>
+          </cell>
+          <cell r="S951">
+            <v>65003003</v>
           </cell>
         </row>
         <row r="952">
           <cell r="C952">
-            <v>13003006</v>
+            <v>13003004</v>
+          </cell>
+          <cell r="S952">
+            <v>65003004</v>
           </cell>
         </row>
         <row r="953">
           <cell r="C953">
-            <v>13003101</v>
+            <v>13003005</v>
+          </cell>
+          <cell r="S953">
+            <v>65003005</v>
           </cell>
         </row>
         <row r="954">
           <cell r="C954">
-            <v>13003102</v>
+            <v>13003006</v>
+          </cell>
+          <cell r="S954">
+            <v>65003006</v>
           </cell>
         </row>
         <row r="955">
           <cell r="C955">
-            <v>13003103</v>
+            <v>13003101</v>
+          </cell>
+          <cell r="S955">
+            <v>65003101</v>
           </cell>
         </row>
         <row r="956">
           <cell r="C956">
-            <v>13003104</v>
+            <v>13003102</v>
+          </cell>
+          <cell r="S956">
+            <v>65003102</v>
           </cell>
         </row>
         <row r="957">
           <cell r="C957">
-            <v>13003105</v>
+            <v>13003103</v>
+          </cell>
+          <cell r="S957">
+            <v>65003103</v>
           </cell>
         </row>
         <row r="958">
           <cell r="C958">
-            <v>13004001</v>
+            <v>13003104</v>
+          </cell>
+          <cell r="S958">
+            <v>65003104</v>
           </cell>
         </row>
         <row r="959">
           <cell r="C959">
-            <v>13004002</v>
+            <v>13003105</v>
+          </cell>
+          <cell r="S959">
+            <v>65003105</v>
           </cell>
         </row>
         <row r="960">
           <cell r="C960">
-            <v>13004003</v>
+            <v>13004001</v>
+          </cell>
+          <cell r="S960">
+            <v>65004001</v>
           </cell>
         </row>
         <row r="961">
           <cell r="C961">
-            <v>13004004</v>
+            <v>13004002</v>
+          </cell>
+          <cell r="S961">
+            <v>65004002</v>
           </cell>
         </row>
         <row r="962">
           <cell r="C962">
-            <v>13004005</v>
+            <v>13004003</v>
+          </cell>
+          <cell r="S962">
+            <v>65004003</v>
           </cell>
         </row>
         <row r="963">
           <cell r="C963">
-            <v>13004006</v>
+            <v>13004004</v>
+          </cell>
+          <cell r="S963">
+            <v>65004004</v>
           </cell>
         </row>
         <row r="964">
           <cell r="C964">
-            <v>13004101</v>
+            <v>13004005</v>
+          </cell>
+          <cell r="S964">
+            <v>65004005</v>
           </cell>
         </row>
         <row r="965">
           <cell r="C965">
-            <v>13004102</v>
+            <v>13004006</v>
+          </cell>
+          <cell r="S965">
+            <v>65004006</v>
           </cell>
         </row>
         <row r="966">
           <cell r="C966">
-            <v>13004103</v>
+            <v>13004101</v>
+          </cell>
+          <cell r="S966">
+            <v>65004101</v>
           </cell>
         </row>
         <row r="967">
           <cell r="C967">
-            <v>13004104</v>
+            <v>13004102</v>
+          </cell>
+          <cell r="S967">
+            <v>65004102</v>
           </cell>
         </row>
         <row r="968">
           <cell r="C968">
-            <v>13004105</v>
+            <v>13004103</v>
+          </cell>
+          <cell r="S968">
+            <v>65004103</v>
           </cell>
         </row>
         <row r="969">
           <cell r="C969">
-            <v>13005001</v>
+            <v>13004104</v>
+          </cell>
+          <cell r="S969">
+            <v>65004104</v>
           </cell>
         </row>
         <row r="970">
           <cell r="C970">
-            <v>13005002</v>
+            <v>13004105</v>
+          </cell>
+          <cell r="S970">
+            <v>65004105</v>
           </cell>
         </row>
         <row r="971">
           <cell r="C971">
-            <v>13005003</v>
+            <v>13005001</v>
+          </cell>
+          <cell r="S971">
+            <v>65005001</v>
           </cell>
         </row>
         <row r="972">
           <cell r="C972">
-            <v>13005004</v>
+            <v>13005002</v>
+          </cell>
+          <cell r="S972">
+            <v>65005002</v>
           </cell>
         </row>
         <row r="973">
           <cell r="C973">
-            <v>13005005</v>
+            <v>13005003</v>
+          </cell>
+          <cell r="S973">
+            <v>65005003</v>
           </cell>
         </row>
         <row r="974">
           <cell r="C974">
-            <v>13005006</v>
+            <v>13005004</v>
+          </cell>
+          <cell r="S974">
+            <v>65005004</v>
           </cell>
         </row>
         <row r="975">
           <cell r="C975">
-            <v>13005101</v>
+            <v>13005005</v>
+          </cell>
+          <cell r="S975">
+            <v>65005005</v>
           </cell>
         </row>
         <row r="976">
           <cell r="C976">
-            <v>13005102</v>
+            <v>13005006</v>
+          </cell>
+          <cell r="S976">
+            <v>65005006</v>
           </cell>
         </row>
         <row r="977">
           <cell r="C977">
-            <v>13005103</v>
+            <v>13005101</v>
+          </cell>
+          <cell r="S977">
+            <v>65005101</v>
           </cell>
         </row>
         <row r="978">
           <cell r="C978">
-            <v>13005104</v>
+            <v>13005102</v>
+          </cell>
+          <cell r="S978">
+            <v>65005102</v>
           </cell>
         </row>
         <row r="979">
           <cell r="C979">
-            <v>13005105</v>
+            <v>13005103</v>
+          </cell>
+          <cell r="S979">
+            <v>65005103</v>
           </cell>
         </row>
         <row r="980">
           <cell r="C980">
-            <v>13006001</v>
+            <v>13005104</v>
+          </cell>
+          <cell r="S980">
+            <v>65005104</v>
           </cell>
         </row>
         <row r="981">
           <cell r="C981">
-            <v>13006002</v>
+            <v>13005105</v>
+          </cell>
+          <cell r="S981">
+            <v>65005105</v>
           </cell>
         </row>
         <row r="982">
           <cell r="C982">
-            <v>13006003</v>
+            <v>13006001</v>
           </cell>
           <cell r="S982">
-            <v>0</v>
+            <v>65006001</v>
           </cell>
         </row>
         <row r="983">
           <cell r="C983">
-            <v>13006004</v>
+            <v>13006002</v>
           </cell>
           <cell r="S983">
-            <v>0</v>
+            <v>65006002</v>
           </cell>
         </row>
         <row r="984">
           <cell r="C984">
-            <v>13009001</v>
+            <v>13006003</v>
+          </cell>
+          <cell r="S984">
+            <v>65006003</v>
           </cell>
         </row>
         <row r="985">
           <cell r="C985">
-            <v>13009002</v>
+            <v>13006004</v>
+          </cell>
+          <cell r="S985">
+            <v>65006004</v>
           </cell>
         </row>
         <row r="986">
           <cell r="C986">
-            <v>14000001</v>
+            <v>13009001</v>
+          </cell>
+          <cell r="S986" t="str">
+            <v>4;20</v>
           </cell>
         </row>
         <row r="987">
           <cell r="C987">
-            <v>14000002</v>
+            <v>13009002</v>
+          </cell>
+          <cell r="S987" t="str">
+            <v>5;20</v>
           </cell>
         </row>
         <row r="988">
           <cell r="C988">
-            <v>14000003</v>
-          </cell>
-          <cell r="S988">
-            <v>69000011</v>
+            <v>14000001</v>
           </cell>
         </row>
         <row r="989">
           <cell r="C989">
-            <v>14000004</v>
+            <v>14000002</v>
           </cell>
         </row>
         <row r="990">
           <cell r="C990">
-            <v>14000005</v>
+            <v>14000003</v>
           </cell>
         </row>
         <row r="991">
           <cell r="C991">
-            <v>14010001</v>
+            <v>14000004</v>
           </cell>
         </row>
         <row r="992">
           <cell r="C992">
-            <v>14010002</v>
+            <v>14000005</v>
           </cell>
         </row>
         <row r="993">
           <cell r="C993">
-            <v>14010003</v>
+            <v>14010001</v>
           </cell>
         </row>
         <row r="994">
           <cell r="C994">
-            <v>14010004</v>
+            <v>14010002</v>
           </cell>
         </row>
         <row r="995">
           <cell r="C995">
-            <v>14010005</v>
+            <v>14010003</v>
           </cell>
         </row>
         <row r="996">
           <cell r="C996">
-            <v>14010006</v>
+            <v>14010004</v>
           </cell>
         </row>
         <row r="997">
           <cell r="C997">
-            <v>14010007</v>
+            <v>14010005</v>
           </cell>
         </row>
         <row r="998">
           <cell r="C998">
-            <v>14010008</v>
+            <v>14010006</v>
           </cell>
         </row>
         <row r="999">
           <cell r="C999">
-            <v>14010009</v>
+            <v>14010007</v>
           </cell>
         </row>
         <row r="1000">
           <cell r="C1000">
-            <v>14010010</v>
+            <v>14010008</v>
           </cell>
         </row>
         <row r="1001">
           <cell r="C1001">
-            <v>14010011</v>
+            <v>14010009</v>
           </cell>
         </row>
         <row r="1002">
           <cell r="C1002">
-            <v>14010012</v>
+            <v>14010010</v>
           </cell>
         </row>
         <row r="1003">
           <cell r="C1003">
-            <v>14020001</v>
+            <v>14010011</v>
           </cell>
         </row>
         <row r="1004">
           <cell r="C1004">
-            <v>14020002</v>
+            <v>14010012</v>
           </cell>
         </row>
         <row r="1005">
           <cell r="C1005">
-            <v>14020003</v>
+            <v>14020001</v>
           </cell>
         </row>
         <row r="1006">
           <cell r="C1006">
-            <v>14020004</v>
+            <v>14020002</v>
           </cell>
         </row>
         <row r="1007">
           <cell r="C1007">
-            <v>14020005</v>
+            <v>14020003</v>
           </cell>
         </row>
         <row r="1008">
           <cell r="C1008">
-            <v>14020006</v>
+            <v>14020004</v>
           </cell>
         </row>
         <row r="1009">
           <cell r="C1009">
-            <v>14020007</v>
+            <v>14020005</v>
           </cell>
         </row>
         <row r="1010">
           <cell r="C1010">
-            <v>14020008</v>
+            <v>14020006</v>
           </cell>
         </row>
         <row r="1011">
           <cell r="C1011">
-            <v>14020009</v>
+            <v>14020007</v>
           </cell>
         </row>
         <row r="1012">
           <cell r="C1012">
-            <v>14020010</v>
+            <v>14020008</v>
           </cell>
         </row>
         <row r="1013">
           <cell r="C1013">
-            <v>14020011</v>
+            <v>14020009</v>
           </cell>
         </row>
         <row r="1014">
           <cell r="C1014">
-            <v>14020012</v>
+            <v>14020010</v>
           </cell>
         </row>
         <row r="1015">
           <cell r="C1015">
-            <v>14020013</v>
+            <v>14020011</v>
           </cell>
         </row>
         <row r="1016">
           <cell r="C1016">
-            <v>14030001</v>
+            <v>14020012</v>
           </cell>
         </row>
         <row r="1017">
           <cell r="C1017">
-            <v>14030002</v>
+            <v>14020013</v>
           </cell>
         </row>
         <row r="1018">
           <cell r="C1018">
-            <v>14030003</v>
+            <v>14030001</v>
           </cell>
         </row>
         <row r="1019">
           <cell r="C1019">
-            <v>14030004</v>
+            <v>14030002</v>
           </cell>
         </row>
         <row r="1020">
           <cell r="C1020">
-            <v>14030005</v>
+            <v>14030003</v>
           </cell>
         </row>
         <row r="1021">
           <cell r="C1021">
-            <v>14030006</v>
+            <v>14030004</v>
           </cell>
         </row>
         <row r="1022">
           <cell r="C1022">
-            <v>14030007</v>
+            <v>14030005</v>
           </cell>
         </row>
         <row r="1023">
           <cell r="C1023">
-            <v>14030008</v>
+            <v>14030006</v>
           </cell>
         </row>
         <row r="1024">
           <cell r="C1024">
-            <v>14030009</v>
+            <v>14030007</v>
           </cell>
         </row>
         <row r="1025">
           <cell r="C1025">
-            <v>14030010</v>
+            <v>14030008</v>
           </cell>
         </row>
         <row r="1026">
           <cell r="C1026">
-            <v>14030011</v>
+            <v>14030009</v>
           </cell>
         </row>
         <row r="1027">
           <cell r="C1027">
-            <v>14030012</v>
+            <v>14030010</v>
           </cell>
         </row>
         <row r="1028">
           <cell r="C1028">
-            <v>14030013</v>
+            <v>14030011</v>
           </cell>
         </row>
         <row r="1029">
           <cell r="C1029">
-            <v>14040001</v>
+            <v>14030012</v>
           </cell>
         </row>
         <row r="1030">
           <cell r="C1030">
-            <v>14040002</v>
+            <v>14030013</v>
           </cell>
         </row>
         <row r="1031">
           <cell r="C1031">
-            <v>14040003</v>
+            <v>14040001</v>
           </cell>
         </row>
         <row r="1032">
           <cell r="C1032">
-            <v>14040004</v>
+            <v>14040002</v>
           </cell>
         </row>
         <row r="1033">
           <cell r="C1033">
-            <v>14040005</v>
+            <v>14040003</v>
           </cell>
         </row>
         <row r="1034">
           <cell r="C1034">
-            <v>14040006</v>
+            <v>14040004</v>
           </cell>
         </row>
         <row r="1035">
           <cell r="C1035">
-            <v>14040007</v>
+            <v>14040005</v>
           </cell>
         </row>
         <row r="1036">
           <cell r="C1036">
-            <v>14040008</v>
+            <v>14040006</v>
           </cell>
         </row>
         <row r="1037">
           <cell r="C1037">
-            <v>14040009</v>
+            <v>14040007</v>
           </cell>
         </row>
         <row r="1038">
           <cell r="C1038">
-            <v>14040010</v>
+            <v>14040008</v>
           </cell>
         </row>
         <row r="1039">
           <cell r="C1039">
-            <v>14040011</v>
+            <v>14040009</v>
           </cell>
         </row>
         <row r="1040">
           <cell r="C1040">
-            <v>14040012</v>
+            <v>14040010</v>
           </cell>
         </row>
         <row r="1041">
           <cell r="C1041">
-            <v>14050001</v>
+            <v>14040011</v>
           </cell>
         </row>
         <row r="1042">
           <cell r="C1042">
-            <v>14050002</v>
+            <v>14040012</v>
           </cell>
         </row>
         <row r="1043">
           <cell r="C1043">
-            <v>14050003</v>
+            <v>14050001</v>
           </cell>
         </row>
         <row r="1044">
           <cell r="C1044">
-            <v>14050004</v>
+            <v>14050002</v>
           </cell>
         </row>
         <row r="1045">
           <cell r="C1045">
-            <v>14050005</v>
+            <v>14050003</v>
           </cell>
         </row>
         <row r="1046">
           <cell r="C1046">
-            <v>14050006</v>
+            <v>14050004</v>
           </cell>
         </row>
         <row r="1047">
           <cell r="C1047">
-            <v>14050007</v>
+            <v>14050005</v>
           </cell>
         </row>
         <row r="1048">
           <cell r="C1048">
-            <v>14050008</v>
+            <v>14050006</v>
           </cell>
         </row>
         <row r="1049">
           <cell r="C1049">
-            <v>14050009</v>
+            <v>14050007</v>
           </cell>
         </row>
         <row r="1050">
           <cell r="C1050">
-            <v>14050010</v>
+            <v>14050008</v>
           </cell>
         </row>
         <row r="1051">
           <cell r="C1051">
-            <v>14050011</v>
+            <v>14050009</v>
           </cell>
         </row>
         <row r="1052">
           <cell r="C1052">
-            <v>14050012</v>
+            <v>14050010</v>
           </cell>
         </row>
         <row r="1053">
           <cell r="C1053">
-            <v>14060001</v>
+            <v>14050011</v>
           </cell>
         </row>
         <row r="1054">
           <cell r="C1054">
-            <v>14060002</v>
+            <v>14050012</v>
           </cell>
         </row>
         <row r="1055">
           <cell r="C1055">
-            <v>14060003</v>
+            <v>14060001</v>
           </cell>
         </row>
         <row r="1056">
           <cell r="C1056">
-            <v>14060004</v>
+            <v>14060002</v>
           </cell>
         </row>
         <row r="1057">
           <cell r="C1057">
-            <v>14060005</v>
+            <v>14060003</v>
           </cell>
         </row>
         <row r="1058">
           <cell r="C1058">
-            <v>14060006</v>
-          </cell>
-          <cell r="S1058">
-            <v>68000018</v>
+            <v>14060004</v>
           </cell>
         </row>
         <row r="1059">
           <cell r="C1059">
-            <v>14070001</v>
+            <v>14060005</v>
           </cell>
         </row>
         <row r="1060">
           <cell r="C1060">
-            <v>14070002</v>
+            <v>14060006</v>
           </cell>
         </row>
         <row r="1061">
           <cell r="C1061">
-            <v>14070003</v>
+            <v>14070001</v>
           </cell>
         </row>
         <row r="1062">
           <cell r="C1062">
-            <v>14070004</v>
+            <v>14070002</v>
           </cell>
         </row>
         <row r="1063">
           <cell r="C1063">
-            <v>14080001</v>
-          </cell>
-          <cell r="S1063">
-            <v>66001001</v>
+            <v>14070003</v>
           </cell>
         </row>
         <row r="1064">
           <cell r="C1064">
-            <v>14080002</v>
-          </cell>
-          <cell r="S1064">
-            <v>66001002</v>
+            <v>14070004</v>
           </cell>
         </row>
         <row r="1065">
           <cell r="C1065">
-            <v>14080003</v>
-          </cell>
-          <cell r="S1065">
-            <v>66001003</v>
+            <v>14080001</v>
           </cell>
         </row>
         <row r="1066">
           <cell r="C1066">
-            <v>14080004</v>
-          </cell>
-          <cell r="S1066">
-            <v>66001012</v>
+            <v>14080002</v>
           </cell>
         </row>
         <row r="1067">
           <cell r="C1067">
-            <v>14090001</v>
+            <v>14080003</v>
           </cell>
         </row>
         <row r="1068">
           <cell r="C1068">
-            <v>14090002</v>
+            <v>14080004</v>
           </cell>
         </row>
         <row r="1069">
           <cell r="C1069">
-            <v>14090003</v>
+            <v>14090001</v>
           </cell>
         </row>
         <row r="1070">
           <cell r="C1070">
-            <v>14090004</v>
+            <v>14090002</v>
           </cell>
         </row>
         <row r="1071">
           <cell r="C1071">
-            <v>14100001</v>
+            <v>14090003</v>
           </cell>
         </row>
         <row r="1072">
           <cell r="C1072">
-            <v>14100002</v>
+            <v>14090004</v>
           </cell>
         </row>
         <row r="1073">
           <cell r="C1073">
-            <v>14100003</v>
+            <v>14100001</v>
           </cell>
         </row>
         <row r="1074">
           <cell r="C1074">
-            <v>14100004</v>
+            <v>14100002</v>
           </cell>
         </row>
         <row r="1075">
           <cell r="C1075">
-            <v>14100005</v>
+            <v>14100003</v>
           </cell>
         </row>
         <row r="1076">
           <cell r="C1076">
-            <v>14100006</v>
+            <v>14100004</v>
           </cell>
         </row>
         <row r="1077">
           <cell r="C1077">
-            <v>14100007</v>
+            <v>14100005</v>
           </cell>
         </row>
         <row r="1078">
           <cell r="C1078">
-            <v>14100008</v>
+            <v>14100006</v>
           </cell>
         </row>
         <row r="1079">
           <cell r="C1079">
-            <v>14100011</v>
-          </cell>
-          <cell r="S1079">
-            <v>69000001</v>
+            <v>14100007</v>
           </cell>
         </row>
         <row r="1080">
           <cell r="C1080">
-            <v>14100012</v>
+            <v>14100008</v>
           </cell>
         </row>
         <row r="1081">
           <cell r="C1081">
-            <v>14100021</v>
+            <v>14100011</v>
           </cell>
         </row>
         <row r="1082">
           <cell r="C1082">
-            <v>14100022</v>
+            <v>14100012</v>
           </cell>
         </row>
         <row r="1083">
           <cell r="C1083">
-            <v>14100101</v>
+            <v>14100021</v>
           </cell>
         </row>
         <row r="1084">
           <cell r="C1084">
-            <v>14100102</v>
+            <v>14100022</v>
           </cell>
         </row>
         <row r="1085">
           <cell r="C1085">
-            <v>14100103</v>
+            <v>14100101</v>
           </cell>
         </row>
         <row r="1086">
           <cell r="C1086">
-            <v>14100104</v>
+            <v>14100102</v>
           </cell>
         </row>
         <row r="1087">
           <cell r="C1087">
-            <v>14100105</v>
+            <v>14100103</v>
           </cell>
         </row>
         <row r="1088">
           <cell r="C1088">
-            <v>14100106</v>
+            <v>14100104</v>
           </cell>
         </row>
         <row r="1089">
           <cell r="C1089">
-            <v>14100107</v>
+            <v>14100105</v>
           </cell>
         </row>
         <row r="1090">
           <cell r="C1090">
-            <v>14100108</v>
+            <v>14100106</v>
           </cell>
         </row>
         <row r="1091">
           <cell r="C1091">
-            <v>14100111</v>
-          </cell>
-          <cell r="S1091">
-            <v>69000002</v>
+            <v>14100107</v>
           </cell>
         </row>
         <row r="1092">
           <cell r="C1092">
-            <v>14100112</v>
-          </cell>
-          <cell r="S1092">
-            <v>69000003</v>
+            <v>14100108</v>
           </cell>
         </row>
         <row r="1093">
           <cell r="C1093">
-            <v>14100121</v>
+            <v>14100111</v>
           </cell>
         </row>
         <row r="1094">
           <cell r="C1094">
-            <v>14100122</v>
+            <v>14100112</v>
           </cell>
         </row>
         <row r="1095">
           <cell r="C1095">
-            <v>14100201</v>
+            <v>14100121</v>
           </cell>
         </row>
         <row r="1096">
           <cell r="C1096">
-            <v>14100202</v>
+            <v>14100122</v>
           </cell>
         </row>
         <row r="1097">
           <cell r="C1097">
-            <v>14100203</v>
+            <v>14100201</v>
           </cell>
         </row>
         <row r="1098">
           <cell r="C1098">
-            <v>14100204</v>
+            <v>14100202</v>
           </cell>
         </row>
         <row r="1099">
           <cell r="C1099">
-            <v>14100211</v>
-          </cell>
-          <cell r="S1099">
-            <v>69000002</v>
+            <v>14100203</v>
           </cell>
         </row>
         <row r="1100">
           <cell r="C1100">
-            <v>14100221</v>
+            <v>14100204</v>
           </cell>
         </row>
         <row r="1101">
           <cell r="C1101">
-            <v>14110001</v>
+            <v>14100211</v>
           </cell>
         </row>
         <row r="1102">
           <cell r="C1102">
-            <v>14110002</v>
+            <v>14100221</v>
           </cell>
         </row>
         <row r="1103">
           <cell r="C1103">
-            <v>14110003</v>
+            <v>14110001</v>
           </cell>
         </row>
         <row r="1104">
           <cell r="C1104">
-            <v>14110004</v>
+            <v>14110002</v>
           </cell>
         </row>
         <row r="1105">
           <cell r="C1105">
-            <v>14110005</v>
+            <v>14110003</v>
           </cell>
         </row>
         <row r="1106">
           <cell r="C1106">
-            <v>14110006</v>
+            <v>14110004</v>
           </cell>
         </row>
         <row r="1107">
           <cell r="C1107">
-            <v>14110007</v>
+            <v>14110005</v>
           </cell>
         </row>
         <row r="1108">
           <cell r="C1108">
-            <v>14110008</v>
+            <v>14110006</v>
           </cell>
         </row>
         <row r="1109">
           <cell r="C1109">
-            <v>14110009</v>
+            <v>14110007</v>
           </cell>
         </row>
         <row r="1110">
           <cell r="C1110">
-            <v>14110010</v>
+            <v>14110008</v>
           </cell>
         </row>
         <row r="1111">
           <cell r="C1111">
-            <v>14110011</v>
+            <v>14110009</v>
           </cell>
         </row>
         <row r="1112">
           <cell r="C1112">
-            <v>14110012</v>
+            <v>14110010</v>
           </cell>
         </row>
         <row r="1113">
           <cell r="C1113">
-            <v>14110021</v>
+            <v>14110011</v>
           </cell>
         </row>
         <row r="1114">
           <cell r="C1114">
-            <v>14110022</v>
+            <v>14110012</v>
           </cell>
         </row>
         <row r="1115">
           <cell r="C1115">
-            <v>14110023</v>
+            <v>14110021</v>
           </cell>
         </row>
         <row r="1116">
           <cell r="C1116">
-            <v>15201001</v>
+            <v>14110022</v>
           </cell>
         </row>
         <row r="1117">
           <cell r="C1117">
-            <v>15201002</v>
+            <v>14110023</v>
           </cell>
         </row>
         <row r="1118">
           <cell r="C1118">
-            <v>15201003</v>
+            <v>15201001</v>
           </cell>
         </row>
         <row r="1119">
           <cell r="C1119">
-            <v>15201004</v>
+            <v>15201002</v>
           </cell>
         </row>
         <row r="1120">
           <cell r="C1120">
-            <v>15201005</v>
+            <v>15201003</v>
           </cell>
         </row>
         <row r="1121">
           <cell r="C1121">
-            <v>15201006</v>
+            <v>15201004</v>
           </cell>
         </row>
         <row r="1122">
           <cell r="C1122">
-            <v>15202001</v>
+            <v>15201005</v>
           </cell>
         </row>
         <row r="1123">
           <cell r="C1123">
-            <v>15202002</v>
+            <v>15201006</v>
           </cell>
         </row>
         <row r="1124">
           <cell r="C1124">
-            <v>15202003</v>
+            <v>15202001</v>
           </cell>
         </row>
         <row r="1125">
           <cell r="C1125">
-            <v>15202004</v>
+            <v>15202002</v>
           </cell>
         </row>
         <row r="1126">
           <cell r="C1126">
-            <v>15202005</v>
+            <v>15202003</v>
           </cell>
         </row>
         <row r="1127">
           <cell r="C1127">
-            <v>15202006</v>
+            <v>15202004</v>
           </cell>
         </row>
         <row r="1128">
           <cell r="C1128">
-            <v>15203001</v>
+            <v>15202005</v>
           </cell>
         </row>
         <row r="1129">
           <cell r="C1129">
-            <v>15203002</v>
+            <v>15202006</v>
           </cell>
         </row>
         <row r="1130">
           <cell r="C1130">
-            <v>15203003</v>
+            <v>15203001</v>
           </cell>
         </row>
         <row r="1131">
           <cell r="C1131">
-            <v>15203004</v>
+            <v>15203002</v>
           </cell>
         </row>
         <row r="1132">
           <cell r="C1132">
-            <v>15203005</v>
+            <v>15203003</v>
           </cell>
         </row>
         <row r="1133">
           <cell r="C1133">
-            <v>15203006</v>
+            <v>15203004</v>
           </cell>
         </row>
         <row r="1134">
           <cell r="C1134">
-            <v>15204001</v>
+            <v>15203005</v>
           </cell>
         </row>
         <row r="1135">
           <cell r="C1135">
-            <v>15204002</v>
+            <v>15203006</v>
           </cell>
         </row>
         <row r="1136">
           <cell r="C1136">
-            <v>15204003</v>
+            <v>15204001</v>
           </cell>
         </row>
         <row r="1137">
           <cell r="C1137">
-            <v>15204004</v>
+            <v>15204002</v>
           </cell>
         </row>
         <row r="1138">
           <cell r="C1138">
-            <v>15204005</v>
+            <v>15204003</v>
           </cell>
         </row>
         <row r="1139">
           <cell r="C1139">
-            <v>15204006</v>
+            <v>15204004</v>
           </cell>
         </row>
         <row r="1140">
           <cell r="C1140">
-            <v>15205001</v>
+            <v>15204005</v>
           </cell>
         </row>
         <row r="1141">
           <cell r="C1141">
-            <v>15205002</v>
+            <v>15204006</v>
           </cell>
         </row>
         <row r="1142">
           <cell r="C1142">
-            <v>15205003</v>
+            <v>15205001</v>
           </cell>
         </row>
         <row r="1143">
           <cell r="C1143">
-            <v>15205004</v>
+            <v>15205002</v>
           </cell>
         </row>
         <row r="1144">
           <cell r="C1144">
-            <v>15205005</v>
+            <v>15205003</v>
           </cell>
         </row>
         <row r="1145">
           <cell r="C1145">
-            <v>15205006</v>
+            <v>15205004</v>
           </cell>
         </row>
         <row r="1146">
           <cell r="C1146">
-            <v>15205007</v>
+            <v>15205005</v>
           </cell>
         </row>
         <row r="1147">
           <cell r="C1147">
-            <v>15206001</v>
+            <v>15205006</v>
           </cell>
         </row>
         <row r="1148">
           <cell r="C1148">
-            <v>15206002</v>
+            <v>15205007</v>
           </cell>
         </row>
         <row r="1149">
           <cell r="C1149">
-            <v>15206003</v>
+            <v>15206001</v>
           </cell>
         </row>
         <row r="1150">
           <cell r="C1150">
-            <v>15207001</v>
+            <v>15206002</v>
           </cell>
         </row>
         <row r="1151">
           <cell r="C1151">
-            <v>15207002</v>
+            <v>15206003</v>
           </cell>
         </row>
         <row r="1152">
           <cell r="C1152">
-            <v>15207003</v>
+            <v>15207001</v>
           </cell>
         </row>
         <row r="1153">
           <cell r="C1153">
-            <v>15208001</v>
-          </cell>
-          <cell r="S1153">
-            <v>66001004</v>
+            <v>15207002</v>
           </cell>
         </row>
         <row r="1154">
           <cell r="C1154">
-            <v>15208002</v>
-          </cell>
-          <cell r="S1154">
-            <v>66001005</v>
+            <v>15207003</v>
           </cell>
         </row>
         <row r="1155">
           <cell r="C1155">
-            <v>15208003</v>
-          </cell>
-          <cell r="S1155">
-            <v>66001013</v>
+            <v>15208001</v>
           </cell>
         </row>
         <row r="1156">
           <cell r="C1156">
-            <v>15209001</v>
+            <v>15208002</v>
           </cell>
         </row>
         <row r="1157">
           <cell r="C1157">
-            <v>15209002</v>
+            <v>15208003</v>
           </cell>
         </row>
         <row r="1158">
           <cell r="C1158">
-            <v>15210001</v>
+            <v>15209001</v>
           </cell>
         </row>
         <row r="1159">
           <cell r="C1159">
-            <v>15210002</v>
+            <v>15209002</v>
           </cell>
         </row>
         <row r="1160">
           <cell r="C1160">
-            <v>15210003</v>
+            <v>15210001</v>
           </cell>
         </row>
         <row r="1161">
           <cell r="C1161">
-            <v>15210004</v>
+            <v>15210002</v>
           </cell>
         </row>
         <row r="1162">
           <cell r="C1162">
-            <v>15210011</v>
-          </cell>
-          <cell r="S1162">
-            <v>69000016</v>
+            <v>15210003</v>
           </cell>
         </row>
         <row r="1163">
           <cell r="C1163">
-            <v>15210012</v>
+            <v>15210004</v>
           </cell>
         </row>
         <row r="1164">
           <cell r="C1164">
-            <v>15210101</v>
+            <v>15210011</v>
           </cell>
         </row>
         <row r="1165">
           <cell r="C1165">
-            <v>15210102</v>
+            <v>15210012</v>
           </cell>
         </row>
         <row r="1166">
           <cell r="C1166">
-            <v>15210103</v>
+            <v>15210101</v>
           </cell>
         </row>
         <row r="1167">
           <cell r="C1167">
-            <v>15210104</v>
+            <v>15210102</v>
           </cell>
         </row>
         <row r="1168">
           <cell r="C1168">
-            <v>15210111</v>
+            <v>15210103</v>
           </cell>
         </row>
         <row r="1169">
           <cell r="C1169">
-            <v>15210112</v>
+            <v>15210104</v>
           </cell>
         </row>
         <row r="1170">
           <cell r="C1170">
-            <v>15210201</v>
+            <v>15210111</v>
           </cell>
         </row>
         <row r="1171">
           <cell r="C1171">
-            <v>15210202</v>
+            <v>15210112</v>
           </cell>
         </row>
         <row r="1172">
           <cell r="C1172">
-            <v>15210211</v>
-          </cell>
-          <cell r="S1172">
-            <v>69000014</v>
+            <v>15210201</v>
           </cell>
         </row>
         <row r="1173">
           <cell r="C1173">
-            <v>15211001</v>
+            <v>15210202</v>
           </cell>
         </row>
         <row r="1174">
           <cell r="C1174">
-            <v>15211002</v>
+            <v>15210211</v>
           </cell>
         </row>
         <row r="1175">
           <cell r="C1175">
-            <v>15211003</v>
+            <v>15211001</v>
           </cell>
         </row>
         <row r="1176">
           <cell r="C1176">
-            <v>15211004</v>
+            <v>15211002</v>
           </cell>
         </row>
         <row r="1177">
           <cell r="C1177">
-            <v>15211005</v>
+            <v>15211003</v>
           </cell>
         </row>
         <row r="1178">
           <cell r="C1178">
-            <v>15211006</v>
+            <v>15211004</v>
           </cell>
         </row>
         <row r="1179">
           <cell r="C1179">
-            <v>15211011</v>
+            <v>15211005</v>
           </cell>
         </row>
         <row r="1180">
           <cell r="C1180">
-            <v>15211012</v>
+            <v>15211006</v>
           </cell>
         </row>
         <row r="1181">
           <cell r="C1181">
-            <v>15211013</v>
-          </cell>
-          <cell r="S1181">
-            <v>69000004</v>
+            <v>15211011</v>
           </cell>
         </row>
         <row r="1182">
           <cell r="C1182">
-            <v>15301001</v>
+            <v>15211012</v>
           </cell>
         </row>
         <row r="1183">
           <cell r="C1183">
-            <v>15301002</v>
+            <v>15211013</v>
           </cell>
         </row>
         <row r="1184">
           <cell r="C1184">
-            <v>15301003</v>
+            <v>15301001</v>
           </cell>
         </row>
         <row r="1185">
           <cell r="C1185">
-            <v>15301004</v>
+            <v>15301002</v>
           </cell>
         </row>
         <row r="1186">
           <cell r="C1186">
-            <v>15301005</v>
+            <v>15301003</v>
           </cell>
         </row>
         <row r="1187">
           <cell r="C1187">
-            <v>15301006</v>
+            <v>15301004</v>
           </cell>
         </row>
         <row r="1188">
           <cell r="C1188">
-            <v>15302001</v>
+            <v>15301005</v>
           </cell>
         </row>
         <row r="1189">
           <cell r="C1189">
-            <v>15302002</v>
+            <v>15301006</v>
           </cell>
         </row>
         <row r="1190">
           <cell r="C1190">
-            <v>15302003</v>
+            <v>15302001</v>
           </cell>
         </row>
         <row r="1191">
           <cell r="C1191">
-            <v>15302004</v>
+            <v>15302002</v>
           </cell>
         </row>
         <row r="1192">
           <cell r="C1192">
-            <v>15302005</v>
+            <v>15302003</v>
           </cell>
         </row>
         <row r="1193">
           <cell r="C1193">
-            <v>15302006</v>
+            <v>15302004</v>
           </cell>
         </row>
         <row r="1194">
           <cell r="C1194">
-            <v>15302007</v>
+            <v>15302005</v>
           </cell>
         </row>
         <row r="1195">
           <cell r="C1195">
-            <v>15303001</v>
+            <v>15302006</v>
           </cell>
         </row>
         <row r="1196">
           <cell r="C1196">
-            <v>15303002</v>
+            <v>15302007</v>
           </cell>
         </row>
         <row r="1197">
           <cell r="C1197">
-            <v>15303003</v>
+            <v>15303001</v>
           </cell>
         </row>
         <row r="1198">
           <cell r="C1198">
-            <v>15303004</v>
+            <v>15303002</v>
           </cell>
         </row>
         <row r="1199">
           <cell r="C1199">
-            <v>15303005</v>
+            <v>15303003</v>
           </cell>
         </row>
         <row r="1200">
           <cell r="C1200">
-            <v>15303006</v>
+            <v>15303004</v>
           </cell>
         </row>
         <row r="1201">
           <cell r="C1201">
-            <v>15304001</v>
+            <v>15303005</v>
           </cell>
         </row>
         <row r="1202">
           <cell r="C1202">
-            <v>15304002</v>
+            <v>15303006</v>
           </cell>
         </row>
         <row r="1203">
           <cell r="C1203">
-            <v>15304003</v>
+            <v>15304001</v>
           </cell>
         </row>
         <row r="1204">
           <cell r="C1204">
-            <v>15304004</v>
+            <v>15304002</v>
           </cell>
         </row>
         <row r="1205">
           <cell r="C1205">
-            <v>15304005</v>
+            <v>15304003</v>
           </cell>
         </row>
         <row r="1206">
           <cell r="C1206">
-            <v>15304006</v>
+            <v>15304004</v>
           </cell>
         </row>
         <row r="1207">
           <cell r="C1207">
-            <v>15305001</v>
+            <v>15304005</v>
           </cell>
         </row>
         <row r="1208">
           <cell r="C1208">
-            <v>15305002</v>
+            <v>15304006</v>
           </cell>
         </row>
         <row r="1209">
           <cell r="C1209">
-            <v>15305003</v>
+            <v>15305001</v>
           </cell>
         </row>
         <row r="1210">
           <cell r="C1210">
-            <v>15305004</v>
+            <v>15305002</v>
           </cell>
         </row>
         <row r="1211">
           <cell r="C1211">
-            <v>15305005</v>
+            <v>15305003</v>
           </cell>
         </row>
         <row r="1212">
           <cell r="C1212">
-            <v>15305006</v>
+            <v>15305004</v>
           </cell>
         </row>
         <row r="1213">
           <cell r="C1213">
-            <v>15306001</v>
+            <v>15305005</v>
           </cell>
         </row>
         <row r="1214">
           <cell r="C1214">
-            <v>15306002</v>
+            <v>15305006</v>
           </cell>
         </row>
         <row r="1215">
           <cell r="C1215">
-            <v>15306003</v>
+            <v>15306001</v>
           </cell>
         </row>
         <row r="1216">
           <cell r="C1216">
-            <v>15307001</v>
+            <v>15306002</v>
           </cell>
         </row>
         <row r="1217">
           <cell r="C1217">
-            <v>15307002</v>
+            <v>15306003</v>
           </cell>
         </row>
         <row r="1218">
           <cell r="C1218">
-            <v>15308001</v>
-          </cell>
-          <cell r="S1218">
-            <v>66001006</v>
+            <v>15307001</v>
           </cell>
         </row>
         <row r="1219">
           <cell r="C1219">
-            <v>15308002</v>
-          </cell>
-          <cell r="S1219">
-            <v>66001007</v>
+            <v>15307002</v>
           </cell>
         </row>
         <row r="1220">
           <cell r="C1220">
-            <v>15308003</v>
-          </cell>
-          <cell r="S1220">
-            <v>66001014</v>
+            <v>15308001</v>
           </cell>
         </row>
         <row r="1221">
           <cell r="C1221">
-            <v>15308004</v>
-          </cell>
-          <cell r="S1221">
-            <v>66001017</v>
+            <v>15308002</v>
           </cell>
         </row>
         <row r="1222">
           <cell r="C1222">
-            <v>15309001</v>
+            <v>15308003</v>
           </cell>
         </row>
         <row r="1223">
           <cell r="C1223">
-            <v>15309002</v>
+            <v>15308004</v>
           </cell>
         </row>
         <row r="1224">
           <cell r="C1224">
-            <v>15309003</v>
+            <v>15309001</v>
           </cell>
         </row>
         <row r="1225">
           <cell r="C1225">
-            <v>15310001</v>
+            <v>15309002</v>
           </cell>
         </row>
         <row r="1226">
           <cell r="C1226">
-            <v>15310002</v>
+            <v>15309003</v>
           </cell>
         </row>
         <row r="1227">
           <cell r="C1227">
-            <v>15310003</v>
+            <v>15310001</v>
           </cell>
         </row>
         <row r="1228">
           <cell r="C1228">
-            <v>15310004</v>
+            <v>15310002</v>
           </cell>
         </row>
         <row r="1229">
           <cell r="C1229">
-            <v>15310011</v>
-          </cell>
-          <cell r="S1229">
-            <v>69000016</v>
+            <v>15310003</v>
           </cell>
         </row>
         <row r="1230">
           <cell r="C1230">
-            <v>15310012</v>
+            <v>15310004</v>
           </cell>
         </row>
         <row r="1231">
           <cell r="C1231">
-            <v>15310101</v>
+            <v>15310011</v>
           </cell>
         </row>
         <row r="1232">
           <cell r="C1232">
-            <v>15310102</v>
+            <v>15310012</v>
           </cell>
         </row>
         <row r="1233">
           <cell r="C1233">
-            <v>15310103</v>
+            <v>15310101</v>
           </cell>
         </row>
         <row r="1234">
           <cell r="C1234">
-            <v>15310104</v>
+            <v>15310102</v>
           </cell>
         </row>
         <row r="1235">
           <cell r="C1235">
-            <v>15310111</v>
-          </cell>
-          <cell r="S1235">
-            <v>69000018</v>
+            <v>15310103</v>
           </cell>
         </row>
         <row r="1236">
           <cell r="C1236">
-            <v>15310112</v>
+            <v>15310104</v>
           </cell>
         </row>
         <row r="1237">
           <cell r="C1237">
-            <v>15310201</v>
+            <v>15310111</v>
           </cell>
         </row>
         <row r="1238">
           <cell r="C1238">
-            <v>15310202</v>
+            <v>15310112</v>
           </cell>
         </row>
         <row r="1239">
           <cell r="C1239">
-            <v>15310211</v>
-          </cell>
-          <cell r="S1239">
-            <v>69000002</v>
+            <v>15310201</v>
           </cell>
         </row>
         <row r="1240">
           <cell r="C1240">
-            <v>15311001</v>
+            <v>15310202</v>
           </cell>
         </row>
         <row r="1241">
           <cell r="C1241">
-            <v>15311002</v>
+            <v>15310211</v>
           </cell>
         </row>
         <row r="1242">
           <cell r="C1242">
-            <v>15311003</v>
+            <v>15311001</v>
           </cell>
         </row>
         <row r="1243">
           <cell r="C1243">
-            <v>15311004</v>
+            <v>15311002</v>
           </cell>
         </row>
         <row r="1244">
           <cell r="C1244">
-            <v>15311005</v>
+            <v>15311003</v>
           </cell>
         </row>
         <row r="1245">
           <cell r="C1245">
-            <v>15311006</v>
+            <v>15311004</v>
           </cell>
         </row>
         <row r="1246">
           <cell r="C1246">
-            <v>15311011</v>
+            <v>15311005</v>
           </cell>
         </row>
         <row r="1247">
           <cell r="C1247">
-            <v>15311012</v>
+            <v>15311006</v>
           </cell>
         </row>
         <row r="1248">
           <cell r="C1248">
-            <v>15311013</v>
-          </cell>
-          <cell r="S1248">
-            <v>69000006</v>
+            <v>15311011</v>
           </cell>
         </row>
         <row r="1249">
           <cell r="C1249">
-            <v>15401001</v>
+            <v>15311012</v>
           </cell>
         </row>
         <row r="1250">
           <cell r="C1250">
-            <v>15401002</v>
+            <v>15311013</v>
           </cell>
         </row>
         <row r="1251">
           <cell r="C1251">
-            <v>15401003</v>
+            <v>15401001</v>
           </cell>
         </row>
         <row r="1252">
           <cell r="C1252">
-            <v>15401004</v>
+            <v>15401002</v>
           </cell>
         </row>
         <row r="1253">
           <cell r="C1253">
-            <v>15401005</v>
+            <v>15401003</v>
           </cell>
         </row>
         <row r="1254">
           <cell r="C1254">
-            <v>15401006</v>
+            <v>15401004</v>
           </cell>
         </row>
         <row r="1255">
           <cell r="C1255">
-            <v>15401007</v>
+            <v>15401005</v>
           </cell>
         </row>
         <row r="1256">
           <cell r="C1256">
-            <v>15402001</v>
+            <v>15401006</v>
           </cell>
         </row>
         <row r="1257">
           <cell r="C1257">
-            <v>15402002</v>
+            <v>15401007</v>
           </cell>
         </row>
         <row r="1258">
           <cell r="C1258">
-            <v>15402003</v>
+            <v>15402001</v>
           </cell>
         </row>
         <row r="1259">
           <cell r="C1259">
-            <v>15402004</v>
+            <v>15402002</v>
           </cell>
         </row>
         <row r="1260">
           <cell r="C1260">
-            <v>15402005</v>
+            <v>15402003</v>
           </cell>
         </row>
         <row r="1261">
           <cell r="C1261">
-            <v>15402006</v>
+            <v>15402004</v>
           </cell>
         </row>
         <row r="1262">
           <cell r="C1262">
-            <v>15403001</v>
+            <v>15402005</v>
           </cell>
         </row>
         <row r="1263">
           <cell r="C1263">
-            <v>15403002</v>
+            <v>15402006</v>
           </cell>
         </row>
         <row r="1264">
           <cell r="C1264">
-            <v>15403003</v>
+            <v>15403001</v>
           </cell>
         </row>
         <row r="1265">
           <cell r="C1265">
-            <v>15403004</v>
+            <v>15403002</v>
           </cell>
         </row>
         <row r="1266">
           <cell r="C1266">
-            <v>15403005</v>
+            <v>15403003</v>
           </cell>
         </row>
         <row r="1267">
           <cell r="C1267">
-            <v>15403006</v>
+            <v>15403004</v>
           </cell>
         </row>
         <row r="1268">
           <cell r="C1268">
-            <v>15404001</v>
+            <v>15403005</v>
           </cell>
         </row>
         <row r="1269">
           <cell r="C1269">
-            <v>15404002</v>
+            <v>15403006</v>
           </cell>
         </row>
         <row r="1270">
           <cell r="C1270">
-            <v>15404003</v>
+            <v>15404001</v>
           </cell>
         </row>
         <row r="1271">
           <cell r="C1271">
-            <v>15404004</v>
+            <v>15404002</v>
           </cell>
         </row>
         <row r="1272">
           <cell r="C1272">
-            <v>15404005</v>
+            <v>15404003</v>
           </cell>
         </row>
         <row r="1273">
           <cell r="C1273">
-            <v>15404006</v>
+            <v>15404004</v>
           </cell>
         </row>
         <row r="1274">
           <cell r="C1274">
-            <v>15405001</v>
+            <v>15404005</v>
           </cell>
         </row>
         <row r="1275">
           <cell r="C1275">
-            <v>15405002</v>
+            <v>15404006</v>
           </cell>
         </row>
         <row r="1276">
           <cell r="C1276">
-            <v>15405003</v>
+            <v>15405001</v>
           </cell>
         </row>
         <row r="1277">
           <cell r="C1277">
-            <v>15405004</v>
+            <v>15405002</v>
           </cell>
         </row>
         <row r="1278">
           <cell r="C1278">
-            <v>15405005</v>
+            <v>15405003</v>
           </cell>
         </row>
         <row r="1279">
           <cell r="C1279">
-            <v>15405006</v>
+            <v>15405004</v>
           </cell>
         </row>
         <row r="1280">
           <cell r="C1280">
-            <v>15406001</v>
+            <v>15405005</v>
           </cell>
         </row>
         <row r="1281">
           <cell r="C1281">
-            <v>15406002</v>
+            <v>15405006</v>
           </cell>
         </row>
         <row r="1282">
           <cell r="C1282">
-            <v>15406003</v>
-          </cell>
-          <cell r="S1282">
-            <v>69000007</v>
+            <v>15406001</v>
           </cell>
         </row>
         <row r="1283">
           <cell r="C1283">
-            <v>15407001</v>
+            <v>15406002</v>
           </cell>
         </row>
         <row r="1284">
           <cell r="C1284">
-            <v>15407002</v>
+            <v>15406003</v>
           </cell>
         </row>
         <row r="1285">
           <cell r="C1285">
-            <v>15407003</v>
+            <v>15407001</v>
           </cell>
         </row>
         <row r="1286">
           <cell r="C1286">
-            <v>15408001</v>
-          </cell>
-          <cell r="S1286">
-            <v>66001008</v>
+            <v>15407002</v>
           </cell>
         </row>
         <row r="1287">
           <cell r="C1287">
-            <v>15408002</v>
-          </cell>
-          <cell r="S1287">
-            <v>66001009</v>
+            <v>15407003</v>
           </cell>
         </row>
         <row r="1288">
           <cell r="C1288">
-            <v>15408003</v>
-          </cell>
-          <cell r="S1288">
-            <v>66001015</v>
+            <v>15408001</v>
           </cell>
         </row>
         <row r="1289">
           <cell r="C1289">
-            <v>15409001</v>
+            <v>15408002</v>
           </cell>
         </row>
         <row r="1290">
           <cell r="C1290">
-            <v>15409002</v>
+            <v>15408003</v>
           </cell>
         </row>
         <row r="1291">
           <cell r="C1291">
-            <v>15410001</v>
+            <v>15409001</v>
           </cell>
         </row>
         <row r="1292">
           <cell r="C1292">
-            <v>15410002</v>
+            <v>15409002</v>
           </cell>
         </row>
         <row r="1293">
           <cell r="C1293">
-            <v>15410003</v>
+            <v>15410001</v>
           </cell>
         </row>
         <row r="1294">
           <cell r="C1294">
-            <v>15410004</v>
+            <v>15410002</v>
           </cell>
         </row>
         <row r="1295">
           <cell r="C1295">
-            <v>15410011</v>
-          </cell>
-          <cell r="S1295" t="str">
-            <v>69000013;69000017</v>
+            <v>15410003</v>
           </cell>
         </row>
         <row r="1296">
           <cell r="C1296">
-            <v>15410012</v>
+            <v>15410004</v>
           </cell>
         </row>
         <row r="1297">
           <cell r="C1297">
-            <v>15410101</v>
+            <v>15410011</v>
           </cell>
         </row>
         <row r="1298">
           <cell r="C1298">
-            <v>15410102</v>
+            <v>15410012</v>
           </cell>
         </row>
         <row r="1299">
           <cell r="C1299">
-            <v>15410103</v>
+            <v>15410101</v>
           </cell>
         </row>
         <row r="1300">
           <cell r="C1300">
-            <v>15410104</v>
+            <v>15410102</v>
           </cell>
         </row>
         <row r="1301">
           <cell r="C1301">
-            <v>15410111</v>
+            <v>15410103</v>
           </cell>
         </row>
         <row r="1302">
           <cell r="C1302">
-            <v>15410112</v>
-          </cell>
-          <cell r="S1302">
-            <v>69000009</v>
+            <v>15410104</v>
           </cell>
         </row>
         <row r="1303">
           <cell r="C1303">
-            <v>15410201</v>
+            <v>15410111</v>
           </cell>
         </row>
         <row r="1304">
           <cell r="C1304">
-            <v>15410202</v>
+            <v>15410112</v>
           </cell>
         </row>
         <row r="1305">
           <cell r="C1305">
-            <v>15410211</v>
+            <v>15410201</v>
           </cell>
         </row>
         <row r="1306">
           <cell r="C1306">
-            <v>15411001</v>
+            <v>15410202</v>
           </cell>
         </row>
         <row r="1307">
           <cell r="C1307">
-            <v>15411002</v>
+            <v>15410211</v>
           </cell>
         </row>
         <row r="1308">
           <cell r="C1308">
-            <v>15411003</v>
+            <v>15411001</v>
           </cell>
         </row>
         <row r="1309">
           <cell r="C1309">
-            <v>15411004</v>
+            <v>15411002</v>
           </cell>
         </row>
         <row r="1310">
           <cell r="C1310">
-            <v>15411005</v>
+            <v>15411003</v>
           </cell>
         </row>
         <row r="1311">
           <cell r="C1311">
-            <v>15411006</v>
+            <v>15411004</v>
           </cell>
         </row>
         <row r="1312">
           <cell r="C1312">
-            <v>15411011</v>
-          </cell>
-          <cell r="S1312">
-            <v>69000010</v>
+            <v>15411005</v>
           </cell>
         </row>
         <row r="1313">
           <cell r="C1313">
-            <v>15411012</v>
+            <v>15411006</v>
           </cell>
         </row>
         <row r="1314">
           <cell r="C1314">
-            <v>15411013</v>
+            <v>15411011</v>
           </cell>
         </row>
         <row r="1315">
           <cell r="C1315">
-            <v>15501001</v>
+            <v>15411012</v>
           </cell>
         </row>
         <row r="1316">
           <cell r="C1316">
-            <v>15501002</v>
+            <v>15411013</v>
           </cell>
         </row>
         <row r="1317">
           <cell r="C1317">
-            <v>15501003</v>
+            <v>15501001</v>
           </cell>
         </row>
         <row r="1318">
           <cell r="C1318">
-            <v>15501004</v>
+            <v>15501002</v>
           </cell>
         </row>
         <row r="1319">
           <cell r="C1319">
-            <v>15501005</v>
+            <v>15501003</v>
           </cell>
         </row>
         <row r="1320">
           <cell r="C1320">
-            <v>15501006</v>
+            <v>15501004</v>
           </cell>
         </row>
         <row r="1321">
           <cell r="C1321">
-            <v>15502001</v>
+            <v>15501005</v>
           </cell>
         </row>
         <row r="1322">
           <cell r="C1322">
-            <v>15502002</v>
+            <v>15501006</v>
           </cell>
         </row>
         <row r="1323">
           <cell r="C1323">
-            <v>15502003</v>
+            <v>15502001</v>
           </cell>
         </row>
         <row r="1324">
           <cell r="C1324">
-            <v>15502004</v>
+            <v>15502002</v>
           </cell>
         </row>
         <row r="1325">
           <cell r="C1325">
-            <v>15502005</v>
+            <v>15502003</v>
           </cell>
         </row>
         <row r="1326">
           <cell r="C1326">
-            <v>15502006</v>
+            <v>15502004</v>
           </cell>
         </row>
         <row r="1327">
           <cell r="C1327">
-            <v>15503001</v>
+            <v>15502005</v>
           </cell>
         </row>
         <row r="1328">
           <cell r="C1328">
-            <v>15503002</v>
+            <v>15502006</v>
           </cell>
         </row>
         <row r="1329">
           <cell r="C1329">
-            <v>15503003</v>
+            <v>15503001</v>
           </cell>
         </row>
         <row r="1330">
           <cell r="C1330">
-            <v>15503004</v>
+            <v>15503002</v>
           </cell>
         </row>
         <row r="1331">
           <cell r="C1331">
-            <v>15503005</v>
+            <v>15503003</v>
           </cell>
         </row>
         <row r="1332">
           <cell r="C1332">
-            <v>15503006</v>
+            <v>15503004</v>
           </cell>
         </row>
         <row r="1333">
           <cell r="C1333">
-            <v>15503007</v>
+            <v>15503005</v>
           </cell>
         </row>
       </sheetData>
@@ -35826,6 +36557,1298 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91ED6A3E-D209-48A9-B20C-34EAD5F589C0}">
+  <dimension ref="B1:Q100"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="3" width="9" style="22"/>
+    <col min="7" max="7" width="12.625" style="22" customWidth="1"/>
+    <col min="8" max="8" width="9" style="22"/>
+    <col min="9" max="9" width="70.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.625" customWidth="1"/>
+    <col min="15" max="15" width="22.5" customWidth="1"/>
+    <col min="17" max="17" width="19.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="N2" s="3" t="s">
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B3" s="1" t="s">
+        <v>2957</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2962</v>
+      </c>
+      <c r="F3" s="67"/>
+      <c r="G3" s="4" t="s">
+        <v>2957</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>2953</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>2950</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>2978</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>2979</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B4" s="1" t="s">
+        <v>2958</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>2964</v>
+      </c>
+      <c r="F4" s="67"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="3" t="s">
+        <v>2971</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>2982</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B5" s="1" t="s">
+        <v>2960</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>2963</v>
+      </c>
+      <c r="F5" s="67"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="3" t="s">
+        <v>2972</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>2983</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B6" s="1" t="s">
+        <v>2959</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>2961</v>
+      </c>
+      <c r="F6" s="67"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="N6" s="3" t="s">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="4" t="s">
+        <v>2960</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>2954</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>2954</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>2970</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>2995</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="3" t="s">
+        <v>2975</v>
+      </c>
+      <c r="K9" s="3">
+        <v>60</v>
+      </c>
+      <c r="L9" s="3">
+        <f>K9*30</f>
+        <v>1800</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>2697</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>2710</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>2997</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="K10" s="3">
+        <f>K9*9</f>
+        <v>540</v>
+      </c>
+      <c r="N10" s="1">
+        <v>2</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>2699</v>
+      </c>
+      <c r="P10" s="1">
+        <v>300</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="N11" s="1">
+        <v>3</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>2700</v>
+      </c>
+      <c r="P11" s="1">
+        <v>500</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>2999</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="1" t="s">
+        <v>2967</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="4" t="s">
+        <v>2959</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>2955</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>2952</v>
+      </c>
+      <c r="N12" s="1">
+        <v>4</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>2996</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1000</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>2982</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="1" t="s">
+        <v>2968</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4" t="s">
+        <v>2956</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>2969</v>
+      </c>
+      <c r="N13" s="1">
+        <v>5</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>2698</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1500</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="3" t="s">
+        <v>2976</v>
+      </c>
+      <c r="N14" s="1">
+        <v>6</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>3000</v>
+      </c>
+      <c r="P14" s="1">
+        <v>2000</v>
+      </c>
+      <c r="Q14" s="1"/>
+    </row>
+    <row r="15" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B15" s="1" t="s">
+        <v>2992</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="3" t="s">
+        <v>2977</v>
+      </c>
+      <c r="N15" s="1">
+        <v>7</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>2997</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>3002</v>
+      </c>
+      <c r="Q15" s="1"/>
+    </row>
+    <row r="16" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>2991</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>3003</v>
+      </c>
+      <c r="F16" s="67"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="N16" s="1">
+        <v>8</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>2998</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>3002</v>
+      </c>
+      <c r="Q16" s="1"/>
+    </row>
+    <row r="17" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B17" s="1" t="s">
+        <v>2986</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>2987</v>
+      </c>
+      <c r="D17" s="1">
+        <v>10</v>
+      </c>
+      <c r="F17" s="67"/>
+      <c r="G17" s="4" t="s">
+        <v>2958</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>2965</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>2966</v>
+      </c>
+      <c r="N17" s="1">
+        <v>9</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>2999</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>3002</v>
+      </c>
+      <c r="Q17" s="1"/>
+    </row>
+    <row r="18" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B18" s="1" t="s">
+        <v>2988</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>2989</v>
+      </c>
+      <c r="D18" s="1">
+        <v>30</v>
+      </c>
+      <c r="F18" s="67"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="3" t="s">
+        <v>2973</v>
+      </c>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B19" s="1" t="s">
+        <v>2990</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>2989</v>
+      </c>
+      <c r="D19" s="1">
+        <v>100</v>
+      </c>
+      <c r="F19" s="67"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="3" t="s">
+        <v>2974</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="3" t="s">
+        <v>3004</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1">
+        <v>100</v>
+      </c>
+      <c r="E21" s="1">
+        <f>D21/30</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+    </row>
+    <row r="22" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1">
+        <v>2</v>
+      </c>
+      <c r="D22" s="1">
+        <v>300</v>
+      </c>
+      <c r="E22" s="1">
+        <f t="shared" ref="E22:E24" si="0">D22/30</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1">
+        <v>500</v>
+      </c>
+      <c r="E23" s="1">
+        <f t="shared" si="0"/>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>3005</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1">
+        <v>4</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="1">
+        <f t="shared" si="0"/>
+        <v>33.333333333333336</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>3039</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>3042</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="C25" s="1">
+        <v>5</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="G25" s="1" t="s">
+        <v>3039</v>
+      </c>
+      <c r="H25" s="1">
+        <v>2</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>3043</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>2982</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>3039</v>
+      </c>
+      <c r="H26" s="1">
+        <v>3</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>3044</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>2983</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="7"/>
+      <c r="O27" s="3" t="s">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B28" s="3" t="s">
+        <v>2993</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>3009</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>3006</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" ht="20.100000000000001" customHeight="1">
+      <c r="B29" s="3" t="s">
+        <v>2994</v>
+      </c>
+      <c r="E29" s="22"/>
+      <c r="G29" s="1" t="s">
+        <v>3009</v>
+      </c>
+      <c r="H29" s="1">
+        <v>2</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" ht="20.100000000000001" customHeight="1">
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="G30" s="1" t="s">
+        <v>3009</v>
+      </c>
+      <c r="H30" s="1">
+        <v>3</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" ht="20.100000000000001" customHeight="1">
+      <c r="B31" s="3" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="7"/>
+    </row>
+    <row r="32" spans="2:17" ht="20.100000000000001" customHeight="1">
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="G32" s="1" t="s">
+        <v>2960</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>3045</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="G33" s="1" t="s">
+        <v>2960</v>
+      </c>
+      <c r="H33" s="1">
+        <v>2</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="G34" s="1" t="s">
+        <v>2960</v>
+      </c>
+      <c r="H34" s="1">
+        <v>3</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>3047</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="G36" s="1" t="s">
+        <v>3025</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="G37" s="1" t="s">
+        <v>3025</v>
+      </c>
+      <c r="H37" s="1">
+        <v>2</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>3041</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="G38" s="1" t="s">
+        <v>3025</v>
+      </c>
+      <c r="H38" s="1">
+        <v>3</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>3048</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+    </row>
+    <row r="40" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="G40" s="1" t="s">
+        <v>3026</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>3049</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="G41" s="1" t="s">
+        <v>3026</v>
+      </c>
+      <c r="H41" s="1">
+        <v>2</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="G42" s="1" t="s">
+        <v>3026</v>
+      </c>
+      <c r="H42" s="1">
+        <v>3</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>3051</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+    </row>
+    <row r="44" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
+      <c r="G44" s="1" t="s">
+        <v>3031</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3028</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3027</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="G45" s="1" t="s">
+        <v>3031</v>
+      </c>
+      <c r="H45" s="1">
+        <v>2</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3029</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="G46" s="1" t="s">
+        <v>3031</v>
+      </c>
+      <c r="H46" s="1">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>3030</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+    </row>
+    <row r="48" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
+      <c r="G48" s="1" t="s">
+        <v>3069</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3032</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="G49" s="1" t="s">
+        <v>3069</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3033</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
+      <c r="G50" s="1" t="s">
+        <v>3069</v>
+      </c>
+      <c r="H50" s="1">
+        <v>3</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="G52" s="1" t="s">
+        <v>3068</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3053</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="G53" s="1" t="s">
+        <v>3068</v>
+      </c>
+      <c r="H53" s="1">
+        <v>2</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>3054</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="G54" s="1" t="s">
+        <v>3068</v>
+      </c>
+      <c r="H54" s="1">
+        <v>3</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>3055</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
+      <c r="G56" s="1" t="s">
+        <v>3035</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>3036</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="G57" s="1" t="s">
+        <v>3035</v>
+      </c>
+      <c r="H57" s="1">
+        <v>2</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="G58" s="1" t="s">
+        <v>3035</v>
+      </c>
+      <c r="H58" s="1">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3038</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
+    </row>
+    <row r="60" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
+    </row>
+    <row r="61" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+    </row>
+    <row r="62" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
+    </row>
+    <row r="63" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
+    </row>
+    <row r="64" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+      <c r="G64" s="1" t="s">
+        <v>3014</v>
+      </c>
+      <c r="H64" s="1"/>
+      <c r="I64" s="3"/>
+    </row>
+    <row r="65" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
+      <c r="G65" s="1" t="s">
+        <v>3010</v>
+      </c>
+      <c r="H65" s="1">
+        <v>1</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
+      <c r="G66" s="1" t="s">
+        <v>3010</v>
+      </c>
+      <c r="H66" s="1">
+        <v>2</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>3013</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
+      <c r="G67" s="1" t="s">
+        <v>3010</v>
+      </c>
+      <c r="H67" s="1">
+        <v>3</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B68" s="29"/>
+      <c r="C68" s="29"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="3"/>
+    </row>
+    <row r="69" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
+      <c r="G69" s="1" t="s">
+        <v>2961</v>
+      </c>
+      <c r="H69" s="1">
+        <v>1</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>3056</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+      <c r="G70" s="1" t="s">
+        <v>2961</v>
+      </c>
+      <c r="H70" s="1">
+        <v>2</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>3057</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B71" s="29"/>
+      <c r="C71" s="29"/>
+      <c r="G71" s="1" t="s">
+        <v>2961</v>
+      </c>
+      <c r="H71" s="1">
+        <v>3</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>3058</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B72" s="29"/>
+      <c r="C72" s="29"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="3"/>
+    </row>
+    <row r="73" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B73" s="29"/>
+      <c r="C73" s="29"/>
+      <c r="G73" s="1" t="s">
+        <v>3015</v>
+      </c>
+      <c r="H73" s="1">
+        <v>1</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>3059</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B74" s="29"/>
+      <c r="C74" s="29"/>
+      <c r="G74" s="1" t="s">
+        <v>3015</v>
+      </c>
+      <c r="H74" s="1">
+        <v>2</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B75" s="29"/>
+      <c r="C75" s="29"/>
+      <c r="G75" s="1" t="s">
+        <v>3015</v>
+      </c>
+      <c r="H75" s="1">
+        <v>3</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="3"/>
+    </row>
+    <row r="77" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B77" s="29"/>
+      <c r="C77" s="29"/>
+      <c r="G77" s="1" t="s">
+        <v>3016</v>
+      </c>
+      <c r="H77" s="1">
+        <v>1</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>3062</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B78" s="29"/>
+      <c r="C78" s="29"/>
+      <c r="G78" s="1" t="s">
+        <v>3016</v>
+      </c>
+      <c r="H78" s="1">
+        <v>2</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B79" s="29"/>
+      <c r="C79" s="29"/>
+      <c r="G79" s="1" t="s">
+        <v>3016</v>
+      </c>
+      <c r="H79" s="1">
+        <v>3</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>3064</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B80" s="29"/>
+      <c r="C80" s="29"/>
+      <c r="G80" s="29"/>
+      <c r="H80" s="29"/>
+    </row>
+    <row r="81" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B81" s="29"/>
+      <c r="C81" s="29"/>
+      <c r="G81" s="1" t="s">
+        <v>2964</v>
+      </c>
+      <c r="H81" s="1">
+        <v>1</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
+      <c r="G82" s="1" t="s">
+        <v>2964</v>
+      </c>
+      <c r="H82" s="1">
+        <v>2</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>3018</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B83" s="29"/>
+      <c r="C83" s="29"/>
+      <c r="G83" s="1" t="s">
+        <v>2964</v>
+      </c>
+      <c r="H83" s="1">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3019</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B84" s="29"/>
+      <c r="C84" s="29"/>
+      <c r="G84" s="29"/>
+      <c r="H84" s="29"/>
+    </row>
+    <row r="85" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B85" s="29"/>
+      <c r="C85" s="29"/>
+      <c r="G85" s="1" t="s">
+        <v>3023</v>
+      </c>
+      <c r="H85" s="1">
+        <v>1</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B86" s="29"/>
+      <c r="C86" s="29"/>
+      <c r="G86" s="1" t="s">
+        <v>3023</v>
+      </c>
+      <c r="H86" s="1">
+        <v>2</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B87" s="29"/>
+      <c r="C87" s="29"/>
+      <c r="G87" s="1" t="s">
+        <v>3023</v>
+      </c>
+      <c r="H87" s="1">
+        <v>3</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>3022</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
+      <c r="G88" s="29"/>
+      <c r="H88" s="29"/>
+    </row>
+    <row r="89" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B89" s="29"/>
+      <c r="C89" s="29"/>
+      <c r="G89" s="1" t="s">
+        <v>3024</v>
+      </c>
+      <c r="H89" s="1">
+        <v>1</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3065</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B90" s="29"/>
+      <c r="C90" s="29"/>
+      <c r="G90" s="1" t="s">
+        <v>3024</v>
+      </c>
+      <c r="H90" s="1">
+        <v>2</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>3066</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B91" s="29"/>
+      <c r="C91" s="29"/>
+      <c r="G91" s="1" t="s">
+        <v>3024</v>
+      </c>
+      <c r="H91" s="1">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3067</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B92" s="29"/>
+      <c r="C92" s="29"/>
+      <c r="G92" s="29"/>
+      <c r="H92" s="29"/>
+    </row>
+    <row r="93" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B93" s="29"/>
+      <c r="C93" s="29"/>
+      <c r="G93" s="29" t="s">
+        <v>3052</v>
+      </c>
+      <c r="H93" s="29"/>
+    </row>
+    <row r="94" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
+    </row>
+    <row r="95" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B95" s="29"/>
+      <c r="C95" s="29"/>
+    </row>
+    <row r="96" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B96" s="29"/>
+      <c r="C96" s="29"/>
+      <c r="G96" s="29"/>
+      <c r="H96" s="29"/>
+    </row>
+    <row r="97" spans="2:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B97" s="29"/>
+      <c r="C97" s="29"/>
+      <c r="G97" s="29"/>
+      <c r="H97" s="29"/>
+    </row>
+    <row r="98" spans="2:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B98" s="29"/>
+      <c r="C98" s="29"/>
+      <c r="G98" s="29"/>
+      <c r="H98" s="29"/>
+    </row>
+    <row r="99" spans="2:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B99" s="29"/>
+      <c r="C99" s="29"/>
+      <c r="G99" s="29"/>
+      <c r="H99" s="29"/>
+    </row>
+    <row r="100" spans="2:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
+      <c r="G100" s="29"/>
+      <c r="H100" s="29"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="35" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:AV200"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -46131,7 +48154,2078 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H71"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="7" width="9" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1">
+        <f>B2*[1]属性总表!$E$5</f>
+        <v>5250</v>
+      </c>
+      <c r="E2" s="1">
+        <f>ROUND([1]等级属性!C2*[1]属性总表!$F$5,0)</f>
+        <v>500</v>
+      </c>
+      <c r="F2" s="1">
+        <f>ROUND(C2*[1]属性总表!$G$5,0)</f>
+        <v>150</v>
+      </c>
+      <c r="G2" s="1">
+        <f>ROUND(C2*[1]属性总表!$H$5,0)</f>
+        <v>150</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <f>B2+0.25</f>
+        <v>5.25</v>
+      </c>
+      <c r="C3" s="1">
+        <f>C2+0.12</f>
+        <v>5.12</v>
+      </c>
+      <c r="D3" s="1">
+        <f>B3*[1]属性总表!$E$5</f>
+        <v>5512.5</v>
+      </c>
+      <c r="E3" s="1">
+        <f>ROUND([1]等级属性!C3*[1]属性总表!$F$5,0)</f>
+        <v>512</v>
+      </c>
+      <c r="F3" s="1">
+        <f>ROUND(C3*[1]属性总表!$G$5,0)</f>
+        <v>154</v>
+      </c>
+      <c r="G3" s="1">
+        <f>ROUND(C3*[1]属性总表!$H$5,0)</f>
+        <v>154</v>
+      </c>
+      <c r="H3" s="1">
+        <f>D3-D2</f>
+        <v>262.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <f t="shared" ref="B4:B67" si="0">B3+0.25</f>
+        <v>5.5</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" ref="C4:C67" si="1">C3+0.12</f>
+        <v>5.24</v>
+      </c>
+      <c r="D4" s="1">
+        <f>B4*[1]属性总表!$E$5</f>
+        <v>5775</v>
+      </c>
+      <c r="E4" s="1">
+        <f>ROUND([1]等级属性!C4*[1]属性总表!$F$5,0)</f>
+        <v>524</v>
+      </c>
+      <c r="F4" s="1">
+        <f>ROUND(C4*[1]属性总表!$G$5,0)</f>
+        <v>157</v>
+      </c>
+      <c r="G4" s="1">
+        <f>ROUND(C4*[1]属性总表!$H$5,0)</f>
+        <v>157</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <f t="shared" si="0"/>
+        <v>5.75</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="1"/>
+        <v>5.36</v>
+      </c>
+      <c r="D5" s="1">
+        <f>B5*[1]属性总表!$E$5</f>
+        <v>6037.5</v>
+      </c>
+      <c r="E5" s="1">
+        <f>ROUND([1]等级属性!C5*[1]属性总表!$F$5,0)</f>
+        <v>536</v>
+      </c>
+      <c r="F5" s="1">
+        <f>ROUND(C5*[1]属性总表!$G$5,0)</f>
+        <v>161</v>
+      </c>
+      <c r="G5" s="1">
+        <f>ROUND(C5*[1]属性总表!$H$5,0)</f>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="1"/>
+        <v>5.48</v>
+      </c>
+      <c r="D6" s="1">
+        <f>B6*[1]属性总表!$E$5</f>
+        <v>6300</v>
+      </c>
+      <c r="E6" s="1">
+        <f>ROUND([1]等级属性!C6*[1]属性总表!$F$5,0)</f>
+        <v>548</v>
+      </c>
+      <c r="F6" s="1">
+        <f>ROUND(C6*[1]属性总表!$G$5,0)</f>
+        <v>164</v>
+      </c>
+      <c r="G6" s="1">
+        <f>ROUND(C6*[1]属性总表!$H$5,0)</f>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <f t="shared" si="0"/>
+        <v>6.25</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
+      </c>
+      <c r="D7" s="1">
+        <f>B7*[1]属性总表!$E$5</f>
+        <v>6562.5</v>
+      </c>
+      <c r="E7" s="1">
+        <f>ROUND([1]等级属性!C7*[1]属性总表!$F$5,0)</f>
+        <v>560</v>
+      </c>
+      <c r="F7" s="1">
+        <f>ROUND(C7*[1]属性总表!$G$5,0)</f>
+        <v>168</v>
+      </c>
+      <c r="G7" s="1">
+        <f>ROUND(C7*[1]属性总表!$H$5,0)</f>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="1"/>
+        <v>5.7200000000000006</v>
+      </c>
+      <c r="D8" s="1">
+        <f>B8*[1]属性总表!$E$5</f>
+        <v>6825</v>
+      </c>
+      <c r="E8" s="1">
+        <f>ROUND([1]等级属性!C8*[1]属性总表!$F$5,0)</f>
+        <v>572</v>
+      </c>
+      <c r="F8" s="1">
+        <f>ROUND(C8*[1]属性总表!$G$5,0)</f>
+        <v>172</v>
+      </c>
+      <c r="G8" s="1">
+        <f>ROUND(C8*[1]属性总表!$H$5,0)</f>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <f t="shared" si="0"/>
+        <v>6.75</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="1"/>
+        <v>5.8400000000000007</v>
+      </c>
+      <c r="D9" s="1">
+        <f>B9*[1]属性总表!$E$5</f>
+        <v>7087.5</v>
+      </c>
+      <c r="E9" s="1">
+        <f>ROUND([1]等级属性!C9*[1]属性总表!$F$5,0)</f>
+        <v>584</v>
+      </c>
+      <c r="F9" s="1">
+        <f>ROUND(C9*[1]属性总表!$G$5,0)</f>
+        <v>175</v>
+      </c>
+      <c r="G9" s="1">
+        <f>ROUND(C9*[1]属性总表!$H$5,0)</f>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" si="1"/>
+        <v>5.9600000000000009</v>
+      </c>
+      <c r="D10" s="1">
+        <f>B10*[1]属性总表!$E$5</f>
+        <v>7350</v>
+      </c>
+      <c r="E10" s="1">
+        <f>ROUND([1]等级属性!C10*[1]属性总表!$F$5,0)</f>
+        <v>596</v>
+      </c>
+      <c r="F10" s="1">
+        <f>ROUND(C10*[1]属性总表!$G$5,0)</f>
+        <v>179</v>
+      </c>
+      <c r="G10" s="1">
+        <f>ROUND(C10*[1]属性总表!$H$5,0)</f>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <f t="shared" si="0"/>
+        <v>7.25</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" si="1"/>
+        <v>6.080000000000001</v>
+      </c>
+      <c r="D11" s="1">
+        <f>B11*[1]属性总表!$E$5</f>
+        <v>7612.5</v>
+      </c>
+      <c r="E11" s="1">
+        <f>ROUND([1]等级属性!C11*[1]属性总表!$F$5,0)</f>
+        <v>608</v>
+      </c>
+      <c r="F11" s="1">
+        <f>ROUND(C11*[1]属性总表!$G$5,0)</f>
+        <v>182</v>
+      </c>
+      <c r="G11" s="1">
+        <f>ROUND(C11*[1]属性总表!$H$5,0)</f>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" si="1"/>
+        <v>6.2000000000000011</v>
+      </c>
+      <c r="D12" s="1">
+        <f>B12*[1]属性总表!$E$5</f>
+        <v>7875</v>
+      </c>
+      <c r="E12" s="1">
+        <f>ROUND([1]等级属性!C12*[1]属性总表!$F$5,0)</f>
+        <v>620</v>
+      </c>
+      <c r="F12" s="1">
+        <f>ROUND(C12*[1]属性总表!$G$5,0)</f>
+        <v>186</v>
+      </c>
+      <c r="G12" s="1">
+        <f>ROUND(C12*[1]属性总表!$H$5,0)</f>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <f t="shared" si="0"/>
+        <v>7.75</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" si="1"/>
+        <v>6.3200000000000012</v>
+      </c>
+      <c r="D13" s="1">
+        <f>B13*[1]属性总表!$E$5</f>
+        <v>8137.5</v>
+      </c>
+      <c r="E13" s="1">
+        <f>ROUND([1]等级属性!C13*[1]属性总表!$F$5,0)</f>
+        <v>632</v>
+      </c>
+      <c r="F13" s="1">
+        <f>ROUND(C13*[1]属性总表!$G$5,0)</f>
+        <v>190</v>
+      </c>
+      <c r="G13" s="1">
+        <f>ROUND(C13*[1]属性总表!$H$5,0)</f>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="1">
+        <f t="shared" si="1"/>
+        <v>6.4400000000000013</v>
+      </c>
+      <c r="D14" s="1">
+        <f>B14*[1]属性总表!$E$5</f>
+        <v>8400</v>
+      </c>
+      <c r="E14" s="1">
+        <f>ROUND([1]等级属性!C14*[1]属性总表!$F$5,0)</f>
+        <v>644</v>
+      </c>
+      <c r="F14" s="1">
+        <f>ROUND(C14*[1]属性总表!$G$5,0)</f>
+        <v>193</v>
+      </c>
+      <c r="G14" s="1">
+        <f>ROUND(C14*[1]属性总表!$H$5,0)</f>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <f t="shared" si="0"/>
+        <v>8.25</v>
+      </c>
+      <c r="C15" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5600000000000014</v>
+      </c>
+      <c r="D15" s="1">
+        <f>B15*[1]属性总表!$E$5</f>
+        <v>8662.5</v>
+      </c>
+      <c r="E15" s="1">
+        <f>ROUND([1]等级属性!C15*[1]属性总表!$F$5,0)</f>
+        <v>656</v>
+      </c>
+      <c r="F15" s="1">
+        <f>ROUND(C15*[1]属性总表!$G$5,0)</f>
+        <v>197</v>
+      </c>
+      <c r="G15" s="1">
+        <f>ROUND(C15*[1]属性总表!$H$5,0)</f>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+      <c r="C16" s="1">
+        <f t="shared" si="1"/>
+        <v>6.6800000000000015</v>
+      </c>
+      <c r="D16" s="1">
+        <f>B16*[1]属性总表!$E$5</f>
+        <v>8925</v>
+      </c>
+      <c r="E16" s="1">
+        <f>ROUND([1]等级属性!C16*[1]属性总表!$F$5,0)</f>
+        <v>668</v>
+      </c>
+      <c r="F16" s="1">
+        <f>ROUND(C16*[1]属性总表!$G$5,0)</f>
+        <v>200</v>
+      </c>
+      <c r="G16" s="1">
+        <f>ROUND(C16*[1]属性总表!$H$5,0)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <f t="shared" si="0"/>
+        <v>8.75</v>
+      </c>
+      <c r="C17" s="1">
+        <f t="shared" si="1"/>
+        <v>6.8000000000000016</v>
+      </c>
+      <c r="D17" s="1">
+        <f>B17*[1]属性总表!$E$5</f>
+        <v>9187.5</v>
+      </c>
+      <c r="E17" s="1">
+        <f>ROUND([1]等级属性!C17*[1]属性总表!$F$5,0)</f>
+        <v>680</v>
+      </c>
+      <c r="F17" s="1">
+        <f>ROUND(C17*[1]属性总表!$G$5,0)</f>
+        <v>204</v>
+      </c>
+      <c r="G17" s="1">
+        <f>ROUND(C17*[1]属性总表!$H$5,0)</f>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" si="1"/>
+        <v>6.9200000000000017</v>
+      </c>
+      <c r="D18" s="1">
+        <f>B18*[1]属性总表!$E$5</f>
+        <v>9450</v>
+      </c>
+      <c r="E18" s="1">
+        <f>ROUND([1]等级属性!C18*[1]属性总表!$F$5,0)</f>
+        <v>692</v>
+      </c>
+      <c r="F18" s="1">
+        <f>ROUND(C18*[1]属性总表!$G$5,0)</f>
+        <v>208</v>
+      </c>
+      <c r="G18" s="1">
+        <f>ROUND(C18*[1]属性总表!$H$5,0)</f>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <f t="shared" si="0"/>
+        <v>9.25</v>
+      </c>
+      <c r="C19" s="1">
+        <f t="shared" si="1"/>
+        <v>7.0400000000000018</v>
+      </c>
+      <c r="D19" s="1">
+        <f>B19*[1]属性总表!$E$5</f>
+        <v>9712.5</v>
+      </c>
+      <c r="E19" s="1">
+        <f>ROUND([1]等级属性!C19*[1]属性总表!$F$5,0)</f>
+        <v>704</v>
+      </c>
+      <c r="F19" s="1">
+        <f>ROUND(C19*[1]属性总表!$G$5,0)</f>
+        <v>211</v>
+      </c>
+      <c r="G19" s="1">
+        <f>ROUND(C19*[1]属性总表!$H$5,0)</f>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" si="1"/>
+        <v>7.1600000000000019</v>
+      </c>
+      <c r="D20" s="1">
+        <f>B20*[1]属性总表!$E$5</f>
+        <v>9975</v>
+      </c>
+      <c r="E20" s="1">
+        <f>ROUND([1]等级属性!C20*[1]属性总表!$F$5,0)</f>
+        <v>716</v>
+      </c>
+      <c r="F20" s="1">
+        <f>ROUND(C20*[1]属性总表!$G$5,0)</f>
+        <v>215</v>
+      </c>
+      <c r="G20" s="1">
+        <f>ROUND(C20*[1]属性总表!$H$5,0)</f>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <f t="shared" si="0"/>
+        <v>9.75</v>
+      </c>
+      <c r="C21" s="1">
+        <f t="shared" si="1"/>
+        <v>7.280000000000002</v>
+      </c>
+      <c r="D21" s="1">
+        <f>B21*[1]属性总表!$E$5</f>
+        <v>10237.5</v>
+      </c>
+      <c r="E21" s="1">
+        <f>ROUND([1]等级属性!C21*[1]属性总表!$F$5,0)</f>
+        <v>728</v>
+      </c>
+      <c r="F21" s="1">
+        <f>ROUND(C21*[1]属性总表!$G$5,0)</f>
+        <v>218</v>
+      </c>
+      <c r="G21" s="1">
+        <f>ROUND(C21*[1]属性总表!$H$5,0)</f>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" si="1"/>
+        <v>7.4000000000000021</v>
+      </c>
+      <c r="D22" s="1">
+        <f>B22*[1]属性总表!$E$5</f>
+        <v>10500</v>
+      </c>
+      <c r="E22" s="1">
+        <f>ROUND([1]等级属性!C22*[1]属性总表!$F$5,0)</f>
+        <v>740</v>
+      </c>
+      <c r="F22" s="1">
+        <f>ROUND(C22*[1]属性总表!$G$5,0)</f>
+        <v>222</v>
+      </c>
+      <c r="G22" s="1">
+        <f>ROUND(C22*[1]属性总表!$H$5,0)</f>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <f t="shared" si="0"/>
+        <v>10.25</v>
+      </c>
+      <c r="C23" s="1">
+        <f t="shared" si="1"/>
+        <v>7.5200000000000022</v>
+      </c>
+      <c r="D23" s="1">
+        <f>B23*[1]属性总表!$E$5</f>
+        <v>10762.5</v>
+      </c>
+      <c r="E23" s="1">
+        <f>ROUND([1]等级属性!C23*[1]属性总表!$F$5,0)</f>
+        <v>752</v>
+      </c>
+      <c r="F23" s="1">
+        <f>ROUND(C23*[1]属性总表!$G$5,0)</f>
+        <v>226</v>
+      </c>
+      <c r="G23" s="1">
+        <f>ROUND(C23*[1]属性总表!$H$5,0)</f>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" si="1"/>
+        <v>7.6400000000000023</v>
+      </c>
+      <c r="D24" s="1">
+        <f>B24*[1]属性总表!$E$5</f>
+        <v>11025</v>
+      </c>
+      <c r="E24" s="1">
+        <f>ROUND([1]等级属性!C24*[1]属性总表!$F$5,0)</f>
+        <v>764</v>
+      </c>
+      <c r="F24" s="1">
+        <f>ROUND(C24*[1]属性总表!$G$5,0)</f>
+        <v>229</v>
+      </c>
+      <c r="G24" s="1">
+        <f>ROUND(C24*[1]属性总表!$H$5,0)</f>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
+        <f t="shared" si="0"/>
+        <v>10.75</v>
+      </c>
+      <c r="C25" s="1">
+        <f t="shared" si="1"/>
+        <v>7.7600000000000025</v>
+      </c>
+      <c r="D25" s="1">
+        <f>B25*[1]属性总表!$E$5</f>
+        <v>11287.5</v>
+      </c>
+      <c r="E25" s="1">
+        <f>ROUND([1]等级属性!C25*[1]属性总表!$F$5,0)</f>
+        <v>776</v>
+      </c>
+      <c r="F25" s="1">
+        <f>ROUND(C25*[1]属性总表!$G$5,0)</f>
+        <v>233</v>
+      </c>
+      <c r="G25" s="1">
+        <f>ROUND(C25*[1]属性总表!$H$5,0)</f>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C26" s="1">
+        <f t="shared" si="1"/>
+        <v>7.8800000000000026</v>
+      </c>
+      <c r="D26" s="1">
+        <f>B26*[1]属性总表!$E$5</f>
+        <v>11550</v>
+      </c>
+      <c r="E26" s="1">
+        <f>ROUND([1]等级属性!C26*[1]属性总表!$F$5,0)</f>
+        <v>788</v>
+      </c>
+      <c r="F26" s="1">
+        <f>ROUND(C26*[1]属性总表!$G$5,0)</f>
+        <v>236</v>
+      </c>
+      <c r="G26" s="1">
+        <f>ROUND(C26*[1]属性总表!$H$5,0)</f>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
+        <f t="shared" si="0"/>
+        <v>11.25</v>
+      </c>
+      <c r="C27" s="1">
+        <f t="shared" si="1"/>
+        <v>8.0000000000000018</v>
+      </c>
+      <c r="D27" s="1">
+        <f>B27*[1]属性总表!$E$5</f>
+        <v>11812.5</v>
+      </c>
+      <c r="E27" s="1">
+        <f>ROUND([1]等级属性!C27*[1]属性总表!$F$5,0)</f>
+        <v>800</v>
+      </c>
+      <c r="F27" s="1">
+        <f>ROUND(C27*[1]属性总表!$G$5,0)</f>
+        <v>240</v>
+      </c>
+      <c r="G27" s="1">
+        <f>ROUND(C27*[1]属性总表!$H$5,0)</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="C28" s="1">
+        <f t="shared" si="1"/>
+        <v>8.120000000000001</v>
+      </c>
+      <c r="D28" s="1">
+        <f>B28*[1]属性总表!$E$5</f>
+        <v>12075</v>
+      </c>
+      <c r="E28" s="1">
+        <f>ROUND([1]等级属性!C28*[1]属性总表!$F$5,0)</f>
+        <v>812</v>
+      </c>
+      <c r="F28" s="1">
+        <f>ROUND(C28*[1]属性总表!$G$5,0)</f>
+        <v>244</v>
+      </c>
+      <c r="G28" s="1">
+        <f>ROUND(C28*[1]属性总表!$H$5,0)</f>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <f t="shared" si="0"/>
+        <v>11.75</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="shared" si="1"/>
+        <v>8.24</v>
+      </c>
+      <c r="D29" s="1">
+        <f>B29*[1]属性总表!$E$5</f>
+        <v>12337.5</v>
+      </c>
+      <c r="E29" s="1">
+        <f>ROUND([1]等级属性!C29*[1]属性总表!$F$5,0)</f>
+        <v>824</v>
+      </c>
+      <c r="F29" s="1">
+        <f>ROUND(C29*[1]属性总表!$G$5,0)</f>
+        <v>247</v>
+      </c>
+      <c r="G29" s="1">
+        <f>ROUND(C29*[1]属性总表!$H$5,0)</f>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C30" s="1">
+        <f t="shared" si="1"/>
+        <v>8.36</v>
+      </c>
+      <c r="D30" s="1">
+        <f>B30*[1]属性总表!$E$5</f>
+        <v>12600</v>
+      </c>
+      <c r="E30" s="1">
+        <f>ROUND([1]等级属性!C30*[1]属性总表!$F$5,0)</f>
+        <v>836</v>
+      </c>
+      <c r="F30" s="1">
+        <f>ROUND(C30*[1]属性总表!$G$5,0)</f>
+        <v>251</v>
+      </c>
+      <c r="G30" s="1">
+        <f>ROUND(C30*[1]属性总表!$H$5,0)</f>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1">
+        <f t="shared" si="0"/>
+        <v>12.25</v>
+      </c>
+      <c r="C31" s="1">
+        <f t="shared" si="1"/>
+        <v>8.4799999999999986</v>
+      </c>
+      <c r="D31" s="1">
+        <f>B31*[1]属性总表!$E$5</f>
+        <v>12862.5</v>
+      </c>
+      <c r="E31" s="1">
+        <f>ROUND([1]等级属性!C31*[1]属性总表!$F$5,0)</f>
+        <v>848</v>
+      </c>
+      <c r="F31" s="1">
+        <f>ROUND(C31*[1]属性总表!$G$5,0)</f>
+        <v>254</v>
+      </c>
+      <c r="G31" s="1">
+        <f>ROUND(C31*[1]属性总表!$H$5,0)</f>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="C32" s="1">
+        <f t="shared" si="1"/>
+        <v>8.5999999999999979</v>
+      </c>
+      <c r="D32" s="1">
+        <f>B32*[1]属性总表!$E$5</f>
+        <v>13125</v>
+      </c>
+      <c r="E32" s="1">
+        <f>ROUND([1]等级属性!C32*[1]属性总表!$F$5,0)</f>
+        <v>860</v>
+      </c>
+      <c r="F32" s="1">
+        <f>ROUND(C32*[1]属性总表!$G$5,0)</f>
+        <v>258</v>
+      </c>
+      <c r="G32" s="1">
+        <f>ROUND(C32*[1]属性总表!$H$5,0)</f>
+        <v>258</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
+        <f t="shared" si="0"/>
+        <v>12.75</v>
+      </c>
+      <c r="C33" s="1">
+        <f t="shared" si="1"/>
+        <v>8.7199999999999971</v>
+      </c>
+      <c r="D33" s="1">
+        <f>B33*[1]属性总表!$E$5</f>
+        <v>13387.5</v>
+      </c>
+      <c r="E33" s="1">
+        <f>ROUND([1]等级属性!C33*[1]属性总表!$F$5,0)</f>
+        <v>872</v>
+      </c>
+      <c r="F33" s="1">
+        <f>ROUND(C33*[1]属性总表!$G$5,0)</f>
+        <v>262</v>
+      </c>
+      <c r="G33" s="1">
+        <f>ROUND(C33*[1]属性总表!$H$5,0)</f>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C34" s="1">
+        <f t="shared" si="1"/>
+        <v>8.8399999999999963</v>
+      </c>
+      <c r="D34" s="1">
+        <f>B34*[1]属性总表!$E$5</f>
+        <v>13650</v>
+      </c>
+      <c r="E34" s="1">
+        <f>ROUND([1]等级属性!C34*[1]属性总表!$F$5,0)</f>
+        <v>884</v>
+      </c>
+      <c r="F34" s="1">
+        <f>ROUND(C34*[1]属性总表!$G$5,0)</f>
+        <v>265</v>
+      </c>
+      <c r="G34" s="1">
+        <f>ROUND(C34*[1]属性总表!$H$5,0)</f>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <f t="shared" si="0"/>
+        <v>13.25</v>
+      </c>
+      <c r="C35" s="1">
+        <f t="shared" si="1"/>
+        <v>8.9599999999999955</v>
+      </c>
+      <c r="D35" s="1">
+        <f>B35*[1]属性总表!$E$5</f>
+        <v>13912.5</v>
+      </c>
+      <c r="E35" s="1">
+        <f>ROUND([1]等级属性!C35*[1]属性总表!$F$5,0)</f>
+        <v>896</v>
+      </c>
+      <c r="F35" s="1">
+        <f>ROUND(C35*[1]属性总表!$G$5,0)</f>
+        <v>269</v>
+      </c>
+      <c r="G35" s="1">
+        <f>ROUND(C35*[1]属性总表!$H$5,0)</f>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="C36" s="1">
+        <f t="shared" si="1"/>
+        <v>9.0799999999999947</v>
+      </c>
+      <c r="D36" s="1">
+        <f>B36*[1]属性总表!$E$5</f>
+        <v>14175</v>
+      </c>
+      <c r="E36" s="1">
+        <f>ROUND([1]等级属性!C36*[1]属性总表!$F$5,0)</f>
+        <v>908</v>
+      </c>
+      <c r="F36" s="1">
+        <f>ROUND(C36*[1]属性总表!$G$5,0)</f>
+        <v>272</v>
+      </c>
+      <c r="G36" s="1">
+        <f>ROUND(C36*[1]属性总表!$H$5,0)</f>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1">
+        <f t="shared" si="0"/>
+        <v>13.75</v>
+      </c>
+      <c r="C37" s="1">
+        <f t="shared" si="1"/>
+        <v>9.199999999999994</v>
+      </c>
+      <c r="D37" s="1">
+        <f>B37*[1]属性总表!$E$5</f>
+        <v>14437.5</v>
+      </c>
+      <c r="E37" s="1">
+        <f>ROUND([1]等级属性!C37*[1]属性总表!$F$5,0)</f>
+        <v>920</v>
+      </c>
+      <c r="F37" s="1">
+        <f>ROUND(C37*[1]属性总表!$G$5,0)</f>
+        <v>276</v>
+      </c>
+      <c r="G37" s="1">
+        <f>ROUND(C37*[1]属性总表!$H$5,0)</f>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C38" s="1">
+        <f t="shared" si="1"/>
+        <v>9.3199999999999932</v>
+      </c>
+      <c r="D38" s="1">
+        <f>B38*[1]属性总表!$E$5</f>
+        <v>14700</v>
+      </c>
+      <c r="E38" s="1">
+        <f>ROUND([1]等级属性!C38*[1]属性总表!$F$5,0)</f>
+        <v>932</v>
+      </c>
+      <c r="F38" s="1">
+        <f>ROUND(C38*[1]属性总表!$G$5,0)</f>
+        <v>280</v>
+      </c>
+      <c r="G38" s="1">
+        <f>ROUND(C38*[1]属性总表!$H$5,0)</f>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1">
+        <f t="shared" si="0"/>
+        <v>14.25</v>
+      </c>
+      <c r="C39" s="1">
+        <f t="shared" si="1"/>
+        <v>9.4399999999999924</v>
+      </c>
+      <c r="D39" s="1">
+        <f>B39*[1]属性总表!$E$5</f>
+        <v>14962.5</v>
+      </c>
+      <c r="E39" s="1">
+        <f>ROUND([1]等级属性!C39*[1]属性总表!$F$5,0)</f>
+        <v>944</v>
+      </c>
+      <c r="F39" s="1">
+        <f>ROUND(C39*[1]属性总表!$G$5,0)</f>
+        <v>283</v>
+      </c>
+      <c r="G39" s="1">
+        <f>ROUND(C39*[1]属性总表!$H$5,0)</f>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+      <c r="C40" s="1">
+        <f t="shared" si="1"/>
+        <v>9.5599999999999916</v>
+      </c>
+      <c r="D40" s="1">
+        <f>B40*[1]属性总表!$E$5</f>
+        <v>15225</v>
+      </c>
+      <c r="E40" s="1">
+        <f>ROUND([1]等级属性!C40*[1]属性总表!$F$5,0)</f>
+        <v>956</v>
+      </c>
+      <c r="F40" s="1">
+        <f>ROUND(C40*[1]属性总表!$G$5,0)</f>
+        <v>287</v>
+      </c>
+      <c r="G40" s="1">
+        <f>ROUND(C40*[1]属性总表!$H$5,0)</f>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1">
+        <f t="shared" si="0"/>
+        <v>14.75</v>
+      </c>
+      <c r="C41" s="1">
+        <f t="shared" si="1"/>
+        <v>9.6799999999999908</v>
+      </c>
+      <c r="D41" s="1">
+        <f>B41*[1]属性总表!$E$5</f>
+        <v>15487.5</v>
+      </c>
+      <c r="E41" s="1">
+        <f>ROUND([1]等级属性!C41*[1]属性总表!$F$5,0)</f>
+        <v>968</v>
+      </c>
+      <c r="F41" s="1">
+        <f>ROUND(C41*[1]属性总表!$G$5,0)</f>
+        <v>290</v>
+      </c>
+      <c r="G41" s="1">
+        <f>ROUND(C41*[1]属性总表!$H$5,0)</f>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C42" s="1">
+        <f t="shared" si="1"/>
+        <v>9.7999999999999901</v>
+      </c>
+      <c r="D42" s="1">
+        <f>B42*[1]属性总表!$E$5</f>
+        <v>15750</v>
+      </c>
+      <c r="E42" s="1">
+        <f>ROUND([1]等级属性!C42*[1]属性总表!$F$5,0)</f>
+        <v>980</v>
+      </c>
+      <c r="F42" s="1">
+        <f>ROUND(C42*[1]属性总表!$G$5,0)</f>
+        <v>294</v>
+      </c>
+      <c r="G42" s="1">
+        <f>ROUND(C42*[1]属性总表!$H$5,0)</f>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <f t="shared" si="0"/>
+        <v>15.25</v>
+      </c>
+      <c r="C43" s="1">
+        <f t="shared" si="1"/>
+        <v>9.9199999999999893</v>
+      </c>
+      <c r="D43" s="1">
+        <f>B43*[1]属性总表!$E$5</f>
+        <v>16012.5</v>
+      </c>
+      <c r="E43" s="1">
+        <f>ROUND([1]等级属性!C43*[1]属性总表!$F$5,0)</f>
+        <v>992</v>
+      </c>
+      <c r="F43" s="1">
+        <f>ROUND(C43*[1]属性总表!$G$5,0)</f>
+        <v>298</v>
+      </c>
+      <c r="G43" s="1">
+        <f>ROUND(C43*[1]属性总表!$H$5,0)</f>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="C44" s="1">
+        <f t="shared" si="1"/>
+        <v>10.039999999999988</v>
+      </c>
+      <c r="D44" s="1">
+        <f>B44*[1]属性总表!$E$5</f>
+        <v>16275</v>
+      </c>
+      <c r="E44" s="1">
+        <f>ROUND([1]等级属性!C44*[1]属性总表!$F$5,0)</f>
+        <v>1004</v>
+      </c>
+      <c r="F44" s="1">
+        <f>ROUND(C44*[1]属性总表!$G$5,0)</f>
+        <v>301</v>
+      </c>
+      <c r="G44" s="1">
+        <f>ROUND(C44*[1]属性总表!$H$5,0)</f>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1">
+        <f t="shared" si="0"/>
+        <v>15.75</v>
+      </c>
+      <c r="C45" s="1">
+        <f t="shared" si="1"/>
+        <v>10.159999999999988</v>
+      </c>
+      <c r="D45" s="1">
+        <f>B45*[1]属性总表!$E$5</f>
+        <v>16537.5</v>
+      </c>
+      <c r="E45" s="1">
+        <f>ROUND([1]等级属性!C45*[1]属性总表!$F$5,0)</f>
+        <v>1016</v>
+      </c>
+      <c r="F45" s="1">
+        <f>ROUND(C45*[1]属性总表!$G$5,0)</f>
+        <v>305</v>
+      </c>
+      <c r="G45" s="1">
+        <f>ROUND(C45*[1]属性总表!$H$5,0)</f>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C46" s="1">
+        <f t="shared" si="1"/>
+        <v>10.279999999999987</v>
+      </c>
+      <c r="D46" s="1">
+        <f>B46*[1]属性总表!$E$5</f>
+        <v>16800</v>
+      </c>
+      <c r="E46" s="1">
+        <f>ROUND([1]等级属性!C46*[1]属性总表!$F$5,0)</f>
+        <v>1028</v>
+      </c>
+      <c r="F46" s="1">
+        <f>ROUND(C46*[1]属性总表!$G$5,0)</f>
+        <v>308</v>
+      </c>
+      <c r="G46" s="1">
+        <f>ROUND(C46*[1]属性总表!$H$5,0)</f>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1">
+        <f t="shared" si="0"/>
+        <v>16.25</v>
+      </c>
+      <c r="C47" s="1">
+        <f t="shared" si="1"/>
+        <v>10.399999999999986</v>
+      </c>
+      <c r="D47" s="1">
+        <f>B47*[1]属性总表!$E$5</f>
+        <v>17062.5</v>
+      </c>
+      <c r="E47" s="1">
+        <f>ROUND([1]等级属性!C47*[1]属性总表!$F$5,0)</f>
+        <v>1040</v>
+      </c>
+      <c r="F47" s="1">
+        <f>ROUND(C47*[1]属性总表!$G$5,0)</f>
+        <v>312</v>
+      </c>
+      <c r="G47" s="1">
+        <f>ROUND(C47*[1]属性总表!$H$5,0)</f>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="C48" s="1">
+        <f t="shared" si="1"/>
+        <v>10.519999999999985</v>
+      </c>
+      <c r="D48" s="1">
+        <f>B48*[1]属性总表!$E$5</f>
+        <v>17325</v>
+      </c>
+      <c r="E48" s="1">
+        <f>ROUND([1]等级属性!C48*[1]属性总表!$F$5,0)</f>
+        <v>1052</v>
+      </c>
+      <c r="F48" s="1">
+        <f>ROUND(C48*[1]属性总表!$G$5,0)</f>
+        <v>316</v>
+      </c>
+      <c r="G48" s="1">
+        <f>ROUND(C48*[1]属性总表!$H$5,0)</f>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1">
+        <f t="shared" si="0"/>
+        <v>16.75</v>
+      </c>
+      <c r="C49" s="1">
+        <f t="shared" si="1"/>
+        <v>10.639999999999985</v>
+      </c>
+      <c r="D49" s="1">
+        <f>B49*[1]属性总表!$E$5</f>
+        <v>17587.5</v>
+      </c>
+      <c r="E49" s="1">
+        <f>ROUND([1]等级属性!C49*[1]属性总表!$F$5,0)</f>
+        <v>1064</v>
+      </c>
+      <c r="F49" s="1">
+        <f>ROUND(C49*[1]属性总表!$G$5,0)</f>
+        <v>319</v>
+      </c>
+      <c r="G49" s="1">
+        <f>ROUND(C49*[1]属性总表!$H$5,0)</f>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C50" s="1">
+        <f t="shared" si="1"/>
+        <v>10.759999999999984</v>
+      </c>
+      <c r="D50" s="1">
+        <f>B50*[1]属性总表!$E$5</f>
+        <v>17850</v>
+      </c>
+      <c r="E50" s="1">
+        <f>ROUND([1]等级属性!C50*[1]属性总表!$F$5,0)</f>
+        <v>1076</v>
+      </c>
+      <c r="F50" s="1">
+        <f>ROUND(C50*[1]属性总表!$G$5,0)</f>
+        <v>323</v>
+      </c>
+      <c r="G50" s="1">
+        <f>ROUND(C50*[1]属性总表!$H$5,0)</f>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1">
+        <f t="shared" si="0"/>
+        <v>17.25</v>
+      </c>
+      <c r="C51" s="1">
+        <f t="shared" si="1"/>
+        <v>10.879999999999983</v>
+      </c>
+      <c r="D51" s="1">
+        <f>B51*[1]属性总表!$E$5</f>
+        <v>18112.5</v>
+      </c>
+      <c r="E51" s="1">
+        <f>ROUND([1]等级属性!C51*[1]属性总表!$F$5,0)</f>
+        <v>1088</v>
+      </c>
+      <c r="F51" s="1">
+        <f>ROUND(C51*[1]属性总表!$G$5,0)</f>
+        <v>326</v>
+      </c>
+      <c r="G51" s="1">
+        <f>ROUND(C51*[1]属性总表!$H$5,0)</f>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+      <c r="C52" s="1">
+        <f t="shared" si="1"/>
+        <v>10.999999999999982</v>
+      </c>
+      <c r="D52" s="1">
+        <f>B52*[1]属性总表!$E$5</f>
+        <v>18375</v>
+      </c>
+      <c r="E52" s="1">
+        <f>ROUND([1]等级属性!C52*[1]属性总表!$F$5,0)</f>
+        <v>1100</v>
+      </c>
+      <c r="F52" s="1">
+        <f>ROUND(C52*[1]属性总表!$G$5,0)</f>
+        <v>330</v>
+      </c>
+      <c r="G52" s="1">
+        <f>ROUND(C52*[1]属性总表!$H$5,0)</f>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1">
+        <f t="shared" si="0"/>
+        <v>17.75</v>
+      </c>
+      <c r="C53" s="1">
+        <f t="shared" si="1"/>
+        <v>11.119999999999981</v>
+      </c>
+      <c r="D53" s="1">
+        <f>B53*[1]属性总表!$E$5</f>
+        <v>18637.5</v>
+      </c>
+      <c r="E53" s="1">
+        <f>ROUND([1]等级属性!C53*[1]属性总表!$F$5,0)</f>
+        <v>1112</v>
+      </c>
+      <c r="F53" s="1">
+        <f>ROUND(C53*[1]属性总表!$G$5,0)</f>
+        <v>334</v>
+      </c>
+      <c r="G53" s="1">
+        <f>ROUND(C53*[1]属性总表!$H$5,0)</f>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C54" s="1">
+        <f t="shared" si="1"/>
+        <v>11.239999999999981</v>
+      </c>
+      <c r="D54" s="1">
+        <f>B54*[1]属性总表!$E$5</f>
+        <v>18900</v>
+      </c>
+      <c r="E54" s="1">
+        <f>ROUND([1]等级属性!C54*[1]属性总表!$F$5,0)</f>
+        <v>1124</v>
+      </c>
+      <c r="F54" s="1">
+        <f>ROUND(C54*[1]属性总表!$G$5,0)</f>
+        <v>337</v>
+      </c>
+      <c r="G54" s="1">
+        <f>ROUND(C54*[1]属性总表!$H$5,0)</f>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1">
+        <f t="shared" si="0"/>
+        <v>18.25</v>
+      </c>
+      <c r="C55" s="1">
+        <f t="shared" si="1"/>
+        <v>11.35999999999998</v>
+      </c>
+      <c r="D55" s="1">
+        <f>B55*[1]属性总表!$E$5</f>
+        <v>19162.5</v>
+      </c>
+      <c r="E55" s="1">
+        <f>ROUND([1]等级属性!C55*[1]属性总表!$F$5,0)</f>
+        <v>1136</v>
+      </c>
+      <c r="F55" s="1">
+        <f>ROUND(C55*[1]属性总表!$G$5,0)</f>
+        <v>341</v>
+      </c>
+      <c r="G55" s="1">
+        <f>ROUND(C55*[1]属性总表!$H$5,0)</f>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1">
+        <f t="shared" si="0"/>
+        <v>18.5</v>
+      </c>
+      <c r="C56" s="1">
+        <f t="shared" si="1"/>
+        <v>11.479999999999979</v>
+      </c>
+      <c r="D56" s="1">
+        <f>B56*[1]属性总表!$E$5</f>
+        <v>19425</v>
+      </c>
+      <c r="E56" s="1">
+        <f>ROUND([1]等级属性!C56*[1]属性总表!$F$5,0)</f>
+        <v>1148</v>
+      </c>
+      <c r="F56" s="1">
+        <f>ROUND(C56*[1]属性总表!$G$5,0)</f>
+        <v>344</v>
+      </c>
+      <c r="G56" s="1">
+        <f>ROUND(C56*[1]属性总表!$H$5,0)</f>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1">
+        <f t="shared" si="0"/>
+        <v>18.75</v>
+      </c>
+      <c r="C57" s="1">
+        <f t="shared" si="1"/>
+        <v>11.599999999999978</v>
+      </c>
+      <c r="D57" s="1">
+        <f>B57*[1]属性总表!$E$5</f>
+        <v>19687.5</v>
+      </c>
+      <c r="E57" s="1">
+        <f>ROUND([1]等级属性!C57*[1]属性总表!$F$5,0)</f>
+        <v>1160</v>
+      </c>
+      <c r="F57" s="1">
+        <f>ROUND(C57*[1]属性总表!$G$5,0)</f>
+        <v>348</v>
+      </c>
+      <c r="G57" s="1">
+        <f>ROUND(C57*[1]属性总表!$H$5,0)</f>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C58" s="1">
+        <f t="shared" si="1"/>
+        <v>11.719999999999978</v>
+      </c>
+      <c r="D58" s="1">
+        <f>B58*[1]属性总表!$E$5</f>
+        <v>19950</v>
+      </c>
+      <c r="E58" s="1">
+        <f>ROUND([1]等级属性!C58*[1]属性总表!$F$5,0)</f>
+        <v>1172</v>
+      </c>
+      <c r="F58" s="1">
+        <f>ROUND(C58*[1]属性总表!$G$5,0)</f>
+        <v>352</v>
+      </c>
+      <c r="G58" s="1">
+        <f>ROUND(C58*[1]属性总表!$H$5,0)</f>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1">
+        <f t="shared" si="0"/>
+        <v>19.25</v>
+      </c>
+      <c r="C59" s="1">
+        <f t="shared" si="1"/>
+        <v>11.839999999999977</v>
+      </c>
+      <c r="D59" s="1">
+        <f>B59*[1]属性总表!$E$5</f>
+        <v>20212.5</v>
+      </c>
+      <c r="E59" s="1">
+        <f>ROUND([1]等级属性!C59*[1]属性总表!$F$5,0)</f>
+        <v>1184</v>
+      </c>
+      <c r="F59" s="1">
+        <f>ROUND(C59*[1]属性总表!$G$5,0)</f>
+        <v>355</v>
+      </c>
+      <c r="G59" s="1">
+        <f>ROUND(C59*[1]属性总表!$H$5,0)</f>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1">
+        <f t="shared" si="0"/>
+        <v>19.5</v>
+      </c>
+      <c r="C60" s="1">
+        <f t="shared" si="1"/>
+        <v>11.959999999999976</v>
+      </c>
+      <c r="D60" s="1">
+        <f>B60*[1]属性总表!$E$5</f>
+        <v>20475</v>
+      </c>
+      <c r="E60" s="1">
+        <f>ROUND([1]等级属性!C60*[1]属性总表!$F$5,0)</f>
+        <v>1196</v>
+      </c>
+      <c r="F60" s="1">
+        <f>ROUND(C60*[1]属性总表!$G$5,0)</f>
+        <v>359</v>
+      </c>
+      <c r="G60" s="1">
+        <f>ROUND(C60*[1]属性总表!$H$5,0)</f>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1">
+        <f t="shared" si="0"/>
+        <v>19.75</v>
+      </c>
+      <c r="C61" s="1">
+        <f t="shared" si="1"/>
+        <v>12.079999999999975</v>
+      </c>
+      <c r="D61" s="1">
+        <f>B61*[1]属性总表!$E$5</f>
+        <v>20737.5</v>
+      </c>
+      <c r="E61" s="1">
+        <f>ROUND([1]等级属性!C61*[1]属性总表!$F$5,0)</f>
+        <v>1208</v>
+      </c>
+      <c r="F61" s="1">
+        <f>ROUND(C61*[1]属性总表!$G$5,0)</f>
+        <v>362</v>
+      </c>
+      <c r="G61" s="1">
+        <f>ROUND(C61*[1]属性总表!$H$5,0)</f>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C62" s="1">
+        <f t="shared" si="1"/>
+        <v>12.199999999999974</v>
+      </c>
+      <c r="D62" s="1">
+        <f>B62*[1]属性总表!$E$5</f>
+        <v>21000</v>
+      </c>
+      <c r="E62" s="1">
+        <f>ROUND([1]等级属性!C62*[1]属性总表!$F$5,0)</f>
+        <v>1220</v>
+      </c>
+      <c r="F62" s="1">
+        <f>ROUND(C62*[1]属性总表!$G$5,0)</f>
+        <v>366</v>
+      </c>
+      <c r="G62" s="1">
+        <f>ROUND(C62*[1]属性总表!$H$5,0)</f>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1">
+        <f t="shared" si="0"/>
+        <v>20.25</v>
+      </c>
+      <c r="C63" s="1">
+        <f t="shared" si="1"/>
+        <v>12.319999999999974</v>
+      </c>
+      <c r="D63" s="1">
+        <f>B63*[1]属性总表!$E$5</f>
+        <v>21262.5</v>
+      </c>
+      <c r="E63" s="1">
+        <f>ROUND([1]等级属性!C63*[1]属性总表!$F$5,0)</f>
+        <v>1232</v>
+      </c>
+      <c r="F63" s="1">
+        <f>ROUND(C63*[1]属性总表!$G$5,0)</f>
+        <v>370</v>
+      </c>
+      <c r="G63" s="1">
+        <f>ROUND(C63*[1]属性总表!$H$5,0)</f>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1">
+        <f t="shared" si="0"/>
+        <v>20.5</v>
+      </c>
+      <c r="C64" s="1">
+        <f t="shared" si="1"/>
+        <v>12.439999999999973</v>
+      </c>
+      <c r="D64" s="1">
+        <f>B64*[1]属性总表!$E$5</f>
+        <v>21525</v>
+      </c>
+      <c r="E64" s="1">
+        <f>ROUND([1]等级属性!C64*[1]属性总表!$F$5,0)</f>
+        <v>1244</v>
+      </c>
+      <c r="F64" s="1">
+        <f>ROUND(C64*[1]属性总表!$G$5,0)</f>
+        <v>373</v>
+      </c>
+      <c r="G64" s="1">
+        <f>ROUND(C64*[1]属性总表!$H$5,0)</f>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1">
+        <f t="shared" si="0"/>
+        <v>20.75</v>
+      </c>
+      <c r="C65" s="1">
+        <f t="shared" si="1"/>
+        <v>12.559999999999972</v>
+      </c>
+      <c r="D65" s="1">
+        <f>B65*[1]属性总表!$E$5</f>
+        <v>21787.5</v>
+      </c>
+      <c r="E65" s="1">
+        <f>ROUND([1]等级属性!C65*[1]属性总表!$F$5,0)</f>
+        <v>1256</v>
+      </c>
+      <c r="F65" s="1">
+        <f>ROUND(C65*[1]属性总表!$G$5,0)</f>
+        <v>377</v>
+      </c>
+      <c r="G65" s="1">
+        <f>ROUND(C65*[1]属性总表!$H$5,0)</f>
+        <v>377</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C66" s="1">
+        <f t="shared" si="1"/>
+        <v>12.679999999999971</v>
+      </c>
+      <c r="D66" s="1">
+        <f>B66*[1]属性总表!$E$5</f>
+        <v>22050</v>
+      </c>
+      <c r="E66" s="1">
+        <f>ROUND([1]等级属性!C66*[1]属性总表!$F$5,0)</f>
+        <v>1268</v>
+      </c>
+      <c r="F66" s="1">
+        <f>ROUND(C66*[1]属性总表!$G$5,0)</f>
+        <v>380</v>
+      </c>
+      <c r="G66" s="1">
+        <f>ROUND(C66*[1]属性总表!$H$5,0)</f>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1">
+        <f t="shared" si="0"/>
+        <v>21.25</v>
+      </c>
+      <c r="C67" s="1">
+        <f t="shared" si="1"/>
+        <v>12.799999999999971</v>
+      </c>
+      <c r="D67" s="1">
+        <f>B67*[1]属性总表!$E$5</f>
+        <v>22312.5</v>
+      </c>
+      <c r="E67" s="1">
+        <f>ROUND([1]等级属性!C67*[1]属性总表!$F$5,0)</f>
+        <v>1280</v>
+      </c>
+      <c r="F67" s="1">
+        <f>ROUND(C67*[1]属性总表!$G$5,0)</f>
+        <v>384</v>
+      </c>
+      <c r="G67" s="1">
+        <f>ROUND(C67*[1]属性总表!$H$5,0)</f>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1">
+        <f t="shared" ref="B68:B71" si="2">B67+0.25</f>
+        <v>21.5</v>
+      </c>
+      <c r="C68" s="1">
+        <f t="shared" ref="C68:C71" si="3">C67+0.12</f>
+        <v>12.91999999999997</v>
+      </c>
+      <c r="D68" s="1">
+        <f>B68*[1]属性总表!$E$5</f>
+        <v>22575</v>
+      </c>
+      <c r="E68" s="1">
+        <f>ROUND([1]等级属性!C68*[1]属性总表!$F$5,0)</f>
+        <v>1292</v>
+      </c>
+      <c r="F68" s="1">
+        <f>ROUND(C68*[1]属性总表!$G$5,0)</f>
+        <v>388</v>
+      </c>
+      <c r="G68" s="1">
+        <f>ROUND(C68*[1]属性总表!$H$5,0)</f>
+        <v>388</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1">
+        <f t="shared" si="2"/>
+        <v>21.75</v>
+      </c>
+      <c r="C69" s="1">
+        <f t="shared" si="3"/>
+        <v>13.039999999999969</v>
+      </c>
+      <c r="D69" s="1">
+        <f>B69*[1]属性总表!$E$5</f>
+        <v>22837.5</v>
+      </c>
+      <c r="E69" s="1">
+        <f>ROUND([1]等级属性!C69*[1]属性总表!$F$5,0)</f>
+        <v>1304</v>
+      </c>
+      <c r="F69" s="1">
+        <f>ROUND(C69*[1]属性总表!$G$5,0)</f>
+        <v>391</v>
+      </c>
+      <c r="G69" s="1">
+        <f>ROUND(C69*[1]属性总表!$H$5,0)</f>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="C70" s="1">
+        <f t="shared" si="3"/>
+        <v>13.159999999999968</v>
+      </c>
+      <c r="D70" s="1">
+        <f>B70*[1]属性总表!$E$5</f>
+        <v>23100</v>
+      </c>
+      <c r="E70" s="1">
+        <f>ROUND([1]等级属性!C70*[1]属性总表!$F$5,0)</f>
+        <v>1316</v>
+      </c>
+      <c r="F70" s="1">
+        <f>ROUND(C70*[1]属性总表!$G$5,0)</f>
+        <v>395</v>
+      </c>
+      <c r="G70" s="1">
+        <f>ROUND(C70*[1]属性总表!$H$5,0)</f>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1">
+        <f t="shared" si="2"/>
+        <v>22.25</v>
+      </c>
+      <c r="C71" s="1">
+        <f t="shared" si="3"/>
+        <v>13.279999999999967</v>
+      </c>
+      <c r="D71" s="1">
+        <f>B71*[1]属性总表!$E$5</f>
+        <v>23362.5</v>
+      </c>
+      <c r="E71" s="1">
+        <f>ROUND([1]等级属性!C71*[1]属性总表!$F$5,0)</f>
+        <v>1328</v>
+      </c>
+      <c r="F71" s="1">
+        <f>ROUND(C71*[1]属性总表!$G$5,0)</f>
+        <v>398</v>
+      </c>
+      <c r="G71" s="1">
+        <f>ROUND(C71*[1]属性总表!$H$5,0)</f>
+        <v>398</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="35" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:U54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -48024,2078 +52118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="7" width="9" style="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1">
-        <f>B2*[1]属性总表!$E$5</f>
-        <v>5250</v>
-      </c>
-      <c r="E2" s="1">
-        <f>ROUND([1]等级属性!C2*[1]属性总表!$F$5,0)</f>
-        <v>500</v>
-      </c>
-      <c r="F2" s="1">
-        <f>ROUND(C2*[1]属性总表!$G$5,0)</f>
-        <v>150</v>
-      </c>
-      <c r="G2" s="1">
-        <f>ROUND(C2*[1]属性总表!$H$5,0)</f>
-        <v>150</v>
-      </c>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <f>B2+0.25</f>
-        <v>5.25</v>
-      </c>
-      <c r="C3" s="1">
-        <f>C2+0.12</f>
-        <v>5.12</v>
-      </c>
-      <c r="D3" s="1">
-        <f>B3*[1]属性总表!$E$5</f>
-        <v>5512.5</v>
-      </c>
-      <c r="E3" s="1">
-        <f>ROUND([1]等级属性!C3*[1]属性总表!$F$5,0)</f>
-        <v>512</v>
-      </c>
-      <c r="F3" s="1">
-        <f>ROUND(C3*[1]属性总表!$G$5,0)</f>
-        <v>154</v>
-      </c>
-      <c r="G3" s="1">
-        <f>ROUND(C3*[1]属性总表!$H$5,0)</f>
-        <v>154</v>
-      </c>
-      <c r="H3" s="1">
-        <f>D3-D2</f>
-        <v>262.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1">
-        <f t="shared" ref="B4:B67" si="0">B3+0.25</f>
-        <v>5.5</v>
-      </c>
-      <c r="C4" s="1">
-        <f t="shared" ref="C4:C67" si="1">C3+0.12</f>
-        <v>5.24</v>
-      </c>
-      <c r="D4" s="1">
-        <f>B4*[1]属性总表!$E$5</f>
-        <v>5775</v>
-      </c>
-      <c r="E4" s="1">
-        <f>ROUND([1]等级属性!C4*[1]属性总表!$F$5,0)</f>
-        <v>524</v>
-      </c>
-      <c r="F4" s="1">
-        <f>ROUND(C4*[1]属性总表!$G$5,0)</f>
-        <v>157</v>
-      </c>
-      <c r="G4" s="1">
-        <f>ROUND(C4*[1]属性总表!$H$5,0)</f>
-        <v>157</v>
-      </c>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
-        <f t="shared" si="0"/>
-        <v>5.75</v>
-      </c>
-      <c r="C5" s="1">
-        <f t="shared" si="1"/>
-        <v>5.36</v>
-      </c>
-      <c r="D5" s="1">
-        <f>B5*[1]属性总表!$E$5</f>
-        <v>6037.5</v>
-      </c>
-      <c r="E5" s="1">
-        <f>ROUND([1]等级属性!C5*[1]属性总表!$F$5,0)</f>
-        <v>536</v>
-      </c>
-      <c r="F5" s="1">
-        <f>ROUND(C5*[1]属性总表!$G$5,0)</f>
-        <v>161</v>
-      </c>
-      <c r="G5" s="1">
-        <f>ROUND(C5*[1]属性总表!$H$5,0)</f>
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C6" s="1">
-        <f t="shared" si="1"/>
-        <v>5.48</v>
-      </c>
-      <c r="D6" s="1">
-        <f>B6*[1]属性总表!$E$5</f>
-        <v>6300</v>
-      </c>
-      <c r="E6" s="1">
-        <f>ROUND([1]等级属性!C6*[1]属性总表!$F$5,0)</f>
-        <v>548</v>
-      </c>
-      <c r="F6" s="1">
-        <f>ROUND(C6*[1]属性总表!$G$5,0)</f>
-        <v>164</v>
-      </c>
-      <c r="G6" s="1">
-        <f>ROUND(C6*[1]属性总表!$H$5,0)</f>
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1">
-        <f t="shared" si="0"/>
-        <v>6.25</v>
-      </c>
-      <c r="C7" s="1">
-        <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
-      </c>
-      <c r="D7" s="1">
-        <f>B7*[1]属性总表!$E$5</f>
-        <v>6562.5</v>
-      </c>
-      <c r="E7" s="1">
-        <f>ROUND([1]等级属性!C7*[1]属性总表!$F$5,0)</f>
-        <v>560</v>
-      </c>
-      <c r="F7" s="1">
-        <f>ROUND(C7*[1]属性总表!$G$5,0)</f>
-        <v>168</v>
-      </c>
-      <c r="G7" s="1">
-        <f>ROUND(C7*[1]属性总表!$H$5,0)</f>
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>6.5</v>
-      </c>
-      <c r="C8" s="1">
-        <f t="shared" si="1"/>
-        <v>5.7200000000000006</v>
-      </c>
-      <c r="D8" s="1">
-        <f>B8*[1]属性总表!$E$5</f>
-        <v>6825</v>
-      </c>
-      <c r="E8" s="1">
-        <f>ROUND([1]等级属性!C8*[1]属性总表!$F$5,0)</f>
-        <v>572</v>
-      </c>
-      <c r="F8" s="1">
-        <f>ROUND(C8*[1]属性总表!$G$5,0)</f>
-        <v>172</v>
-      </c>
-      <c r="G8" s="1">
-        <f>ROUND(C8*[1]属性总表!$H$5,0)</f>
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1">
-        <f t="shared" si="0"/>
-        <v>6.75</v>
-      </c>
-      <c r="C9" s="1">
-        <f t="shared" si="1"/>
-        <v>5.8400000000000007</v>
-      </c>
-      <c r="D9" s="1">
-        <f>B9*[1]属性总表!$E$5</f>
-        <v>7087.5</v>
-      </c>
-      <c r="E9" s="1">
-        <f>ROUND([1]等级属性!C9*[1]属性总表!$F$5,0)</f>
-        <v>584</v>
-      </c>
-      <c r="F9" s="1">
-        <f>ROUND(C9*[1]属性总表!$G$5,0)</f>
-        <v>175</v>
-      </c>
-      <c r="G9" s="1">
-        <f>ROUND(C9*[1]属性总表!$H$5,0)</f>
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C10" s="1">
-        <f t="shared" si="1"/>
-        <v>5.9600000000000009</v>
-      </c>
-      <c r="D10" s="1">
-        <f>B10*[1]属性总表!$E$5</f>
-        <v>7350</v>
-      </c>
-      <c r="E10" s="1">
-        <f>ROUND([1]等级属性!C10*[1]属性总表!$F$5,0)</f>
-        <v>596</v>
-      </c>
-      <c r="F10" s="1">
-        <f>ROUND(C10*[1]属性总表!$G$5,0)</f>
-        <v>179</v>
-      </c>
-      <c r="G10" s="1">
-        <f>ROUND(C10*[1]属性总表!$H$5,0)</f>
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1">
-        <f t="shared" si="0"/>
-        <v>7.25</v>
-      </c>
-      <c r="C11" s="1">
-        <f t="shared" si="1"/>
-        <v>6.080000000000001</v>
-      </c>
-      <c r="D11" s="1">
-        <f>B11*[1]属性总表!$E$5</f>
-        <v>7612.5</v>
-      </c>
-      <c r="E11" s="1">
-        <f>ROUND([1]等级属性!C11*[1]属性总表!$F$5,0)</f>
-        <v>608</v>
-      </c>
-      <c r="F11" s="1">
-        <f>ROUND(C11*[1]属性总表!$G$5,0)</f>
-        <v>182</v>
-      </c>
-      <c r="G11" s="1">
-        <f>ROUND(C11*[1]属性总表!$H$5,0)</f>
-        <v>182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1">
-        <f t="shared" si="0"/>
-        <v>7.5</v>
-      </c>
-      <c r="C12" s="1">
-        <f t="shared" si="1"/>
-        <v>6.2000000000000011</v>
-      </c>
-      <c r="D12" s="1">
-        <f>B12*[1]属性总表!$E$5</f>
-        <v>7875</v>
-      </c>
-      <c r="E12" s="1">
-        <f>ROUND([1]等级属性!C12*[1]属性总表!$F$5,0)</f>
-        <v>620</v>
-      </c>
-      <c r="F12" s="1">
-        <f>ROUND(C12*[1]属性总表!$G$5,0)</f>
-        <v>186</v>
-      </c>
-      <c r="G12" s="1">
-        <f>ROUND(C12*[1]属性总表!$H$5,0)</f>
-        <v>186</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1">
-        <f t="shared" si="0"/>
-        <v>7.75</v>
-      </c>
-      <c r="C13" s="1">
-        <f t="shared" si="1"/>
-        <v>6.3200000000000012</v>
-      </c>
-      <c r="D13" s="1">
-        <f>B13*[1]属性总表!$E$5</f>
-        <v>8137.5</v>
-      </c>
-      <c r="E13" s="1">
-        <f>ROUND([1]等级属性!C13*[1]属性总表!$F$5,0)</f>
-        <v>632</v>
-      </c>
-      <c r="F13" s="1">
-        <f>ROUND(C13*[1]属性总表!$G$5,0)</f>
-        <v>190</v>
-      </c>
-      <c r="G13" s="1">
-        <f>ROUND(C13*[1]属性总表!$H$5,0)</f>
-        <v>190</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C14" s="1">
-        <f t="shared" si="1"/>
-        <v>6.4400000000000013</v>
-      </c>
-      <c r="D14" s="1">
-        <f>B14*[1]属性总表!$E$5</f>
-        <v>8400</v>
-      </c>
-      <c r="E14" s="1">
-        <f>ROUND([1]等级属性!C14*[1]属性总表!$F$5,0)</f>
-        <v>644</v>
-      </c>
-      <c r="F14" s="1">
-        <f>ROUND(C14*[1]属性总表!$G$5,0)</f>
-        <v>193</v>
-      </c>
-      <c r="G14" s="1">
-        <f>ROUND(C14*[1]属性总表!$H$5,0)</f>
-        <v>193</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1">
-        <f t="shared" si="0"/>
-        <v>8.25</v>
-      </c>
-      <c r="C15" s="1">
-        <f t="shared" si="1"/>
-        <v>6.5600000000000014</v>
-      </c>
-      <c r="D15" s="1">
-        <f>B15*[1]属性总表!$E$5</f>
-        <v>8662.5</v>
-      </c>
-      <c r="E15" s="1">
-        <f>ROUND([1]等级属性!C15*[1]属性总表!$F$5,0)</f>
-        <v>656</v>
-      </c>
-      <c r="F15" s="1">
-        <f>ROUND(C15*[1]属性总表!$G$5,0)</f>
-        <v>197</v>
-      </c>
-      <c r="G15" s="1">
-        <f>ROUND(C15*[1]属性总表!$H$5,0)</f>
-        <v>197</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1">
-        <f t="shared" si="0"/>
-        <v>8.5</v>
-      </c>
-      <c r="C16" s="1">
-        <f t="shared" si="1"/>
-        <v>6.6800000000000015</v>
-      </c>
-      <c r="D16" s="1">
-        <f>B16*[1]属性总表!$E$5</f>
-        <v>8925</v>
-      </c>
-      <c r="E16" s="1">
-        <f>ROUND([1]等级属性!C16*[1]属性总表!$F$5,0)</f>
-        <v>668</v>
-      </c>
-      <c r="F16" s="1">
-        <f>ROUND(C16*[1]属性总表!$G$5,0)</f>
-        <v>200</v>
-      </c>
-      <c r="G16" s="1">
-        <f>ROUND(C16*[1]属性总表!$H$5,0)</f>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1">
-        <f t="shared" si="0"/>
-        <v>8.75</v>
-      </c>
-      <c r="C17" s="1">
-        <f t="shared" si="1"/>
-        <v>6.8000000000000016</v>
-      </c>
-      <c r="D17" s="1">
-        <f>B17*[1]属性总表!$E$5</f>
-        <v>9187.5</v>
-      </c>
-      <c r="E17" s="1">
-        <f>ROUND([1]等级属性!C17*[1]属性总表!$F$5,0)</f>
-        <v>680</v>
-      </c>
-      <c r="F17" s="1">
-        <f>ROUND(C17*[1]属性总表!$G$5,0)</f>
-        <v>204</v>
-      </c>
-      <c r="G17" s="1">
-        <f>ROUND(C17*[1]属性总表!$H$5,0)</f>
-        <v>204</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C18" s="1">
-        <f t="shared" si="1"/>
-        <v>6.9200000000000017</v>
-      </c>
-      <c r="D18" s="1">
-        <f>B18*[1]属性总表!$E$5</f>
-        <v>9450</v>
-      </c>
-      <c r="E18" s="1">
-        <f>ROUND([1]等级属性!C18*[1]属性总表!$F$5,0)</f>
-        <v>692</v>
-      </c>
-      <c r="F18" s="1">
-        <f>ROUND(C18*[1]属性总表!$G$5,0)</f>
-        <v>208</v>
-      </c>
-      <c r="G18" s="1">
-        <f>ROUND(C18*[1]属性总表!$H$5,0)</f>
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1">
-        <f t="shared" si="0"/>
-        <v>9.25</v>
-      </c>
-      <c r="C19" s="1">
-        <f t="shared" si="1"/>
-        <v>7.0400000000000018</v>
-      </c>
-      <c r="D19" s="1">
-        <f>B19*[1]属性总表!$E$5</f>
-        <v>9712.5</v>
-      </c>
-      <c r="E19" s="1">
-        <f>ROUND([1]等级属性!C19*[1]属性总表!$F$5,0)</f>
-        <v>704</v>
-      </c>
-      <c r="F19" s="1">
-        <f>ROUND(C19*[1]属性总表!$G$5,0)</f>
-        <v>211</v>
-      </c>
-      <c r="G19" s="1">
-        <f>ROUND(C19*[1]属性总表!$H$5,0)</f>
-        <v>211</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>9.5</v>
-      </c>
-      <c r="C20" s="1">
-        <f t="shared" si="1"/>
-        <v>7.1600000000000019</v>
-      </c>
-      <c r="D20" s="1">
-        <f>B20*[1]属性总表!$E$5</f>
-        <v>9975</v>
-      </c>
-      <c r="E20" s="1">
-        <f>ROUND([1]等级属性!C20*[1]属性总表!$F$5,0)</f>
-        <v>716</v>
-      </c>
-      <c r="F20" s="1">
-        <f>ROUND(C20*[1]属性总表!$G$5,0)</f>
-        <v>215</v>
-      </c>
-      <c r="G20" s="1">
-        <f>ROUND(C20*[1]属性总表!$H$5,0)</f>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1">
-        <f t="shared" si="0"/>
-        <v>9.75</v>
-      </c>
-      <c r="C21" s="1">
-        <f t="shared" si="1"/>
-        <v>7.280000000000002</v>
-      </c>
-      <c r="D21" s="1">
-        <f>B21*[1]属性总表!$E$5</f>
-        <v>10237.5</v>
-      </c>
-      <c r="E21" s="1">
-        <f>ROUND([1]等级属性!C21*[1]属性总表!$F$5,0)</f>
-        <v>728</v>
-      </c>
-      <c r="F21" s="1">
-        <f>ROUND(C21*[1]属性总表!$G$5,0)</f>
-        <v>218</v>
-      </c>
-      <c r="G21" s="1">
-        <f>ROUND(C21*[1]属性总表!$H$5,0)</f>
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C22" s="1">
-        <f t="shared" si="1"/>
-        <v>7.4000000000000021</v>
-      </c>
-      <c r="D22" s="1">
-        <f>B22*[1]属性总表!$E$5</f>
-        <v>10500</v>
-      </c>
-      <c r="E22" s="1">
-        <f>ROUND([1]等级属性!C22*[1]属性总表!$F$5,0)</f>
-        <v>740</v>
-      </c>
-      <c r="F22" s="1">
-        <f>ROUND(C22*[1]属性总表!$G$5,0)</f>
-        <v>222</v>
-      </c>
-      <c r="G22" s="1">
-        <f>ROUND(C22*[1]属性总表!$H$5,0)</f>
-        <v>222</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="1">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1">
-        <f t="shared" si="0"/>
-        <v>10.25</v>
-      </c>
-      <c r="C23" s="1">
-        <f t="shared" si="1"/>
-        <v>7.5200000000000022</v>
-      </c>
-      <c r="D23" s="1">
-        <f>B23*[1]属性总表!$E$5</f>
-        <v>10762.5</v>
-      </c>
-      <c r="E23" s="1">
-        <f>ROUND([1]等级属性!C23*[1]属性总表!$F$5,0)</f>
-        <v>752</v>
-      </c>
-      <c r="F23" s="1">
-        <f>ROUND(C23*[1]属性总表!$G$5,0)</f>
-        <v>226</v>
-      </c>
-      <c r="G23" s="1">
-        <f>ROUND(C23*[1]属性总表!$H$5,0)</f>
-        <v>226</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="1">
-        <v>23</v>
-      </c>
-      <c r="B24" s="1">
-        <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="C24" s="1">
-        <f t="shared" si="1"/>
-        <v>7.6400000000000023</v>
-      </c>
-      <c r="D24" s="1">
-        <f>B24*[1]属性总表!$E$5</f>
-        <v>11025</v>
-      </c>
-      <c r="E24" s="1">
-        <f>ROUND([1]等级属性!C24*[1]属性总表!$F$5,0)</f>
-        <v>764</v>
-      </c>
-      <c r="F24" s="1">
-        <f>ROUND(C24*[1]属性总表!$G$5,0)</f>
-        <v>229</v>
-      </c>
-      <c r="G24" s="1">
-        <f>ROUND(C24*[1]属性总表!$H$5,0)</f>
-        <v>229</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1">
-        <f t="shared" si="0"/>
-        <v>10.75</v>
-      </c>
-      <c r="C25" s="1">
-        <f t="shared" si="1"/>
-        <v>7.7600000000000025</v>
-      </c>
-      <c r="D25" s="1">
-        <f>B25*[1]属性总表!$E$5</f>
-        <v>11287.5</v>
-      </c>
-      <c r="E25" s="1">
-        <f>ROUND([1]等级属性!C25*[1]属性总表!$F$5,0)</f>
-        <v>776</v>
-      </c>
-      <c r="F25" s="1">
-        <f>ROUND(C25*[1]属性总表!$G$5,0)</f>
-        <v>233</v>
-      </c>
-      <c r="G25" s="1">
-        <f>ROUND(C25*[1]属性总表!$H$5,0)</f>
-        <v>233</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="1">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C26" s="1">
-        <f t="shared" si="1"/>
-        <v>7.8800000000000026</v>
-      </c>
-      <c r="D26" s="1">
-        <f>B26*[1]属性总表!$E$5</f>
-        <v>11550</v>
-      </c>
-      <c r="E26" s="1">
-        <f>ROUND([1]等级属性!C26*[1]属性总表!$F$5,0)</f>
-        <v>788</v>
-      </c>
-      <c r="F26" s="1">
-        <f>ROUND(C26*[1]属性总表!$G$5,0)</f>
-        <v>236</v>
-      </c>
-      <c r="G26" s="1">
-        <f>ROUND(C26*[1]属性总表!$H$5,0)</f>
-        <v>236</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="1">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1">
-        <f t="shared" si="0"/>
-        <v>11.25</v>
-      </c>
-      <c r="C27" s="1">
-        <f t="shared" si="1"/>
-        <v>8.0000000000000018</v>
-      </c>
-      <c r="D27" s="1">
-        <f>B27*[1]属性总表!$E$5</f>
-        <v>11812.5</v>
-      </c>
-      <c r="E27" s="1">
-        <f>ROUND([1]等级属性!C27*[1]属性总表!$F$5,0)</f>
-        <v>800</v>
-      </c>
-      <c r="F27" s="1">
-        <f>ROUND(C27*[1]属性总表!$G$5,0)</f>
-        <v>240</v>
-      </c>
-      <c r="G27" s="1">
-        <f>ROUND(C27*[1]属性总表!$H$5,0)</f>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="1">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1">
-        <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="C28" s="1">
-        <f t="shared" si="1"/>
-        <v>8.120000000000001</v>
-      </c>
-      <c r="D28" s="1">
-        <f>B28*[1]属性总表!$E$5</f>
-        <v>12075</v>
-      </c>
-      <c r="E28" s="1">
-        <f>ROUND([1]等级属性!C28*[1]属性总表!$F$5,0)</f>
-        <v>812</v>
-      </c>
-      <c r="F28" s="1">
-        <f>ROUND(C28*[1]属性总表!$G$5,0)</f>
-        <v>244</v>
-      </c>
-      <c r="G28" s="1">
-        <f>ROUND(C28*[1]属性总表!$H$5,0)</f>
-        <v>244</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="1">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1">
-        <f t="shared" si="0"/>
-        <v>11.75</v>
-      </c>
-      <c r="C29" s="1">
-        <f t="shared" si="1"/>
-        <v>8.24</v>
-      </c>
-      <c r="D29" s="1">
-        <f>B29*[1]属性总表!$E$5</f>
-        <v>12337.5</v>
-      </c>
-      <c r="E29" s="1">
-        <f>ROUND([1]等级属性!C29*[1]属性总表!$F$5,0)</f>
-        <v>824</v>
-      </c>
-      <c r="F29" s="1">
-        <f>ROUND(C29*[1]属性总表!$G$5,0)</f>
-        <v>247</v>
-      </c>
-      <c r="G29" s="1">
-        <f>ROUND(C29*[1]属性总表!$H$5,0)</f>
-        <v>247</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="1">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C30" s="1">
-        <f t="shared" si="1"/>
-        <v>8.36</v>
-      </c>
-      <c r="D30" s="1">
-        <f>B30*[1]属性总表!$E$5</f>
-        <v>12600</v>
-      </c>
-      <c r="E30" s="1">
-        <f>ROUND([1]等级属性!C30*[1]属性总表!$F$5,0)</f>
-        <v>836</v>
-      </c>
-      <c r="F30" s="1">
-        <f>ROUND(C30*[1]属性总表!$G$5,0)</f>
-        <v>251</v>
-      </c>
-      <c r="G30" s="1">
-        <f>ROUND(C30*[1]属性总表!$H$5,0)</f>
-        <v>251</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="1">
-        <v>30</v>
-      </c>
-      <c r="B31" s="1">
-        <f t="shared" si="0"/>
-        <v>12.25</v>
-      </c>
-      <c r="C31" s="1">
-        <f t="shared" si="1"/>
-        <v>8.4799999999999986</v>
-      </c>
-      <c r="D31" s="1">
-        <f>B31*[1]属性总表!$E$5</f>
-        <v>12862.5</v>
-      </c>
-      <c r="E31" s="1">
-        <f>ROUND([1]等级属性!C31*[1]属性总表!$F$5,0)</f>
-        <v>848</v>
-      </c>
-      <c r="F31" s="1">
-        <f>ROUND(C31*[1]属性总表!$G$5,0)</f>
-        <v>254</v>
-      </c>
-      <c r="G31" s="1">
-        <f>ROUND(C31*[1]属性总表!$H$5,0)</f>
-        <v>254</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="1">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1">
-        <f t="shared" si="0"/>
-        <v>12.5</v>
-      </c>
-      <c r="C32" s="1">
-        <f t="shared" si="1"/>
-        <v>8.5999999999999979</v>
-      </c>
-      <c r="D32" s="1">
-        <f>B32*[1]属性总表!$E$5</f>
-        <v>13125</v>
-      </c>
-      <c r="E32" s="1">
-        <f>ROUND([1]等级属性!C32*[1]属性总表!$F$5,0)</f>
-        <v>860</v>
-      </c>
-      <c r="F32" s="1">
-        <f>ROUND(C32*[1]属性总表!$G$5,0)</f>
-        <v>258</v>
-      </c>
-      <c r="G32" s="1">
-        <f>ROUND(C32*[1]属性总表!$H$5,0)</f>
-        <v>258</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="1">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1">
-        <f t="shared" si="0"/>
-        <v>12.75</v>
-      </c>
-      <c r="C33" s="1">
-        <f t="shared" si="1"/>
-        <v>8.7199999999999971</v>
-      </c>
-      <c r="D33" s="1">
-        <f>B33*[1]属性总表!$E$5</f>
-        <v>13387.5</v>
-      </c>
-      <c r="E33" s="1">
-        <f>ROUND([1]等级属性!C33*[1]属性总表!$F$5,0)</f>
-        <v>872</v>
-      </c>
-      <c r="F33" s="1">
-        <f>ROUND(C33*[1]属性总表!$G$5,0)</f>
-        <v>262</v>
-      </c>
-      <c r="G33" s="1">
-        <f>ROUND(C33*[1]属性总表!$H$5,0)</f>
-        <v>262</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="1">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="C34" s="1">
-        <f t="shared" si="1"/>
-        <v>8.8399999999999963</v>
-      </c>
-      <c r="D34" s="1">
-        <f>B34*[1]属性总表!$E$5</f>
-        <v>13650</v>
-      </c>
-      <c r="E34" s="1">
-        <f>ROUND([1]等级属性!C34*[1]属性总表!$F$5,0)</f>
-        <v>884</v>
-      </c>
-      <c r="F34" s="1">
-        <f>ROUND(C34*[1]属性总表!$G$5,0)</f>
-        <v>265</v>
-      </c>
-      <c r="G34" s="1">
-        <f>ROUND(C34*[1]属性总表!$H$5,0)</f>
-        <v>265</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="1">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1">
-        <f t="shared" si="0"/>
-        <v>13.25</v>
-      </c>
-      <c r="C35" s="1">
-        <f t="shared" si="1"/>
-        <v>8.9599999999999955</v>
-      </c>
-      <c r="D35" s="1">
-        <f>B35*[1]属性总表!$E$5</f>
-        <v>13912.5</v>
-      </c>
-      <c r="E35" s="1">
-        <f>ROUND([1]等级属性!C35*[1]属性总表!$F$5,0)</f>
-        <v>896</v>
-      </c>
-      <c r="F35" s="1">
-        <f>ROUND(C35*[1]属性总表!$G$5,0)</f>
-        <v>269</v>
-      </c>
-      <c r="G35" s="1">
-        <f>ROUND(C35*[1]属性总表!$H$5,0)</f>
-        <v>269</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="1">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1">
-        <f t="shared" si="0"/>
-        <v>13.5</v>
-      </c>
-      <c r="C36" s="1">
-        <f t="shared" si="1"/>
-        <v>9.0799999999999947</v>
-      </c>
-      <c r="D36" s="1">
-        <f>B36*[1]属性总表!$E$5</f>
-        <v>14175</v>
-      </c>
-      <c r="E36" s="1">
-        <f>ROUND([1]等级属性!C36*[1]属性总表!$F$5,0)</f>
-        <v>908</v>
-      </c>
-      <c r="F36" s="1">
-        <f>ROUND(C36*[1]属性总表!$G$5,0)</f>
-        <v>272</v>
-      </c>
-      <c r="G36" s="1">
-        <f>ROUND(C36*[1]属性总表!$H$5,0)</f>
-        <v>272</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="1">
-        <v>36</v>
-      </c>
-      <c r="B37" s="1">
-        <f t="shared" si="0"/>
-        <v>13.75</v>
-      </c>
-      <c r="C37" s="1">
-        <f t="shared" si="1"/>
-        <v>9.199999999999994</v>
-      </c>
-      <c r="D37" s="1">
-        <f>B37*[1]属性总表!$E$5</f>
-        <v>14437.5</v>
-      </c>
-      <c r="E37" s="1">
-        <f>ROUND([1]等级属性!C37*[1]属性总表!$F$5,0)</f>
-        <v>920</v>
-      </c>
-      <c r="F37" s="1">
-        <f>ROUND(C37*[1]属性总表!$G$5,0)</f>
-        <v>276</v>
-      </c>
-      <c r="G37" s="1">
-        <f>ROUND(C37*[1]属性总表!$H$5,0)</f>
-        <v>276</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="1">
-        <v>37</v>
-      </c>
-      <c r="B38" s="1">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C38" s="1">
-        <f t="shared" si="1"/>
-        <v>9.3199999999999932</v>
-      </c>
-      <c r="D38" s="1">
-        <f>B38*[1]属性总表!$E$5</f>
-        <v>14700</v>
-      </c>
-      <c r="E38" s="1">
-        <f>ROUND([1]等级属性!C38*[1]属性总表!$F$5,0)</f>
-        <v>932</v>
-      </c>
-      <c r="F38" s="1">
-        <f>ROUND(C38*[1]属性总表!$G$5,0)</f>
-        <v>280</v>
-      </c>
-      <c r="G38" s="1">
-        <f>ROUND(C38*[1]属性总表!$H$5,0)</f>
-        <v>280</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="1">
-        <v>38</v>
-      </c>
-      <c r="B39" s="1">
-        <f t="shared" si="0"/>
-        <v>14.25</v>
-      </c>
-      <c r="C39" s="1">
-        <f t="shared" si="1"/>
-        <v>9.4399999999999924</v>
-      </c>
-      <c r="D39" s="1">
-        <f>B39*[1]属性总表!$E$5</f>
-        <v>14962.5</v>
-      </c>
-      <c r="E39" s="1">
-        <f>ROUND([1]等级属性!C39*[1]属性总表!$F$5,0)</f>
-        <v>944</v>
-      </c>
-      <c r="F39" s="1">
-        <f>ROUND(C39*[1]属性总表!$G$5,0)</f>
-        <v>283</v>
-      </c>
-      <c r="G39" s="1">
-        <f>ROUND(C39*[1]属性总表!$H$5,0)</f>
-        <v>283</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="1">
-        <v>39</v>
-      </c>
-      <c r="B40" s="1">
-        <f t="shared" si="0"/>
-        <v>14.5</v>
-      </c>
-      <c r="C40" s="1">
-        <f t="shared" si="1"/>
-        <v>9.5599999999999916</v>
-      </c>
-      <c r="D40" s="1">
-        <f>B40*[1]属性总表!$E$5</f>
-        <v>15225</v>
-      </c>
-      <c r="E40" s="1">
-        <f>ROUND([1]等级属性!C40*[1]属性总表!$F$5,0)</f>
-        <v>956</v>
-      </c>
-      <c r="F40" s="1">
-        <f>ROUND(C40*[1]属性总表!$G$5,0)</f>
-        <v>287</v>
-      </c>
-      <c r="G40" s="1">
-        <f>ROUND(C40*[1]属性总表!$H$5,0)</f>
-        <v>287</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="1">
-        <v>40</v>
-      </c>
-      <c r="B41" s="1">
-        <f t="shared" si="0"/>
-        <v>14.75</v>
-      </c>
-      <c r="C41" s="1">
-        <f t="shared" si="1"/>
-        <v>9.6799999999999908</v>
-      </c>
-      <c r="D41" s="1">
-        <f>B41*[1]属性总表!$E$5</f>
-        <v>15487.5</v>
-      </c>
-      <c r="E41" s="1">
-        <f>ROUND([1]等级属性!C41*[1]属性总表!$F$5,0)</f>
-        <v>968</v>
-      </c>
-      <c r="F41" s="1">
-        <f>ROUND(C41*[1]属性总表!$G$5,0)</f>
-        <v>290</v>
-      </c>
-      <c r="G41" s="1">
-        <f>ROUND(C41*[1]属性总表!$H$5,0)</f>
-        <v>290</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="1">
-        <v>41</v>
-      </c>
-      <c r="B42" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C42" s="1">
-        <f t="shared" si="1"/>
-        <v>9.7999999999999901</v>
-      </c>
-      <c r="D42" s="1">
-        <f>B42*[1]属性总表!$E$5</f>
-        <v>15750</v>
-      </c>
-      <c r="E42" s="1">
-        <f>ROUND([1]等级属性!C42*[1]属性总表!$F$5,0)</f>
-        <v>980</v>
-      </c>
-      <c r="F42" s="1">
-        <f>ROUND(C42*[1]属性总表!$G$5,0)</f>
-        <v>294</v>
-      </c>
-      <c r="G42" s="1">
-        <f>ROUND(C42*[1]属性总表!$H$5,0)</f>
-        <v>294</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="1">
-        <v>42</v>
-      </c>
-      <c r="B43" s="1">
-        <f t="shared" si="0"/>
-        <v>15.25</v>
-      </c>
-      <c r="C43" s="1">
-        <f t="shared" si="1"/>
-        <v>9.9199999999999893</v>
-      </c>
-      <c r="D43" s="1">
-        <f>B43*[1]属性总表!$E$5</f>
-        <v>16012.5</v>
-      </c>
-      <c r="E43" s="1">
-        <f>ROUND([1]等级属性!C43*[1]属性总表!$F$5,0)</f>
-        <v>992</v>
-      </c>
-      <c r="F43" s="1">
-        <f>ROUND(C43*[1]属性总表!$G$5,0)</f>
-        <v>298</v>
-      </c>
-      <c r="G43" s="1">
-        <f>ROUND(C43*[1]属性总表!$H$5,0)</f>
-        <v>298</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="1">
-        <v>43</v>
-      </c>
-      <c r="B44" s="1">
-        <f t="shared" si="0"/>
-        <v>15.5</v>
-      </c>
-      <c r="C44" s="1">
-        <f t="shared" si="1"/>
-        <v>10.039999999999988</v>
-      </c>
-      <c r="D44" s="1">
-        <f>B44*[1]属性总表!$E$5</f>
-        <v>16275</v>
-      </c>
-      <c r="E44" s="1">
-        <f>ROUND([1]等级属性!C44*[1]属性总表!$F$5,0)</f>
-        <v>1004</v>
-      </c>
-      <c r="F44" s="1">
-        <f>ROUND(C44*[1]属性总表!$G$5,0)</f>
-        <v>301</v>
-      </c>
-      <c r="G44" s="1">
-        <f>ROUND(C44*[1]属性总表!$H$5,0)</f>
-        <v>301</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="1">
-        <v>44</v>
-      </c>
-      <c r="B45" s="1">
-        <f t="shared" si="0"/>
-        <v>15.75</v>
-      </c>
-      <c r="C45" s="1">
-        <f t="shared" si="1"/>
-        <v>10.159999999999988</v>
-      </c>
-      <c r="D45" s="1">
-        <f>B45*[1]属性总表!$E$5</f>
-        <v>16537.5</v>
-      </c>
-      <c r="E45" s="1">
-        <f>ROUND([1]等级属性!C45*[1]属性总表!$F$5,0)</f>
-        <v>1016</v>
-      </c>
-      <c r="F45" s="1">
-        <f>ROUND(C45*[1]属性总表!$G$5,0)</f>
-        <v>305</v>
-      </c>
-      <c r="G45" s="1">
-        <f>ROUND(C45*[1]属性总表!$H$5,0)</f>
-        <v>305</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="1">
-        <v>45</v>
-      </c>
-      <c r="B46" s="1">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C46" s="1">
-        <f t="shared" si="1"/>
-        <v>10.279999999999987</v>
-      </c>
-      <c r="D46" s="1">
-        <f>B46*[1]属性总表!$E$5</f>
-        <v>16800</v>
-      </c>
-      <c r="E46" s="1">
-        <f>ROUND([1]等级属性!C46*[1]属性总表!$F$5,0)</f>
-        <v>1028</v>
-      </c>
-      <c r="F46" s="1">
-        <f>ROUND(C46*[1]属性总表!$G$5,0)</f>
-        <v>308</v>
-      </c>
-      <c r="G46" s="1">
-        <f>ROUND(C46*[1]属性总表!$H$5,0)</f>
-        <v>308</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="1">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1">
-        <f t="shared" si="0"/>
-        <v>16.25</v>
-      </c>
-      <c r="C47" s="1">
-        <f t="shared" si="1"/>
-        <v>10.399999999999986</v>
-      </c>
-      <c r="D47" s="1">
-        <f>B47*[1]属性总表!$E$5</f>
-        <v>17062.5</v>
-      </c>
-      <c r="E47" s="1">
-        <f>ROUND([1]等级属性!C47*[1]属性总表!$F$5,0)</f>
-        <v>1040</v>
-      </c>
-      <c r="F47" s="1">
-        <f>ROUND(C47*[1]属性总表!$G$5,0)</f>
-        <v>312</v>
-      </c>
-      <c r="G47" s="1">
-        <f>ROUND(C47*[1]属性总表!$H$5,0)</f>
-        <v>312</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="1">
-        <v>47</v>
-      </c>
-      <c r="B48" s="1">
-        <f t="shared" si="0"/>
-        <v>16.5</v>
-      </c>
-      <c r="C48" s="1">
-        <f t="shared" si="1"/>
-        <v>10.519999999999985</v>
-      </c>
-      <c r="D48" s="1">
-        <f>B48*[1]属性总表!$E$5</f>
-        <v>17325</v>
-      </c>
-      <c r="E48" s="1">
-        <f>ROUND([1]等级属性!C48*[1]属性总表!$F$5,0)</f>
-        <v>1052</v>
-      </c>
-      <c r="F48" s="1">
-        <f>ROUND(C48*[1]属性总表!$G$5,0)</f>
-        <v>316</v>
-      </c>
-      <c r="G48" s="1">
-        <f>ROUND(C48*[1]属性总表!$H$5,0)</f>
-        <v>316</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="1">
-        <v>48</v>
-      </c>
-      <c r="B49" s="1">
-        <f t="shared" si="0"/>
-        <v>16.75</v>
-      </c>
-      <c r="C49" s="1">
-        <f t="shared" si="1"/>
-        <v>10.639999999999985</v>
-      </c>
-      <c r="D49" s="1">
-        <f>B49*[1]属性总表!$E$5</f>
-        <v>17587.5</v>
-      </c>
-      <c r="E49" s="1">
-        <f>ROUND([1]等级属性!C49*[1]属性总表!$F$5,0)</f>
-        <v>1064</v>
-      </c>
-      <c r="F49" s="1">
-        <f>ROUND(C49*[1]属性总表!$G$5,0)</f>
-        <v>319</v>
-      </c>
-      <c r="G49" s="1">
-        <f>ROUND(C49*[1]属性总表!$H$5,0)</f>
-        <v>319</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="1">
-        <v>49</v>
-      </c>
-      <c r="B50" s="1">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C50" s="1">
-        <f t="shared" si="1"/>
-        <v>10.759999999999984</v>
-      </c>
-      <c r="D50" s="1">
-        <f>B50*[1]属性总表!$E$5</f>
-        <v>17850</v>
-      </c>
-      <c r="E50" s="1">
-        <f>ROUND([1]等级属性!C50*[1]属性总表!$F$5,0)</f>
-        <v>1076</v>
-      </c>
-      <c r="F50" s="1">
-        <f>ROUND(C50*[1]属性总表!$G$5,0)</f>
-        <v>323</v>
-      </c>
-      <c r="G50" s="1">
-        <f>ROUND(C50*[1]属性总表!$H$5,0)</f>
-        <v>323</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="1">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1">
-        <f t="shared" si="0"/>
-        <v>17.25</v>
-      </c>
-      <c r="C51" s="1">
-        <f t="shared" si="1"/>
-        <v>10.879999999999983</v>
-      </c>
-      <c r="D51" s="1">
-        <f>B51*[1]属性总表!$E$5</f>
-        <v>18112.5</v>
-      </c>
-      <c r="E51" s="1">
-        <f>ROUND([1]等级属性!C51*[1]属性总表!$F$5,0)</f>
-        <v>1088</v>
-      </c>
-      <c r="F51" s="1">
-        <f>ROUND(C51*[1]属性总表!$G$5,0)</f>
-        <v>326</v>
-      </c>
-      <c r="G51" s="1">
-        <f>ROUND(C51*[1]属性总表!$H$5,0)</f>
-        <v>326</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="1">
-        <v>51</v>
-      </c>
-      <c r="B52" s="1">
-        <f t="shared" si="0"/>
-        <v>17.5</v>
-      </c>
-      <c r="C52" s="1">
-        <f t="shared" si="1"/>
-        <v>10.999999999999982</v>
-      </c>
-      <c r="D52" s="1">
-        <f>B52*[1]属性总表!$E$5</f>
-        <v>18375</v>
-      </c>
-      <c r="E52" s="1">
-        <f>ROUND([1]等级属性!C52*[1]属性总表!$F$5,0)</f>
-        <v>1100</v>
-      </c>
-      <c r="F52" s="1">
-        <f>ROUND(C52*[1]属性总表!$G$5,0)</f>
-        <v>330</v>
-      </c>
-      <c r="G52" s="1">
-        <f>ROUND(C52*[1]属性总表!$H$5,0)</f>
-        <v>330</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="1">
-        <v>52</v>
-      </c>
-      <c r="B53" s="1">
-        <f t="shared" si="0"/>
-        <v>17.75</v>
-      </c>
-      <c r="C53" s="1">
-        <f t="shared" si="1"/>
-        <v>11.119999999999981</v>
-      </c>
-      <c r="D53" s="1">
-        <f>B53*[1]属性总表!$E$5</f>
-        <v>18637.5</v>
-      </c>
-      <c r="E53" s="1">
-        <f>ROUND([1]等级属性!C53*[1]属性总表!$F$5,0)</f>
-        <v>1112</v>
-      </c>
-      <c r="F53" s="1">
-        <f>ROUND(C53*[1]属性总表!$G$5,0)</f>
-        <v>334</v>
-      </c>
-      <c r="G53" s="1">
-        <f>ROUND(C53*[1]属性总表!$H$5,0)</f>
-        <v>334</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="1">
-        <v>53</v>
-      </c>
-      <c r="B54" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="C54" s="1">
-        <f t="shared" si="1"/>
-        <v>11.239999999999981</v>
-      </c>
-      <c r="D54" s="1">
-        <f>B54*[1]属性总表!$E$5</f>
-        <v>18900</v>
-      </c>
-      <c r="E54" s="1">
-        <f>ROUND([1]等级属性!C54*[1]属性总表!$F$5,0)</f>
-        <v>1124</v>
-      </c>
-      <c r="F54" s="1">
-        <f>ROUND(C54*[1]属性总表!$G$5,0)</f>
-        <v>337</v>
-      </c>
-      <c r="G54" s="1">
-        <f>ROUND(C54*[1]属性总表!$H$5,0)</f>
-        <v>337</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="1">
-        <v>54</v>
-      </c>
-      <c r="B55" s="1">
-        <f t="shared" si="0"/>
-        <v>18.25</v>
-      </c>
-      <c r="C55" s="1">
-        <f t="shared" si="1"/>
-        <v>11.35999999999998</v>
-      </c>
-      <c r="D55" s="1">
-        <f>B55*[1]属性总表!$E$5</f>
-        <v>19162.5</v>
-      </c>
-      <c r="E55" s="1">
-        <f>ROUND([1]等级属性!C55*[1]属性总表!$F$5,0)</f>
-        <v>1136</v>
-      </c>
-      <c r="F55" s="1">
-        <f>ROUND(C55*[1]属性总表!$G$5,0)</f>
-        <v>341</v>
-      </c>
-      <c r="G55" s="1">
-        <f>ROUND(C55*[1]属性总表!$H$5,0)</f>
-        <v>341</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="1">
-        <v>55</v>
-      </c>
-      <c r="B56" s="1">
-        <f t="shared" si="0"/>
-        <v>18.5</v>
-      </c>
-      <c r="C56" s="1">
-        <f t="shared" si="1"/>
-        <v>11.479999999999979</v>
-      </c>
-      <c r="D56" s="1">
-        <f>B56*[1]属性总表!$E$5</f>
-        <v>19425</v>
-      </c>
-      <c r="E56" s="1">
-        <f>ROUND([1]等级属性!C56*[1]属性总表!$F$5,0)</f>
-        <v>1148</v>
-      </c>
-      <c r="F56" s="1">
-        <f>ROUND(C56*[1]属性总表!$G$5,0)</f>
-        <v>344</v>
-      </c>
-      <c r="G56" s="1">
-        <f>ROUND(C56*[1]属性总表!$H$5,0)</f>
-        <v>344</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="1">
-        <v>56</v>
-      </c>
-      <c r="B57" s="1">
-        <f t="shared" si="0"/>
-        <v>18.75</v>
-      </c>
-      <c r="C57" s="1">
-        <f t="shared" si="1"/>
-        <v>11.599999999999978</v>
-      </c>
-      <c r="D57" s="1">
-        <f>B57*[1]属性总表!$E$5</f>
-        <v>19687.5</v>
-      </c>
-      <c r="E57" s="1">
-        <f>ROUND([1]等级属性!C57*[1]属性总表!$F$5,0)</f>
-        <v>1160</v>
-      </c>
-      <c r="F57" s="1">
-        <f>ROUND(C57*[1]属性总表!$G$5,0)</f>
-        <v>348</v>
-      </c>
-      <c r="G57" s="1">
-        <f>ROUND(C57*[1]属性总表!$H$5,0)</f>
-        <v>348</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="1">
-        <v>57</v>
-      </c>
-      <c r="B58" s="1">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C58" s="1">
-        <f t="shared" si="1"/>
-        <v>11.719999999999978</v>
-      </c>
-      <c r="D58" s="1">
-        <f>B58*[1]属性总表!$E$5</f>
-        <v>19950</v>
-      </c>
-      <c r="E58" s="1">
-        <f>ROUND([1]等级属性!C58*[1]属性总表!$F$5,0)</f>
-        <v>1172</v>
-      </c>
-      <c r="F58" s="1">
-        <f>ROUND(C58*[1]属性总表!$G$5,0)</f>
-        <v>352</v>
-      </c>
-      <c r="G58" s="1">
-        <f>ROUND(C58*[1]属性总表!$H$5,0)</f>
-        <v>352</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="1">
-        <v>58</v>
-      </c>
-      <c r="B59" s="1">
-        <f t="shared" si="0"/>
-        <v>19.25</v>
-      </c>
-      <c r="C59" s="1">
-        <f t="shared" si="1"/>
-        <v>11.839999999999977</v>
-      </c>
-      <c r="D59" s="1">
-        <f>B59*[1]属性总表!$E$5</f>
-        <v>20212.5</v>
-      </c>
-      <c r="E59" s="1">
-        <f>ROUND([1]等级属性!C59*[1]属性总表!$F$5,0)</f>
-        <v>1184</v>
-      </c>
-      <c r="F59" s="1">
-        <f>ROUND(C59*[1]属性总表!$G$5,0)</f>
-        <v>355</v>
-      </c>
-      <c r="G59" s="1">
-        <f>ROUND(C59*[1]属性总表!$H$5,0)</f>
-        <v>355</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="1">
-        <v>59</v>
-      </c>
-      <c r="B60" s="1">
-        <f t="shared" si="0"/>
-        <v>19.5</v>
-      </c>
-      <c r="C60" s="1">
-        <f t="shared" si="1"/>
-        <v>11.959999999999976</v>
-      </c>
-      <c r="D60" s="1">
-        <f>B60*[1]属性总表!$E$5</f>
-        <v>20475</v>
-      </c>
-      <c r="E60" s="1">
-        <f>ROUND([1]等级属性!C60*[1]属性总表!$F$5,0)</f>
-        <v>1196</v>
-      </c>
-      <c r="F60" s="1">
-        <f>ROUND(C60*[1]属性总表!$G$5,0)</f>
-        <v>359</v>
-      </c>
-      <c r="G60" s="1">
-        <f>ROUND(C60*[1]属性总表!$H$5,0)</f>
-        <v>359</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="1">
-        <v>60</v>
-      </c>
-      <c r="B61" s="1">
-        <f t="shared" si="0"/>
-        <v>19.75</v>
-      </c>
-      <c r="C61" s="1">
-        <f t="shared" si="1"/>
-        <v>12.079999999999975</v>
-      </c>
-      <c r="D61" s="1">
-        <f>B61*[1]属性总表!$E$5</f>
-        <v>20737.5</v>
-      </c>
-      <c r="E61" s="1">
-        <f>ROUND([1]等级属性!C61*[1]属性总表!$F$5,0)</f>
-        <v>1208</v>
-      </c>
-      <c r="F61" s="1">
-        <f>ROUND(C61*[1]属性总表!$G$5,0)</f>
-        <v>362</v>
-      </c>
-      <c r="G61" s="1">
-        <f>ROUND(C61*[1]属性总表!$H$5,0)</f>
-        <v>362</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="1">
-        <v>61</v>
-      </c>
-      <c r="B62" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="C62" s="1">
-        <f t="shared" si="1"/>
-        <v>12.199999999999974</v>
-      </c>
-      <c r="D62" s="1">
-        <f>B62*[1]属性总表!$E$5</f>
-        <v>21000</v>
-      </c>
-      <c r="E62" s="1">
-        <f>ROUND([1]等级属性!C62*[1]属性总表!$F$5,0)</f>
-        <v>1220</v>
-      </c>
-      <c r="F62" s="1">
-        <f>ROUND(C62*[1]属性总表!$G$5,0)</f>
-        <v>366</v>
-      </c>
-      <c r="G62" s="1">
-        <f>ROUND(C62*[1]属性总表!$H$5,0)</f>
-        <v>366</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="1">
-        <v>62</v>
-      </c>
-      <c r="B63" s="1">
-        <f t="shared" si="0"/>
-        <v>20.25</v>
-      </c>
-      <c r="C63" s="1">
-        <f t="shared" si="1"/>
-        <v>12.319999999999974</v>
-      </c>
-      <c r="D63" s="1">
-        <f>B63*[1]属性总表!$E$5</f>
-        <v>21262.5</v>
-      </c>
-      <c r="E63" s="1">
-        <f>ROUND([1]等级属性!C63*[1]属性总表!$F$5,0)</f>
-        <v>1232</v>
-      </c>
-      <c r="F63" s="1">
-        <f>ROUND(C63*[1]属性总表!$G$5,0)</f>
-        <v>370</v>
-      </c>
-      <c r="G63" s="1">
-        <f>ROUND(C63*[1]属性总表!$H$5,0)</f>
-        <v>370</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="1">
-        <v>63</v>
-      </c>
-      <c r="B64" s="1">
-        <f t="shared" si="0"/>
-        <v>20.5</v>
-      </c>
-      <c r="C64" s="1">
-        <f t="shared" si="1"/>
-        <v>12.439999999999973</v>
-      </c>
-      <c r="D64" s="1">
-        <f>B64*[1]属性总表!$E$5</f>
-        <v>21525</v>
-      </c>
-      <c r="E64" s="1">
-        <f>ROUND([1]等级属性!C64*[1]属性总表!$F$5,0)</f>
-        <v>1244</v>
-      </c>
-      <c r="F64" s="1">
-        <f>ROUND(C64*[1]属性总表!$G$5,0)</f>
-        <v>373</v>
-      </c>
-      <c r="G64" s="1">
-        <f>ROUND(C64*[1]属性总表!$H$5,0)</f>
-        <v>373</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="1">
-        <v>64</v>
-      </c>
-      <c r="B65" s="1">
-        <f t="shared" si="0"/>
-        <v>20.75</v>
-      </c>
-      <c r="C65" s="1">
-        <f t="shared" si="1"/>
-        <v>12.559999999999972</v>
-      </c>
-      <c r="D65" s="1">
-        <f>B65*[1]属性总表!$E$5</f>
-        <v>21787.5</v>
-      </c>
-      <c r="E65" s="1">
-        <f>ROUND([1]等级属性!C65*[1]属性总表!$F$5,0)</f>
-        <v>1256</v>
-      </c>
-      <c r="F65" s="1">
-        <f>ROUND(C65*[1]属性总表!$G$5,0)</f>
-        <v>377</v>
-      </c>
-      <c r="G65" s="1">
-        <f>ROUND(C65*[1]属性总表!$H$5,0)</f>
-        <v>377</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="1">
-        <v>65</v>
-      </c>
-      <c r="B66" s="1">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C66" s="1">
-        <f t="shared" si="1"/>
-        <v>12.679999999999971</v>
-      </c>
-      <c r="D66" s="1">
-        <f>B66*[1]属性总表!$E$5</f>
-        <v>22050</v>
-      </c>
-      <c r="E66" s="1">
-        <f>ROUND([1]等级属性!C66*[1]属性总表!$F$5,0)</f>
-        <v>1268</v>
-      </c>
-      <c r="F66" s="1">
-        <f>ROUND(C66*[1]属性总表!$G$5,0)</f>
-        <v>380</v>
-      </c>
-      <c r="G66" s="1">
-        <f>ROUND(C66*[1]属性总表!$H$5,0)</f>
-        <v>380</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="1">
-        <v>66</v>
-      </c>
-      <c r="B67" s="1">
-        <f t="shared" si="0"/>
-        <v>21.25</v>
-      </c>
-      <c r="C67" s="1">
-        <f t="shared" si="1"/>
-        <v>12.799999999999971</v>
-      </c>
-      <c r="D67" s="1">
-        <f>B67*[1]属性总表!$E$5</f>
-        <v>22312.5</v>
-      </c>
-      <c r="E67" s="1">
-        <f>ROUND([1]等级属性!C67*[1]属性总表!$F$5,0)</f>
-        <v>1280</v>
-      </c>
-      <c r="F67" s="1">
-        <f>ROUND(C67*[1]属性总表!$G$5,0)</f>
-        <v>384</v>
-      </c>
-      <c r="G67" s="1">
-        <f>ROUND(C67*[1]属性总表!$H$5,0)</f>
-        <v>384</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="1">
-        <v>67</v>
-      </c>
-      <c r="B68" s="1">
-        <f t="shared" ref="B68:B71" si="2">B67+0.25</f>
-        <v>21.5</v>
-      </c>
-      <c r="C68" s="1">
-        <f t="shared" ref="C68:C71" si="3">C67+0.12</f>
-        <v>12.91999999999997</v>
-      </c>
-      <c r="D68" s="1">
-        <f>B68*[1]属性总表!$E$5</f>
-        <v>22575</v>
-      </c>
-      <c r="E68" s="1">
-        <f>ROUND([1]等级属性!C68*[1]属性总表!$F$5,0)</f>
-        <v>1292</v>
-      </c>
-      <c r="F68" s="1">
-        <f>ROUND(C68*[1]属性总表!$G$5,0)</f>
-        <v>388</v>
-      </c>
-      <c r="G68" s="1">
-        <f>ROUND(C68*[1]属性总表!$H$5,0)</f>
-        <v>388</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="1">
-        <v>68</v>
-      </c>
-      <c r="B69" s="1">
-        <f t="shared" si="2"/>
-        <v>21.75</v>
-      </c>
-      <c r="C69" s="1">
-        <f t="shared" si="3"/>
-        <v>13.039999999999969</v>
-      </c>
-      <c r="D69" s="1">
-        <f>B69*[1]属性总表!$E$5</f>
-        <v>22837.5</v>
-      </c>
-      <c r="E69" s="1">
-        <f>ROUND([1]等级属性!C69*[1]属性总表!$F$5,0)</f>
-        <v>1304</v>
-      </c>
-      <c r="F69" s="1">
-        <f>ROUND(C69*[1]属性总表!$G$5,0)</f>
-        <v>391</v>
-      </c>
-      <c r="G69" s="1">
-        <f>ROUND(C69*[1]属性总表!$H$5,0)</f>
-        <v>391</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="1">
-        <v>69</v>
-      </c>
-      <c r="B70" s="1">
-        <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="C70" s="1">
-        <f t="shared" si="3"/>
-        <v>13.159999999999968</v>
-      </c>
-      <c r="D70" s="1">
-        <f>B70*[1]属性总表!$E$5</f>
-        <v>23100</v>
-      </c>
-      <c r="E70" s="1">
-        <f>ROUND([1]等级属性!C70*[1]属性总表!$F$5,0)</f>
-        <v>1316</v>
-      </c>
-      <c r="F70" s="1">
-        <f>ROUND(C70*[1]属性总表!$G$5,0)</f>
-        <v>395</v>
-      </c>
-      <c r="G70" s="1">
-        <f>ROUND(C70*[1]属性总表!$H$5,0)</f>
-        <v>395</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="1">
-        <v>70</v>
-      </c>
-      <c r="B71" s="1">
-        <f t="shared" si="2"/>
-        <v>22.25</v>
-      </c>
-      <c r="C71" s="1">
-        <f t="shared" si="3"/>
-        <v>13.279999999999967</v>
-      </c>
-      <c r="D71" s="1">
-        <f>B71*[1]属性总表!$E$5</f>
-        <v>23362.5</v>
-      </c>
-      <c r="E71" s="1">
-        <f>ROUND([1]等级属性!C71*[1]属性总表!$F$5,0)</f>
-        <v>1328</v>
-      </c>
-      <c r="F71" s="1">
-        <f>ROUND(C71*[1]属性总表!$G$5,0)</f>
-        <v>398</v>
-      </c>
-      <c r="G71" s="1">
-        <f>ROUND(C71*[1]属性总表!$H$5,0)</f>
-        <v>398</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="35" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="C1:P41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -50287,7 +52310,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:AL154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -60580,7 +62603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="B1:X50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -60923,7 +62946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A3:J34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -61136,7 +63159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="C1:R30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -66100,6 +68123,13 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="CP23:CP25"/>
+    <mergeCell ref="CP26:CP28"/>
+    <mergeCell ref="CP8:CP10"/>
+    <mergeCell ref="CP11:CP13"/>
+    <mergeCell ref="CP14:CP16"/>
+    <mergeCell ref="CP17:CP19"/>
+    <mergeCell ref="CP20:CP22"/>
     <mergeCell ref="K18:K20"/>
     <mergeCell ref="K21:K23"/>
     <mergeCell ref="AX4:AX6"/>
@@ -66114,13 +68144,6 @@
     <mergeCell ref="K9:K11"/>
     <mergeCell ref="K12:K14"/>
     <mergeCell ref="K15:K17"/>
-    <mergeCell ref="CP23:CP25"/>
-    <mergeCell ref="CP26:CP28"/>
-    <mergeCell ref="CP8:CP10"/>
-    <mergeCell ref="CP11:CP13"/>
-    <mergeCell ref="CP14:CP16"/>
-    <mergeCell ref="CP17:CP19"/>
-    <mergeCell ref="CP20:CP22"/>
   </mergeCells>
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -80844,7 +82867,7 @@
       </c>
       <c r="P96" s="1">
         <f>LOOKUP(Q96,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
-        <v>69000002</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="1">
         <v>14100111</v>
@@ -80953,7 +82976,7 @@
       <c r="AA97" s="3"/>
       <c r="AB97" s="3">
         <f>LOOKUP(AC97,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
-        <v>69000016</v>
+        <v>0</v>
       </c>
       <c r="AC97" s="1">
         <v>15310011</v>
@@ -81089,7 +83112,7 @@
       <c r="U99" s="3"/>
       <c r="V99" s="3">
         <f>LOOKUP(W99,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
-        <v>69000010</v>
+        <v>0</v>
       </c>
       <c r="W99" s="1">
         <v>15411011</v>
@@ -81102,9 +83125,9 @@
       </c>
       <c r="Z99" s="3"/>
       <c r="AA99" s="3"/>
-      <c r="AB99" s="3" t="str">
+      <c r="AB99" s="3">
         <f>LOOKUP(AC99,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
-        <v>69000013;69000017</v>
+        <v>0</v>
       </c>
       <c r="AC99" s="1">
         <v>15410011</v>

--- a/WeiJingShuZhi/属性表.xlsx
+++ b/WeiJingShuZhi/属性表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\WeiJingShuZhi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99650F50-E752-4DA2-B9C2-5B917F011D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E027E5-C51F-4F30-BBCC-8960D2729CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="10" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="10" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5467" uniqueCount="3070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5479" uniqueCount="3075">
   <si>
     <t>人物属性</t>
   </si>
@@ -9644,10 +9644,6 @@
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
   <si>
-    <t>受到攻击有一定概率触发爆炸,立即对自身范围触发爆炸，造成100%伤害+1000点固定伤害</t>
-    <phoneticPr fontId="35" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击时有概率触发地裂,造成100%伤害+500点固定伤害。</t>
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
@@ -9672,22 +9668,10 @@
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
   <si>
-    <t>受到攻击有一定概率触发爆炸,立即对自身范围触发爆炸，造成100%伤害+1500点固定伤害</t>
-    <phoneticPr fontId="35" type="noConversion"/>
-  </si>
-  <si>
     <t>受到攻击有一定概率在施法者目标处触发爆炸，造成100%伤害+500点固定伤害</t>
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
   <si>
-    <t>受到攻击有一定概率在施法者目标处触发爆炸，造成100%伤害+1000点固定伤害</t>
-    <phoneticPr fontId="35" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到攻击有一定概率在施法者目标处触发爆炸，造成100%伤害+1500点固定伤害</t>
-    <phoneticPr fontId="35" type="noConversion"/>
-  </si>
-  <si>
     <t>抗暴</t>
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
@@ -9758,6 +9742,37 @@
   <si>
     <t>暴伤</t>
     <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击有一定概率触发爆炸,立即对自身范围触发爆炸，造成150%伤害+1000点固定伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击有一定概率触发爆炸,立即对自身范围触发爆炸，造成200%伤害+1500点固定伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击有一定概率在施法者目标处触发爆炸，造成150%伤害+1000点固定伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到攻击有一定概率在施法者目标处触发爆炸，造成200%伤害+1500点固定伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击1</t>
+  </si>
+  <si>
+    <t>普通攻击2</t>
+  </si>
+  <si>
+    <t>普通攻击3</t>
+  </si>
+  <si>
+    <t>法师普通攻击</t>
+  </si>
+  <si>
+    <t>猎人普通攻击</t>
   </si>
 </sst>
 </file>
@@ -11281,95 +11296,95 @@
       <sheetData sheetId="0">
         <row r="856">
           <cell r="C856">
-            <v>10302004</v>
+            <v>10302002</v>
           </cell>
           <cell r="S856">
-            <v>6204004</v>
+            <v>6202003</v>
           </cell>
         </row>
         <row r="857">
           <cell r="C857">
-            <v>10302005</v>
+            <v>10302003</v>
           </cell>
           <cell r="S857">
-            <v>6205004</v>
+            <v>6203003</v>
           </cell>
         </row>
         <row r="858">
           <cell r="C858">
-            <v>10302006</v>
+            <v>10302004</v>
           </cell>
           <cell r="S858">
-            <v>6206003</v>
+            <v>6204004</v>
           </cell>
         </row>
         <row r="859">
           <cell r="C859">
-            <v>10303001</v>
+            <v>10302005</v>
           </cell>
           <cell r="S859">
-            <v>6301003</v>
+            <v>6205004</v>
           </cell>
         </row>
         <row r="860">
           <cell r="C860">
-            <v>10303002</v>
+            <v>10302006</v>
           </cell>
           <cell r="S860">
-            <v>6302003</v>
+            <v>6206003</v>
           </cell>
         </row>
         <row r="861">
           <cell r="C861">
-            <v>10303003</v>
+            <v>10303001</v>
           </cell>
           <cell r="S861">
-            <v>6303003</v>
+            <v>6301003</v>
           </cell>
         </row>
         <row r="862">
           <cell r="C862">
-            <v>10303004</v>
+            <v>10303002</v>
           </cell>
           <cell r="S862">
-            <v>6304004</v>
+            <v>6302003</v>
           </cell>
         </row>
         <row r="863">
           <cell r="C863">
-            <v>10303005</v>
+            <v>10303003</v>
           </cell>
           <cell r="S863">
-            <v>6305004</v>
+            <v>6303003</v>
           </cell>
         </row>
         <row r="864">
           <cell r="C864">
-            <v>10303006</v>
+            <v>10303004</v>
           </cell>
           <cell r="S864">
-            <v>6306003</v>
+            <v>6304004</v>
           </cell>
         </row>
         <row r="865">
           <cell r="C865">
-            <v>11200000</v>
+            <v>10303005</v>
           </cell>
           <cell r="S865">
-            <v>500</v>
+            <v>6305004</v>
           </cell>
         </row>
         <row r="866">
           <cell r="C866">
-            <v>11200001</v>
+            <v>10303006</v>
           </cell>
           <cell r="S866">
-            <v>500</v>
+            <v>6306003</v>
           </cell>
         </row>
         <row r="867">
           <cell r="C867">
-            <v>11200002</v>
+            <v>11200000</v>
           </cell>
           <cell r="S867">
             <v>500</v>
@@ -11377,7 +11392,7 @@
         </row>
         <row r="868">
           <cell r="C868">
-            <v>11200003</v>
+            <v>11200001</v>
           </cell>
           <cell r="S868">
             <v>500</v>
@@ -11385,7 +11400,7 @@
         </row>
         <row r="869">
           <cell r="C869">
-            <v>11200010</v>
+            <v>11200002</v>
           </cell>
           <cell r="S869">
             <v>500</v>
@@ -11393,2631 +11408,2637 @@
         </row>
         <row r="870">
           <cell r="C870">
-            <v>11300001</v>
+            <v>11200003</v>
           </cell>
-          <cell r="S870" t="str">
-            <v>1;3901</v>
+          <cell r="S870">
+            <v>500</v>
           </cell>
         </row>
         <row r="871">
           <cell r="C871">
-            <v>11300002</v>
+            <v>11200010</v>
           </cell>
-          <cell r="S871" t="str">
-            <v>1;3906</v>
+          <cell r="S871">
+            <v>500</v>
           </cell>
         </row>
         <row r="872">
           <cell r="C872">
-            <v>11300003</v>
+            <v>11300001</v>
           </cell>
           <cell r="S872" t="str">
-            <v>1;3907</v>
+            <v>1;3901</v>
           </cell>
         </row>
         <row r="873">
           <cell r="C873">
-            <v>11300004</v>
+            <v>11300002</v>
           </cell>
           <cell r="S873" t="str">
-            <v>1;3908</v>
+            <v>1;3906</v>
           </cell>
         </row>
         <row r="874">
           <cell r="C874">
-            <v>11300005</v>
+            <v>11300003</v>
           </cell>
           <cell r="S874" t="str">
-            <v>1;3909</v>
+            <v>1;3907</v>
           </cell>
         </row>
         <row r="875">
           <cell r="C875">
-            <v>11300006</v>
+            <v>11300004</v>
           </cell>
           <cell r="S875" t="str">
-            <v>1;3910</v>
+            <v>1;3908</v>
           </cell>
         </row>
         <row r="876">
           <cell r="C876">
-            <v>11300007</v>
+            <v>11300005</v>
           </cell>
           <cell r="S876" t="str">
-            <v>2;3902</v>
+            <v>1;3909</v>
           </cell>
         </row>
         <row r="877">
           <cell r="C877">
-            <v>11300008</v>
+            <v>11300006</v>
           </cell>
           <cell r="S877" t="str">
-            <v>2;3903</v>
+            <v>1;3910</v>
           </cell>
         </row>
         <row r="878">
           <cell r="C878">
-            <v>11300009</v>
+            <v>11300007</v>
           </cell>
           <cell r="S878" t="str">
-            <v>2;3904</v>
+            <v>2;3902</v>
           </cell>
         </row>
         <row r="879">
           <cell r="C879">
-            <v>11300101</v>
+            <v>11300008</v>
           </cell>
           <cell r="S879" t="str">
-            <v>1;3101</v>
+            <v>2;3903</v>
           </cell>
         </row>
         <row r="880">
           <cell r="C880">
-            <v>11300102</v>
+            <v>11300009</v>
           </cell>
           <cell r="S880" t="str">
-            <v>1;3102</v>
+            <v>2;3904</v>
           </cell>
         </row>
         <row r="881">
           <cell r="C881">
-            <v>11300103</v>
+            <v>11300101</v>
           </cell>
           <cell r="S881" t="str">
-            <v>1;3103</v>
+            <v>1;3101</v>
           </cell>
         </row>
         <row r="882">
           <cell r="C882">
-            <v>11300104</v>
+            <v>11300102</v>
           </cell>
           <cell r="S882" t="str">
-            <v>1;3104</v>
+            <v>1;3102</v>
           </cell>
         </row>
         <row r="883">
           <cell r="C883">
-            <v>11300105</v>
+            <v>11300103</v>
           </cell>
           <cell r="S883" t="str">
-            <v>1;3105</v>
+            <v>1;3103</v>
           </cell>
         </row>
         <row r="884">
           <cell r="C884">
-            <v>11300201</v>
+            <v>11300104</v>
           </cell>
           <cell r="S884" t="str">
-            <v>1;3201</v>
+            <v>1;3104</v>
           </cell>
         </row>
         <row r="885">
           <cell r="C885">
-            <v>11300202</v>
+            <v>11300105</v>
           </cell>
           <cell r="S885" t="str">
-            <v>1;3202</v>
+            <v>1;3105</v>
           </cell>
         </row>
         <row r="886">
           <cell r="C886">
-            <v>11300203</v>
+            <v>11300201</v>
           </cell>
           <cell r="S886" t="str">
-            <v>1;3203</v>
+            <v>1;3201</v>
           </cell>
         </row>
         <row r="887">
           <cell r="C887">
-            <v>11300204</v>
+            <v>11300202</v>
           </cell>
           <cell r="S887" t="str">
-            <v>1;3204</v>
+            <v>1;3202</v>
           </cell>
         </row>
         <row r="888">
           <cell r="C888">
-            <v>11300205</v>
+            <v>11300203</v>
           </cell>
           <cell r="S888" t="str">
-            <v>1;3205</v>
+            <v>1;3203</v>
           </cell>
         </row>
         <row r="889">
           <cell r="C889">
-            <v>11300301</v>
+            <v>11300204</v>
           </cell>
           <cell r="S889" t="str">
-            <v>1;3301</v>
+            <v>1;3204</v>
           </cell>
         </row>
         <row r="890">
           <cell r="C890">
-            <v>11300302</v>
+            <v>11300205</v>
           </cell>
           <cell r="S890" t="str">
-            <v>1;3302</v>
+            <v>1;3205</v>
           </cell>
         </row>
         <row r="891">
           <cell r="C891">
-            <v>11300303</v>
+            <v>11300301</v>
           </cell>
           <cell r="S891" t="str">
-            <v>1;3303</v>
+            <v>1;3301</v>
           </cell>
         </row>
         <row r="892">
           <cell r="C892">
-            <v>11300304</v>
+            <v>11300302</v>
           </cell>
           <cell r="S892" t="str">
-            <v>1;3304</v>
+            <v>1;3302</v>
           </cell>
         </row>
         <row r="893">
           <cell r="C893">
-            <v>11300305</v>
+            <v>11300303</v>
           </cell>
           <cell r="S893" t="str">
-            <v>1;3305</v>
+            <v>1;3303</v>
           </cell>
         </row>
         <row r="894">
           <cell r="C894">
-            <v>11300401</v>
+            <v>11300304</v>
           </cell>
           <cell r="S894" t="str">
-            <v>1;3401</v>
+            <v>1;3304</v>
           </cell>
         </row>
         <row r="895">
           <cell r="C895">
-            <v>11300402</v>
+            <v>11300305</v>
           </cell>
           <cell r="S895" t="str">
-            <v>1;3402</v>
+            <v>1;3305</v>
           </cell>
         </row>
         <row r="896">
           <cell r="C896">
-            <v>11300403</v>
+            <v>11300401</v>
           </cell>
           <cell r="S896" t="str">
-            <v>1;3403</v>
+            <v>1;3401</v>
           </cell>
         </row>
         <row r="897">
           <cell r="C897">
-            <v>11300404</v>
+            <v>11300402</v>
           </cell>
           <cell r="S897" t="str">
-            <v>1;3404</v>
+            <v>1;3402</v>
           </cell>
         </row>
         <row r="898">
           <cell r="C898">
-            <v>11300405</v>
+            <v>11300403</v>
           </cell>
           <cell r="S898" t="str">
-            <v>1;3405</v>
+            <v>1;3403</v>
           </cell>
         </row>
         <row r="899">
           <cell r="C899">
-            <v>11300501</v>
+            <v>11300404</v>
           </cell>
           <cell r="S899" t="str">
-            <v>1;3501</v>
+            <v>1;3404</v>
           </cell>
         </row>
         <row r="900">
           <cell r="C900">
-            <v>11300502</v>
+            <v>11300405</v>
           </cell>
           <cell r="S900" t="str">
-            <v>1;3502</v>
+            <v>1;3405</v>
           </cell>
         </row>
         <row r="901">
           <cell r="C901">
-            <v>11300503</v>
+            <v>11300501</v>
           </cell>
           <cell r="S901" t="str">
-            <v>1;3503</v>
+            <v>1;3501</v>
           </cell>
         </row>
         <row r="902">
           <cell r="C902">
-            <v>11300504</v>
+            <v>11300502</v>
           </cell>
           <cell r="S902" t="str">
-            <v>1;3504</v>
+            <v>1;3502</v>
           </cell>
         </row>
         <row r="903">
           <cell r="C903">
-            <v>11300505</v>
+            <v>11300503</v>
           </cell>
           <cell r="S903" t="str">
-            <v>1;3505</v>
+            <v>1;3503</v>
           </cell>
         </row>
         <row r="904">
           <cell r="C904">
-            <v>11300601</v>
+            <v>11300504</v>
           </cell>
           <cell r="S904" t="str">
-            <v>1;3601</v>
+            <v>1;3504</v>
           </cell>
         </row>
         <row r="905">
           <cell r="C905">
-            <v>11300602</v>
+            <v>11300505</v>
           </cell>
           <cell r="S905" t="str">
-            <v>1;3602</v>
+            <v>1;3505</v>
           </cell>
         </row>
         <row r="906">
           <cell r="C906">
-            <v>11300603</v>
+            <v>11300601</v>
           </cell>
           <cell r="S906" t="str">
-            <v>1;3603</v>
+            <v>1;3601</v>
           </cell>
         </row>
         <row r="907">
           <cell r="C907">
-            <v>11300604</v>
+            <v>11300602</v>
           </cell>
           <cell r="S907" t="str">
-            <v>1;3604</v>
+            <v>1;3602</v>
           </cell>
         </row>
         <row r="908">
           <cell r="C908">
-            <v>11300605</v>
+            <v>11300603</v>
           </cell>
           <cell r="S908" t="str">
-            <v>1;3605</v>
+            <v>1;3603</v>
           </cell>
         </row>
         <row r="909">
           <cell r="C909">
-            <v>11400101</v>
+            <v>11300604</v>
           </cell>
           <cell r="S909" t="str">
-            <v>1,30@1;202103,0.01,0.03</v>
+            <v>1;3604</v>
           </cell>
         </row>
         <row r="910">
           <cell r="C910">
-            <v>11400102</v>
+            <v>11300605</v>
           </cell>
           <cell r="S910" t="str">
-            <v>1,30@1;100203,100,200</v>
+            <v>1;3605</v>
           </cell>
         </row>
         <row r="911">
           <cell r="C911">
-            <v>11400103</v>
+            <v>11400101</v>
           </cell>
           <cell r="S911" t="str">
-            <v>1,30@2;62000001</v>
+            <v>1,30@1;202103,0.01,0.03</v>
           </cell>
         </row>
         <row r="912">
           <cell r="C912">
-            <v>11500101</v>
+            <v>11400102</v>
+          </cell>
+          <cell r="S912" t="str">
+            <v>1,30@1;100203,100,200</v>
           </cell>
         </row>
         <row r="913">
           <cell r="C913">
-            <v>11500102</v>
+            <v>11400103</v>
+          </cell>
+          <cell r="S913" t="str">
+            <v>1,30@2;62000001</v>
           </cell>
         </row>
         <row r="914">
           <cell r="C914">
-            <v>11500103</v>
+            <v>11500101</v>
           </cell>
         </row>
         <row r="915">
           <cell r="C915">
-            <v>11500201</v>
+            <v>11500102</v>
           </cell>
         </row>
         <row r="916">
           <cell r="C916">
-            <v>11500202</v>
+            <v>11500103</v>
           </cell>
         </row>
         <row r="917">
           <cell r="C917">
-            <v>11500203</v>
+            <v>11500201</v>
           </cell>
         </row>
         <row r="918">
           <cell r="C918">
-            <v>11500301</v>
+            <v>11500202</v>
           </cell>
         </row>
         <row r="919">
           <cell r="C919">
-            <v>11500302</v>
+            <v>11500203</v>
           </cell>
         </row>
         <row r="920">
           <cell r="C920">
-            <v>11500303</v>
+            <v>11500301</v>
           </cell>
         </row>
         <row r="921">
           <cell r="C921">
-            <v>11500401</v>
+            <v>11500302</v>
           </cell>
         </row>
         <row r="922">
           <cell r="C922">
-            <v>11500402</v>
+            <v>11500303</v>
           </cell>
         </row>
         <row r="923">
           <cell r="C923">
-            <v>11500403</v>
+            <v>11500401</v>
           </cell>
         </row>
         <row r="924">
           <cell r="C924">
-            <v>11500501</v>
+            <v>11500402</v>
           </cell>
         </row>
         <row r="925">
           <cell r="C925">
-            <v>11500502</v>
+            <v>11500403</v>
           </cell>
         </row>
         <row r="926">
           <cell r="C926">
-            <v>11500503</v>
+            <v>11500501</v>
           </cell>
         </row>
         <row r="927">
           <cell r="C927">
-            <v>13001001</v>
-          </cell>
-          <cell r="S927">
-            <v>65001001</v>
+            <v>11500502</v>
           </cell>
         </row>
         <row r="928">
           <cell r="C928">
-            <v>13001002</v>
-          </cell>
-          <cell r="S928">
-            <v>65001002</v>
+            <v>11500503</v>
           </cell>
         </row>
         <row r="929">
           <cell r="C929">
-            <v>13001003</v>
-          </cell>
-          <cell r="S929">
-            <v>65001003</v>
+            <v>11600101</v>
           </cell>
         </row>
         <row r="930">
           <cell r="C930">
-            <v>13001004</v>
-          </cell>
-          <cell r="S930">
-            <v>65001004</v>
+            <v>11600102</v>
           </cell>
         </row>
         <row r="931">
           <cell r="C931">
-            <v>13001005</v>
-          </cell>
-          <cell r="S931">
-            <v>65001005</v>
+            <v>11600103</v>
           </cell>
         </row>
         <row r="932">
           <cell r="C932">
-            <v>13001006</v>
-          </cell>
-          <cell r="S932">
-            <v>65001006</v>
+            <v>11600201</v>
           </cell>
         </row>
         <row r="933">
           <cell r="C933">
-            <v>13001101</v>
-          </cell>
-          <cell r="S933">
-            <v>65001101</v>
+            <v>11600202</v>
           </cell>
         </row>
         <row r="934">
           <cell r="C934">
-            <v>13001102</v>
-          </cell>
-          <cell r="S934">
-            <v>65001102</v>
+            <v>11600203</v>
           </cell>
         </row>
         <row r="935">
           <cell r="C935">
-            <v>13001103</v>
-          </cell>
-          <cell r="S935">
-            <v>65001103</v>
+            <v>11600301</v>
           </cell>
         </row>
         <row r="936">
           <cell r="C936">
-            <v>13001104</v>
-          </cell>
-          <cell r="S936">
-            <v>65001104</v>
+            <v>11600302</v>
           </cell>
         </row>
         <row r="937">
           <cell r="C937">
-            <v>13001105</v>
-          </cell>
-          <cell r="S937">
-            <v>65001105</v>
+            <v>11600303</v>
           </cell>
         </row>
         <row r="938">
           <cell r="C938">
-            <v>13002001</v>
-          </cell>
-          <cell r="S938">
-            <v>65002001</v>
+            <v>11600401</v>
           </cell>
         </row>
         <row r="939">
           <cell r="C939">
-            <v>13002002</v>
-          </cell>
-          <cell r="S939">
-            <v>65002002</v>
+            <v>11600402</v>
           </cell>
         </row>
         <row r="940">
           <cell r="C940">
-            <v>13002003</v>
-          </cell>
-          <cell r="S940">
-            <v>65002003</v>
+            <v>11600403</v>
           </cell>
         </row>
         <row r="941">
           <cell r="C941">
-            <v>13002004</v>
-          </cell>
-          <cell r="S941">
-            <v>65002004</v>
+            <v>11600501</v>
           </cell>
         </row>
         <row r="942">
           <cell r="C942">
-            <v>13002005</v>
-          </cell>
-          <cell r="S942">
-            <v>65002005</v>
+            <v>11600502</v>
           </cell>
         </row>
         <row r="943">
           <cell r="C943">
-            <v>13002006</v>
-          </cell>
-          <cell r="S943">
-            <v>65002006</v>
+            <v>11600503</v>
           </cell>
         </row>
         <row r="944">
           <cell r="C944">
-            <v>13002101</v>
-          </cell>
-          <cell r="S944">
-            <v>65002101</v>
+            <v>11600601</v>
           </cell>
         </row>
         <row r="945">
           <cell r="C945">
-            <v>13002102</v>
-          </cell>
-          <cell r="S945">
-            <v>65002102</v>
+            <v>11600602</v>
           </cell>
         </row>
         <row r="946">
           <cell r="C946">
-            <v>13002103</v>
-          </cell>
-          <cell r="S946">
-            <v>65002103</v>
+            <v>11600603</v>
           </cell>
         </row>
         <row r="947">
           <cell r="C947">
-            <v>13002104</v>
-          </cell>
-          <cell r="S947">
-            <v>65002104</v>
+            <v>11600701</v>
           </cell>
         </row>
         <row r="948">
           <cell r="C948">
-            <v>13002105</v>
-          </cell>
-          <cell r="S948">
-            <v>65002105</v>
+            <v>11600702</v>
           </cell>
         </row>
         <row r="949">
           <cell r="C949">
-            <v>13003001</v>
-          </cell>
-          <cell r="S949">
-            <v>65003001</v>
+            <v>11600703</v>
           </cell>
         </row>
         <row r="950">
           <cell r="C950">
-            <v>13003002</v>
-          </cell>
-          <cell r="S950">
-            <v>65003002</v>
+            <v>11600801</v>
           </cell>
         </row>
         <row r="951">
           <cell r="C951">
-            <v>13003003</v>
-          </cell>
-          <cell r="S951">
-            <v>65003003</v>
+            <v>11600802</v>
           </cell>
         </row>
         <row r="952">
           <cell r="C952">
-            <v>13003004</v>
-          </cell>
-          <cell r="S952">
-            <v>65003004</v>
+            <v>11600803</v>
           </cell>
         </row>
         <row r="953">
           <cell r="C953">
-            <v>13003005</v>
-          </cell>
-          <cell r="S953">
-            <v>65003005</v>
+            <v>11600901</v>
           </cell>
         </row>
         <row r="954">
           <cell r="C954">
-            <v>13003006</v>
-          </cell>
-          <cell r="S954">
-            <v>65003006</v>
+            <v>11600902</v>
           </cell>
         </row>
         <row r="955">
           <cell r="C955">
-            <v>13003101</v>
-          </cell>
-          <cell r="S955">
-            <v>65003101</v>
+            <v>11600903</v>
           </cell>
         </row>
         <row r="956">
           <cell r="C956">
-            <v>13003102</v>
-          </cell>
-          <cell r="S956">
-            <v>65003102</v>
+            <v>11610101</v>
           </cell>
         </row>
         <row r="957">
           <cell r="C957">
-            <v>13003103</v>
-          </cell>
-          <cell r="S957">
-            <v>65003103</v>
+            <v>11610102</v>
           </cell>
         </row>
         <row r="958">
           <cell r="C958">
-            <v>13003104</v>
-          </cell>
-          <cell r="S958">
-            <v>65003104</v>
+            <v>11610103</v>
           </cell>
         </row>
         <row r="959">
           <cell r="C959">
-            <v>13003105</v>
-          </cell>
-          <cell r="S959">
-            <v>65003105</v>
+            <v>11610201</v>
           </cell>
         </row>
         <row r="960">
           <cell r="C960">
-            <v>13004001</v>
-          </cell>
-          <cell r="S960">
-            <v>65004001</v>
+            <v>11610202</v>
           </cell>
         </row>
         <row r="961">
           <cell r="C961">
-            <v>13004002</v>
-          </cell>
-          <cell r="S961">
-            <v>65004002</v>
+            <v>11610203</v>
           </cell>
         </row>
         <row r="962">
           <cell r="C962">
-            <v>13004003</v>
-          </cell>
-          <cell r="S962">
-            <v>65004003</v>
+            <v>11610301</v>
           </cell>
         </row>
         <row r="963">
           <cell r="C963">
-            <v>13004004</v>
-          </cell>
-          <cell r="S963">
-            <v>65004004</v>
+            <v>11610302</v>
           </cell>
         </row>
         <row r="964">
           <cell r="C964">
-            <v>13004005</v>
-          </cell>
-          <cell r="S964">
-            <v>65004005</v>
+            <v>11610303</v>
           </cell>
         </row>
         <row r="965">
           <cell r="C965">
-            <v>13004006</v>
-          </cell>
-          <cell r="S965">
-            <v>65004006</v>
+            <v>11610401</v>
           </cell>
         </row>
         <row r="966">
           <cell r="C966">
-            <v>13004101</v>
-          </cell>
-          <cell r="S966">
-            <v>65004101</v>
+            <v>11610402</v>
           </cell>
         </row>
         <row r="967">
           <cell r="C967">
-            <v>13004102</v>
-          </cell>
-          <cell r="S967">
-            <v>65004102</v>
+            <v>11610403</v>
           </cell>
         </row>
         <row r="968">
           <cell r="C968">
-            <v>13004103</v>
-          </cell>
-          <cell r="S968">
-            <v>65004103</v>
+            <v>11610501</v>
           </cell>
         </row>
         <row r="969">
           <cell r="C969">
-            <v>13004104</v>
-          </cell>
-          <cell r="S969">
-            <v>65004104</v>
+            <v>11610502</v>
           </cell>
         </row>
         <row r="970">
           <cell r="C970">
-            <v>13004105</v>
-          </cell>
-          <cell r="S970">
-            <v>65004105</v>
+            <v>11610503</v>
           </cell>
         </row>
         <row r="971">
           <cell r="C971">
-            <v>13005001</v>
-          </cell>
-          <cell r="S971">
-            <v>65005001</v>
+            <v>11610601</v>
           </cell>
         </row>
         <row r="972">
           <cell r="C972">
-            <v>13005002</v>
-          </cell>
-          <cell r="S972">
-            <v>65005002</v>
+            <v>11610602</v>
           </cell>
         </row>
         <row r="973">
           <cell r="C973">
-            <v>13005003</v>
-          </cell>
-          <cell r="S973">
-            <v>65005003</v>
+            <v>11610603</v>
           </cell>
         </row>
         <row r="974">
           <cell r="C974">
-            <v>13005004</v>
-          </cell>
-          <cell r="S974">
-            <v>65005004</v>
+            <v>11610701</v>
           </cell>
         </row>
         <row r="975">
           <cell r="C975">
-            <v>13005005</v>
-          </cell>
-          <cell r="S975">
-            <v>65005005</v>
+            <v>11610702</v>
           </cell>
         </row>
         <row r="976">
           <cell r="C976">
-            <v>13005006</v>
-          </cell>
-          <cell r="S976">
-            <v>65005006</v>
+            <v>11610703</v>
           </cell>
         </row>
         <row r="977">
           <cell r="C977">
-            <v>13005101</v>
+            <v>13001001</v>
           </cell>
           <cell r="S977">
-            <v>65005101</v>
+            <v>65001001</v>
           </cell>
         </row>
         <row r="978">
           <cell r="C978">
-            <v>13005102</v>
+            <v>13001002</v>
           </cell>
           <cell r="S978">
-            <v>65005102</v>
+            <v>65001002</v>
           </cell>
         </row>
         <row r="979">
           <cell r="C979">
-            <v>13005103</v>
+            <v>13001003</v>
           </cell>
           <cell r="S979">
-            <v>65005103</v>
+            <v>65001003</v>
           </cell>
         </row>
         <row r="980">
           <cell r="C980">
-            <v>13005104</v>
+            <v>13001004</v>
           </cell>
           <cell r="S980">
-            <v>65005104</v>
+            <v>65001004</v>
           </cell>
         </row>
         <row r="981">
           <cell r="C981">
-            <v>13005105</v>
+            <v>13001005</v>
           </cell>
           <cell r="S981">
-            <v>65005105</v>
+            <v>65001005</v>
           </cell>
         </row>
         <row r="982">
           <cell r="C982">
-            <v>13006001</v>
+            <v>13001006</v>
           </cell>
           <cell r="S982">
-            <v>65006001</v>
+            <v>65001006</v>
           </cell>
         </row>
         <row r="983">
           <cell r="C983">
-            <v>13006002</v>
+            <v>13001101</v>
           </cell>
           <cell r="S983">
-            <v>65006002</v>
+            <v>65001101</v>
           </cell>
         </row>
         <row r="984">
           <cell r="C984">
-            <v>13006003</v>
+            <v>13001102</v>
           </cell>
           <cell r="S984">
-            <v>65006003</v>
+            <v>65001102</v>
           </cell>
         </row>
         <row r="985">
           <cell r="C985">
-            <v>13006004</v>
+            <v>13001103</v>
           </cell>
           <cell r="S985">
-            <v>65006004</v>
+            <v>65001103</v>
           </cell>
         </row>
         <row r="986">
           <cell r="C986">
-            <v>13009001</v>
+            <v>13001104</v>
           </cell>
-          <cell r="S986" t="str">
-            <v>4;20</v>
+          <cell r="S986">
+            <v>65001104</v>
           </cell>
         </row>
         <row r="987">
           <cell r="C987">
-            <v>13009002</v>
+            <v>13001105</v>
           </cell>
-          <cell r="S987" t="str">
-            <v>5;20</v>
+          <cell r="S987">
+            <v>65001105</v>
           </cell>
         </row>
         <row r="988">
           <cell r="C988">
-            <v>14000001</v>
+            <v>13002001</v>
+          </cell>
+          <cell r="S988">
+            <v>65002001</v>
           </cell>
         </row>
         <row r="989">
           <cell r="C989">
-            <v>14000002</v>
+            <v>13002002</v>
+          </cell>
+          <cell r="S989">
+            <v>65002002</v>
           </cell>
         </row>
         <row r="990">
           <cell r="C990">
-            <v>14000003</v>
+            <v>13002003</v>
+          </cell>
+          <cell r="S990">
+            <v>65002003</v>
           </cell>
         </row>
         <row r="991">
           <cell r="C991">
-            <v>14000004</v>
+            <v>13002004</v>
+          </cell>
+          <cell r="S991">
+            <v>65002004</v>
           </cell>
         </row>
         <row r="992">
           <cell r="C992">
-            <v>14000005</v>
+            <v>13002005</v>
+          </cell>
+          <cell r="S992">
+            <v>65002005</v>
           </cell>
         </row>
         <row r="993">
           <cell r="C993">
-            <v>14010001</v>
+            <v>13002006</v>
+          </cell>
+          <cell r="S993">
+            <v>65002006</v>
           </cell>
         </row>
         <row r="994">
           <cell r="C994">
-            <v>14010002</v>
+            <v>13002101</v>
+          </cell>
+          <cell r="S994">
+            <v>65002101</v>
           </cell>
         </row>
         <row r="995">
           <cell r="C995">
-            <v>14010003</v>
+            <v>13002102</v>
+          </cell>
+          <cell r="S995">
+            <v>65002102</v>
           </cell>
         </row>
         <row r="996">
           <cell r="C996">
-            <v>14010004</v>
+            <v>13002103</v>
+          </cell>
+          <cell r="S996">
+            <v>65002103</v>
           </cell>
         </row>
         <row r="997">
           <cell r="C997">
-            <v>14010005</v>
+            <v>13002104</v>
+          </cell>
+          <cell r="S997">
+            <v>65002104</v>
           </cell>
         </row>
         <row r="998">
           <cell r="C998">
-            <v>14010006</v>
+            <v>13002105</v>
+          </cell>
+          <cell r="S998">
+            <v>65002105</v>
           </cell>
         </row>
         <row r="999">
           <cell r="C999">
-            <v>14010007</v>
+            <v>13003001</v>
+          </cell>
+          <cell r="S999">
+            <v>65003001</v>
           </cell>
         </row>
         <row r="1000">
           <cell r="C1000">
-            <v>14010008</v>
+            <v>13003002</v>
+          </cell>
+          <cell r="S1000">
+            <v>65003002</v>
           </cell>
         </row>
         <row r="1001">
           <cell r="C1001">
-            <v>14010009</v>
+            <v>13003003</v>
+          </cell>
+          <cell r="S1001">
+            <v>65003003</v>
           </cell>
         </row>
         <row r="1002">
           <cell r="C1002">
-            <v>14010010</v>
+            <v>13003004</v>
+          </cell>
+          <cell r="S1002">
+            <v>65003004</v>
           </cell>
         </row>
         <row r="1003">
           <cell r="C1003">
-            <v>14010011</v>
+            <v>13003005</v>
+          </cell>
+          <cell r="S1003">
+            <v>65003005</v>
           </cell>
         </row>
         <row r="1004">
           <cell r="C1004">
-            <v>14010012</v>
+            <v>13003006</v>
+          </cell>
+          <cell r="S1004">
+            <v>65003006</v>
           </cell>
         </row>
         <row r="1005">
           <cell r="C1005">
-            <v>14020001</v>
+            <v>13003101</v>
+          </cell>
+          <cell r="S1005">
+            <v>65003101</v>
           </cell>
         </row>
         <row r="1006">
           <cell r="C1006">
-            <v>14020002</v>
+            <v>13003102</v>
+          </cell>
+          <cell r="S1006">
+            <v>65003102</v>
           </cell>
         </row>
         <row r="1007">
           <cell r="C1007">
-            <v>14020003</v>
+            <v>13003103</v>
+          </cell>
+          <cell r="S1007">
+            <v>65003103</v>
           </cell>
         </row>
         <row r="1008">
           <cell r="C1008">
-            <v>14020004</v>
+            <v>13003104</v>
+          </cell>
+          <cell r="S1008">
+            <v>65003104</v>
           </cell>
         </row>
         <row r="1009">
           <cell r="C1009">
-            <v>14020005</v>
+            <v>13003105</v>
+          </cell>
+          <cell r="S1009">
+            <v>65003105</v>
           </cell>
         </row>
         <row r="1010">
           <cell r="C1010">
-            <v>14020006</v>
+            <v>13004001</v>
+          </cell>
+          <cell r="S1010">
+            <v>65004001</v>
           </cell>
         </row>
         <row r="1011">
           <cell r="C1011">
-            <v>14020007</v>
+            <v>13004002</v>
+          </cell>
+          <cell r="S1011">
+            <v>65004002</v>
           </cell>
         </row>
         <row r="1012">
           <cell r="C1012">
-            <v>14020008</v>
+            <v>13004003</v>
+          </cell>
+          <cell r="S1012">
+            <v>65004003</v>
           </cell>
         </row>
         <row r="1013">
           <cell r="C1013">
-            <v>14020009</v>
+            <v>13004004</v>
+          </cell>
+          <cell r="S1013">
+            <v>65004004</v>
           </cell>
         </row>
         <row r="1014">
           <cell r="C1014">
-            <v>14020010</v>
+            <v>13004005</v>
+          </cell>
+          <cell r="S1014">
+            <v>65004005</v>
           </cell>
         </row>
         <row r="1015">
           <cell r="C1015">
-            <v>14020011</v>
+            <v>13004006</v>
+          </cell>
+          <cell r="S1015">
+            <v>65004006</v>
           </cell>
         </row>
         <row r="1016">
           <cell r="C1016">
-            <v>14020012</v>
+            <v>13004101</v>
+          </cell>
+          <cell r="S1016">
+            <v>65004101</v>
           </cell>
         </row>
         <row r="1017">
           <cell r="C1017">
-            <v>14020013</v>
+            <v>13004102</v>
+          </cell>
+          <cell r="S1017">
+            <v>65004102</v>
           </cell>
         </row>
         <row r="1018">
           <cell r="C1018">
-            <v>14030001</v>
+            <v>13004103</v>
+          </cell>
+          <cell r="S1018">
+            <v>65004103</v>
           </cell>
         </row>
         <row r="1019">
           <cell r="C1019">
-            <v>14030002</v>
+            <v>13004104</v>
+          </cell>
+          <cell r="S1019">
+            <v>65004104</v>
           </cell>
         </row>
         <row r="1020">
           <cell r="C1020">
-            <v>14030003</v>
+            <v>13004105</v>
+          </cell>
+          <cell r="S1020">
+            <v>65004105</v>
           </cell>
         </row>
         <row r="1021">
           <cell r="C1021">
-            <v>14030004</v>
+            <v>13005001</v>
+          </cell>
+          <cell r="S1021">
+            <v>65005001</v>
           </cell>
         </row>
         <row r="1022">
           <cell r="C1022">
-            <v>14030005</v>
+            <v>13005002</v>
+          </cell>
+          <cell r="S1022">
+            <v>65005002</v>
           </cell>
         </row>
         <row r="1023">
           <cell r="C1023">
-            <v>14030006</v>
+            <v>13005003</v>
+          </cell>
+          <cell r="S1023">
+            <v>65005003</v>
           </cell>
         </row>
         <row r="1024">
           <cell r="C1024">
-            <v>14030007</v>
+            <v>13005004</v>
+          </cell>
+          <cell r="S1024">
+            <v>65005004</v>
           </cell>
         </row>
         <row r="1025">
           <cell r="C1025">
-            <v>14030008</v>
+            <v>13005005</v>
+          </cell>
+          <cell r="S1025">
+            <v>65005005</v>
           </cell>
         </row>
         <row r="1026">
           <cell r="C1026">
-            <v>14030009</v>
+            <v>13005006</v>
+          </cell>
+          <cell r="S1026">
+            <v>65005006</v>
           </cell>
         </row>
         <row r="1027">
           <cell r="C1027">
-            <v>14030010</v>
+            <v>13005101</v>
+          </cell>
+          <cell r="S1027">
+            <v>65005101</v>
           </cell>
         </row>
         <row r="1028">
           <cell r="C1028">
-            <v>14030011</v>
+            <v>13005102</v>
+          </cell>
+          <cell r="S1028">
+            <v>65005102</v>
           </cell>
         </row>
         <row r="1029">
           <cell r="C1029">
-            <v>14030012</v>
+            <v>13005103</v>
+          </cell>
+          <cell r="S1029">
+            <v>65005103</v>
           </cell>
         </row>
         <row r="1030">
           <cell r="C1030">
-            <v>14030013</v>
+            <v>13005104</v>
+          </cell>
+          <cell r="S1030">
+            <v>65005104</v>
           </cell>
         </row>
         <row r="1031">
           <cell r="C1031">
-            <v>14040001</v>
+            <v>13005105</v>
+          </cell>
+          <cell r="S1031">
+            <v>65005105</v>
           </cell>
         </row>
         <row r="1032">
           <cell r="C1032">
-            <v>14040002</v>
+            <v>13006001</v>
+          </cell>
+          <cell r="S1032">
+            <v>65006001</v>
           </cell>
         </row>
         <row r="1033">
           <cell r="C1033">
-            <v>14040003</v>
+            <v>13006002</v>
+          </cell>
+          <cell r="S1033">
+            <v>65006002</v>
           </cell>
         </row>
         <row r="1034">
           <cell r="C1034">
-            <v>14040004</v>
+            <v>13006003</v>
+          </cell>
+          <cell r="S1034">
+            <v>65006003</v>
           </cell>
         </row>
         <row r="1035">
           <cell r="C1035">
-            <v>14040005</v>
+            <v>13006004</v>
+          </cell>
+          <cell r="S1035">
+            <v>65006004</v>
           </cell>
         </row>
         <row r="1036">
           <cell r="C1036">
-            <v>14040006</v>
+            <v>13009001</v>
+          </cell>
+          <cell r="S1036" t="str">
+            <v>4;20</v>
           </cell>
         </row>
         <row r="1037">
           <cell r="C1037">
-            <v>14040007</v>
+            <v>13009002</v>
+          </cell>
+          <cell r="S1037" t="str">
+            <v>5;20</v>
           </cell>
         </row>
         <row r="1038">
           <cell r="C1038">
-            <v>14040008</v>
+            <v>14000001</v>
           </cell>
         </row>
         <row r="1039">
           <cell r="C1039">
-            <v>14040009</v>
+            <v>14000002</v>
           </cell>
         </row>
         <row r="1040">
           <cell r="C1040">
-            <v>14040010</v>
+            <v>14000003</v>
           </cell>
         </row>
         <row r="1041">
           <cell r="C1041">
-            <v>14040011</v>
+            <v>14000004</v>
           </cell>
         </row>
         <row r="1042">
           <cell r="C1042">
-            <v>14040012</v>
+            <v>14000005</v>
           </cell>
         </row>
         <row r="1043">
           <cell r="C1043">
-            <v>14050001</v>
+            <v>14010001</v>
           </cell>
         </row>
         <row r="1044">
           <cell r="C1044">
-            <v>14050002</v>
+            <v>14010002</v>
           </cell>
         </row>
         <row r="1045">
           <cell r="C1045">
-            <v>14050003</v>
+            <v>14010003</v>
           </cell>
         </row>
         <row r="1046">
           <cell r="C1046">
-            <v>14050004</v>
+            <v>14010004</v>
           </cell>
         </row>
         <row r="1047">
           <cell r="C1047">
-            <v>14050005</v>
+            <v>14010005</v>
           </cell>
         </row>
         <row r="1048">
           <cell r="C1048">
-            <v>14050006</v>
+            <v>14010006</v>
           </cell>
         </row>
         <row r="1049">
           <cell r="C1049">
-            <v>14050007</v>
+            <v>14010007</v>
           </cell>
         </row>
         <row r="1050">
           <cell r="C1050">
-            <v>14050008</v>
+            <v>14010008</v>
           </cell>
         </row>
         <row r="1051">
           <cell r="C1051">
-            <v>14050009</v>
+            <v>14010009</v>
           </cell>
         </row>
         <row r="1052">
           <cell r="C1052">
-            <v>14050010</v>
+            <v>14010010</v>
           </cell>
         </row>
         <row r="1053">
           <cell r="C1053">
-            <v>14050011</v>
+            <v>14010011</v>
           </cell>
         </row>
         <row r="1054">
           <cell r="C1054">
-            <v>14050012</v>
+            <v>14010012</v>
           </cell>
         </row>
         <row r="1055">
           <cell r="C1055">
-            <v>14060001</v>
+            <v>14020001</v>
           </cell>
         </row>
         <row r="1056">
           <cell r="C1056">
-            <v>14060002</v>
+            <v>14020002</v>
           </cell>
         </row>
         <row r="1057">
           <cell r="C1057">
-            <v>14060003</v>
+            <v>14020003</v>
           </cell>
         </row>
         <row r="1058">
           <cell r="C1058">
-            <v>14060004</v>
+            <v>14020004</v>
           </cell>
         </row>
         <row r="1059">
           <cell r="C1059">
-            <v>14060005</v>
+            <v>14020005</v>
           </cell>
         </row>
         <row r="1060">
           <cell r="C1060">
-            <v>14060006</v>
+            <v>14020006</v>
           </cell>
         </row>
         <row r="1061">
           <cell r="C1061">
-            <v>14070001</v>
+            <v>14020007</v>
           </cell>
         </row>
         <row r="1062">
           <cell r="C1062">
-            <v>14070002</v>
+            <v>14020008</v>
           </cell>
         </row>
         <row r="1063">
           <cell r="C1063">
-            <v>14070003</v>
+            <v>14020009</v>
           </cell>
         </row>
         <row r="1064">
           <cell r="C1064">
-            <v>14070004</v>
+            <v>14020010</v>
           </cell>
         </row>
         <row r="1065">
           <cell r="C1065">
-            <v>14080001</v>
+            <v>14020011</v>
           </cell>
         </row>
         <row r="1066">
           <cell r="C1066">
-            <v>14080002</v>
+            <v>14020012</v>
           </cell>
         </row>
         <row r="1067">
           <cell r="C1067">
-            <v>14080003</v>
+            <v>14020013</v>
           </cell>
         </row>
         <row r="1068">
           <cell r="C1068">
-            <v>14080004</v>
+            <v>14030001</v>
           </cell>
         </row>
         <row r="1069">
           <cell r="C1069">
-            <v>14090001</v>
+            <v>14030002</v>
           </cell>
         </row>
         <row r="1070">
           <cell r="C1070">
-            <v>14090002</v>
+            <v>14030003</v>
           </cell>
         </row>
         <row r="1071">
           <cell r="C1071">
-            <v>14090003</v>
+            <v>14030004</v>
           </cell>
         </row>
         <row r="1072">
           <cell r="C1072">
-            <v>14090004</v>
+            <v>14030005</v>
           </cell>
         </row>
         <row r="1073">
           <cell r="C1073">
-            <v>14100001</v>
+            <v>14030006</v>
           </cell>
         </row>
         <row r="1074">
           <cell r="C1074">
-            <v>14100002</v>
+            <v>14030007</v>
           </cell>
         </row>
         <row r="1075">
           <cell r="C1075">
-            <v>14100003</v>
+            <v>14030008</v>
           </cell>
         </row>
         <row r="1076">
           <cell r="C1076">
-            <v>14100004</v>
+            <v>14030009</v>
           </cell>
         </row>
         <row r="1077">
           <cell r="C1077">
-            <v>14100005</v>
+            <v>14030010</v>
           </cell>
         </row>
         <row r="1078">
           <cell r="C1078">
-            <v>14100006</v>
+            <v>14030011</v>
           </cell>
         </row>
         <row r="1079">
           <cell r="C1079">
-            <v>14100007</v>
+            <v>14030012</v>
           </cell>
         </row>
         <row r="1080">
           <cell r="C1080">
-            <v>14100008</v>
+            <v>14030013</v>
           </cell>
         </row>
         <row r="1081">
           <cell r="C1081">
-            <v>14100011</v>
+            <v>14040001</v>
           </cell>
         </row>
         <row r="1082">
           <cell r="C1082">
-            <v>14100012</v>
+            <v>14040002</v>
           </cell>
         </row>
         <row r="1083">
           <cell r="C1083">
-            <v>14100021</v>
+            <v>14040003</v>
           </cell>
         </row>
         <row r="1084">
           <cell r="C1084">
-            <v>14100022</v>
+            <v>14040004</v>
           </cell>
         </row>
         <row r="1085">
           <cell r="C1085">
-            <v>14100101</v>
+            <v>14040005</v>
           </cell>
         </row>
         <row r="1086">
           <cell r="C1086">
-            <v>14100102</v>
+            <v>14040006</v>
           </cell>
         </row>
         <row r="1087">
           <cell r="C1087">
-            <v>14100103</v>
+            <v>14040007</v>
           </cell>
         </row>
         <row r="1088">
           <cell r="C1088">
-            <v>14100104</v>
+            <v>14040008</v>
           </cell>
         </row>
         <row r="1089">
           <cell r="C1089">
-            <v>14100105</v>
+            <v>14040009</v>
           </cell>
         </row>
         <row r="1090">
           <cell r="C1090">
-            <v>14100106</v>
+            <v>14040010</v>
           </cell>
         </row>
         <row r="1091">
           <cell r="C1091">
-            <v>14100107</v>
+            <v>14040011</v>
           </cell>
         </row>
         <row r="1092">
           <cell r="C1092">
-            <v>14100108</v>
+            <v>14040012</v>
           </cell>
         </row>
         <row r="1093">
           <cell r="C1093">
-            <v>14100111</v>
+            <v>14050001</v>
           </cell>
         </row>
         <row r="1094">
           <cell r="C1094">
-            <v>14100112</v>
+            <v>14050002</v>
           </cell>
         </row>
         <row r="1095">
           <cell r="C1095">
-            <v>14100121</v>
+            <v>14050003</v>
           </cell>
         </row>
         <row r="1096">
           <cell r="C1096">
-            <v>14100122</v>
+            <v>14050004</v>
           </cell>
         </row>
         <row r="1097">
           <cell r="C1097">
-            <v>14100201</v>
+            <v>14050005</v>
           </cell>
         </row>
         <row r="1098">
           <cell r="C1098">
-            <v>14100202</v>
+            <v>14050006</v>
           </cell>
         </row>
         <row r="1099">
           <cell r="C1099">
-            <v>14100203</v>
+            <v>14050007</v>
           </cell>
         </row>
         <row r="1100">
           <cell r="C1100">
-            <v>14100204</v>
+            <v>14050008</v>
           </cell>
         </row>
         <row r="1101">
           <cell r="C1101">
-            <v>14100211</v>
+            <v>14050009</v>
           </cell>
         </row>
         <row r="1102">
           <cell r="C1102">
-            <v>14100221</v>
+            <v>14050010</v>
           </cell>
         </row>
         <row r="1103">
           <cell r="C1103">
-            <v>14110001</v>
+            <v>14050011</v>
           </cell>
         </row>
         <row r="1104">
           <cell r="C1104">
-            <v>14110002</v>
+            <v>14050012</v>
           </cell>
         </row>
         <row r="1105">
           <cell r="C1105">
-            <v>14110003</v>
+            <v>14060001</v>
           </cell>
         </row>
         <row r="1106">
           <cell r="C1106">
-            <v>14110004</v>
+            <v>14060002</v>
           </cell>
         </row>
         <row r="1107">
           <cell r="C1107">
-            <v>14110005</v>
+            <v>14060003</v>
           </cell>
         </row>
         <row r="1108">
           <cell r="C1108">
-            <v>14110006</v>
+            <v>14060004</v>
           </cell>
         </row>
         <row r="1109">
           <cell r="C1109">
-            <v>14110007</v>
+            <v>14060005</v>
           </cell>
         </row>
         <row r="1110">
           <cell r="C1110">
-            <v>14110008</v>
+            <v>14060006</v>
           </cell>
         </row>
         <row r="1111">
           <cell r="C1111">
-            <v>14110009</v>
+            <v>14070001</v>
           </cell>
         </row>
         <row r="1112">
           <cell r="C1112">
-            <v>14110010</v>
+            <v>14070002</v>
           </cell>
         </row>
         <row r="1113">
           <cell r="C1113">
-            <v>14110011</v>
+            <v>14070003</v>
           </cell>
         </row>
         <row r="1114">
           <cell r="C1114">
-            <v>14110012</v>
+            <v>14070004</v>
           </cell>
         </row>
         <row r="1115">
           <cell r="C1115">
-            <v>14110021</v>
+            <v>14080001</v>
           </cell>
         </row>
         <row r="1116">
           <cell r="C1116">
-            <v>14110022</v>
+            <v>14080002</v>
           </cell>
         </row>
         <row r="1117">
           <cell r="C1117">
-            <v>14110023</v>
+            <v>14080003</v>
           </cell>
         </row>
         <row r="1118">
           <cell r="C1118">
-            <v>15201001</v>
+            <v>14080004</v>
           </cell>
         </row>
         <row r="1119">
           <cell r="C1119">
-            <v>15201002</v>
+            <v>14090001</v>
           </cell>
         </row>
         <row r="1120">
           <cell r="C1120">
-            <v>15201003</v>
+            <v>14090002</v>
           </cell>
         </row>
         <row r="1121">
           <cell r="C1121">
-            <v>15201004</v>
+            <v>14090003</v>
           </cell>
         </row>
         <row r="1122">
           <cell r="C1122">
-            <v>15201005</v>
+            <v>14090004</v>
           </cell>
         </row>
         <row r="1123">
           <cell r="C1123">
-            <v>15201006</v>
+            <v>14100001</v>
           </cell>
         </row>
         <row r="1124">
           <cell r="C1124">
-            <v>15202001</v>
+            <v>14100002</v>
           </cell>
         </row>
         <row r="1125">
           <cell r="C1125">
-            <v>15202002</v>
+            <v>14100003</v>
           </cell>
         </row>
         <row r="1126">
           <cell r="C1126">
-            <v>15202003</v>
+            <v>14100004</v>
           </cell>
         </row>
         <row r="1127">
           <cell r="C1127">
-            <v>15202004</v>
+            <v>14100005</v>
           </cell>
         </row>
         <row r="1128">
           <cell r="C1128">
-            <v>15202005</v>
+            <v>14100006</v>
           </cell>
         </row>
         <row r="1129">
           <cell r="C1129">
-            <v>15202006</v>
+            <v>14100007</v>
           </cell>
         </row>
         <row r="1130">
           <cell r="C1130">
-            <v>15203001</v>
+            <v>14100008</v>
           </cell>
         </row>
         <row r="1131">
           <cell r="C1131">
-            <v>15203002</v>
+            <v>14100011</v>
           </cell>
         </row>
         <row r="1132">
           <cell r="C1132">
-            <v>15203003</v>
+            <v>14100012</v>
           </cell>
         </row>
         <row r="1133">
           <cell r="C1133">
-            <v>15203004</v>
+            <v>14100021</v>
           </cell>
         </row>
         <row r="1134">
           <cell r="C1134">
-            <v>15203005</v>
+            <v>14100022</v>
           </cell>
         </row>
         <row r="1135">
           <cell r="C1135">
-            <v>15203006</v>
+            <v>14100101</v>
           </cell>
         </row>
         <row r="1136">
           <cell r="C1136">
-            <v>15204001</v>
+            <v>14100102</v>
           </cell>
         </row>
         <row r="1137">
           <cell r="C1137">
-            <v>15204002</v>
+            <v>14100103</v>
           </cell>
         </row>
         <row r="1138">
           <cell r="C1138">
-            <v>15204003</v>
+            <v>14100104</v>
           </cell>
         </row>
         <row r="1139">
           <cell r="C1139">
-            <v>15204004</v>
+            <v>14100105</v>
           </cell>
         </row>
         <row r="1140">
           <cell r="C1140">
-            <v>15204005</v>
+            <v>14100106</v>
           </cell>
         </row>
         <row r="1141">
           <cell r="C1141">
-            <v>15204006</v>
+            <v>14100107</v>
           </cell>
         </row>
         <row r="1142">
           <cell r="C1142">
-            <v>15205001</v>
+            <v>14100108</v>
           </cell>
         </row>
         <row r="1143">
           <cell r="C1143">
-            <v>15205002</v>
+            <v>14100111</v>
           </cell>
         </row>
         <row r="1144">
           <cell r="C1144">
-            <v>15205003</v>
+            <v>14100112</v>
           </cell>
         </row>
         <row r="1145">
           <cell r="C1145">
-            <v>15205004</v>
+            <v>14100121</v>
           </cell>
         </row>
         <row r="1146">
           <cell r="C1146">
-            <v>15205005</v>
+            <v>14100122</v>
           </cell>
         </row>
         <row r="1147">
           <cell r="C1147">
-            <v>15205006</v>
+            <v>14100201</v>
           </cell>
         </row>
         <row r="1148">
           <cell r="C1148">
-            <v>15205007</v>
+            <v>14100202</v>
           </cell>
         </row>
         <row r="1149">
           <cell r="C1149">
-            <v>15206001</v>
+            <v>14100203</v>
           </cell>
         </row>
         <row r="1150">
           <cell r="C1150">
-            <v>15206002</v>
+            <v>14100204</v>
           </cell>
         </row>
         <row r="1151">
           <cell r="C1151">
-            <v>15206003</v>
+            <v>14100211</v>
           </cell>
         </row>
         <row r="1152">
           <cell r="C1152">
-            <v>15207001</v>
+            <v>14100221</v>
           </cell>
         </row>
         <row r="1153">
           <cell r="C1153">
-            <v>15207002</v>
+            <v>14110001</v>
           </cell>
         </row>
         <row r="1154">
           <cell r="C1154">
-            <v>15207003</v>
+            <v>14110002</v>
           </cell>
         </row>
         <row r="1155">
           <cell r="C1155">
-            <v>15208001</v>
+            <v>14110003</v>
           </cell>
         </row>
         <row r="1156">
           <cell r="C1156">
-            <v>15208002</v>
+            <v>14110004</v>
           </cell>
         </row>
         <row r="1157">
           <cell r="C1157">
-            <v>15208003</v>
+            <v>14110005</v>
           </cell>
         </row>
         <row r="1158">
           <cell r="C1158">
-            <v>15209001</v>
+            <v>14110006</v>
           </cell>
         </row>
         <row r="1159">
           <cell r="C1159">
-            <v>15209002</v>
+            <v>14110007</v>
           </cell>
         </row>
         <row r="1160">
           <cell r="C1160">
-            <v>15210001</v>
+            <v>14110008</v>
           </cell>
         </row>
         <row r="1161">
           <cell r="C1161">
-            <v>15210002</v>
+            <v>14110009</v>
           </cell>
         </row>
         <row r="1162">
           <cell r="C1162">
-            <v>15210003</v>
+            <v>14110010</v>
           </cell>
         </row>
         <row r="1163">
           <cell r="C1163">
-            <v>15210004</v>
+            <v>14110011</v>
           </cell>
         </row>
         <row r="1164">
           <cell r="C1164">
-            <v>15210011</v>
+            <v>14110012</v>
           </cell>
         </row>
         <row r="1165">
           <cell r="C1165">
-            <v>15210012</v>
+            <v>14110021</v>
           </cell>
         </row>
         <row r="1166">
           <cell r="C1166">
-            <v>15210101</v>
+            <v>14110022</v>
           </cell>
         </row>
         <row r="1167">
           <cell r="C1167">
-            <v>15210102</v>
+            <v>14110023</v>
           </cell>
         </row>
         <row r="1168">
           <cell r="C1168">
-            <v>15210103</v>
+            <v>15201001</v>
           </cell>
         </row>
         <row r="1169">
           <cell r="C1169">
-            <v>15210104</v>
+            <v>15201002</v>
           </cell>
         </row>
         <row r="1170">
           <cell r="C1170">
-            <v>15210111</v>
+            <v>15201003</v>
           </cell>
         </row>
         <row r="1171">
           <cell r="C1171">
-            <v>15210112</v>
+            <v>15201004</v>
           </cell>
         </row>
         <row r="1172">
           <cell r="C1172">
-            <v>15210201</v>
+            <v>15201005</v>
           </cell>
         </row>
         <row r="1173">
           <cell r="C1173">
-            <v>15210202</v>
+            <v>15201006</v>
           </cell>
         </row>
         <row r="1174">
           <cell r="C1174">
-            <v>15210211</v>
+            <v>15202001</v>
           </cell>
         </row>
         <row r="1175">
           <cell r="C1175">
-            <v>15211001</v>
+            <v>15202002</v>
           </cell>
         </row>
         <row r="1176">
           <cell r="C1176">
-            <v>15211002</v>
+            <v>15202003</v>
           </cell>
         </row>
         <row r="1177">
           <cell r="C1177">
-            <v>15211003</v>
+            <v>15202004</v>
           </cell>
         </row>
         <row r="1178">
           <cell r="C1178">
-            <v>15211004</v>
+            <v>15202005</v>
           </cell>
         </row>
         <row r="1179">
           <cell r="C1179">
-            <v>15211005</v>
+            <v>15202006</v>
           </cell>
         </row>
         <row r="1180">
           <cell r="C1180">
-            <v>15211006</v>
+            <v>15203001</v>
           </cell>
         </row>
         <row r="1181">
           <cell r="C1181">
-            <v>15211011</v>
+            <v>15203002</v>
           </cell>
         </row>
         <row r="1182">
           <cell r="C1182">
-            <v>15211012</v>
+            <v>15203003</v>
           </cell>
         </row>
         <row r="1183">
           <cell r="C1183">
-            <v>15211013</v>
+            <v>15203004</v>
           </cell>
         </row>
         <row r="1184">
           <cell r="C1184">
-            <v>15301001</v>
+            <v>15203005</v>
           </cell>
         </row>
         <row r="1185">
           <cell r="C1185">
-            <v>15301002</v>
+            <v>15203006</v>
           </cell>
         </row>
         <row r="1186">
           <cell r="C1186">
-            <v>15301003</v>
+            <v>15204001</v>
           </cell>
         </row>
         <row r="1187">
           <cell r="C1187">
-            <v>15301004</v>
+            <v>15204002</v>
           </cell>
         </row>
         <row r="1188">
           <cell r="C1188">
-            <v>15301005</v>
+            <v>15204003</v>
           </cell>
         </row>
         <row r="1189">
           <cell r="C1189">
-            <v>15301006</v>
+            <v>15204004</v>
           </cell>
         </row>
         <row r="1190">
           <cell r="C1190">
-            <v>15302001</v>
+            <v>15204005</v>
           </cell>
         </row>
         <row r="1191">
           <cell r="C1191">
-            <v>15302002</v>
+            <v>15204006</v>
           </cell>
         </row>
         <row r="1192">
           <cell r="C1192">
-            <v>15302003</v>
+            <v>15205001</v>
           </cell>
         </row>
         <row r="1193">
           <cell r="C1193">
-            <v>15302004</v>
+            <v>15205002</v>
           </cell>
         </row>
         <row r="1194">
           <cell r="C1194">
-            <v>15302005</v>
+            <v>15205003</v>
           </cell>
         </row>
         <row r="1195">
           <cell r="C1195">
-            <v>15302006</v>
+            <v>15205004</v>
           </cell>
         </row>
         <row r="1196">
           <cell r="C1196">
-            <v>15302007</v>
+            <v>15205005</v>
           </cell>
         </row>
         <row r="1197">
           <cell r="C1197">
-            <v>15303001</v>
+            <v>15205006</v>
           </cell>
         </row>
         <row r="1198">
           <cell r="C1198">
-            <v>15303002</v>
+            <v>15205007</v>
           </cell>
         </row>
         <row r="1199">
           <cell r="C1199">
-            <v>15303003</v>
+            <v>15206001</v>
           </cell>
         </row>
         <row r="1200">
           <cell r="C1200">
-            <v>15303004</v>
+            <v>15206002</v>
           </cell>
         </row>
         <row r="1201">
           <cell r="C1201">
-            <v>15303005</v>
+            <v>15206003</v>
           </cell>
         </row>
         <row r="1202">
           <cell r="C1202">
-            <v>15303006</v>
+            <v>15207001</v>
           </cell>
         </row>
         <row r="1203">
           <cell r="C1203">
-            <v>15304001</v>
+            <v>15207002</v>
           </cell>
         </row>
         <row r="1204">
           <cell r="C1204">
-            <v>15304002</v>
+            <v>15207003</v>
           </cell>
         </row>
         <row r="1205">
           <cell r="C1205">
-            <v>15304003</v>
+            <v>15208001</v>
           </cell>
         </row>
         <row r="1206">
           <cell r="C1206">
-            <v>15304004</v>
+            <v>15208002</v>
           </cell>
         </row>
         <row r="1207">
           <cell r="C1207">
-            <v>15304005</v>
+            <v>15208003</v>
           </cell>
         </row>
         <row r="1208">
           <cell r="C1208">
-            <v>15304006</v>
+            <v>15209001</v>
           </cell>
         </row>
         <row r="1209">
           <cell r="C1209">
-            <v>15305001</v>
+            <v>15209002</v>
           </cell>
         </row>
         <row r="1210">
           <cell r="C1210">
-            <v>15305002</v>
+            <v>15210001</v>
           </cell>
         </row>
         <row r="1211">
           <cell r="C1211">
-            <v>15305003</v>
+            <v>15210002</v>
           </cell>
         </row>
         <row r="1212">
           <cell r="C1212">
-            <v>15305004</v>
+            <v>15210003</v>
           </cell>
         </row>
         <row r="1213">
           <cell r="C1213">
-            <v>15305005</v>
+            <v>15210004</v>
           </cell>
         </row>
         <row r="1214">
           <cell r="C1214">
-            <v>15305006</v>
+            <v>15210011</v>
           </cell>
         </row>
         <row r="1215">
           <cell r="C1215">
-            <v>15306001</v>
+            <v>15210012</v>
           </cell>
         </row>
         <row r="1216">
           <cell r="C1216">
-            <v>15306002</v>
+            <v>15210101</v>
           </cell>
         </row>
         <row r="1217">
           <cell r="C1217">
-            <v>15306003</v>
+            <v>15210102</v>
           </cell>
         </row>
         <row r="1218">
           <cell r="C1218">
-            <v>15307001</v>
+            <v>15210103</v>
           </cell>
         </row>
         <row r="1219">
           <cell r="C1219">
-            <v>15307002</v>
+            <v>15210104</v>
           </cell>
         </row>
         <row r="1220">
           <cell r="C1220">
-            <v>15308001</v>
+            <v>15210111</v>
           </cell>
         </row>
         <row r="1221">
           <cell r="C1221">
-            <v>15308002</v>
+            <v>15210112</v>
           </cell>
         </row>
         <row r="1222">
           <cell r="C1222">
-            <v>15308003</v>
+            <v>15210201</v>
           </cell>
         </row>
         <row r="1223">
           <cell r="C1223">
-            <v>15308004</v>
+            <v>15210202</v>
           </cell>
         </row>
         <row r="1224">
           <cell r="C1224">
-            <v>15309001</v>
+            <v>15210211</v>
           </cell>
         </row>
         <row r="1225">
           <cell r="C1225">
-            <v>15309002</v>
+            <v>15211001</v>
           </cell>
         </row>
         <row r="1226">
           <cell r="C1226">
-            <v>15309003</v>
+            <v>15211002</v>
           </cell>
         </row>
         <row r="1227">
           <cell r="C1227">
-            <v>15310001</v>
+            <v>15211003</v>
           </cell>
         </row>
         <row r="1228">
           <cell r="C1228">
-            <v>15310002</v>
+            <v>15211004</v>
           </cell>
         </row>
         <row r="1229">
           <cell r="C1229">
-            <v>15310003</v>
+            <v>15211005</v>
           </cell>
         </row>
         <row r="1230">
           <cell r="C1230">
-            <v>15310004</v>
+            <v>15211006</v>
           </cell>
         </row>
         <row r="1231">
           <cell r="C1231">
-            <v>15310011</v>
+            <v>15211011</v>
           </cell>
         </row>
         <row r="1232">
           <cell r="C1232">
-            <v>15310012</v>
+            <v>15211012</v>
           </cell>
         </row>
         <row r="1233">
           <cell r="C1233">
-            <v>15310101</v>
+            <v>15211013</v>
           </cell>
         </row>
         <row r="1234">
           <cell r="C1234">
-            <v>15310102</v>
+            <v>15301001</v>
           </cell>
         </row>
         <row r="1235">
           <cell r="C1235">
-            <v>15310103</v>
+            <v>15301002</v>
           </cell>
         </row>
         <row r="1236">
           <cell r="C1236">
-            <v>15310104</v>
+            <v>15301003</v>
           </cell>
         </row>
         <row r="1237">
           <cell r="C1237">
-            <v>15310111</v>
+            <v>15301004</v>
           </cell>
         </row>
         <row r="1238">
           <cell r="C1238">
-            <v>15310112</v>
+            <v>15301005</v>
           </cell>
         </row>
         <row r="1239">
           <cell r="C1239">
-            <v>15310201</v>
+            <v>15301006</v>
           </cell>
         </row>
         <row r="1240">
           <cell r="C1240">
-            <v>15310202</v>
+            <v>15302001</v>
           </cell>
         </row>
         <row r="1241">
           <cell r="C1241">
-            <v>15310211</v>
+            <v>15302002</v>
           </cell>
         </row>
         <row r="1242">
           <cell r="C1242">
-            <v>15311001</v>
+            <v>15302003</v>
           </cell>
         </row>
         <row r="1243">
           <cell r="C1243">
-            <v>15311002</v>
+            <v>15302004</v>
           </cell>
         </row>
         <row r="1244">
           <cell r="C1244">
-            <v>15311003</v>
+            <v>15302005</v>
           </cell>
         </row>
         <row r="1245">
           <cell r="C1245">
-            <v>15311004</v>
+            <v>15302006</v>
           </cell>
         </row>
         <row r="1246">
           <cell r="C1246">
-            <v>15311005</v>
+            <v>15302007</v>
           </cell>
         </row>
         <row r="1247">
           <cell r="C1247">
-            <v>15311006</v>
+            <v>15303001</v>
           </cell>
         </row>
         <row r="1248">
           <cell r="C1248">
-            <v>15311011</v>
+            <v>15303002</v>
           </cell>
         </row>
         <row r="1249">
           <cell r="C1249">
-            <v>15311012</v>
+            <v>15303003</v>
           </cell>
         </row>
         <row r="1250">
           <cell r="C1250">
-            <v>15311013</v>
+            <v>15303004</v>
           </cell>
         </row>
         <row r="1251">
           <cell r="C1251">
-            <v>15401001</v>
+            <v>15303005</v>
           </cell>
         </row>
         <row r="1252">
           <cell r="C1252">
-            <v>15401002</v>
+            <v>15303006</v>
           </cell>
         </row>
         <row r="1253">
           <cell r="C1253">
-            <v>15401003</v>
+            <v>15304001</v>
           </cell>
         </row>
         <row r="1254">
           <cell r="C1254">
-            <v>15401004</v>
+            <v>15304002</v>
           </cell>
         </row>
         <row r="1255">
           <cell r="C1255">
-            <v>15401005</v>
+            <v>15304003</v>
           </cell>
         </row>
         <row r="1256">
           <cell r="C1256">
-            <v>15401006</v>
+            <v>15304004</v>
           </cell>
         </row>
         <row r="1257">
           <cell r="C1257">
-            <v>15401007</v>
+            <v>15304005</v>
           </cell>
         </row>
         <row r="1258">
           <cell r="C1258">
-            <v>15402001</v>
+            <v>15304006</v>
           </cell>
         </row>
         <row r="1259">
           <cell r="C1259">
-            <v>15402002</v>
+            <v>15305001</v>
           </cell>
         </row>
         <row r="1260">
           <cell r="C1260">
-            <v>15402003</v>
+            <v>15305002</v>
           </cell>
         </row>
         <row r="1261">
           <cell r="C1261">
-            <v>15402004</v>
+            <v>15305003</v>
           </cell>
         </row>
         <row r="1262">
           <cell r="C1262">
-            <v>15402005</v>
+            <v>15305004</v>
           </cell>
         </row>
         <row r="1263">
           <cell r="C1263">
-            <v>15402006</v>
+            <v>15305005</v>
           </cell>
         </row>
         <row r="1264">
           <cell r="C1264">
-            <v>15403001</v>
+            <v>15305006</v>
           </cell>
         </row>
         <row r="1265">
           <cell r="C1265">
-            <v>15403002</v>
+            <v>15306001</v>
           </cell>
         </row>
         <row r="1266">
           <cell r="C1266">
-            <v>15403003</v>
+            <v>15306002</v>
           </cell>
         </row>
         <row r="1267">
           <cell r="C1267">
-            <v>15403004</v>
+            <v>15306003</v>
           </cell>
         </row>
         <row r="1268">
           <cell r="C1268">
-            <v>15403005</v>
+            <v>15307001</v>
           </cell>
         </row>
         <row r="1269">
           <cell r="C1269">
-            <v>15403006</v>
+            <v>15307002</v>
           </cell>
         </row>
         <row r="1270">
           <cell r="C1270">
-            <v>15404001</v>
+            <v>15308001</v>
           </cell>
         </row>
         <row r="1271">
           <cell r="C1271">
-            <v>15404002</v>
+            <v>15308002</v>
           </cell>
         </row>
         <row r="1272">
           <cell r="C1272">
-            <v>15404003</v>
+            <v>15308003</v>
           </cell>
         </row>
         <row r="1273">
           <cell r="C1273">
-            <v>15404004</v>
+            <v>15308004</v>
           </cell>
         </row>
         <row r="1274">
           <cell r="C1274">
-            <v>15404005</v>
+            <v>15309001</v>
           </cell>
         </row>
         <row r="1275">
           <cell r="C1275">
-            <v>15404006</v>
+            <v>15309002</v>
           </cell>
         </row>
         <row r="1276">
           <cell r="C1276">
-            <v>15405001</v>
+            <v>15309003</v>
           </cell>
         </row>
         <row r="1277">
           <cell r="C1277">
-            <v>15405002</v>
+            <v>15310001</v>
           </cell>
         </row>
         <row r="1278">
           <cell r="C1278">
-            <v>15405003</v>
+            <v>15310002</v>
           </cell>
         </row>
         <row r="1279">
           <cell r="C1279">
-            <v>15405004</v>
+            <v>15310003</v>
           </cell>
         </row>
         <row r="1280">
           <cell r="C1280">
-            <v>15405005</v>
+            <v>15310004</v>
           </cell>
         </row>
         <row r="1281">
           <cell r="C1281">
-            <v>15405006</v>
+            <v>15310011</v>
           </cell>
         </row>
         <row r="1282">
           <cell r="C1282">
-            <v>15406001</v>
+            <v>15310012</v>
           </cell>
         </row>
         <row r="1283">
           <cell r="C1283">
-            <v>15406002</v>
+            <v>15310101</v>
           </cell>
         </row>
         <row r="1284">
           <cell r="C1284">
-            <v>15406003</v>
+            <v>15310102</v>
           </cell>
         </row>
         <row r="1285">
           <cell r="C1285">
-            <v>15407001</v>
+            <v>15310103</v>
           </cell>
         </row>
         <row r="1286">
           <cell r="C1286">
-            <v>15407002</v>
+            <v>15310104</v>
           </cell>
         </row>
         <row r="1287">
           <cell r="C1287">
-            <v>15407003</v>
+            <v>15310111</v>
           </cell>
         </row>
         <row r="1288">
           <cell r="C1288">
-            <v>15408001</v>
+            <v>15310112</v>
           </cell>
         </row>
         <row r="1289">
           <cell r="C1289">
-            <v>15408002</v>
+            <v>15310201</v>
           </cell>
         </row>
         <row r="1290">
           <cell r="C1290">
-            <v>15408003</v>
+            <v>15310202</v>
           </cell>
         </row>
         <row r="1291">
           <cell r="C1291">
-            <v>15409001</v>
+            <v>15310211</v>
           </cell>
         </row>
         <row r="1292">
           <cell r="C1292">
-            <v>15409002</v>
+            <v>15311001</v>
           </cell>
         </row>
         <row r="1293">
           <cell r="C1293">
-            <v>15410001</v>
+            <v>15311002</v>
           </cell>
         </row>
         <row r="1294">
           <cell r="C1294">
-            <v>15410002</v>
+            <v>15311003</v>
           </cell>
         </row>
         <row r="1295">
           <cell r="C1295">
-            <v>15410003</v>
+            <v>15311004</v>
           </cell>
         </row>
         <row r="1296">
           <cell r="C1296">
-            <v>15410004</v>
+            <v>15311005</v>
           </cell>
         </row>
         <row r="1297">
           <cell r="C1297">
-            <v>15410011</v>
+            <v>15311006</v>
           </cell>
         </row>
         <row r="1298">
           <cell r="C1298">
-            <v>15410012</v>
+            <v>15311011</v>
           </cell>
         </row>
         <row r="1299">
           <cell r="C1299">
-            <v>15410101</v>
+            <v>15311012</v>
           </cell>
         </row>
         <row r="1300">
           <cell r="C1300">
-            <v>15410102</v>
+            <v>15311013</v>
           </cell>
         </row>
         <row r="1301">
           <cell r="C1301">
-            <v>15410103</v>
+            <v>15401001</v>
           </cell>
         </row>
         <row r="1302">
           <cell r="C1302">
-            <v>15410104</v>
+            <v>15401002</v>
           </cell>
         </row>
         <row r="1303">
           <cell r="C1303">
-            <v>15410111</v>
+            <v>15401003</v>
           </cell>
         </row>
         <row r="1304">
           <cell r="C1304">
-            <v>15410112</v>
+            <v>15401004</v>
           </cell>
         </row>
         <row r="1305">
           <cell r="C1305">
-            <v>15410201</v>
+            <v>15401005</v>
           </cell>
         </row>
         <row r="1306">
           <cell r="C1306">
-            <v>15410202</v>
+            <v>15401006</v>
           </cell>
         </row>
         <row r="1307">
           <cell r="C1307">
-            <v>15410211</v>
+            <v>15401007</v>
           </cell>
         </row>
         <row r="1308">
           <cell r="C1308">
-            <v>15411001</v>
+            <v>15402001</v>
           </cell>
         </row>
         <row r="1309">
           <cell r="C1309">
-            <v>15411002</v>
+            <v>15402002</v>
           </cell>
         </row>
         <row r="1310">
           <cell r="C1310">
-            <v>15411003</v>
+            <v>15402003</v>
           </cell>
         </row>
         <row r="1311">
           <cell r="C1311">
-            <v>15411004</v>
+            <v>15402004</v>
           </cell>
         </row>
         <row r="1312">
           <cell r="C1312">
-            <v>15411005</v>
+            <v>15402005</v>
           </cell>
         </row>
         <row r="1313">
           <cell r="C1313">
-            <v>15411006</v>
+            <v>15402006</v>
           </cell>
         </row>
         <row r="1314">
           <cell r="C1314">
-            <v>15411011</v>
+            <v>15403001</v>
           </cell>
         </row>
         <row r="1315">
           <cell r="C1315">
-            <v>15411012</v>
+            <v>15403002</v>
           </cell>
         </row>
         <row r="1316">
           <cell r="C1316">
-            <v>15411013</v>
+            <v>15403003</v>
           </cell>
         </row>
         <row r="1317">
           <cell r="C1317">
-            <v>15501001</v>
+            <v>15403004</v>
           </cell>
         </row>
         <row r="1318">
           <cell r="C1318">
-            <v>15501002</v>
+            <v>15403005</v>
           </cell>
         </row>
         <row r="1319">
           <cell r="C1319">
-            <v>15501003</v>
+            <v>15403006</v>
           </cell>
         </row>
         <row r="1320">
           <cell r="C1320">
-            <v>15501004</v>
+            <v>15404001</v>
           </cell>
         </row>
         <row r="1321">
           <cell r="C1321">
-            <v>15501005</v>
+            <v>15404002</v>
           </cell>
         </row>
         <row r="1322">
           <cell r="C1322">
-            <v>15501006</v>
+            <v>15404003</v>
           </cell>
         </row>
         <row r="1323">
           <cell r="C1323">
-            <v>15502001</v>
+            <v>15404004</v>
           </cell>
         </row>
         <row r="1324">
           <cell r="C1324">
-            <v>15502002</v>
+            <v>15404005</v>
           </cell>
         </row>
         <row r="1325">
           <cell r="C1325">
-            <v>15502003</v>
+            <v>15404006</v>
           </cell>
         </row>
         <row r="1326">
           <cell r="C1326">
-            <v>15502004</v>
+            <v>15405001</v>
           </cell>
         </row>
         <row r="1327">
           <cell r="C1327">
-            <v>15502005</v>
+            <v>15405002</v>
           </cell>
         </row>
         <row r="1328">
           <cell r="C1328">
-            <v>15502006</v>
+            <v>15405003</v>
           </cell>
         </row>
         <row r="1329">
           <cell r="C1329">
-            <v>15503001</v>
+            <v>15405004</v>
           </cell>
         </row>
         <row r="1330">
           <cell r="C1330">
-            <v>15503002</v>
+            <v>15405005</v>
           </cell>
         </row>
         <row r="1331">
           <cell r="C1331">
-            <v>15503003</v>
+            <v>15405006</v>
           </cell>
         </row>
         <row r="1332">
           <cell r="C1332">
-            <v>15503004</v>
+            <v>15406001</v>
           </cell>
         </row>
         <row r="1333">
           <cell r="C1333">
-            <v>15503005</v>
+            <v>15406002</v>
           </cell>
         </row>
       </sheetData>
@@ -37024,7 +37045,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>2981</v>
@@ -37042,7 +37063,7 @@
         <v>2</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="O25" s="3" t="s">
         <v>2982</v>
@@ -37059,7 +37080,7 @@
         <v>3</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>2983</v>
@@ -37145,10 +37166,10 @@
         <v>1</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>3045</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" ht="20.100000000000001" customHeight="1">
+        <v>3044</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" ht="20.100000000000001" customHeight="1">
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
       <c r="D33" s="13"/>
@@ -37160,10 +37181,10 @@
         <v>2</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>3046</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" ht="20.100000000000001" customHeight="1">
+        <v>3045</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" ht="20.100000000000001" customHeight="1">
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
       <c r="D34" s="13"/>
@@ -37175,10 +37196,10 @@
         <v>3</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>3047</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12" ht="20.100000000000001" customHeight="1">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" ht="20.100000000000001" customHeight="1">
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
       <c r="D35" s="13"/>
@@ -37187,7 +37208,7 @@
       <c r="H35" s="1"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="36" spans="2:12" ht="20.100000000000001" customHeight="1">
+    <row r="36" spans="2:15" ht="20.100000000000001" customHeight="1">
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -37202,7 +37223,7 @@
         <v>3040</v>
       </c>
     </row>
-    <row r="37" spans="2:12" ht="20.100000000000001" customHeight="1">
+    <row r="37" spans="2:15" ht="20.100000000000001" customHeight="1">
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -37214,10 +37235,10 @@
         <v>2</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>3041</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" ht="20.100000000000001" customHeight="1">
+        <v>3066</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" ht="20.100000000000001" customHeight="1">
       <c r="G38" s="1" t="s">
         <v>3025</v>
       </c>
@@ -37225,14 +37246,14 @@
         <v>3</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>3048</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+        <v>3067</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B39" s="29"/>
       <c r="C39" s="29"/>
     </row>
-    <row r="40" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="40" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
       <c r="G40" s="1" t="s">
@@ -37242,10 +37263,10 @@
         <v>1</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>3049</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+        <v>3047</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B41" s="29"/>
       <c r="C41" s="29"/>
       <c r="G41" s="1" t="s">
@@ -37255,10 +37276,10 @@
         <v>2</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>3050</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+        <v>3068</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B42" s="29"/>
       <c r="C42" s="29"/>
       <c r="G42" s="1" t="s">
@@ -37268,14 +37289,14 @@
         <v>3</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>3051</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
     </row>
-    <row r="44" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="44" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B44" s="29"/>
       <c r="C44" s="29"/>
       <c r="G44" s="1" t="s">
@@ -37290,8 +37311,14 @@
       <c r="L44" s="3" t="s">
         <v>3027</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="N44" s="1">
+        <v>50000101</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B45" s="29"/>
       <c r="C45" s="29"/>
       <c r="G45" s="1" t="s">
@@ -37303,8 +37330,14 @@
       <c r="I45" s="3" t="s">
         <v>3029</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="N45" s="1">
+        <v>50000102</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>3071</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
       <c r="G46" s="1" t="s">
@@ -37316,16 +37349,28 @@
       <c r="I46" s="3" t="s">
         <v>3030</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="N46" s="1">
+        <v>50000103</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>3072</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B47" s="29"/>
       <c r="C47" s="29"/>
-    </row>
-    <row r="48" spans="2:12" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="N47" s="1">
+        <v>50000201</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>3073</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B48" s="29"/>
       <c r="C48" s="29"/>
       <c r="G48" s="1" t="s">
-        <v>3069</v>
+        <v>3065</v>
       </c>
       <c r="H48" s="1">
         <v>1</v>
@@ -37333,12 +37378,18 @@
       <c r="I48" s="3" t="s">
         <v>3032</v>
       </c>
-    </row>
-    <row r="49" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="N48" s="1">
+        <v>50000202</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>3073</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B49" s="29"/>
       <c r="C49" s="29"/>
       <c r="G49" s="1" t="s">
-        <v>3069</v>
+        <v>3065</v>
       </c>
       <c r="H49" s="1">
         <v>2</v>
@@ -37346,12 +37397,18 @@
       <c r="I49" s="3" t="s">
         <v>3033</v>
       </c>
-    </row>
-    <row r="50" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="N49" s="1">
+        <v>50000301</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B50" s="29"/>
       <c r="C50" s="29"/>
       <c r="G50" s="1" t="s">
-        <v>3069</v>
+        <v>3065</v>
       </c>
       <c r="H50" s="1">
         <v>3</v>
@@ -37359,57 +37416,93 @@
       <c r="I50" s="3" t="s">
         <v>3034</v>
       </c>
-    </row>
-    <row r="51" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="N50" s="1">
+        <v>50000302</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B51" s="29"/>
       <c r="C51" s="29"/>
       <c r="H51" s="1"/>
-    </row>
-    <row r="52" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="N51" s="1">
+        <v>50000401</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>3073</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
       <c r="G52" s="1" t="s">
-        <v>3068</v>
+        <v>3064</v>
       </c>
       <c r="H52" s="1">
         <v>1</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>3053</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+        <v>3049</v>
+      </c>
+      <c r="N52" s="1">
+        <v>50000402</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>3073</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B53" s="29"/>
       <c r="C53" s="29"/>
       <c r="G53" s="1" t="s">
-        <v>3068</v>
+        <v>3064</v>
       </c>
       <c r="H53" s="1">
         <v>2</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>3054</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+        <v>3050</v>
+      </c>
+      <c r="N53" s="1">
+        <v>50000501</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B54" s="29"/>
       <c r="C54" s="29"/>
       <c r="G54" s="1" t="s">
-        <v>3068</v>
+        <v>3064</v>
       </c>
       <c r="H54" s="1">
         <v>3</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>3055</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+        <v>3051</v>
+      </c>
+      <c r="N54" s="1">
+        <v>50000502</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>3071</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B55" s="29"/>
       <c r="C55" s="29"/>
       <c r="H55" s="1"/>
-    </row>
-    <row r="56" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="N55" s="1">
+        <v>50000503</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>3072</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B56" s="29"/>
       <c r="C56" s="29"/>
       <c r="G56" s="1" t="s">
@@ -37422,7 +37515,7 @@
         <v>3036</v>
       </c>
     </row>
-    <row r="57" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="57" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B57" s="29"/>
       <c r="C57" s="29"/>
       <c r="G57" s="1" t="s">
@@ -37435,7 +37528,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="58" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="58" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B58" s="29"/>
       <c r="C58" s="29"/>
       <c r="G58" s="1" t="s">
@@ -37448,27 +37541,27 @@
         <v>3038</v>
       </c>
     </row>
-    <row r="59" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="59" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B59" s="29"/>
       <c r="C59" s="29"/>
     </row>
-    <row r="60" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="60" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B60" s="29"/>
       <c r="C60" s="29"/>
     </row>
-    <row r="61" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="61" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B61" s="29"/>
       <c r="C61" s="29"/>
     </row>
-    <row r="62" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="62" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B62" s="29"/>
       <c r="C62" s="29"/>
     </row>
-    <row r="63" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="63" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B63" s="29"/>
       <c r="C63" s="29"/>
     </row>
-    <row r="64" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="64" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B64" s="29"/>
       <c r="C64" s="29"/>
       <c r="G64" s="1" t="s">
@@ -37533,7 +37626,7 @@
         <v>1</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>3056</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="70" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37546,7 +37639,7 @@
         <v>2</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>3057</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="71" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37559,7 +37652,7 @@
         <v>3</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>3058</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="72" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37579,7 +37672,7 @@
         <v>1</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>3059</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="74" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37592,7 +37685,7 @@
         <v>2</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>3060</v>
+        <v>3056</v>
       </c>
     </row>
     <row r="75" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37605,7 +37698,7 @@
         <v>3</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>3061</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="76" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37625,7 +37718,7 @@
         <v>1</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>3062</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="78" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37638,7 +37731,7 @@
         <v>2</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>3063</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="79" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37651,7 +37744,7 @@
         <v>3</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>3064</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="80" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37760,7 +37853,7 @@
         <v>1</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>3065</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="90" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37773,7 +37866,7 @@
         <v>2</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>3066</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="91" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37786,7 +37879,7 @@
         <v>3</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="92" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37799,7 +37892,7 @@
       <c r="B93" s="29"/>
       <c r="C93" s="29"/>
       <c r="G93" s="29" t="s">
-        <v>3052</v>
+        <v>3048</v>
       </c>
       <c r="H93" s="29"/>
     </row>
@@ -68123,13 +68216,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="CP23:CP25"/>
-    <mergeCell ref="CP26:CP28"/>
-    <mergeCell ref="CP8:CP10"/>
-    <mergeCell ref="CP11:CP13"/>
-    <mergeCell ref="CP14:CP16"/>
-    <mergeCell ref="CP17:CP19"/>
-    <mergeCell ref="CP20:CP22"/>
     <mergeCell ref="K18:K20"/>
     <mergeCell ref="K21:K23"/>
     <mergeCell ref="AX4:AX6"/>
@@ -68144,6 +68230,13 @@
     <mergeCell ref="K9:K11"/>
     <mergeCell ref="K12:K14"/>
     <mergeCell ref="K15:K17"/>
+    <mergeCell ref="CP23:CP25"/>
+    <mergeCell ref="CP26:CP28"/>
+    <mergeCell ref="CP8:CP10"/>
+    <mergeCell ref="CP11:CP13"/>
+    <mergeCell ref="CP14:CP16"/>
+    <mergeCell ref="CP17:CP19"/>
+    <mergeCell ref="CP20:CP22"/>
   </mergeCells>
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/WeiJingShuZhi/属性表.xlsx
+++ b/WeiJingShuZhi/属性表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\WeiJingShuZhi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E027E5-C51F-4F30-BBCC-8960D2729CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7D775A-F101-40C0-B7CA-A568130A7C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="10" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9644,30 +9644,6 @@
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
   <si>
-    <t>攻击时有概率触发地裂,造成100%伤害+500点固定伤害。</t>
-    <phoneticPr fontId="35" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时有概率触发地裂,造成150%伤害+1000点固定伤害。</t>
-    <phoneticPr fontId="35" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击时有概率触发地裂,造成200%伤害+1500点固定伤害。</t>
-    <phoneticPr fontId="35" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放技时有一定概率触发烈焰,造成100%伤害+500点固定伤害。</t>
-    <phoneticPr fontId="35" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放技时有一定概率触发烈焰造成150%伤害+1000点固定伤害。</t>
-    <phoneticPr fontId="35" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放技时有一定概率触发烈焰,造成200%伤害+1500点固定伤害。</t>
-    <phoneticPr fontId="35" type="noConversion"/>
-  </si>
-  <si>
     <t>受到攻击有一定概率在施法者目标处触发爆炸，造成100%伤害+500点固定伤害</t>
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
@@ -9773,6 +9749,30 @@
   </si>
   <si>
     <t>猎人普通攻击</t>
+  </si>
+  <si>
+    <t>攻击时有概率触发御剑一击造成150%伤害+1000点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击时有概率触发御剑一击造成100%伤害+500点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击时有概率触发御剑一击造成200%伤害+1500点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放技时有一定概率触发御剑一击,造成100%伤害+500点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放技时有一定概率触发御剑一击造成150%伤害+1000点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>释放技时有一定概率触发御剑一击,造成200%伤害+1500点固定伤害。</t>
+    <phoneticPr fontId="35" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -37045,7 +37045,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>3041</v>
+        <v>3070</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>2981</v>
@@ -37063,7 +37063,7 @@
         <v>2</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>3042</v>
+        <v>3069</v>
       </c>
       <c r="O25" s="3" t="s">
         <v>2982</v>
@@ -37080,7 +37080,7 @@
         <v>3</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>3043</v>
+        <v>3071</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>2983</v>
@@ -37166,7 +37166,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>3044</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="33" spans="2:15" ht="20.100000000000001" customHeight="1">
@@ -37181,7 +37181,7 @@
         <v>2</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>3045</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="34" spans="2:15" ht="20.100000000000001" customHeight="1">
@@ -37196,7 +37196,7 @@
         <v>3</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>3046</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="35" spans="2:15" ht="20.100000000000001" customHeight="1">
@@ -37235,7 +37235,7 @@
         <v>2</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>3066</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="38" spans="2:15" ht="20.100000000000001" customHeight="1">
@@ -37246,7 +37246,7 @@
         <v>3</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>3067</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="39" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37263,7 +37263,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>3047</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="41" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37276,7 +37276,7 @@
         <v>2</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>3068</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="42" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37289,7 +37289,7 @@
         <v>3</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>3069</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="43" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37315,7 +37315,7 @@
         <v>50000101</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>3070</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="45" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37334,7 +37334,7 @@
         <v>50000102</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>3071</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="46" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37353,7 +37353,7 @@
         <v>50000103</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>3072</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="47" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37363,14 +37363,14 @@
         <v>50000201</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>3073</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="48" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B48" s="29"/>
       <c r="C48" s="29"/>
       <c r="G48" s="1" t="s">
-        <v>3065</v>
+        <v>3059</v>
       </c>
       <c r="H48" s="1">
         <v>1</v>
@@ -37382,14 +37382,14 @@
         <v>50000202</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>3073</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="49" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B49" s="29"/>
       <c r="C49" s="29"/>
       <c r="G49" s="1" t="s">
-        <v>3065</v>
+        <v>3059</v>
       </c>
       <c r="H49" s="1">
         <v>2</v>
@@ -37401,14 +37401,14 @@
         <v>50000301</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>3074</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="50" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B50" s="29"/>
       <c r="C50" s="29"/>
       <c r="G50" s="1" t="s">
-        <v>3065</v>
+        <v>3059</v>
       </c>
       <c r="H50" s="1">
         <v>3</v>
@@ -37420,7 +37420,7 @@
         <v>50000302</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>3074</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="51" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37431,64 +37431,64 @@
         <v>50000401</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>3073</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="52" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
       <c r="G52" s="1" t="s">
-        <v>3064</v>
+        <v>3058</v>
       </c>
       <c r="H52" s="1">
         <v>1</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>3049</v>
+        <v>3043</v>
       </c>
       <c r="N52" s="1">
         <v>50000402</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>3073</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="53" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B53" s="29"/>
       <c r="C53" s="29"/>
       <c r="G53" s="1" t="s">
-        <v>3064</v>
+        <v>3058</v>
       </c>
       <c r="H53" s="1">
         <v>2</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>3050</v>
+        <v>3044</v>
       </c>
       <c r="N53" s="1">
         <v>50000501</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>3070</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="54" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B54" s="29"/>
       <c r="C54" s="29"/>
       <c r="G54" s="1" t="s">
-        <v>3064</v>
+        <v>3058</v>
       </c>
       <c r="H54" s="1">
         <v>3</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>3051</v>
+        <v>3045</v>
       </c>
       <c r="N54" s="1">
         <v>50000502</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>3071</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="55" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37499,7 +37499,7 @@
         <v>50000503</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>3072</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="56" spans="2:15" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37626,7 +37626,7 @@
         <v>1</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>3052</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="70" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37639,7 +37639,7 @@
         <v>2</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>3053</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="71" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37652,7 +37652,7 @@
         <v>3</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>3054</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="72" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37672,7 +37672,7 @@
         <v>1</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>3055</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="74" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37685,7 +37685,7 @@
         <v>2</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>3056</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="75" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37698,7 +37698,7 @@
         <v>3</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>3057</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="76" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37718,7 +37718,7 @@
         <v>1</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>3058</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="78" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37731,7 +37731,7 @@
         <v>2</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>3059</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="79" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37744,7 +37744,7 @@
         <v>3</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>3060</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="80" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37853,7 +37853,7 @@
         <v>1</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>3061</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="90" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37866,7 +37866,7 @@
         <v>2</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>3062</v>
+        <v>3056</v>
       </c>
     </row>
     <row r="91" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37879,7 +37879,7 @@
         <v>3</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>3063</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="92" spans="2:9" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -37892,7 +37892,7 @@
       <c r="B93" s="29"/>
       <c r="C93" s="29"/>
       <c r="G93" s="29" t="s">
-        <v>3048</v>
+        <v>3042</v>
       </c>
       <c r="H93" s="29"/>
     </row>

--- a/WeiJingShuZhi/属性表.xlsx
+++ b/WeiJingShuZhi/属性表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\WeiJingShuZhi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7D775A-F101-40C0-B7CA-A568130A7C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E840A4E-FF92-4E67-9313-E9BB374E2746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="10" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5479" uniqueCount="3075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5540" uniqueCount="3120">
   <si>
     <t>人物属性</t>
   </si>
@@ -9773,6 +9773,171 @@
   <si>
     <t>释放技时有一定概率触发御剑一击,造成200%伤害+1500点固定伤害。</t>
     <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>500万</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000万</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000万</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000万</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000万</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>递增值</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>总值</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>值</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>预计每天获得材料</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>道具转换材料</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接材料</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>总消耗</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>天数</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币(单位:万)</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>力度伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>300万</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>100203;150</t>
+  </si>
+  <si>
+    <t>生命</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>101003;4600</t>
+  </si>
+  <si>
+    <t>100603;15</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理防御+15</t>
+  </si>
+  <si>
+    <t>100803;21</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法防御+21</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>1号</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>开启栏位</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack +10; Physical Defense +10</t>
+  </si>
+  <si>
+    <t>Attack +25; Physical Defense +25</t>
+  </si>
+  <si>
+    <t>Attack +40; Physical Defense +40</t>
+  </si>
+  <si>
+    <t>Attack +60; Physical Defense +60</t>
+  </si>
+  <si>
+    <t>Attack +90; Physical Defense +90</t>
+  </si>
+  <si>
+    <t>Attack +120; Physical Defense +120</t>
+  </si>
+  <si>
+    <t>Attack +150; Physical Defense +150</t>
+  </si>
+  <si>
+    <t>Attack +180; Physical Defense +180</t>
+  </si>
+  <si>
+    <t>Attack +210; Physical Defense +210</t>
+  </si>
+  <si>
+    <t>Attack +240; Physical Defense +240</t>
+  </si>
+  <si>
+    <t>魔能之尘</t>
+  </si>
+  <si>
+    <t>魔能之钥</t>
   </si>
 </sst>
 </file>
@@ -10053,7 +10218,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10180,8 +10345,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14847254860072634"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -10286,12 +10457,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </left>
+      <right style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39844965971861934"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39844965971861934"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </left>
+      <right style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39844965971861934"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10626,6 +10827,18 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -36579,7 +36792,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91ED6A3E-D209-48A9-B20C-34EAD5F589C0}">
-  <dimension ref="B1:Q100"/>
+  <dimension ref="B1:AT100"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="3" width="9" style="22"/>
@@ -36587,18 +36800,33 @@
     <col min="8" max="8" width="9" style="22"/>
     <col min="9" max="9" width="70.375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.625" customWidth="1"/>
+    <col min="12" max="12" width="16.5" customWidth="1"/>
     <col min="14" max="14" width="12.625" customWidth="1"/>
     <col min="15" max="15" width="22.5" customWidth="1"/>
-    <col min="17" max="17" width="19.625" customWidth="1"/>
+    <col min="18" max="18" width="22.375" customWidth="1"/>
+    <col min="24" max="24" width="11.75" customWidth="1"/>
+    <col min="35" max="35" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="29.375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="31.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="1" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="F2" s="67"/>
@@ -36607,8 +36835,17 @@
       <c r="N2" s="3" t="s">
         <v>2980</v>
       </c>
-    </row>
-    <row r="3" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+    </row>
+    <row r="3" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B3" s="1" t="s">
         <v>2957</v>
       </c>
@@ -36625,17 +36862,23 @@
       <c r="I3" s="3" t="s">
         <v>2950</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>2978</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="1" t="s">
         <v>2979</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>2981</v>
       </c>
-    </row>
-    <row r="4" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="S3" s="1"/>
+      <c r="Y3" s="1" t="s">
+        <v>3083</v>
+      </c>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+    </row>
+    <row r="4" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B4" s="1" t="s">
         <v>2958</v>
       </c>
@@ -36651,8 +36894,18 @@
       <c r="N4" s="3" t="s">
         <v>2982</v>
       </c>
-    </row>
-    <row r="5" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="S4" s="1"/>
+      <c r="Y4" s="1" t="s">
+        <v>3086</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>3084</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>3085</v>
+      </c>
+    </row>
+    <row r="5" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>2960</v>
       </c>
@@ -36668,8 +36921,18 @@
       <c r="N5" s="3" t="s">
         <v>2983</v>
       </c>
-    </row>
-    <row r="6" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="S5" s="1"/>
+      <c r="Y5" s="1">
+        <v>10500</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>1000</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B6" s="1" t="s">
         <v>2959</v>
       </c>
@@ -36679,11 +36942,23 @@
       <c r="F6" s="67"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
+      <c r="K6" s="1" t="s">
+        <v>3097</v>
+      </c>
       <c r="N6" s="3" t="s">
         <v>2984</v>
       </c>
-    </row>
-    <row r="7" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+    </row>
+    <row r="7" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="F7" s="67"/>
@@ -36696,8 +36971,37 @@
       <c r="I7" s="3" t="s">
         <v>2951</v>
       </c>
-    </row>
-    <row r="8" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="O7" s="1" t="s">
+        <v>2996</v>
+      </c>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1" t="s">
+        <v>3084</v>
+      </c>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="F8" s="67"/>
@@ -36714,8 +37018,72 @@
       <c r="P8" s="4" t="s">
         <v>3001</v>
       </c>
-    </row>
-    <row r="9" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="Q8" s="4" t="s">
+        <v>3075</v>
+      </c>
+      <c r="S8" s="1"/>
+      <c r="T8" s="4" t="s">
+        <v>3081</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>3095</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>3094</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>3090</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>3096</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>3082</v>
+      </c>
+      <c r="Z8" s="4" t="s">
+        <v>3088</v>
+      </c>
+      <c r="AA8" s="4" t="s">
+        <v>3087</v>
+      </c>
+      <c r="AB8" s="4" t="s">
+        <v>3085</v>
+      </c>
+      <c r="AC8" s="4" t="s">
+        <v>3085</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>3086</v>
+      </c>
+      <c r="AE8" s="1" t="s">
+        <v>3086</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>3086</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>3089</v>
+      </c>
+      <c r="AI8" s="3" t="s">
+        <v>3106</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>2</v>
+      </c>
+      <c r="AM8" s="3">
+        <v>3</v>
+      </c>
+      <c r="AO8" s="3">
+        <v>4</v>
+      </c>
+      <c r="AQ8" s="3">
+        <v>5</v>
+      </c>
+      <c r="AS8" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="F9" s="67"/>
@@ -36724,10 +37092,10 @@
       <c r="I9" s="3" t="s">
         <v>2975</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="1">
         <v>60</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="1">
         <f>K9*30</f>
         <v>1800</v>
       </c>
@@ -36735,39 +37103,245 @@
         <v>1</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>2697</v>
+        <v>2997</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>2710</v>
       </c>
       <c r="Q9" s="1" t="s">
+        <v>3098</v>
+      </c>
+      <c r="R9" s="1" t="s">
         <v>2997</v>
       </c>
-    </row>
-    <row r="10" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="S9" s="1"/>
+      <c r="T9" s="4">
+        <v>1</v>
+      </c>
+      <c r="U9" s="4">
+        <f>V9/$M$19</f>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="V9" s="4">
+        <f>SUM($W$9:W9)</f>
+        <v>100</v>
+      </c>
+      <c r="W9" s="1">
+        <v>100</v>
+      </c>
+      <c r="X9" s="1">
+        <v>100</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z9" s="1">
+        <f>Y9</f>
+        <v>10</v>
+      </c>
+      <c r="AA9" s="1">
+        <f>Z9*3</f>
+        <v>30</v>
+      </c>
+      <c r="AB9" s="1">
+        <f>Z9</f>
+        <v>10</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="1">
+        <f>Z9*5</f>
+        <v>50</v>
+      </c>
+      <c r="AE9" s="1">
+        <f>Z9*2.5</f>
+        <v>25</v>
+      </c>
+      <c r="AF9" s="1">
+        <f>Z9*2.5</f>
+        <v>25</v>
+      </c>
+      <c r="AG9" s="1">
+        <f>Z9</f>
+        <v>10</v>
+      </c>
+      <c r="AI9" s="3" t="str">
+        <f>"100403;"&amp;Z9&amp;"@100603;"&amp;AB9</f>
+        <v>100403;10@100603;10</v>
+      </c>
+      <c r="AJ9" s="3" t="str">
+        <f>"攻击提升"&amp;Z9&amp;"点;物防提升"&amp;AB9&amp;"点"</f>
+        <v>攻击提升10点;物防提升10点</v>
+      </c>
+      <c r="AK9" s="3" t="str">
+        <f>"100403;"&amp;Z9&amp;"@100803;"&amp;AB9</f>
+        <v>100403;10@100803;10</v>
+      </c>
+      <c r="AL9" s="3" t="str">
+        <f>"攻击提升"&amp;Z9&amp;"点;魔防提升"&amp;AB9&amp;"点"</f>
+        <v>攻击提升10点;魔防提升10点</v>
+      </c>
+      <c r="AM9" s="3" t="str">
+        <f>"100403;"&amp;Z9&amp;"@100203;"&amp;AE9</f>
+        <v>100403;10@100203;25</v>
+      </c>
+      <c r="AN9" s="3" t="str">
+        <f>"攻击提升"&amp;Z9&amp;"点;血量提升"&amp;AE9&amp;"点"</f>
+        <v>攻击提升10点;血量提升25点</v>
+      </c>
+      <c r="AO9" s="3" t="str">
+        <f>"100203;"&amp;AD9</f>
+        <v>100203;50</v>
+      </c>
+      <c r="AP9" s="3" t="str">
+        <f>"血量提升"&amp;AD9&amp;"点"</f>
+        <v>血量提升50点</v>
+      </c>
+      <c r="AQ9" s="3" t="str">
+        <f>"101003;"&amp;Z9&amp;"@100203;"&amp;AE9</f>
+        <v>101003;10@100203;25</v>
+      </c>
+      <c r="AR9" s="3" t="str">
+        <f>"魔法提升"&amp;Z9&amp;"点;血量提升"&amp;AE9&amp;"点"</f>
+        <v>魔法提升10点;血量提升25点</v>
+      </c>
+      <c r="AS9" s="3" t="str">
+        <f>"100203;"&amp;AE9&amp;"@100603;"&amp;AC9&amp;"@100803;"&amp;AC9</f>
+        <v>100203;25@100603;5@100803;5</v>
+      </c>
+      <c r="AT9" s="3" t="str">
+        <f>"血量提升"&amp;AE9&amp;"点;物防提升"&amp;AC9&amp;"点"&amp;"点;魔防提升"&amp;AC9&amp;"点"</f>
+        <v>血量提升25点;物防提升5点点;魔防提升5点</v>
+      </c>
+    </row>
+    <row r="10" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="F10" s="67"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
-      <c r="K10" s="3">
+      <c r="K10" s="1">
         <f>K9*9</f>
         <v>540</v>
       </c>
+      <c r="L10" s="1"/>
       <c r="N10" s="1">
         <v>2</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>2699</v>
+        <v>2998</v>
       </c>
       <c r="P10" s="1">
         <v>300</v>
       </c>
       <c r="Q10" s="1" t="s">
+        <v>3076</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>2998</v>
       </c>
-    </row>
-    <row r="11" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="S10" s="1"/>
+      <c r="T10" s="4">
+        <v>2</v>
+      </c>
+      <c r="U10" s="4">
+        <f t="shared" ref="U10:U18" si="0">V10/$M$19</f>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="V10" s="4">
+        <f>SUM($W$9:W10)</f>
+        <v>250</v>
+      </c>
+      <c r="W10" s="1">
+        <v>150</v>
+      </c>
+      <c r="X10" s="1">
+        <f>X9+100</f>
+        <v>200</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>15</v>
+      </c>
+      <c r="Z10" s="1">
+        <f>SUM($Y$9:Y10)</f>
+        <v>25</v>
+      </c>
+      <c r="AA10" s="1">
+        <f t="shared" ref="AA10:AA18" si="1">Z10*3</f>
+        <v>75</v>
+      </c>
+      <c r="AB10" s="1">
+        <f>Z10</f>
+        <v>25</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>10</v>
+      </c>
+      <c r="AD10" s="1">
+        <f>Z10*5</f>
+        <v>125</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>60</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>60</v>
+      </c>
+      <c r="AG10" s="1">
+        <f t="shared" ref="AG10:AG18" si="2">Z10</f>
+        <v>25</v>
+      </c>
+      <c r="AI10" s="3" t="str">
+        <f t="shared" ref="AI10:AI18" si="3">"100403;"&amp;Z10&amp;"@100603;"&amp;AB10</f>
+        <v>100403;25@100603;25</v>
+      </c>
+      <c r="AJ10" s="3" t="str">
+        <f t="shared" ref="AJ10:AJ18" si="4">"攻击提升"&amp;Z10&amp;"点;物防提升"&amp;AB10&amp;"点"</f>
+        <v>攻击提升25点;物防提升25点</v>
+      </c>
+      <c r="AK10" s="3" t="str">
+        <f t="shared" ref="AK10:AK18" si="5">"100403;"&amp;Z10&amp;"@100803;"&amp;AB10</f>
+        <v>100403;25@100803;25</v>
+      </c>
+      <c r="AL10" s="3" t="str">
+        <f t="shared" ref="AL10:AL18" si="6">"攻击提升"&amp;Z10&amp;"点;魔防提升"&amp;AB10&amp;"点"</f>
+        <v>攻击提升25点;魔防提升25点</v>
+      </c>
+      <c r="AM10" s="3" t="str">
+        <f t="shared" ref="AM10:AM18" si="7">"100403;"&amp;Z10&amp;"@100203;"&amp;AE10</f>
+        <v>100403;25@100203;60</v>
+      </c>
+      <c r="AN10" s="3" t="str">
+        <f t="shared" ref="AN10:AN18" si="8">"攻击提升"&amp;Z10&amp;"点;血量提升"&amp;AE10&amp;"点"</f>
+        <v>攻击提升25点;血量提升60点</v>
+      </c>
+      <c r="AO10" s="3" t="str">
+        <f t="shared" ref="AO10:AO18" si="9">"100203;"&amp;AD10</f>
+        <v>100203;125</v>
+      </c>
+      <c r="AP10" s="3" t="str">
+        <f t="shared" ref="AP10:AP18" si="10">"血量提升"&amp;AD10&amp;"点"</f>
+        <v>血量提升125点</v>
+      </c>
+      <c r="AQ10" s="3" t="str">
+        <f t="shared" ref="AQ10:AQ18" si="11">"101003;"&amp;Z10&amp;"@100203;"&amp;AE10</f>
+        <v>101003;25@100203;60</v>
+      </c>
+      <c r="AR10" s="3" t="str">
+        <f t="shared" ref="AR10:AR18" si="12">"魔法提升"&amp;Z10&amp;"点;血量提升"&amp;AE10&amp;"点"</f>
+        <v>魔法提升25点;血量提升60点</v>
+      </c>
+      <c r="AS10" s="3" t="str">
+        <f t="shared" ref="AS10:AS18" si="13">"100203;"&amp;AE10&amp;"@100603;"&amp;AC10&amp;"@100803;"&amp;AC10</f>
+        <v>100203;60@100603;10@100803;10</v>
+      </c>
+      <c r="AT10" s="3" t="str">
+        <f t="shared" ref="AT10:AT18" si="14">"血量提升"&amp;AE10&amp;"点;物防提升"&amp;AC10&amp;"点"&amp;"点;魔防提升"&amp;AC10&amp;"点"</f>
+        <v>血量提升60点;物防提升10点点;魔防提升10点</v>
+      </c>
+    </row>
+    <row r="11" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="F11" s="67"/>
@@ -36777,16 +37351,120 @@
         <v>3</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>2700</v>
+        <v>2999</v>
       </c>
       <c r="P11" s="1">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Q11" s="1" t="s">
+        <v>3077</v>
+      </c>
+      <c r="R11" s="1" t="s">
         <v>2999</v>
       </c>
-    </row>
-    <row r="12" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="S11" s="1"/>
+      <c r="T11" s="4">
+        <v>3</v>
+      </c>
+      <c r="U11" s="4">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="V11" s="4">
+        <f>SUM($W$9:W11)</f>
+        <v>450</v>
+      </c>
+      <c r="W11" s="1">
+        <v>200</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" ref="W11:X18" si="15">X10+100</f>
+        <v>300</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>15</v>
+      </c>
+      <c r="Z11" s="1">
+        <f>SUM($Y$9:Y11)</f>
+        <v>40</v>
+      </c>
+      <c r="AA11" s="1">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="AB11" s="1">
+        <f>Z11</f>
+        <v>40</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>15</v>
+      </c>
+      <c r="AD11" s="1">
+        <f>Z11*5</f>
+        <v>200</v>
+      </c>
+      <c r="AE11" s="1">
+        <f>Z11*2.5</f>
+        <v>100</v>
+      </c>
+      <c r="AF11" s="1">
+        <f>Z11*2.5</f>
+        <v>100</v>
+      </c>
+      <c r="AG11" s="1">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="AI11" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>100403;40@100603;40</v>
+      </c>
+      <c r="AJ11" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>攻击提升40点;物防提升40点</v>
+      </c>
+      <c r="AK11" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;40@100803;40</v>
+      </c>
+      <c r="AL11" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升40点;魔防提升40点</v>
+      </c>
+      <c r="AM11" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;40@100203;100</v>
+      </c>
+      <c r="AN11" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升40点;血量提升100点</v>
+      </c>
+      <c r="AO11" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100203;200</v>
+      </c>
+      <c r="AP11" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>血量提升200点</v>
+      </c>
+      <c r="AQ11" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>101003;40@100203;100</v>
+      </c>
+      <c r="AR11" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>魔法提升40点;血量提升100点</v>
+      </c>
+      <c r="AS11" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>100203;100@100603;15@100803;15</v>
+      </c>
+      <c r="AT11" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>血量提升100点;物防提升15点点;魔防提升15点</v>
+      </c>
+    </row>
+    <row r="12" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B12" s="1" t="s">
         <v>2967</v>
       </c>
@@ -36810,11 +37488,117 @@
       <c r="P12" s="1">
         <v>1000</v>
       </c>
-      <c r="Q12" s="3" t="s">
+      <c r="Q12" s="1" t="s">
+        <v>3078</v>
+      </c>
+      <c r="R12" s="1" t="s">
         <v>2982</v>
       </c>
-    </row>
-    <row r="13" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="S12" s="1"/>
+      <c r="T12" s="4">
+        <v>4</v>
+      </c>
+      <c r="U12" s="4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="V12" s="4">
+        <f>SUM($W$9:W12)</f>
+        <v>750</v>
+      </c>
+      <c r="W12" s="1">
+        <f t="shared" si="15"/>
+        <v>300</v>
+      </c>
+      <c r="X12" s="1">
+        <f t="shared" si="15"/>
+        <v>400</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>20</v>
+      </c>
+      <c r="Z12" s="1">
+        <f>SUM($Y$9:Y12)</f>
+        <v>60</v>
+      </c>
+      <c r="AA12" s="1">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="AB12" s="1">
+        <f>Z12</f>
+        <v>60</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" ref="AC12:AC18" si="16">AB12/3</f>
+        <v>20</v>
+      </c>
+      <c r="AD12" s="1">
+        <f>Z12*5</f>
+        <v>300</v>
+      </c>
+      <c r="AE12" s="1">
+        <f>Z12*2.5</f>
+        <v>150</v>
+      </c>
+      <c r="AF12" s="1">
+        <f>Z12*2.5</f>
+        <v>150</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="AI12" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>100403;60@100603;60</v>
+      </c>
+      <c r="AJ12" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>攻击提升60点;物防提升60点</v>
+      </c>
+      <c r="AK12" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;60@100803;60</v>
+      </c>
+      <c r="AL12" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升60点;魔防提升60点</v>
+      </c>
+      <c r="AM12" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;60@100203;150</v>
+      </c>
+      <c r="AN12" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升60点;血量提升150点</v>
+      </c>
+      <c r="AO12" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100203;300</v>
+      </c>
+      <c r="AP12" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>血量提升300点</v>
+      </c>
+      <c r="AQ12" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>101003;60@100203;150</v>
+      </c>
+      <c r="AR12" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>魔法提升60点;血量提升150点</v>
+      </c>
+      <c r="AS12" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>100203;150@100603;20@100803;20</v>
+      </c>
+      <c r="AT12" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>血量提升150点;物防提升20点点;魔防提升20点</v>
+      </c>
+    </row>
+    <row r="13" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B13" s="1" t="s">
         <v>2968</v>
       </c>
@@ -36837,10 +37621,115 @@
         <v>1500</v>
       </c>
       <c r="Q13" s="1" t="s">
+        <v>3079</v>
+      </c>
+      <c r="R13" s="1" t="s">
         <v>2698</v>
       </c>
-    </row>
-    <row r="14" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="S13" s="1"/>
+      <c r="T13" s="4">
+        <v>5</v>
+      </c>
+      <c r="U13" s="4">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="V13" s="4">
+        <f>SUM($W$9:W13)</f>
+        <v>1200</v>
+      </c>
+      <c r="W13" s="1">
+        <v>450</v>
+      </c>
+      <c r="X13" s="1">
+        <f t="shared" si="15"/>
+        <v>500</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>30</v>
+      </c>
+      <c r="Z13" s="1">
+        <f>SUM($Y$9:Y13)</f>
+        <v>90</v>
+      </c>
+      <c r="AA13" s="1">
+        <f t="shared" si="1"/>
+        <v>270</v>
+      </c>
+      <c r="AB13" s="1">
+        <f>Z13</f>
+        <v>90</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" si="16"/>
+        <v>30</v>
+      </c>
+      <c r="AD13" s="1">
+        <f>Z13*5</f>
+        <v>450</v>
+      </c>
+      <c r="AE13" s="1">
+        <f>Z13*2.5</f>
+        <v>225</v>
+      </c>
+      <c r="AF13" s="1">
+        <f>Z13*2.5</f>
+        <v>225</v>
+      </c>
+      <c r="AG13" s="1">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="AI13" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>100403;90@100603;90</v>
+      </c>
+      <c r="AJ13" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>攻击提升90点;物防提升90点</v>
+      </c>
+      <c r="AK13" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;90@100803;90</v>
+      </c>
+      <c r="AL13" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升90点;魔防提升90点</v>
+      </c>
+      <c r="AM13" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;90@100203;225</v>
+      </c>
+      <c r="AN13" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升90点;血量提升225点</v>
+      </c>
+      <c r="AO13" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100203;450</v>
+      </c>
+      <c r="AP13" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>血量提升450点</v>
+      </c>
+      <c r="AQ13" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>101003;90@100203;225</v>
+      </c>
+      <c r="AR13" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>魔法提升90点;血量提升225点</v>
+      </c>
+      <c r="AS13" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>100203;225@100603;30@100803;30</v>
+      </c>
+      <c r="AT13" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>血量提升225点;物防提升30点点;魔防提升30点</v>
+      </c>
+    </row>
+    <row r="14" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="F14" s="67"/>
@@ -36858,9 +37747,114 @@
       <c r="P14" s="1">
         <v>2000</v>
       </c>
-      <c r="Q14" s="1"/>
-    </row>
-    <row r="15" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="Q14" s="1" t="s">
+        <v>3080</v>
+      </c>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="4">
+        <v>6</v>
+      </c>
+      <c r="U14" s="4">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="V14" s="4">
+        <f>SUM($W$9:W14)</f>
+        <v>1800</v>
+      </c>
+      <c r="W14" s="1">
+        <v>600</v>
+      </c>
+      <c r="X14" s="1">
+        <f t="shared" si="15"/>
+        <v>600</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>30</v>
+      </c>
+      <c r="Z14" s="1">
+        <f>SUM($Y$9:Y14)</f>
+        <v>120</v>
+      </c>
+      <c r="AA14" s="1">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+      <c r="AB14" s="1">
+        <f>Z14</f>
+        <v>120</v>
+      </c>
+      <c r="AC14" s="1">
+        <f t="shared" si="16"/>
+        <v>40</v>
+      </c>
+      <c r="AD14" s="1">
+        <f>Z14*5</f>
+        <v>600</v>
+      </c>
+      <c r="AE14" s="1">
+        <f>Z14*2.5</f>
+        <v>300</v>
+      </c>
+      <c r="AF14" s="1">
+        <f>Z14*2.5</f>
+        <v>300</v>
+      </c>
+      <c r="AG14" s="1">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+      <c r="AI14" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>100403;120@100603;120</v>
+      </c>
+      <c r="AJ14" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>攻击提升120点;物防提升120点</v>
+      </c>
+      <c r="AK14" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;120@100803;120</v>
+      </c>
+      <c r="AL14" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升120点;魔防提升120点</v>
+      </c>
+      <c r="AM14" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;120@100203;300</v>
+      </c>
+      <c r="AN14" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升120点;血量提升300点</v>
+      </c>
+      <c r="AO14" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100203;600</v>
+      </c>
+      <c r="AP14" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>血量提升600点</v>
+      </c>
+      <c r="AQ14" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>101003;120@100203;300</v>
+      </c>
+      <c r="AR14" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>魔法提升120点;血量提升300点</v>
+      </c>
+      <c r="AS14" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>100203;300@100603;40@100803;40</v>
+      </c>
+      <c r="AT14" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>血量提升300点;物防提升40点点;魔防提升40点</v>
+      </c>
+    </row>
+    <row r="15" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B15" s="1" t="s">
         <v>2992</v>
       </c>
@@ -36881,8 +37875,111 @@
         <v>3002</v>
       </c>
       <c r="Q15" s="1"/>
-    </row>
-    <row r="16" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="4">
+        <v>7</v>
+      </c>
+      <c r="U15" s="4">
+        <f t="shared" si="0"/>
+        <v>86.666666666666671</v>
+      </c>
+      <c r="V15" s="4">
+        <f>SUM($W$9:W15)</f>
+        <v>2600</v>
+      </c>
+      <c r="W15" s="1">
+        <v>800</v>
+      </c>
+      <c r="X15" s="1">
+        <f t="shared" si="15"/>
+        <v>700</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>30</v>
+      </c>
+      <c r="Z15" s="1">
+        <f>SUM($Y$9:Y15)</f>
+        <v>150</v>
+      </c>
+      <c r="AA15" s="1">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="AB15" s="1">
+        <f>Z15</f>
+        <v>150</v>
+      </c>
+      <c r="AC15" s="1">
+        <f t="shared" si="16"/>
+        <v>50</v>
+      </c>
+      <c r="AD15" s="1">
+        <f>Z15*5</f>
+        <v>750</v>
+      </c>
+      <c r="AE15" s="1">
+        <f>Z15*2.5</f>
+        <v>375</v>
+      </c>
+      <c r="AF15" s="1">
+        <f>Z15*2.5</f>
+        <v>375</v>
+      </c>
+      <c r="AG15" s="1">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="AI15" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>100403;150@100603;150</v>
+      </c>
+      <c r="AJ15" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>攻击提升150点;物防提升150点</v>
+      </c>
+      <c r="AK15" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;150@100803;150</v>
+      </c>
+      <c r="AL15" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升150点;魔防提升150点</v>
+      </c>
+      <c r="AM15" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;150@100203;375</v>
+      </c>
+      <c r="AN15" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升150点;血量提升375点</v>
+      </c>
+      <c r="AO15" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100203;750</v>
+      </c>
+      <c r="AP15" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>血量提升750点</v>
+      </c>
+      <c r="AQ15" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>101003;150@100203;375</v>
+      </c>
+      <c r="AR15" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>魔法提升150点;血量提升375点</v>
+      </c>
+      <c r="AS15" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>100203;375@100603;50@100803;50</v>
+      </c>
+      <c r="AT15" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>血量提升375点;物防提升50点点;魔防提升50点</v>
+      </c>
+    </row>
+    <row r="16" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
@@ -36904,8 +38001,111 @@
         <v>3002</v>
       </c>
       <c r="Q16" s="1"/>
-    </row>
-    <row r="17" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="4">
+        <v>8</v>
+      </c>
+      <c r="U16" s="4">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="V16" s="4">
+        <f>SUM($W$9:W16)</f>
+        <v>3600</v>
+      </c>
+      <c r="W16" s="1">
+        <v>1000</v>
+      </c>
+      <c r="X16" s="1">
+        <f>X15+150</f>
+        <v>850</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>30</v>
+      </c>
+      <c r="Z16" s="1">
+        <f>SUM($Y$9:Y16)</f>
+        <v>180</v>
+      </c>
+      <c r="AA16" s="1">
+        <f t="shared" si="1"/>
+        <v>540</v>
+      </c>
+      <c r="AB16" s="1">
+        <f>Z16</f>
+        <v>180</v>
+      </c>
+      <c r="AC16" s="1">
+        <f t="shared" si="16"/>
+        <v>60</v>
+      </c>
+      <c r="AD16" s="1">
+        <f>Z16*5</f>
+        <v>900</v>
+      </c>
+      <c r="AE16" s="1">
+        <f>Z16*2.5</f>
+        <v>450</v>
+      </c>
+      <c r="AF16" s="1">
+        <f>Z16*2.5</f>
+        <v>450</v>
+      </c>
+      <c r="AG16" s="1">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+      <c r="AI16" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>100403;180@100603;180</v>
+      </c>
+      <c r="AJ16" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>攻击提升180点;物防提升180点</v>
+      </c>
+      <c r="AK16" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;180@100803;180</v>
+      </c>
+      <c r="AL16" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升180点;魔防提升180点</v>
+      </c>
+      <c r="AM16" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;180@100203;450</v>
+      </c>
+      <c r="AN16" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升180点;血量提升450点</v>
+      </c>
+      <c r="AO16" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100203;900</v>
+      </c>
+      <c r="AP16" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>血量提升900点</v>
+      </c>
+      <c r="AQ16" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>101003;180@100203;450</v>
+      </c>
+      <c r="AR16" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>魔法提升180点;血量提升450点</v>
+      </c>
+      <c r="AS16" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>100203;450@100603;60@100803;60</v>
+      </c>
+      <c r="AT16" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>血量提升450点;物防提升60点点;魔防提升60点</v>
+      </c>
+    </row>
+    <row r="17" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>2986</v>
       </c>
@@ -36935,8 +38135,111 @@
         <v>3002</v>
       </c>
       <c r="Q17" s="1"/>
-    </row>
-    <row r="18" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="4">
+        <v>9</v>
+      </c>
+      <c r="U17" s="4">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="V17" s="4">
+        <f>SUM($W$9:W17)</f>
+        <v>4800</v>
+      </c>
+      <c r="W17" s="1">
+        <v>1200</v>
+      </c>
+      <c r="X17" s="1">
+        <f>X16+150</f>
+        <v>1000</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>30</v>
+      </c>
+      <c r="Z17" s="1">
+        <f>SUM($Y$9:Y17)</f>
+        <v>210</v>
+      </c>
+      <c r="AA17" s="1">
+        <f t="shared" si="1"/>
+        <v>630</v>
+      </c>
+      <c r="AB17" s="1">
+        <f>Z17</f>
+        <v>210</v>
+      </c>
+      <c r="AC17" s="1">
+        <f t="shared" si="16"/>
+        <v>70</v>
+      </c>
+      <c r="AD17" s="1">
+        <f>Z17*5</f>
+        <v>1050</v>
+      </c>
+      <c r="AE17" s="1">
+        <f>Z17*2.5</f>
+        <v>525</v>
+      </c>
+      <c r="AF17" s="1">
+        <f>Z17*2.5</f>
+        <v>525</v>
+      </c>
+      <c r="AG17" s="1">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+      <c r="AI17" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>100403;210@100603;210</v>
+      </c>
+      <c r="AJ17" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>攻击提升210点;物防提升210点</v>
+      </c>
+      <c r="AK17" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;210@100803;210</v>
+      </c>
+      <c r="AL17" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升210点;魔防提升210点</v>
+      </c>
+      <c r="AM17" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;210@100203;525</v>
+      </c>
+      <c r="AN17" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升210点;血量提升525点</v>
+      </c>
+      <c r="AO17" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100203;1050</v>
+      </c>
+      <c r="AP17" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>血量提升1050点</v>
+      </c>
+      <c r="AQ17" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>101003;210@100203;525</v>
+      </c>
+      <c r="AR17" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>魔法提升210点;血量提升525点</v>
+      </c>
+      <c r="AS17" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>100203;525@100603;70@100803;70</v>
+      </c>
+      <c r="AT17" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>血量提升525点;物防提升70点点;魔防提升70点</v>
+      </c>
+    </row>
+    <row r="18" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B18" s="1" t="s">
         <v>2988</v>
       </c>
@@ -36953,8 +38256,111 @@
         <v>2973</v>
       </c>
       <c r="N18" s="1"/>
-    </row>
-    <row r="19" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="S18" s="1"/>
+      <c r="T18" s="4">
+        <v>10</v>
+      </c>
+      <c r="U18" s="4">
+        <f t="shared" si="0"/>
+        <v>203.33333333333334</v>
+      </c>
+      <c r="V18" s="4">
+        <f>SUM($W$9:W18)</f>
+        <v>6100</v>
+      </c>
+      <c r="W18" s="1">
+        <f t="shared" si="15"/>
+        <v>1300</v>
+      </c>
+      <c r="X18" s="1">
+        <f>X17+200</f>
+        <v>1200</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>30</v>
+      </c>
+      <c r="Z18" s="1">
+        <f>SUM($Y$9:Y18)</f>
+        <v>240</v>
+      </c>
+      <c r="AA18" s="1">
+        <f t="shared" si="1"/>
+        <v>720</v>
+      </c>
+      <c r="AB18" s="1">
+        <f>Z18</f>
+        <v>240</v>
+      </c>
+      <c r="AC18" s="1">
+        <f t="shared" si="16"/>
+        <v>80</v>
+      </c>
+      <c r="AD18" s="1">
+        <f>Z18*5</f>
+        <v>1200</v>
+      </c>
+      <c r="AE18" s="1">
+        <f>Z18*2.5</f>
+        <v>600</v>
+      </c>
+      <c r="AF18" s="1">
+        <f>Z18*2.5</f>
+        <v>600</v>
+      </c>
+      <c r="AG18" s="1">
+        <f t="shared" si="2"/>
+        <v>240</v>
+      </c>
+      <c r="AI18" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>100403;240@100603;240</v>
+      </c>
+      <c r="AJ18" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v>攻击提升240点;物防提升240点</v>
+      </c>
+      <c r="AK18" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;240@100803;240</v>
+      </c>
+      <c r="AL18" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升240点;魔防提升240点</v>
+      </c>
+      <c r="AM18" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;240@100203;600</v>
+      </c>
+      <c r="AN18" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升240点;血量提升600点</v>
+      </c>
+      <c r="AO18" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100203;1200</v>
+      </c>
+      <c r="AP18" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>血量提升1200点</v>
+      </c>
+      <c r="AQ18" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>101003;240@100203;600</v>
+      </c>
+      <c r="AR18" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>魔法提升240点;血量提升600点</v>
+      </c>
+      <c r="AS18" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>100203;600@100603;80@100803;80</v>
+      </c>
+      <c r="AT18" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>血量提升600点;物防提升80点点;魔防提升80点</v>
+      </c>
+    </row>
+    <row r="19" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B19" s="1" t="s">
         <v>2990</v>
       </c>
@@ -36970,8 +38376,41 @@
       <c r="I19" s="3" t="s">
         <v>2974</v>
       </c>
-    </row>
-    <row r="20" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L19" s="1" t="s">
+        <v>3091</v>
+      </c>
+      <c r="M19" s="1">
+        <v>30</v>
+      </c>
+      <c r="N19" s="7"/>
+      <c r="O19" s="1" t="s">
+        <v>3094</v>
+      </c>
+      <c r="P19" s="1">
+        <f>SUM(P10:P14)</f>
+        <v>5400</v>
+      </c>
+      <c r="Q19" s="1">
+        <f>P19/30</f>
+        <v>180</v>
+      </c>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1"/>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+    </row>
+    <row r="20" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="F20" s="67"/>
@@ -36980,8 +38419,29 @@
       <c r="I20" s="3" t="s">
         <v>3004</v>
       </c>
-    </row>
-    <row r="21" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L20" s="1" t="s">
+        <v>3092</v>
+      </c>
+      <c r="M20" s="1">
+        <v>10</v>
+      </c>
+      <c r="N20" s="7"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z20" s="1"/>
+    </row>
+    <row r="21" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B21" s="1"/>
       <c r="C21" s="1">
         <v>1</v>
@@ -36996,8 +38456,44 @@
       <c r="F21" s="67"/>
       <c r="G21" s="67"/>
       <c r="H21" s="67"/>
-    </row>
-    <row r="22" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="L21" s="1" t="s">
+        <v>3093</v>
+      </c>
+      <c r="M21" s="1">
+        <v>20</v>
+      </c>
+      <c r="N21" s="7"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1" t="s">
+        <v>3107</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>3107</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>3107</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>3107</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>3107</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>3107</v>
+      </c>
+      <c r="AE21" s="1"/>
+    </row>
+    <row r="22" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B22" s="1"/>
       <c r="C22" s="1">
         <v>2</v>
@@ -37006,11 +38502,46 @@
         <v>300</v>
       </c>
       <c r="E22" s="1">
-        <f t="shared" ref="E22:E24" si="0">D22/30</f>
+        <f t="shared" ref="E22:E24" si="17">D22/30</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="R22" s="3">
+        <v>100403</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>3084</v>
+      </c>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="4" t="s">
+        <v>3081</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="1">
+        <v>2</v>
+      </c>
+      <c r="AA22" s="1">
+        <v>3</v>
+      </c>
+      <c r="AB22" s="1">
+        <v>4</v>
+      </c>
+      <c r="AC22" s="1">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="1">
+        <v>6</v>
+      </c>
+      <c r="AE22" s="1"/>
+      <c r="AJ22" s="3" t="s">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="23" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B23" s="1"/>
       <c r="C23" s="1">
         <v>3</v>
@@ -37019,14 +38550,44 @@
         <v>500</v>
       </c>
       <c r="E23" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="17"/>
         <v>16.666666666666668</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>3005</v>
       </c>
-    </row>
-    <row r="24" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="R23" s="119" t="s">
+        <v>3099</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3100</v>
+      </c>
+      <c r="X23" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="1">
+        <v>12</v>
+      </c>
+      <c r="AB23" s="1">
+        <v>18</v>
+      </c>
+      <c r="AC23" s="1">
+        <v>24</v>
+      </c>
+      <c r="AD23" s="1">
+        <v>30</v>
+      </c>
+      <c r="AJ23" s="3" t="s">
+        <v>3109</v>
+      </c>
+    </row>
+    <row r="24" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B24" s="1"/>
       <c r="C24" s="1">
         <v>4</v>
@@ -37035,7 +38596,7 @@
         <v>1000</v>
       </c>
       <c r="E24" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="17"/>
         <v>33.333333333333336</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -37050,8 +38611,24 @@
       <c r="O24" s="3" t="s">
         <v>2981</v>
       </c>
-    </row>
-    <row r="25" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="R24" s="119"/>
+      <c r="S24" s="120"/>
+      <c r="T24" s="121"/>
+      <c r="U24" s="119"/>
+      <c r="V24" s="108"/>
+      <c r="W24" s="119"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="1"/>
+      <c r="AJ24" s="3" t="s">
+        <v>3110</v>
+      </c>
+    </row>
+    <row r="25" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="C25" s="1">
         <v>5</v>
       </c>
@@ -37068,8 +38645,18 @@
       <c r="O25" s="3" t="s">
         <v>2982</v>
       </c>
-    </row>
-    <row r="26" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="R25" s="119"/>
+      <c r="S25" s="120"/>
+      <c r="T25" s="121"/>
+      <c r="U25" s="119"/>
+      <c r="V25" s="108"/>
+      <c r="W25" s="119"/>
+      <c r="X25" s="4"/>
+      <c r="AJ25" s="3" t="s">
+        <v>3111</v>
+      </c>
+    </row>
+    <row r="26" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="E26" s="1"/>
@@ -37085,8 +38672,18 @@
       <c r="O26" s="3" t="s">
         <v>2983</v>
       </c>
-    </row>
-    <row r="27" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="R26" s="3" t="s">
+        <v>3101</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3089</v>
+      </c>
+      <c r="X26" s="4"/>
+      <c r="AJ26" s="3" t="s">
+        <v>3112</v>
+      </c>
+    </row>
+    <row r="27" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="E27" s="1"/>
@@ -37096,8 +38693,12 @@
       <c r="O27" s="3" t="s">
         <v>2984</v>
       </c>
-    </row>
-    <row r="28" spans="2:17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="X27" s="4"/>
+      <c r="AJ27" s="3" t="s">
+        <v>3113</v>
+      </c>
+    </row>
+    <row r="28" spans="2:46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="B28" s="3" t="s">
         <v>2993</v>
       </c>
@@ -37112,8 +38713,18 @@
       <c r="I28" s="7" t="s">
         <v>3006</v>
       </c>
-    </row>
-    <row r="29" spans="2:17" ht="20.100000000000001" customHeight="1">
+      <c r="R28" s="3" t="s">
+        <v>3102</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>3103</v>
+      </c>
+      <c r="X28" s="4"/>
+      <c r="AJ28" s="3" t="s">
+        <v>3114</v>
+      </c>
+    </row>
+    <row r="29" spans="2:46" ht="20.100000000000001" customHeight="1">
       <c r="B29" s="3" t="s">
         <v>2994</v>
       </c>
@@ -37127,8 +38738,24 @@
       <c r="I29" s="7" t="s">
         <v>3007</v>
       </c>
-    </row>
-    <row r="30" spans="2:17" ht="20.100000000000001" customHeight="1">
+      <c r="O29" s="1">
+        <v>10000180</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>3118</v>
+      </c>
+      <c r="R29" s="122" t="s">
+        <v>3104</v>
+      </c>
+      <c r="S29" s="105" t="s">
+        <v>3105</v>
+      </c>
+      <c r="X29" s="4"/>
+      <c r="AJ29" t="s">
+        <v>3115</v>
+      </c>
+    </row>
+    <row r="30" spans="2:46" ht="20.100000000000001" customHeight="1">
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
@@ -37142,8 +38769,18 @@
       <c r="I30" s="7" t="s">
         <v>3008</v>
       </c>
-    </row>
-    <row r="31" spans="2:17" ht="20.100000000000001" customHeight="1">
+      <c r="O30" s="1">
+        <v>10000181</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>3119</v>
+      </c>
+      <c r="X30" s="4"/>
+      <c r="AJ30" t="s">
+        <v>3116</v>
+      </c>
+    </row>
+    <row r="31" spans="2:46" ht="20.100000000000001" customHeight="1">
       <c r="B31" s="3" t="s">
         <v>2985</v>
       </c>
@@ -37153,8 +38790,12 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="7"/>
-    </row>
-    <row r="32" spans="2:17" ht="20.100000000000001" customHeight="1">
+      <c r="X31" s="4"/>
+      <c r="AJ31" t="s">
+        <v>3117</v>
+      </c>
+    </row>
+    <row r="32" spans="2:46" ht="20.100000000000001" customHeight="1">
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
@@ -37168,6 +38809,7 @@
       <c r="I32" s="7" t="s">
         <v>3072</v>
       </c>
+      <c r="X32" s="4"/>
     </row>
     <row r="33" spans="2:15" ht="20.100000000000001" customHeight="1">
       <c r="B33" s="13"/>
@@ -37308,7 +38950,7 @@
       <c r="I44" s="3" t="s">
         <v>3028</v>
       </c>
-      <c r="L44" s="3" t="s">
+      <c r="L44" s="1" t="s">
         <v>3027</v>
       </c>
       <c r="N44" s="1">
@@ -37938,6 +39580,9 @@
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="Z10:Z17 Z18 V10:V17" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -68216,6 +69861,13 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="CP23:CP25"/>
+    <mergeCell ref="CP26:CP28"/>
+    <mergeCell ref="CP8:CP10"/>
+    <mergeCell ref="CP11:CP13"/>
+    <mergeCell ref="CP14:CP16"/>
+    <mergeCell ref="CP17:CP19"/>
+    <mergeCell ref="CP20:CP22"/>
     <mergeCell ref="K18:K20"/>
     <mergeCell ref="K21:K23"/>
     <mergeCell ref="AX4:AX6"/>
@@ -68230,13 +69882,6 @@
     <mergeCell ref="K9:K11"/>
     <mergeCell ref="K12:K14"/>
     <mergeCell ref="K15:K17"/>
-    <mergeCell ref="CP23:CP25"/>
-    <mergeCell ref="CP26:CP28"/>
-    <mergeCell ref="CP8:CP10"/>
-    <mergeCell ref="CP11:CP13"/>
-    <mergeCell ref="CP14:CP16"/>
-    <mergeCell ref="CP17:CP19"/>
-    <mergeCell ref="CP20:CP22"/>
   </mergeCells>
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -79309,6 +80954,7 @@
   </sheetData>
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/WeiJingShuZhi/属性表.xlsx
+++ b/WeiJingShuZhi/属性表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\WeiJingShuZhi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E840A4E-FF92-4E67-9313-E9BB374E2746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C169BC-AC60-4C26-93F2-3D893E196680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5540" uniqueCount="3120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5546" uniqueCount="3126">
   <si>
     <t>人物属性</t>
   </si>
@@ -9938,6 +9938,30 @@
   </si>
   <si>
     <t>魔能之钥</t>
+  </si>
+  <si>
+    <t>开启</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>65级后</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉落方式</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">每天掉落 </t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>后期BOSS掉材料</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔能装备野外BOSS掉落</t>
+    <phoneticPr fontId="35" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -10492,7 +10516,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10822,12 +10846,6 @@
     <xf numFmtId="0" fontId="1" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10837,8 +10855,11 @@
     <xf numFmtId="0" fontId="1" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11509,2749 +11530,2836 @@
       <sheetData sheetId="0">
         <row r="856">
           <cell r="C856">
-            <v>10302002</v>
+            <v>10103602</v>
           </cell>
-          <cell r="S856">
-            <v>6202003</v>
+          <cell r="S856" t="str">
+            <v>6@100803;50;150</v>
           </cell>
         </row>
         <row r="857">
           <cell r="C857">
-            <v>10302003</v>
+            <v>10103603</v>
           </cell>
-          <cell r="S857">
-            <v>6203003</v>
+          <cell r="S857" t="str">
+            <v>6@200303;0.01;0.03</v>
           </cell>
         </row>
         <row r="858">
           <cell r="C858">
-            <v>10302004</v>
+            <v>10201101</v>
           </cell>
           <cell r="S858">
-            <v>6204004</v>
+            <v>7102001</v>
           </cell>
         </row>
         <row r="859">
           <cell r="C859">
-            <v>10302005</v>
+            <v>10201102</v>
           </cell>
           <cell r="S859">
-            <v>6205004</v>
+            <v>7102002</v>
           </cell>
         </row>
         <row r="860">
           <cell r="C860">
-            <v>10302006</v>
+            <v>10201103</v>
           </cell>
           <cell r="S860">
-            <v>6206003</v>
+            <v>7102003</v>
           </cell>
         </row>
         <row r="861">
           <cell r="C861">
-            <v>10303001</v>
+            <v>10201104</v>
           </cell>
           <cell r="S861">
-            <v>6301003</v>
+            <v>7102004</v>
           </cell>
         </row>
         <row r="862">
           <cell r="C862">
-            <v>10303002</v>
+            <v>10201201</v>
           </cell>
           <cell r="S862">
-            <v>6302003</v>
+            <v>7103001</v>
           </cell>
         </row>
         <row r="863">
           <cell r="C863">
-            <v>10303003</v>
+            <v>10201202</v>
           </cell>
           <cell r="S863">
-            <v>6303003</v>
+            <v>7103002</v>
           </cell>
         </row>
         <row r="864">
           <cell r="C864">
-            <v>10303004</v>
+            <v>10201203</v>
           </cell>
           <cell r="S864">
-            <v>6304004</v>
+            <v>7103003</v>
           </cell>
         </row>
         <row r="865">
           <cell r="C865">
-            <v>10303005</v>
+            <v>10201204</v>
           </cell>
           <cell r="S865">
-            <v>6305004</v>
+            <v>7103004</v>
           </cell>
         </row>
         <row r="866">
           <cell r="C866">
-            <v>10303006</v>
+            <v>10202101</v>
           </cell>
           <cell r="S866">
-            <v>6306003</v>
+            <v>7202001</v>
           </cell>
         </row>
         <row r="867">
           <cell r="C867">
-            <v>11200000</v>
+            <v>10202102</v>
           </cell>
           <cell r="S867">
-            <v>500</v>
+            <v>7202002</v>
           </cell>
         </row>
         <row r="868">
           <cell r="C868">
-            <v>11200001</v>
+            <v>10202103</v>
           </cell>
           <cell r="S868">
-            <v>500</v>
+            <v>7202003</v>
           </cell>
         </row>
         <row r="869">
           <cell r="C869">
-            <v>11200002</v>
+            <v>10202104</v>
           </cell>
           <cell r="S869">
-            <v>500</v>
+            <v>7202004</v>
           </cell>
         </row>
         <row r="870">
           <cell r="C870">
-            <v>11200003</v>
+            <v>10202201</v>
           </cell>
           <cell r="S870">
-            <v>500</v>
+            <v>7203001</v>
           </cell>
         </row>
         <row r="871">
           <cell r="C871">
-            <v>11200010</v>
+            <v>10202202</v>
           </cell>
           <cell r="S871">
-            <v>500</v>
+            <v>7203002</v>
           </cell>
         </row>
         <row r="872">
           <cell r="C872">
-            <v>11300001</v>
+            <v>10202203</v>
           </cell>
-          <cell r="S872" t="str">
-            <v>1;3901</v>
+          <cell r="S872">
+            <v>7203003</v>
           </cell>
         </row>
         <row r="873">
           <cell r="C873">
-            <v>11300002</v>
+            <v>10202204</v>
           </cell>
-          <cell r="S873" t="str">
-            <v>1;3906</v>
+          <cell r="S873">
+            <v>7203004</v>
           </cell>
         </row>
         <row r="874">
           <cell r="C874">
-            <v>11300003</v>
+            <v>10203101</v>
           </cell>
-          <cell r="S874" t="str">
-            <v>1;3907</v>
+          <cell r="S874">
+            <v>7302001</v>
           </cell>
         </row>
         <row r="875">
           <cell r="C875">
-            <v>11300004</v>
+            <v>10203102</v>
           </cell>
-          <cell r="S875" t="str">
-            <v>1;3908</v>
+          <cell r="S875">
+            <v>7302002</v>
           </cell>
         </row>
         <row r="876">
           <cell r="C876">
-            <v>11300005</v>
+            <v>10203201</v>
           </cell>
-          <cell r="S876" t="str">
-            <v>1;3909</v>
+          <cell r="S876">
+            <v>7303001</v>
           </cell>
         </row>
         <row r="877">
           <cell r="C877">
-            <v>11300006</v>
+            <v>10203202</v>
           </cell>
-          <cell r="S877" t="str">
-            <v>1;3910</v>
+          <cell r="S877">
+            <v>7303002</v>
           </cell>
         </row>
         <row r="878">
           <cell r="C878">
-            <v>11300007</v>
+            <v>10301001</v>
           </cell>
-          <cell r="S878" t="str">
-            <v>2;3902</v>
+          <cell r="S878">
+            <v>6101003</v>
           </cell>
         </row>
         <row r="879">
           <cell r="C879">
-            <v>11300008</v>
+            <v>10301002</v>
           </cell>
-          <cell r="S879" t="str">
-            <v>2;3903</v>
+          <cell r="S879">
+            <v>6102003</v>
           </cell>
         </row>
         <row r="880">
           <cell r="C880">
-            <v>11300009</v>
+            <v>10301003</v>
           </cell>
-          <cell r="S880" t="str">
-            <v>2;3904</v>
+          <cell r="S880">
+            <v>6103003</v>
           </cell>
         </row>
         <row r="881">
           <cell r="C881">
-            <v>11300101</v>
+            <v>10301004</v>
           </cell>
-          <cell r="S881" t="str">
-            <v>1;3101</v>
+          <cell r="S881">
+            <v>6104004</v>
           </cell>
         </row>
         <row r="882">
           <cell r="C882">
-            <v>11300102</v>
+            <v>10301005</v>
           </cell>
-          <cell r="S882" t="str">
-            <v>1;3102</v>
+          <cell r="S882">
+            <v>6105004</v>
           </cell>
         </row>
         <row r="883">
           <cell r="C883">
-            <v>11300103</v>
+            <v>10301006</v>
           </cell>
-          <cell r="S883" t="str">
-            <v>1;3103</v>
+          <cell r="S883">
+            <v>6106003</v>
           </cell>
         </row>
         <row r="884">
           <cell r="C884">
-            <v>11300104</v>
+            <v>10302001</v>
           </cell>
-          <cell r="S884" t="str">
-            <v>1;3104</v>
+          <cell r="S884">
+            <v>6201003</v>
           </cell>
         </row>
         <row r="885">
           <cell r="C885">
-            <v>11300105</v>
+            <v>10302002</v>
           </cell>
-          <cell r="S885" t="str">
-            <v>1;3105</v>
+          <cell r="S885">
+            <v>6202003</v>
           </cell>
         </row>
         <row r="886">
           <cell r="C886">
-            <v>11300201</v>
+            <v>10302003</v>
           </cell>
-          <cell r="S886" t="str">
-            <v>1;3201</v>
+          <cell r="S886">
+            <v>6203003</v>
           </cell>
         </row>
         <row r="887">
           <cell r="C887">
-            <v>11300202</v>
+            <v>10302004</v>
           </cell>
-          <cell r="S887" t="str">
-            <v>1;3202</v>
+          <cell r="S887">
+            <v>6204004</v>
           </cell>
         </row>
         <row r="888">
           <cell r="C888">
-            <v>11300203</v>
+            <v>10302005</v>
           </cell>
-          <cell r="S888" t="str">
-            <v>1;3203</v>
+          <cell r="S888">
+            <v>6205004</v>
           </cell>
         </row>
         <row r="889">
           <cell r="C889">
-            <v>11300204</v>
+            <v>10302006</v>
           </cell>
-          <cell r="S889" t="str">
-            <v>1;3204</v>
+          <cell r="S889">
+            <v>6206003</v>
           </cell>
         </row>
         <row r="890">
           <cell r="C890">
-            <v>11300205</v>
+            <v>10303001</v>
           </cell>
-          <cell r="S890" t="str">
-            <v>1;3205</v>
+          <cell r="S890">
+            <v>6301003</v>
           </cell>
         </row>
         <row r="891">
           <cell r="C891">
-            <v>11300301</v>
+            <v>10303002</v>
           </cell>
-          <cell r="S891" t="str">
-            <v>1;3301</v>
+          <cell r="S891">
+            <v>6302003</v>
           </cell>
         </row>
         <row r="892">
           <cell r="C892">
-            <v>11300302</v>
+            <v>10303003</v>
           </cell>
-          <cell r="S892" t="str">
-            <v>1;3302</v>
+          <cell r="S892">
+            <v>6303003</v>
           </cell>
         </row>
         <row r="893">
           <cell r="C893">
-            <v>11300303</v>
+            <v>10303004</v>
           </cell>
-          <cell r="S893" t="str">
-            <v>1;3303</v>
+          <cell r="S893">
+            <v>6304004</v>
           </cell>
         </row>
         <row r="894">
           <cell r="C894">
-            <v>11300304</v>
+            <v>10303005</v>
           </cell>
-          <cell r="S894" t="str">
-            <v>1;3304</v>
+          <cell r="S894">
+            <v>6305004</v>
           </cell>
         </row>
         <row r="895">
           <cell r="C895">
-            <v>11300305</v>
+            <v>10303006</v>
           </cell>
-          <cell r="S895" t="str">
-            <v>1;3305</v>
+          <cell r="S895">
+            <v>6306003</v>
           </cell>
         </row>
         <row r="896">
           <cell r="C896">
-            <v>11300401</v>
+            <v>11200000</v>
           </cell>
-          <cell r="S896" t="str">
-            <v>1;3401</v>
+          <cell r="S896">
+            <v>500</v>
           </cell>
         </row>
         <row r="897">
           <cell r="C897">
-            <v>11300402</v>
+            <v>11200001</v>
           </cell>
-          <cell r="S897" t="str">
-            <v>1;3402</v>
+          <cell r="S897">
+            <v>500</v>
           </cell>
         </row>
         <row r="898">
           <cell r="C898">
-            <v>11300403</v>
+            <v>11200002</v>
           </cell>
-          <cell r="S898" t="str">
-            <v>1;3403</v>
+          <cell r="S898">
+            <v>500</v>
           </cell>
         </row>
         <row r="899">
           <cell r="C899">
-            <v>11300404</v>
+            <v>11200003</v>
           </cell>
-          <cell r="S899" t="str">
-            <v>1;3404</v>
+          <cell r="S899">
+            <v>500</v>
           </cell>
         </row>
         <row r="900">
           <cell r="C900">
-            <v>11300405</v>
+            <v>11200010</v>
           </cell>
-          <cell r="S900" t="str">
-            <v>1;3405</v>
+          <cell r="S900">
+            <v>500</v>
           </cell>
         </row>
         <row r="901">
           <cell r="C901">
-            <v>11300501</v>
+            <v>11300001</v>
           </cell>
           <cell r="S901" t="str">
-            <v>1;3501</v>
+            <v>1;3901</v>
           </cell>
         </row>
         <row r="902">
           <cell r="C902">
-            <v>11300502</v>
+            <v>11300002</v>
           </cell>
           <cell r="S902" t="str">
-            <v>1;3502</v>
+            <v>1;3906</v>
           </cell>
         </row>
         <row r="903">
           <cell r="C903">
-            <v>11300503</v>
+            <v>11300003</v>
           </cell>
           <cell r="S903" t="str">
-            <v>1;3503</v>
+            <v>1;3907</v>
           </cell>
         </row>
         <row r="904">
           <cell r="C904">
-            <v>11300504</v>
+            <v>11300004</v>
           </cell>
           <cell r="S904" t="str">
-            <v>1;3504</v>
+            <v>1;3908</v>
           </cell>
         </row>
         <row r="905">
           <cell r="C905">
-            <v>11300505</v>
+            <v>11300005</v>
           </cell>
           <cell r="S905" t="str">
-            <v>1;3505</v>
+            <v>1;3909</v>
           </cell>
         </row>
         <row r="906">
           <cell r="C906">
-            <v>11300601</v>
+            <v>11300006</v>
           </cell>
           <cell r="S906" t="str">
-            <v>1;3601</v>
+            <v>1;3910</v>
           </cell>
         </row>
         <row r="907">
           <cell r="C907">
-            <v>11300602</v>
+            <v>11300007</v>
           </cell>
           <cell r="S907" t="str">
-            <v>1;3602</v>
+            <v>2;3902</v>
           </cell>
         </row>
         <row r="908">
           <cell r="C908">
-            <v>11300603</v>
+            <v>11300008</v>
           </cell>
           <cell r="S908" t="str">
-            <v>1;3603</v>
+            <v>2;3903</v>
           </cell>
         </row>
         <row r="909">
           <cell r="C909">
-            <v>11300604</v>
+            <v>11300009</v>
           </cell>
           <cell r="S909" t="str">
-            <v>1;3604</v>
+            <v>2;3904</v>
           </cell>
         </row>
         <row r="910">
           <cell r="C910">
-            <v>11300605</v>
+            <v>11300101</v>
           </cell>
           <cell r="S910" t="str">
-            <v>1;3605</v>
+            <v>1;3101</v>
           </cell>
         </row>
         <row r="911">
           <cell r="C911">
-            <v>11400101</v>
+            <v>11300102</v>
           </cell>
           <cell r="S911" t="str">
-            <v>1,30@1;202103,0.01,0.03</v>
+            <v>1;3102</v>
           </cell>
         </row>
         <row r="912">
           <cell r="C912">
-            <v>11400102</v>
+            <v>11300103</v>
           </cell>
           <cell r="S912" t="str">
-            <v>1,30@1;100203,100,200</v>
+            <v>1;3103</v>
           </cell>
         </row>
         <row r="913">
           <cell r="C913">
-            <v>11400103</v>
+            <v>11300104</v>
           </cell>
           <cell r="S913" t="str">
-            <v>1,30@2;62000001</v>
+            <v>1;3104</v>
           </cell>
         </row>
         <row r="914">
           <cell r="C914">
-            <v>11500101</v>
+            <v>11300105</v>
+          </cell>
+          <cell r="S914" t="str">
+            <v>1;3105</v>
           </cell>
         </row>
         <row r="915">
           <cell r="C915">
-            <v>11500102</v>
+            <v>11300201</v>
+          </cell>
+          <cell r="S915" t="str">
+            <v>1;3201</v>
           </cell>
         </row>
         <row r="916">
           <cell r="C916">
-            <v>11500103</v>
+            <v>11300202</v>
+          </cell>
+          <cell r="S916" t="str">
+            <v>1;3202</v>
           </cell>
         </row>
         <row r="917">
           <cell r="C917">
-            <v>11500201</v>
+            <v>11300203</v>
+          </cell>
+          <cell r="S917" t="str">
+            <v>1;3203</v>
           </cell>
         </row>
         <row r="918">
           <cell r="C918">
-            <v>11500202</v>
+            <v>11300204</v>
+          </cell>
+          <cell r="S918" t="str">
+            <v>1;3204</v>
           </cell>
         </row>
         <row r="919">
           <cell r="C919">
-            <v>11500203</v>
+            <v>11300205</v>
+          </cell>
+          <cell r="S919" t="str">
+            <v>1;3205</v>
           </cell>
         </row>
         <row r="920">
           <cell r="C920">
-            <v>11500301</v>
+            <v>11300301</v>
+          </cell>
+          <cell r="S920" t="str">
+            <v>1;3301</v>
           </cell>
         </row>
         <row r="921">
           <cell r="C921">
-            <v>11500302</v>
+            <v>11300302</v>
+          </cell>
+          <cell r="S921" t="str">
+            <v>1;3302</v>
           </cell>
         </row>
         <row r="922">
           <cell r="C922">
-            <v>11500303</v>
+            <v>11300303</v>
+          </cell>
+          <cell r="S922" t="str">
+            <v>1;3303</v>
           </cell>
         </row>
         <row r="923">
           <cell r="C923">
-            <v>11500401</v>
+            <v>11300304</v>
+          </cell>
+          <cell r="S923" t="str">
+            <v>1;3304</v>
           </cell>
         </row>
         <row r="924">
           <cell r="C924">
-            <v>11500402</v>
+            <v>11300305</v>
+          </cell>
+          <cell r="S924" t="str">
+            <v>1;3305</v>
           </cell>
         </row>
         <row r="925">
           <cell r="C925">
-            <v>11500403</v>
+            <v>11300401</v>
+          </cell>
+          <cell r="S925" t="str">
+            <v>1;3401</v>
           </cell>
         </row>
         <row r="926">
           <cell r="C926">
-            <v>11500501</v>
+            <v>11300402</v>
+          </cell>
+          <cell r="S926" t="str">
+            <v>1;3402</v>
           </cell>
         </row>
         <row r="927">
           <cell r="C927">
-            <v>11500502</v>
+            <v>11300403</v>
+          </cell>
+          <cell r="S927" t="str">
+            <v>1;3403</v>
           </cell>
         </row>
         <row r="928">
           <cell r="C928">
-            <v>11500503</v>
+            <v>11300404</v>
+          </cell>
+          <cell r="S928" t="str">
+            <v>1;3404</v>
           </cell>
         </row>
         <row r="929">
           <cell r="C929">
-            <v>11600101</v>
+            <v>11300405</v>
+          </cell>
+          <cell r="S929" t="str">
+            <v>1;3405</v>
           </cell>
         </row>
         <row r="930">
           <cell r="C930">
-            <v>11600102</v>
+            <v>11300501</v>
+          </cell>
+          <cell r="S930" t="str">
+            <v>1;3501</v>
           </cell>
         </row>
         <row r="931">
           <cell r="C931">
-            <v>11600103</v>
+            <v>11300502</v>
+          </cell>
+          <cell r="S931" t="str">
+            <v>1;3502</v>
           </cell>
         </row>
         <row r="932">
           <cell r="C932">
-            <v>11600201</v>
+            <v>11300503</v>
+          </cell>
+          <cell r="S932" t="str">
+            <v>1;3503</v>
           </cell>
         </row>
         <row r="933">
           <cell r="C933">
-            <v>11600202</v>
+            <v>11300504</v>
+          </cell>
+          <cell r="S933" t="str">
+            <v>1;3504</v>
           </cell>
         </row>
         <row r="934">
           <cell r="C934">
-            <v>11600203</v>
+            <v>11300505</v>
+          </cell>
+          <cell r="S934" t="str">
+            <v>1;3505</v>
           </cell>
         </row>
         <row r="935">
           <cell r="C935">
-            <v>11600301</v>
+            <v>11300601</v>
+          </cell>
+          <cell r="S935" t="str">
+            <v>1;3601</v>
           </cell>
         </row>
         <row r="936">
           <cell r="C936">
-            <v>11600302</v>
+            <v>11300602</v>
+          </cell>
+          <cell r="S936" t="str">
+            <v>1;3602</v>
           </cell>
         </row>
         <row r="937">
           <cell r="C937">
-            <v>11600303</v>
+            <v>11300603</v>
+          </cell>
+          <cell r="S937" t="str">
+            <v>1;3603</v>
           </cell>
         </row>
         <row r="938">
           <cell r="C938">
-            <v>11600401</v>
+            <v>11300604</v>
+          </cell>
+          <cell r="S938" t="str">
+            <v>1;3604</v>
           </cell>
         </row>
         <row r="939">
           <cell r="C939">
-            <v>11600402</v>
+            <v>11300605</v>
+          </cell>
+          <cell r="S939" t="str">
+            <v>1;3605</v>
           </cell>
         </row>
         <row r="940">
           <cell r="C940">
-            <v>11600403</v>
+            <v>11400101</v>
+          </cell>
+          <cell r="S940" t="str">
+            <v>1,30@1;202103,0.01,0.03</v>
           </cell>
         </row>
         <row r="941">
           <cell r="C941">
-            <v>11600501</v>
+            <v>11400102</v>
+          </cell>
+          <cell r="S941" t="str">
+            <v>1,30@1;100203,100,200</v>
           </cell>
         </row>
         <row r="942">
           <cell r="C942">
-            <v>11600502</v>
+            <v>11400103</v>
+          </cell>
+          <cell r="S942" t="str">
+            <v>1,30@2;62000001</v>
           </cell>
         </row>
         <row r="943">
           <cell r="C943">
-            <v>11600503</v>
+            <v>11500101</v>
           </cell>
         </row>
         <row r="944">
           <cell r="C944">
-            <v>11600601</v>
+            <v>11500102</v>
           </cell>
         </row>
         <row r="945">
           <cell r="C945">
-            <v>11600602</v>
+            <v>11500103</v>
           </cell>
         </row>
         <row r="946">
           <cell r="C946">
-            <v>11600603</v>
+            <v>11500201</v>
           </cell>
         </row>
         <row r="947">
           <cell r="C947">
-            <v>11600701</v>
+            <v>11500202</v>
           </cell>
         </row>
         <row r="948">
           <cell r="C948">
-            <v>11600702</v>
+            <v>11500203</v>
           </cell>
         </row>
         <row r="949">
           <cell r="C949">
-            <v>11600703</v>
+            <v>11500301</v>
           </cell>
         </row>
         <row r="950">
           <cell r="C950">
-            <v>11600801</v>
+            <v>11500302</v>
           </cell>
         </row>
         <row r="951">
           <cell r="C951">
-            <v>11600802</v>
+            <v>11500303</v>
           </cell>
         </row>
         <row r="952">
           <cell r="C952">
-            <v>11600803</v>
+            <v>11500401</v>
           </cell>
         </row>
         <row r="953">
           <cell r="C953">
-            <v>11600901</v>
+            <v>11500402</v>
           </cell>
         </row>
         <row r="954">
           <cell r="C954">
-            <v>11600902</v>
+            <v>11500403</v>
           </cell>
         </row>
         <row r="955">
           <cell r="C955">
-            <v>11600903</v>
+            <v>11500501</v>
           </cell>
         </row>
         <row r="956">
           <cell r="C956">
-            <v>11610101</v>
+            <v>11500502</v>
           </cell>
         </row>
         <row r="957">
           <cell r="C957">
-            <v>11610102</v>
+            <v>11500503</v>
           </cell>
         </row>
         <row r="958">
           <cell r="C958">
-            <v>11610103</v>
+            <v>11600101</v>
           </cell>
         </row>
         <row r="959">
           <cell r="C959">
-            <v>11610201</v>
+            <v>11600102</v>
           </cell>
         </row>
         <row r="960">
           <cell r="C960">
-            <v>11610202</v>
+            <v>11600103</v>
           </cell>
         </row>
         <row r="961">
           <cell r="C961">
-            <v>11610203</v>
+            <v>11600201</v>
           </cell>
         </row>
         <row r="962">
           <cell r="C962">
-            <v>11610301</v>
+            <v>11600202</v>
           </cell>
         </row>
         <row r="963">
           <cell r="C963">
-            <v>11610302</v>
+            <v>11600203</v>
           </cell>
         </row>
         <row r="964">
           <cell r="C964">
-            <v>11610303</v>
+            <v>11600301</v>
           </cell>
         </row>
         <row r="965">
           <cell r="C965">
-            <v>11610401</v>
+            <v>11600302</v>
           </cell>
         </row>
         <row r="966">
           <cell r="C966">
-            <v>11610402</v>
+            <v>11600303</v>
           </cell>
         </row>
         <row r="967">
           <cell r="C967">
-            <v>11610403</v>
+            <v>11600401</v>
           </cell>
         </row>
         <row r="968">
           <cell r="C968">
-            <v>11610501</v>
+            <v>11600402</v>
           </cell>
         </row>
         <row r="969">
           <cell r="C969">
-            <v>11610502</v>
+            <v>11600403</v>
           </cell>
         </row>
         <row r="970">
           <cell r="C970">
-            <v>11610503</v>
+            <v>11600501</v>
           </cell>
         </row>
         <row r="971">
           <cell r="C971">
-            <v>11610601</v>
+            <v>11600502</v>
           </cell>
         </row>
         <row r="972">
           <cell r="C972">
-            <v>11610602</v>
+            <v>11600503</v>
           </cell>
         </row>
         <row r="973">
           <cell r="C973">
-            <v>11610603</v>
+            <v>11600601</v>
           </cell>
         </row>
         <row r="974">
           <cell r="C974">
-            <v>11610701</v>
+            <v>11600602</v>
           </cell>
         </row>
         <row r="975">
           <cell r="C975">
-            <v>11610702</v>
+            <v>11600603</v>
           </cell>
         </row>
         <row r="976">
           <cell r="C976">
-            <v>11610703</v>
+            <v>11600701</v>
           </cell>
         </row>
         <row r="977">
           <cell r="C977">
-            <v>13001001</v>
-          </cell>
-          <cell r="S977">
-            <v>65001001</v>
+            <v>11600702</v>
           </cell>
         </row>
         <row r="978">
           <cell r="C978">
-            <v>13001002</v>
-          </cell>
-          <cell r="S978">
-            <v>65001002</v>
+            <v>11600703</v>
           </cell>
         </row>
         <row r="979">
           <cell r="C979">
-            <v>13001003</v>
-          </cell>
-          <cell r="S979">
-            <v>65001003</v>
+            <v>11600801</v>
           </cell>
         </row>
         <row r="980">
           <cell r="C980">
-            <v>13001004</v>
-          </cell>
-          <cell r="S980">
-            <v>65001004</v>
+            <v>11600802</v>
           </cell>
         </row>
         <row r="981">
           <cell r="C981">
-            <v>13001005</v>
-          </cell>
-          <cell r="S981">
-            <v>65001005</v>
+            <v>11600803</v>
           </cell>
         </row>
         <row r="982">
           <cell r="C982">
-            <v>13001006</v>
-          </cell>
-          <cell r="S982">
-            <v>65001006</v>
+            <v>11600901</v>
           </cell>
         </row>
         <row r="983">
           <cell r="C983">
-            <v>13001101</v>
-          </cell>
-          <cell r="S983">
-            <v>65001101</v>
+            <v>11600902</v>
           </cell>
         </row>
         <row r="984">
           <cell r="C984">
-            <v>13001102</v>
-          </cell>
-          <cell r="S984">
-            <v>65001102</v>
+            <v>11600903</v>
           </cell>
         </row>
         <row r="985">
           <cell r="C985">
-            <v>13001103</v>
-          </cell>
-          <cell r="S985">
-            <v>65001103</v>
+            <v>11610101</v>
           </cell>
         </row>
         <row r="986">
           <cell r="C986">
-            <v>13001104</v>
-          </cell>
-          <cell r="S986">
-            <v>65001104</v>
+            <v>11610102</v>
           </cell>
         </row>
         <row r="987">
           <cell r="C987">
-            <v>13001105</v>
-          </cell>
-          <cell r="S987">
-            <v>65001105</v>
+            <v>11610103</v>
           </cell>
         </row>
         <row r="988">
           <cell r="C988">
-            <v>13002001</v>
-          </cell>
-          <cell r="S988">
-            <v>65002001</v>
+            <v>11610201</v>
           </cell>
         </row>
         <row r="989">
           <cell r="C989">
-            <v>13002002</v>
-          </cell>
-          <cell r="S989">
-            <v>65002002</v>
+            <v>11610202</v>
           </cell>
         </row>
         <row r="990">
           <cell r="C990">
-            <v>13002003</v>
-          </cell>
-          <cell r="S990">
-            <v>65002003</v>
+            <v>11610203</v>
           </cell>
         </row>
         <row r="991">
           <cell r="C991">
-            <v>13002004</v>
-          </cell>
-          <cell r="S991">
-            <v>65002004</v>
+            <v>11610301</v>
           </cell>
         </row>
         <row r="992">
           <cell r="C992">
-            <v>13002005</v>
-          </cell>
-          <cell r="S992">
-            <v>65002005</v>
+            <v>11610302</v>
           </cell>
         </row>
         <row r="993">
           <cell r="C993">
-            <v>13002006</v>
-          </cell>
-          <cell r="S993">
-            <v>65002006</v>
+            <v>11610303</v>
           </cell>
         </row>
         <row r="994">
           <cell r="C994">
-            <v>13002101</v>
-          </cell>
-          <cell r="S994">
-            <v>65002101</v>
+            <v>11610401</v>
           </cell>
         </row>
         <row r="995">
           <cell r="C995">
-            <v>13002102</v>
-          </cell>
-          <cell r="S995">
-            <v>65002102</v>
+            <v>11610402</v>
           </cell>
         </row>
         <row r="996">
           <cell r="C996">
-            <v>13002103</v>
-          </cell>
-          <cell r="S996">
-            <v>65002103</v>
+            <v>11610403</v>
           </cell>
         </row>
         <row r="997">
           <cell r="C997">
-            <v>13002104</v>
-          </cell>
-          <cell r="S997">
-            <v>65002104</v>
+            <v>11610501</v>
           </cell>
         </row>
         <row r="998">
           <cell r="C998">
-            <v>13002105</v>
-          </cell>
-          <cell r="S998">
-            <v>65002105</v>
+            <v>11610502</v>
           </cell>
         </row>
         <row r="999">
           <cell r="C999">
-            <v>13003001</v>
-          </cell>
-          <cell r="S999">
-            <v>65003001</v>
+            <v>11610503</v>
           </cell>
         </row>
         <row r="1000">
           <cell r="C1000">
-            <v>13003002</v>
-          </cell>
-          <cell r="S1000">
-            <v>65003002</v>
+            <v>11610601</v>
           </cell>
         </row>
         <row r="1001">
           <cell r="C1001">
-            <v>13003003</v>
-          </cell>
-          <cell r="S1001">
-            <v>65003003</v>
+            <v>11610602</v>
           </cell>
         </row>
         <row r="1002">
           <cell r="C1002">
-            <v>13003004</v>
-          </cell>
-          <cell r="S1002">
-            <v>65003004</v>
+            <v>11610603</v>
           </cell>
         </row>
         <row r="1003">
           <cell r="C1003">
-            <v>13003005</v>
-          </cell>
-          <cell r="S1003">
-            <v>65003005</v>
+            <v>11610701</v>
           </cell>
         </row>
         <row r="1004">
           <cell r="C1004">
-            <v>13003006</v>
-          </cell>
-          <cell r="S1004">
-            <v>65003006</v>
+            <v>11610702</v>
           </cell>
         </row>
         <row r="1005">
           <cell r="C1005">
-            <v>13003101</v>
-          </cell>
-          <cell r="S1005">
-            <v>65003101</v>
+            <v>11610703</v>
           </cell>
         </row>
         <row r="1006">
           <cell r="C1006">
-            <v>13003102</v>
+            <v>13001001</v>
           </cell>
           <cell r="S1006">
-            <v>65003102</v>
+            <v>65001001</v>
           </cell>
         </row>
         <row r="1007">
           <cell r="C1007">
-            <v>13003103</v>
+            <v>13001002</v>
           </cell>
           <cell r="S1007">
-            <v>65003103</v>
+            <v>65001002</v>
           </cell>
         </row>
         <row r="1008">
           <cell r="C1008">
-            <v>13003104</v>
+            <v>13001003</v>
           </cell>
           <cell r="S1008">
-            <v>65003104</v>
+            <v>65001003</v>
           </cell>
         </row>
         <row r="1009">
           <cell r="C1009">
-            <v>13003105</v>
+            <v>13001004</v>
           </cell>
           <cell r="S1009">
-            <v>65003105</v>
+            <v>65001004</v>
           </cell>
         </row>
         <row r="1010">
           <cell r="C1010">
-            <v>13004001</v>
+            <v>13001005</v>
           </cell>
           <cell r="S1010">
-            <v>65004001</v>
+            <v>65001005</v>
           </cell>
         </row>
         <row r="1011">
           <cell r="C1011">
-            <v>13004002</v>
+            <v>13001006</v>
           </cell>
           <cell r="S1011">
-            <v>65004002</v>
+            <v>65001006</v>
           </cell>
         </row>
         <row r="1012">
           <cell r="C1012">
-            <v>13004003</v>
+            <v>13001101</v>
           </cell>
           <cell r="S1012">
-            <v>65004003</v>
+            <v>65001101</v>
           </cell>
         </row>
         <row r="1013">
           <cell r="C1013">
-            <v>13004004</v>
+            <v>13001102</v>
           </cell>
           <cell r="S1013">
-            <v>65004004</v>
+            <v>65001102</v>
           </cell>
         </row>
         <row r="1014">
           <cell r="C1014">
-            <v>13004005</v>
+            <v>13001103</v>
           </cell>
           <cell r="S1014">
-            <v>65004005</v>
+            <v>65001103</v>
           </cell>
         </row>
         <row r="1015">
           <cell r="C1015">
-            <v>13004006</v>
+            <v>13001104</v>
           </cell>
           <cell r="S1015">
-            <v>65004006</v>
+            <v>65001104</v>
           </cell>
         </row>
         <row r="1016">
           <cell r="C1016">
-            <v>13004101</v>
+            <v>13001105</v>
           </cell>
           <cell r="S1016">
-            <v>65004101</v>
+            <v>65001105</v>
           </cell>
         </row>
         <row r="1017">
           <cell r="C1017">
-            <v>13004102</v>
+            <v>13002001</v>
           </cell>
           <cell r="S1017">
-            <v>65004102</v>
+            <v>65002001</v>
           </cell>
         </row>
         <row r="1018">
           <cell r="C1018">
-            <v>13004103</v>
+            <v>13002002</v>
           </cell>
           <cell r="S1018">
-            <v>65004103</v>
+            <v>65002002</v>
           </cell>
         </row>
         <row r="1019">
           <cell r="C1019">
-            <v>13004104</v>
+            <v>13002003</v>
           </cell>
           <cell r="S1019">
-            <v>65004104</v>
+            <v>65002003</v>
           </cell>
         </row>
         <row r="1020">
           <cell r="C1020">
-            <v>13004105</v>
+            <v>13002004</v>
           </cell>
           <cell r="S1020">
-            <v>65004105</v>
+            <v>65002004</v>
           </cell>
         </row>
         <row r="1021">
           <cell r="C1021">
-            <v>13005001</v>
+            <v>13002005</v>
           </cell>
           <cell r="S1021">
-            <v>65005001</v>
+            <v>65002005</v>
           </cell>
         </row>
         <row r="1022">
           <cell r="C1022">
-            <v>13005002</v>
+            <v>13002006</v>
           </cell>
           <cell r="S1022">
-            <v>65005002</v>
+            <v>65002006</v>
           </cell>
         </row>
         <row r="1023">
           <cell r="C1023">
-            <v>13005003</v>
+            <v>13002101</v>
           </cell>
           <cell r="S1023">
-            <v>65005003</v>
+            <v>65002101</v>
           </cell>
         </row>
         <row r="1024">
           <cell r="C1024">
-            <v>13005004</v>
+            <v>13002102</v>
           </cell>
           <cell r="S1024">
-            <v>65005004</v>
+            <v>65002102</v>
           </cell>
         </row>
         <row r="1025">
           <cell r="C1025">
-            <v>13005005</v>
+            <v>13002103</v>
           </cell>
           <cell r="S1025">
-            <v>65005005</v>
+            <v>65002103</v>
           </cell>
         </row>
         <row r="1026">
           <cell r="C1026">
-            <v>13005006</v>
+            <v>13002104</v>
           </cell>
           <cell r="S1026">
-            <v>65005006</v>
+            <v>65002104</v>
           </cell>
         </row>
         <row r="1027">
           <cell r="C1027">
-            <v>13005101</v>
+            <v>13002105</v>
           </cell>
           <cell r="S1027">
-            <v>65005101</v>
+            <v>65002105</v>
           </cell>
         </row>
         <row r="1028">
           <cell r="C1028">
-            <v>13005102</v>
+            <v>13003001</v>
           </cell>
           <cell r="S1028">
-            <v>65005102</v>
+            <v>65003001</v>
           </cell>
         </row>
         <row r="1029">
           <cell r="C1029">
-            <v>13005103</v>
+            <v>13003002</v>
           </cell>
           <cell r="S1029">
-            <v>65005103</v>
+            <v>65003002</v>
           </cell>
         </row>
         <row r="1030">
           <cell r="C1030">
-            <v>13005104</v>
+            <v>13003003</v>
           </cell>
           <cell r="S1030">
-            <v>65005104</v>
+            <v>65003003</v>
           </cell>
         </row>
         <row r="1031">
           <cell r="C1031">
-            <v>13005105</v>
+            <v>13003004</v>
           </cell>
           <cell r="S1031">
-            <v>65005105</v>
+            <v>65003004</v>
           </cell>
         </row>
         <row r="1032">
           <cell r="C1032">
-            <v>13006001</v>
+            <v>13003005</v>
           </cell>
           <cell r="S1032">
-            <v>65006001</v>
+            <v>65003005</v>
           </cell>
         </row>
         <row r="1033">
           <cell r="C1033">
-            <v>13006002</v>
+            <v>13003006</v>
           </cell>
           <cell r="S1033">
-            <v>65006002</v>
+            <v>65003006</v>
           </cell>
         </row>
         <row r="1034">
           <cell r="C1034">
-            <v>13006003</v>
+            <v>13003101</v>
           </cell>
           <cell r="S1034">
-            <v>65006003</v>
+            <v>65003101</v>
           </cell>
         </row>
         <row r="1035">
           <cell r="C1035">
-            <v>13006004</v>
+            <v>13003102</v>
           </cell>
           <cell r="S1035">
-            <v>65006004</v>
+            <v>65003102</v>
           </cell>
         </row>
         <row r="1036">
           <cell r="C1036">
-            <v>13009001</v>
+            <v>13003103</v>
           </cell>
-          <cell r="S1036" t="str">
-            <v>4;20</v>
+          <cell r="S1036">
+            <v>65003103</v>
           </cell>
         </row>
         <row r="1037">
           <cell r="C1037">
-            <v>13009002</v>
+            <v>13003104</v>
           </cell>
-          <cell r="S1037" t="str">
-            <v>5;20</v>
+          <cell r="S1037">
+            <v>65003104</v>
           </cell>
         </row>
         <row r="1038">
           <cell r="C1038">
-            <v>14000001</v>
+            <v>13003105</v>
+          </cell>
+          <cell r="S1038">
+            <v>65003105</v>
           </cell>
         </row>
         <row r="1039">
           <cell r="C1039">
-            <v>14000002</v>
+            <v>13004001</v>
+          </cell>
+          <cell r="S1039">
+            <v>65004001</v>
           </cell>
         </row>
         <row r="1040">
           <cell r="C1040">
-            <v>14000003</v>
+            <v>13004002</v>
+          </cell>
+          <cell r="S1040">
+            <v>65004002</v>
           </cell>
         </row>
         <row r="1041">
           <cell r="C1041">
-            <v>14000004</v>
+            <v>13004003</v>
+          </cell>
+          <cell r="S1041">
+            <v>65004003</v>
           </cell>
         </row>
         <row r="1042">
           <cell r="C1042">
-            <v>14000005</v>
+            <v>13004004</v>
+          </cell>
+          <cell r="S1042">
+            <v>65004004</v>
           </cell>
         </row>
         <row r="1043">
           <cell r="C1043">
-            <v>14010001</v>
+            <v>13004005</v>
+          </cell>
+          <cell r="S1043">
+            <v>65004005</v>
           </cell>
         </row>
         <row r="1044">
           <cell r="C1044">
-            <v>14010002</v>
+            <v>13004006</v>
+          </cell>
+          <cell r="S1044">
+            <v>65004006</v>
           </cell>
         </row>
         <row r="1045">
           <cell r="C1045">
-            <v>14010003</v>
+            <v>13004101</v>
+          </cell>
+          <cell r="S1045">
+            <v>65004101</v>
           </cell>
         </row>
         <row r="1046">
           <cell r="C1046">
-            <v>14010004</v>
+            <v>13004102</v>
+          </cell>
+          <cell r="S1046">
+            <v>65004102</v>
           </cell>
         </row>
         <row r="1047">
           <cell r="C1047">
-            <v>14010005</v>
+            <v>13004103</v>
+          </cell>
+          <cell r="S1047">
+            <v>65004103</v>
           </cell>
         </row>
         <row r="1048">
           <cell r="C1048">
-            <v>14010006</v>
+            <v>13004104</v>
+          </cell>
+          <cell r="S1048">
+            <v>65004104</v>
           </cell>
         </row>
         <row r="1049">
           <cell r="C1049">
-            <v>14010007</v>
+            <v>13004105</v>
+          </cell>
+          <cell r="S1049">
+            <v>65004105</v>
           </cell>
         </row>
         <row r="1050">
           <cell r="C1050">
-            <v>14010008</v>
+            <v>13005001</v>
+          </cell>
+          <cell r="S1050">
+            <v>65005001</v>
           </cell>
         </row>
         <row r="1051">
           <cell r="C1051">
-            <v>14010009</v>
+            <v>13005002</v>
+          </cell>
+          <cell r="S1051">
+            <v>65005002</v>
           </cell>
         </row>
         <row r="1052">
           <cell r="C1052">
-            <v>14010010</v>
+            <v>13005003</v>
+          </cell>
+          <cell r="S1052">
+            <v>65005003</v>
           </cell>
         </row>
         <row r="1053">
           <cell r="C1053">
-            <v>14010011</v>
+            <v>13005004</v>
+          </cell>
+          <cell r="S1053">
+            <v>65005004</v>
           </cell>
         </row>
         <row r="1054">
           <cell r="C1054">
-            <v>14010012</v>
+            <v>13005005</v>
+          </cell>
+          <cell r="S1054">
+            <v>65005005</v>
           </cell>
         </row>
         <row r="1055">
           <cell r="C1055">
-            <v>14020001</v>
+            <v>13005006</v>
+          </cell>
+          <cell r="S1055">
+            <v>65005006</v>
           </cell>
         </row>
         <row r="1056">
           <cell r="C1056">
-            <v>14020002</v>
+            <v>13005101</v>
+          </cell>
+          <cell r="S1056">
+            <v>65005101</v>
           </cell>
         </row>
         <row r="1057">
           <cell r="C1057">
-            <v>14020003</v>
+            <v>13005102</v>
+          </cell>
+          <cell r="S1057">
+            <v>65005102</v>
           </cell>
         </row>
         <row r="1058">
           <cell r="C1058">
-            <v>14020004</v>
+            <v>13005103</v>
+          </cell>
+          <cell r="S1058">
+            <v>65005103</v>
           </cell>
         </row>
         <row r="1059">
           <cell r="C1059">
-            <v>14020005</v>
+            <v>13005104</v>
+          </cell>
+          <cell r="S1059">
+            <v>65005104</v>
           </cell>
         </row>
         <row r="1060">
           <cell r="C1060">
-            <v>14020006</v>
+            <v>13005105</v>
+          </cell>
+          <cell r="S1060">
+            <v>65005105</v>
           </cell>
         </row>
         <row r="1061">
           <cell r="C1061">
-            <v>14020007</v>
+            <v>13006001</v>
+          </cell>
+          <cell r="S1061">
+            <v>65006001</v>
           </cell>
         </row>
         <row r="1062">
           <cell r="C1062">
-            <v>14020008</v>
+            <v>13006002</v>
+          </cell>
+          <cell r="S1062">
+            <v>65006002</v>
           </cell>
         </row>
         <row r="1063">
           <cell r="C1063">
-            <v>14020009</v>
+            <v>13006003</v>
+          </cell>
+          <cell r="S1063">
+            <v>65006003</v>
           </cell>
         </row>
         <row r="1064">
           <cell r="C1064">
-            <v>14020010</v>
+            <v>13006004</v>
+          </cell>
+          <cell r="S1064">
+            <v>65006004</v>
           </cell>
         </row>
         <row r="1065">
           <cell r="C1065">
-            <v>14020011</v>
+            <v>13009001</v>
+          </cell>
+          <cell r="S1065" t="str">
+            <v>4;20</v>
           </cell>
         </row>
         <row r="1066">
           <cell r="C1066">
-            <v>14020012</v>
+            <v>13009002</v>
+          </cell>
+          <cell r="S1066" t="str">
+            <v>5;20</v>
           </cell>
         </row>
         <row r="1067">
           <cell r="C1067">
-            <v>14020013</v>
+            <v>14000001</v>
           </cell>
         </row>
         <row r="1068">
           <cell r="C1068">
-            <v>14030001</v>
+            <v>14000002</v>
           </cell>
         </row>
         <row r="1069">
           <cell r="C1069">
-            <v>14030002</v>
+            <v>14000003</v>
           </cell>
         </row>
         <row r="1070">
           <cell r="C1070">
-            <v>14030003</v>
+            <v>14000004</v>
           </cell>
         </row>
         <row r="1071">
           <cell r="C1071">
-            <v>14030004</v>
+            <v>14000005</v>
           </cell>
         </row>
         <row r="1072">
           <cell r="C1072">
-            <v>14030005</v>
+            <v>14010001</v>
           </cell>
         </row>
         <row r="1073">
           <cell r="C1073">
-            <v>14030006</v>
+            <v>14010002</v>
           </cell>
         </row>
         <row r="1074">
           <cell r="C1074">
-            <v>14030007</v>
+            <v>14010003</v>
           </cell>
         </row>
         <row r="1075">
           <cell r="C1075">
-            <v>14030008</v>
+            <v>14010004</v>
           </cell>
         </row>
         <row r="1076">
           <cell r="C1076">
-            <v>14030009</v>
+            <v>14010005</v>
           </cell>
         </row>
         <row r="1077">
           <cell r="C1077">
-            <v>14030010</v>
+            <v>14010006</v>
           </cell>
         </row>
         <row r="1078">
           <cell r="C1078">
-            <v>14030011</v>
+            <v>14010007</v>
           </cell>
         </row>
         <row r="1079">
           <cell r="C1079">
-            <v>14030012</v>
+            <v>14010008</v>
           </cell>
         </row>
         <row r="1080">
           <cell r="C1080">
-            <v>14030013</v>
+            <v>14010009</v>
           </cell>
         </row>
         <row r="1081">
           <cell r="C1081">
-            <v>14040001</v>
+            <v>14010010</v>
           </cell>
         </row>
         <row r="1082">
           <cell r="C1082">
-            <v>14040002</v>
+            <v>14010011</v>
           </cell>
         </row>
         <row r="1083">
           <cell r="C1083">
-            <v>14040003</v>
+            <v>14010012</v>
           </cell>
         </row>
         <row r="1084">
           <cell r="C1084">
-            <v>14040004</v>
+            <v>14020001</v>
           </cell>
         </row>
         <row r="1085">
           <cell r="C1085">
-            <v>14040005</v>
+            <v>14020002</v>
           </cell>
         </row>
         <row r="1086">
           <cell r="C1086">
-            <v>14040006</v>
+            <v>14020003</v>
           </cell>
         </row>
         <row r="1087">
           <cell r="C1087">
-            <v>14040007</v>
+            <v>14020004</v>
           </cell>
         </row>
         <row r="1088">
           <cell r="C1088">
-            <v>14040008</v>
+            <v>14020005</v>
           </cell>
         </row>
         <row r="1089">
           <cell r="C1089">
-            <v>14040009</v>
+            <v>14020006</v>
           </cell>
         </row>
         <row r="1090">
           <cell r="C1090">
-            <v>14040010</v>
+            <v>14020007</v>
           </cell>
         </row>
         <row r="1091">
           <cell r="C1091">
-            <v>14040011</v>
+            <v>14020008</v>
           </cell>
         </row>
         <row r="1092">
           <cell r="C1092">
-            <v>14040012</v>
+            <v>14020009</v>
           </cell>
         </row>
         <row r="1093">
           <cell r="C1093">
-            <v>14050001</v>
+            <v>14020010</v>
           </cell>
         </row>
         <row r="1094">
           <cell r="C1094">
-            <v>14050002</v>
+            <v>14020011</v>
           </cell>
         </row>
         <row r="1095">
           <cell r="C1095">
-            <v>14050003</v>
+            <v>14020012</v>
           </cell>
         </row>
         <row r="1096">
           <cell r="C1096">
-            <v>14050004</v>
+            <v>14020013</v>
           </cell>
         </row>
         <row r="1097">
           <cell r="C1097">
-            <v>14050005</v>
+            <v>14030001</v>
           </cell>
         </row>
         <row r="1098">
           <cell r="C1098">
-            <v>14050006</v>
+            <v>14030002</v>
           </cell>
         </row>
         <row r="1099">
           <cell r="C1099">
-            <v>14050007</v>
+            <v>14030003</v>
           </cell>
         </row>
         <row r="1100">
           <cell r="C1100">
-            <v>14050008</v>
+            <v>14030004</v>
           </cell>
         </row>
         <row r="1101">
           <cell r="C1101">
-            <v>14050009</v>
+            <v>14030005</v>
           </cell>
         </row>
         <row r="1102">
           <cell r="C1102">
-            <v>14050010</v>
+            <v>14030006</v>
           </cell>
         </row>
         <row r="1103">
           <cell r="C1103">
-            <v>14050011</v>
+            <v>14030007</v>
           </cell>
         </row>
         <row r="1104">
           <cell r="C1104">
-            <v>14050012</v>
+            <v>14030008</v>
           </cell>
         </row>
         <row r="1105">
           <cell r="C1105">
-            <v>14060001</v>
+            <v>14030009</v>
           </cell>
         </row>
         <row r="1106">
           <cell r="C1106">
-            <v>14060002</v>
+            <v>14030010</v>
           </cell>
         </row>
         <row r="1107">
           <cell r="C1107">
-            <v>14060003</v>
+            <v>14030011</v>
           </cell>
         </row>
         <row r="1108">
           <cell r="C1108">
-            <v>14060004</v>
+            <v>14030012</v>
           </cell>
         </row>
         <row r="1109">
           <cell r="C1109">
-            <v>14060005</v>
+            <v>14030013</v>
           </cell>
         </row>
         <row r="1110">
           <cell r="C1110">
-            <v>14060006</v>
+            <v>14040001</v>
           </cell>
         </row>
         <row r="1111">
           <cell r="C1111">
-            <v>14070001</v>
+            <v>14040002</v>
           </cell>
         </row>
         <row r="1112">
           <cell r="C1112">
-            <v>14070002</v>
+            <v>14040003</v>
           </cell>
         </row>
         <row r="1113">
           <cell r="C1113">
-            <v>14070003</v>
+            <v>14040004</v>
           </cell>
         </row>
         <row r="1114">
           <cell r="C1114">
-            <v>14070004</v>
+            <v>14040005</v>
           </cell>
         </row>
         <row r="1115">
           <cell r="C1115">
-            <v>14080001</v>
+            <v>14040006</v>
           </cell>
         </row>
         <row r="1116">
           <cell r="C1116">
-            <v>14080002</v>
+            <v>14040007</v>
           </cell>
         </row>
         <row r="1117">
           <cell r="C1117">
-            <v>14080003</v>
+            <v>14040008</v>
           </cell>
         </row>
         <row r="1118">
           <cell r="C1118">
-            <v>14080004</v>
+            <v>14040009</v>
           </cell>
         </row>
         <row r="1119">
           <cell r="C1119">
-            <v>14090001</v>
+            <v>14040010</v>
           </cell>
         </row>
         <row r="1120">
           <cell r="C1120">
-            <v>14090002</v>
+            <v>14040011</v>
           </cell>
         </row>
         <row r="1121">
           <cell r="C1121">
-            <v>14090003</v>
+            <v>14040012</v>
           </cell>
         </row>
         <row r="1122">
           <cell r="C1122">
-            <v>14090004</v>
+            <v>14050001</v>
           </cell>
         </row>
         <row r="1123">
           <cell r="C1123">
-            <v>14100001</v>
+            <v>14050002</v>
           </cell>
         </row>
         <row r="1124">
           <cell r="C1124">
-            <v>14100002</v>
+            <v>14050003</v>
           </cell>
         </row>
         <row r="1125">
           <cell r="C1125">
-            <v>14100003</v>
+            <v>14050004</v>
           </cell>
         </row>
         <row r="1126">
           <cell r="C1126">
-            <v>14100004</v>
+            <v>14050005</v>
           </cell>
         </row>
         <row r="1127">
           <cell r="C1127">
-            <v>14100005</v>
+            <v>14050006</v>
           </cell>
         </row>
         <row r="1128">
           <cell r="C1128">
-            <v>14100006</v>
+            <v>14050007</v>
           </cell>
         </row>
         <row r="1129">
           <cell r="C1129">
-            <v>14100007</v>
+            <v>14050008</v>
           </cell>
         </row>
         <row r="1130">
           <cell r="C1130">
-            <v>14100008</v>
+            <v>14050009</v>
           </cell>
         </row>
         <row r="1131">
           <cell r="C1131">
-            <v>14100011</v>
+            <v>14050010</v>
           </cell>
         </row>
         <row r="1132">
           <cell r="C1132">
-            <v>14100012</v>
+            <v>14050011</v>
           </cell>
         </row>
         <row r="1133">
           <cell r="C1133">
-            <v>14100021</v>
+            <v>14050012</v>
           </cell>
         </row>
         <row r="1134">
           <cell r="C1134">
-            <v>14100022</v>
+            <v>14060001</v>
           </cell>
         </row>
         <row r="1135">
           <cell r="C1135">
-            <v>14100101</v>
+            <v>14060002</v>
           </cell>
         </row>
         <row r="1136">
           <cell r="C1136">
-            <v>14100102</v>
+            <v>14060003</v>
           </cell>
         </row>
         <row r="1137">
           <cell r="C1137">
-            <v>14100103</v>
+            <v>14060004</v>
           </cell>
         </row>
         <row r="1138">
           <cell r="C1138">
-            <v>14100104</v>
+            <v>14060005</v>
           </cell>
         </row>
         <row r="1139">
           <cell r="C1139">
-            <v>14100105</v>
+            <v>14060006</v>
           </cell>
         </row>
         <row r="1140">
           <cell r="C1140">
-            <v>14100106</v>
+            <v>14070001</v>
           </cell>
         </row>
         <row r="1141">
           <cell r="C1141">
-            <v>14100107</v>
+            <v>14070002</v>
           </cell>
         </row>
         <row r="1142">
           <cell r="C1142">
-            <v>14100108</v>
+            <v>14070003</v>
           </cell>
         </row>
         <row r="1143">
           <cell r="C1143">
-            <v>14100111</v>
+            <v>14070004</v>
           </cell>
         </row>
         <row r="1144">
           <cell r="C1144">
-            <v>14100112</v>
+            <v>14080001</v>
           </cell>
         </row>
         <row r="1145">
           <cell r="C1145">
-            <v>14100121</v>
+            <v>14080002</v>
           </cell>
         </row>
         <row r="1146">
           <cell r="C1146">
-            <v>14100122</v>
+            <v>14080003</v>
           </cell>
         </row>
         <row r="1147">
           <cell r="C1147">
-            <v>14100201</v>
+            <v>14080004</v>
           </cell>
         </row>
         <row r="1148">
           <cell r="C1148">
-            <v>14100202</v>
+            <v>14090001</v>
           </cell>
         </row>
         <row r="1149">
           <cell r="C1149">
-            <v>14100203</v>
+            <v>14090002</v>
           </cell>
         </row>
         <row r="1150">
           <cell r="C1150">
-            <v>14100204</v>
+            <v>14090003</v>
           </cell>
         </row>
         <row r="1151">
           <cell r="C1151">
-            <v>14100211</v>
+            <v>14090004</v>
           </cell>
         </row>
         <row r="1152">
           <cell r="C1152">
-            <v>14100221</v>
+            <v>14100001</v>
           </cell>
         </row>
         <row r="1153">
           <cell r="C1153">
-            <v>14110001</v>
+            <v>14100002</v>
           </cell>
         </row>
         <row r="1154">
           <cell r="C1154">
-            <v>14110002</v>
+            <v>14100003</v>
           </cell>
         </row>
         <row r="1155">
           <cell r="C1155">
-            <v>14110003</v>
+            <v>14100004</v>
           </cell>
         </row>
         <row r="1156">
           <cell r="C1156">
-            <v>14110004</v>
+            <v>14100005</v>
           </cell>
         </row>
         <row r="1157">
           <cell r="C1157">
-            <v>14110005</v>
+            <v>14100006</v>
           </cell>
         </row>
         <row r="1158">
           <cell r="C1158">
-            <v>14110006</v>
+            <v>14100007</v>
           </cell>
         </row>
         <row r="1159">
           <cell r="C1159">
-            <v>14110007</v>
+            <v>14100008</v>
           </cell>
         </row>
         <row r="1160">
           <cell r="C1160">
-            <v>14110008</v>
+            <v>14100011</v>
           </cell>
         </row>
         <row r="1161">
           <cell r="C1161">
-            <v>14110009</v>
+            <v>14100012</v>
           </cell>
         </row>
         <row r="1162">
           <cell r="C1162">
-            <v>14110010</v>
+            <v>14100021</v>
           </cell>
         </row>
         <row r="1163">
           <cell r="C1163">
-            <v>14110011</v>
+            <v>14100022</v>
           </cell>
         </row>
         <row r="1164">
           <cell r="C1164">
-            <v>14110012</v>
+            <v>14100101</v>
           </cell>
         </row>
         <row r="1165">
           <cell r="C1165">
-            <v>14110021</v>
+            <v>14100102</v>
           </cell>
         </row>
         <row r="1166">
           <cell r="C1166">
-            <v>14110022</v>
+            <v>14100103</v>
           </cell>
         </row>
         <row r="1167">
           <cell r="C1167">
-            <v>14110023</v>
+            <v>14100104</v>
           </cell>
         </row>
         <row r="1168">
           <cell r="C1168">
-            <v>15201001</v>
+            <v>14100105</v>
           </cell>
         </row>
         <row r="1169">
           <cell r="C1169">
-            <v>15201002</v>
+            <v>14100106</v>
           </cell>
         </row>
         <row r="1170">
           <cell r="C1170">
-            <v>15201003</v>
+            <v>14100107</v>
           </cell>
         </row>
         <row r="1171">
           <cell r="C1171">
-            <v>15201004</v>
+            <v>14100108</v>
           </cell>
         </row>
         <row r="1172">
           <cell r="C1172">
-            <v>15201005</v>
+            <v>14100111</v>
           </cell>
         </row>
         <row r="1173">
           <cell r="C1173">
-            <v>15201006</v>
+            <v>14100112</v>
           </cell>
         </row>
         <row r="1174">
           <cell r="C1174">
-            <v>15202001</v>
+            <v>14100121</v>
           </cell>
         </row>
         <row r="1175">
           <cell r="C1175">
-            <v>15202002</v>
+            <v>14100122</v>
           </cell>
         </row>
         <row r="1176">
           <cell r="C1176">
-            <v>15202003</v>
+            <v>14100201</v>
           </cell>
         </row>
         <row r="1177">
           <cell r="C1177">
-            <v>15202004</v>
+            <v>14100202</v>
           </cell>
         </row>
         <row r="1178">
           <cell r="C1178">
-            <v>15202005</v>
+            <v>14100203</v>
           </cell>
         </row>
         <row r="1179">
           <cell r="C1179">
-            <v>15202006</v>
+            <v>14100204</v>
           </cell>
         </row>
         <row r="1180">
           <cell r="C1180">
-            <v>15203001</v>
+            <v>14100211</v>
           </cell>
         </row>
         <row r="1181">
           <cell r="C1181">
-            <v>15203002</v>
+            <v>14100221</v>
           </cell>
         </row>
         <row r="1182">
           <cell r="C1182">
-            <v>15203003</v>
+            <v>14110001</v>
           </cell>
         </row>
         <row r="1183">
           <cell r="C1183">
-            <v>15203004</v>
+            <v>14110002</v>
           </cell>
         </row>
         <row r="1184">
           <cell r="C1184">
-            <v>15203005</v>
+            <v>14110003</v>
           </cell>
         </row>
         <row r="1185">
           <cell r="C1185">
-            <v>15203006</v>
+            <v>14110004</v>
           </cell>
         </row>
         <row r="1186">
           <cell r="C1186">
-            <v>15204001</v>
+            <v>14110005</v>
           </cell>
         </row>
         <row r="1187">
           <cell r="C1187">
-            <v>15204002</v>
+            <v>14110006</v>
           </cell>
         </row>
         <row r="1188">
           <cell r="C1188">
-            <v>15204003</v>
+            <v>14110007</v>
           </cell>
         </row>
         <row r="1189">
           <cell r="C1189">
-            <v>15204004</v>
+            <v>14110008</v>
           </cell>
         </row>
         <row r="1190">
           <cell r="C1190">
-            <v>15204005</v>
+            <v>14110009</v>
           </cell>
         </row>
         <row r="1191">
           <cell r="C1191">
-            <v>15204006</v>
+            <v>14110010</v>
           </cell>
         </row>
         <row r="1192">
           <cell r="C1192">
-            <v>15205001</v>
+            <v>14110011</v>
           </cell>
         </row>
         <row r="1193">
           <cell r="C1193">
-            <v>15205002</v>
+            <v>14110012</v>
           </cell>
         </row>
         <row r="1194">
           <cell r="C1194">
-            <v>15205003</v>
+            <v>14110021</v>
           </cell>
         </row>
         <row r="1195">
           <cell r="C1195">
-            <v>15205004</v>
+            <v>14110022</v>
           </cell>
         </row>
         <row r="1196">
           <cell r="C1196">
-            <v>15205005</v>
+            <v>14110023</v>
           </cell>
         </row>
         <row r="1197">
           <cell r="C1197">
-            <v>15205006</v>
+            <v>15201001</v>
           </cell>
         </row>
         <row r="1198">
           <cell r="C1198">
-            <v>15205007</v>
+            <v>15201002</v>
           </cell>
         </row>
         <row r="1199">
           <cell r="C1199">
-            <v>15206001</v>
+            <v>15201003</v>
           </cell>
         </row>
         <row r="1200">
           <cell r="C1200">
-            <v>15206002</v>
+            <v>15201004</v>
           </cell>
         </row>
         <row r="1201">
           <cell r="C1201">
-            <v>15206003</v>
+            <v>15201005</v>
           </cell>
         </row>
         <row r="1202">
           <cell r="C1202">
-            <v>15207001</v>
+            <v>15201006</v>
           </cell>
         </row>
         <row r="1203">
           <cell r="C1203">
-            <v>15207002</v>
+            <v>15202001</v>
           </cell>
         </row>
         <row r="1204">
           <cell r="C1204">
-            <v>15207003</v>
+            <v>15202002</v>
           </cell>
         </row>
         <row r="1205">
           <cell r="C1205">
-            <v>15208001</v>
+            <v>15202003</v>
           </cell>
         </row>
         <row r="1206">
           <cell r="C1206">
-            <v>15208002</v>
+            <v>15202004</v>
           </cell>
         </row>
         <row r="1207">
           <cell r="C1207">
-            <v>15208003</v>
+            <v>15202005</v>
           </cell>
         </row>
         <row r="1208">
           <cell r="C1208">
-            <v>15209001</v>
+            <v>15202006</v>
           </cell>
         </row>
         <row r="1209">
           <cell r="C1209">
-            <v>15209002</v>
+            <v>15203001</v>
           </cell>
         </row>
         <row r="1210">
           <cell r="C1210">
-            <v>15210001</v>
+            <v>15203002</v>
           </cell>
         </row>
         <row r="1211">
           <cell r="C1211">
-            <v>15210002</v>
+            <v>15203003</v>
           </cell>
         </row>
         <row r="1212">
           <cell r="C1212">
-            <v>15210003</v>
+            <v>15203004</v>
           </cell>
         </row>
         <row r="1213">
           <cell r="C1213">
-            <v>15210004</v>
+            <v>15203005</v>
           </cell>
         </row>
         <row r="1214">
           <cell r="C1214">
-            <v>15210011</v>
+            <v>15203006</v>
           </cell>
         </row>
         <row r="1215">
           <cell r="C1215">
-            <v>15210012</v>
+            <v>15204001</v>
           </cell>
         </row>
         <row r="1216">
           <cell r="C1216">
-            <v>15210101</v>
+            <v>15204002</v>
           </cell>
         </row>
         <row r="1217">
           <cell r="C1217">
-            <v>15210102</v>
+            <v>15204003</v>
           </cell>
         </row>
         <row r="1218">
           <cell r="C1218">
-            <v>15210103</v>
+            <v>15204004</v>
           </cell>
         </row>
         <row r="1219">
           <cell r="C1219">
-            <v>15210104</v>
+            <v>15204005</v>
           </cell>
         </row>
         <row r="1220">
           <cell r="C1220">
-            <v>15210111</v>
+            <v>15204006</v>
           </cell>
         </row>
         <row r="1221">
           <cell r="C1221">
-            <v>15210112</v>
+            <v>15205001</v>
           </cell>
         </row>
         <row r="1222">
           <cell r="C1222">
-            <v>15210201</v>
+            <v>15205002</v>
           </cell>
         </row>
         <row r="1223">
           <cell r="C1223">
-            <v>15210202</v>
+            <v>15205003</v>
           </cell>
         </row>
         <row r="1224">
           <cell r="C1224">
-            <v>15210211</v>
+            <v>15205004</v>
           </cell>
         </row>
         <row r="1225">
           <cell r="C1225">
-            <v>15211001</v>
+            <v>15205005</v>
           </cell>
         </row>
         <row r="1226">
           <cell r="C1226">
-            <v>15211002</v>
+            <v>15205006</v>
           </cell>
         </row>
         <row r="1227">
           <cell r="C1227">
-            <v>15211003</v>
+            <v>15205007</v>
           </cell>
         </row>
         <row r="1228">
           <cell r="C1228">
-            <v>15211004</v>
+            <v>15206001</v>
           </cell>
         </row>
         <row r="1229">
           <cell r="C1229">
-            <v>15211005</v>
+            <v>15206002</v>
           </cell>
         </row>
         <row r="1230">
           <cell r="C1230">
-            <v>15211006</v>
+            <v>15206003</v>
           </cell>
         </row>
         <row r="1231">
           <cell r="C1231">
-            <v>15211011</v>
+            <v>15207001</v>
           </cell>
         </row>
         <row r="1232">
           <cell r="C1232">
-            <v>15211012</v>
+            <v>15207002</v>
           </cell>
         </row>
         <row r="1233">
           <cell r="C1233">
-            <v>15211013</v>
+            <v>15207003</v>
           </cell>
         </row>
         <row r="1234">
           <cell r="C1234">
-            <v>15301001</v>
+            <v>15208001</v>
           </cell>
         </row>
         <row r="1235">
           <cell r="C1235">
-            <v>15301002</v>
+            <v>15208002</v>
           </cell>
         </row>
         <row r="1236">
           <cell r="C1236">
-            <v>15301003</v>
+            <v>15208003</v>
           </cell>
         </row>
         <row r="1237">
           <cell r="C1237">
-            <v>15301004</v>
+            <v>15209001</v>
           </cell>
         </row>
         <row r="1238">
           <cell r="C1238">
-            <v>15301005</v>
+            <v>15209002</v>
           </cell>
         </row>
         <row r="1239">
           <cell r="C1239">
-            <v>15301006</v>
+            <v>15210001</v>
           </cell>
         </row>
         <row r="1240">
           <cell r="C1240">
-            <v>15302001</v>
+            <v>15210002</v>
           </cell>
         </row>
         <row r="1241">
           <cell r="C1241">
-            <v>15302002</v>
+            <v>15210003</v>
           </cell>
         </row>
         <row r="1242">
           <cell r="C1242">
-            <v>15302003</v>
+            <v>15210004</v>
           </cell>
         </row>
         <row r="1243">
           <cell r="C1243">
-            <v>15302004</v>
+            <v>15210011</v>
           </cell>
         </row>
         <row r="1244">
           <cell r="C1244">
-            <v>15302005</v>
+            <v>15210012</v>
           </cell>
         </row>
         <row r="1245">
           <cell r="C1245">
-            <v>15302006</v>
+            <v>15210101</v>
           </cell>
         </row>
         <row r="1246">
           <cell r="C1246">
-            <v>15302007</v>
+            <v>15210102</v>
           </cell>
         </row>
         <row r="1247">
           <cell r="C1247">
-            <v>15303001</v>
+            <v>15210103</v>
           </cell>
         </row>
         <row r="1248">
           <cell r="C1248">
-            <v>15303002</v>
+            <v>15210104</v>
           </cell>
         </row>
         <row r="1249">
           <cell r="C1249">
-            <v>15303003</v>
+            <v>15210111</v>
           </cell>
         </row>
         <row r="1250">
           <cell r="C1250">
-            <v>15303004</v>
+            <v>15210112</v>
           </cell>
         </row>
         <row r="1251">
           <cell r="C1251">
-            <v>15303005</v>
+            <v>15210201</v>
           </cell>
         </row>
         <row r="1252">
           <cell r="C1252">
-            <v>15303006</v>
+            <v>15210202</v>
           </cell>
         </row>
         <row r="1253">
           <cell r="C1253">
-            <v>15304001</v>
+            <v>15210211</v>
           </cell>
         </row>
         <row r="1254">
           <cell r="C1254">
-            <v>15304002</v>
+            <v>15211001</v>
           </cell>
         </row>
         <row r="1255">
           <cell r="C1255">
-            <v>15304003</v>
+            <v>15211002</v>
           </cell>
         </row>
         <row r="1256">
           <cell r="C1256">
-            <v>15304004</v>
+            <v>15211003</v>
           </cell>
         </row>
         <row r="1257">
           <cell r="C1257">
-            <v>15304005</v>
+            <v>15211004</v>
           </cell>
         </row>
         <row r="1258">
           <cell r="C1258">
-            <v>15304006</v>
+            <v>15211005</v>
           </cell>
         </row>
         <row r="1259">
           <cell r="C1259">
-            <v>15305001</v>
+            <v>15211006</v>
           </cell>
         </row>
         <row r="1260">
           <cell r="C1260">
-            <v>15305002</v>
+            <v>15211011</v>
           </cell>
         </row>
         <row r="1261">
           <cell r="C1261">
-            <v>15305003</v>
+            <v>15211012</v>
           </cell>
         </row>
         <row r="1262">
           <cell r="C1262">
-            <v>15305004</v>
+            <v>15211013</v>
           </cell>
         </row>
         <row r="1263">
           <cell r="C1263">
-            <v>15305005</v>
+            <v>15301001</v>
           </cell>
         </row>
         <row r="1264">
           <cell r="C1264">
-            <v>15305006</v>
+            <v>15301002</v>
           </cell>
         </row>
         <row r="1265">
           <cell r="C1265">
-            <v>15306001</v>
+            <v>15301003</v>
           </cell>
         </row>
         <row r="1266">
           <cell r="C1266">
-            <v>15306002</v>
+            <v>15301004</v>
           </cell>
         </row>
         <row r="1267">
           <cell r="C1267">
-            <v>15306003</v>
+            <v>15301005</v>
           </cell>
         </row>
         <row r="1268">
           <cell r="C1268">
-            <v>15307001</v>
+            <v>15301006</v>
           </cell>
         </row>
         <row r="1269">
           <cell r="C1269">
-            <v>15307002</v>
+            <v>15302001</v>
           </cell>
         </row>
         <row r="1270">
           <cell r="C1270">
-            <v>15308001</v>
+            <v>15302002</v>
           </cell>
         </row>
         <row r="1271">
           <cell r="C1271">
-            <v>15308002</v>
+            <v>15302003</v>
           </cell>
         </row>
         <row r="1272">
           <cell r="C1272">
-            <v>15308003</v>
+            <v>15302004</v>
           </cell>
         </row>
         <row r="1273">
           <cell r="C1273">
-            <v>15308004</v>
+            <v>15302005</v>
           </cell>
         </row>
         <row r="1274">
           <cell r="C1274">
-            <v>15309001</v>
+            <v>15302006</v>
           </cell>
         </row>
         <row r="1275">
           <cell r="C1275">
-            <v>15309002</v>
+            <v>15302007</v>
           </cell>
         </row>
         <row r="1276">
           <cell r="C1276">
-            <v>15309003</v>
+            <v>15303001</v>
           </cell>
         </row>
         <row r="1277">
           <cell r="C1277">
-            <v>15310001</v>
+            <v>15303002</v>
           </cell>
         </row>
         <row r="1278">
           <cell r="C1278">
-            <v>15310002</v>
+            <v>15303003</v>
           </cell>
         </row>
         <row r="1279">
           <cell r="C1279">
-            <v>15310003</v>
+            <v>15303004</v>
           </cell>
         </row>
         <row r="1280">
           <cell r="C1280">
-            <v>15310004</v>
+            <v>15303005</v>
           </cell>
         </row>
         <row r="1281">
           <cell r="C1281">
-            <v>15310011</v>
+            <v>15303006</v>
           </cell>
         </row>
         <row r="1282">
           <cell r="C1282">
-            <v>15310012</v>
+            <v>15304001</v>
           </cell>
         </row>
         <row r="1283">
           <cell r="C1283">
-            <v>15310101</v>
+            <v>15304002</v>
           </cell>
         </row>
         <row r="1284">
           <cell r="C1284">
-            <v>15310102</v>
+            <v>15304003</v>
           </cell>
         </row>
         <row r="1285">
           <cell r="C1285">
-            <v>15310103</v>
+            <v>15304004</v>
           </cell>
         </row>
         <row r="1286">
           <cell r="C1286">
-            <v>15310104</v>
+            <v>15304005</v>
           </cell>
         </row>
         <row r="1287">
           <cell r="C1287">
-            <v>15310111</v>
+            <v>15304006</v>
           </cell>
         </row>
         <row r="1288">
           <cell r="C1288">
-            <v>15310112</v>
+            <v>15305001</v>
           </cell>
         </row>
         <row r="1289">
           <cell r="C1289">
-            <v>15310201</v>
+            <v>15305002</v>
           </cell>
         </row>
         <row r="1290">
           <cell r="C1290">
-            <v>15310202</v>
+            <v>15305003</v>
           </cell>
         </row>
         <row r="1291">
           <cell r="C1291">
-            <v>15310211</v>
+            <v>15305004</v>
           </cell>
         </row>
         <row r="1292">
           <cell r="C1292">
-            <v>15311001</v>
+            <v>15305005</v>
           </cell>
         </row>
         <row r="1293">
           <cell r="C1293">
-            <v>15311002</v>
+            <v>15305006</v>
           </cell>
         </row>
         <row r="1294">
           <cell r="C1294">
-            <v>15311003</v>
+            <v>15306001</v>
           </cell>
         </row>
         <row r="1295">
           <cell r="C1295">
-            <v>15311004</v>
+            <v>15306002</v>
           </cell>
         </row>
         <row r="1296">
           <cell r="C1296">
-            <v>15311005</v>
+            <v>15306003</v>
           </cell>
         </row>
         <row r="1297">
           <cell r="C1297">
-            <v>15311006</v>
+            <v>15307001</v>
           </cell>
         </row>
         <row r="1298">
           <cell r="C1298">
-            <v>15311011</v>
+            <v>15307002</v>
           </cell>
         </row>
         <row r="1299">
           <cell r="C1299">
-            <v>15311012</v>
+            <v>15308001</v>
           </cell>
         </row>
         <row r="1300">
           <cell r="C1300">
-            <v>15311013</v>
+            <v>15308002</v>
           </cell>
         </row>
         <row r="1301">
           <cell r="C1301">
-            <v>15401001</v>
+            <v>15308003</v>
           </cell>
         </row>
         <row r="1302">
           <cell r="C1302">
-            <v>15401002</v>
+            <v>15308004</v>
           </cell>
         </row>
         <row r="1303">
           <cell r="C1303">
-            <v>15401003</v>
+            <v>15309001</v>
           </cell>
         </row>
         <row r="1304">
           <cell r="C1304">
-            <v>15401004</v>
+            <v>15309002</v>
           </cell>
         </row>
         <row r="1305">
           <cell r="C1305">
-            <v>15401005</v>
+            <v>15309003</v>
           </cell>
         </row>
         <row r="1306">
           <cell r="C1306">
-            <v>15401006</v>
+            <v>15310001</v>
           </cell>
         </row>
         <row r="1307">
           <cell r="C1307">
-            <v>15401007</v>
+            <v>15310002</v>
           </cell>
         </row>
         <row r="1308">
           <cell r="C1308">
-            <v>15402001</v>
+            <v>15310003</v>
           </cell>
         </row>
         <row r="1309">
           <cell r="C1309">
-            <v>15402002</v>
+            <v>15310004</v>
           </cell>
         </row>
         <row r="1310">
           <cell r="C1310">
-            <v>15402003</v>
+            <v>15310011</v>
           </cell>
         </row>
         <row r="1311">
           <cell r="C1311">
-            <v>15402004</v>
+            <v>15310012</v>
           </cell>
         </row>
         <row r="1312">
           <cell r="C1312">
-            <v>15402005</v>
+            <v>15310101</v>
           </cell>
         </row>
         <row r="1313">
           <cell r="C1313">
-            <v>15402006</v>
+            <v>15310102</v>
           </cell>
         </row>
         <row r="1314">
           <cell r="C1314">
-            <v>15403001</v>
+            <v>15310103</v>
           </cell>
         </row>
         <row r="1315">
           <cell r="C1315">
-            <v>15403002</v>
+            <v>15310104</v>
           </cell>
         </row>
         <row r="1316">
           <cell r="C1316">
-            <v>15403003</v>
+            <v>15310111</v>
           </cell>
         </row>
         <row r="1317">
           <cell r="C1317">
-            <v>15403004</v>
+            <v>15310112</v>
           </cell>
         </row>
         <row r="1318">
           <cell r="C1318">
-            <v>15403005</v>
+            <v>15310201</v>
           </cell>
         </row>
         <row r="1319">
           <cell r="C1319">
-            <v>15403006</v>
+            <v>15310202</v>
           </cell>
         </row>
         <row r="1320">
           <cell r="C1320">
-            <v>15404001</v>
+            <v>15310211</v>
           </cell>
         </row>
         <row r="1321">
           <cell r="C1321">
-            <v>15404002</v>
+            <v>15311001</v>
           </cell>
         </row>
         <row r="1322">
           <cell r="C1322">
-            <v>15404003</v>
+            <v>15311002</v>
           </cell>
         </row>
         <row r="1323">
           <cell r="C1323">
-            <v>15404004</v>
+            <v>15311003</v>
           </cell>
         </row>
         <row r="1324">
           <cell r="C1324">
-            <v>15404005</v>
+            <v>15311004</v>
           </cell>
         </row>
         <row r="1325">
           <cell r="C1325">
-            <v>15404006</v>
+            <v>15311005</v>
           </cell>
         </row>
         <row r="1326">
           <cell r="C1326">
-            <v>15405001</v>
+            <v>15311006</v>
           </cell>
         </row>
         <row r="1327">
           <cell r="C1327">
-            <v>15405002</v>
+            <v>15311011</v>
           </cell>
         </row>
         <row r="1328">
           <cell r="C1328">
-            <v>15405003</v>
+            <v>15311012</v>
           </cell>
         </row>
         <row r="1329">
           <cell r="C1329">
-            <v>15405004</v>
+            <v>15311013</v>
           </cell>
         </row>
         <row r="1330">
           <cell r="C1330">
-            <v>15405005</v>
+            <v>15401001</v>
           </cell>
         </row>
         <row r="1331">
           <cell r="C1331">
-            <v>15405006</v>
+            <v>15401002</v>
           </cell>
         </row>
         <row r="1332">
           <cell r="C1332">
-            <v>15406001</v>
+            <v>15401003</v>
           </cell>
         </row>
         <row r="1333">
           <cell r="C1333">
-            <v>15406002</v>
+            <v>15401004</v>
           </cell>
         </row>
       </sheetData>
@@ -36835,6 +36943,12 @@
       <c r="N2" s="3" t="s">
         <v>2980</v>
       </c>
+      <c r="P2" s="3" t="s">
+        <v>3120</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>3122</v>
+      </c>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
@@ -36871,6 +36985,12 @@
       <c r="N3" s="3" t="s">
         <v>2981</v>
       </c>
+      <c r="P3" s="3" t="s">
+        <v>3121</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>3124</v>
+      </c>
       <c r="S3" s="1"/>
       <c r="Y3" s="1" t="s">
         <v>3083</v>
@@ -36893,6 +37013,9 @@
       </c>
       <c r="N4" s="3" t="s">
         <v>2982</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>3125</v>
       </c>
       <c r="S4" s="1"/>
       <c r="Y4" s="1" t="s">
@@ -37144,14 +37267,14 @@
         <v>30</v>
       </c>
       <c r="AB9" s="1">
-        <f>Z9</f>
+        <f t="shared" ref="AB9:AB18" si="0">Z9</f>
         <v>10</v>
       </c>
       <c r="AC9" s="1">
         <v>5</v>
       </c>
       <c r="AD9" s="1">
-        <f>Z9*5</f>
+        <f t="shared" ref="AD9:AD18" si="1">Z9*5</f>
         <v>50</v>
       </c>
       <c r="AE9" s="1">
@@ -37246,7 +37369,7 @@
         <v>2</v>
       </c>
       <c r="U10" s="4">
-        <f t="shared" ref="U10:U18" si="0">V10/$M$19</f>
+        <f t="shared" ref="U10:U18" si="2">V10/$M$19</f>
         <v>8.3333333333333339</v>
       </c>
       <c r="V10" s="4">
@@ -37268,18 +37391,18 @@
         <v>25</v>
       </c>
       <c r="AA10" s="1">
-        <f t="shared" ref="AA10:AA18" si="1">Z10*3</f>
+        <f t="shared" ref="AA10:AA18" si="3">Z10*3</f>
         <v>75</v>
       </c>
       <c r="AB10" s="1">
-        <f>Z10</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="AC10" s="1">
         <v>10</v>
       </c>
       <c r="AD10" s="1">
-        <f>Z10*5</f>
+        <f t="shared" si="1"/>
         <v>125</v>
       </c>
       <c r="AE10" s="1">
@@ -37289,55 +37412,55 @@
         <v>60</v>
       </c>
       <c r="AG10" s="1">
-        <f t="shared" ref="AG10:AG18" si="2">Z10</f>
+        <f t="shared" ref="AG10:AG18" si="4">Z10</f>
         <v>25</v>
       </c>
       <c r="AI10" s="3" t="str">
-        <f t="shared" ref="AI10:AI18" si="3">"100403;"&amp;Z10&amp;"@100603;"&amp;AB10</f>
+        <f t="shared" ref="AI10:AI18" si="5">"100403;"&amp;Z10&amp;"@100603;"&amp;AB10</f>
         <v>100403;25@100603;25</v>
       </c>
       <c r="AJ10" s="3" t="str">
-        <f t="shared" ref="AJ10:AJ18" si="4">"攻击提升"&amp;Z10&amp;"点;物防提升"&amp;AB10&amp;"点"</f>
+        <f t="shared" ref="AJ10:AJ18" si="6">"攻击提升"&amp;Z10&amp;"点;物防提升"&amp;AB10&amp;"点"</f>
         <v>攻击提升25点;物防提升25点</v>
       </c>
       <c r="AK10" s="3" t="str">
-        <f t="shared" ref="AK10:AK18" si="5">"100403;"&amp;Z10&amp;"@100803;"&amp;AB10</f>
+        <f t="shared" ref="AK10:AK18" si="7">"100403;"&amp;Z10&amp;"@100803;"&amp;AB10</f>
         <v>100403;25@100803;25</v>
       </c>
       <c r="AL10" s="3" t="str">
-        <f t="shared" ref="AL10:AL18" si="6">"攻击提升"&amp;Z10&amp;"点;魔防提升"&amp;AB10&amp;"点"</f>
+        <f t="shared" ref="AL10:AL18" si="8">"攻击提升"&amp;Z10&amp;"点;魔防提升"&amp;AB10&amp;"点"</f>
         <v>攻击提升25点;魔防提升25点</v>
       </c>
       <c r="AM10" s="3" t="str">
-        <f t="shared" ref="AM10:AM18" si="7">"100403;"&amp;Z10&amp;"@100203;"&amp;AE10</f>
+        <f t="shared" ref="AM10:AM18" si="9">"100403;"&amp;Z10&amp;"@100203;"&amp;AE10</f>
         <v>100403;25@100203;60</v>
       </c>
       <c r="AN10" s="3" t="str">
-        <f t="shared" ref="AN10:AN18" si="8">"攻击提升"&amp;Z10&amp;"点;血量提升"&amp;AE10&amp;"点"</f>
+        <f t="shared" ref="AN10:AN18" si="10">"攻击提升"&amp;Z10&amp;"点;血量提升"&amp;AE10&amp;"点"</f>
         <v>攻击提升25点;血量提升60点</v>
       </c>
       <c r="AO10" s="3" t="str">
-        <f t="shared" ref="AO10:AO18" si="9">"100203;"&amp;AD10</f>
+        <f t="shared" ref="AO10:AO18" si="11">"100203;"&amp;AD10</f>
         <v>100203;125</v>
       </c>
       <c r="AP10" s="3" t="str">
-        <f t="shared" ref="AP10:AP18" si="10">"血量提升"&amp;AD10&amp;"点"</f>
+        <f t="shared" ref="AP10:AP18" si="12">"血量提升"&amp;AD10&amp;"点"</f>
         <v>血量提升125点</v>
       </c>
       <c r="AQ10" s="3" t="str">
-        <f t="shared" ref="AQ10:AQ18" si="11">"101003;"&amp;Z10&amp;"@100203;"&amp;AE10</f>
+        <f t="shared" ref="AQ10:AQ18" si="13">"101003;"&amp;Z10&amp;"@100203;"&amp;AE10</f>
         <v>101003;25@100203;60</v>
       </c>
       <c r="AR10" s="3" t="str">
-        <f t="shared" ref="AR10:AR18" si="12">"魔法提升"&amp;Z10&amp;"点;血量提升"&amp;AE10&amp;"点"</f>
+        <f t="shared" ref="AR10:AR18" si="14">"魔法提升"&amp;Z10&amp;"点;血量提升"&amp;AE10&amp;"点"</f>
         <v>魔法提升25点;血量提升60点</v>
       </c>
       <c r="AS10" s="3" t="str">
-        <f t="shared" ref="AS10:AS18" si="13">"100203;"&amp;AE10&amp;"@100603;"&amp;AC10&amp;"@100803;"&amp;AC10</f>
+        <f t="shared" ref="AS10:AS18" si="15">"100203;"&amp;AE10&amp;"@100603;"&amp;AC10&amp;"@100803;"&amp;AC10</f>
         <v>100203;60@100603;10@100803;10</v>
       </c>
       <c r="AT10" s="3" t="str">
-        <f t="shared" ref="AT10:AT18" si="14">"血量提升"&amp;AE10&amp;"点;物防提升"&amp;AC10&amp;"点"&amp;"点;魔防提升"&amp;AC10&amp;"点"</f>
+        <f t="shared" ref="AT10:AT18" si="16">"血量提升"&amp;AE10&amp;"点;物防提升"&amp;AC10&amp;"点"&amp;"点;魔防提升"&amp;AC10&amp;"点"</f>
         <v>血量提升60点;物防提升10点点;魔防提升10点</v>
       </c>
     </row>
@@ -37367,7 +37490,7 @@
         <v>3</v>
       </c>
       <c r="U11" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="V11" s="4">
@@ -37378,7 +37501,7 @@
         <v>200</v>
       </c>
       <c r="X11" s="1">
-        <f t="shared" ref="W11:X18" si="15">X10+100</f>
+        <f t="shared" ref="W11:X18" si="17">X10+100</f>
         <v>300</v>
       </c>
       <c r="Y11" s="1">
@@ -37389,78 +37512,78 @@
         <v>40</v>
       </c>
       <c r="AA11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="AB11" s="1">
-        <f>Z11</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="AC11" s="1">
         <v>15</v>
       </c>
       <c r="AD11" s="1">
-        <f>Z11*5</f>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="AE11" s="1">
-        <f>Z11*2.5</f>
+        <f t="shared" ref="AE11:AE18" si="18">Z11*2.5</f>
         <v>100</v>
       </c>
       <c r="AF11" s="1">
-        <f>Z11*2.5</f>
+        <f t="shared" ref="AF11:AF18" si="19">Z11*2.5</f>
         <v>100</v>
       </c>
       <c r="AG11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="AI11" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>100403;40@100603;40</v>
       </c>
       <c r="AJ11" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>攻击提升40点;物防提升40点</v>
       </c>
       <c r="AK11" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>100403;40@100803;40</v>
       </c>
       <c r="AL11" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>攻击提升40点;魔防提升40点</v>
       </c>
       <c r="AM11" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>100403;40@100203;100</v>
       </c>
       <c r="AN11" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>攻击提升40点;血量提升100点</v>
       </c>
       <c r="AO11" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>100203;200</v>
       </c>
       <c r="AP11" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>血量提升200点</v>
       </c>
       <c r="AQ11" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>101003;40@100203;100</v>
       </c>
       <c r="AR11" s="3" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>魔法提升40点;血量提升100点</v>
       </c>
       <c r="AS11" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>100203;100@100603;15@100803;15</v>
       </c>
       <c r="AT11" s="3" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>血量提升100点;物防提升15点点;魔防提升15点</v>
       </c>
     </row>
@@ -37499,7 +37622,7 @@
         <v>4</v>
       </c>
       <c r="U12" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="V12" s="4">
@@ -37507,11 +37630,11 @@
         <v>750</v>
       </c>
       <c r="W12" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>300</v>
       </c>
       <c r="X12" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>400</v>
       </c>
       <c r="Y12" s="1">
@@ -37522,79 +37645,79 @@
         <v>60</v>
       </c>
       <c r="AA12" s="1">
+        <f t="shared" si="3"/>
+        <v>180</v>
+      </c>
+      <c r="AB12" s="1">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="AC12" s="1">
+        <f t="shared" ref="AC12:AC18" si="20">AB12/3</f>
+        <v>20</v>
+      </c>
+      <c r="AD12" s="1">
         <f t="shared" si="1"/>
-        <v>180</v>
-      </c>
-      <c r="AB12" s="1">
-        <f>Z12</f>
+        <v>300</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" si="18"/>
+        <v>150</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" si="19"/>
+        <v>150</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="AC12" s="1">
-        <f t="shared" ref="AC12:AC18" si="16">AB12/3</f>
-        <v>20</v>
-      </c>
-      <c r="AD12" s="1">
-        <f>Z12*5</f>
-        <v>300</v>
-      </c>
-      <c r="AE12" s="1">
-        <f>Z12*2.5</f>
-        <v>150</v>
-      </c>
-      <c r="AF12" s="1">
-        <f>Z12*2.5</f>
-        <v>150</v>
-      </c>
-      <c r="AG12" s="1">
-        <f t="shared" si="2"/>
-        <v>60</v>
-      </c>
       <c r="AI12" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>100403;60@100603;60</v>
       </c>
       <c r="AJ12" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>攻击提升60点;物防提升60点</v>
       </c>
       <c r="AK12" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>100403;60@100803;60</v>
       </c>
       <c r="AL12" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>攻击提升60点;魔防提升60点</v>
       </c>
       <c r="AM12" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>100403;60@100203;150</v>
       </c>
       <c r="AN12" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>攻击提升60点;血量提升150点</v>
       </c>
       <c r="AO12" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>100203;300</v>
       </c>
       <c r="AP12" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>血量提升300点</v>
       </c>
       <c r="AQ12" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>101003;60@100203;150</v>
       </c>
       <c r="AR12" s="3" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>魔法提升60点;血量提升150点</v>
       </c>
       <c r="AS12" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>100203;150@100603;20@100803;20</v>
       </c>
       <c r="AT12" s="3" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>血量提升150点;物防提升20点点;魔防提升20点</v>
       </c>
     </row>
@@ -37631,7 +37754,7 @@
         <v>5</v>
       </c>
       <c r="U13" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="V13" s="4">
@@ -37642,7 +37765,7 @@
         <v>450</v>
       </c>
       <c r="X13" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>500</v>
       </c>
       <c r="Y13" s="1">
@@ -37653,79 +37776,79 @@
         <v>90</v>
       </c>
       <c r="AA13" s="1">
+        <f t="shared" si="3"/>
+        <v>270</v>
+      </c>
+      <c r="AB13" s="1">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="AC13" s="1">
+        <f t="shared" si="20"/>
+        <v>30</v>
+      </c>
+      <c r="AD13" s="1">
         <f t="shared" si="1"/>
-        <v>270</v>
-      </c>
-      <c r="AB13" s="1">
-        <f>Z13</f>
+        <v>450</v>
+      </c>
+      <c r="AE13" s="1">
+        <f t="shared" si="18"/>
+        <v>225</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" si="19"/>
+        <v>225</v>
+      </c>
+      <c r="AG13" s="1">
+        <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="AC13" s="1">
+      <c r="AI13" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;90@100603;90</v>
+      </c>
+      <c r="AJ13" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升90点;物防提升90点</v>
+      </c>
+      <c r="AK13" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;90@100803;90</v>
+      </c>
+      <c r="AL13" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升90点;魔防提升90点</v>
+      </c>
+      <c r="AM13" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100403;90@100203;225</v>
+      </c>
+      <c r="AN13" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>攻击提升90点;血量提升225点</v>
+      </c>
+      <c r="AO13" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>100203;450</v>
+      </c>
+      <c r="AP13" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>血量提升450点</v>
+      </c>
+      <c r="AQ13" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>101003;90@100203;225</v>
+      </c>
+      <c r="AR13" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>魔法提升90点;血量提升225点</v>
+      </c>
+      <c r="AS13" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>100203;225@100603;30@100803;30</v>
+      </c>
+      <c r="AT13" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>30</v>
-      </c>
-      <c r="AD13" s="1">
-        <f>Z13*5</f>
-        <v>450</v>
-      </c>
-      <c r="AE13" s="1">
-        <f>Z13*2.5</f>
-        <v>225</v>
-      </c>
-      <c r="AF13" s="1">
-        <f>Z13*2.5</f>
-        <v>225</v>
-      </c>
-      <c r="AG13" s="1">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-      <c r="AI13" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>100403;90@100603;90</v>
-      </c>
-      <c r="AJ13" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>攻击提升90点;物防提升90点</v>
-      </c>
-      <c r="AK13" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>100403;90@100803;90</v>
-      </c>
-      <c r="AL13" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>攻击提升90点;魔防提升90点</v>
-      </c>
-      <c r="AM13" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>100403;90@100203;225</v>
-      </c>
-      <c r="AN13" s="3" t="str">
-        <f t="shared" si="8"/>
-        <v>攻击提升90点;血量提升225点</v>
-      </c>
-      <c r="AO13" s="3" t="str">
-        <f t="shared" si="9"/>
-        <v>100203;450</v>
-      </c>
-      <c r="AP13" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>血量提升450点</v>
-      </c>
-      <c r="AQ13" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>101003;90@100203;225</v>
-      </c>
-      <c r="AR13" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>魔法提升90点;血量提升225点</v>
-      </c>
-      <c r="AS13" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>100203;225@100603;30@100803;30</v>
-      </c>
-      <c r="AT13" s="3" t="str">
-        <f t="shared" si="14"/>
         <v>血量提升225点;物防提升30点点;魔防提升30点</v>
       </c>
     </row>
@@ -37756,7 +37879,7 @@
         <v>6</v>
       </c>
       <c r="U14" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="V14" s="4">
@@ -37767,7 +37890,7 @@
         <v>600</v>
       </c>
       <c r="X14" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>600</v>
       </c>
       <c r="Y14" s="1">
@@ -37778,79 +37901,79 @@
         <v>120</v>
       </c>
       <c r="AA14" s="1">
+        <f t="shared" si="3"/>
+        <v>360</v>
+      </c>
+      <c r="AB14" s="1">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="AC14" s="1">
+        <f t="shared" si="20"/>
+        <v>40</v>
+      </c>
+      <c r="AD14" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
-      </c>
-      <c r="AB14" s="1">
-        <f>Z14</f>
+        <v>600</v>
+      </c>
+      <c r="AE14" s="1">
+        <f t="shared" si="18"/>
+        <v>300</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" si="19"/>
+        <v>300</v>
+      </c>
+      <c r="AG14" s="1">
+        <f t="shared" si="4"/>
         <v>120</v>
       </c>
-      <c r="AC14" s="1">
+      <c r="AI14" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;120@100603;120</v>
+      </c>
+      <c r="AJ14" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升120点;物防提升120点</v>
+      </c>
+      <c r="AK14" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;120@100803;120</v>
+      </c>
+      <c r="AL14" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升120点;魔防提升120点</v>
+      </c>
+      <c r="AM14" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100403;120@100203;300</v>
+      </c>
+      <c r="AN14" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>攻击提升120点;血量提升300点</v>
+      </c>
+      <c r="AO14" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>100203;600</v>
+      </c>
+      <c r="AP14" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>血量提升600点</v>
+      </c>
+      <c r="AQ14" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>101003;120@100203;300</v>
+      </c>
+      <c r="AR14" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>魔法提升120点;血量提升300点</v>
+      </c>
+      <c r="AS14" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>100203;300@100603;40@100803;40</v>
+      </c>
+      <c r="AT14" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>40</v>
-      </c>
-      <c r="AD14" s="1">
-        <f>Z14*5</f>
-        <v>600</v>
-      </c>
-      <c r="AE14" s="1">
-        <f>Z14*2.5</f>
-        <v>300</v>
-      </c>
-      <c r="AF14" s="1">
-        <f>Z14*2.5</f>
-        <v>300</v>
-      </c>
-      <c r="AG14" s="1">
-        <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="AI14" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>100403;120@100603;120</v>
-      </c>
-      <c r="AJ14" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>攻击提升120点;物防提升120点</v>
-      </c>
-      <c r="AK14" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>100403;120@100803;120</v>
-      </c>
-      <c r="AL14" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>攻击提升120点;魔防提升120点</v>
-      </c>
-      <c r="AM14" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>100403;120@100203;300</v>
-      </c>
-      <c r="AN14" s="3" t="str">
-        <f t="shared" si="8"/>
-        <v>攻击提升120点;血量提升300点</v>
-      </c>
-      <c r="AO14" s="3" t="str">
-        <f t="shared" si="9"/>
-        <v>100203;600</v>
-      </c>
-      <c r="AP14" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>血量提升600点</v>
-      </c>
-      <c r="AQ14" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>101003;120@100203;300</v>
-      </c>
-      <c r="AR14" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>魔法提升120点;血量提升300点</v>
-      </c>
-      <c r="AS14" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>100203;300@100603;40@100803;40</v>
-      </c>
-      <c r="AT14" s="3" t="str">
-        <f t="shared" si="14"/>
         <v>血量提升300点;物防提升40点点;魔防提升40点</v>
       </c>
     </row>
@@ -37881,7 +38004,7 @@
         <v>7</v>
       </c>
       <c r="U15" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>86.666666666666671</v>
       </c>
       <c r="V15" s="4">
@@ -37892,7 +38015,7 @@
         <v>800</v>
       </c>
       <c r="X15" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>700</v>
       </c>
       <c r="Y15" s="1">
@@ -37903,79 +38026,79 @@
         <v>150</v>
       </c>
       <c r="AA15" s="1">
+        <f t="shared" si="3"/>
+        <v>450</v>
+      </c>
+      <c r="AB15" s="1">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="AC15" s="1">
+        <f t="shared" si="20"/>
+        <v>50</v>
+      </c>
+      <c r="AD15" s="1">
         <f t="shared" si="1"/>
-        <v>450</v>
-      </c>
-      <c r="AB15" s="1">
-        <f>Z15</f>
+        <v>750</v>
+      </c>
+      <c r="AE15" s="1">
+        <f t="shared" si="18"/>
+        <v>375</v>
+      </c>
+      <c r="AF15" s="1">
+        <f t="shared" si="19"/>
+        <v>375</v>
+      </c>
+      <c r="AG15" s="1">
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
-      <c r="AC15" s="1">
+      <c r="AI15" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;150@100603;150</v>
+      </c>
+      <c r="AJ15" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升150点;物防提升150点</v>
+      </c>
+      <c r="AK15" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;150@100803;150</v>
+      </c>
+      <c r="AL15" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升150点;魔防提升150点</v>
+      </c>
+      <c r="AM15" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100403;150@100203;375</v>
+      </c>
+      <c r="AN15" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>攻击提升150点;血量提升375点</v>
+      </c>
+      <c r="AO15" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>100203;750</v>
+      </c>
+      <c r="AP15" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>血量提升750点</v>
+      </c>
+      <c r="AQ15" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>101003;150@100203;375</v>
+      </c>
+      <c r="AR15" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>魔法提升150点;血量提升375点</v>
+      </c>
+      <c r="AS15" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>100203;375@100603;50@100803;50</v>
+      </c>
+      <c r="AT15" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>50</v>
-      </c>
-      <c r="AD15" s="1">
-        <f>Z15*5</f>
-        <v>750</v>
-      </c>
-      <c r="AE15" s="1">
-        <f>Z15*2.5</f>
-        <v>375</v>
-      </c>
-      <c r="AF15" s="1">
-        <f>Z15*2.5</f>
-        <v>375</v>
-      </c>
-      <c r="AG15" s="1">
-        <f t="shared" si="2"/>
-        <v>150</v>
-      </c>
-      <c r="AI15" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>100403;150@100603;150</v>
-      </c>
-      <c r="AJ15" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>攻击提升150点;物防提升150点</v>
-      </c>
-      <c r="AK15" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>100403;150@100803;150</v>
-      </c>
-      <c r="AL15" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>攻击提升150点;魔防提升150点</v>
-      </c>
-      <c r="AM15" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>100403;150@100203;375</v>
-      </c>
-      <c r="AN15" s="3" t="str">
-        <f t="shared" si="8"/>
-        <v>攻击提升150点;血量提升375点</v>
-      </c>
-      <c r="AO15" s="3" t="str">
-        <f t="shared" si="9"/>
-        <v>100203;750</v>
-      </c>
-      <c r="AP15" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>血量提升750点</v>
-      </c>
-      <c r="AQ15" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>101003;150@100203;375</v>
-      </c>
-      <c r="AR15" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>魔法提升150点;血量提升375点</v>
-      </c>
-      <c r="AS15" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>100203;375@100603;50@100803;50</v>
-      </c>
-      <c r="AT15" s="3" t="str">
-        <f t="shared" si="14"/>
         <v>血量提升375点;物防提升50点点;魔防提升50点</v>
       </c>
     </row>
@@ -38007,7 +38130,7 @@
         <v>8</v>
       </c>
       <c r="U16" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>120</v>
       </c>
       <c r="V16" s="4">
@@ -38029,79 +38152,79 @@
         <v>180</v>
       </c>
       <c r="AA16" s="1">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+      <c r="AB16" s="1">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+      <c r="AC16" s="1">
+        <f t="shared" si="20"/>
+        <v>60</v>
+      </c>
+      <c r="AD16" s="1">
         <f t="shared" si="1"/>
-        <v>540</v>
-      </c>
-      <c r="AB16" s="1">
-        <f>Z16</f>
+        <v>900</v>
+      </c>
+      <c r="AE16" s="1">
+        <f t="shared" si="18"/>
+        <v>450</v>
+      </c>
+      <c r="AF16" s="1">
+        <f t="shared" si="19"/>
+        <v>450</v>
+      </c>
+      <c r="AG16" s="1">
+        <f t="shared" si="4"/>
         <v>180</v>
       </c>
-      <c r="AC16" s="1">
+      <c r="AI16" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;180@100603;180</v>
+      </c>
+      <c r="AJ16" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升180点;物防提升180点</v>
+      </c>
+      <c r="AK16" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;180@100803;180</v>
+      </c>
+      <c r="AL16" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升180点;魔防提升180点</v>
+      </c>
+      <c r="AM16" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100403;180@100203;450</v>
+      </c>
+      <c r="AN16" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>攻击提升180点;血量提升450点</v>
+      </c>
+      <c r="AO16" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>100203;900</v>
+      </c>
+      <c r="AP16" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>血量提升900点</v>
+      </c>
+      <c r="AQ16" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>101003;180@100203;450</v>
+      </c>
+      <c r="AR16" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>魔法提升180点;血量提升450点</v>
+      </c>
+      <c r="AS16" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>100203;450@100603;60@100803;60</v>
+      </c>
+      <c r="AT16" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>60</v>
-      </c>
-      <c r="AD16" s="1">
-        <f>Z16*5</f>
-        <v>900</v>
-      </c>
-      <c r="AE16" s="1">
-        <f>Z16*2.5</f>
-        <v>450</v>
-      </c>
-      <c r="AF16" s="1">
-        <f>Z16*2.5</f>
-        <v>450</v>
-      </c>
-      <c r="AG16" s="1">
-        <f t="shared" si="2"/>
-        <v>180</v>
-      </c>
-      <c r="AI16" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>100403;180@100603;180</v>
-      </c>
-      <c r="AJ16" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>攻击提升180点;物防提升180点</v>
-      </c>
-      <c r="AK16" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>100403;180@100803;180</v>
-      </c>
-      <c r="AL16" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>攻击提升180点;魔防提升180点</v>
-      </c>
-      <c r="AM16" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>100403;180@100203;450</v>
-      </c>
-      <c r="AN16" s="3" t="str">
-        <f t="shared" si="8"/>
-        <v>攻击提升180点;血量提升450点</v>
-      </c>
-      <c r="AO16" s="3" t="str">
-        <f t="shared" si="9"/>
-        <v>100203;900</v>
-      </c>
-      <c r="AP16" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>血量提升900点</v>
-      </c>
-      <c r="AQ16" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>101003;180@100203;450</v>
-      </c>
-      <c r="AR16" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>魔法提升180点;血量提升450点</v>
-      </c>
-      <c r="AS16" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>100203;450@100603;60@100803;60</v>
-      </c>
-      <c r="AT16" s="3" t="str">
-        <f t="shared" si="14"/>
         <v>血量提升450点;物防提升60点点;魔防提升60点</v>
       </c>
     </row>
@@ -38141,7 +38264,7 @@
         <v>9</v>
       </c>
       <c r="U17" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>160</v>
       </c>
       <c r="V17" s="4">
@@ -38163,79 +38286,79 @@
         <v>210</v>
       </c>
       <c r="AA17" s="1">
+        <f t="shared" si="3"/>
+        <v>630</v>
+      </c>
+      <c r="AB17" s="1">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="AC17" s="1">
+        <f t="shared" si="20"/>
+        <v>70</v>
+      </c>
+      <c r="AD17" s="1">
         <f t="shared" si="1"/>
-        <v>630</v>
-      </c>
-      <c r="AB17" s="1">
-        <f>Z17</f>
+        <v>1050</v>
+      </c>
+      <c r="AE17" s="1">
+        <f t="shared" si="18"/>
+        <v>525</v>
+      </c>
+      <c r="AF17" s="1">
+        <f t="shared" si="19"/>
+        <v>525</v>
+      </c>
+      <c r="AG17" s="1">
+        <f t="shared" si="4"/>
         <v>210</v>
       </c>
-      <c r="AC17" s="1">
+      <c r="AI17" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;210@100603;210</v>
+      </c>
+      <c r="AJ17" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升210点;物防提升210点</v>
+      </c>
+      <c r="AK17" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;210@100803;210</v>
+      </c>
+      <c r="AL17" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升210点;魔防提升210点</v>
+      </c>
+      <c r="AM17" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100403;210@100203;525</v>
+      </c>
+      <c r="AN17" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>攻击提升210点;血量提升525点</v>
+      </c>
+      <c r="AO17" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>100203;1050</v>
+      </c>
+      <c r="AP17" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>血量提升1050点</v>
+      </c>
+      <c r="AQ17" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>101003;210@100203;525</v>
+      </c>
+      <c r="AR17" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>魔法提升210点;血量提升525点</v>
+      </c>
+      <c r="AS17" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>100203;525@100603;70@100803;70</v>
+      </c>
+      <c r="AT17" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>70</v>
-      </c>
-      <c r="AD17" s="1">
-        <f>Z17*5</f>
-        <v>1050</v>
-      </c>
-      <c r="AE17" s="1">
-        <f>Z17*2.5</f>
-        <v>525</v>
-      </c>
-      <c r="AF17" s="1">
-        <f>Z17*2.5</f>
-        <v>525</v>
-      </c>
-      <c r="AG17" s="1">
-        <f t="shared" si="2"/>
-        <v>210</v>
-      </c>
-      <c r="AI17" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>100403;210@100603;210</v>
-      </c>
-      <c r="AJ17" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>攻击提升210点;物防提升210点</v>
-      </c>
-      <c r="AK17" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>100403;210@100803;210</v>
-      </c>
-      <c r="AL17" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>攻击提升210点;魔防提升210点</v>
-      </c>
-      <c r="AM17" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>100403;210@100203;525</v>
-      </c>
-      <c r="AN17" s="3" t="str">
-        <f t="shared" si="8"/>
-        <v>攻击提升210点;血量提升525点</v>
-      </c>
-      <c r="AO17" s="3" t="str">
-        <f t="shared" si="9"/>
-        <v>100203;1050</v>
-      </c>
-      <c r="AP17" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>血量提升1050点</v>
-      </c>
-      <c r="AQ17" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>101003;210@100203;525</v>
-      </c>
-      <c r="AR17" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>魔法提升210点;血量提升525点</v>
-      </c>
-      <c r="AS17" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>100203;525@100603;70@100803;70</v>
-      </c>
-      <c r="AT17" s="3" t="str">
-        <f t="shared" si="14"/>
         <v>血量提升525点;物防提升70点点;魔防提升70点</v>
       </c>
     </row>
@@ -38261,7 +38384,7 @@
         <v>10</v>
       </c>
       <c r="U18" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>203.33333333333334</v>
       </c>
       <c r="V18" s="4">
@@ -38269,7 +38392,7 @@
         <v>6100</v>
       </c>
       <c r="W18" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1300</v>
       </c>
       <c r="X18" s="1">
@@ -38284,79 +38407,79 @@
         <v>240</v>
       </c>
       <c r="AA18" s="1">
+        <f t="shared" si="3"/>
+        <v>720</v>
+      </c>
+      <c r="AB18" s="1">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="AC18" s="1">
+        <f t="shared" si="20"/>
+        <v>80</v>
+      </c>
+      <c r="AD18" s="1">
         <f t="shared" si="1"/>
-        <v>720</v>
-      </c>
-      <c r="AB18" s="1">
-        <f>Z18</f>
+        <v>1200</v>
+      </c>
+      <c r="AE18" s="1">
+        <f t="shared" si="18"/>
+        <v>600</v>
+      </c>
+      <c r="AF18" s="1">
+        <f t="shared" si="19"/>
+        <v>600</v>
+      </c>
+      <c r="AG18" s="1">
+        <f t="shared" si="4"/>
         <v>240</v>
       </c>
-      <c r="AC18" s="1">
+      <c r="AI18" s="3" t="str">
+        <f t="shared" si="5"/>
+        <v>100403;240@100603;240</v>
+      </c>
+      <c r="AJ18" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>攻击提升240点;物防提升240点</v>
+      </c>
+      <c r="AK18" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>100403;240@100803;240</v>
+      </c>
+      <c r="AL18" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>攻击提升240点;魔防提升240点</v>
+      </c>
+      <c r="AM18" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v>100403;240@100203;600</v>
+      </c>
+      <c r="AN18" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>攻击提升240点;血量提升600点</v>
+      </c>
+      <c r="AO18" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>100203;1200</v>
+      </c>
+      <c r="AP18" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v>血量提升1200点</v>
+      </c>
+      <c r="AQ18" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>101003;240@100203;600</v>
+      </c>
+      <c r="AR18" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>魔法提升240点;血量提升600点</v>
+      </c>
+      <c r="AS18" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>100203;600@100603;80@100803;80</v>
+      </c>
+      <c r="AT18" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>80</v>
-      </c>
-      <c r="AD18" s="1">
-        <f>Z18*5</f>
-        <v>1200</v>
-      </c>
-      <c r="AE18" s="1">
-        <f>Z18*2.5</f>
-        <v>600</v>
-      </c>
-      <c r="AF18" s="1">
-        <f>Z18*2.5</f>
-        <v>600</v>
-      </c>
-      <c r="AG18" s="1">
-        <f t="shared" si="2"/>
-        <v>240</v>
-      </c>
-      <c r="AI18" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v>100403;240@100603;240</v>
-      </c>
-      <c r="AJ18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>攻击提升240点;物防提升240点</v>
-      </c>
-      <c r="AK18" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>100403;240@100803;240</v>
-      </c>
-      <c r="AL18" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>攻击提升240点;魔防提升240点</v>
-      </c>
-      <c r="AM18" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>100403;240@100203;600</v>
-      </c>
-      <c r="AN18" s="3" t="str">
-        <f t="shared" si="8"/>
-        <v>攻击提升240点;血量提升600点</v>
-      </c>
-      <c r="AO18" s="3" t="str">
-        <f t="shared" si="9"/>
-        <v>100203;1200</v>
-      </c>
-      <c r="AP18" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>血量提升1200点</v>
-      </c>
-      <c r="AQ18" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>101003;240@100203;600</v>
-      </c>
-      <c r="AR18" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>魔法提升240点;血量提升600点</v>
-      </c>
-      <c r="AS18" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>100203;600@100603;80@100803;80</v>
-      </c>
-      <c r="AT18" s="3" t="str">
-        <f t="shared" si="14"/>
         <v>血量提升600点;物防提升80点点;魔防提升80点</v>
       </c>
     </row>
@@ -38502,7 +38625,7 @@
         <v>300</v>
       </c>
       <c r="E22" s="1">
-        <f t="shared" ref="E22:E24" si="17">D22/30</f>
+        <f t="shared" ref="E22:E24" si="21">D22/30</f>
         <v>10</v>
       </c>
       <c r="R22" s="3">
@@ -38550,13 +38673,13 @@
         <v>500</v>
       </c>
       <c r="E23" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>16.666666666666668</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>3005</v>
       </c>
-      <c r="R23" s="119" t="s">
+      <c r="R23" s="117" t="s">
         <v>3099</v>
       </c>
       <c r="S23" s="3" t="s">
@@ -38596,7 +38719,7 @@
         <v>1000</v>
       </c>
       <c r="E24" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>33.333333333333336</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -38608,15 +38731,21 @@
       <c r="I24" s="7" t="s">
         <v>3070</v>
       </c>
+      <c r="L24" s="1" t="s">
+        <v>3123</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0.5</v>
+      </c>
       <c r="O24" s="3" t="s">
         <v>2981</v>
       </c>
-      <c r="R24" s="119"/>
-      <c r="S24" s="120"/>
-      <c r="T24" s="121"/>
-      <c r="U24" s="119"/>
+      <c r="R24" s="117"/>
+      <c r="S24" s="118"/>
+      <c r="T24" s="119"/>
+      <c r="U24" s="117"/>
       <c r="V24" s="108"/>
-      <c r="W24" s="119"/>
+      <c r="W24" s="117"/>
       <c r="X24" s="4"/>
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
@@ -38642,15 +38771,18 @@
       <c r="I25" s="7" t="s">
         <v>3069</v>
       </c>
+      <c r="M25" s="1">
+        <v>15</v>
+      </c>
       <c r="O25" s="3" t="s">
         <v>2982</v>
       </c>
-      <c r="R25" s="119"/>
-      <c r="S25" s="120"/>
-      <c r="T25" s="121"/>
-      <c r="U25" s="119"/>
+      <c r="R25" s="117"/>
+      <c r="S25" s="118"/>
+      <c r="T25" s="119"/>
+      <c r="U25" s="117"/>
       <c r="V25" s="108"/>
-      <c r="W25" s="119"/>
+      <c r="W25" s="117"/>
       <c r="X25" s="4"/>
       <c r="AJ25" s="3" t="s">
         <v>3111</v>
@@ -38690,6 +38822,9 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="7"/>
+      <c r="M27" s="1">
+        <v>9</v>
+      </c>
       <c r="O27" s="3" t="s">
         <v>2984</v>
       </c>
@@ -38713,6 +38848,9 @@
       <c r="I28" s="7" t="s">
         <v>3006</v>
       </c>
+      <c r="M28" s="1">
+        <v>5</v>
+      </c>
       <c r="R28" s="3" t="s">
         <v>3102</v>
       </c>
@@ -38744,7 +38882,7 @@
       <c r="P29" s="1" t="s">
         <v>3118</v>
       </c>
-      <c r="R29" s="122" t="s">
+      <c r="R29" s="3" t="s">
         <v>3104</v>
       </c>
       <c r="S29" s="105" t="s">
@@ -65779,7 +65917,7 @@
       <c r="J3" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="117" t="s">
+      <c r="K3" s="120" t="s">
         <v>50</v>
       </c>
       <c r="L3" s="68" t="s">
@@ -65861,7 +65999,7 @@
       <c r="I4" s="78">
         <v>10002</v>
       </c>
-      <c r="K4" s="117"/>
+      <c r="K4" s="120"/>
       <c r="L4" s="68" t="s">
         <v>61</v>
       </c>
@@ -65916,7 +66054,7 @@
       <c r="AW4" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="AX4" s="117" t="s">
+      <c r="AX4" s="120" t="s">
         <v>50</v>
       </c>
       <c r="AY4" s="68" t="s">
@@ -65972,7 +66110,7 @@
       <c r="I5" s="78">
         <v>10003</v>
       </c>
-      <c r="K5" s="117"/>
+      <c r="K5" s="120"/>
       <c r="L5" s="68" t="s">
         <v>81</v>
       </c>
@@ -66024,7 +66162,7 @@
       <c r="AV5" s="68">
         <v>10002</v>
       </c>
-      <c r="AX5" s="117"/>
+      <c r="AX5" s="120"/>
       <c r="AY5" s="68" t="s">
         <v>61</v>
       </c>
@@ -66070,7 +66208,7 @@
       <c r="I6" s="78">
         <v>10011</v>
       </c>
-      <c r="K6" s="117" t="s">
+      <c r="K6" s="120" t="s">
         <v>101</v>
       </c>
       <c r="L6" s="68" t="s">
@@ -66100,7 +66238,7 @@
       <c r="AV6" s="68">
         <v>10003</v>
       </c>
-      <c r="AX6" s="117"/>
+      <c r="AX6" s="120"/>
       <c r="AY6" s="68" t="s">
         <v>81</v>
       </c>
@@ -66130,7 +66268,7 @@
       <c r="I7" s="78">
         <v>10012</v>
       </c>
-      <c r="K7" s="117"/>
+      <c r="K7" s="120"/>
       <c r="L7" s="68" t="s">
         <v>61</v>
       </c>
@@ -66176,7 +66314,7 @@
       <c r="AV7" s="68">
         <v>10011</v>
       </c>
-      <c r="AX7" s="117" t="s">
+      <c r="AX7" s="120" t="s">
         <v>101</v>
       </c>
       <c r="AY7" s="68" t="s">
@@ -66223,7 +66361,7 @@
       <c r="I8" s="78">
         <v>10013</v>
       </c>
-      <c r="K8" s="117"/>
+      <c r="K8" s="120"/>
       <c r="L8" s="68" t="s">
         <v>81</v>
       </c>
@@ -66263,7 +66401,7 @@
       <c r="AV8" s="68">
         <v>10012</v>
       </c>
-      <c r="AX8" s="117"/>
+      <c r="AX8" s="120"/>
       <c r="AY8" s="68" t="s">
         <v>61</v>
       </c>
@@ -66297,7 +66435,7 @@
       <c r="CO8" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="CP8" s="117" t="s">
+      <c r="CP8" s="120" t="s">
         <v>50</v>
       </c>
       <c r="CQ8" s="68" t="s">
@@ -66316,7 +66454,7 @@
       <c r="I9" s="78">
         <v>10021</v>
       </c>
-      <c r="K9" s="117" t="s">
+      <c r="K9" s="120" t="s">
         <v>142</v>
       </c>
       <c r="L9" s="68" t="s">
@@ -66340,7 +66478,7 @@
       <c r="AV9" s="68">
         <v>10013</v>
       </c>
-      <c r="AX9" s="117"/>
+      <c r="AX9" s="120"/>
       <c r="AY9" s="68" t="s">
         <v>81</v>
       </c>
@@ -66359,7 +66497,7 @@
       <c r="CN9" s="78">
         <v>10002</v>
       </c>
-      <c r="CP9" s="117"/>
+      <c r="CP9" s="120"/>
       <c r="CQ9" s="68" t="s">
         <v>61</v>
       </c>
@@ -66387,7 +66525,7 @@
       <c r="I10" s="78">
         <v>10022</v>
       </c>
-      <c r="K10" s="117"/>
+      <c r="K10" s="120"/>
       <c r="L10" s="68" t="s">
         <v>61</v>
       </c>
@@ -66431,7 +66569,7 @@
       <c r="AV10" s="68">
         <v>10021</v>
       </c>
-      <c r="AX10" s="117" t="s">
+      <c r="AX10" s="120" t="s">
         <v>142</v>
       </c>
       <c r="AY10" s="68" t="s">
@@ -66447,7 +66585,7 @@
       <c r="CN10" s="78">
         <v>10003</v>
       </c>
-      <c r="CP10" s="117"/>
+      <c r="CP10" s="120"/>
       <c r="CQ10" s="68" t="s">
         <v>81</v>
       </c>
@@ -66474,7 +66612,7 @@
       <c r="I11" s="78">
         <v>10023</v>
       </c>
-      <c r="K11" s="117"/>
+      <c r="K11" s="120"/>
       <c r="L11" s="68" t="s">
         <v>81</v>
       </c>
@@ -66526,7 +66664,7 @@
       <c r="AV11" s="68">
         <v>10022</v>
       </c>
-      <c r="AX11" s="117"/>
+      <c r="AX11" s="120"/>
       <c r="AY11" s="68" t="s">
         <v>61</v>
       </c>
@@ -66564,7 +66702,7 @@
       <c r="CN11" s="78">
         <v>10011</v>
       </c>
-      <c r="CP11" s="117" t="s">
+      <c r="CP11" s="120" t="s">
         <v>101</v>
       </c>
       <c r="CQ11" s="68" t="s">
@@ -66584,7 +66722,7 @@
       <c r="I12" s="78">
         <v>10031</v>
       </c>
-      <c r="K12" s="117" t="s">
+      <c r="K12" s="120" t="s">
         <v>186</v>
       </c>
       <c r="L12" s="68" t="s">
@@ -66617,7 +66755,7 @@
       <c r="AV12" s="68">
         <v>10023</v>
       </c>
-      <c r="AX12" s="117"/>
+      <c r="AX12" s="120"/>
       <c r="AY12" s="68" t="s">
         <v>81</v>
       </c>
@@ -66666,7 +66804,7 @@
       <c r="CN12" s="78">
         <v>10012</v>
       </c>
-      <c r="CP12" s="117"/>
+      <c r="CP12" s="120"/>
       <c r="CQ12" s="68" t="s">
         <v>61</v>
       </c>
@@ -66687,7 +66825,7 @@
       <c r="I13" s="78">
         <v>10032</v>
       </c>
-      <c r="K13" s="117"/>
+      <c r="K13" s="120"/>
       <c r="L13" s="68" t="s">
         <v>61</v>
       </c>
@@ -66715,7 +66853,7 @@
       <c r="AV13" s="68">
         <v>10031</v>
       </c>
-      <c r="AX13" s="117" t="s">
+      <c r="AX13" s="120" t="s">
         <v>186</v>
       </c>
       <c r="AY13" s="68" t="s">
@@ -66751,7 +66889,7 @@
       <c r="CN13" s="78">
         <v>10013</v>
       </c>
-      <c r="CP13" s="117"/>
+      <c r="CP13" s="120"/>
       <c r="CQ13" s="68" t="s">
         <v>81</v>
       </c>
@@ -66783,7 +66921,7 @@
       <c r="I14" s="78">
         <v>10033</v>
       </c>
-      <c r="K14" s="117"/>
+      <c r="K14" s="120"/>
       <c r="L14" s="68" t="s">
         <v>81</v>
       </c>
@@ -66814,7 +66952,7 @@
       <c r="AV14" s="68">
         <v>10032</v>
       </c>
-      <c r="AX14" s="117"/>
+      <c r="AX14" s="120"/>
       <c r="AY14" s="68" t="s">
         <v>61</v>
       </c>
@@ -66849,7 +66987,7 @@
       <c r="CN14" s="78">
         <v>10021</v>
       </c>
-      <c r="CP14" s="117" t="s">
+      <c r="CP14" s="120" t="s">
         <v>142</v>
       </c>
       <c r="CQ14" s="68" t="s">
@@ -66877,7 +67015,7 @@
       <c r="I15" s="78">
         <v>10041</v>
       </c>
-      <c r="K15" s="117" t="s">
+      <c r="K15" s="120" t="s">
         <v>241</v>
       </c>
       <c r="L15" s="68" t="s">
@@ -66907,7 +67045,7 @@
       <c r="AV15" s="68">
         <v>10033</v>
       </c>
-      <c r="AX15" s="117"/>
+      <c r="AX15" s="120"/>
       <c r="AY15" s="68" t="s">
         <v>81</v>
       </c>
@@ -66932,7 +67070,7 @@
       <c r="CN15" s="78">
         <v>10022</v>
       </c>
-      <c r="CP15" s="117"/>
+      <c r="CP15" s="120"/>
       <c r="CQ15" s="68" t="s">
         <v>61</v>
       </c>
@@ -66958,7 +67096,7 @@
       <c r="I16" s="78">
         <v>10042</v>
       </c>
-      <c r="K16" s="117"/>
+      <c r="K16" s="120"/>
       <c r="L16" s="68" t="s">
         <v>61</v>
       </c>
@@ -66986,7 +67124,7 @@
       <c r="AV16" s="68">
         <v>10041</v>
       </c>
-      <c r="AX16" s="117" t="s">
+      <c r="AX16" s="120" t="s">
         <v>241</v>
       </c>
       <c r="AY16" s="68" t="s">
@@ -67004,7 +67142,7 @@
       <c r="CN16" s="78">
         <v>10023</v>
       </c>
-      <c r="CP16" s="117"/>
+      <c r="CP16" s="120"/>
       <c r="CQ16" s="68" t="s">
         <v>81</v>
       </c>
@@ -67030,7 +67168,7 @@
       <c r="I17" s="78">
         <v>10043</v>
       </c>
-      <c r="K17" s="117"/>
+      <c r="K17" s="120"/>
       <c r="L17" s="68" t="s">
         <v>81</v>
       </c>
@@ -67053,7 +67191,7 @@
       <c r="AV17" s="68">
         <v>10042</v>
       </c>
-      <c r="AX17" s="117"/>
+      <c r="AX17" s="120"/>
       <c r="AY17" s="68" t="s">
         <v>61</v>
       </c>
@@ -67078,7 +67216,7 @@
       <c r="CN17" s="78">
         <v>10031</v>
       </c>
-      <c r="CP17" s="117" t="s">
+      <c r="CP17" s="120" t="s">
         <v>186</v>
       </c>
       <c r="CQ17" s="68" t="s">
@@ -67106,7 +67244,7 @@
       <c r="I18" s="68">
         <v>10051</v>
       </c>
-      <c r="K18" s="117" t="s">
+      <c r="K18" s="120" t="s">
         <v>275</v>
       </c>
       <c r="L18" s="68" t="s">
@@ -67142,7 +67280,7 @@
       <c r="AV18" s="68">
         <v>10043</v>
       </c>
-      <c r="AX18" s="117"/>
+      <c r="AX18" s="120"/>
       <c r="AY18" s="68" t="s">
         <v>81</v>
       </c>
@@ -67158,7 +67296,7 @@
       <c r="CN18" s="78">
         <v>10032</v>
       </c>
-      <c r="CP18" s="117"/>
+      <c r="CP18" s="120"/>
       <c r="CQ18" s="68" t="s">
         <v>61</v>
       </c>
@@ -67181,7 +67319,7 @@
       <c r="I19" s="68">
         <v>10052</v>
       </c>
-      <c r="K19" s="117"/>
+      <c r="K19" s="120"/>
       <c r="L19" s="68" t="s">
         <v>61</v>
       </c>
@@ -67215,7 +67353,7 @@
       <c r="AV19" s="68">
         <v>10051</v>
       </c>
-      <c r="AX19" s="117" t="s">
+      <c r="AX19" s="120" t="s">
         <v>275</v>
       </c>
       <c r="AY19" s="68" t="s">
@@ -67239,7 +67377,7 @@
       <c r="CN19" s="78">
         <v>10033</v>
       </c>
-      <c r="CP19" s="117"/>
+      <c r="CP19" s="120"/>
       <c r="CQ19" s="68" t="s">
         <v>81</v>
       </c>
@@ -67255,7 +67393,7 @@
       <c r="I20" s="68">
         <v>10053</v>
       </c>
-      <c r="K20" s="117"/>
+      <c r="K20" s="120"/>
       <c r="L20" s="68" t="s">
         <v>81</v>
       </c>
@@ -67286,7 +67424,7 @@
       <c r="AV20" s="68">
         <v>10052</v>
       </c>
-      <c r="AX20" s="117"/>
+      <c r="AX20" s="120"/>
       <c r="AY20" s="68" t="s">
         <v>61</v>
       </c>
@@ -67311,7 +67449,7 @@
       <c r="CN20" s="78">
         <v>10041</v>
       </c>
-      <c r="CP20" s="117" t="s">
+      <c r="CP20" s="120" t="s">
         <v>241</v>
       </c>
       <c r="CQ20" s="68" t="s">
@@ -67343,7 +67481,7 @@
         <v>10051</v>
       </c>
       <c r="J21" s="70"/>
-      <c r="K21" s="118" t="s">
+      <c r="K21" s="121" t="s">
         <v>315</v>
       </c>
       <c r="L21" s="70" t="s">
@@ -67370,7 +67508,7 @@
       <c r="AV21" s="68">
         <v>10053</v>
       </c>
-      <c r="AX21" s="117"/>
+      <c r="AX21" s="120"/>
       <c r="AY21" s="68" t="s">
         <v>81</v>
       </c>
@@ -67386,7 +67524,7 @@
       <c r="CN21" s="78">
         <v>10042</v>
       </c>
-      <c r="CP21" s="117"/>
+      <c r="CP21" s="120"/>
       <c r="CQ21" s="68" t="s">
         <v>61</v>
       </c>
@@ -67413,7 +67551,7 @@
         <v>10052</v>
       </c>
       <c r="J22" s="70"/>
-      <c r="K22" s="118"/>
+      <c r="K22" s="121"/>
       <c r="L22" s="70" t="s">
         <v>61</v>
       </c>
@@ -67437,7 +67575,7 @@
         <v>10051</v>
       </c>
       <c r="AW22" s="70"/>
-      <c r="AX22" s="118" t="s">
+      <c r="AX22" s="121" t="s">
         <v>315</v>
       </c>
       <c r="AY22" s="70" t="s">
@@ -67462,7 +67600,7 @@
       <c r="CN22" s="78">
         <v>10043</v>
       </c>
-      <c r="CP22" s="117"/>
+      <c r="CP22" s="120"/>
       <c r="CQ22" s="68" t="s">
         <v>81</v>
       </c>
@@ -67489,7 +67627,7 @@
         <v>10053</v>
       </c>
       <c r="J23" s="70"/>
-      <c r="K23" s="118"/>
+      <c r="K23" s="121"/>
       <c r="L23" s="70" t="s">
         <v>81</v>
       </c>
@@ -67523,7 +67661,7 @@
         <v>10052</v>
       </c>
       <c r="AW23" s="70"/>
-      <c r="AX23" s="118"/>
+      <c r="AX23" s="121"/>
       <c r="AY23" s="70" t="s">
         <v>61</v>
       </c>
@@ -67546,7 +67684,7 @@
       <c r="CN23" s="68">
         <v>10051</v>
       </c>
-      <c r="CP23" s="117" t="s">
+      <c r="CP23" s="120" t="s">
         <v>275</v>
       </c>
       <c r="CQ23" s="68" t="s">
@@ -67612,7 +67750,7 @@
         <v>10053</v>
       </c>
       <c r="AW24" s="70"/>
-      <c r="AX24" s="118"/>
+      <c r="AX24" s="121"/>
       <c r="AY24" s="70" t="s">
         <v>81</v>
       </c>
@@ -67648,7 +67786,7 @@
       <c r="CN24" s="68">
         <v>10052</v>
       </c>
-      <c r="CP24" s="117"/>
+      <c r="CP24" s="120"/>
       <c r="CQ24" s="68" t="s">
         <v>61</v>
       </c>
@@ -67738,7 +67876,7 @@
       <c r="CN25" s="68">
         <v>10053</v>
       </c>
-      <c r="CP25" s="117"/>
+      <c r="CP25" s="120"/>
       <c r="CQ25" s="68" t="s">
         <v>81</v>
       </c>
@@ -67839,7 +67977,7 @@
         <v>10051</v>
       </c>
       <c r="CO26" s="70"/>
-      <c r="CP26" s="118" t="s">
+      <c r="CP26" s="121" t="s">
         <v>315</v>
       </c>
       <c r="CQ26" s="70" t="s">
@@ -67942,7 +68080,7 @@
         <v>10052</v>
       </c>
       <c r="CO27" s="70"/>
-      <c r="CP27" s="118"/>
+      <c r="CP27" s="121"/>
       <c r="CQ27" s="70" t="s">
         <v>61</v>
       </c>
@@ -68045,7 +68183,7 @@
         <v>10053</v>
       </c>
       <c r="CO28" s="70"/>
-      <c r="CP28" s="118"/>
+      <c r="CP28" s="121"/>
       <c r="CQ28" s="70" t="s">
         <v>81</v>
       </c>
@@ -69861,13 +69999,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="CP23:CP25"/>
-    <mergeCell ref="CP26:CP28"/>
-    <mergeCell ref="CP8:CP10"/>
-    <mergeCell ref="CP11:CP13"/>
-    <mergeCell ref="CP14:CP16"/>
-    <mergeCell ref="CP17:CP19"/>
-    <mergeCell ref="CP20:CP22"/>
     <mergeCell ref="K18:K20"/>
     <mergeCell ref="K21:K23"/>
     <mergeCell ref="AX4:AX6"/>
@@ -69882,6 +70013,13 @@
     <mergeCell ref="K9:K11"/>
     <mergeCell ref="K12:K14"/>
     <mergeCell ref="K15:K17"/>
+    <mergeCell ref="CP23:CP25"/>
+    <mergeCell ref="CP26:CP28"/>
+    <mergeCell ref="CP8:CP10"/>
+    <mergeCell ref="CP11:CP13"/>
+    <mergeCell ref="CP14:CP16"/>
+    <mergeCell ref="CP17:CP19"/>
+    <mergeCell ref="CP20:CP22"/>
   </mergeCells>
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/WeiJingShuZhi/属性表.xlsx
+++ b/WeiJingShuZhi/属性表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\WeiJingShuZhi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C169BC-AC60-4C26-93F2-3D893E196680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108C2DBF-CD80-4915-A58C-45ADE69D5C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5546" uniqueCount="3126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5548" uniqueCount="3128">
   <si>
     <t>人物属性</t>
   </si>
@@ -9961,6 +9961,14 @@
   </si>
   <si>
     <t>魔能装备野外BOSS掉落</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成</t>
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
 </sst>
@@ -11528,337 +11536,329 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="856">
-          <cell r="C856">
+        <row r="857">
+          <cell r="C857">
             <v>10103602</v>
           </cell>
-          <cell r="S856" t="str">
+          <cell r="S857" t="str">
             <v>6@100803;50;150</v>
-          </cell>
-        </row>
-        <row r="857">
-          <cell r="C857">
-            <v>10103603</v>
-          </cell>
-          <cell r="S857" t="str">
-            <v>6@200303;0.01;0.03</v>
           </cell>
         </row>
         <row r="858">
           <cell r="C858">
-            <v>10201101</v>
+            <v>10103603</v>
           </cell>
-          <cell r="S858">
-            <v>7102001</v>
+          <cell r="S858" t="str">
+            <v>6@200303;0.01;0.03</v>
           </cell>
         </row>
         <row r="859">
           <cell r="C859">
-            <v>10201102</v>
+            <v>10201101</v>
           </cell>
           <cell r="S859">
-            <v>7102002</v>
+            <v>7102001</v>
           </cell>
         </row>
         <row r="860">
           <cell r="C860">
-            <v>10201103</v>
+            <v>10201102</v>
           </cell>
           <cell r="S860">
-            <v>7102003</v>
+            <v>7102002</v>
           </cell>
         </row>
         <row r="861">
           <cell r="C861">
-            <v>10201104</v>
+            <v>10201103</v>
           </cell>
           <cell r="S861">
-            <v>7102004</v>
+            <v>7102003</v>
           </cell>
         </row>
         <row r="862">
           <cell r="C862">
-            <v>10201201</v>
+            <v>10201104</v>
           </cell>
           <cell r="S862">
-            <v>7103001</v>
+            <v>7102004</v>
           </cell>
         </row>
         <row r="863">
           <cell r="C863">
-            <v>10201202</v>
+            <v>10201201</v>
           </cell>
           <cell r="S863">
-            <v>7103002</v>
+            <v>7103001</v>
           </cell>
         </row>
         <row r="864">
           <cell r="C864">
-            <v>10201203</v>
+            <v>10201202</v>
           </cell>
           <cell r="S864">
-            <v>7103003</v>
+            <v>7103002</v>
           </cell>
         </row>
         <row r="865">
           <cell r="C865">
-            <v>10201204</v>
+            <v>10201203</v>
           </cell>
           <cell r="S865">
-            <v>7103004</v>
+            <v>7103003</v>
           </cell>
         </row>
         <row r="866">
           <cell r="C866">
-            <v>10202101</v>
+            <v>10201204</v>
           </cell>
           <cell r="S866">
-            <v>7202001</v>
+            <v>7103004</v>
           </cell>
         </row>
         <row r="867">
           <cell r="C867">
-            <v>10202102</v>
+            <v>10202101</v>
           </cell>
           <cell r="S867">
-            <v>7202002</v>
+            <v>7202001</v>
           </cell>
         </row>
         <row r="868">
           <cell r="C868">
-            <v>10202103</v>
+            <v>10202102</v>
           </cell>
           <cell r="S868">
-            <v>7202003</v>
+            <v>7202002</v>
           </cell>
         </row>
         <row r="869">
           <cell r="C869">
-            <v>10202104</v>
+            <v>10202103</v>
           </cell>
           <cell r="S869">
-            <v>7202004</v>
+            <v>7202003</v>
           </cell>
         </row>
         <row r="870">
           <cell r="C870">
-            <v>10202201</v>
+            <v>10202104</v>
           </cell>
           <cell r="S870">
-            <v>7203001</v>
+            <v>7202004</v>
           </cell>
         </row>
         <row r="871">
           <cell r="C871">
-            <v>10202202</v>
+            <v>10202201</v>
           </cell>
           <cell r="S871">
-            <v>7203002</v>
+            <v>7203001</v>
           </cell>
         </row>
         <row r="872">
           <cell r="C872">
-            <v>10202203</v>
+            <v>10202202</v>
           </cell>
           <cell r="S872">
-            <v>7203003</v>
+            <v>7203002</v>
           </cell>
         </row>
         <row r="873">
           <cell r="C873">
-            <v>10202204</v>
+            <v>10202203</v>
           </cell>
           <cell r="S873">
-            <v>7203004</v>
+            <v>7203003</v>
           </cell>
         </row>
         <row r="874">
           <cell r="C874">
-            <v>10203101</v>
+            <v>10202204</v>
           </cell>
           <cell r="S874">
-            <v>7302001</v>
+            <v>7203004</v>
           </cell>
         </row>
         <row r="875">
           <cell r="C875">
-            <v>10203102</v>
+            <v>10203101</v>
           </cell>
           <cell r="S875">
-            <v>7302002</v>
+            <v>7302001</v>
           </cell>
         </row>
         <row r="876">
           <cell r="C876">
-            <v>10203201</v>
+            <v>10203102</v>
           </cell>
           <cell r="S876">
-            <v>7303001</v>
+            <v>7302002</v>
           </cell>
         </row>
         <row r="877">
           <cell r="C877">
-            <v>10203202</v>
+            <v>10203201</v>
           </cell>
           <cell r="S877">
-            <v>7303002</v>
+            <v>7303001</v>
           </cell>
         </row>
         <row r="878">
           <cell r="C878">
-            <v>10301001</v>
+            <v>10203202</v>
           </cell>
           <cell r="S878">
-            <v>6101003</v>
+            <v>7303002</v>
           </cell>
         </row>
         <row r="879">
           <cell r="C879">
-            <v>10301002</v>
+            <v>10301001</v>
           </cell>
           <cell r="S879">
-            <v>6102003</v>
+            <v>6101003</v>
           </cell>
         </row>
         <row r="880">
           <cell r="C880">
-            <v>10301003</v>
+            <v>10301002</v>
           </cell>
           <cell r="S880">
-            <v>6103003</v>
+            <v>6102003</v>
           </cell>
         </row>
         <row r="881">
           <cell r="C881">
-            <v>10301004</v>
+            <v>10301003</v>
           </cell>
           <cell r="S881">
-            <v>6104004</v>
+            <v>6103003</v>
           </cell>
         </row>
         <row r="882">
           <cell r="C882">
-            <v>10301005</v>
+            <v>10301004</v>
           </cell>
           <cell r="S882">
-            <v>6105004</v>
+            <v>6104004</v>
           </cell>
         </row>
         <row r="883">
           <cell r="C883">
-            <v>10301006</v>
+            <v>10301005</v>
           </cell>
           <cell r="S883">
-            <v>6106003</v>
+            <v>6105004</v>
           </cell>
         </row>
         <row r="884">
           <cell r="C884">
-            <v>10302001</v>
+            <v>10301006</v>
           </cell>
           <cell r="S884">
-            <v>6201003</v>
+            <v>6106003</v>
           </cell>
         </row>
         <row r="885">
           <cell r="C885">
-            <v>10302002</v>
+            <v>10302001</v>
           </cell>
           <cell r="S885">
-            <v>6202003</v>
+            <v>6201003</v>
           </cell>
         </row>
         <row r="886">
           <cell r="C886">
-            <v>10302003</v>
+            <v>10302002</v>
           </cell>
           <cell r="S886">
-            <v>6203003</v>
+            <v>6202003</v>
           </cell>
         </row>
         <row r="887">
           <cell r="C887">
-            <v>10302004</v>
+            <v>10302003</v>
           </cell>
           <cell r="S887">
-            <v>6204004</v>
+            <v>6203003</v>
           </cell>
         </row>
         <row r="888">
           <cell r="C888">
-            <v>10302005</v>
+            <v>10302004</v>
           </cell>
           <cell r="S888">
-            <v>6205004</v>
+            <v>6204004</v>
           </cell>
         </row>
         <row r="889">
           <cell r="C889">
-            <v>10302006</v>
+            <v>10302005</v>
           </cell>
           <cell r="S889">
-            <v>6206003</v>
+            <v>6205004</v>
           </cell>
         </row>
         <row r="890">
           <cell r="C890">
-            <v>10303001</v>
+            <v>10302006</v>
           </cell>
           <cell r="S890">
-            <v>6301003</v>
+            <v>6206003</v>
           </cell>
         </row>
         <row r="891">
           <cell r="C891">
-            <v>10303002</v>
+            <v>10303001</v>
           </cell>
           <cell r="S891">
-            <v>6302003</v>
+            <v>6301003</v>
           </cell>
         </row>
         <row r="892">
           <cell r="C892">
-            <v>10303003</v>
+            <v>10303002</v>
           </cell>
           <cell r="S892">
-            <v>6303003</v>
+            <v>6302003</v>
           </cell>
         </row>
         <row r="893">
           <cell r="C893">
-            <v>10303004</v>
+            <v>10303003</v>
           </cell>
           <cell r="S893">
-            <v>6304004</v>
+            <v>6303003</v>
           </cell>
         </row>
         <row r="894">
           <cell r="C894">
-            <v>10303005</v>
+            <v>10303004</v>
           </cell>
           <cell r="S894">
-            <v>6305004</v>
+            <v>6304004</v>
           </cell>
         </row>
         <row r="895">
           <cell r="C895">
-            <v>10303006</v>
+            <v>10303005</v>
           </cell>
           <cell r="S895">
-            <v>6306003</v>
+            <v>6305004</v>
           </cell>
         </row>
         <row r="896">
           <cell r="C896">
-            <v>11200000</v>
+            <v>10303006</v>
           </cell>
           <cell r="S896">
-            <v>500</v>
+            <v>6306003</v>
           </cell>
         </row>
         <row r="897">
           <cell r="C897">
-            <v>11200001</v>
+            <v>11200000</v>
           </cell>
           <cell r="S897">
             <v>500</v>
@@ -11866,7 +11866,7 @@
         </row>
         <row r="898">
           <cell r="C898">
-            <v>11200002</v>
+            <v>11200001</v>
           </cell>
           <cell r="S898">
             <v>500</v>
@@ -11874,7 +11874,7 @@
         </row>
         <row r="899">
           <cell r="C899">
-            <v>11200003</v>
+            <v>11200002</v>
           </cell>
           <cell r="S899">
             <v>500</v>
@@ -11882,7 +11882,7 @@
         </row>
         <row r="900">
           <cell r="C900">
-            <v>11200010</v>
+            <v>11200003</v>
           </cell>
           <cell r="S900">
             <v>500</v>
@@ -11890,2475 +11890,2483 @@
         </row>
         <row r="901">
           <cell r="C901">
-            <v>11300001</v>
+            <v>11200010</v>
           </cell>
-          <cell r="S901" t="str">
-            <v>1;3901</v>
+          <cell r="S901">
+            <v>500</v>
           </cell>
         </row>
         <row r="902">
           <cell r="C902">
-            <v>11300002</v>
+            <v>11300001</v>
           </cell>
           <cell r="S902" t="str">
-            <v>1;3906</v>
+            <v>1;3901</v>
           </cell>
         </row>
         <row r="903">
           <cell r="C903">
-            <v>11300003</v>
+            <v>11300002</v>
           </cell>
           <cell r="S903" t="str">
-            <v>1;3907</v>
+            <v>1;3906</v>
           </cell>
         </row>
         <row r="904">
           <cell r="C904">
-            <v>11300004</v>
+            <v>11300003</v>
           </cell>
           <cell r="S904" t="str">
-            <v>1;3908</v>
+            <v>1;3907</v>
           </cell>
         </row>
         <row r="905">
           <cell r="C905">
-            <v>11300005</v>
+            <v>11300004</v>
           </cell>
           <cell r="S905" t="str">
-            <v>1;3909</v>
+            <v>1;3908</v>
           </cell>
         </row>
         <row r="906">
           <cell r="C906">
-            <v>11300006</v>
+            <v>11300005</v>
           </cell>
           <cell r="S906" t="str">
-            <v>1;3910</v>
+            <v>1;3909</v>
           </cell>
         </row>
         <row r="907">
           <cell r="C907">
-            <v>11300007</v>
+            <v>11300006</v>
           </cell>
           <cell r="S907" t="str">
-            <v>2;3902</v>
+            <v>1;3910</v>
           </cell>
         </row>
         <row r="908">
           <cell r="C908">
-            <v>11300008</v>
+            <v>11300007</v>
           </cell>
           <cell r="S908" t="str">
-            <v>2;3903</v>
+            <v>2;3902</v>
           </cell>
         </row>
         <row r="909">
           <cell r="C909">
-            <v>11300009</v>
+            <v>11300008</v>
           </cell>
           <cell r="S909" t="str">
-            <v>2;3904</v>
+            <v>2;3903</v>
           </cell>
         </row>
         <row r="910">
           <cell r="C910">
-            <v>11300101</v>
+            <v>11300009</v>
           </cell>
           <cell r="S910" t="str">
-            <v>1;3101</v>
+            <v>2;3904</v>
           </cell>
         </row>
         <row r="911">
           <cell r="C911">
-            <v>11300102</v>
+            <v>11300101</v>
           </cell>
           <cell r="S911" t="str">
-            <v>1;3102</v>
+            <v>1;3101</v>
           </cell>
         </row>
         <row r="912">
           <cell r="C912">
-            <v>11300103</v>
+            <v>11300102</v>
           </cell>
           <cell r="S912" t="str">
-            <v>1;3103</v>
+            <v>1;3102</v>
           </cell>
         </row>
         <row r="913">
           <cell r="C913">
-            <v>11300104</v>
+            <v>11300103</v>
           </cell>
           <cell r="S913" t="str">
-            <v>1;3104</v>
+            <v>1;3103</v>
           </cell>
         </row>
         <row r="914">
           <cell r="C914">
-            <v>11300105</v>
+            <v>11300104</v>
           </cell>
           <cell r="S914" t="str">
-            <v>1;3105</v>
+            <v>1;3104</v>
           </cell>
         </row>
         <row r="915">
           <cell r="C915">
-            <v>11300201</v>
+            <v>11300105</v>
           </cell>
           <cell r="S915" t="str">
-            <v>1;3201</v>
+            <v>1;3105</v>
           </cell>
         </row>
         <row r="916">
           <cell r="C916">
-            <v>11300202</v>
+            <v>11300201</v>
           </cell>
           <cell r="S916" t="str">
-            <v>1;3202</v>
+            <v>1;3201</v>
           </cell>
         </row>
         <row r="917">
           <cell r="C917">
-            <v>11300203</v>
+            <v>11300202</v>
           </cell>
           <cell r="S917" t="str">
-            <v>1;3203</v>
+            <v>1;3202</v>
           </cell>
         </row>
         <row r="918">
           <cell r="C918">
-            <v>11300204</v>
+            <v>11300203</v>
           </cell>
           <cell r="S918" t="str">
-            <v>1;3204</v>
+            <v>1;3203</v>
           </cell>
         </row>
         <row r="919">
           <cell r="C919">
-            <v>11300205</v>
+            <v>11300204</v>
           </cell>
           <cell r="S919" t="str">
-            <v>1;3205</v>
+            <v>1;3204</v>
           </cell>
         </row>
         <row r="920">
           <cell r="C920">
-            <v>11300301</v>
+            <v>11300205</v>
           </cell>
           <cell r="S920" t="str">
-            <v>1;3301</v>
+            <v>1;3205</v>
           </cell>
         </row>
         <row r="921">
           <cell r="C921">
-            <v>11300302</v>
+            <v>11300301</v>
           </cell>
           <cell r="S921" t="str">
-            <v>1;3302</v>
+            <v>1;3301</v>
           </cell>
         </row>
         <row r="922">
           <cell r="C922">
-            <v>11300303</v>
+            <v>11300302</v>
           </cell>
           <cell r="S922" t="str">
-            <v>1;3303</v>
+            <v>1;3302</v>
           </cell>
         </row>
         <row r="923">
           <cell r="C923">
-            <v>11300304</v>
+            <v>11300303</v>
           </cell>
           <cell r="S923" t="str">
-            <v>1;3304</v>
+            <v>1;3303</v>
           </cell>
         </row>
         <row r="924">
           <cell r="C924">
-            <v>11300305</v>
+            <v>11300304</v>
           </cell>
           <cell r="S924" t="str">
-            <v>1;3305</v>
+            <v>1;3304</v>
           </cell>
         </row>
         <row r="925">
           <cell r="C925">
-            <v>11300401</v>
+            <v>11300305</v>
           </cell>
           <cell r="S925" t="str">
-            <v>1;3401</v>
+            <v>1;3305</v>
           </cell>
         </row>
         <row r="926">
           <cell r="C926">
-            <v>11300402</v>
+            <v>11300401</v>
           </cell>
           <cell r="S926" t="str">
-            <v>1;3402</v>
+            <v>1;3401</v>
           </cell>
         </row>
         <row r="927">
           <cell r="C927">
-            <v>11300403</v>
+            <v>11300402</v>
           </cell>
           <cell r="S927" t="str">
-            <v>1;3403</v>
+            <v>1;3402</v>
           </cell>
         </row>
         <row r="928">
           <cell r="C928">
-            <v>11300404</v>
+            <v>11300403</v>
           </cell>
           <cell r="S928" t="str">
-            <v>1;3404</v>
+            <v>1;3403</v>
           </cell>
         </row>
         <row r="929">
           <cell r="C929">
-            <v>11300405</v>
+            <v>11300404</v>
           </cell>
           <cell r="S929" t="str">
-            <v>1;3405</v>
+            <v>1;3404</v>
           </cell>
         </row>
         <row r="930">
           <cell r="C930">
-            <v>11300501</v>
+            <v>11300405</v>
           </cell>
           <cell r="S930" t="str">
-            <v>1;3501</v>
+            <v>1;3405</v>
           </cell>
         </row>
         <row r="931">
           <cell r="C931">
-            <v>11300502</v>
+            <v>11300501</v>
           </cell>
           <cell r="S931" t="str">
-            <v>1;3502</v>
+            <v>1;3501</v>
           </cell>
         </row>
         <row r="932">
           <cell r="C932">
-            <v>11300503</v>
+            <v>11300502</v>
           </cell>
           <cell r="S932" t="str">
-            <v>1;3503</v>
+            <v>1;3502</v>
           </cell>
         </row>
         <row r="933">
           <cell r="C933">
-            <v>11300504</v>
+            <v>11300503</v>
           </cell>
           <cell r="S933" t="str">
-            <v>1;3504</v>
+            <v>1;3503</v>
           </cell>
         </row>
         <row r="934">
           <cell r="C934">
-            <v>11300505</v>
+            <v>11300504</v>
           </cell>
           <cell r="S934" t="str">
-            <v>1;3505</v>
+            <v>1;3504</v>
           </cell>
         </row>
         <row r="935">
           <cell r="C935">
-            <v>11300601</v>
+            <v>11300505</v>
           </cell>
           <cell r="S935" t="str">
-            <v>1;3601</v>
+            <v>1;3505</v>
           </cell>
         </row>
         <row r="936">
           <cell r="C936">
-            <v>11300602</v>
+            <v>11300601</v>
           </cell>
           <cell r="S936" t="str">
-            <v>1;3602</v>
+            <v>1;3601</v>
           </cell>
         </row>
         <row r="937">
           <cell r="C937">
-            <v>11300603</v>
+            <v>11300602</v>
           </cell>
           <cell r="S937" t="str">
-            <v>1;3603</v>
+            <v>1;3602</v>
           </cell>
         </row>
         <row r="938">
           <cell r="C938">
-            <v>11300604</v>
+            <v>11300603</v>
           </cell>
           <cell r="S938" t="str">
-            <v>1;3604</v>
+            <v>1;3603</v>
           </cell>
         </row>
         <row r="939">
           <cell r="C939">
-            <v>11300605</v>
+            <v>11300604</v>
           </cell>
           <cell r="S939" t="str">
-            <v>1;3605</v>
+            <v>1;3604</v>
           </cell>
         </row>
         <row r="940">
           <cell r="C940">
-            <v>11400101</v>
+            <v>11300605</v>
           </cell>
           <cell r="S940" t="str">
-            <v>1,30@1;202103,0.01,0.03</v>
+            <v>1;3605</v>
           </cell>
         </row>
         <row r="941">
           <cell r="C941">
-            <v>11400102</v>
+            <v>11400101</v>
           </cell>
           <cell r="S941" t="str">
-            <v>1,30@1;100203,100,200</v>
+            <v>1,30@1;202103,0.01,0.03</v>
           </cell>
         </row>
         <row r="942">
           <cell r="C942">
-            <v>11400103</v>
+            <v>11400102</v>
           </cell>
           <cell r="S942" t="str">
-            <v>1,30@2;62000001</v>
+            <v>1,30@1;100203,100,200</v>
           </cell>
         </row>
         <row r="943">
           <cell r="C943">
-            <v>11500101</v>
+            <v>11400103</v>
+          </cell>
+          <cell r="S943" t="str">
+            <v>1,30@2;62000001</v>
           </cell>
         </row>
         <row r="944">
           <cell r="C944">
-            <v>11500102</v>
+            <v>11500101</v>
           </cell>
         </row>
         <row r="945">
           <cell r="C945">
-            <v>11500103</v>
+            <v>11500102</v>
           </cell>
         </row>
         <row r="946">
           <cell r="C946">
-            <v>11500201</v>
+            <v>11500103</v>
           </cell>
         </row>
         <row r="947">
           <cell r="C947">
-            <v>11500202</v>
+            <v>11500201</v>
           </cell>
         </row>
         <row r="948">
           <cell r="C948">
-            <v>11500203</v>
+            <v>11500202</v>
           </cell>
         </row>
         <row r="949">
           <cell r="C949">
-            <v>11500301</v>
+            <v>11500203</v>
           </cell>
         </row>
         <row r="950">
           <cell r="C950">
-            <v>11500302</v>
+            <v>11500301</v>
           </cell>
         </row>
         <row r="951">
           <cell r="C951">
-            <v>11500303</v>
+            <v>11500302</v>
           </cell>
         </row>
         <row r="952">
           <cell r="C952">
-            <v>11500401</v>
+            <v>11500303</v>
           </cell>
         </row>
         <row r="953">
           <cell r="C953">
-            <v>11500402</v>
+            <v>11500401</v>
           </cell>
         </row>
         <row r="954">
           <cell r="C954">
-            <v>11500403</v>
+            <v>11500402</v>
           </cell>
         </row>
         <row r="955">
           <cell r="C955">
-            <v>11500501</v>
+            <v>11500403</v>
           </cell>
         </row>
         <row r="956">
           <cell r="C956">
-            <v>11500502</v>
+            <v>11500501</v>
           </cell>
         </row>
         <row r="957">
           <cell r="C957">
-            <v>11500503</v>
+            <v>11500502</v>
           </cell>
         </row>
         <row r="958">
           <cell r="C958">
-            <v>11600101</v>
+            <v>11500503</v>
           </cell>
         </row>
         <row r="959">
           <cell r="C959">
-            <v>11600102</v>
+            <v>11600101</v>
           </cell>
         </row>
         <row r="960">
           <cell r="C960">
-            <v>11600103</v>
+            <v>11600102</v>
           </cell>
         </row>
         <row r="961">
           <cell r="C961">
-            <v>11600201</v>
+            <v>11600103</v>
           </cell>
         </row>
         <row r="962">
           <cell r="C962">
-            <v>11600202</v>
+            <v>11600201</v>
           </cell>
         </row>
         <row r="963">
           <cell r="C963">
-            <v>11600203</v>
+            <v>11600202</v>
           </cell>
         </row>
         <row r="964">
           <cell r="C964">
-            <v>11600301</v>
+            <v>11600203</v>
           </cell>
         </row>
         <row r="965">
           <cell r="C965">
-            <v>11600302</v>
+            <v>11600301</v>
           </cell>
         </row>
         <row r="966">
           <cell r="C966">
-            <v>11600303</v>
+            <v>11600302</v>
           </cell>
         </row>
         <row r="967">
           <cell r="C967">
-            <v>11600401</v>
+            <v>11600303</v>
           </cell>
         </row>
         <row r="968">
           <cell r="C968">
-            <v>11600402</v>
+            <v>11600401</v>
           </cell>
         </row>
         <row r="969">
           <cell r="C969">
-            <v>11600403</v>
+            <v>11600402</v>
           </cell>
         </row>
         <row r="970">
           <cell r="C970">
-            <v>11600501</v>
+            <v>11600403</v>
           </cell>
         </row>
         <row r="971">
           <cell r="C971">
-            <v>11600502</v>
+            <v>11600501</v>
           </cell>
         </row>
         <row r="972">
           <cell r="C972">
-            <v>11600503</v>
+            <v>11600502</v>
           </cell>
         </row>
         <row r="973">
           <cell r="C973">
-            <v>11600601</v>
+            <v>11600503</v>
           </cell>
         </row>
         <row r="974">
           <cell r="C974">
-            <v>11600602</v>
+            <v>11600601</v>
           </cell>
         </row>
         <row r="975">
           <cell r="C975">
-            <v>11600603</v>
+            <v>11600602</v>
           </cell>
         </row>
         <row r="976">
           <cell r="C976">
-            <v>11600701</v>
+            <v>11600603</v>
           </cell>
         </row>
         <row r="977">
           <cell r="C977">
-            <v>11600702</v>
+            <v>11600701</v>
           </cell>
         </row>
         <row r="978">
           <cell r="C978">
-            <v>11600703</v>
+            <v>11600702</v>
           </cell>
         </row>
         <row r="979">
           <cell r="C979">
-            <v>11600801</v>
+            <v>11600703</v>
           </cell>
         </row>
         <row r="980">
           <cell r="C980">
-            <v>11600802</v>
+            <v>11600801</v>
           </cell>
         </row>
         <row r="981">
           <cell r="C981">
-            <v>11600803</v>
+            <v>11600802</v>
           </cell>
         </row>
         <row r="982">
           <cell r="C982">
-            <v>11600901</v>
+            <v>11600803</v>
           </cell>
         </row>
         <row r="983">
           <cell r="C983">
-            <v>11600902</v>
+            <v>11600901</v>
           </cell>
         </row>
         <row r="984">
           <cell r="C984">
-            <v>11600903</v>
+            <v>11600902</v>
           </cell>
         </row>
         <row r="985">
           <cell r="C985">
-            <v>11610101</v>
+            <v>11600903</v>
           </cell>
         </row>
         <row r="986">
           <cell r="C986">
-            <v>11610102</v>
+            <v>11610101</v>
           </cell>
         </row>
         <row r="987">
           <cell r="C987">
-            <v>11610103</v>
+            <v>11610102</v>
           </cell>
         </row>
         <row r="988">
           <cell r="C988">
-            <v>11610201</v>
+            <v>11610103</v>
           </cell>
         </row>
         <row r="989">
           <cell r="C989">
-            <v>11610202</v>
+            <v>11610201</v>
           </cell>
         </row>
         <row r="990">
           <cell r="C990">
-            <v>11610203</v>
+            <v>11610202</v>
           </cell>
         </row>
         <row r="991">
           <cell r="C991">
-            <v>11610301</v>
+            <v>11610203</v>
           </cell>
         </row>
         <row r="992">
           <cell r="C992">
-            <v>11610302</v>
+            <v>11610301</v>
           </cell>
         </row>
         <row r="993">
           <cell r="C993">
-            <v>11610303</v>
+            <v>11610302</v>
           </cell>
         </row>
         <row r="994">
           <cell r="C994">
-            <v>11610401</v>
+            <v>11610303</v>
           </cell>
         </row>
         <row r="995">
           <cell r="C995">
-            <v>11610402</v>
+            <v>11610401</v>
           </cell>
         </row>
         <row r="996">
           <cell r="C996">
-            <v>11610403</v>
+            <v>11610402</v>
           </cell>
         </row>
         <row r="997">
           <cell r="C997">
-            <v>11610501</v>
+            <v>11610403</v>
           </cell>
         </row>
         <row r="998">
           <cell r="C998">
-            <v>11610502</v>
+            <v>11610501</v>
           </cell>
         </row>
         <row r="999">
           <cell r="C999">
-            <v>11610503</v>
+            <v>11610502</v>
           </cell>
         </row>
         <row r="1000">
           <cell r="C1000">
-            <v>11610601</v>
+            <v>11610503</v>
           </cell>
         </row>
         <row r="1001">
           <cell r="C1001">
-            <v>11610602</v>
+            <v>11610601</v>
           </cell>
         </row>
         <row r="1002">
           <cell r="C1002">
-            <v>11610603</v>
+            <v>11610602</v>
           </cell>
         </row>
         <row r="1003">
           <cell r="C1003">
-            <v>11610701</v>
+            <v>11610603</v>
           </cell>
         </row>
         <row r="1004">
           <cell r="C1004">
-            <v>11610702</v>
+            <v>11610701</v>
           </cell>
         </row>
         <row r="1005">
           <cell r="C1005">
-            <v>11610703</v>
+            <v>11610702</v>
           </cell>
         </row>
         <row r="1006">
           <cell r="C1006">
-            <v>13001001</v>
-          </cell>
-          <cell r="S1006">
-            <v>65001001</v>
+            <v>11610703</v>
           </cell>
         </row>
         <row r="1007">
           <cell r="C1007">
-            <v>13001002</v>
+            <v>13001001</v>
           </cell>
           <cell r="S1007">
-            <v>65001002</v>
+            <v>65001001</v>
           </cell>
         </row>
         <row r="1008">
           <cell r="C1008">
-            <v>13001003</v>
+            <v>13001002</v>
           </cell>
           <cell r="S1008">
-            <v>65001003</v>
+            <v>65001002</v>
           </cell>
         </row>
         <row r="1009">
           <cell r="C1009">
-            <v>13001004</v>
+            <v>13001003</v>
           </cell>
           <cell r="S1009">
-            <v>65001004</v>
+            <v>65001003</v>
           </cell>
         </row>
         <row r="1010">
           <cell r="C1010">
-            <v>13001005</v>
+            <v>13001004</v>
           </cell>
           <cell r="S1010">
-            <v>65001005</v>
+            <v>65001004</v>
           </cell>
         </row>
         <row r="1011">
           <cell r="C1011">
-            <v>13001006</v>
+            <v>13001005</v>
           </cell>
           <cell r="S1011">
-            <v>65001006</v>
+            <v>65001005</v>
           </cell>
         </row>
         <row r="1012">
           <cell r="C1012">
-            <v>13001101</v>
+            <v>13001006</v>
           </cell>
           <cell r="S1012">
-            <v>65001101</v>
+            <v>65001006</v>
           </cell>
         </row>
         <row r="1013">
           <cell r="C1013">
-            <v>13001102</v>
+            <v>13001101</v>
           </cell>
           <cell r="S1013">
-            <v>65001102</v>
+            <v>65001101</v>
           </cell>
         </row>
         <row r="1014">
           <cell r="C1014">
-            <v>13001103</v>
+            <v>13001102</v>
           </cell>
           <cell r="S1014">
-            <v>65001103</v>
+            <v>65001102</v>
           </cell>
         </row>
         <row r="1015">
           <cell r="C1015">
-            <v>13001104</v>
+            <v>13001103</v>
           </cell>
           <cell r="S1015">
-            <v>65001104</v>
+            <v>65001103</v>
           </cell>
         </row>
         <row r="1016">
           <cell r="C1016">
-            <v>13001105</v>
+            <v>13001104</v>
           </cell>
           <cell r="S1016">
-            <v>65001105</v>
+            <v>65001104</v>
           </cell>
         </row>
         <row r="1017">
           <cell r="C1017">
-            <v>13002001</v>
+            <v>13001105</v>
           </cell>
           <cell r="S1017">
-            <v>65002001</v>
+            <v>65001105</v>
           </cell>
         </row>
         <row r="1018">
           <cell r="C1018">
-            <v>13002002</v>
+            <v>13002001</v>
           </cell>
           <cell r="S1018">
-            <v>65002002</v>
+            <v>65002001</v>
           </cell>
         </row>
         <row r="1019">
           <cell r="C1019">
-            <v>13002003</v>
+            <v>13002002</v>
           </cell>
           <cell r="S1019">
-            <v>65002003</v>
+            <v>65002002</v>
           </cell>
         </row>
         <row r="1020">
           <cell r="C1020">
-            <v>13002004</v>
+            <v>13002003</v>
           </cell>
           <cell r="S1020">
-            <v>65002004</v>
+            <v>65002003</v>
           </cell>
         </row>
         <row r="1021">
           <cell r="C1021">
-            <v>13002005</v>
+            <v>13002004</v>
           </cell>
           <cell r="S1021">
-            <v>65002005</v>
+            <v>65002004</v>
           </cell>
         </row>
         <row r="1022">
           <cell r="C1022">
-            <v>13002006</v>
+            <v>13002005</v>
           </cell>
           <cell r="S1022">
-            <v>65002006</v>
+            <v>65002005</v>
           </cell>
         </row>
         <row r="1023">
           <cell r="C1023">
-            <v>13002101</v>
+            <v>13002006</v>
           </cell>
           <cell r="S1023">
-            <v>65002101</v>
+            <v>65002006</v>
           </cell>
         </row>
         <row r="1024">
           <cell r="C1024">
-            <v>13002102</v>
+            <v>13002101</v>
           </cell>
           <cell r="S1024">
-            <v>65002102</v>
+            <v>65002101</v>
           </cell>
         </row>
         <row r="1025">
           <cell r="C1025">
-            <v>13002103</v>
+            <v>13002102</v>
           </cell>
           <cell r="S1025">
-            <v>65002103</v>
+            <v>65002102</v>
           </cell>
         </row>
         <row r="1026">
           <cell r="C1026">
-            <v>13002104</v>
+            <v>13002103</v>
           </cell>
           <cell r="S1026">
-            <v>65002104</v>
+            <v>65002103</v>
           </cell>
         </row>
         <row r="1027">
           <cell r="C1027">
-            <v>13002105</v>
+            <v>13002104</v>
           </cell>
           <cell r="S1027">
-            <v>65002105</v>
+            <v>65002104</v>
           </cell>
         </row>
         <row r="1028">
           <cell r="C1028">
-            <v>13003001</v>
+            <v>13002105</v>
           </cell>
           <cell r="S1028">
-            <v>65003001</v>
+            <v>65002105</v>
           </cell>
         </row>
         <row r="1029">
           <cell r="C1029">
-            <v>13003002</v>
+            <v>13003001</v>
           </cell>
           <cell r="S1029">
-            <v>65003002</v>
+            <v>65003001</v>
           </cell>
         </row>
         <row r="1030">
           <cell r="C1030">
-            <v>13003003</v>
+            <v>13003002</v>
           </cell>
           <cell r="S1030">
-            <v>65003003</v>
+            <v>65003002</v>
           </cell>
         </row>
         <row r="1031">
           <cell r="C1031">
-            <v>13003004</v>
+            <v>13003003</v>
           </cell>
           <cell r="S1031">
-            <v>65003004</v>
+            <v>65003003</v>
           </cell>
         </row>
         <row r="1032">
           <cell r="C1032">
-            <v>13003005</v>
+            <v>13003004</v>
           </cell>
           <cell r="S1032">
-            <v>65003005</v>
+            <v>65003004</v>
           </cell>
         </row>
         <row r="1033">
           <cell r="C1033">
-            <v>13003006</v>
+            <v>13003005</v>
           </cell>
           <cell r="S1033">
-            <v>65003006</v>
+            <v>65003005</v>
           </cell>
         </row>
         <row r="1034">
           <cell r="C1034">
-            <v>13003101</v>
+            <v>13003006</v>
           </cell>
           <cell r="S1034">
-            <v>65003101</v>
+            <v>65003006</v>
           </cell>
         </row>
         <row r="1035">
           <cell r="C1035">
-            <v>13003102</v>
+            <v>13003101</v>
           </cell>
           <cell r="S1035">
-            <v>65003102</v>
+            <v>65003101</v>
           </cell>
         </row>
         <row r="1036">
           <cell r="C1036">
-            <v>13003103</v>
+            <v>13003102</v>
           </cell>
           <cell r="S1036">
-            <v>65003103</v>
+            <v>65003102</v>
           </cell>
         </row>
         <row r="1037">
           <cell r="C1037">
-            <v>13003104</v>
+            <v>13003103</v>
           </cell>
           <cell r="S1037">
-            <v>65003104</v>
+            <v>65003103</v>
           </cell>
         </row>
         <row r="1038">
           <cell r="C1038">
-            <v>13003105</v>
+            <v>13003104</v>
           </cell>
           <cell r="S1038">
-            <v>65003105</v>
+            <v>65003104</v>
           </cell>
         </row>
         <row r="1039">
           <cell r="C1039">
-            <v>13004001</v>
+            <v>13003105</v>
           </cell>
           <cell r="S1039">
-            <v>65004001</v>
+            <v>65003105</v>
           </cell>
         </row>
         <row r="1040">
           <cell r="C1040">
-            <v>13004002</v>
+            <v>13004001</v>
           </cell>
           <cell r="S1040">
-            <v>65004002</v>
+            <v>65004001</v>
           </cell>
         </row>
         <row r="1041">
           <cell r="C1041">
-            <v>13004003</v>
+            <v>13004002</v>
           </cell>
           <cell r="S1041">
-            <v>65004003</v>
+            <v>65004002</v>
           </cell>
         </row>
         <row r="1042">
           <cell r="C1042">
-            <v>13004004</v>
+            <v>13004003</v>
           </cell>
           <cell r="S1042">
-            <v>65004004</v>
+            <v>65004003</v>
           </cell>
         </row>
         <row r="1043">
           <cell r="C1043">
-            <v>13004005</v>
+            <v>13004004</v>
           </cell>
           <cell r="S1043">
-            <v>65004005</v>
+            <v>65004004</v>
           </cell>
         </row>
         <row r="1044">
           <cell r="C1044">
-            <v>13004006</v>
+            <v>13004005</v>
           </cell>
           <cell r="S1044">
-            <v>65004006</v>
+            <v>65004005</v>
           </cell>
         </row>
         <row r="1045">
           <cell r="C1045">
-            <v>13004101</v>
+            <v>13004006</v>
           </cell>
           <cell r="S1045">
-            <v>65004101</v>
+            <v>65004006</v>
           </cell>
         </row>
         <row r="1046">
           <cell r="C1046">
-            <v>13004102</v>
+            <v>13004101</v>
           </cell>
           <cell r="S1046">
-            <v>65004102</v>
+            <v>65004101</v>
           </cell>
         </row>
         <row r="1047">
           <cell r="C1047">
-            <v>13004103</v>
+            <v>13004102</v>
           </cell>
           <cell r="S1047">
-            <v>65004103</v>
+            <v>65004102</v>
           </cell>
         </row>
         <row r="1048">
           <cell r="C1048">
-            <v>13004104</v>
+            <v>13004103</v>
           </cell>
           <cell r="S1048">
-            <v>65004104</v>
+            <v>65004103</v>
           </cell>
         </row>
         <row r="1049">
           <cell r="C1049">
-            <v>13004105</v>
+            <v>13004104</v>
           </cell>
           <cell r="S1049">
-            <v>65004105</v>
+            <v>65004104</v>
           </cell>
         </row>
         <row r="1050">
           <cell r="C1050">
-            <v>13005001</v>
+            <v>13004105</v>
           </cell>
           <cell r="S1050">
-            <v>65005001</v>
+            <v>65004105</v>
           </cell>
         </row>
         <row r="1051">
           <cell r="C1051">
-            <v>13005002</v>
+            <v>13005001</v>
           </cell>
           <cell r="S1051">
-            <v>65005002</v>
+            <v>65005001</v>
           </cell>
         </row>
         <row r="1052">
           <cell r="C1052">
-            <v>13005003</v>
+            <v>13005002</v>
           </cell>
           <cell r="S1052">
-            <v>65005003</v>
+            <v>65005002</v>
           </cell>
         </row>
         <row r="1053">
           <cell r="C1053">
-            <v>13005004</v>
+            <v>13005003</v>
           </cell>
           <cell r="S1053">
-            <v>65005004</v>
+            <v>65005003</v>
           </cell>
         </row>
         <row r="1054">
           <cell r="C1054">
-            <v>13005005</v>
+            <v>13005004</v>
           </cell>
           <cell r="S1054">
-            <v>65005005</v>
+            <v>65005004</v>
           </cell>
         </row>
         <row r="1055">
           <cell r="C1055">
-            <v>13005006</v>
+            <v>13005005</v>
           </cell>
           <cell r="S1055">
-            <v>65005006</v>
+            <v>65005005</v>
           </cell>
         </row>
         <row r="1056">
           <cell r="C1056">
-            <v>13005101</v>
+            <v>13005006</v>
           </cell>
           <cell r="S1056">
-            <v>65005101</v>
+            <v>65005006</v>
           </cell>
         </row>
         <row r="1057">
           <cell r="C1057">
-            <v>13005102</v>
+            <v>13005101</v>
           </cell>
           <cell r="S1057">
-            <v>65005102</v>
+            <v>65005101</v>
           </cell>
         </row>
         <row r="1058">
           <cell r="C1058">
-            <v>13005103</v>
+            <v>13005102</v>
           </cell>
           <cell r="S1058">
-            <v>65005103</v>
+            <v>65005102</v>
           </cell>
         </row>
         <row r="1059">
           <cell r="C1059">
-            <v>13005104</v>
+            <v>13005103</v>
           </cell>
           <cell r="S1059">
-            <v>65005104</v>
+            <v>65005103</v>
           </cell>
         </row>
         <row r="1060">
           <cell r="C1060">
-            <v>13005105</v>
+            <v>13005104</v>
           </cell>
           <cell r="S1060">
-            <v>65005105</v>
+            <v>65005104</v>
           </cell>
         </row>
         <row r="1061">
           <cell r="C1061">
-            <v>13006001</v>
+            <v>13005105</v>
           </cell>
           <cell r="S1061">
-            <v>65006001</v>
+            <v>65005105</v>
           </cell>
         </row>
         <row r="1062">
           <cell r="C1062">
-            <v>13006002</v>
+            <v>13006001</v>
           </cell>
           <cell r="S1062">
-            <v>65006002</v>
+            <v>65006001</v>
           </cell>
         </row>
         <row r="1063">
           <cell r="C1063">
-            <v>13006003</v>
+            <v>13006002</v>
           </cell>
           <cell r="S1063">
-            <v>65006003</v>
+            <v>65006002</v>
           </cell>
         </row>
         <row r="1064">
           <cell r="C1064">
-            <v>13006004</v>
+            <v>13006003</v>
           </cell>
           <cell r="S1064">
-            <v>65006004</v>
+            <v>65006003</v>
           </cell>
         </row>
         <row r="1065">
           <cell r="C1065">
-            <v>13009001</v>
+            <v>13006004</v>
           </cell>
-          <cell r="S1065" t="str">
-            <v>4;20</v>
+          <cell r="S1065">
+            <v>65006004</v>
           </cell>
         </row>
         <row r="1066">
           <cell r="C1066">
-            <v>13009002</v>
+            <v>13009001</v>
           </cell>
           <cell r="S1066" t="str">
-            <v>5;20</v>
+            <v>4;20</v>
           </cell>
         </row>
         <row r="1067">
           <cell r="C1067">
-            <v>14000001</v>
+            <v>13009002</v>
+          </cell>
+          <cell r="S1067" t="str">
+            <v>5;20</v>
           </cell>
         </row>
         <row r="1068">
           <cell r="C1068">
-            <v>14000002</v>
+            <v>14000001</v>
           </cell>
         </row>
         <row r="1069">
           <cell r="C1069">
-            <v>14000003</v>
+            <v>14000002</v>
           </cell>
         </row>
         <row r="1070">
           <cell r="C1070">
-            <v>14000004</v>
+            <v>14000003</v>
           </cell>
         </row>
         <row r="1071">
           <cell r="C1071">
-            <v>14000005</v>
+            <v>14000004</v>
           </cell>
         </row>
         <row r="1072">
           <cell r="C1072">
-            <v>14010001</v>
+            <v>14000005</v>
           </cell>
         </row>
         <row r="1073">
           <cell r="C1073">
-            <v>14010002</v>
+            <v>14010001</v>
           </cell>
         </row>
         <row r="1074">
           <cell r="C1074">
-            <v>14010003</v>
+            <v>14010002</v>
           </cell>
         </row>
         <row r="1075">
           <cell r="C1075">
-            <v>14010004</v>
+            <v>14010003</v>
           </cell>
         </row>
         <row r="1076">
           <cell r="C1076">
-            <v>14010005</v>
+            <v>14010004</v>
           </cell>
         </row>
         <row r="1077">
           <cell r="C1077">
-            <v>14010006</v>
+            <v>14010005</v>
           </cell>
         </row>
         <row r="1078">
           <cell r="C1078">
-            <v>14010007</v>
+            <v>14010006</v>
           </cell>
         </row>
         <row r="1079">
           <cell r="C1079">
-            <v>14010008</v>
+            <v>14010007</v>
           </cell>
         </row>
         <row r="1080">
           <cell r="C1080">
-            <v>14010009</v>
+            <v>14010008</v>
           </cell>
         </row>
         <row r="1081">
           <cell r="C1081">
-            <v>14010010</v>
+            <v>14010009</v>
           </cell>
         </row>
         <row r="1082">
           <cell r="C1082">
-            <v>14010011</v>
+            <v>14010010</v>
           </cell>
         </row>
         <row r="1083">
           <cell r="C1083">
-            <v>14010012</v>
+            <v>14010011</v>
           </cell>
         </row>
         <row r="1084">
           <cell r="C1084">
-            <v>14020001</v>
+            <v>14010012</v>
           </cell>
         </row>
         <row r="1085">
           <cell r="C1085">
-            <v>14020002</v>
+            <v>14020001</v>
           </cell>
         </row>
         <row r="1086">
           <cell r="C1086">
-            <v>14020003</v>
+            <v>14020002</v>
           </cell>
         </row>
         <row r="1087">
           <cell r="C1087">
-            <v>14020004</v>
+            <v>14020003</v>
           </cell>
         </row>
         <row r="1088">
           <cell r="C1088">
-            <v>14020005</v>
+            <v>14020004</v>
           </cell>
         </row>
         <row r="1089">
           <cell r="C1089">
-            <v>14020006</v>
+            <v>14020005</v>
           </cell>
         </row>
         <row r="1090">
           <cell r="C1090">
-            <v>14020007</v>
+            <v>14020006</v>
           </cell>
         </row>
         <row r="1091">
           <cell r="C1091">
-            <v>14020008</v>
+            <v>14020007</v>
           </cell>
         </row>
         <row r="1092">
           <cell r="C1092">
-            <v>14020009</v>
+            <v>14020008</v>
           </cell>
         </row>
         <row r="1093">
           <cell r="C1093">
-            <v>14020010</v>
+            <v>14020009</v>
           </cell>
         </row>
         <row r="1094">
           <cell r="C1094">
-            <v>14020011</v>
+            <v>14020010</v>
           </cell>
         </row>
         <row r="1095">
           <cell r="C1095">
-            <v>14020012</v>
+            <v>14020011</v>
           </cell>
         </row>
         <row r="1096">
           <cell r="C1096">
-            <v>14020013</v>
+            <v>14020012</v>
           </cell>
         </row>
         <row r="1097">
           <cell r="C1097">
-            <v>14030001</v>
+            <v>14020013</v>
           </cell>
         </row>
         <row r="1098">
           <cell r="C1098">
-            <v>14030002</v>
+            <v>14030001</v>
           </cell>
         </row>
         <row r="1099">
           <cell r="C1099">
-            <v>14030003</v>
+            <v>14030002</v>
           </cell>
         </row>
         <row r="1100">
           <cell r="C1100">
-            <v>14030004</v>
+            <v>14030003</v>
           </cell>
         </row>
         <row r="1101">
           <cell r="C1101">
-            <v>14030005</v>
+            <v>14030004</v>
           </cell>
         </row>
         <row r="1102">
           <cell r="C1102">
-            <v>14030006</v>
+            <v>14030005</v>
           </cell>
         </row>
         <row r="1103">
           <cell r="C1103">
-            <v>14030007</v>
+            <v>14030006</v>
           </cell>
         </row>
         <row r="1104">
           <cell r="C1104">
-            <v>14030008</v>
+            <v>14030007</v>
           </cell>
         </row>
         <row r="1105">
           <cell r="C1105">
-            <v>14030009</v>
+            <v>14030008</v>
           </cell>
         </row>
         <row r="1106">
           <cell r="C1106">
-            <v>14030010</v>
+            <v>14030009</v>
           </cell>
         </row>
         <row r="1107">
           <cell r="C1107">
-            <v>14030011</v>
+            <v>14030010</v>
           </cell>
         </row>
         <row r="1108">
           <cell r="C1108">
-            <v>14030012</v>
+            <v>14030011</v>
           </cell>
         </row>
         <row r="1109">
           <cell r="C1109">
-            <v>14030013</v>
+            <v>14030012</v>
           </cell>
         </row>
         <row r="1110">
           <cell r="C1110">
-            <v>14040001</v>
+            <v>14030013</v>
           </cell>
         </row>
         <row r="1111">
           <cell r="C1111">
-            <v>14040002</v>
+            <v>14040001</v>
           </cell>
         </row>
         <row r="1112">
           <cell r="C1112">
-            <v>14040003</v>
+            <v>14040002</v>
           </cell>
         </row>
         <row r="1113">
           <cell r="C1113">
-            <v>14040004</v>
+            <v>14040003</v>
           </cell>
         </row>
         <row r="1114">
           <cell r="C1114">
-            <v>14040005</v>
+            <v>14040004</v>
           </cell>
         </row>
         <row r="1115">
           <cell r="C1115">
-            <v>14040006</v>
+            <v>14040005</v>
           </cell>
         </row>
         <row r="1116">
           <cell r="C1116">
-            <v>14040007</v>
+            <v>14040006</v>
           </cell>
         </row>
         <row r="1117">
           <cell r="C1117">
-            <v>14040008</v>
+            <v>14040007</v>
           </cell>
         </row>
         <row r="1118">
           <cell r="C1118">
-            <v>14040009</v>
+            <v>14040008</v>
           </cell>
         </row>
         <row r="1119">
           <cell r="C1119">
-            <v>14040010</v>
+            <v>14040009</v>
           </cell>
         </row>
         <row r="1120">
           <cell r="C1120">
-            <v>14040011</v>
+            <v>14040010</v>
           </cell>
         </row>
         <row r="1121">
           <cell r="C1121">
-            <v>14040012</v>
+            <v>14040011</v>
           </cell>
         </row>
         <row r="1122">
           <cell r="C1122">
-            <v>14050001</v>
+            <v>14040012</v>
           </cell>
         </row>
         <row r="1123">
           <cell r="C1123">
-            <v>14050002</v>
+            <v>14050001</v>
           </cell>
         </row>
         <row r="1124">
           <cell r="C1124">
-            <v>14050003</v>
+            <v>14050002</v>
           </cell>
         </row>
         <row r="1125">
           <cell r="C1125">
-            <v>14050004</v>
+            <v>14050003</v>
           </cell>
         </row>
         <row r="1126">
           <cell r="C1126">
-            <v>14050005</v>
+            <v>14050004</v>
           </cell>
         </row>
         <row r="1127">
           <cell r="C1127">
-            <v>14050006</v>
+            <v>14050005</v>
           </cell>
         </row>
         <row r="1128">
           <cell r="C1128">
-            <v>14050007</v>
+            <v>14050006</v>
           </cell>
         </row>
         <row r="1129">
           <cell r="C1129">
-            <v>14050008</v>
+            <v>14050007</v>
           </cell>
         </row>
         <row r="1130">
           <cell r="C1130">
-            <v>14050009</v>
+            <v>14050008</v>
           </cell>
         </row>
         <row r="1131">
           <cell r="C1131">
-            <v>14050010</v>
+            <v>14050009</v>
           </cell>
         </row>
         <row r="1132">
           <cell r="C1132">
-            <v>14050011</v>
+            <v>14050010</v>
           </cell>
         </row>
         <row r="1133">
           <cell r="C1133">
-            <v>14050012</v>
+            <v>14050011</v>
           </cell>
         </row>
         <row r="1134">
           <cell r="C1134">
-            <v>14060001</v>
+            <v>14050012</v>
           </cell>
         </row>
         <row r="1135">
           <cell r="C1135">
-            <v>14060002</v>
+            <v>14060001</v>
           </cell>
         </row>
         <row r="1136">
           <cell r="C1136">
-            <v>14060003</v>
+            <v>14060002</v>
           </cell>
         </row>
         <row r="1137">
           <cell r="C1137">
-            <v>14060004</v>
+            <v>14060003</v>
           </cell>
         </row>
         <row r="1138">
           <cell r="C1138">
-            <v>14060005</v>
+            <v>14060004</v>
           </cell>
         </row>
         <row r="1139">
           <cell r="C1139">
-            <v>14060006</v>
+            <v>14060005</v>
           </cell>
         </row>
         <row r="1140">
           <cell r="C1140">
-            <v>14070001</v>
+            <v>14060006</v>
           </cell>
         </row>
         <row r="1141">
           <cell r="C1141">
-            <v>14070002</v>
+            <v>14070001</v>
           </cell>
         </row>
         <row r="1142">
           <cell r="C1142">
-            <v>14070003</v>
+            <v>14070002</v>
           </cell>
         </row>
         <row r="1143">
           <cell r="C1143">
-            <v>14070004</v>
+            <v>14070003</v>
           </cell>
         </row>
         <row r="1144">
           <cell r="C1144">
-            <v>14080001</v>
+            <v>14070004</v>
           </cell>
         </row>
         <row r="1145">
           <cell r="C1145">
-            <v>14080002</v>
+            <v>14080001</v>
           </cell>
         </row>
         <row r="1146">
           <cell r="C1146">
-            <v>14080003</v>
+            <v>14080002</v>
           </cell>
         </row>
         <row r="1147">
           <cell r="C1147">
-            <v>14080004</v>
+            <v>14080003</v>
           </cell>
         </row>
         <row r="1148">
           <cell r="C1148">
-            <v>14090001</v>
+            <v>14080004</v>
           </cell>
         </row>
         <row r="1149">
           <cell r="C1149">
-            <v>14090002</v>
+            <v>14090001</v>
           </cell>
         </row>
         <row r="1150">
           <cell r="C1150">
-            <v>14090003</v>
+            <v>14090002</v>
           </cell>
         </row>
         <row r="1151">
           <cell r="C1151">
-            <v>14090004</v>
+            <v>14090003</v>
           </cell>
         </row>
         <row r="1152">
           <cell r="C1152">
-            <v>14100001</v>
+            <v>14090004</v>
           </cell>
         </row>
         <row r="1153">
           <cell r="C1153">
-            <v>14100002</v>
+            <v>14100001</v>
           </cell>
         </row>
         <row r="1154">
           <cell r="C1154">
-            <v>14100003</v>
+            <v>14100002</v>
           </cell>
         </row>
         <row r="1155">
           <cell r="C1155">
-            <v>14100004</v>
+            <v>14100003</v>
           </cell>
         </row>
         <row r="1156">
           <cell r="C1156">
-            <v>14100005</v>
+            <v>14100004</v>
           </cell>
         </row>
         <row r="1157">
           <cell r="C1157">
-            <v>14100006</v>
+            <v>14100005</v>
           </cell>
         </row>
         <row r="1158">
           <cell r="C1158">
-            <v>14100007</v>
+            <v>14100006</v>
           </cell>
         </row>
         <row r="1159">
           <cell r="C1159">
-            <v>14100008</v>
+            <v>14100007</v>
           </cell>
         </row>
         <row r="1160">
           <cell r="C1160">
-            <v>14100011</v>
+            <v>14100008</v>
           </cell>
         </row>
         <row r="1161">
           <cell r="C1161">
-            <v>14100012</v>
+            <v>14100011</v>
           </cell>
         </row>
         <row r="1162">
           <cell r="C1162">
-            <v>14100021</v>
+            <v>14100012</v>
           </cell>
         </row>
         <row r="1163">
           <cell r="C1163">
-            <v>14100022</v>
+            <v>14100021</v>
           </cell>
         </row>
         <row r="1164">
           <cell r="C1164">
-            <v>14100101</v>
+            <v>14100022</v>
           </cell>
         </row>
         <row r="1165">
           <cell r="C1165">
-            <v>14100102</v>
+            <v>14100101</v>
           </cell>
         </row>
         <row r="1166">
           <cell r="C1166">
-            <v>14100103</v>
+            <v>14100102</v>
           </cell>
         </row>
         <row r="1167">
           <cell r="C1167">
-            <v>14100104</v>
+            <v>14100103</v>
           </cell>
         </row>
         <row r="1168">
           <cell r="C1168">
-            <v>14100105</v>
+            <v>14100104</v>
           </cell>
         </row>
         <row r="1169">
           <cell r="C1169">
-            <v>14100106</v>
+            <v>14100105</v>
           </cell>
         </row>
         <row r="1170">
           <cell r="C1170">
-            <v>14100107</v>
+            <v>14100106</v>
           </cell>
         </row>
         <row r="1171">
           <cell r="C1171">
-            <v>14100108</v>
+            <v>14100107</v>
           </cell>
         </row>
         <row r="1172">
           <cell r="C1172">
-            <v>14100111</v>
+            <v>14100108</v>
           </cell>
         </row>
         <row r="1173">
           <cell r="C1173">
-            <v>14100112</v>
+            <v>14100111</v>
           </cell>
         </row>
         <row r="1174">
           <cell r="C1174">
-            <v>14100121</v>
+            <v>14100112</v>
           </cell>
         </row>
         <row r="1175">
           <cell r="C1175">
-            <v>14100122</v>
+            <v>14100121</v>
           </cell>
         </row>
         <row r="1176">
           <cell r="C1176">
-            <v>14100201</v>
+            <v>14100122</v>
           </cell>
         </row>
         <row r="1177">
           <cell r="C1177">
-            <v>14100202</v>
+            <v>14100201</v>
           </cell>
         </row>
         <row r="1178">
           <cell r="C1178">
-            <v>14100203</v>
+            <v>14100202</v>
           </cell>
         </row>
         <row r="1179">
           <cell r="C1179">
-            <v>14100204</v>
+            <v>14100203</v>
           </cell>
         </row>
         <row r="1180">
           <cell r="C1180">
-            <v>14100211</v>
+            <v>14100204</v>
           </cell>
         </row>
         <row r="1181">
           <cell r="C1181">
-            <v>14100221</v>
+            <v>14100211</v>
           </cell>
         </row>
         <row r="1182">
           <cell r="C1182">
-            <v>14110001</v>
+            <v>14100221</v>
           </cell>
         </row>
         <row r="1183">
           <cell r="C1183">
-            <v>14110002</v>
+            <v>14110001</v>
           </cell>
         </row>
         <row r="1184">
           <cell r="C1184">
-            <v>14110003</v>
+            <v>14110002</v>
           </cell>
         </row>
         <row r="1185">
           <cell r="C1185">
-            <v>14110004</v>
+            <v>14110003</v>
           </cell>
         </row>
         <row r="1186">
           <cell r="C1186">
-            <v>14110005</v>
+            <v>14110004</v>
           </cell>
         </row>
         <row r="1187">
           <cell r="C1187">
-            <v>14110006</v>
+            <v>14110005</v>
           </cell>
         </row>
         <row r="1188">
           <cell r="C1188">
-            <v>14110007</v>
+            <v>14110006</v>
           </cell>
         </row>
         <row r="1189">
           <cell r="C1189">
-            <v>14110008</v>
+            <v>14110007</v>
           </cell>
         </row>
         <row r="1190">
           <cell r="C1190">
-            <v>14110009</v>
+            <v>14110008</v>
           </cell>
         </row>
         <row r="1191">
           <cell r="C1191">
-            <v>14110010</v>
+            <v>14110009</v>
           </cell>
         </row>
         <row r="1192">
           <cell r="C1192">
-            <v>14110011</v>
+            <v>14110010</v>
           </cell>
         </row>
         <row r="1193">
           <cell r="C1193">
-            <v>14110012</v>
+            <v>14110011</v>
           </cell>
         </row>
         <row r="1194">
           <cell r="C1194">
-            <v>14110021</v>
+            <v>14110012</v>
           </cell>
         </row>
         <row r="1195">
           <cell r="C1195">
-            <v>14110022</v>
+            <v>14110021</v>
           </cell>
         </row>
         <row r="1196">
           <cell r="C1196">
-            <v>14110023</v>
+            <v>14110022</v>
           </cell>
         </row>
         <row r="1197">
           <cell r="C1197">
-            <v>15201001</v>
+            <v>14110023</v>
           </cell>
         </row>
         <row r="1198">
           <cell r="C1198">
-            <v>15201002</v>
+            <v>15201001</v>
           </cell>
         </row>
         <row r="1199">
           <cell r="C1199">
-            <v>15201003</v>
+            <v>15201002</v>
           </cell>
         </row>
         <row r="1200">
           <cell r="C1200">
-            <v>15201004</v>
+            <v>15201003</v>
           </cell>
         </row>
         <row r="1201">
           <cell r="C1201">
-            <v>15201005</v>
+            <v>15201004</v>
           </cell>
         </row>
         <row r="1202">
           <cell r="C1202">
-            <v>15201006</v>
+            <v>15201005</v>
           </cell>
         </row>
         <row r="1203">
           <cell r="C1203">
-            <v>15202001</v>
+            <v>15201006</v>
           </cell>
         </row>
         <row r="1204">
           <cell r="C1204">
-            <v>15202002</v>
+            <v>15202001</v>
           </cell>
         </row>
         <row r="1205">
           <cell r="C1205">
-            <v>15202003</v>
+            <v>15202002</v>
           </cell>
         </row>
         <row r="1206">
           <cell r="C1206">
-            <v>15202004</v>
+            <v>15202003</v>
           </cell>
         </row>
         <row r="1207">
           <cell r="C1207">
-            <v>15202005</v>
+            <v>15202004</v>
           </cell>
         </row>
         <row r="1208">
           <cell r="C1208">
-            <v>15202006</v>
+            <v>15202005</v>
           </cell>
         </row>
         <row r="1209">
           <cell r="C1209">
-            <v>15203001</v>
+            <v>15202006</v>
           </cell>
         </row>
         <row r="1210">
           <cell r="C1210">
-            <v>15203002</v>
+            <v>15203001</v>
           </cell>
         </row>
         <row r="1211">
           <cell r="C1211">
-            <v>15203003</v>
+            <v>15203002</v>
           </cell>
         </row>
         <row r="1212">
           <cell r="C1212">
-            <v>15203004</v>
+            <v>15203003</v>
           </cell>
         </row>
         <row r="1213">
           <cell r="C1213">
-            <v>15203005</v>
+            <v>15203004</v>
           </cell>
         </row>
         <row r="1214">
           <cell r="C1214">
-            <v>15203006</v>
+            <v>15203005</v>
           </cell>
         </row>
         <row r="1215">
           <cell r="C1215">
-            <v>15204001</v>
+            <v>15203006</v>
           </cell>
         </row>
         <row r="1216">
           <cell r="C1216">
-            <v>15204002</v>
+            <v>15204001</v>
           </cell>
         </row>
         <row r="1217">
           <cell r="C1217">
-            <v>15204003</v>
+            <v>15204002</v>
           </cell>
         </row>
         <row r="1218">
           <cell r="C1218">
-            <v>15204004</v>
+            <v>15204003</v>
           </cell>
         </row>
         <row r="1219">
           <cell r="C1219">
-            <v>15204005</v>
+            <v>15204004</v>
           </cell>
         </row>
         <row r="1220">
           <cell r="C1220">
-            <v>15204006</v>
+            <v>15204005</v>
           </cell>
         </row>
         <row r="1221">
           <cell r="C1221">
-            <v>15205001</v>
+            <v>15204006</v>
           </cell>
         </row>
         <row r="1222">
           <cell r="C1222">
-            <v>15205002</v>
+            <v>15205001</v>
           </cell>
         </row>
         <row r="1223">
           <cell r="C1223">
-            <v>15205003</v>
+            <v>15205002</v>
           </cell>
         </row>
         <row r="1224">
           <cell r="C1224">
-            <v>15205004</v>
+            <v>15205003</v>
           </cell>
         </row>
         <row r="1225">
           <cell r="C1225">
-            <v>15205005</v>
+            <v>15205004</v>
           </cell>
         </row>
         <row r="1226">
           <cell r="C1226">
-            <v>15205006</v>
+            <v>15205005</v>
           </cell>
         </row>
         <row r="1227">
           <cell r="C1227">
-            <v>15205007</v>
+            <v>15205006</v>
           </cell>
         </row>
         <row r="1228">
           <cell r="C1228">
-            <v>15206001</v>
+            <v>15205007</v>
           </cell>
         </row>
         <row r="1229">
           <cell r="C1229">
-            <v>15206002</v>
+            <v>15206001</v>
           </cell>
         </row>
         <row r="1230">
           <cell r="C1230">
-            <v>15206003</v>
+            <v>15206002</v>
           </cell>
         </row>
         <row r="1231">
           <cell r="C1231">
-            <v>15207001</v>
+            <v>15206003</v>
           </cell>
         </row>
         <row r="1232">
           <cell r="C1232">
-            <v>15207002</v>
+            <v>15207001</v>
           </cell>
         </row>
         <row r="1233">
           <cell r="C1233">
-            <v>15207003</v>
+            <v>15207002</v>
           </cell>
         </row>
         <row r="1234">
           <cell r="C1234">
-            <v>15208001</v>
+            <v>15207003</v>
           </cell>
         </row>
         <row r="1235">
           <cell r="C1235">
-            <v>15208002</v>
+            <v>15208001</v>
           </cell>
         </row>
         <row r="1236">
           <cell r="C1236">
-            <v>15208003</v>
+            <v>15208002</v>
           </cell>
         </row>
         <row r="1237">
           <cell r="C1237">
-            <v>15209001</v>
+            <v>15208003</v>
           </cell>
         </row>
         <row r="1238">
           <cell r="C1238">
-            <v>15209002</v>
+            <v>15209001</v>
           </cell>
         </row>
         <row r="1239">
           <cell r="C1239">
-            <v>15210001</v>
+            <v>15209002</v>
           </cell>
         </row>
         <row r="1240">
           <cell r="C1240">
-            <v>15210002</v>
+            <v>15210001</v>
           </cell>
         </row>
         <row r="1241">
           <cell r="C1241">
-            <v>15210003</v>
+            <v>15210002</v>
           </cell>
         </row>
         <row r="1242">
           <cell r="C1242">
-            <v>15210004</v>
+            <v>15210003</v>
           </cell>
         </row>
         <row r="1243">
           <cell r="C1243">
-            <v>15210011</v>
+            <v>15210004</v>
           </cell>
         </row>
         <row r="1244">
           <cell r="C1244">
-            <v>15210012</v>
+            <v>15210011</v>
           </cell>
         </row>
         <row r="1245">
           <cell r="C1245">
-            <v>15210101</v>
+            <v>15210012</v>
           </cell>
         </row>
         <row r="1246">
           <cell r="C1246">
-            <v>15210102</v>
+            <v>15210101</v>
           </cell>
         </row>
         <row r="1247">
           <cell r="C1247">
-            <v>15210103</v>
+            <v>15210102</v>
           </cell>
         </row>
         <row r="1248">
           <cell r="C1248">
-            <v>15210104</v>
+            <v>15210103</v>
           </cell>
         </row>
         <row r="1249">
           <cell r="C1249">
-            <v>15210111</v>
+            <v>15210104</v>
           </cell>
         </row>
         <row r="1250">
           <cell r="C1250">
-            <v>15210112</v>
+            <v>15210111</v>
           </cell>
         </row>
         <row r="1251">
           <cell r="C1251">
-            <v>15210201</v>
+            <v>15210112</v>
           </cell>
         </row>
         <row r="1252">
           <cell r="C1252">
-            <v>15210202</v>
+            <v>15210201</v>
           </cell>
         </row>
         <row r="1253">
           <cell r="C1253">
-            <v>15210211</v>
+            <v>15210202</v>
           </cell>
         </row>
         <row r="1254">
           <cell r="C1254">
-            <v>15211001</v>
+            <v>15210211</v>
           </cell>
         </row>
         <row r="1255">
           <cell r="C1255">
-            <v>15211002</v>
+            <v>15211001</v>
           </cell>
         </row>
         <row r="1256">
           <cell r="C1256">
-            <v>15211003</v>
+            <v>15211002</v>
           </cell>
         </row>
         <row r="1257">
           <cell r="C1257">
-            <v>15211004</v>
+            <v>15211003</v>
           </cell>
         </row>
         <row r="1258">
           <cell r="C1258">
-            <v>15211005</v>
+            <v>15211004</v>
           </cell>
         </row>
         <row r="1259">
           <cell r="C1259">
-            <v>15211006</v>
+            <v>15211005</v>
           </cell>
         </row>
         <row r="1260">
           <cell r="C1260">
-            <v>15211011</v>
+            <v>15211006</v>
           </cell>
         </row>
         <row r="1261">
           <cell r="C1261">
-            <v>15211012</v>
+            <v>15211011</v>
           </cell>
         </row>
         <row r="1262">
           <cell r="C1262">
-            <v>15211013</v>
+            <v>15211012</v>
           </cell>
         </row>
         <row r="1263">
           <cell r="C1263">
-            <v>15301001</v>
+            <v>15211013</v>
           </cell>
         </row>
         <row r="1264">
           <cell r="C1264">
-            <v>15301002</v>
+            <v>15301001</v>
           </cell>
         </row>
         <row r="1265">
           <cell r="C1265">
-            <v>15301003</v>
+            <v>15301002</v>
           </cell>
         </row>
         <row r="1266">
           <cell r="C1266">
-            <v>15301004</v>
+            <v>15301003</v>
           </cell>
         </row>
         <row r="1267">
           <cell r="C1267">
-            <v>15301005</v>
+            <v>15301004</v>
           </cell>
         </row>
         <row r="1268">
           <cell r="C1268">
-            <v>15301006</v>
+            <v>15301005</v>
           </cell>
         </row>
         <row r="1269">
           <cell r="C1269">
-            <v>15302001</v>
+            <v>15301006</v>
           </cell>
         </row>
         <row r="1270">
           <cell r="C1270">
-            <v>15302002</v>
+            <v>15302001</v>
           </cell>
         </row>
         <row r="1271">
           <cell r="C1271">
-            <v>15302003</v>
+            <v>15302002</v>
           </cell>
         </row>
         <row r="1272">
           <cell r="C1272">
-            <v>15302004</v>
+            <v>15302003</v>
           </cell>
         </row>
         <row r="1273">
           <cell r="C1273">
-            <v>15302005</v>
+            <v>15302004</v>
           </cell>
         </row>
         <row r="1274">
           <cell r="C1274">
-            <v>15302006</v>
+            <v>15302005</v>
           </cell>
         </row>
         <row r="1275">
           <cell r="C1275">
-            <v>15302007</v>
+            <v>15302006</v>
           </cell>
         </row>
         <row r="1276">
           <cell r="C1276">
-            <v>15303001</v>
+            <v>15302007</v>
           </cell>
         </row>
         <row r="1277">
           <cell r="C1277">
-            <v>15303002</v>
+            <v>15303001</v>
           </cell>
         </row>
         <row r="1278">
           <cell r="C1278">
-            <v>15303003</v>
+            <v>15303002</v>
           </cell>
         </row>
         <row r="1279">
           <cell r="C1279">
-            <v>15303004</v>
+            <v>15303003</v>
           </cell>
         </row>
         <row r="1280">
           <cell r="C1280">
-            <v>15303005</v>
+            <v>15303004</v>
           </cell>
         </row>
         <row r="1281">
           <cell r="C1281">
-            <v>15303006</v>
+            <v>15303005</v>
           </cell>
         </row>
         <row r="1282">
           <cell r="C1282">
-            <v>15304001</v>
+            <v>15303006</v>
           </cell>
         </row>
         <row r="1283">
           <cell r="C1283">
-            <v>15304002</v>
+            <v>15304001</v>
           </cell>
         </row>
         <row r="1284">
           <cell r="C1284">
-            <v>15304003</v>
+            <v>15304002</v>
           </cell>
         </row>
         <row r="1285">
           <cell r="C1285">
-            <v>15304004</v>
+            <v>15304003</v>
           </cell>
         </row>
         <row r="1286">
           <cell r="C1286">
-            <v>15304005</v>
+            <v>15304004</v>
           </cell>
         </row>
         <row r="1287">
           <cell r="C1287">
-            <v>15304006</v>
+            <v>15304005</v>
           </cell>
         </row>
         <row r="1288">
           <cell r="C1288">
-            <v>15305001</v>
+            <v>15304006</v>
           </cell>
         </row>
         <row r="1289">
           <cell r="C1289">
-            <v>15305002</v>
+            <v>15305001</v>
           </cell>
         </row>
         <row r="1290">
           <cell r="C1290">
-            <v>15305003</v>
+            <v>15305002</v>
           </cell>
         </row>
         <row r="1291">
           <cell r="C1291">
-            <v>15305004</v>
+            <v>15305003</v>
           </cell>
         </row>
         <row r="1292">
           <cell r="C1292">
-            <v>15305005</v>
+            <v>15305004</v>
           </cell>
         </row>
         <row r="1293">
           <cell r="C1293">
-            <v>15305006</v>
+            <v>15305005</v>
           </cell>
         </row>
         <row r="1294">
           <cell r="C1294">
-            <v>15306001</v>
+            <v>15305006</v>
           </cell>
         </row>
         <row r="1295">
           <cell r="C1295">
-            <v>15306002</v>
+            <v>15306001</v>
           </cell>
         </row>
         <row r="1296">
           <cell r="C1296">
-            <v>15306003</v>
+            <v>15306002</v>
           </cell>
         </row>
         <row r="1297">
           <cell r="C1297">
-            <v>15307001</v>
+            <v>15306003</v>
           </cell>
         </row>
         <row r="1298">
           <cell r="C1298">
-            <v>15307002</v>
+            <v>15307001</v>
           </cell>
         </row>
         <row r="1299">
           <cell r="C1299">
-            <v>15308001</v>
+            <v>15307002</v>
           </cell>
         </row>
         <row r="1300">
           <cell r="C1300">
-            <v>15308002</v>
+            <v>15308001</v>
           </cell>
         </row>
         <row r="1301">
           <cell r="C1301">
-            <v>15308003</v>
+            <v>15308002</v>
           </cell>
         </row>
         <row r="1302">
           <cell r="C1302">
-            <v>15308004</v>
+            <v>15308003</v>
           </cell>
         </row>
         <row r="1303">
           <cell r="C1303">
-            <v>15309001</v>
+            <v>15308004</v>
           </cell>
         </row>
         <row r="1304">
           <cell r="C1304">
-            <v>15309002</v>
+            <v>15309001</v>
           </cell>
         </row>
         <row r="1305">
           <cell r="C1305">
-            <v>15309003</v>
+            <v>15309002</v>
           </cell>
         </row>
         <row r="1306">
           <cell r="C1306">
-            <v>15310001</v>
+            <v>15309003</v>
           </cell>
         </row>
         <row r="1307">
           <cell r="C1307">
-            <v>15310002</v>
+            <v>15310001</v>
           </cell>
         </row>
         <row r="1308">
           <cell r="C1308">
-            <v>15310003</v>
+            <v>15310002</v>
           </cell>
         </row>
         <row r="1309">
           <cell r="C1309">
-            <v>15310004</v>
+            <v>15310003</v>
           </cell>
         </row>
         <row r="1310">
           <cell r="C1310">
-            <v>15310011</v>
+            <v>15310004</v>
           </cell>
         </row>
         <row r="1311">
           <cell r="C1311">
-            <v>15310012</v>
+            <v>15310011</v>
           </cell>
         </row>
         <row r="1312">
           <cell r="C1312">
-            <v>15310101</v>
+            <v>15310012</v>
           </cell>
         </row>
         <row r="1313">
           <cell r="C1313">
-            <v>15310102</v>
+            <v>15310101</v>
           </cell>
         </row>
         <row r="1314">
           <cell r="C1314">
-            <v>15310103</v>
+            <v>15310102</v>
           </cell>
         </row>
         <row r="1315">
           <cell r="C1315">
-            <v>15310104</v>
+            <v>15310103</v>
           </cell>
         </row>
         <row r="1316">
           <cell r="C1316">
-            <v>15310111</v>
+            <v>15310104</v>
           </cell>
         </row>
         <row r="1317">
           <cell r="C1317">
-            <v>15310112</v>
+            <v>15310111</v>
           </cell>
         </row>
         <row r="1318">
           <cell r="C1318">
-            <v>15310201</v>
+            <v>15310112</v>
           </cell>
         </row>
         <row r="1319">
           <cell r="C1319">
-            <v>15310202</v>
+            <v>15310201</v>
           </cell>
         </row>
         <row r="1320">
           <cell r="C1320">
-            <v>15310211</v>
+            <v>15310202</v>
           </cell>
         </row>
         <row r="1321">
           <cell r="C1321">
-            <v>15311001</v>
+            <v>15310211</v>
           </cell>
         </row>
         <row r="1322">
           <cell r="C1322">
-            <v>15311002</v>
+            <v>15311001</v>
           </cell>
         </row>
         <row r="1323">
           <cell r="C1323">
-            <v>15311003</v>
+            <v>15311002</v>
           </cell>
         </row>
         <row r="1324">
           <cell r="C1324">
-            <v>15311004</v>
+            <v>15311003</v>
           </cell>
         </row>
         <row r="1325">
           <cell r="C1325">
-            <v>15311005</v>
+            <v>15311004</v>
           </cell>
         </row>
         <row r="1326">
           <cell r="C1326">
-            <v>15311006</v>
+            <v>15311005</v>
           </cell>
         </row>
         <row r="1327">
           <cell r="C1327">
-            <v>15311011</v>
+            <v>15311006</v>
           </cell>
         </row>
         <row r="1328">
           <cell r="C1328">
-            <v>15311012</v>
+            <v>15311011</v>
           </cell>
         </row>
         <row r="1329">
           <cell r="C1329">
-            <v>15311013</v>
+            <v>15311012</v>
           </cell>
         </row>
         <row r="1330">
           <cell r="C1330">
-            <v>15401001</v>
+            <v>15311013</v>
           </cell>
         </row>
         <row r="1331">
           <cell r="C1331">
-            <v>15401002</v>
+            <v>15401001</v>
           </cell>
         </row>
         <row r="1332">
           <cell r="C1332">
-            <v>15401003</v>
+            <v>15401002</v>
           </cell>
         </row>
         <row r="1333">
           <cell r="C1333">
+            <v>15401003</v>
+          </cell>
+        </row>
+        <row r="1334">
+          <cell r="C1334">
             <v>15401004</v>
           </cell>
         </row>
@@ -36949,7 +36957,9 @@
       <c r="R2" s="3" t="s">
         <v>3122</v>
       </c>
-      <c r="S2" s="1"/>
+      <c r="S2" s="1" t="s">
+        <v>3126</v>
+      </c>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -36991,7 +37001,9 @@
       <c r="R3" s="3" t="s">
         <v>3124</v>
       </c>
-      <c r="S3" s="1"/>
+      <c r="S3" s="1" t="s">
+        <v>3127</v>
+      </c>
       <c r="Y3" s="1" t="s">
         <v>3083</v>
       </c>
@@ -69999,6 +70011,13 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="CP23:CP25"/>
+    <mergeCell ref="CP26:CP28"/>
+    <mergeCell ref="CP8:CP10"/>
+    <mergeCell ref="CP11:CP13"/>
+    <mergeCell ref="CP14:CP16"/>
+    <mergeCell ref="CP17:CP19"/>
+    <mergeCell ref="CP20:CP22"/>
     <mergeCell ref="K18:K20"/>
     <mergeCell ref="K21:K23"/>
     <mergeCell ref="AX4:AX6"/>
@@ -70013,13 +70032,6 @@
     <mergeCell ref="K9:K11"/>
     <mergeCell ref="K12:K14"/>
     <mergeCell ref="K15:K17"/>
-    <mergeCell ref="CP23:CP25"/>
-    <mergeCell ref="CP26:CP28"/>
-    <mergeCell ref="CP8:CP10"/>
-    <mergeCell ref="CP11:CP13"/>
-    <mergeCell ref="CP14:CP16"/>
-    <mergeCell ref="CP17:CP19"/>
-    <mergeCell ref="CP20:CP22"/>
   </mergeCells>
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -84743,7 +84755,7 @@
         <v>1200</v>
       </c>
       <c r="P96" s="1">
-        <f>LOOKUP(Q96,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(Q96,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="Q96" s="1">
@@ -84758,7 +84770,7 @@
       <c r="T96" s="3"/>
       <c r="U96" s="3"/>
       <c r="V96" s="3">
-        <f>LOOKUP(W96,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(W96,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="W96" s="1">
@@ -84773,7 +84785,7 @@
       <c r="Z96" s="3"/>
       <c r="AA96" s="3"/>
       <c r="AB96" s="3">
-        <f>LOOKUP(AC96,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(AC96,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="AC96" s="1">
@@ -84822,7 +84834,7 @@
       </c>
       <c r="N97" s="5"/>
       <c r="P97" s="1">
-        <f>LOOKUP(Q97,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(Q97,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="Q97" s="1">
@@ -84837,7 +84849,7 @@
       <c r="T97" s="3"/>
       <c r="U97" s="3"/>
       <c r="V97" s="3">
-        <f>LOOKUP(W97,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(W97,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="W97" s="1">
@@ -84852,7 +84864,7 @@
       <c r="Z97" s="3"/>
       <c r="AA97" s="3"/>
       <c r="AB97" s="3">
-        <f>LOOKUP(AC97,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(AC97,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="AC97" s="1">
@@ -84897,7 +84909,7 @@
       </c>
       <c r="N98" s="5"/>
       <c r="P98" s="1" t="e">
-        <f>LOOKUP(Q98,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(Q98,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>#N/A</v>
       </c>
       <c r="R98" s="1" t="s">
@@ -84909,7 +84921,7 @@
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
       <c r="V98" s="3">
-        <f>LOOKUP(W98,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(W98,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="W98" s="1">
@@ -84924,7 +84936,7 @@
       <c r="Z98" s="3"/>
       <c r="AA98" s="3"/>
       <c r="AB98" s="3">
-        <f>LOOKUP(AC98,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(AC98,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="AC98" s="1">
@@ -84973,7 +84985,7 @@
       </c>
       <c r="N99" s="5"/>
       <c r="P99" s="1">
-        <f>LOOKUP(Q99,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(Q99,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="Q99" s="1">
@@ -84988,7 +85000,7 @@
       <c r="T99" s="3"/>
       <c r="U99" s="3"/>
       <c r="V99" s="3">
-        <f>LOOKUP(W99,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(W99,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="W99" s="1">
@@ -85003,7 +85015,7 @@
       <c r="Z99" s="3"/>
       <c r="AA99" s="3"/>
       <c r="AB99" s="3">
-        <f>LOOKUP(AC99,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(AC99,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="AC99" s="1">
@@ -85031,7 +85043,7 @@
       </c>
       <c r="N100" s="5"/>
       <c r="P100" s="1">
-        <f>LOOKUP(Q100,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(Q100,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="Q100" s="1">
@@ -85046,7 +85058,7 @@
       <c r="T100" s="3"/>
       <c r="U100" s="3"/>
       <c r="V100" s="3">
-        <f>LOOKUP(W100,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(W100,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="W100" s="1">
@@ -85061,7 +85073,7 @@
       <c r="Z100" s="3"/>
       <c r="AA100" s="3"/>
       <c r="AB100" s="3">
-        <f>LOOKUP(AC100,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(AC100,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="AC100" s="1">
@@ -85107,7 +85119,7 @@
       <c r="Z101" s="3"/>
       <c r="AA101" s="3"/>
       <c r="AB101" s="3">
-        <f>LOOKUP(AC101,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(AC101,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="AC101" s="1">
@@ -85264,7 +85276,7 @@
         <v>1307</v>
       </c>
       <c r="AB105" s="3">
-        <f>LOOKUP(AC105,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(AC105,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="AC105" s="1">
@@ -85299,7 +85311,7 @@
       <c r="N106" s="5"/>
       <c r="R106" s="1"/>
       <c r="AB106" s="3">
-        <f>LOOKUP(AC106,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(AC106,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="AC106" s="1">
@@ -85333,7 +85345,7 @@
       </c>
       <c r="N107" s="5"/>
       <c r="AB107" s="3">
-        <f>LOOKUP(AC107,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(AC107,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="AC107" s="1">
@@ -85371,7 +85383,7 @@
       </c>
       <c r="N108" s="5"/>
       <c r="AB108" s="3">
-        <f>LOOKUP(AC108,[2]ItemProto!$C$856:$C$1333,[2]ItemProto!$S$856:$S$1333)</f>
+        <f>LOOKUP(AC108,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
         <v>0</v>
       </c>
       <c r="AC108" s="1">

--- a/WeiJingShuZhi/属性表.xlsx
+++ b/WeiJingShuZhi/属性表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\WeiJingShuZhi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108C2DBF-CD80-4915-A58C-45ADE69D5C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE389202-CCF9-4BC6-A749-311272C05C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/WeiJingShuZhi/属性表.xlsx
+++ b/WeiJingShuZhi/属性表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\WeiJingShuZhi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE389202-CCF9-4BC6-A749-311272C05C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AD7A73-FD0E-4B74-AA51-C19EE5C58C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -11536,353 +11536,350 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="857">
-          <cell r="C857">
-            <v>10103602</v>
-          </cell>
-          <cell r="S857" t="str">
-            <v>6@100803;50;150</v>
+        <row r="268">
+          <cell r="C268">
+            <v>10014022</v>
           </cell>
         </row>
         <row r="858">
           <cell r="C858">
-            <v>10103603</v>
+            <v>10103504</v>
           </cell>
           <cell r="S858" t="str">
-            <v>6@200303;0.01;0.03</v>
+            <v>7@204103;0.01;0.03</v>
           </cell>
         </row>
         <row r="859">
           <cell r="C859">
-            <v>10201101</v>
+            <v>10103601</v>
           </cell>
-          <cell r="S859">
-            <v>7102001</v>
+          <cell r="S859" t="str">
+            <v>6@100603;50;150</v>
           </cell>
         </row>
         <row r="860">
           <cell r="C860">
-            <v>10201102</v>
+            <v>10103602</v>
           </cell>
-          <cell r="S860">
-            <v>7102002</v>
+          <cell r="S860" t="str">
+            <v>6@100803;50;150</v>
           </cell>
         </row>
         <row r="861">
           <cell r="C861">
-            <v>10201103</v>
+            <v>10103603</v>
           </cell>
-          <cell r="S861">
-            <v>7102003</v>
+          <cell r="S861" t="str">
+            <v>6@200303;0.01;0.03</v>
           </cell>
         </row>
         <row r="862">
           <cell r="C862">
-            <v>10201104</v>
+            <v>10201101</v>
           </cell>
           <cell r="S862">
-            <v>7102004</v>
+            <v>7102001</v>
           </cell>
         </row>
         <row r="863">
           <cell r="C863">
-            <v>10201201</v>
+            <v>10201102</v>
           </cell>
           <cell r="S863">
-            <v>7103001</v>
+            <v>7102002</v>
           </cell>
         </row>
         <row r="864">
           <cell r="C864">
-            <v>10201202</v>
+            <v>10201103</v>
           </cell>
           <cell r="S864">
-            <v>7103002</v>
+            <v>7102003</v>
           </cell>
         </row>
         <row r="865">
           <cell r="C865">
-            <v>10201203</v>
+            <v>10201104</v>
           </cell>
           <cell r="S865">
-            <v>7103003</v>
+            <v>7102004</v>
           </cell>
         </row>
         <row r="866">
           <cell r="C866">
-            <v>10201204</v>
+            <v>10201201</v>
           </cell>
           <cell r="S866">
-            <v>7103004</v>
+            <v>7103001</v>
           </cell>
         </row>
         <row r="867">
           <cell r="C867">
-            <v>10202101</v>
+            <v>10201202</v>
           </cell>
           <cell r="S867">
-            <v>7202001</v>
+            <v>7103002</v>
           </cell>
         </row>
         <row r="868">
           <cell r="C868">
-            <v>10202102</v>
+            <v>10201203</v>
           </cell>
           <cell r="S868">
-            <v>7202002</v>
+            <v>7103003</v>
           </cell>
         </row>
         <row r="869">
           <cell r="C869">
-            <v>10202103</v>
+            <v>10201204</v>
           </cell>
           <cell r="S869">
-            <v>7202003</v>
+            <v>7103004</v>
           </cell>
         </row>
         <row r="870">
           <cell r="C870">
-            <v>10202104</v>
+            <v>10202101</v>
           </cell>
           <cell r="S870">
-            <v>7202004</v>
+            <v>7202001</v>
           </cell>
         </row>
         <row r="871">
           <cell r="C871">
-            <v>10202201</v>
+            <v>10202102</v>
           </cell>
           <cell r="S871">
-            <v>7203001</v>
+            <v>7202002</v>
           </cell>
         </row>
         <row r="872">
           <cell r="C872">
-            <v>10202202</v>
+            <v>10202103</v>
           </cell>
           <cell r="S872">
-            <v>7203002</v>
+            <v>7202003</v>
           </cell>
         </row>
         <row r="873">
           <cell r="C873">
-            <v>10202203</v>
+            <v>10202104</v>
           </cell>
           <cell r="S873">
-            <v>7203003</v>
+            <v>7202004</v>
           </cell>
         </row>
         <row r="874">
           <cell r="C874">
-            <v>10202204</v>
+            <v>10202201</v>
           </cell>
           <cell r="S874">
-            <v>7203004</v>
+            <v>7203001</v>
           </cell>
         </row>
         <row r="875">
           <cell r="C875">
-            <v>10203101</v>
+            <v>10202202</v>
           </cell>
           <cell r="S875">
-            <v>7302001</v>
+            <v>7203002</v>
           </cell>
         </row>
         <row r="876">
           <cell r="C876">
-            <v>10203102</v>
+            <v>10202203</v>
           </cell>
           <cell r="S876">
-            <v>7302002</v>
+            <v>7203003</v>
           </cell>
         </row>
         <row r="877">
           <cell r="C877">
-            <v>10203201</v>
+            <v>10202204</v>
           </cell>
           <cell r="S877">
-            <v>7303001</v>
+            <v>7203004</v>
           </cell>
         </row>
         <row r="878">
           <cell r="C878">
-            <v>10203202</v>
+            <v>10203101</v>
           </cell>
           <cell r="S878">
-            <v>7303002</v>
+            <v>7302001</v>
           </cell>
         </row>
         <row r="879">
           <cell r="C879">
-            <v>10301001</v>
+            <v>10203102</v>
           </cell>
           <cell r="S879">
-            <v>6101003</v>
+            <v>7302002</v>
           </cell>
         </row>
         <row r="880">
           <cell r="C880">
-            <v>10301002</v>
+            <v>10203201</v>
           </cell>
           <cell r="S880">
-            <v>6102003</v>
+            <v>7303001</v>
           </cell>
         </row>
         <row r="881">
           <cell r="C881">
-            <v>10301003</v>
+            <v>10203202</v>
           </cell>
           <cell r="S881">
-            <v>6103003</v>
+            <v>7303002</v>
           </cell>
         </row>
         <row r="882">
           <cell r="C882">
-            <v>10301004</v>
+            <v>10301001</v>
           </cell>
           <cell r="S882">
-            <v>6104004</v>
+            <v>6101003</v>
           </cell>
         </row>
         <row r="883">
           <cell r="C883">
-            <v>10301005</v>
+            <v>10301002</v>
           </cell>
           <cell r="S883">
-            <v>6105004</v>
+            <v>6102003</v>
           </cell>
         </row>
         <row r="884">
           <cell r="C884">
-            <v>10301006</v>
+            <v>10301003</v>
           </cell>
           <cell r="S884">
-            <v>6106003</v>
+            <v>6103003</v>
           </cell>
         </row>
         <row r="885">
           <cell r="C885">
-            <v>10302001</v>
+            <v>10301004</v>
           </cell>
           <cell r="S885">
-            <v>6201003</v>
+            <v>6104004</v>
           </cell>
         </row>
         <row r="886">
           <cell r="C886">
-            <v>10302002</v>
+            <v>10301005</v>
           </cell>
           <cell r="S886">
-            <v>6202003</v>
+            <v>6105004</v>
           </cell>
         </row>
         <row r="887">
           <cell r="C887">
-            <v>10302003</v>
+            <v>10301006</v>
           </cell>
           <cell r="S887">
-            <v>6203003</v>
+            <v>6106003</v>
           </cell>
         </row>
         <row r="888">
           <cell r="C888">
-            <v>10302004</v>
+            <v>10302001</v>
           </cell>
           <cell r="S888">
-            <v>6204004</v>
+            <v>6201003</v>
           </cell>
         </row>
         <row r="889">
           <cell r="C889">
-            <v>10302005</v>
+            <v>10302002</v>
           </cell>
           <cell r="S889">
-            <v>6205004</v>
+            <v>6202003</v>
           </cell>
         </row>
         <row r="890">
           <cell r="C890">
-            <v>10302006</v>
+            <v>10302003</v>
           </cell>
           <cell r="S890">
-            <v>6206003</v>
+            <v>6203003</v>
           </cell>
         </row>
         <row r="891">
           <cell r="C891">
-            <v>10303001</v>
+            <v>10302004</v>
           </cell>
           <cell r="S891">
-            <v>6301003</v>
+            <v>6204004</v>
           </cell>
         </row>
         <row r="892">
           <cell r="C892">
-            <v>10303002</v>
+            <v>10302005</v>
           </cell>
           <cell r="S892">
-            <v>6302003</v>
+            <v>6205004</v>
           </cell>
         </row>
         <row r="893">
           <cell r="C893">
-            <v>10303003</v>
+            <v>10302006</v>
           </cell>
           <cell r="S893">
-            <v>6303003</v>
+            <v>6206003</v>
           </cell>
         </row>
         <row r="894">
           <cell r="C894">
-            <v>10303004</v>
+            <v>10303001</v>
           </cell>
           <cell r="S894">
-            <v>6304004</v>
+            <v>6301003</v>
           </cell>
         </row>
         <row r="895">
           <cell r="C895">
-            <v>10303005</v>
+            <v>10303002</v>
           </cell>
           <cell r="S895">
-            <v>6305004</v>
+            <v>6302003</v>
           </cell>
         </row>
         <row r="896">
           <cell r="C896">
-            <v>10303006</v>
+            <v>10303003</v>
           </cell>
           <cell r="S896">
-            <v>6306003</v>
+            <v>6303003</v>
           </cell>
         </row>
         <row r="897">
           <cell r="C897">
-            <v>11200000</v>
+            <v>10303004</v>
           </cell>
           <cell r="S897">
-            <v>500</v>
+            <v>6304004</v>
           </cell>
         </row>
         <row r="898">
           <cell r="C898">
-            <v>11200001</v>
+            <v>10303005</v>
           </cell>
           <cell r="S898">
-            <v>500</v>
+            <v>6305004</v>
           </cell>
         </row>
         <row r="899">
           <cell r="C899">
-            <v>11200002</v>
+            <v>10303006</v>
           </cell>
           <cell r="S899">
-            <v>500</v>
+            <v>6306003</v>
           </cell>
         </row>
         <row r="900">
           <cell r="C900">
-            <v>11200003</v>
+            <v>11200000</v>
           </cell>
           <cell r="S900">
             <v>500</v>
@@ -11890,7 +11887,7 @@
         </row>
         <row r="901">
           <cell r="C901">
-            <v>11200010</v>
+            <v>11200001</v>
           </cell>
           <cell r="S901">
             <v>500</v>
@@ -11898,2476 +11895,2490 @@
         </row>
         <row r="902">
           <cell r="C902">
-            <v>11300001</v>
+            <v>11200002</v>
           </cell>
-          <cell r="S902" t="str">
-            <v>1;3901</v>
+          <cell r="S902">
+            <v>500</v>
           </cell>
         </row>
         <row r="903">
           <cell r="C903">
-            <v>11300002</v>
+            <v>11200003</v>
           </cell>
-          <cell r="S903" t="str">
-            <v>1;3906</v>
+          <cell r="S903">
+            <v>500</v>
           </cell>
         </row>
         <row r="904">
           <cell r="C904">
-            <v>11300003</v>
+            <v>11200010</v>
           </cell>
-          <cell r="S904" t="str">
-            <v>1;3907</v>
+          <cell r="S904">
+            <v>500</v>
           </cell>
         </row>
         <row r="905">
           <cell r="C905">
-            <v>11300004</v>
+            <v>11300001</v>
           </cell>
           <cell r="S905" t="str">
-            <v>1;3908</v>
+            <v>1;3901</v>
           </cell>
         </row>
         <row r="906">
           <cell r="C906">
-            <v>11300005</v>
+            <v>11300002</v>
           </cell>
           <cell r="S906" t="str">
-            <v>1;3909</v>
+            <v>1;3906</v>
           </cell>
         </row>
         <row r="907">
           <cell r="C907">
-            <v>11300006</v>
+            <v>11300003</v>
           </cell>
           <cell r="S907" t="str">
-            <v>1;3910</v>
+            <v>1;3907</v>
           </cell>
         </row>
         <row r="908">
           <cell r="C908">
-            <v>11300007</v>
+            <v>11300004</v>
           </cell>
           <cell r="S908" t="str">
-            <v>2;3902</v>
+            <v>1;3908</v>
           </cell>
         </row>
         <row r="909">
           <cell r="C909">
-            <v>11300008</v>
+            <v>11300005</v>
           </cell>
           <cell r="S909" t="str">
-            <v>2;3903</v>
+            <v>1;3909</v>
           </cell>
         </row>
         <row r="910">
           <cell r="C910">
-            <v>11300009</v>
+            <v>11300006</v>
           </cell>
           <cell r="S910" t="str">
-            <v>2;3904</v>
+            <v>1;3910</v>
           </cell>
         </row>
         <row r="911">
           <cell r="C911">
-            <v>11300101</v>
+            <v>11300007</v>
           </cell>
           <cell r="S911" t="str">
-            <v>1;3101</v>
+            <v>2;3902</v>
           </cell>
         </row>
         <row r="912">
           <cell r="C912">
-            <v>11300102</v>
+            <v>11300008</v>
           </cell>
           <cell r="S912" t="str">
-            <v>1;3102</v>
+            <v>2;3903</v>
           </cell>
         </row>
         <row r="913">
           <cell r="C913">
-            <v>11300103</v>
+            <v>11300009</v>
           </cell>
           <cell r="S913" t="str">
-            <v>1;3103</v>
+            <v>2;3904</v>
           </cell>
         </row>
         <row r="914">
           <cell r="C914">
-            <v>11300104</v>
+            <v>11300101</v>
           </cell>
           <cell r="S914" t="str">
-            <v>1;3104</v>
+            <v>1;3101</v>
           </cell>
         </row>
         <row r="915">
           <cell r="C915">
-            <v>11300105</v>
+            <v>11300102</v>
           </cell>
           <cell r="S915" t="str">
-            <v>1;3105</v>
+            <v>1;3102</v>
           </cell>
         </row>
         <row r="916">
           <cell r="C916">
-            <v>11300201</v>
+            <v>11300103</v>
           </cell>
           <cell r="S916" t="str">
-            <v>1;3201</v>
+            <v>1;3103</v>
           </cell>
         </row>
         <row r="917">
           <cell r="C917">
-            <v>11300202</v>
+            <v>11300104</v>
           </cell>
           <cell r="S917" t="str">
-            <v>1;3202</v>
+            <v>1;3104</v>
           </cell>
         </row>
         <row r="918">
           <cell r="C918">
-            <v>11300203</v>
+            <v>11300105</v>
           </cell>
           <cell r="S918" t="str">
-            <v>1;3203</v>
+            <v>1;3105</v>
           </cell>
         </row>
         <row r="919">
           <cell r="C919">
-            <v>11300204</v>
+            <v>11300201</v>
           </cell>
           <cell r="S919" t="str">
-            <v>1;3204</v>
+            <v>1;3201</v>
           </cell>
         </row>
         <row r="920">
           <cell r="C920">
-            <v>11300205</v>
+            <v>11300202</v>
           </cell>
           <cell r="S920" t="str">
-            <v>1;3205</v>
+            <v>1;3202</v>
           </cell>
         </row>
         <row r="921">
           <cell r="C921">
-            <v>11300301</v>
+            <v>11300203</v>
           </cell>
           <cell r="S921" t="str">
-            <v>1;3301</v>
+            <v>1;3203</v>
           </cell>
         </row>
         <row r="922">
           <cell r="C922">
-            <v>11300302</v>
+            <v>11300204</v>
           </cell>
           <cell r="S922" t="str">
-            <v>1;3302</v>
+            <v>1;3204</v>
           </cell>
         </row>
         <row r="923">
           <cell r="C923">
-            <v>11300303</v>
+            <v>11300205</v>
           </cell>
           <cell r="S923" t="str">
-            <v>1;3303</v>
+            <v>1;3205</v>
           </cell>
         </row>
         <row r="924">
           <cell r="C924">
-            <v>11300304</v>
+            <v>11300301</v>
           </cell>
           <cell r="S924" t="str">
-            <v>1;3304</v>
+            <v>1;3301</v>
           </cell>
         </row>
         <row r="925">
           <cell r="C925">
-            <v>11300305</v>
+            <v>11300302</v>
           </cell>
           <cell r="S925" t="str">
-            <v>1;3305</v>
+            <v>1;3302</v>
           </cell>
         </row>
         <row r="926">
           <cell r="C926">
-            <v>11300401</v>
+            <v>11300303</v>
           </cell>
           <cell r="S926" t="str">
-            <v>1;3401</v>
+            <v>1;3303</v>
           </cell>
         </row>
         <row r="927">
           <cell r="C927">
-            <v>11300402</v>
+            <v>11300304</v>
           </cell>
           <cell r="S927" t="str">
-            <v>1;3402</v>
+            <v>1;3304</v>
           </cell>
         </row>
         <row r="928">
           <cell r="C928">
-            <v>11300403</v>
+            <v>11300305</v>
           </cell>
           <cell r="S928" t="str">
-            <v>1;3403</v>
+            <v>1;3305</v>
           </cell>
         </row>
         <row r="929">
           <cell r="C929">
-            <v>11300404</v>
+            <v>11300401</v>
           </cell>
           <cell r="S929" t="str">
-            <v>1;3404</v>
+            <v>1;3401</v>
           </cell>
         </row>
         <row r="930">
           <cell r="C930">
-            <v>11300405</v>
+            <v>11300402</v>
           </cell>
           <cell r="S930" t="str">
-            <v>1;3405</v>
+            <v>1;3402</v>
           </cell>
         </row>
         <row r="931">
           <cell r="C931">
-            <v>11300501</v>
+            <v>11300403</v>
           </cell>
           <cell r="S931" t="str">
-            <v>1;3501</v>
+            <v>1;3403</v>
           </cell>
         </row>
         <row r="932">
           <cell r="C932">
-            <v>11300502</v>
+            <v>11300404</v>
           </cell>
           <cell r="S932" t="str">
-            <v>1;3502</v>
+            <v>1;3404</v>
           </cell>
         </row>
         <row r="933">
           <cell r="C933">
-            <v>11300503</v>
+            <v>11300405</v>
           </cell>
           <cell r="S933" t="str">
-            <v>1;3503</v>
+            <v>1;3405</v>
           </cell>
         </row>
         <row r="934">
           <cell r="C934">
-            <v>11300504</v>
+            <v>11300501</v>
           </cell>
           <cell r="S934" t="str">
-            <v>1;3504</v>
+            <v>1;3501</v>
           </cell>
         </row>
         <row r="935">
           <cell r="C935">
-            <v>11300505</v>
+            <v>11300502</v>
           </cell>
           <cell r="S935" t="str">
-            <v>1;3505</v>
+            <v>1;3502</v>
           </cell>
         </row>
         <row r="936">
           <cell r="C936">
-            <v>11300601</v>
+            <v>11300503</v>
           </cell>
           <cell r="S936" t="str">
-            <v>1;3601</v>
+            <v>1;3503</v>
           </cell>
         </row>
         <row r="937">
           <cell r="C937">
-            <v>11300602</v>
+            <v>11300504</v>
           </cell>
           <cell r="S937" t="str">
-            <v>1;3602</v>
+            <v>1;3504</v>
           </cell>
         </row>
         <row r="938">
           <cell r="C938">
-            <v>11300603</v>
+            <v>11300505</v>
           </cell>
           <cell r="S938" t="str">
-            <v>1;3603</v>
+            <v>1;3505</v>
           </cell>
         </row>
         <row r="939">
           <cell r="C939">
-            <v>11300604</v>
+            <v>11300601</v>
           </cell>
           <cell r="S939" t="str">
-            <v>1;3604</v>
+            <v>1;3601</v>
           </cell>
         </row>
         <row r="940">
           <cell r="C940">
-            <v>11300605</v>
+            <v>11300602</v>
           </cell>
           <cell r="S940" t="str">
-            <v>1;3605</v>
+            <v>1;3602</v>
           </cell>
         </row>
         <row r="941">
           <cell r="C941">
-            <v>11400101</v>
+            <v>11300603</v>
           </cell>
           <cell r="S941" t="str">
-            <v>1,30@1;202103,0.01,0.03</v>
+            <v>1;3603</v>
           </cell>
         </row>
         <row r="942">
           <cell r="C942">
-            <v>11400102</v>
+            <v>11300604</v>
           </cell>
           <cell r="S942" t="str">
-            <v>1,30@1;100203,100,200</v>
+            <v>1;3604</v>
           </cell>
         </row>
         <row r="943">
           <cell r="C943">
-            <v>11400103</v>
+            <v>11300605</v>
           </cell>
           <cell r="S943" t="str">
-            <v>1,30@2;62000001</v>
+            <v>1;3605</v>
           </cell>
         </row>
         <row r="944">
           <cell r="C944">
-            <v>11500101</v>
+            <v>11400101</v>
+          </cell>
+          <cell r="S944" t="str">
+            <v>1,30@1;202103,0.01,0.03</v>
           </cell>
         </row>
         <row r="945">
           <cell r="C945">
-            <v>11500102</v>
+            <v>11400102</v>
+          </cell>
+          <cell r="S945" t="str">
+            <v>1,30@1;100203,100,200</v>
           </cell>
         </row>
         <row r="946">
           <cell r="C946">
-            <v>11500103</v>
+            <v>11400103</v>
+          </cell>
+          <cell r="S946" t="str">
+            <v>1,30@2;62000001</v>
           </cell>
         </row>
         <row r="947">
           <cell r="C947">
-            <v>11500201</v>
+            <v>11500101</v>
           </cell>
         </row>
         <row r="948">
           <cell r="C948">
-            <v>11500202</v>
+            <v>11500102</v>
           </cell>
         </row>
         <row r="949">
           <cell r="C949">
-            <v>11500203</v>
+            <v>11500103</v>
           </cell>
         </row>
         <row r="950">
           <cell r="C950">
-            <v>11500301</v>
+            <v>11500201</v>
           </cell>
         </row>
         <row r="951">
           <cell r="C951">
-            <v>11500302</v>
+            <v>11500202</v>
           </cell>
         </row>
         <row r="952">
           <cell r="C952">
-            <v>11500303</v>
+            <v>11500203</v>
           </cell>
         </row>
         <row r="953">
           <cell r="C953">
-            <v>11500401</v>
+            <v>11500301</v>
           </cell>
         </row>
         <row r="954">
           <cell r="C954">
-            <v>11500402</v>
+            <v>11500302</v>
           </cell>
         </row>
         <row r="955">
           <cell r="C955">
-            <v>11500403</v>
+            <v>11500303</v>
           </cell>
         </row>
         <row r="956">
           <cell r="C956">
-            <v>11500501</v>
+            <v>11500401</v>
           </cell>
         </row>
         <row r="957">
           <cell r="C957">
-            <v>11500502</v>
+            <v>11500402</v>
           </cell>
         </row>
         <row r="958">
           <cell r="C958">
-            <v>11500503</v>
+            <v>11500403</v>
           </cell>
         </row>
         <row r="959">
           <cell r="C959">
-            <v>11600101</v>
+            <v>11500501</v>
           </cell>
         </row>
         <row r="960">
           <cell r="C960">
-            <v>11600102</v>
+            <v>11500502</v>
           </cell>
         </row>
         <row r="961">
           <cell r="C961">
-            <v>11600103</v>
+            <v>11500503</v>
           </cell>
         </row>
         <row r="962">
           <cell r="C962">
-            <v>11600201</v>
+            <v>11600101</v>
           </cell>
         </row>
         <row r="963">
           <cell r="C963">
-            <v>11600202</v>
+            <v>11600102</v>
           </cell>
         </row>
         <row r="964">
           <cell r="C964">
-            <v>11600203</v>
+            <v>11600103</v>
           </cell>
         </row>
         <row r="965">
           <cell r="C965">
-            <v>11600301</v>
+            <v>11600201</v>
           </cell>
         </row>
         <row r="966">
           <cell r="C966">
-            <v>11600302</v>
+            <v>11600202</v>
           </cell>
         </row>
         <row r="967">
           <cell r="C967">
-            <v>11600303</v>
+            <v>11600203</v>
           </cell>
         </row>
         <row r="968">
           <cell r="C968">
-            <v>11600401</v>
+            <v>11600301</v>
           </cell>
         </row>
         <row r="969">
           <cell r="C969">
-            <v>11600402</v>
+            <v>11600302</v>
           </cell>
         </row>
         <row r="970">
           <cell r="C970">
-            <v>11600403</v>
+            <v>11600303</v>
           </cell>
         </row>
         <row r="971">
           <cell r="C971">
-            <v>11600501</v>
+            <v>11600401</v>
           </cell>
         </row>
         <row r="972">
           <cell r="C972">
-            <v>11600502</v>
+            <v>11600402</v>
           </cell>
         </row>
         <row r="973">
           <cell r="C973">
-            <v>11600503</v>
+            <v>11600403</v>
           </cell>
         </row>
         <row r="974">
           <cell r="C974">
-            <v>11600601</v>
+            <v>11600501</v>
           </cell>
         </row>
         <row r="975">
           <cell r="C975">
-            <v>11600602</v>
+            <v>11600502</v>
           </cell>
         </row>
         <row r="976">
           <cell r="C976">
-            <v>11600603</v>
+            <v>11600503</v>
           </cell>
         </row>
         <row r="977">
           <cell r="C977">
-            <v>11600701</v>
+            <v>11600601</v>
           </cell>
         </row>
         <row r="978">
           <cell r="C978">
-            <v>11600702</v>
+            <v>11600602</v>
           </cell>
         </row>
         <row r="979">
           <cell r="C979">
-            <v>11600703</v>
+            <v>11600603</v>
           </cell>
         </row>
         <row r="980">
           <cell r="C980">
-            <v>11600801</v>
+            <v>11600701</v>
           </cell>
         </row>
         <row r="981">
           <cell r="C981">
-            <v>11600802</v>
+            <v>11600702</v>
           </cell>
         </row>
         <row r="982">
           <cell r="C982">
-            <v>11600803</v>
+            <v>11600703</v>
           </cell>
         </row>
         <row r="983">
           <cell r="C983">
-            <v>11600901</v>
+            <v>11600801</v>
           </cell>
         </row>
         <row r="984">
           <cell r="C984">
-            <v>11600902</v>
+            <v>11600802</v>
           </cell>
         </row>
         <row r="985">
           <cell r="C985">
-            <v>11600903</v>
+            <v>11600803</v>
           </cell>
         </row>
         <row r="986">
           <cell r="C986">
-            <v>11610101</v>
+            <v>11600901</v>
           </cell>
         </row>
         <row r="987">
           <cell r="C987">
-            <v>11610102</v>
+            <v>11600902</v>
           </cell>
         </row>
         <row r="988">
           <cell r="C988">
-            <v>11610103</v>
+            <v>11600903</v>
           </cell>
         </row>
         <row r="989">
           <cell r="C989">
-            <v>11610201</v>
+            <v>11610101</v>
           </cell>
         </row>
         <row r="990">
           <cell r="C990">
-            <v>11610202</v>
+            <v>11610102</v>
           </cell>
         </row>
         <row r="991">
           <cell r="C991">
-            <v>11610203</v>
+            <v>11610103</v>
           </cell>
         </row>
         <row r="992">
           <cell r="C992">
-            <v>11610301</v>
+            <v>11610201</v>
           </cell>
         </row>
         <row r="993">
           <cell r="C993">
-            <v>11610302</v>
+            <v>11610202</v>
           </cell>
         </row>
         <row r="994">
           <cell r="C994">
-            <v>11610303</v>
+            <v>11610203</v>
           </cell>
         </row>
         <row r="995">
           <cell r="C995">
-            <v>11610401</v>
+            <v>11610301</v>
           </cell>
         </row>
         <row r="996">
           <cell r="C996">
-            <v>11610402</v>
+            <v>11610302</v>
           </cell>
         </row>
         <row r="997">
           <cell r="C997">
-            <v>11610403</v>
+            <v>11610303</v>
           </cell>
         </row>
         <row r="998">
           <cell r="C998">
-            <v>11610501</v>
+            <v>11610401</v>
           </cell>
         </row>
         <row r="999">
           <cell r="C999">
-            <v>11610502</v>
+            <v>11610402</v>
           </cell>
         </row>
         <row r="1000">
           <cell r="C1000">
-            <v>11610503</v>
+            <v>11610403</v>
           </cell>
         </row>
         <row r="1001">
           <cell r="C1001">
-            <v>11610601</v>
+            <v>11610501</v>
           </cell>
         </row>
         <row r="1002">
           <cell r="C1002">
-            <v>11610602</v>
+            <v>11610502</v>
           </cell>
         </row>
         <row r="1003">
           <cell r="C1003">
-            <v>11610603</v>
+            <v>11610503</v>
           </cell>
         </row>
         <row r="1004">
           <cell r="C1004">
-            <v>11610701</v>
+            <v>11610601</v>
           </cell>
         </row>
         <row r="1005">
           <cell r="C1005">
-            <v>11610702</v>
+            <v>11610602</v>
           </cell>
         </row>
         <row r="1006">
           <cell r="C1006">
-            <v>11610703</v>
+            <v>11610603</v>
           </cell>
         </row>
         <row r="1007">
           <cell r="C1007">
-            <v>13001001</v>
-          </cell>
-          <cell r="S1007">
-            <v>65001001</v>
+            <v>11610701</v>
           </cell>
         </row>
         <row r="1008">
           <cell r="C1008">
-            <v>13001002</v>
-          </cell>
-          <cell r="S1008">
-            <v>65001002</v>
+            <v>11610702</v>
           </cell>
         </row>
         <row r="1009">
           <cell r="C1009">
-            <v>13001003</v>
-          </cell>
-          <cell r="S1009">
-            <v>65001003</v>
+            <v>11610703</v>
           </cell>
         </row>
         <row r="1010">
           <cell r="C1010">
-            <v>13001004</v>
+            <v>13001001</v>
           </cell>
           <cell r="S1010">
-            <v>65001004</v>
+            <v>65001001</v>
           </cell>
         </row>
         <row r="1011">
           <cell r="C1011">
-            <v>13001005</v>
+            <v>13001002</v>
           </cell>
           <cell r="S1011">
-            <v>65001005</v>
+            <v>65001002</v>
           </cell>
         </row>
         <row r="1012">
           <cell r="C1012">
-            <v>13001006</v>
+            <v>13001003</v>
           </cell>
           <cell r="S1012">
-            <v>65001006</v>
+            <v>65001003</v>
           </cell>
         </row>
         <row r="1013">
           <cell r="C1013">
-            <v>13001101</v>
+            <v>13001004</v>
           </cell>
           <cell r="S1013">
-            <v>65001101</v>
+            <v>65001004</v>
           </cell>
         </row>
         <row r="1014">
           <cell r="C1014">
-            <v>13001102</v>
+            <v>13001005</v>
           </cell>
           <cell r="S1014">
-            <v>65001102</v>
+            <v>65001005</v>
           </cell>
         </row>
         <row r="1015">
           <cell r="C1015">
-            <v>13001103</v>
+            <v>13001006</v>
           </cell>
           <cell r="S1015">
-            <v>65001103</v>
+            <v>65001006</v>
           </cell>
         </row>
         <row r="1016">
           <cell r="C1016">
-            <v>13001104</v>
+            <v>13001101</v>
           </cell>
           <cell r="S1016">
-            <v>65001104</v>
+            <v>65001101</v>
           </cell>
         </row>
         <row r="1017">
           <cell r="C1017">
-            <v>13001105</v>
+            <v>13001102</v>
           </cell>
           <cell r="S1017">
-            <v>65001105</v>
+            <v>65001102</v>
           </cell>
         </row>
         <row r="1018">
           <cell r="C1018">
-            <v>13002001</v>
+            <v>13001103</v>
           </cell>
           <cell r="S1018">
-            <v>65002001</v>
+            <v>65001103</v>
           </cell>
         </row>
         <row r="1019">
           <cell r="C1019">
-            <v>13002002</v>
+            <v>13001104</v>
           </cell>
           <cell r="S1019">
-            <v>65002002</v>
+            <v>65001104</v>
           </cell>
         </row>
         <row r="1020">
           <cell r="C1020">
-            <v>13002003</v>
+            <v>13001105</v>
           </cell>
           <cell r="S1020">
-            <v>65002003</v>
+            <v>65001105</v>
           </cell>
         </row>
         <row r="1021">
           <cell r="C1021">
-            <v>13002004</v>
+            <v>13002001</v>
           </cell>
           <cell r="S1021">
-            <v>65002004</v>
+            <v>65002001</v>
           </cell>
         </row>
         <row r="1022">
           <cell r="C1022">
-            <v>13002005</v>
+            <v>13002002</v>
           </cell>
           <cell r="S1022">
-            <v>65002005</v>
+            <v>65002002</v>
           </cell>
         </row>
         <row r="1023">
           <cell r="C1023">
-            <v>13002006</v>
+            <v>13002003</v>
           </cell>
           <cell r="S1023">
-            <v>65002006</v>
+            <v>65002003</v>
           </cell>
         </row>
         <row r="1024">
           <cell r="C1024">
-            <v>13002101</v>
+            <v>13002004</v>
           </cell>
           <cell r="S1024">
-            <v>65002101</v>
+            <v>65002004</v>
           </cell>
         </row>
         <row r="1025">
           <cell r="C1025">
-            <v>13002102</v>
+            <v>13002005</v>
           </cell>
           <cell r="S1025">
-            <v>65002102</v>
+            <v>65002005</v>
           </cell>
         </row>
         <row r="1026">
           <cell r="C1026">
-            <v>13002103</v>
+            <v>13002006</v>
           </cell>
           <cell r="S1026">
-            <v>65002103</v>
+            <v>65002006</v>
           </cell>
         </row>
         <row r="1027">
           <cell r="C1027">
-            <v>13002104</v>
+            <v>13002101</v>
           </cell>
           <cell r="S1027">
-            <v>65002104</v>
+            <v>65002101</v>
           </cell>
         </row>
         <row r="1028">
           <cell r="C1028">
-            <v>13002105</v>
+            <v>13002102</v>
           </cell>
           <cell r="S1028">
-            <v>65002105</v>
+            <v>65002102</v>
           </cell>
         </row>
         <row r="1029">
           <cell r="C1029">
-            <v>13003001</v>
+            <v>13002103</v>
           </cell>
           <cell r="S1029">
-            <v>65003001</v>
+            <v>65002103</v>
           </cell>
         </row>
         <row r="1030">
           <cell r="C1030">
-            <v>13003002</v>
+            <v>13002104</v>
           </cell>
           <cell r="S1030">
-            <v>65003002</v>
+            <v>65002104</v>
           </cell>
         </row>
         <row r="1031">
           <cell r="C1031">
-            <v>13003003</v>
+            <v>13002105</v>
           </cell>
           <cell r="S1031">
-            <v>65003003</v>
+            <v>65002105</v>
           </cell>
         </row>
         <row r="1032">
           <cell r="C1032">
-            <v>13003004</v>
+            <v>13003001</v>
           </cell>
           <cell r="S1032">
-            <v>65003004</v>
+            <v>65003001</v>
           </cell>
         </row>
         <row r="1033">
           <cell r="C1033">
-            <v>13003005</v>
+            <v>13003002</v>
           </cell>
           <cell r="S1033">
-            <v>65003005</v>
+            <v>65003002</v>
           </cell>
         </row>
         <row r="1034">
           <cell r="C1034">
-            <v>13003006</v>
+            <v>13003003</v>
           </cell>
           <cell r="S1034">
-            <v>65003006</v>
+            <v>65003003</v>
           </cell>
         </row>
         <row r="1035">
           <cell r="C1035">
-            <v>13003101</v>
+            <v>13003004</v>
           </cell>
           <cell r="S1035">
-            <v>65003101</v>
+            <v>65003004</v>
           </cell>
         </row>
         <row r="1036">
           <cell r="C1036">
-            <v>13003102</v>
+            <v>13003005</v>
           </cell>
           <cell r="S1036">
-            <v>65003102</v>
+            <v>65003005</v>
           </cell>
         </row>
         <row r="1037">
           <cell r="C1037">
-            <v>13003103</v>
+            <v>13003006</v>
           </cell>
           <cell r="S1037">
-            <v>65003103</v>
+            <v>65003006</v>
           </cell>
         </row>
         <row r="1038">
           <cell r="C1038">
-            <v>13003104</v>
+            <v>13003101</v>
           </cell>
           <cell r="S1038">
-            <v>65003104</v>
+            <v>65003101</v>
           </cell>
         </row>
         <row r="1039">
           <cell r="C1039">
-            <v>13003105</v>
+            <v>13003102</v>
           </cell>
           <cell r="S1039">
-            <v>65003105</v>
+            <v>65003102</v>
           </cell>
         </row>
         <row r="1040">
           <cell r="C1040">
-            <v>13004001</v>
+            <v>13003103</v>
           </cell>
           <cell r="S1040">
-            <v>65004001</v>
+            <v>65003103</v>
           </cell>
         </row>
         <row r="1041">
           <cell r="C1041">
-            <v>13004002</v>
+            <v>13003104</v>
           </cell>
           <cell r="S1041">
-            <v>65004002</v>
+            <v>65003104</v>
           </cell>
         </row>
         <row r="1042">
           <cell r="C1042">
-            <v>13004003</v>
+            <v>13003105</v>
           </cell>
           <cell r="S1042">
-            <v>65004003</v>
+            <v>65003105</v>
           </cell>
         </row>
         <row r="1043">
           <cell r="C1043">
-            <v>13004004</v>
+            <v>13004001</v>
           </cell>
           <cell r="S1043">
-            <v>65004004</v>
+            <v>65004001</v>
           </cell>
         </row>
         <row r="1044">
           <cell r="C1044">
-            <v>13004005</v>
+            <v>13004002</v>
           </cell>
           <cell r="S1044">
-            <v>65004005</v>
+            <v>65004002</v>
           </cell>
         </row>
         <row r="1045">
           <cell r="C1045">
-            <v>13004006</v>
+            <v>13004003</v>
           </cell>
           <cell r="S1045">
-            <v>65004006</v>
+            <v>65004003</v>
           </cell>
         </row>
         <row r="1046">
           <cell r="C1046">
-            <v>13004101</v>
+            <v>13004004</v>
           </cell>
           <cell r="S1046">
-            <v>65004101</v>
+            <v>65004004</v>
           </cell>
         </row>
         <row r="1047">
           <cell r="C1047">
-            <v>13004102</v>
+            <v>13004005</v>
           </cell>
           <cell r="S1047">
-            <v>65004102</v>
+            <v>65004005</v>
           </cell>
         </row>
         <row r="1048">
           <cell r="C1048">
-            <v>13004103</v>
+            <v>13004006</v>
           </cell>
           <cell r="S1048">
-            <v>65004103</v>
+            <v>65004006</v>
           </cell>
         </row>
         <row r="1049">
           <cell r="C1049">
-            <v>13004104</v>
+            <v>13004101</v>
           </cell>
           <cell r="S1049">
-            <v>65004104</v>
+            <v>65004101</v>
           </cell>
         </row>
         <row r="1050">
           <cell r="C1050">
-            <v>13004105</v>
+            <v>13004102</v>
           </cell>
           <cell r="S1050">
-            <v>65004105</v>
+            <v>65004102</v>
           </cell>
         </row>
         <row r="1051">
           <cell r="C1051">
-            <v>13005001</v>
+            <v>13004103</v>
           </cell>
           <cell r="S1051">
-            <v>65005001</v>
+            <v>65004103</v>
           </cell>
         </row>
         <row r="1052">
           <cell r="C1052">
-            <v>13005002</v>
+            <v>13004104</v>
           </cell>
           <cell r="S1052">
-            <v>65005002</v>
+            <v>65004104</v>
           </cell>
         </row>
         <row r="1053">
           <cell r="C1053">
-            <v>13005003</v>
+            <v>13004105</v>
           </cell>
           <cell r="S1053">
-            <v>65005003</v>
+            <v>65004105</v>
           </cell>
         </row>
         <row r="1054">
           <cell r="C1054">
-            <v>13005004</v>
+            <v>13005001</v>
           </cell>
           <cell r="S1054">
-            <v>65005004</v>
+            <v>65005001</v>
           </cell>
         </row>
         <row r="1055">
           <cell r="C1055">
-            <v>13005005</v>
+            <v>13005002</v>
           </cell>
           <cell r="S1055">
-            <v>65005005</v>
+            <v>65005002</v>
           </cell>
         </row>
         <row r="1056">
           <cell r="C1056">
-            <v>13005006</v>
+            <v>13005003</v>
           </cell>
           <cell r="S1056">
-            <v>65005006</v>
+            <v>65005003</v>
           </cell>
         </row>
         <row r="1057">
           <cell r="C1057">
-            <v>13005101</v>
+            <v>13005004</v>
           </cell>
           <cell r="S1057">
-            <v>65005101</v>
+            <v>65005004</v>
           </cell>
         </row>
         <row r="1058">
           <cell r="C1058">
-            <v>13005102</v>
+            <v>13005005</v>
           </cell>
           <cell r="S1058">
-            <v>65005102</v>
+            <v>65005005</v>
           </cell>
         </row>
         <row r="1059">
           <cell r="C1059">
-            <v>13005103</v>
+            <v>13005006</v>
           </cell>
           <cell r="S1059">
-            <v>65005103</v>
+            <v>65005006</v>
           </cell>
         </row>
         <row r="1060">
           <cell r="C1060">
-            <v>13005104</v>
+            <v>13005101</v>
           </cell>
           <cell r="S1060">
-            <v>65005104</v>
+            <v>65005101</v>
           </cell>
         </row>
         <row r="1061">
           <cell r="C1061">
-            <v>13005105</v>
+            <v>13005102</v>
           </cell>
           <cell r="S1061">
-            <v>65005105</v>
+            <v>65005102</v>
           </cell>
         </row>
         <row r="1062">
           <cell r="C1062">
-            <v>13006001</v>
+            <v>13005103</v>
           </cell>
           <cell r="S1062">
-            <v>65006001</v>
+            <v>65005103</v>
           </cell>
         </row>
         <row r="1063">
           <cell r="C1063">
-            <v>13006002</v>
+            <v>13005104</v>
           </cell>
           <cell r="S1063">
-            <v>65006002</v>
+            <v>65005104</v>
           </cell>
         </row>
         <row r="1064">
           <cell r="C1064">
-            <v>13006003</v>
+            <v>13005105</v>
           </cell>
           <cell r="S1064">
-            <v>65006003</v>
+            <v>65005105</v>
           </cell>
         </row>
         <row r="1065">
           <cell r="C1065">
-            <v>13006004</v>
+            <v>13006001</v>
           </cell>
           <cell r="S1065">
-            <v>65006004</v>
+            <v>65006001</v>
           </cell>
         </row>
         <row r="1066">
           <cell r="C1066">
-            <v>13009001</v>
+            <v>13006002</v>
           </cell>
-          <cell r="S1066" t="str">
-            <v>4;20</v>
+          <cell r="S1066">
+            <v>65006002</v>
           </cell>
         </row>
         <row r="1067">
           <cell r="C1067">
-            <v>13009002</v>
+            <v>13006003</v>
           </cell>
-          <cell r="S1067" t="str">
-            <v>5;20</v>
+          <cell r="S1067">
+            <v>65006003</v>
           </cell>
         </row>
         <row r="1068">
           <cell r="C1068">
-            <v>14000001</v>
+            <v>13006004</v>
+          </cell>
+          <cell r="S1068">
+            <v>65006004</v>
           </cell>
         </row>
         <row r="1069">
           <cell r="C1069">
-            <v>14000002</v>
+            <v>13009001</v>
+          </cell>
+          <cell r="S1069" t="str">
+            <v>4;20</v>
           </cell>
         </row>
         <row r="1070">
           <cell r="C1070">
-            <v>14000003</v>
+            <v>13009002</v>
+          </cell>
+          <cell r="S1070" t="str">
+            <v>5;20</v>
           </cell>
         </row>
         <row r="1071">
           <cell r="C1071">
-            <v>14000004</v>
+            <v>14000001</v>
           </cell>
         </row>
         <row r="1072">
           <cell r="C1072">
-            <v>14000005</v>
+            <v>14000002</v>
           </cell>
         </row>
         <row r="1073">
           <cell r="C1073">
-            <v>14010001</v>
+            <v>14000003</v>
           </cell>
         </row>
         <row r="1074">
           <cell r="C1074">
-            <v>14010002</v>
+            <v>14000004</v>
           </cell>
         </row>
         <row r="1075">
           <cell r="C1075">
-            <v>14010003</v>
+            <v>14000005</v>
           </cell>
         </row>
         <row r="1076">
           <cell r="C1076">
-            <v>14010004</v>
+            <v>14010001</v>
           </cell>
         </row>
         <row r="1077">
           <cell r="C1077">
-            <v>14010005</v>
+            <v>14010002</v>
           </cell>
         </row>
         <row r="1078">
           <cell r="C1078">
-            <v>14010006</v>
+            <v>14010003</v>
           </cell>
         </row>
         <row r="1079">
           <cell r="C1079">
-            <v>14010007</v>
+            <v>14010004</v>
           </cell>
         </row>
         <row r="1080">
           <cell r="C1080">
-            <v>14010008</v>
+            <v>14010005</v>
           </cell>
         </row>
         <row r="1081">
           <cell r="C1081">
-            <v>14010009</v>
+            <v>14010006</v>
           </cell>
         </row>
         <row r="1082">
           <cell r="C1082">
-            <v>14010010</v>
+            <v>14010007</v>
           </cell>
         </row>
         <row r="1083">
           <cell r="C1083">
-            <v>14010011</v>
+            <v>14010008</v>
           </cell>
         </row>
         <row r="1084">
           <cell r="C1084">
-            <v>14010012</v>
+            <v>14010009</v>
           </cell>
         </row>
         <row r="1085">
           <cell r="C1085">
-            <v>14020001</v>
+            <v>14010010</v>
           </cell>
         </row>
         <row r="1086">
           <cell r="C1086">
-            <v>14020002</v>
+            <v>14010011</v>
           </cell>
         </row>
         <row r="1087">
           <cell r="C1087">
-            <v>14020003</v>
+            <v>14010012</v>
           </cell>
         </row>
         <row r="1088">
           <cell r="C1088">
-            <v>14020004</v>
+            <v>14020001</v>
           </cell>
         </row>
         <row r="1089">
           <cell r="C1089">
-            <v>14020005</v>
+            <v>14020002</v>
           </cell>
         </row>
         <row r="1090">
           <cell r="C1090">
-            <v>14020006</v>
+            <v>14020003</v>
           </cell>
         </row>
         <row r="1091">
           <cell r="C1091">
-            <v>14020007</v>
+            <v>14020004</v>
           </cell>
         </row>
         <row r="1092">
           <cell r="C1092">
-            <v>14020008</v>
+            <v>14020005</v>
           </cell>
         </row>
         <row r="1093">
           <cell r="C1093">
-            <v>14020009</v>
+            <v>14020006</v>
           </cell>
         </row>
         <row r="1094">
           <cell r="C1094">
-            <v>14020010</v>
+            <v>14020007</v>
           </cell>
         </row>
         <row r="1095">
           <cell r="C1095">
-            <v>14020011</v>
+            <v>14020008</v>
           </cell>
         </row>
         <row r="1096">
           <cell r="C1096">
-            <v>14020012</v>
+            <v>14020009</v>
           </cell>
         </row>
         <row r="1097">
           <cell r="C1097">
-            <v>14020013</v>
+            <v>14020010</v>
           </cell>
         </row>
         <row r="1098">
           <cell r="C1098">
-            <v>14030001</v>
+            <v>14020011</v>
           </cell>
         </row>
         <row r="1099">
           <cell r="C1099">
-            <v>14030002</v>
+            <v>14020012</v>
           </cell>
         </row>
         <row r="1100">
           <cell r="C1100">
-            <v>14030003</v>
+            <v>14020013</v>
           </cell>
         </row>
         <row r="1101">
           <cell r="C1101">
-            <v>14030004</v>
+            <v>14030001</v>
           </cell>
         </row>
         <row r="1102">
           <cell r="C1102">
-            <v>14030005</v>
+            <v>14030002</v>
           </cell>
         </row>
         <row r="1103">
           <cell r="C1103">
-            <v>14030006</v>
+            <v>14030003</v>
           </cell>
         </row>
         <row r="1104">
           <cell r="C1104">
-            <v>14030007</v>
+            <v>14030004</v>
           </cell>
         </row>
         <row r="1105">
           <cell r="C1105">
-            <v>14030008</v>
+            <v>14030005</v>
           </cell>
         </row>
         <row r="1106">
           <cell r="C1106">
-            <v>14030009</v>
+            <v>14030006</v>
           </cell>
         </row>
         <row r="1107">
           <cell r="C1107">
-            <v>14030010</v>
+            <v>14030007</v>
           </cell>
         </row>
         <row r="1108">
           <cell r="C1108">
-            <v>14030011</v>
+            <v>14030008</v>
           </cell>
         </row>
         <row r="1109">
           <cell r="C1109">
-            <v>14030012</v>
+            <v>14030009</v>
           </cell>
         </row>
         <row r="1110">
           <cell r="C1110">
-            <v>14030013</v>
+            <v>14030010</v>
           </cell>
         </row>
         <row r="1111">
           <cell r="C1111">
-            <v>14040001</v>
+            <v>14030011</v>
           </cell>
         </row>
         <row r="1112">
           <cell r="C1112">
-            <v>14040002</v>
+            <v>14030012</v>
           </cell>
         </row>
         <row r="1113">
           <cell r="C1113">
-            <v>14040003</v>
+            <v>14030013</v>
           </cell>
         </row>
         <row r="1114">
           <cell r="C1114">
-            <v>14040004</v>
+            <v>14040001</v>
           </cell>
         </row>
         <row r="1115">
           <cell r="C1115">
-            <v>14040005</v>
+            <v>14040002</v>
           </cell>
         </row>
         <row r="1116">
           <cell r="C1116">
-            <v>14040006</v>
+            <v>14040003</v>
           </cell>
         </row>
         <row r="1117">
           <cell r="C1117">
-            <v>14040007</v>
+            <v>14040004</v>
           </cell>
         </row>
         <row r="1118">
           <cell r="C1118">
-            <v>14040008</v>
+            <v>14040005</v>
           </cell>
         </row>
         <row r="1119">
           <cell r="C1119">
-            <v>14040009</v>
+            <v>14040006</v>
           </cell>
         </row>
         <row r="1120">
           <cell r="C1120">
-            <v>14040010</v>
+            <v>14040007</v>
           </cell>
         </row>
         <row r="1121">
           <cell r="C1121">
-            <v>14040011</v>
+            <v>14040008</v>
           </cell>
         </row>
         <row r="1122">
           <cell r="C1122">
-            <v>14040012</v>
+            <v>14040009</v>
           </cell>
         </row>
         <row r="1123">
           <cell r="C1123">
-            <v>14050001</v>
+            <v>14040010</v>
           </cell>
         </row>
         <row r="1124">
           <cell r="C1124">
-            <v>14050002</v>
+            <v>14040011</v>
           </cell>
         </row>
         <row r="1125">
           <cell r="C1125">
-            <v>14050003</v>
+            <v>14040012</v>
           </cell>
         </row>
         <row r="1126">
           <cell r="C1126">
-            <v>14050004</v>
+            <v>14050001</v>
           </cell>
         </row>
         <row r="1127">
           <cell r="C1127">
-            <v>14050005</v>
+            <v>14050002</v>
           </cell>
         </row>
         <row r="1128">
           <cell r="C1128">
-            <v>14050006</v>
+            <v>14050003</v>
           </cell>
         </row>
         <row r="1129">
           <cell r="C1129">
-            <v>14050007</v>
+            <v>14050004</v>
           </cell>
         </row>
         <row r="1130">
           <cell r="C1130">
-            <v>14050008</v>
+            <v>14050005</v>
           </cell>
         </row>
         <row r="1131">
           <cell r="C1131">
-            <v>14050009</v>
+            <v>14050006</v>
           </cell>
         </row>
         <row r="1132">
           <cell r="C1132">
-            <v>14050010</v>
+            <v>14050007</v>
           </cell>
         </row>
         <row r="1133">
           <cell r="C1133">
-            <v>14050011</v>
+            <v>14050008</v>
           </cell>
         </row>
         <row r="1134">
           <cell r="C1134">
-            <v>14050012</v>
+            <v>14050009</v>
           </cell>
         </row>
         <row r="1135">
           <cell r="C1135">
-            <v>14060001</v>
+            <v>14050010</v>
           </cell>
         </row>
         <row r="1136">
           <cell r="C1136">
-            <v>14060002</v>
+            <v>14050011</v>
           </cell>
         </row>
         <row r="1137">
           <cell r="C1137">
-            <v>14060003</v>
+            <v>14050012</v>
           </cell>
         </row>
         <row r="1138">
           <cell r="C1138">
-            <v>14060004</v>
+            <v>14060001</v>
           </cell>
         </row>
         <row r="1139">
           <cell r="C1139">
-            <v>14060005</v>
+            <v>14060002</v>
           </cell>
         </row>
         <row r="1140">
           <cell r="C1140">
-            <v>14060006</v>
+            <v>14060003</v>
           </cell>
         </row>
         <row r="1141">
           <cell r="C1141">
-            <v>14070001</v>
+            <v>14060004</v>
           </cell>
         </row>
         <row r="1142">
           <cell r="C1142">
-            <v>14070002</v>
+            <v>14060005</v>
           </cell>
         </row>
         <row r="1143">
           <cell r="C1143">
-            <v>14070003</v>
+            <v>14060006</v>
           </cell>
         </row>
         <row r="1144">
           <cell r="C1144">
-            <v>14070004</v>
+            <v>14070001</v>
           </cell>
         </row>
         <row r="1145">
           <cell r="C1145">
-            <v>14080001</v>
+            <v>14070002</v>
           </cell>
         </row>
         <row r="1146">
           <cell r="C1146">
-            <v>14080002</v>
+            <v>14070003</v>
           </cell>
         </row>
         <row r="1147">
           <cell r="C1147">
-            <v>14080003</v>
+            <v>14070004</v>
           </cell>
         </row>
         <row r="1148">
           <cell r="C1148">
-            <v>14080004</v>
+            <v>14080001</v>
           </cell>
         </row>
         <row r="1149">
           <cell r="C1149">
-            <v>14090001</v>
+            <v>14080002</v>
           </cell>
         </row>
         <row r="1150">
           <cell r="C1150">
-            <v>14090002</v>
+            <v>14080003</v>
           </cell>
         </row>
         <row r="1151">
           <cell r="C1151">
-            <v>14090003</v>
+            <v>14080004</v>
           </cell>
         </row>
         <row r="1152">
           <cell r="C1152">
-            <v>14090004</v>
+            <v>14090001</v>
           </cell>
         </row>
         <row r="1153">
           <cell r="C1153">
-            <v>14100001</v>
+            <v>14090002</v>
           </cell>
         </row>
         <row r="1154">
           <cell r="C1154">
-            <v>14100002</v>
+            <v>14090003</v>
           </cell>
         </row>
         <row r="1155">
           <cell r="C1155">
-            <v>14100003</v>
+            <v>14090004</v>
           </cell>
         </row>
         <row r="1156">
           <cell r="C1156">
-            <v>14100004</v>
+            <v>14100001</v>
           </cell>
         </row>
         <row r="1157">
           <cell r="C1157">
-            <v>14100005</v>
+            <v>14100002</v>
           </cell>
         </row>
         <row r="1158">
           <cell r="C1158">
-            <v>14100006</v>
+            <v>14100003</v>
           </cell>
         </row>
         <row r="1159">
           <cell r="C1159">
-            <v>14100007</v>
+            <v>14100004</v>
           </cell>
         </row>
         <row r="1160">
           <cell r="C1160">
-            <v>14100008</v>
+            <v>14100005</v>
           </cell>
         </row>
         <row r="1161">
           <cell r="C1161">
-            <v>14100011</v>
+            <v>14100006</v>
           </cell>
         </row>
         <row r="1162">
           <cell r="C1162">
-            <v>14100012</v>
+            <v>14100007</v>
           </cell>
         </row>
         <row r="1163">
           <cell r="C1163">
-            <v>14100021</v>
+            <v>14100008</v>
           </cell>
         </row>
         <row r="1164">
           <cell r="C1164">
-            <v>14100022</v>
+            <v>14100011</v>
           </cell>
         </row>
         <row r="1165">
           <cell r="C1165">
-            <v>14100101</v>
+            <v>14100012</v>
           </cell>
         </row>
         <row r="1166">
           <cell r="C1166">
-            <v>14100102</v>
+            <v>14100021</v>
           </cell>
         </row>
         <row r="1167">
           <cell r="C1167">
-            <v>14100103</v>
+            <v>14100022</v>
           </cell>
         </row>
         <row r="1168">
           <cell r="C1168">
-            <v>14100104</v>
+            <v>14100101</v>
           </cell>
         </row>
         <row r="1169">
           <cell r="C1169">
-            <v>14100105</v>
+            <v>14100102</v>
           </cell>
         </row>
         <row r="1170">
           <cell r="C1170">
-            <v>14100106</v>
+            <v>14100103</v>
           </cell>
         </row>
         <row r="1171">
           <cell r="C1171">
-            <v>14100107</v>
+            <v>14100104</v>
           </cell>
         </row>
         <row r="1172">
           <cell r="C1172">
-            <v>14100108</v>
+            <v>14100105</v>
           </cell>
         </row>
         <row r="1173">
           <cell r="C1173">
-            <v>14100111</v>
+            <v>14100106</v>
           </cell>
         </row>
         <row r="1174">
           <cell r="C1174">
-            <v>14100112</v>
+            <v>14100107</v>
           </cell>
         </row>
         <row r="1175">
           <cell r="C1175">
-            <v>14100121</v>
+            <v>14100108</v>
           </cell>
         </row>
         <row r="1176">
           <cell r="C1176">
-            <v>14100122</v>
+            <v>14100111</v>
           </cell>
         </row>
         <row r="1177">
           <cell r="C1177">
-            <v>14100201</v>
+            <v>14100112</v>
           </cell>
         </row>
         <row r="1178">
           <cell r="C1178">
-            <v>14100202</v>
+            <v>14100121</v>
           </cell>
         </row>
         <row r="1179">
           <cell r="C1179">
-            <v>14100203</v>
+            <v>14100122</v>
           </cell>
         </row>
         <row r="1180">
           <cell r="C1180">
-            <v>14100204</v>
+            <v>14100201</v>
           </cell>
         </row>
         <row r="1181">
           <cell r="C1181">
-            <v>14100211</v>
+            <v>14100202</v>
           </cell>
         </row>
         <row r="1182">
           <cell r="C1182">
-            <v>14100221</v>
+            <v>14100203</v>
           </cell>
         </row>
         <row r="1183">
           <cell r="C1183">
-            <v>14110001</v>
+            <v>14100204</v>
           </cell>
         </row>
         <row r="1184">
           <cell r="C1184">
-            <v>14110002</v>
+            <v>14100211</v>
           </cell>
         </row>
         <row r="1185">
           <cell r="C1185">
-            <v>14110003</v>
+            <v>14100221</v>
           </cell>
         </row>
         <row r="1186">
           <cell r="C1186">
-            <v>14110004</v>
+            <v>14110001</v>
           </cell>
         </row>
         <row r="1187">
           <cell r="C1187">
-            <v>14110005</v>
+            <v>14110002</v>
           </cell>
         </row>
         <row r="1188">
           <cell r="C1188">
-            <v>14110006</v>
+            <v>14110003</v>
           </cell>
         </row>
         <row r="1189">
           <cell r="C1189">
-            <v>14110007</v>
+            <v>14110004</v>
           </cell>
         </row>
         <row r="1190">
           <cell r="C1190">
-            <v>14110008</v>
+            <v>14110005</v>
           </cell>
         </row>
         <row r="1191">
           <cell r="C1191">
-            <v>14110009</v>
+            <v>14110006</v>
           </cell>
         </row>
         <row r="1192">
           <cell r="C1192">
-            <v>14110010</v>
+            <v>14110007</v>
           </cell>
         </row>
         <row r="1193">
           <cell r="C1193">
-            <v>14110011</v>
+            <v>14110008</v>
           </cell>
         </row>
         <row r="1194">
           <cell r="C1194">
-            <v>14110012</v>
+            <v>14110009</v>
           </cell>
         </row>
         <row r="1195">
           <cell r="C1195">
-            <v>14110021</v>
+            <v>14110010</v>
           </cell>
         </row>
         <row r="1196">
           <cell r="C1196">
-            <v>14110022</v>
+            <v>14110011</v>
           </cell>
         </row>
         <row r="1197">
           <cell r="C1197">
-            <v>14110023</v>
+            <v>14110012</v>
           </cell>
         </row>
         <row r="1198">
           <cell r="C1198">
-            <v>15201001</v>
+            <v>14110021</v>
           </cell>
         </row>
         <row r="1199">
           <cell r="C1199">
-            <v>15201002</v>
+            <v>14110022</v>
           </cell>
         </row>
         <row r="1200">
           <cell r="C1200">
-            <v>15201003</v>
+            <v>14110023</v>
           </cell>
         </row>
         <row r="1201">
           <cell r="C1201">
-            <v>15201004</v>
+            <v>15201001</v>
           </cell>
         </row>
         <row r="1202">
           <cell r="C1202">
-            <v>15201005</v>
+            <v>15201002</v>
           </cell>
         </row>
         <row r="1203">
           <cell r="C1203">
-            <v>15201006</v>
+            <v>15201003</v>
           </cell>
         </row>
         <row r="1204">
           <cell r="C1204">
-            <v>15202001</v>
+            <v>15201004</v>
           </cell>
         </row>
         <row r="1205">
           <cell r="C1205">
-            <v>15202002</v>
+            <v>15201005</v>
           </cell>
         </row>
         <row r="1206">
           <cell r="C1206">
-            <v>15202003</v>
+            <v>15201006</v>
           </cell>
         </row>
         <row r="1207">
           <cell r="C1207">
-            <v>15202004</v>
+            <v>15202001</v>
           </cell>
         </row>
         <row r="1208">
           <cell r="C1208">
-            <v>15202005</v>
+            <v>15202002</v>
           </cell>
         </row>
         <row r="1209">
           <cell r="C1209">
-            <v>15202006</v>
+            <v>15202003</v>
           </cell>
         </row>
         <row r="1210">
           <cell r="C1210">
-            <v>15203001</v>
+            <v>15202004</v>
           </cell>
         </row>
         <row r="1211">
           <cell r="C1211">
-            <v>15203002</v>
+            <v>15202005</v>
           </cell>
         </row>
         <row r="1212">
           <cell r="C1212">
-            <v>15203003</v>
+            <v>15202006</v>
           </cell>
         </row>
         <row r="1213">
           <cell r="C1213">
-            <v>15203004</v>
+            <v>15203001</v>
           </cell>
         </row>
         <row r="1214">
           <cell r="C1214">
-            <v>15203005</v>
+            <v>15203002</v>
           </cell>
         </row>
         <row r="1215">
           <cell r="C1215">
-            <v>15203006</v>
+            <v>15203003</v>
           </cell>
         </row>
         <row r="1216">
           <cell r="C1216">
-            <v>15204001</v>
+            <v>15203004</v>
           </cell>
         </row>
         <row r="1217">
           <cell r="C1217">
-            <v>15204002</v>
+            <v>15203005</v>
           </cell>
         </row>
         <row r="1218">
           <cell r="C1218">
-            <v>15204003</v>
+            <v>15203006</v>
           </cell>
         </row>
         <row r="1219">
           <cell r="C1219">
-            <v>15204004</v>
+            <v>15204001</v>
           </cell>
         </row>
         <row r="1220">
           <cell r="C1220">
-            <v>15204005</v>
+            <v>15204002</v>
           </cell>
         </row>
         <row r="1221">
           <cell r="C1221">
-            <v>15204006</v>
+            <v>15204003</v>
           </cell>
         </row>
         <row r="1222">
           <cell r="C1222">
-            <v>15205001</v>
+            <v>15204004</v>
           </cell>
         </row>
         <row r="1223">
           <cell r="C1223">
-            <v>15205002</v>
+            <v>15204005</v>
           </cell>
         </row>
         <row r="1224">
           <cell r="C1224">
-            <v>15205003</v>
+            <v>15204006</v>
           </cell>
         </row>
         <row r="1225">
           <cell r="C1225">
-            <v>15205004</v>
+            <v>15205001</v>
           </cell>
         </row>
         <row r="1226">
           <cell r="C1226">
-            <v>15205005</v>
+            <v>15205002</v>
           </cell>
         </row>
         <row r="1227">
           <cell r="C1227">
-            <v>15205006</v>
+            <v>15205003</v>
           </cell>
         </row>
         <row r="1228">
           <cell r="C1228">
-            <v>15205007</v>
+            <v>15205004</v>
           </cell>
         </row>
         <row r="1229">
           <cell r="C1229">
-            <v>15206001</v>
+            <v>15205005</v>
           </cell>
         </row>
         <row r="1230">
           <cell r="C1230">
-            <v>15206002</v>
+            <v>15205006</v>
           </cell>
         </row>
         <row r="1231">
           <cell r="C1231">
-            <v>15206003</v>
+            <v>15205007</v>
           </cell>
         </row>
         <row r="1232">
           <cell r="C1232">
-            <v>15207001</v>
+            <v>15206001</v>
           </cell>
         </row>
         <row r="1233">
           <cell r="C1233">
-            <v>15207002</v>
+            <v>15206002</v>
           </cell>
         </row>
         <row r="1234">
           <cell r="C1234">
-            <v>15207003</v>
+            <v>15206003</v>
           </cell>
         </row>
         <row r="1235">
           <cell r="C1235">
-            <v>15208001</v>
+            <v>15207001</v>
           </cell>
         </row>
         <row r="1236">
           <cell r="C1236">
-            <v>15208002</v>
+            <v>15207002</v>
           </cell>
         </row>
         <row r="1237">
           <cell r="C1237">
-            <v>15208003</v>
+            <v>15207003</v>
           </cell>
         </row>
         <row r="1238">
           <cell r="C1238">
-            <v>15209001</v>
+            <v>15208001</v>
           </cell>
         </row>
         <row r="1239">
           <cell r="C1239">
-            <v>15209002</v>
+            <v>15208002</v>
           </cell>
         </row>
         <row r="1240">
           <cell r="C1240">
-            <v>15210001</v>
+            <v>15208003</v>
           </cell>
         </row>
         <row r="1241">
           <cell r="C1241">
-            <v>15210002</v>
+            <v>15209001</v>
           </cell>
         </row>
         <row r="1242">
           <cell r="C1242">
-            <v>15210003</v>
+            <v>15209002</v>
           </cell>
         </row>
         <row r="1243">
           <cell r="C1243">
-            <v>15210004</v>
+            <v>15210001</v>
           </cell>
         </row>
         <row r="1244">
           <cell r="C1244">
-            <v>15210011</v>
+            <v>15210002</v>
           </cell>
         </row>
         <row r="1245">
           <cell r="C1245">
-            <v>15210012</v>
+            <v>15210003</v>
           </cell>
         </row>
         <row r="1246">
           <cell r="C1246">
-            <v>15210101</v>
+            <v>15210004</v>
           </cell>
         </row>
         <row r="1247">
           <cell r="C1247">
-            <v>15210102</v>
+            <v>15210011</v>
           </cell>
         </row>
         <row r="1248">
           <cell r="C1248">
-            <v>15210103</v>
+            <v>15210012</v>
           </cell>
         </row>
         <row r="1249">
           <cell r="C1249">
-            <v>15210104</v>
+            <v>15210101</v>
           </cell>
         </row>
         <row r="1250">
           <cell r="C1250">
-            <v>15210111</v>
+            <v>15210102</v>
           </cell>
         </row>
         <row r="1251">
           <cell r="C1251">
-            <v>15210112</v>
+            <v>15210103</v>
           </cell>
         </row>
         <row r="1252">
           <cell r="C1252">
-            <v>15210201</v>
+            <v>15210104</v>
           </cell>
         </row>
         <row r="1253">
           <cell r="C1253">
-            <v>15210202</v>
+            <v>15210111</v>
           </cell>
         </row>
         <row r="1254">
           <cell r="C1254">
-            <v>15210211</v>
+            <v>15210112</v>
           </cell>
         </row>
         <row r="1255">
           <cell r="C1255">
-            <v>15211001</v>
+            <v>15210201</v>
           </cell>
         </row>
         <row r="1256">
           <cell r="C1256">
-            <v>15211002</v>
+            <v>15210202</v>
           </cell>
         </row>
         <row r="1257">
           <cell r="C1257">
-            <v>15211003</v>
+            <v>15210211</v>
           </cell>
         </row>
         <row r="1258">
           <cell r="C1258">
-            <v>15211004</v>
+            <v>15211001</v>
           </cell>
         </row>
         <row r="1259">
           <cell r="C1259">
-            <v>15211005</v>
+            <v>15211002</v>
           </cell>
         </row>
         <row r="1260">
           <cell r="C1260">
-            <v>15211006</v>
+            <v>15211003</v>
           </cell>
         </row>
         <row r="1261">
           <cell r="C1261">
-            <v>15211011</v>
+            <v>15211004</v>
           </cell>
         </row>
         <row r="1262">
           <cell r="C1262">
-            <v>15211012</v>
+            <v>15211005</v>
           </cell>
         </row>
         <row r="1263">
           <cell r="C1263">
-            <v>15211013</v>
+            <v>15211006</v>
           </cell>
         </row>
         <row r="1264">
           <cell r="C1264">
-            <v>15301001</v>
+            <v>15211011</v>
           </cell>
         </row>
         <row r="1265">
           <cell r="C1265">
-            <v>15301002</v>
+            <v>15211012</v>
           </cell>
         </row>
         <row r="1266">
           <cell r="C1266">
-            <v>15301003</v>
+            <v>15211013</v>
           </cell>
         </row>
         <row r="1267">
           <cell r="C1267">
-            <v>15301004</v>
+            <v>15301001</v>
           </cell>
         </row>
         <row r="1268">
           <cell r="C1268">
-            <v>15301005</v>
+            <v>15301002</v>
           </cell>
         </row>
         <row r="1269">
           <cell r="C1269">
-            <v>15301006</v>
+            <v>15301003</v>
           </cell>
         </row>
         <row r="1270">
           <cell r="C1270">
-            <v>15302001</v>
+            <v>15301004</v>
           </cell>
         </row>
         <row r="1271">
           <cell r="C1271">
-            <v>15302002</v>
+            <v>15301005</v>
           </cell>
         </row>
         <row r="1272">
           <cell r="C1272">
-            <v>15302003</v>
+            <v>15301006</v>
           </cell>
         </row>
         <row r="1273">
           <cell r="C1273">
-            <v>15302004</v>
+            <v>15302001</v>
           </cell>
         </row>
         <row r="1274">
           <cell r="C1274">
-            <v>15302005</v>
+            <v>15302002</v>
           </cell>
         </row>
         <row r="1275">
           <cell r="C1275">
-            <v>15302006</v>
+            <v>15302003</v>
           </cell>
         </row>
         <row r="1276">
           <cell r="C1276">
-            <v>15302007</v>
+            <v>15302004</v>
           </cell>
         </row>
         <row r="1277">
           <cell r="C1277">
-            <v>15303001</v>
+            <v>15302005</v>
           </cell>
         </row>
         <row r="1278">
           <cell r="C1278">
-            <v>15303002</v>
+            <v>15302006</v>
           </cell>
         </row>
         <row r="1279">
           <cell r="C1279">
-            <v>15303003</v>
+            <v>15302007</v>
           </cell>
         </row>
         <row r="1280">
           <cell r="C1280">
-            <v>15303004</v>
+            <v>15303001</v>
           </cell>
         </row>
         <row r="1281">
           <cell r="C1281">
-            <v>15303005</v>
+            <v>15303002</v>
           </cell>
         </row>
         <row r="1282">
           <cell r="C1282">
-            <v>15303006</v>
+            <v>15303003</v>
           </cell>
         </row>
         <row r="1283">
           <cell r="C1283">
-            <v>15304001</v>
+            <v>15303004</v>
           </cell>
         </row>
         <row r="1284">
           <cell r="C1284">
-            <v>15304002</v>
+            <v>15303005</v>
           </cell>
         </row>
         <row r="1285">
           <cell r="C1285">
-            <v>15304003</v>
+            <v>15303006</v>
           </cell>
         </row>
         <row r="1286">
           <cell r="C1286">
-            <v>15304004</v>
+            <v>15304001</v>
           </cell>
         </row>
         <row r="1287">
           <cell r="C1287">
-            <v>15304005</v>
+            <v>15304002</v>
           </cell>
         </row>
         <row r="1288">
           <cell r="C1288">
-            <v>15304006</v>
+            <v>15304003</v>
           </cell>
         </row>
         <row r="1289">
           <cell r="C1289">
-            <v>15305001</v>
+            <v>15304004</v>
           </cell>
         </row>
         <row r="1290">
           <cell r="C1290">
-            <v>15305002</v>
+            <v>15304005</v>
           </cell>
         </row>
         <row r="1291">
           <cell r="C1291">
-            <v>15305003</v>
+            <v>15304006</v>
           </cell>
         </row>
         <row r="1292">
           <cell r="C1292">
-            <v>15305004</v>
+            <v>15305001</v>
           </cell>
         </row>
         <row r="1293">
           <cell r="C1293">
-            <v>15305005</v>
+            <v>15305002</v>
           </cell>
         </row>
         <row r="1294">
           <cell r="C1294">
-            <v>15305006</v>
+            <v>15305003</v>
           </cell>
         </row>
         <row r="1295">
           <cell r="C1295">
-            <v>15306001</v>
+            <v>15305004</v>
           </cell>
         </row>
         <row r="1296">
           <cell r="C1296">
-            <v>15306002</v>
+            <v>15305005</v>
           </cell>
         </row>
         <row r="1297">
           <cell r="C1297">
-            <v>15306003</v>
+            <v>15305006</v>
           </cell>
         </row>
         <row r="1298">
           <cell r="C1298">
-            <v>15307001</v>
+            <v>15306001</v>
           </cell>
         </row>
         <row r="1299">
           <cell r="C1299">
-            <v>15307002</v>
+            <v>15306002</v>
           </cell>
         </row>
         <row r="1300">
           <cell r="C1300">
-            <v>15308001</v>
+            <v>15306003</v>
           </cell>
         </row>
         <row r="1301">
           <cell r="C1301">
-            <v>15308002</v>
+            <v>15307001</v>
           </cell>
         </row>
         <row r="1302">
           <cell r="C1302">
-            <v>15308003</v>
+            <v>15307002</v>
           </cell>
         </row>
         <row r="1303">
           <cell r="C1303">
-            <v>15308004</v>
+            <v>15308001</v>
           </cell>
         </row>
         <row r="1304">
           <cell r="C1304">
-            <v>15309001</v>
+            <v>15308002</v>
           </cell>
         </row>
         <row r="1305">
           <cell r="C1305">
-            <v>15309002</v>
+            <v>15308003</v>
           </cell>
         </row>
         <row r="1306">
           <cell r="C1306">
-            <v>15309003</v>
+            <v>15308004</v>
           </cell>
         </row>
         <row r="1307">
           <cell r="C1307">
-            <v>15310001</v>
+            <v>15309001</v>
           </cell>
         </row>
         <row r="1308">
           <cell r="C1308">
-            <v>15310002</v>
+            <v>15309002</v>
           </cell>
         </row>
         <row r="1309">
           <cell r="C1309">
-            <v>15310003</v>
+            <v>15309003</v>
           </cell>
         </row>
         <row r="1310">
           <cell r="C1310">
-            <v>15310004</v>
+            <v>15310001</v>
           </cell>
         </row>
         <row r="1311">
           <cell r="C1311">
-            <v>15310011</v>
+            <v>15310002</v>
           </cell>
         </row>
         <row r="1312">
           <cell r="C1312">
-            <v>15310012</v>
+            <v>15310003</v>
           </cell>
         </row>
         <row r="1313">
           <cell r="C1313">
-            <v>15310101</v>
+            <v>15310004</v>
           </cell>
         </row>
         <row r="1314">
           <cell r="C1314">
-            <v>15310102</v>
+            <v>15310011</v>
           </cell>
         </row>
         <row r="1315">
           <cell r="C1315">
-            <v>15310103</v>
+            <v>15310012</v>
           </cell>
         </row>
         <row r="1316">
           <cell r="C1316">
-            <v>15310104</v>
+            <v>15310101</v>
           </cell>
         </row>
         <row r="1317">
           <cell r="C1317">
-            <v>15310111</v>
+            <v>15310102</v>
           </cell>
         </row>
         <row r="1318">
           <cell r="C1318">
-            <v>15310112</v>
+            <v>15310103</v>
           </cell>
         </row>
         <row r="1319">
           <cell r="C1319">
-            <v>15310201</v>
+            <v>15310104</v>
           </cell>
         </row>
         <row r="1320">
           <cell r="C1320">
-            <v>15310202</v>
+            <v>15310111</v>
           </cell>
         </row>
         <row r="1321">
           <cell r="C1321">
-            <v>15310211</v>
+            <v>15310112</v>
           </cell>
         </row>
         <row r="1322">
           <cell r="C1322">
-            <v>15311001</v>
+            <v>15310201</v>
           </cell>
         </row>
         <row r="1323">
           <cell r="C1323">
-            <v>15311002</v>
+            <v>15310202</v>
           </cell>
         </row>
         <row r="1324">
           <cell r="C1324">
-            <v>15311003</v>
+            <v>15310211</v>
           </cell>
         </row>
         <row r="1325">
           <cell r="C1325">
-            <v>15311004</v>
+            <v>15311001</v>
           </cell>
         </row>
         <row r="1326">
           <cell r="C1326">
-            <v>15311005</v>
+            <v>15311002</v>
           </cell>
         </row>
         <row r="1327">
           <cell r="C1327">
-            <v>15311006</v>
+            <v>15311003</v>
           </cell>
         </row>
         <row r="1328">
           <cell r="C1328">
-            <v>15311011</v>
+            <v>15311004</v>
           </cell>
         </row>
         <row r="1329">
           <cell r="C1329">
-            <v>15311012</v>
+            <v>15311005</v>
           </cell>
         </row>
         <row r="1330">
           <cell r="C1330">
-            <v>15311013</v>
+            <v>15311006</v>
           </cell>
         </row>
         <row r="1331">
           <cell r="C1331">
-            <v>15401001</v>
+            <v>15311011</v>
           </cell>
         </row>
         <row r="1332">
           <cell r="C1332">
-            <v>15401002</v>
+            <v>15311012</v>
           </cell>
         </row>
         <row r="1333">
           <cell r="C1333">
-            <v>15401003</v>
+            <v>15311013</v>
           </cell>
         </row>
         <row r="1334">
           <cell r="C1334">
-            <v>15401004</v>
+            <v>15401001</v>
+          </cell>
+        </row>
+        <row r="1335">
+          <cell r="C1335">
+            <v>15401002</v>
           </cell>
         </row>
       </sheetData>
@@ -70011,13 +70022,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="CP23:CP25"/>
-    <mergeCell ref="CP26:CP28"/>
-    <mergeCell ref="CP8:CP10"/>
-    <mergeCell ref="CP11:CP13"/>
-    <mergeCell ref="CP14:CP16"/>
-    <mergeCell ref="CP17:CP19"/>
-    <mergeCell ref="CP20:CP22"/>
     <mergeCell ref="K18:K20"/>
     <mergeCell ref="K21:K23"/>
     <mergeCell ref="AX4:AX6"/>
@@ -70032,6 +70036,13 @@
     <mergeCell ref="K9:K11"/>
     <mergeCell ref="K12:K14"/>
     <mergeCell ref="K15:K17"/>
+    <mergeCell ref="CP23:CP25"/>
+    <mergeCell ref="CP26:CP28"/>
+    <mergeCell ref="CP8:CP10"/>
+    <mergeCell ref="CP11:CP13"/>
+    <mergeCell ref="CP14:CP16"/>
+    <mergeCell ref="CP17:CP19"/>
+    <mergeCell ref="CP20:CP22"/>
   </mergeCells>
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -84755,7 +84766,7 @@
         <v>1200</v>
       </c>
       <c r="P96" s="1">
-        <f>LOOKUP(Q96,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(Q96,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="Q96" s="1">
@@ -84770,7 +84781,7 @@
       <c r="T96" s="3"/>
       <c r="U96" s="3"/>
       <c r="V96" s="3">
-        <f>LOOKUP(W96,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(W96,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="W96" s="1">
@@ -84785,7 +84796,7 @@
       <c r="Z96" s="3"/>
       <c r="AA96" s="3"/>
       <c r="AB96" s="3">
-        <f>LOOKUP(AC96,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(AC96,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="AC96" s="1">
@@ -84834,7 +84845,7 @@
       </c>
       <c r="N97" s="5"/>
       <c r="P97" s="1">
-        <f>LOOKUP(Q97,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(Q97,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="Q97" s="1">
@@ -84849,7 +84860,7 @@
       <c r="T97" s="3"/>
       <c r="U97" s="3"/>
       <c r="V97" s="3">
-        <f>LOOKUP(W97,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(W97,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="W97" s="1">
@@ -84864,7 +84875,7 @@
       <c r="Z97" s="3"/>
       <c r="AA97" s="3"/>
       <c r="AB97" s="3">
-        <f>LOOKUP(AC97,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(AC97,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="AC97" s="1">
@@ -84909,7 +84920,7 @@
       </c>
       <c r="N98" s="5"/>
       <c r="P98" s="1" t="e">
-        <f>LOOKUP(Q98,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(Q98,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>#N/A</v>
       </c>
       <c r="R98" s="1" t="s">
@@ -84921,7 +84932,7 @@
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
       <c r="V98" s="3">
-        <f>LOOKUP(W98,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(W98,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="W98" s="1">
@@ -84936,7 +84947,7 @@
       <c r="Z98" s="3"/>
       <c r="AA98" s="3"/>
       <c r="AB98" s="3">
-        <f>LOOKUP(AC98,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(AC98,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="AC98" s="1">
@@ -84985,7 +84996,7 @@
       </c>
       <c r="N99" s="5"/>
       <c r="P99" s="1">
-        <f>LOOKUP(Q99,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(Q99,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="Q99" s="1">
@@ -85000,7 +85011,7 @@
       <c r="T99" s="3"/>
       <c r="U99" s="3"/>
       <c r="V99" s="3">
-        <f>LOOKUP(W99,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(W99,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="W99" s="1">
@@ -85015,7 +85026,7 @@
       <c r="Z99" s="3"/>
       <c r="AA99" s="3"/>
       <c r="AB99" s="3">
-        <f>LOOKUP(AC99,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(AC99,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="AC99" s="1">
@@ -85043,7 +85054,7 @@
       </c>
       <c r="N100" s="5"/>
       <c r="P100" s="1">
-        <f>LOOKUP(Q100,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(Q100,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="Q100" s="1">
@@ -85058,7 +85069,7 @@
       <c r="T100" s="3"/>
       <c r="U100" s="3"/>
       <c r="V100" s="3">
-        <f>LOOKUP(W100,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(W100,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="W100" s="1">
@@ -85073,7 +85084,7 @@
       <c r="Z100" s="3"/>
       <c r="AA100" s="3"/>
       <c r="AB100" s="3">
-        <f>LOOKUP(AC100,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(AC100,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="AC100" s="1">
@@ -85119,7 +85130,7 @@
       <c r="Z101" s="3"/>
       <c r="AA101" s="3"/>
       <c r="AB101" s="3">
-        <f>LOOKUP(AC101,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(AC101,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="AC101" s="1">
@@ -85276,7 +85287,7 @@
         <v>1307</v>
       </c>
       <c r="AB105" s="3">
-        <f>LOOKUP(AC105,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(AC105,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="AC105" s="1">
@@ -85311,7 +85322,7 @@
       <c r="N106" s="5"/>
       <c r="R106" s="1"/>
       <c r="AB106" s="3">
-        <f>LOOKUP(AC106,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(AC106,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="AC106" s="1">
@@ -85345,7 +85356,7 @@
       </c>
       <c r="N107" s="5"/>
       <c r="AB107" s="3">
-        <f>LOOKUP(AC107,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(AC107,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="AC107" s="1">
@@ -85383,7 +85394,7 @@
       </c>
       <c r="N108" s="5"/>
       <c r="AB108" s="3">
-        <f>LOOKUP(AC108,[2]ItemProto!$C$857:$C$1334,[2]ItemProto!$S$857:$S$1334)</f>
+        <f>LOOKUP(AC108,[2]ItemProto!$C$858:$C$1335,[2]ItemProto!$S$858:$S$1335)</f>
         <v>0</v>
       </c>
       <c r="AC108" s="1">

--- a/WeiJingShuZhi/属性表.xlsx
+++ b/WeiJingShuZhi/属性表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\WeiJingShuZhi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AD7A73-FD0E-4B74-AA51-C19EE5C58C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A632C4C9-100E-4FA3-AAE0-5B0AE22D3422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5548" uniqueCount="3128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5628" uniqueCount="3161">
   <si>
     <t>人物属性</t>
   </si>
@@ -9970,6 +9970,122 @@
   <si>
     <t>合成</t>
     <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物突破</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>物防</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔防</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+百分比</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命百分比</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法+百分比</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>对怪伤害+百分比  伤害减免+百分比</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础材料</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠灵之尘</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠之冰核</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠之印记</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物之核碎片</t>
+    <phoneticPr fontId="36" type="noConversion"/>
+  </si>
+  <si>
+    <t>1级</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>2级</t>
+  </si>
+  <si>
+    <t>3级</t>
+  </si>
+  <si>
+    <t>4级</t>
+  </si>
+  <si>
+    <t>5级</t>
+  </si>
+  <si>
+    <t>6级</t>
+  </si>
+  <si>
+    <t>7级</t>
+  </si>
+  <si>
+    <t>8级</t>
+  </si>
+  <si>
+    <t>9级</t>
+  </si>
+  <si>
+    <t>金币</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>11级</t>
+  </si>
+  <si>
+    <t>12级</t>
+  </si>
+  <si>
+    <t>13级</t>
+  </si>
+  <si>
+    <t>14级</t>
+  </si>
+  <si>
+    <t>15级</t>
+  </si>
+  <si>
+    <t>16级</t>
+  </si>
+  <si>
+    <t>17级</t>
+  </si>
+  <si>
+    <t>19级</t>
   </si>
 </sst>
 </file>
@@ -10524,7 +10640,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10868,6 +10984,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11536,2849 +11655,2934 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="268">
-          <cell r="C268">
-            <v>10014022</v>
-          </cell>
-        </row>
         <row r="858">
           <cell r="C858">
-            <v>10103504</v>
+            <v>10102302</v>
           </cell>
           <cell r="S858" t="str">
-            <v>7@204103;0.01;0.03</v>
+            <v>9@118203;30;75</v>
           </cell>
         </row>
         <row r="859">
           <cell r="C859">
-            <v>10103601</v>
+            <v>10102303</v>
           </cell>
           <cell r="S859" t="str">
-            <v>6@100603;50;150</v>
+            <v>9@205003;0.01;0.03</v>
           </cell>
         </row>
         <row r="860">
           <cell r="C860">
-            <v>10103602</v>
+            <v>10102401</v>
           </cell>
           <cell r="S860" t="str">
-            <v>6@100803;50;150</v>
+            <v>8@105403;5;20</v>
           </cell>
         </row>
         <row r="861">
           <cell r="C861">
-            <v>10103603</v>
+            <v>10102402</v>
           </cell>
           <cell r="S861" t="str">
-            <v>6@200303;0.01;0.03</v>
+            <v>8@105203;5;20</v>
           </cell>
         </row>
         <row r="862">
           <cell r="C862">
-            <v>10201101</v>
+            <v>10102403</v>
           </cell>
-          <cell r="S862">
-            <v>7102001</v>
+          <cell r="S862" t="str">
+            <v>8@105503;5;20</v>
           </cell>
         </row>
         <row r="863">
           <cell r="C863">
-            <v>10201102</v>
+            <v>10102404</v>
           </cell>
-          <cell r="S863">
-            <v>7102002</v>
+          <cell r="S863" t="str">
+            <v>8@203603;0.01;0.03</v>
           </cell>
         </row>
         <row r="864">
           <cell r="C864">
-            <v>10201103</v>
+            <v>10102501</v>
           </cell>
-          <cell r="S864">
-            <v>7102003</v>
+          <cell r="S864" t="str">
+            <v>7@105103;5;20</v>
           </cell>
         </row>
         <row r="865">
           <cell r="C865">
-            <v>10201104</v>
+            <v>10102502</v>
           </cell>
-          <cell r="S865">
-            <v>7102004</v>
+          <cell r="S865" t="str">
+            <v>7@105303;5;20</v>
           </cell>
         </row>
         <row r="866">
           <cell r="C866">
-            <v>10201201</v>
+            <v>10102503</v>
           </cell>
-          <cell r="S866">
-            <v>7103001</v>
+          <cell r="S866" t="str">
+            <v>7@105503;5;20</v>
           </cell>
         </row>
         <row r="867">
           <cell r="C867">
-            <v>10201202</v>
+            <v>10102504</v>
           </cell>
-          <cell r="S867">
-            <v>7103002</v>
+          <cell r="S867" t="str">
+            <v>7@200503;0.01;0.03</v>
           </cell>
         </row>
         <row r="868">
           <cell r="C868">
-            <v>10201203</v>
+            <v>10102601</v>
           </cell>
-          <cell r="S868">
-            <v>7103003</v>
+          <cell r="S868" t="str">
+            <v>6@100603;30;100</v>
           </cell>
         </row>
         <row r="869">
           <cell r="C869">
-            <v>10201204</v>
+            <v>10102602</v>
           </cell>
-          <cell r="S869">
-            <v>7103004</v>
+          <cell r="S869" t="str">
+            <v>6@100803;30;100</v>
           </cell>
         </row>
         <row r="870">
           <cell r="C870">
-            <v>10202101</v>
+            <v>10102603</v>
           </cell>
-          <cell r="S870">
-            <v>7202001</v>
+          <cell r="S870" t="str">
+            <v>6@200103;0.01;0.03</v>
           </cell>
         </row>
         <row r="871">
           <cell r="C871">
-            <v>10202102</v>
+            <v>10103101</v>
           </cell>
-          <cell r="S871">
-            <v>7202002</v>
+          <cell r="S871" t="str">
+            <v>10@100403;50;150</v>
           </cell>
         </row>
         <row r="872">
           <cell r="C872">
-            <v>10202103</v>
+            <v>10103102</v>
           </cell>
-          <cell r="S872">
-            <v>7202003</v>
+          <cell r="S872" t="str">
+            <v>10@119103;30;100</v>
           </cell>
         </row>
         <row r="873">
           <cell r="C873">
-            <v>10202104</v>
+            <v>10103103</v>
           </cell>
-          <cell r="S873">
-            <v>7202004</v>
+          <cell r="S873" t="str">
+            <v>10@202103;0.01;0.03</v>
           </cell>
         </row>
         <row r="874">
           <cell r="C874">
-            <v>10202201</v>
+            <v>10103201</v>
           </cell>
-          <cell r="S874">
-            <v>7203001</v>
+          <cell r="S874" t="str">
+            <v>2@100203;250;750</v>
           </cell>
         </row>
         <row r="875">
           <cell r="C875">
-            <v>10202202</v>
+            <v>10103202</v>
           </cell>
-          <cell r="S875">
-            <v>7203002</v>
+          <cell r="S875" t="str">
+            <v>2@119403;30;100</v>
           </cell>
         </row>
         <row r="876">
           <cell r="C876">
-            <v>10202203</v>
+            <v>10103203</v>
           </cell>
-          <cell r="S876">
-            <v>7203003</v>
+          <cell r="S876" t="str">
+            <v>2@200903;0.01;0.03</v>
           </cell>
         </row>
         <row r="877">
           <cell r="C877">
-            <v>10202204</v>
+            <v>10103301</v>
           </cell>
-          <cell r="S877">
-            <v>7203004</v>
+          <cell r="S877" t="str">
+            <v>9@118103;50;150</v>
           </cell>
         </row>
         <row r="878">
           <cell r="C878">
-            <v>10203101</v>
+            <v>10103302</v>
           </cell>
-          <cell r="S878">
-            <v>7302001</v>
+          <cell r="S878" t="str">
+            <v>9@118203;50;150</v>
           </cell>
         </row>
         <row r="879">
           <cell r="C879">
-            <v>10203102</v>
+            <v>10103303</v>
           </cell>
-          <cell r="S879">
-            <v>7302002</v>
+          <cell r="S879" t="str">
+            <v>9@110303;50;150</v>
           </cell>
         </row>
         <row r="880">
           <cell r="C880">
-            <v>10203201</v>
+            <v>10103401</v>
           </cell>
-          <cell r="S880">
-            <v>7303001</v>
+          <cell r="S880" t="str">
+            <v>8@105403;8;30</v>
           </cell>
         </row>
         <row r="881">
           <cell r="C881">
-            <v>10203202</v>
+            <v>10103402</v>
           </cell>
-          <cell r="S881">
-            <v>7303002</v>
+          <cell r="S881" t="str">
+            <v>8@105203;8;30</v>
           </cell>
         </row>
         <row r="882">
           <cell r="C882">
-            <v>10301001</v>
+            <v>10103403</v>
           </cell>
-          <cell r="S882">
-            <v>6101003</v>
+          <cell r="S882" t="str">
+            <v>8@105503;8;30</v>
           </cell>
         </row>
         <row r="883">
           <cell r="C883">
-            <v>10301002</v>
+            <v>10103404</v>
           </cell>
-          <cell r="S883">
-            <v>6102003</v>
+          <cell r="S883" t="str">
+            <v>8@100202;0.01;0.03</v>
           </cell>
         </row>
         <row r="884">
           <cell r="C884">
-            <v>10301003</v>
+            <v>10103501</v>
           </cell>
-          <cell r="S884">
-            <v>6103003</v>
+          <cell r="S884" t="str">
+            <v>7@105103;8;30</v>
           </cell>
         </row>
         <row r="885">
           <cell r="C885">
-            <v>10301004</v>
+            <v>10103502</v>
           </cell>
-          <cell r="S885">
-            <v>6104004</v>
+          <cell r="S885" t="str">
+            <v>7@105303;8;30</v>
           </cell>
         </row>
         <row r="886">
           <cell r="C886">
-            <v>10301005</v>
+            <v>10103503</v>
           </cell>
-          <cell r="S886">
-            <v>6105004</v>
+          <cell r="S886" t="str">
+            <v>7@105503;8;30</v>
           </cell>
         </row>
         <row r="887">
           <cell r="C887">
-            <v>10301006</v>
+            <v>10103504</v>
           </cell>
-          <cell r="S887">
-            <v>6106003</v>
+          <cell r="S887" t="str">
+            <v>7@204103;0.01;0.03</v>
           </cell>
         </row>
         <row r="888">
           <cell r="C888">
-            <v>10302001</v>
+            <v>10103601</v>
           </cell>
-          <cell r="S888">
-            <v>6201003</v>
+          <cell r="S888" t="str">
+            <v>6@100603;50;150</v>
           </cell>
         </row>
         <row r="889">
           <cell r="C889">
-            <v>10302002</v>
+            <v>10103602</v>
           </cell>
-          <cell r="S889">
-            <v>6202003</v>
+          <cell r="S889" t="str">
+            <v>6@100803;50;150</v>
           </cell>
         </row>
         <row r="890">
           <cell r="C890">
-            <v>10302003</v>
+            <v>10103603</v>
           </cell>
-          <cell r="S890">
-            <v>6203003</v>
+          <cell r="S890" t="str">
+            <v>6@200303;0.01;0.03</v>
           </cell>
         </row>
         <row r="891">
           <cell r="C891">
-            <v>10302004</v>
+            <v>10201101</v>
           </cell>
           <cell r="S891">
-            <v>6204004</v>
+            <v>7102001</v>
           </cell>
         </row>
         <row r="892">
           <cell r="C892">
-            <v>10302005</v>
+            <v>10201102</v>
           </cell>
           <cell r="S892">
-            <v>6205004</v>
+            <v>7102002</v>
           </cell>
         </row>
         <row r="893">
           <cell r="C893">
-            <v>10302006</v>
+            <v>10201103</v>
           </cell>
           <cell r="S893">
-            <v>6206003</v>
+            <v>7102003</v>
           </cell>
         </row>
         <row r="894">
           <cell r="C894">
-            <v>10303001</v>
+            <v>10201104</v>
           </cell>
           <cell r="S894">
-            <v>6301003</v>
+            <v>7102004</v>
           </cell>
         </row>
         <row r="895">
           <cell r="C895">
-            <v>10303002</v>
+            <v>10201201</v>
           </cell>
           <cell r="S895">
-            <v>6302003</v>
+            <v>7103001</v>
           </cell>
         </row>
         <row r="896">
           <cell r="C896">
-            <v>10303003</v>
+            <v>10201202</v>
           </cell>
           <cell r="S896">
-            <v>6303003</v>
+            <v>7103002</v>
           </cell>
         </row>
         <row r="897">
           <cell r="C897">
-            <v>10303004</v>
+            <v>10201203</v>
           </cell>
           <cell r="S897">
-            <v>6304004</v>
+            <v>7103003</v>
           </cell>
         </row>
         <row r="898">
           <cell r="C898">
-            <v>10303005</v>
+            <v>10201204</v>
           </cell>
           <cell r="S898">
-            <v>6305004</v>
+            <v>7103004</v>
           </cell>
         </row>
         <row r="899">
           <cell r="C899">
-            <v>10303006</v>
+            <v>10202101</v>
           </cell>
           <cell r="S899">
-            <v>6306003</v>
+            <v>7202001</v>
           </cell>
         </row>
         <row r="900">
           <cell r="C900">
-            <v>11200000</v>
+            <v>10202102</v>
           </cell>
           <cell r="S900">
-            <v>500</v>
+            <v>7202002</v>
           </cell>
         </row>
         <row r="901">
           <cell r="C901">
-            <v>11200001</v>
+            <v>10202103</v>
           </cell>
           <cell r="S901">
-            <v>500</v>
+            <v>7202003</v>
           </cell>
         </row>
         <row r="902">
           <cell r="C902">
-            <v>11200002</v>
+            <v>10202104</v>
           </cell>
           <cell r="S902">
-            <v>500</v>
+            <v>7202004</v>
           </cell>
         </row>
         <row r="903">
           <cell r="C903">
-            <v>11200003</v>
+            <v>10202201</v>
           </cell>
           <cell r="S903">
-            <v>500</v>
+            <v>7203001</v>
           </cell>
         </row>
         <row r="904">
           <cell r="C904">
-            <v>11200010</v>
+            <v>10202202</v>
           </cell>
           <cell r="S904">
-            <v>500</v>
+            <v>7203002</v>
           </cell>
         </row>
         <row r="905">
           <cell r="C905">
-            <v>11300001</v>
+            <v>10202203</v>
           </cell>
-          <cell r="S905" t="str">
-            <v>1;3901</v>
+          <cell r="S905">
+            <v>7203003</v>
           </cell>
         </row>
         <row r="906">
           <cell r="C906">
-            <v>11300002</v>
+            <v>10202204</v>
           </cell>
-          <cell r="S906" t="str">
-            <v>1;3906</v>
+          <cell r="S906">
+            <v>7203004</v>
           </cell>
         </row>
         <row r="907">
           <cell r="C907">
-            <v>11300003</v>
+            <v>10203101</v>
           </cell>
-          <cell r="S907" t="str">
-            <v>1;3907</v>
+          <cell r="S907">
+            <v>7302001</v>
           </cell>
         </row>
         <row r="908">
           <cell r="C908">
-            <v>11300004</v>
+            <v>10203102</v>
           </cell>
-          <cell r="S908" t="str">
-            <v>1;3908</v>
+          <cell r="S908">
+            <v>7302002</v>
           </cell>
         </row>
         <row r="909">
           <cell r="C909">
-            <v>11300005</v>
+            <v>10203201</v>
           </cell>
-          <cell r="S909" t="str">
-            <v>1;3909</v>
+          <cell r="S909">
+            <v>7303001</v>
           </cell>
         </row>
         <row r="910">
           <cell r="C910">
-            <v>11300006</v>
+            <v>10203202</v>
           </cell>
-          <cell r="S910" t="str">
-            <v>1;3910</v>
+          <cell r="S910">
+            <v>7303002</v>
           </cell>
         </row>
         <row r="911">
           <cell r="C911">
-            <v>11300007</v>
+            <v>10301001</v>
           </cell>
-          <cell r="S911" t="str">
-            <v>2;3902</v>
+          <cell r="S911">
+            <v>6101003</v>
           </cell>
         </row>
         <row r="912">
           <cell r="C912">
-            <v>11300008</v>
+            <v>10301002</v>
           </cell>
-          <cell r="S912" t="str">
-            <v>2;3903</v>
+          <cell r="S912">
+            <v>6102003</v>
           </cell>
         </row>
         <row r="913">
           <cell r="C913">
-            <v>11300009</v>
+            <v>10301003</v>
           </cell>
-          <cell r="S913" t="str">
-            <v>2;3904</v>
+          <cell r="S913">
+            <v>6103003</v>
           </cell>
         </row>
         <row r="914">
           <cell r="C914">
-            <v>11300101</v>
+            <v>10301004</v>
           </cell>
-          <cell r="S914" t="str">
-            <v>1;3101</v>
+          <cell r="S914">
+            <v>6104004</v>
           </cell>
         </row>
         <row r="915">
           <cell r="C915">
-            <v>11300102</v>
+            <v>10301005</v>
           </cell>
-          <cell r="S915" t="str">
-            <v>1;3102</v>
+          <cell r="S915">
+            <v>6105004</v>
           </cell>
         </row>
         <row r="916">
           <cell r="C916">
-            <v>11300103</v>
+            <v>10301006</v>
           </cell>
-          <cell r="S916" t="str">
-            <v>1;3103</v>
+          <cell r="S916">
+            <v>6106003</v>
           </cell>
         </row>
         <row r="917">
           <cell r="C917">
-            <v>11300104</v>
+            <v>10302001</v>
           </cell>
-          <cell r="S917" t="str">
-            <v>1;3104</v>
+          <cell r="S917">
+            <v>6201003</v>
           </cell>
         </row>
         <row r="918">
           <cell r="C918">
-            <v>11300105</v>
+            <v>10302002</v>
           </cell>
-          <cell r="S918" t="str">
-            <v>1;3105</v>
+          <cell r="S918">
+            <v>6202003</v>
           </cell>
         </row>
         <row r="919">
           <cell r="C919">
-            <v>11300201</v>
+            <v>10302003</v>
           </cell>
-          <cell r="S919" t="str">
-            <v>1;3201</v>
+          <cell r="S919">
+            <v>6203003</v>
           </cell>
         </row>
         <row r="920">
           <cell r="C920">
-            <v>11300202</v>
+            <v>10302004</v>
           </cell>
-          <cell r="S920" t="str">
-            <v>1;3202</v>
+          <cell r="S920">
+            <v>6204004</v>
           </cell>
         </row>
         <row r="921">
           <cell r="C921">
-            <v>11300203</v>
+            <v>10302005</v>
           </cell>
-          <cell r="S921" t="str">
-            <v>1;3203</v>
+          <cell r="S921">
+            <v>6205004</v>
           </cell>
         </row>
         <row r="922">
           <cell r="C922">
-            <v>11300204</v>
+            <v>10302006</v>
           </cell>
-          <cell r="S922" t="str">
-            <v>1;3204</v>
+          <cell r="S922">
+            <v>6206003</v>
           </cell>
         </row>
         <row r="923">
           <cell r="C923">
-            <v>11300205</v>
+            <v>10303001</v>
           </cell>
-          <cell r="S923" t="str">
-            <v>1;3205</v>
+          <cell r="S923">
+            <v>6301003</v>
           </cell>
         </row>
         <row r="924">
           <cell r="C924">
-            <v>11300301</v>
+            <v>10303002</v>
           </cell>
-          <cell r="S924" t="str">
-            <v>1;3301</v>
+          <cell r="S924">
+            <v>6302003</v>
           </cell>
         </row>
         <row r="925">
           <cell r="C925">
-            <v>11300302</v>
+            <v>10303003</v>
           </cell>
-          <cell r="S925" t="str">
-            <v>1;3302</v>
+          <cell r="S925">
+            <v>6303003</v>
           </cell>
         </row>
         <row r="926">
           <cell r="C926">
-            <v>11300303</v>
+            <v>10303004</v>
           </cell>
-          <cell r="S926" t="str">
-            <v>1;3303</v>
+          <cell r="S926">
+            <v>6304004</v>
           </cell>
         </row>
         <row r="927">
           <cell r="C927">
-            <v>11300304</v>
+            <v>10303005</v>
           </cell>
-          <cell r="S927" t="str">
-            <v>1;3304</v>
+          <cell r="S927">
+            <v>6305004</v>
           </cell>
         </row>
         <row r="928">
           <cell r="C928">
-            <v>11300305</v>
+            <v>10303006</v>
           </cell>
-          <cell r="S928" t="str">
-            <v>1;3305</v>
+          <cell r="S928">
+            <v>6306003</v>
           </cell>
         </row>
         <row r="929">
           <cell r="C929">
-            <v>11300401</v>
+            <v>11200000</v>
           </cell>
-          <cell r="S929" t="str">
-            <v>1;3401</v>
+          <cell r="S929">
+            <v>500</v>
           </cell>
         </row>
         <row r="930">
           <cell r="C930">
-            <v>11300402</v>
+            <v>11200001</v>
           </cell>
-          <cell r="S930" t="str">
-            <v>1;3402</v>
+          <cell r="S930">
+            <v>500</v>
           </cell>
         </row>
         <row r="931">
           <cell r="C931">
-            <v>11300403</v>
+            <v>11200002</v>
           </cell>
-          <cell r="S931" t="str">
-            <v>1;3403</v>
+          <cell r="S931">
+            <v>500</v>
           </cell>
         </row>
         <row r="932">
           <cell r="C932">
-            <v>11300404</v>
+            <v>11200003</v>
           </cell>
-          <cell r="S932" t="str">
-            <v>1;3404</v>
+          <cell r="S932">
+            <v>500</v>
           </cell>
         </row>
         <row r="933">
           <cell r="C933">
-            <v>11300405</v>
+            <v>11200010</v>
           </cell>
-          <cell r="S933" t="str">
-            <v>1;3405</v>
+          <cell r="S933">
+            <v>500</v>
           </cell>
         </row>
         <row r="934">
           <cell r="C934">
-            <v>11300501</v>
+            <v>11200011</v>
           </cell>
-          <cell r="S934" t="str">
-            <v>1;3501</v>
+          <cell r="S934">
+            <v>500</v>
           </cell>
         </row>
         <row r="935">
           <cell r="C935">
-            <v>11300502</v>
+            <v>11300001</v>
           </cell>
           <cell r="S935" t="str">
-            <v>1;3502</v>
+            <v>1;3901</v>
           </cell>
         </row>
         <row r="936">
           <cell r="C936">
-            <v>11300503</v>
+            <v>11300002</v>
           </cell>
           <cell r="S936" t="str">
-            <v>1;3503</v>
+            <v>1;3906</v>
           </cell>
         </row>
         <row r="937">
           <cell r="C937">
-            <v>11300504</v>
+            <v>11300003</v>
           </cell>
           <cell r="S937" t="str">
-            <v>1;3504</v>
+            <v>1;3907</v>
           </cell>
         </row>
         <row r="938">
           <cell r="C938">
-            <v>11300505</v>
+            <v>11300004</v>
           </cell>
           <cell r="S938" t="str">
-            <v>1;3505</v>
+            <v>1;3908</v>
           </cell>
         </row>
         <row r="939">
           <cell r="C939">
-            <v>11300601</v>
+            <v>11300005</v>
           </cell>
           <cell r="S939" t="str">
-            <v>1;3601</v>
+            <v>1;3909</v>
           </cell>
         </row>
         <row r="940">
           <cell r="C940">
-            <v>11300602</v>
+            <v>11300006</v>
           </cell>
           <cell r="S940" t="str">
-            <v>1;3602</v>
+            <v>1;3910</v>
           </cell>
         </row>
         <row r="941">
           <cell r="C941">
-            <v>11300603</v>
+            <v>11300007</v>
           </cell>
           <cell r="S941" t="str">
-            <v>1;3603</v>
+            <v>2;3902</v>
           </cell>
         </row>
         <row r="942">
           <cell r="C942">
-            <v>11300604</v>
+            <v>11300008</v>
           </cell>
           <cell r="S942" t="str">
-            <v>1;3604</v>
+            <v>2;3903</v>
           </cell>
         </row>
         <row r="943">
           <cell r="C943">
-            <v>11300605</v>
+            <v>11300009</v>
           </cell>
           <cell r="S943" t="str">
-            <v>1;3605</v>
+            <v>2;3904</v>
           </cell>
         </row>
         <row r="944">
           <cell r="C944">
-            <v>11400101</v>
+            <v>11300101</v>
           </cell>
           <cell r="S944" t="str">
-            <v>1,30@1;202103,0.01,0.03</v>
+            <v>1;3101</v>
           </cell>
         </row>
         <row r="945">
           <cell r="C945">
-            <v>11400102</v>
+            <v>11300102</v>
           </cell>
           <cell r="S945" t="str">
-            <v>1,30@1;100203,100,200</v>
+            <v>1;3102</v>
           </cell>
         </row>
         <row r="946">
           <cell r="C946">
-            <v>11400103</v>
+            <v>11300103</v>
           </cell>
           <cell r="S946" t="str">
-            <v>1,30@2;62000001</v>
+            <v>1;3103</v>
           </cell>
         </row>
         <row r="947">
           <cell r="C947">
-            <v>11500101</v>
+            <v>11300104</v>
+          </cell>
+          <cell r="S947" t="str">
+            <v>1;3104</v>
           </cell>
         </row>
         <row r="948">
           <cell r="C948">
-            <v>11500102</v>
+            <v>11300105</v>
+          </cell>
+          <cell r="S948" t="str">
+            <v>1;3105</v>
           </cell>
         </row>
         <row r="949">
           <cell r="C949">
-            <v>11500103</v>
+            <v>11300201</v>
+          </cell>
+          <cell r="S949" t="str">
+            <v>1;3201</v>
           </cell>
         </row>
         <row r="950">
           <cell r="C950">
-            <v>11500201</v>
+            <v>11300202</v>
+          </cell>
+          <cell r="S950" t="str">
+            <v>1;3202</v>
           </cell>
         </row>
         <row r="951">
           <cell r="C951">
-            <v>11500202</v>
+            <v>11300203</v>
+          </cell>
+          <cell r="S951" t="str">
+            <v>1;3203</v>
           </cell>
         </row>
         <row r="952">
           <cell r="C952">
-            <v>11500203</v>
+            <v>11300204</v>
+          </cell>
+          <cell r="S952" t="str">
+            <v>1;3204</v>
           </cell>
         </row>
         <row r="953">
           <cell r="C953">
-            <v>11500301</v>
+            <v>11300205</v>
+          </cell>
+          <cell r="S953" t="str">
+            <v>1;3205</v>
           </cell>
         </row>
         <row r="954">
           <cell r="C954">
-            <v>11500302</v>
+            <v>11300301</v>
+          </cell>
+          <cell r="S954" t="str">
+            <v>1;3301</v>
           </cell>
         </row>
         <row r="955">
           <cell r="C955">
-            <v>11500303</v>
+            <v>11300302</v>
+          </cell>
+          <cell r="S955" t="str">
+            <v>1;3302</v>
           </cell>
         </row>
         <row r="956">
           <cell r="C956">
-            <v>11500401</v>
+            <v>11300303</v>
+          </cell>
+          <cell r="S956" t="str">
+            <v>1;3303</v>
           </cell>
         </row>
         <row r="957">
           <cell r="C957">
-            <v>11500402</v>
+            <v>11300304</v>
+          </cell>
+          <cell r="S957" t="str">
+            <v>1;3304</v>
           </cell>
         </row>
         <row r="958">
           <cell r="C958">
-            <v>11500403</v>
+            <v>11300305</v>
+          </cell>
+          <cell r="S958" t="str">
+            <v>1;3305</v>
           </cell>
         </row>
         <row r="959">
           <cell r="C959">
-            <v>11500501</v>
+            <v>11300401</v>
+          </cell>
+          <cell r="S959" t="str">
+            <v>1;3401</v>
           </cell>
         </row>
         <row r="960">
           <cell r="C960">
-            <v>11500502</v>
+            <v>11300402</v>
+          </cell>
+          <cell r="S960" t="str">
+            <v>1;3402</v>
           </cell>
         </row>
         <row r="961">
           <cell r="C961">
-            <v>11500503</v>
+            <v>11300403</v>
+          </cell>
+          <cell r="S961" t="str">
+            <v>1;3403</v>
           </cell>
         </row>
         <row r="962">
           <cell r="C962">
-            <v>11600101</v>
+            <v>11300404</v>
+          </cell>
+          <cell r="S962" t="str">
+            <v>1;3404</v>
           </cell>
         </row>
         <row r="963">
           <cell r="C963">
-            <v>11600102</v>
+            <v>11300405</v>
+          </cell>
+          <cell r="S963" t="str">
+            <v>1;3405</v>
           </cell>
         </row>
         <row r="964">
           <cell r="C964">
-            <v>11600103</v>
+            <v>11300501</v>
+          </cell>
+          <cell r="S964" t="str">
+            <v>1;3501</v>
           </cell>
         </row>
         <row r="965">
           <cell r="C965">
-            <v>11600201</v>
+            <v>11300502</v>
+          </cell>
+          <cell r="S965" t="str">
+            <v>1;3502</v>
           </cell>
         </row>
         <row r="966">
           <cell r="C966">
-            <v>11600202</v>
+            <v>11300503</v>
+          </cell>
+          <cell r="S966" t="str">
+            <v>1;3503</v>
           </cell>
         </row>
         <row r="967">
           <cell r="C967">
-            <v>11600203</v>
+            <v>11300504</v>
+          </cell>
+          <cell r="S967" t="str">
+            <v>1;3504</v>
           </cell>
         </row>
         <row r="968">
           <cell r="C968">
-            <v>11600301</v>
+            <v>11300505</v>
+          </cell>
+          <cell r="S968" t="str">
+            <v>1;3505</v>
           </cell>
         </row>
         <row r="969">
           <cell r="C969">
-            <v>11600302</v>
+            <v>11300601</v>
+          </cell>
+          <cell r="S969" t="str">
+            <v>1;3601</v>
           </cell>
         </row>
         <row r="970">
           <cell r="C970">
-            <v>11600303</v>
+            <v>11300602</v>
+          </cell>
+          <cell r="S970" t="str">
+            <v>1;3602</v>
           </cell>
         </row>
         <row r="971">
           <cell r="C971">
-            <v>11600401</v>
+            <v>11300603</v>
+          </cell>
+          <cell r="S971" t="str">
+            <v>1;3603</v>
           </cell>
         </row>
         <row r="972">
           <cell r="C972">
-            <v>11600402</v>
+            <v>11300604</v>
+          </cell>
+          <cell r="S972" t="str">
+            <v>1;3604</v>
           </cell>
         </row>
         <row r="973">
           <cell r="C973">
-            <v>11600403</v>
+            <v>11300605</v>
+          </cell>
+          <cell r="S973" t="str">
+            <v>1;3605</v>
           </cell>
         </row>
         <row r="974">
           <cell r="C974">
-            <v>11600501</v>
+            <v>11400101</v>
+          </cell>
+          <cell r="S974" t="str">
+            <v>1,30@1;202103,0.01,0.03</v>
           </cell>
         </row>
         <row r="975">
           <cell r="C975">
-            <v>11600502</v>
+            <v>11400102</v>
+          </cell>
+          <cell r="S975" t="str">
+            <v>1,30@1;100203,100,200</v>
           </cell>
         </row>
         <row r="976">
           <cell r="C976">
-            <v>11600503</v>
+            <v>11400103</v>
+          </cell>
+          <cell r="S976" t="str">
+            <v>1,30@2;62000001</v>
           </cell>
         </row>
         <row r="977">
           <cell r="C977">
-            <v>11600601</v>
+            <v>11500101</v>
           </cell>
         </row>
         <row r="978">
           <cell r="C978">
-            <v>11600602</v>
+            <v>11500102</v>
           </cell>
         </row>
         <row r="979">
           <cell r="C979">
-            <v>11600603</v>
+            <v>11500103</v>
           </cell>
         </row>
         <row r="980">
           <cell r="C980">
-            <v>11600701</v>
+            <v>11500201</v>
           </cell>
         </row>
         <row r="981">
           <cell r="C981">
-            <v>11600702</v>
+            <v>11500202</v>
           </cell>
         </row>
         <row r="982">
           <cell r="C982">
-            <v>11600703</v>
+            <v>11500203</v>
           </cell>
         </row>
         <row r="983">
           <cell r="C983">
-            <v>11600801</v>
+            <v>11500301</v>
           </cell>
         </row>
         <row r="984">
           <cell r="C984">
-            <v>11600802</v>
+            <v>11500302</v>
           </cell>
         </row>
         <row r="985">
           <cell r="C985">
-            <v>11600803</v>
+            <v>11500303</v>
           </cell>
         </row>
         <row r="986">
           <cell r="C986">
-            <v>11600901</v>
+            <v>11500401</v>
           </cell>
         </row>
         <row r="987">
           <cell r="C987">
-            <v>11600902</v>
+            <v>11500402</v>
           </cell>
         </row>
         <row r="988">
           <cell r="C988">
-            <v>11600903</v>
+            <v>11500403</v>
           </cell>
         </row>
         <row r="989">
           <cell r="C989">
-            <v>11610101</v>
+            <v>11500501</v>
           </cell>
         </row>
         <row r="990">
           <cell r="C990">
-            <v>11610102</v>
+            <v>11500502</v>
           </cell>
         </row>
         <row r="991">
           <cell r="C991">
-            <v>11610103</v>
+            <v>11500503</v>
           </cell>
         </row>
         <row r="992">
           <cell r="C992">
-            <v>11610201</v>
+            <v>11500601</v>
           </cell>
         </row>
         <row r="993">
           <cell r="C993">
-            <v>11610202</v>
+            <v>11500602</v>
           </cell>
         </row>
         <row r="994">
           <cell r="C994">
-            <v>11610203</v>
+            <v>11500603</v>
           </cell>
         </row>
         <row r="995">
           <cell r="C995">
-            <v>11610301</v>
+            <v>11600101</v>
           </cell>
         </row>
         <row r="996">
           <cell r="C996">
-            <v>11610302</v>
+            <v>11600102</v>
           </cell>
         </row>
         <row r="997">
           <cell r="C997">
-            <v>11610303</v>
+            <v>11600103</v>
           </cell>
         </row>
         <row r="998">
           <cell r="C998">
-            <v>11610401</v>
+            <v>11600201</v>
           </cell>
         </row>
         <row r="999">
           <cell r="C999">
-            <v>11610402</v>
+            <v>11600202</v>
           </cell>
         </row>
         <row r="1000">
           <cell r="C1000">
-            <v>11610403</v>
+            <v>11600203</v>
           </cell>
         </row>
         <row r="1001">
           <cell r="C1001">
-            <v>11610501</v>
+            <v>11600301</v>
           </cell>
         </row>
         <row r="1002">
           <cell r="C1002">
-            <v>11610502</v>
+            <v>11600302</v>
           </cell>
         </row>
         <row r="1003">
           <cell r="C1003">
-            <v>11610503</v>
+            <v>11600303</v>
           </cell>
         </row>
         <row r="1004">
           <cell r="C1004">
-            <v>11610601</v>
+            <v>11600401</v>
           </cell>
         </row>
         <row r="1005">
           <cell r="C1005">
-            <v>11610602</v>
+            <v>11600402</v>
           </cell>
         </row>
         <row r="1006">
           <cell r="C1006">
-            <v>11610603</v>
+            <v>11600403</v>
           </cell>
         </row>
         <row r="1007">
           <cell r="C1007">
-            <v>11610701</v>
+            <v>11600501</v>
           </cell>
         </row>
         <row r="1008">
           <cell r="C1008">
-            <v>11610702</v>
+            <v>11600502</v>
           </cell>
         </row>
         <row r="1009">
           <cell r="C1009">
-            <v>11610703</v>
+            <v>11600503</v>
           </cell>
         </row>
         <row r="1010">
           <cell r="C1010">
-            <v>13001001</v>
-          </cell>
-          <cell r="S1010">
-            <v>65001001</v>
+            <v>11600601</v>
           </cell>
         </row>
         <row r="1011">
           <cell r="C1011">
-            <v>13001002</v>
-          </cell>
-          <cell r="S1011">
-            <v>65001002</v>
+            <v>11600602</v>
           </cell>
         </row>
         <row r="1012">
           <cell r="C1012">
-            <v>13001003</v>
-          </cell>
-          <cell r="S1012">
-            <v>65001003</v>
+            <v>11600603</v>
           </cell>
         </row>
         <row r="1013">
           <cell r="C1013">
-            <v>13001004</v>
-          </cell>
-          <cell r="S1013">
-            <v>65001004</v>
+            <v>11600701</v>
           </cell>
         </row>
         <row r="1014">
           <cell r="C1014">
-            <v>13001005</v>
-          </cell>
-          <cell r="S1014">
-            <v>65001005</v>
+            <v>11600702</v>
           </cell>
         </row>
         <row r="1015">
           <cell r="C1015">
-            <v>13001006</v>
-          </cell>
-          <cell r="S1015">
-            <v>65001006</v>
+            <v>11600703</v>
           </cell>
         </row>
         <row r="1016">
           <cell r="C1016">
-            <v>13001101</v>
-          </cell>
-          <cell r="S1016">
-            <v>65001101</v>
+            <v>11600801</v>
           </cell>
         </row>
         <row r="1017">
           <cell r="C1017">
-            <v>13001102</v>
-          </cell>
-          <cell r="S1017">
-            <v>65001102</v>
+            <v>11600802</v>
           </cell>
         </row>
         <row r="1018">
           <cell r="C1018">
-            <v>13001103</v>
-          </cell>
-          <cell r="S1018">
-            <v>65001103</v>
+            <v>11600803</v>
           </cell>
         </row>
         <row r="1019">
           <cell r="C1019">
-            <v>13001104</v>
-          </cell>
-          <cell r="S1019">
-            <v>65001104</v>
+            <v>11600901</v>
           </cell>
         </row>
         <row r="1020">
           <cell r="C1020">
-            <v>13001105</v>
-          </cell>
-          <cell r="S1020">
-            <v>65001105</v>
+            <v>11600902</v>
           </cell>
         </row>
         <row r="1021">
           <cell r="C1021">
-            <v>13002001</v>
-          </cell>
-          <cell r="S1021">
-            <v>65002001</v>
+            <v>11600903</v>
           </cell>
         </row>
         <row r="1022">
           <cell r="C1022">
-            <v>13002002</v>
-          </cell>
-          <cell r="S1022">
-            <v>65002002</v>
+            <v>11610101</v>
           </cell>
         </row>
         <row r="1023">
           <cell r="C1023">
-            <v>13002003</v>
-          </cell>
-          <cell r="S1023">
-            <v>65002003</v>
+            <v>11610102</v>
           </cell>
         </row>
         <row r="1024">
           <cell r="C1024">
-            <v>13002004</v>
-          </cell>
-          <cell r="S1024">
-            <v>65002004</v>
+            <v>11610103</v>
           </cell>
         </row>
         <row r="1025">
           <cell r="C1025">
-            <v>13002005</v>
-          </cell>
-          <cell r="S1025">
-            <v>65002005</v>
+            <v>11610201</v>
           </cell>
         </row>
         <row r="1026">
           <cell r="C1026">
-            <v>13002006</v>
-          </cell>
-          <cell r="S1026">
-            <v>65002006</v>
+            <v>11610202</v>
           </cell>
         </row>
         <row r="1027">
           <cell r="C1027">
-            <v>13002101</v>
-          </cell>
-          <cell r="S1027">
-            <v>65002101</v>
+            <v>11610203</v>
           </cell>
         </row>
         <row r="1028">
           <cell r="C1028">
-            <v>13002102</v>
-          </cell>
-          <cell r="S1028">
-            <v>65002102</v>
+            <v>11610301</v>
           </cell>
         </row>
         <row r="1029">
           <cell r="C1029">
-            <v>13002103</v>
-          </cell>
-          <cell r="S1029">
-            <v>65002103</v>
+            <v>11610302</v>
           </cell>
         </row>
         <row r="1030">
           <cell r="C1030">
-            <v>13002104</v>
-          </cell>
-          <cell r="S1030">
-            <v>65002104</v>
+            <v>11610303</v>
           </cell>
         </row>
         <row r="1031">
           <cell r="C1031">
-            <v>13002105</v>
-          </cell>
-          <cell r="S1031">
-            <v>65002105</v>
+            <v>11610401</v>
           </cell>
         </row>
         <row r="1032">
           <cell r="C1032">
-            <v>13003001</v>
-          </cell>
-          <cell r="S1032">
-            <v>65003001</v>
+            <v>11610402</v>
           </cell>
         </row>
         <row r="1033">
           <cell r="C1033">
-            <v>13003002</v>
-          </cell>
-          <cell r="S1033">
-            <v>65003002</v>
+            <v>11610403</v>
           </cell>
         </row>
         <row r="1034">
           <cell r="C1034">
-            <v>13003003</v>
-          </cell>
-          <cell r="S1034">
-            <v>65003003</v>
+            <v>11610501</v>
           </cell>
         </row>
         <row r="1035">
           <cell r="C1035">
-            <v>13003004</v>
-          </cell>
-          <cell r="S1035">
-            <v>65003004</v>
+            <v>11610502</v>
           </cell>
         </row>
         <row r="1036">
           <cell r="C1036">
-            <v>13003005</v>
-          </cell>
-          <cell r="S1036">
-            <v>65003005</v>
+            <v>11610503</v>
           </cell>
         </row>
         <row r="1037">
           <cell r="C1037">
-            <v>13003006</v>
-          </cell>
-          <cell r="S1037">
-            <v>65003006</v>
+            <v>11610601</v>
           </cell>
         </row>
         <row r="1038">
           <cell r="C1038">
-            <v>13003101</v>
-          </cell>
-          <cell r="S1038">
-            <v>65003101</v>
+            <v>11610602</v>
           </cell>
         </row>
         <row r="1039">
           <cell r="C1039">
-            <v>13003102</v>
-          </cell>
-          <cell r="S1039">
-            <v>65003102</v>
+            <v>11610603</v>
           </cell>
         </row>
         <row r="1040">
           <cell r="C1040">
-            <v>13003103</v>
-          </cell>
-          <cell r="S1040">
-            <v>65003103</v>
+            <v>11610701</v>
           </cell>
         </row>
         <row r="1041">
           <cell r="C1041">
-            <v>13003104</v>
-          </cell>
-          <cell r="S1041">
-            <v>65003104</v>
+            <v>11610702</v>
           </cell>
         </row>
         <row r="1042">
           <cell r="C1042">
-            <v>13003105</v>
-          </cell>
-          <cell r="S1042">
-            <v>65003105</v>
+            <v>11610703</v>
           </cell>
         </row>
         <row r="1043">
           <cell r="C1043">
-            <v>13004001</v>
+            <v>13001001</v>
           </cell>
           <cell r="S1043">
-            <v>65004001</v>
+            <v>65001001</v>
           </cell>
         </row>
         <row r="1044">
           <cell r="C1044">
-            <v>13004002</v>
+            <v>13001002</v>
           </cell>
           <cell r="S1044">
-            <v>65004002</v>
+            <v>65001002</v>
           </cell>
         </row>
         <row r="1045">
           <cell r="C1045">
-            <v>13004003</v>
+            <v>13001003</v>
           </cell>
           <cell r="S1045">
-            <v>65004003</v>
+            <v>65001003</v>
           </cell>
         </row>
         <row r="1046">
           <cell r="C1046">
-            <v>13004004</v>
+            <v>13001004</v>
           </cell>
           <cell r="S1046">
-            <v>65004004</v>
+            <v>65001004</v>
           </cell>
         </row>
         <row r="1047">
           <cell r="C1047">
-            <v>13004005</v>
+            <v>13001005</v>
           </cell>
           <cell r="S1047">
-            <v>65004005</v>
+            <v>65001005</v>
           </cell>
         </row>
         <row r="1048">
           <cell r="C1048">
-            <v>13004006</v>
+            <v>13001006</v>
           </cell>
           <cell r="S1048">
-            <v>65004006</v>
+            <v>65001006</v>
           </cell>
         </row>
         <row r="1049">
           <cell r="C1049">
-            <v>13004101</v>
+            <v>13001101</v>
           </cell>
           <cell r="S1049">
-            <v>65004101</v>
+            <v>65001101</v>
           </cell>
         </row>
         <row r="1050">
           <cell r="C1050">
-            <v>13004102</v>
+            <v>13001102</v>
           </cell>
           <cell r="S1050">
-            <v>65004102</v>
+            <v>65001102</v>
           </cell>
         </row>
         <row r="1051">
           <cell r="C1051">
-            <v>13004103</v>
+            <v>13001103</v>
           </cell>
           <cell r="S1051">
-            <v>65004103</v>
+            <v>65001103</v>
           </cell>
         </row>
         <row r="1052">
           <cell r="C1052">
-            <v>13004104</v>
+            <v>13001104</v>
           </cell>
           <cell r="S1052">
-            <v>65004104</v>
+            <v>65001104</v>
           </cell>
         </row>
         <row r="1053">
           <cell r="C1053">
-            <v>13004105</v>
+            <v>13001105</v>
           </cell>
           <cell r="S1053">
-            <v>65004105</v>
+            <v>65001105</v>
           </cell>
         </row>
         <row r="1054">
           <cell r="C1054">
-            <v>13005001</v>
+            <v>13002001</v>
           </cell>
           <cell r="S1054">
-            <v>65005001</v>
+            <v>65002001</v>
           </cell>
         </row>
         <row r="1055">
           <cell r="C1055">
-            <v>13005002</v>
+            <v>13002002</v>
           </cell>
           <cell r="S1055">
-            <v>65005002</v>
+            <v>65002002</v>
           </cell>
         </row>
         <row r="1056">
           <cell r="C1056">
-            <v>13005003</v>
+            <v>13002003</v>
           </cell>
           <cell r="S1056">
-            <v>65005003</v>
+            <v>65002003</v>
           </cell>
         </row>
         <row r="1057">
           <cell r="C1057">
-            <v>13005004</v>
+            <v>13002004</v>
           </cell>
           <cell r="S1057">
-            <v>65005004</v>
+            <v>65002004</v>
           </cell>
         </row>
         <row r="1058">
           <cell r="C1058">
-            <v>13005005</v>
+            <v>13002005</v>
           </cell>
           <cell r="S1058">
-            <v>65005005</v>
+            <v>65002005</v>
           </cell>
         </row>
         <row r="1059">
           <cell r="C1059">
-            <v>13005006</v>
+            <v>13002006</v>
           </cell>
           <cell r="S1059">
-            <v>65005006</v>
+            <v>65002006</v>
           </cell>
         </row>
         <row r="1060">
           <cell r="C1060">
-            <v>13005101</v>
+            <v>13002101</v>
           </cell>
           <cell r="S1060">
-            <v>65005101</v>
+            <v>65002101</v>
           </cell>
         </row>
         <row r="1061">
           <cell r="C1061">
-            <v>13005102</v>
+            <v>13002102</v>
           </cell>
           <cell r="S1061">
-            <v>65005102</v>
+            <v>65002102</v>
           </cell>
         </row>
         <row r="1062">
           <cell r="C1062">
-            <v>13005103</v>
+            <v>13002103</v>
           </cell>
           <cell r="S1062">
-            <v>65005103</v>
+            <v>65002103</v>
           </cell>
         </row>
         <row r="1063">
           <cell r="C1063">
-            <v>13005104</v>
+            <v>13002104</v>
           </cell>
           <cell r="S1063">
-            <v>65005104</v>
+            <v>65002104</v>
           </cell>
         </row>
         <row r="1064">
           <cell r="C1064">
-            <v>13005105</v>
+            <v>13002105</v>
           </cell>
           <cell r="S1064">
-            <v>65005105</v>
+            <v>65002105</v>
           </cell>
         </row>
         <row r="1065">
           <cell r="C1065">
-            <v>13006001</v>
+            <v>13003001</v>
           </cell>
           <cell r="S1065">
-            <v>65006001</v>
+            <v>65003001</v>
           </cell>
         </row>
         <row r="1066">
           <cell r="C1066">
-            <v>13006002</v>
+            <v>13003002</v>
           </cell>
           <cell r="S1066">
-            <v>65006002</v>
+            <v>65003002</v>
           </cell>
         </row>
         <row r="1067">
           <cell r="C1067">
-            <v>13006003</v>
+            <v>13003003</v>
           </cell>
           <cell r="S1067">
-            <v>65006003</v>
+            <v>65003003</v>
           </cell>
         </row>
         <row r="1068">
           <cell r="C1068">
-            <v>13006004</v>
+            <v>13003004</v>
           </cell>
           <cell r="S1068">
-            <v>65006004</v>
+            <v>65003004</v>
           </cell>
         </row>
         <row r="1069">
           <cell r="C1069">
-            <v>13009001</v>
+            <v>13003005</v>
           </cell>
-          <cell r="S1069" t="str">
-            <v>4;20</v>
+          <cell r="S1069">
+            <v>65003005</v>
           </cell>
         </row>
         <row r="1070">
           <cell r="C1070">
-            <v>13009002</v>
+            <v>13003006</v>
           </cell>
-          <cell r="S1070" t="str">
-            <v>5;20</v>
+          <cell r="S1070">
+            <v>65003006</v>
           </cell>
         </row>
         <row r="1071">
           <cell r="C1071">
-            <v>14000001</v>
+            <v>13003101</v>
+          </cell>
+          <cell r="S1071">
+            <v>65003101</v>
           </cell>
         </row>
         <row r="1072">
           <cell r="C1072">
-            <v>14000002</v>
+            <v>13003102</v>
+          </cell>
+          <cell r="S1072">
+            <v>65003102</v>
           </cell>
         </row>
         <row r="1073">
           <cell r="C1073">
-            <v>14000003</v>
+            <v>13003103</v>
+          </cell>
+          <cell r="S1073">
+            <v>65003103</v>
           </cell>
         </row>
         <row r="1074">
           <cell r="C1074">
-            <v>14000004</v>
+            <v>13003104</v>
+          </cell>
+          <cell r="S1074">
+            <v>65003104</v>
           </cell>
         </row>
         <row r="1075">
           <cell r="C1075">
-            <v>14000005</v>
+            <v>13003105</v>
+          </cell>
+          <cell r="S1075">
+            <v>65003105</v>
           </cell>
         </row>
         <row r="1076">
           <cell r="C1076">
-            <v>14010001</v>
+            <v>13004001</v>
+          </cell>
+          <cell r="S1076">
+            <v>65004001</v>
           </cell>
         </row>
         <row r="1077">
           <cell r="C1077">
-            <v>14010002</v>
+            <v>13004002</v>
+          </cell>
+          <cell r="S1077">
+            <v>65004002</v>
           </cell>
         </row>
         <row r="1078">
           <cell r="C1078">
-            <v>14010003</v>
+            <v>13004003</v>
+          </cell>
+          <cell r="S1078">
+            <v>65004003</v>
           </cell>
         </row>
         <row r="1079">
           <cell r="C1079">
-            <v>14010004</v>
+            <v>13004004</v>
+          </cell>
+          <cell r="S1079">
+            <v>65004004</v>
           </cell>
         </row>
         <row r="1080">
           <cell r="C1080">
-            <v>14010005</v>
+            <v>13004005</v>
+          </cell>
+          <cell r="S1080">
+            <v>65004005</v>
           </cell>
         </row>
         <row r="1081">
           <cell r="C1081">
-            <v>14010006</v>
+            <v>13004006</v>
+          </cell>
+          <cell r="S1081">
+            <v>65004006</v>
           </cell>
         </row>
         <row r="1082">
           <cell r="C1082">
-            <v>14010007</v>
+            <v>13004101</v>
+          </cell>
+          <cell r="S1082">
+            <v>65004101</v>
           </cell>
         </row>
         <row r="1083">
           <cell r="C1083">
-            <v>14010008</v>
+            <v>13004102</v>
+          </cell>
+          <cell r="S1083">
+            <v>65004102</v>
           </cell>
         </row>
         <row r="1084">
           <cell r="C1084">
-            <v>14010009</v>
+            <v>13004103</v>
+          </cell>
+          <cell r="S1084">
+            <v>65004103</v>
           </cell>
         </row>
         <row r="1085">
           <cell r="C1085">
-            <v>14010010</v>
+            <v>13004104</v>
+          </cell>
+          <cell r="S1085">
+            <v>65004104</v>
           </cell>
         </row>
         <row r="1086">
           <cell r="C1086">
-            <v>14010011</v>
+            <v>13004105</v>
+          </cell>
+          <cell r="S1086">
+            <v>65004105</v>
           </cell>
         </row>
         <row r="1087">
           <cell r="C1087">
-            <v>14010012</v>
+            <v>13005001</v>
+          </cell>
+          <cell r="S1087">
+            <v>65005001</v>
           </cell>
         </row>
         <row r="1088">
           <cell r="C1088">
-            <v>14020001</v>
+            <v>13005002</v>
+          </cell>
+          <cell r="S1088">
+            <v>65005002</v>
           </cell>
         </row>
         <row r="1089">
           <cell r="C1089">
-            <v>14020002</v>
+            <v>13005003</v>
+          </cell>
+          <cell r="S1089">
+            <v>65005003</v>
           </cell>
         </row>
         <row r="1090">
           <cell r="C1090">
-            <v>14020003</v>
+            <v>13005004</v>
+          </cell>
+          <cell r="S1090">
+            <v>65005004</v>
           </cell>
         </row>
         <row r="1091">
           <cell r="C1091">
-            <v>14020004</v>
+            <v>13005005</v>
+          </cell>
+          <cell r="S1091">
+            <v>65005005</v>
           </cell>
         </row>
         <row r="1092">
           <cell r="C1092">
-            <v>14020005</v>
+            <v>13005006</v>
+          </cell>
+          <cell r="S1092">
+            <v>65005006</v>
           </cell>
         </row>
         <row r="1093">
           <cell r="C1093">
-            <v>14020006</v>
+            <v>13005101</v>
+          </cell>
+          <cell r="S1093">
+            <v>65005101</v>
           </cell>
         </row>
         <row r="1094">
           <cell r="C1094">
-            <v>14020007</v>
+            <v>13005102</v>
+          </cell>
+          <cell r="S1094">
+            <v>65005102</v>
           </cell>
         </row>
         <row r="1095">
           <cell r="C1095">
-            <v>14020008</v>
+            <v>13005103</v>
+          </cell>
+          <cell r="S1095">
+            <v>65005103</v>
           </cell>
         </row>
         <row r="1096">
           <cell r="C1096">
-            <v>14020009</v>
+            <v>13005104</v>
+          </cell>
+          <cell r="S1096">
+            <v>65005104</v>
           </cell>
         </row>
         <row r="1097">
           <cell r="C1097">
-            <v>14020010</v>
+            <v>13005105</v>
+          </cell>
+          <cell r="S1097">
+            <v>65005105</v>
           </cell>
         </row>
         <row r="1098">
           <cell r="C1098">
-            <v>14020011</v>
+            <v>13006001</v>
+          </cell>
+          <cell r="S1098">
+            <v>65006001</v>
           </cell>
         </row>
         <row r="1099">
           <cell r="C1099">
-            <v>14020012</v>
+            <v>13006002</v>
+          </cell>
+          <cell r="S1099">
+            <v>65006002</v>
           </cell>
         </row>
         <row r="1100">
           <cell r="C1100">
-            <v>14020013</v>
+            <v>13006003</v>
+          </cell>
+          <cell r="S1100">
+            <v>65006003</v>
           </cell>
         </row>
         <row r="1101">
           <cell r="C1101">
-            <v>14030001</v>
+            <v>13006004</v>
+          </cell>
+          <cell r="S1101">
+            <v>65006004</v>
           </cell>
         </row>
         <row r="1102">
           <cell r="C1102">
-            <v>14030002</v>
+            <v>13009001</v>
+          </cell>
+          <cell r="S1102" t="str">
+            <v>4;20</v>
           </cell>
         </row>
         <row r="1103">
           <cell r="C1103">
-            <v>14030003</v>
+            <v>13009002</v>
+          </cell>
+          <cell r="S1103" t="str">
+            <v>5;20</v>
           </cell>
         </row>
         <row r="1104">
           <cell r="C1104">
-            <v>14030004</v>
+            <v>14000001</v>
           </cell>
         </row>
         <row r="1105">
           <cell r="C1105">
-            <v>14030005</v>
+            <v>14000002</v>
           </cell>
         </row>
         <row r="1106">
           <cell r="C1106">
-            <v>14030006</v>
+            <v>14000003</v>
           </cell>
         </row>
         <row r="1107">
           <cell r="C1107">
-            <v>14030007</v>
+            <v>14000004</v>
           </cell>
         </row>
         <row r="1108">
           <cell r="C1108">
-            <v>14030008</v>
+            <v>14000005</v>
           </cell>
         </row>
         <row r="1109">
           <cell r="C1109">
-            <v>14030009</v>
+            <v>14010001</v>
           </cell>
         </row>
         <row r="1110">
           <cell r="C1110">
-            <v>14030010</v>
+            <v>14010002</v>
           </cell>
         </row>
         <row r="1111">
           <cell r="C1111">
-            <v>14030011</v>
+            <v>14010003</v>
           </cell>
         </row>
         <row r="1112">
           <cell r="C1112">
-            <v>14030012</v>
+            <v>14010004</v>
           </cell>
         </row>
         <row r="1113">
           <cell r="C1113">
-            <v>14030013</v>
+            <v>14010005</v>
           </cell>
         </row>
         <row r="1114">
           <cell r="C1114">
-            <v>14040001</v>
+            <v>14010006</v>
           </cell>
         </row>
         <row r="1115">
           <cell r="C1115">
-            <v>14040002</v>
+            <v>14010007</v>
           </cell>
         </row>
         <row r="1116">
           <cell r="C1116">
-            <v>14040003</v>
+            <v>14010008</v>
           </cell>
         </row>
         <row r="1117">
           <cell r="C1117">
-            <v>14040004</v>
+            <v>14010009</v>
           </cell>
         </row>
         <row r="1118">
           <cell r="C1118">
-            <v>14040005</v>
+            <v>14010010</v>
           </cell>
         </row>
         <row r="1119">
           <cell r="C1119">
-            <v>14040006</v>
+            <v>14010011</v>
           </cell>
         </row>
         <row r="1120">
           <cell r="C1120">
-            <v>14040007</v>
+            <v>14010012</v>
           </cell>
         </row>
         <row r="1121">
           <cell r="C1121">
-            <v>14040008</v>
+            <v>14020001</v>
           </cell>
         </row>
         <row r="1122">
           <cell r="C1122">
-            <v>14040009</v>
+            <v>14020002</v>
           </cell>
         </row>
         <row r="1123">
           <cell r="C1123">
-            <v>14040010</v>
+            <v>14020003</v>
           </cell>
         </row>
         <row r="1124">
           <cell r="C1124">
-            <v>14040011</v>
+            <v>14020004</v>
           </cell>
         </row>
         <row r="1125">
           <cell r="C1125">
-            <v>14040012</v>
+            <v>14020005</v>
           </cell>
         </row>
         <row r="1126">
           <cell r="C1126">
-            <v>14050001</v>
+            <v>14020006</v>
           </cell>
         </row>
         <row r="1127">
           <cell r="C1127">
-            <v>14050002</v>
+            <v>14020007</v>
           </cell>
         </row>
         <row r="1128">
           <cell r="C1128">
-            <v>14050003</v>
+            <v>14020008</v>
           </cell>
         </row>
         <row r="1129">
           <cell r="C1129">
-            <v>14050004</v>
+            <v>14020009</v>
           </cell>
         </row>
         <row r="1130">
           <cell r="C1130">
-            <v>14050005</v>
+            <v>14020010</v>
           </cell>
         </row>
         <row r="1131">
           <cell r="C1131">
-            <v>14050006</v>
+            <v>14020011</v>
           </cell>
         </row>
         <row r="1132">
           <cell r="C1132">
-            <v>14050007</v>
+            <v>14020012</v>
           </cell>
         </row>
         <row r="1133">
           <cell r="C1133">
-            <v>14050008</v>
+            <v>14020013</v>
           </cell>
         </row>
         <row r="1134">
           <cell r="C1134">
-            <v>14050009</v>
+            <v>14030001</v>
           </cell>
         </row>
         <row r="1135">
           <cell r="C1135">
-            <v>14050010</v>
+            <v>14030002</v>
           </cell>
         </row>
         <row r="1136">
           <cell r="C1136">
-            <v>14050011</v>
+            <v>14030003</v>
           </cell>
         </row>
         <row r="1137">
           <cell r="C1137">
-            <v>14050012</v>
+            <v>14030004</v>
           </cell>
         </row>
         <row r="1138">
           <cell r="C1138">
-            <v>14060001</v>
+            <v>14030005</v>
           </cell>
         </row>
         <row r="1139">
           <cell r="C1139">
-            <v>14060002</v>
+            <v>14030006</v>
           </cell>
         </row>
         <row r="1140">
           <cell r="C1140">
-            <v>14060003</v>
+            <v>14030007</v>
           </cell>
         </row>
         <row r="1141">
           <cell r="C1141">
-            <v>14060004</v>
+            <v>14030008</v>
           </cell>
         </row>
         <row r="1142">
           <cell r="C1142">
-            <v>14060005</v>
+            <v>14030009</v>
           </cell>
         </row>
         <row r="1143">
           <cell r="C1143">
-            <v>14060006</v>
+            <v>14030010</v>
           </cell>
         </row>
         <row r="1144">
           <cell r="C1144">
-            <v>14070001</v>
+            <v>14030011</v>
           </cell>
         </row>
         <row r="1145">
           <cell r="C1145">
-            <v>14070002</v>
+            <v>14030012</v>
           </cell>
         </row>
         <row r="1146">
           <cell r="C1146">
-            <v>14070003</v>
+            <v>14030013</v>
           </cell>
         </row>
         <row r="1147">
           <cell r="C1147">
-            <v>14070004</v>
+            <v>14040001</v>
           </cell>
         </row>
         <row r="1148">
           <cell r="C1148">
-            <v>14080001</v>
+            <v>14040002</v>
           </cell>
         </row>
         <row r="1149">
           <cell r="C1149">
-            <v>14080002</v>
+            <v>14040003</v>
           </cell>
         </row>
         <row r="1150">
           <cell r="C1150">
-            <v>14080003</v>
+            <v>14040004</v>
           </cell>
         </row>
         <row r="1151">
           <cell r="C1151">
-            <v>14080004</v>
+            <v>14040005</v>
           </cell>
         </row>
         <row r="1152">
           <cell r="C1152">
-            <v>14090001</v>
+            <v>14040006</v>
           </cell>
         </row>
         <row r="1153">
           <cell r="C1153">
-            <v>14090002</v>
+            <v>14040007</v>
           </cell>
         </row>
         <row r="1154">
           <cell r="C1154">
-            <v>14090003</v>
+            <v>14040008</v>
           </cell>
         </row>
         <row r="1155">
           <cell r="C1155">
-            <v>14090004</v>
+            <v>14040009</v>
           </cell>
         </row>
         <row r="1156">
           <cell r="C1156">
-            <v>14100001</v>
+            <v>14040010</v>
           </cell>
         </row>
         <row r="1157">
           <cell r="C1157">
-            <v>14100002</v>
+            <v>14040011</v>
           </cell>
         </row>
         <row r="1158">
           <cell r="C1158">
-            <v>14100003</v>
+            <v>14040012</v>
           </cell>
         </row>
         <row r="1159">
           <cell r="C1159">
-            <v>14100004</v>
+            <v>14050001</v>
           </cell>
         </row>
         <row r="1160">
           <cell r="C1160">
-            <v>14100005</v>
+            <v>14050002</v>
           </cell>
         </row>
         <row r="1161">
           <cell r="C1161">
-            <v>14100006</v>
+            <v>14050003</v>
           </cell>
         </row>
         <row r="1162">
           <cell r="C1162">
-            <v>14100007</v>
+            <v>14050004</v>
           </cell>
         </row>
         <row r="1163">
           <cell r="C1163">
-            <v>14100008</v>
+            <v>14050005</v>
           </cell>
         </row>
         <row r="1164">
           <cell r="C1164">
-            <v>14100011</v>
+            <v>14050006</v>
           </cell>
         </row>
         <row r="1165">
           <cell r="C1165">
-            <v>14100012</v>
+            <v>14050007</v>
           </cell>
         </row>
         <row r="1166">
           <cell r="C1166">
-            <v>14100021</v>
+            <v>14050008</v>
           </cell>
         </row>
         <row r="1167">
           <cell r="C1167">
-            <v>14100022</v>
+            <v>14050009</v>
           </cell>
         </row>
         <row r="1168">
           <cell r="C1168">
-            <v>14100101</v>
+            <v>14050010</v>
           </cell>
         </row>
         <row r="1169">
           <cell r="C1169">
-            <v>14100102</v>
+            <v>14050011</v>
           </cell>
         </row>
         <row r="1170">
           <cell r="C1170">
-            <v>14100103</v>
+            <v>14050012</v>
           </cell>
         </row>
         <row r="1171">
           <cell r="C1171">
-            <v>14100104</v>
+            <v>14060001</v>
           </cell>
         </row>
         <row r="1172">
           <cell r="C1172">
-            <v>14100105</v>
+            <v>14060002</v>
           </cell>
         </row>
         <row r="1173">
           <cell r="C1173">
-            <v>14100106</v>
+            <v>14060003</v>
           </cell>
         </row>
         <row r="1174">
           <cell r="C1174">
-            <v>14100107</v>
+            <v>14060004</v>
           </cell>
         </row>
         <row r="1175">
           <cell r="C1175">
-            <v>14100108</v>
+            <v>14060005</v>
           </cell>
         </row>
         <row r="1176">
           <cell r="C1176">
-            <v>14100111</v>
+            <v>14060006</v>
           </cell>
         </row>
         <row r="1177">
           <cell r="C1177">
-            <v>14100112</v>
+            <v>14070001</v>
           </cell>
         </row>
         <row r="1178">
           <cell r="C1178">
-            <v>14100121</v>
+            <v>14070002</v>
           </cell>
         </row>
         <row r="1179">
           <cell r="C1179">
-            <v>14100122</v>
+            <v>14070003</v>
           </cell>
         </row>
         <row r="1180">
           <cell r="C1180">
-            <v>14100201</v>
+            <v>14070004</v>
           </cell>
         </row>
         <row r="1181">
           <cell r="C1181">
-            <v>14100202</v>
+            <v>14080001</v>
           </cell>
         </row>
         <row r="1182">
           <cell r="C1182">
-            <v>14100203</v>
+            <v>14080002</v>
           </cell>
         </row>
         <row r="1183">
           <cell r="C1183">
-            <v>14100204</v>
+            <v>14080003</v>
           </cell>
         </row>
         <row r="1184">
           <cell r="C1184">
-            <v>14100211</v>
+            <v>14080004</v>
           </cell>
         </row>
         <row r="1185">
           <cell r="C1185">
-            <v>14100221</v>
+            <v>14090001</v>
           </cell>
         </row>
         <row r="1186">
           <cell r="C1186">
-            <v>14110001</v>
+            <v>14090002</v>
           </cell>
         </row>
         <row r="1187">
           <cell r="C1187">
-            <v>14110002</v>
+            <v>14090003</v>
           </cell>
         </row>
         <row r="1188">
           <cell r="C1188">
-            <v>14110003</v>
+            <v>14090004</v>
           </cell>
         </row>
         <row r="1189">
           <cell r="C1189">
-            <v>14110004</v>
+            <v>14100001</v>
           </cell>
         </row>
         <row r="1190">
           <cell r="C1190">
-            <v>14110005</v>
+            <v>14100002</v>
           </cell>
         </row>
         <row r="1191">
           <cell r="C1191">
-            <v>14110006</v>
+            <v>14100003</v>
           </cell>
         </row>
         <row r="1192">
           <cell r="C1192">
-            <v>14110007</v>
+            <v>14100004</v>
           </cell>
         </row>
         <row r="1193">
           <cell r="C1193">
-            <v>14110008</v>
+            <v>14100005</v>
           </cell>
         </row>
         <row r="1194">
           <cell r="C1194">
-            <v>14110009</v>
+            <v>14100006</v>
           </cell>
         </row>
         <row r="1195">
           <cell r="C1195">
-            <v>14110010</v>
+            <v>14100007</v>
           </cell>
         </row>
         <row r="1196">
           <cell r="C1196">
-            <v>14110011</v>
+            <v>14100008</v>
           </cell>
         </row>
         <row r="1197">
           <cell r="C1197">
-            <v>14110012</v>
+            <v>14100011</v>
           </cell>
         </row>
         <row r="1198">
           <cell r="C1198">
-            <v>14110021</v>
+            <v>14100012</v>
           </cell>
         </row>
         <row r="1199">
           <cell r="C1199">
-            <v>14110022</v>
+            <v>14100021</v>
           </cell>
         </row>
         <row r="1200">
           <cell r="C1200">
-            <v>14110023</v>
+            <v>14100022</v>
           </cell>
         </row>
         <row r="1201">
           <cell r="C1201">
-            <v>15201001</v>
+            <v>14100101</v>
           </cell>
         </row>
         <row r="1202">
           <cell r="C1202">
-            <v>15201002</v>
+            <v>14100102</v>
           </cell>
         </row>
         <row r="1203">
           <cell r="C1203">
-            <v>15201003</v>
+            <v>14100103</v>
           </cell>
         </row>
         <row r="1204">
           <cell r="C1204">
-            <v>15201004</v>
+            <v>14100104</v>
           </cell>
         </row>
         <row r="1205">
           <cell r="C1205">
-            <v>15201005</v>
+            <v>14100105</v>
           </cell>
         </row>
         <row r="1206">
           <cell r="C1206">
-            <v>15201006</v>
+            <v>14100106</v>
           </cell>
         </row>
         <row r="1207">
           <cell r="C1207">
-            <v>15202001</v>
+            <v>14100107</v>
           </cell>
         </row>
         <row r="1208">
           <cell r="C1208">
-            <v>15202002</v>
+            <v>14100108</v>
           </cell>
         </row>
         <row r="1209">
           <cell r="C1209">
-            <v>15202003</v>
+            <v>14100111</v>
           </cell>
         </row>
         <row r="1210">
           <cell r="C1210">
-            <v>15202004</v>
+            <v>14100112</v>
           </cell>
         </row>
         <row r="1211">
           <cell r="C1211">
-            <v>15202005</v>
+            <v>14100121</v>
           </cell>
         </row>
         <row r="1212">
           <cell r="C1212">
-            <v>15202006</v>
+            <v>14100122</v>
           </cell>
         </row>
         <row r="1213">
           <cell r="C1213">
-            <v>15203001</v>
+            <v>14100201</v>
           </cell>
         </row>
         <row r="1214">
           <cell r="C1214">
-            <v>15203002</v>
+            <v>14100202</v>
           </cell>
         </row>
         <row r="1215">
           <cell r="C1215">
-            <v>15203003</v>
+            <v>14100203</v>
           </cell>
         </row>
         <row r="1216">
           <cell r="C1216">
-            <v>15203004</v>
+            <v>14100204</v>
           </cell>
         </row>
         <row r="1217">
           <cell r="C1217">
-            <v>15203005</v>
+            <v>14100211</v>
           </cell>
         </row>
         <row r="1218">
           <cell r="C1218">
-            <v>15203006</v>
+            <v>14100221</v>
           </cell>
         </row>
         <row r="1219">
           <cell r="C1219">
-            <v>15204001</v>
+            <v>14110001</v>
           </cell>
         </row>
         <row r="1220">
           <cell r="C1220">
-            <v>15204002</v>
+            <v>14110002</v>
           </cell>
         </row>
         <row r="1221">
           <cell r="C1221">
-            <v>15204003</v>
+            <v>14110003</v>
           </cell>
         </row>
         <row r="1222">
           <cell r="C1222">
-            <v>15204004</v>
+            <v>14110004</v>
           </cell>
         </row>
         <row r="1223">
           <cell r="C1223">
-            <v>15204005</v>
+            <v>14110005</v>
           </cell>
         </row>
         <row r="1224">
           <cell r="C1224">
-            <v>15204006</v>
+            <v>14110006</v>
           </cell>
         </row>
         <row r="1225">
           <cell r="C1225">
-            <v>15205001</v>
+            <v>14110007</v>
           </cell>
         </row>
         <row r="1226">
           <cell r="C1226">
-            <v>15205002</v>
+            <v>14110008</v>
           </cell>
         </row>
         <row r="1227">
           <cell r="C1227">
-            <v>15205003</v>
+            <v>14110009</v>
           </cell>
         </row>
         <row r="1228">
           <cell r="C1228">
-            <v>15205004</v>
+            <v>14110010</v>
           </cell>
         </row>
         <row r="1229">
           <cell r="C1229">
-            <v>15205005</v>
+            <v>14110011</v>
           </cell>
         </row>
         <row r="1230">
           <cell r="C1230">
-            <v>15205006</v>
+            <v>14110012</v>
           </cell>
         </row>
         <row r="1231">
           <cell r="C1231">
-            <v>15205007</v>
+            <v>14110021</v>
           </cell>
         </row>
         <row r="1232">
           <cell r="C1232">
-            <v>15206001</v>
+            <v>14110022</v>
           </cell>
         </row>
         <row r="1233">
           <cell r="C1233">
-            <v>15206002</v>
+            <v>14110023</v>
           </cell>
         </row>
         <row r="1234">
           <cell r="C1234">
-            <v>15206003</v>
+            <v>15201001</v>
           </cell>
         </row>
         <row r="1235">
           <cell r="C1235">
-            <v>15207001</v>
+            <v>15201002</v>
           </cell>
         </row>
         <row r="1236">
           <cell r="C1236">
-            <v>15207002</v>
+            <v>15201003</v>
           </cell>
         </row>
         <row r="1237">
           <cell r="C1237">
-            <v>15207003</v>
+            <v>15201004</v>
           </cell>
         </row>
         <row r="1238">
           <cell r="C1238">
-            <v>15208001</v>
+            <v>15201005</v>
           </cell>
         </row>
         <row r="1239">
           <cell r="C1239">
-            <v>15208002</v>
+            <v>15201006</v>
           </cell>
         </row>
         <row r="1240">
           <cell r="C1240">
-            <v>15208003</v>
+            <v>15202001</v>
           </cell>
         </row>
         <row r="1241">
           <cell r="C1241">
-            <v>15209001</v>
+            <v>15202002</v>
           </cell>
         </row>
         <row r="1242">
           <cell r="C1242">
-            <v>15209002</v>
+            <v>15202003</v>
           </cell>
         </row>
         <row r="1243">
           <cell r="C1243">
-            <v>15210001</v>
+            <v>15202004</v>
           </cell>
         </row>
         <row r="1244">
           <cell r="C1244">
-            <v>15210002</v>
+            <v>15202005</v>
           </cell>
         </row>
         <row r="1245">
           <cell r="C1245">
-            <v>15210003</v>
+            <v>15202006</v>
           </cell>
         </row>
         <row r="1246">
           <cell r="C1246">
-            <v>15210004</v>
+            <v>15203001</v>
           </cell>
         </row>
         <row r="1247">
           <cell r="C1247">
-            <v>15210011</v>
+            <v>15203002</v>
           </cell>
         </row>
         <row r="1248">
           <cell r="C1248">
-            <v>15210012</v>
+            <v>15203003</v>
           </cell>
         </row>
         <row r="1249">
           <cell r="C1249">
-            <v>15210101</v>
+            <v>15203004</v>
           </cell>
         </row>
         <row r="1250">
           <cell r="C1250">
-            <v>15210102</v>
+            <v>15203005</v>
           </cell>
         </row>
         <row r="1251">
           <cell r="C1251">
-            <v>15210103</v>
+            <v>15203006</v>
           </cell>
         </row>
         <row r="1252">
           <cell r="C1252">
-            <v>15210104</v>
+            <v>15204001</v>
           </cell>
         </row>
         <row r="1253">
           <cell r="C1253">
-            <v>15210111</v>
+            <v>15204002</v>
           </cell>
         </row>
         <row r="1254">
           <cell r="C1254">
-            <v>15210112</v>
+            <v>15204003</v>
           </cell>
         </row>
         <row r="1255">
           <cell r="C1255">
-            <v>15210201</v>
+            <v>15204004</v>
           </cell>
         </row>
         <row r="1256">
           <cell r="C1256">
-            <v>15210202</v>
+            <v>15204005</v>
           </cell>
         </row>
         <row r="1257">
           <cell r="C1257">
-            <v>15210211</v>
+            <v>15204006</v>
           </cell>
         </row>
         <row r="1258">
           <cell r="C1258">
-            <v>15211001</v>
+            <v>15205001</v>
           </cell>
         </row>
         <row r="1259">
           <cell r="C1259">
-            <v>15211002</v>
+            <v>15205002</v>
           </cell>
         </row>
         <row r="1260">
           <cell r="C1260">
-            <v>15211003</v>
+            <v>15205003</v>
           </cell>
         </row>
         <row r="1261">
           <cell r="C1261">
-            <v>15211004</v>
+            <v>15205004</v>
           </cell>
         </row>
         <row r="1262">
           <cell r="C1262">
-            <v>15211005</v>
+            <v>15205005</v>
           </cell>
         </row>
         <row r="1263">
           <cell r="C1263">
-            <v>15211006</v>
+            <v>15205006</v>
           </cell>
         </row>
         <row r="1264">
           <cell r="C1264">
-            <v>15211011</v>
+            <v>15205007</v>
           </cell>
         </row>
         <row r="1265">
           <cell r="C1265">
-            <v>15211012</v>
+            <v>15206001</v>
           </cell>
         </row>
         <row r="1266">
           <cell r="C1266">
-            <v>15211013</v>
+            <v>15206002</v>
           </cell>
         </row>
         <row r="1267">
           <cell r="C1267">
-            <v>15301001</v>
+            <v>15206003</v>
           </cell>
         </row>
         <row r="1268">
           <cell r="C1268">
-            <v>15301002</v>
+            <v>15207001</v>
           </cell>
         </row>
         <row r="1269">
           <cell r="C1269">
-            <v>15301003</v>
+            <v>15207002</v>
           </cell>
         </row>
         <row r="1270">
           <cell r="C1270">
-            <v>15301004</v>
+            <v>15207003</v>
           </cell>
         </row>
         <row r="1271">
           <cell r="C1271">
-            <v>15301005</v>
+            <v>15208001</v>
           </cell>
         </row>
         <row r="1272">
           <cell r="C1272">
-            <v>15301006</v>
+            <v>15208002</v>
           </cell>
         </row>
         <row r="1273">
           <cell r="C1273">
-            <v>15302001</v>
+            <v>15208003</v>
           </cell>
         </row>
         <row r="1274">
           <cell r="C1274">
-            <v>15302002</v>
+            <v>15209001</v>
           </cell>
         </row>
         <row r="1275">
           <cell r="C1275">
-            <v>15302003</v>
+            <v>15209002</v>
           </cell>
         </row>
         <row r="1276">
           <cell r="C1276">
-            <v>15302004</v>
+            <v>15210001</v>
           </cell>
         </row>
         <row r="1277">
           <cell r="C1277">
-            <v>15302005</v>
+            <v>15210002</v>
           </cell>
         </row>
         <row r="1278">
           <cell r="C1278">
-            <v>15302006</v>
+            <v>15210003</v>
           </cell>
         </row>
         <row r="1279">
           <cell r="C1279">
-            <v>15302007</v>
+            <v>15210004</v>
           </cell>
         </row>
         <row r="1280">
           <cell r="C1280">
-            <v>15303001</v>
+            <v>15210011</v>
           </cell>
         </row>
         <row r="1281">
           <cell r="C1281">
-            <v>15303002</v>
+            <v>15210012</v>
           </cell>
         </row>
         <row r="1282">
           <cell r="C1282">
-            <v>15303003</v>
+            <v>15210101</v>
           </cell>
         </row>
         <row r="1283">
           <cell r="C1283">
-            <v>15303004</v>
+            <v>15210102</v>
           </cell>
         </row>
         <row r="1284">
           <cell r="C1284">
-            <v>15303005</v>
+            <v>15210103</v>
           </cell>
         </row>
         <row r="1285">
           <cell r="C1285">
-            <v>15303006</v>
+            <v>15210104</v>
           </cell>
         </row>
         <row r="1286">
           <cell r="C1286">
-            <v>15304001</v>
+            <v>15210111</v>
           </cell>
         </row>
         <row r="1287">
           <cell r="C1287">
-            <v>15304002</v>
+            <v>15210112</v>
           </cell>
         </row>
         <row r="1288">
           <cell r="C1288">
-            <v>15304003</v>
+            <v>15210201</v>
           </cell>
         </row>
         <row r="1289">
           <cell r="C1289">
-            <v>15304004</v>
+            <v>15210202</v>
           </cell>
         </row>
         <row r="1290">
           <cell r="C1290">
-            <v>15304005</v>
+            <v>15210211</v>
           </cell>
         </row>
         <row r="1291">
           <cell r="C1291">
-            <v>15304006</v>
+            <v>15211001</v>
           </cell>
         </row>
         <row r="1292">
           <cell r="C1292">
-            <v>15305001</v>
+            <v>15211002</v>
           </cell>
         </row>
         <row r="1293">
           <cell r="C1293">
-            <v>15305002</v>
+            <v>15211003</v>
           </cell>
         </row>
         <row r="1294">
           <cell r="C1294">
-            <v>15305003</v>
+            <v>15211004</v>
           </cell>
         </row>
         <row r="1295">
           <cell r="C1295">
-            <v>15305004</v>
+            <v>15211005</v>
           </cell>
         </row>
         <row r="1296">
           <cell r="C1296">
-            <v>15305005</v>
+            <v>15211006</v>
           </cell>
         </row>
         <row r="1297">
           <cell r="C1297">
-            <v>15305006</v>
+            <v>15211011</v>
           </cell>
         </row>
         <row r="1298">
           <cell r="C1298">
-            <v>15306001</v>
+            <v>15211012</v>
           </cell>
         </row>
         <row r="1299">
           <cell r="C1299">
-            <v>15306002</v>
+            <v>15211013</v>
           </cell>
         </row>
         <row r="1300">
           <cell r="C1300">
-            <v>15306003</v>
+            <v>15301001</v>
           </cell>
         </row>
         <row r="1301">
           <cell r="C1301">
-            <v>15307001</v>
+            <v>15301002</v>
           </cell>
         </row>
         <row r="1302">
           <cell r="C1302">
-            <v>15307002</v>
+            <v>15301003</v>
           </cell>
         </row>
         <row r="1303">
           <cell r="C1303">
-            <v>15308001</v>
+            <v>15301004</v>
           </cell>
         </row>
         <row r="1304">
           <cell r="C1304">
-            <v>15308002</v>
+            <v>15301005</v>
           </cell>
         </row>
         <row r="1305">
           <cell r="C1305">
-            <v>15308003</v>
+            <v>15301006</v>
           </cell>
         </row>
         <row r="1306">
           <cell r="C1306">
-            <v>15308004</v>
+            <v>15302001</v>
           </cell>
         </row>
         <row r="1307">
           <cell r="C1307">
-            <v>15309001</v>
+            <v>15302002</v>
           </cell>
         </row>
         <row r="1308">
           <cell r="C1308">
-            <v>15309002</v>
+            <v>15302003</v>
           </cell>
         </row>
         <row r="1309">
           <cell r="C1309">
-            <v>15309003</v>
+            <v>15302004</v>
           </cell>
         </row>
         <row r="1310">
           <cell r="C1310">
-            <v>15310001</v>
+            <v>15302005</v>
           </cell>
         </row>
         <row r="1311">
           <cell r="C1311">
-            <v>15310002</v>
+            <v>15302006</v>
           </cell>
         </row>
         <row r="1312">
           <cell r="C1312">
-            <v>15310003</v>
+            <v>15302007</v>
           </cell>
         </row>
         <row r="1313">
           <cell r="C1313">
-            <v>15310004</v>
+            <v>15303001</v>
           </cell>
         </row>
         <row r="1314">
           <cell r="C1314">
-            <v>15310011</v>
+            <v>15303002</v>
           </cell>
         </row>
         <row r="1315">
           <cell r="C1315">
-            <v>15310012</v>
+            <v>15303003</v>
           </cell>
         </row>
         <row r="1316">
           <cell r="C1316">
-            <v>15310101</v>
+            <v>15303004</v>
           </cell>
         </row>
         <row r="1317">
           <cell r="C1317">
-            <v>15310102</v>
+            <v>15303005</v>
           </cell>
         </row>
         <row r="1318">
           <cell r="C1318">
-            <v>15310103</v>
+            <v>15303006</v>
           </cell>
         </row>
         <row r="1319">
           <cell r="C1319">
-            <v>15310104</v>
+            <v>15304001</v>
           </cell>
         </row>
         <row r="1320">
           <cell r="C1320">
-            <v>15310111</v>
+            <v>15304002</v>
           </cell>
         </row>
         <row r="1321">
           <cell r="C1321">
-            <v>15310112</v>
+            <v>15304003</v>
           </cell>
         </row>
         <row r="1322">
           <cell r="C1322">
-            <v>15310201</v>
+            <v>15304004</v>
           </cell>
         </row>
         <row r="1323">
           <cell r="C1323">
-            <v>15310202</v>
+            <v>15304005</v>
           </cell>
         </row>
         <row r="1324">
           <cell r="C1324">
-            <v>15310211</v>
+            <v>15304006</v>
           </cell>
         </row>
         <row r="1325">
           <cell r="C1325">
-            <v>15311001</v>
+            <v>15305001</v>
           </cell>
         </row>
         <row r="1326">
           <cell r="C1326">
-            <v>15311002</v>
+            <v>15305002</v>
           </cell>
         </row>
         <row r="1327">
           <cell r="C1327">
-            <v>15311003</v>
+            <v>15305003</v>
           </cell>
         </row>
         <row r="1328">
           <cell r="C1328">
-            <v>15311004</v>
+            <v>15305004</v>
           </cell>
         </row>
         <row r="1329">
           <cell r="C1329">
-            <v>15311005</v>
+            <v>15305005</v>
           </cell>
         </row>
         <row r="1330">
           <cell r="C1330">
-            <v>15311006</v>
+            <v>15305006</v>
           </cell>
         </row>
         <row r="1331">
           <cell r="C1331">
-            <v>15311011</v>
+            <v>15306001</v>
           </cell>
         </row>
         <row r="1332">
           <cell r="C1332">
-            <v>15311012</v>
+            <v>15306002</v>
           </cell>
         </row>
         <row r="1333">
           <cell r="C1333">
-            <v>15311013</v>
+            <v>15306003</v>
           </cell>
         </row>
         <row r="1334">
           <cell r="C1334">
-            <v>15401001</v>
+            <v>15307001</v>
           </cell>
         </row>
         <row r="1335">
           <cell r="C1335">
-            <v>15401002</v>
+            <v>15307002</v>
           </cell>
         </row>
       </sheetData>
@@ -27308,10 +27512,12 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:AJ140"/>
+  <dimension ref="A1:AJ161"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="10" max="10" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="31.625" customWidth="1"/>
+    <col min="5" max="5" width="12.25" customWidth="1"/>
+    <col min="10" max="10" width="13.125" customWidth="1"/>
     <col min="11" max="11" width="12.875" customWidth="1"/>
     <col min="12" max="13" width="10.625" customWidth="1"/>
     <col min="14" max="14" width="10.75" customWidth="1"/>
@@ -31004,7 +31210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="2:36">
+    <row r="102" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B102" s="1">
         <v>80001011</v>
       </c>
@@ -31036,7 +31242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="2:36">
+    <row r="103" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B103" s="1">
         <v>80001012</v>
       </c>
@@ -31068,7 +31274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="2:36">
+    <row r="104" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B104" s="1">
         <v>80001013</v>
       </c>
@@ -31100,7 +31306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="2:36">
+    <row r="105" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B105" s="1">
         <v>80001014</v>
       </c>
@@ -31132,7 +31338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="2:36">
+    <row r="106" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B106" s="1">
         <v>80001015</v>
       </c>
@@ -31164,7 +31370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="2:36">
+    <row r="107" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B107" s="1">
         <v>80001016</v>
       </c>
@@ -31196,7 +31402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="2:36">
+    <row r="108" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B108" s="1">
         <v>80001017</v>
       </c>
@@ -31228,7 +31434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="2:36">
+    <row r="109" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B109" s="1">
         <v>80001018</v>
       </c>
@@ -31260,7 +31466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="2:36">
+    <row r="110" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B110" s="1">
         <v>80001019</v>
       </c>
@@ -31292,7 +31498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="2:36">
+    <row r="111" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B111" s="1">
         <v>80001020</v>
       </c>
@@ -31324,7 +31530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="2:36">
+    <row r="112" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B112" s="1">
         <v>80001021</v>
       </c>
@@ -31358,7 +31564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="2:36">
+    <row r="113" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B113" s="1">
         <v>80001022</v>
       </c>
@@ -31394,7 +31600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="2:36">
+    <row r="114" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B114" s="1">
         <v>80001023</v>
       </c>
@@ -31433,7 +31639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="2:36">
+    <row r="115" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B115" s="1">
         <v>80001024</v>
       </c>
@@ -31472,7 +31678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="2:36">
+    <row r="116" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B116" s="1">
         <v>80001025</v>
       </c>
@@ -31502,7 +31708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="2:36">
+    <row r="117" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B117" s="1">
         <v>80001026</v>
       </c>
@@ -31532,7 +31738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="2:36">
+    <row r="118" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B118" s="1">
         <v>80001027</v>
       </c>
@@ -31562,7 +31768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="2:36">
+    <row r="119" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="B119" s="1">
         <v>80001028</v>
       </c>
@@ -31592,7 +31798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="2:36">
+    <row r="120" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="AE120" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
@@ -31610,7 +31816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="2:36">
+    <row r="121" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="AE121" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -31628,12 +31834,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="2:36">
+    <row r="122" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="AJ122">
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="2:36">
+    <row r="123" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="B123" s="105" t="s">
+        <v>3128</v>
+      </c>
       <c r="AI123">
         <v>80001007</v>
       </c>
@@ -31641,7 +31850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="2:36">
+    <row r="124" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="AI124">
         <v>80001023</v>
       </c>
@@ -31649,7 +31858,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="2:36">
+    <row r="125" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="B125" s="13">
+        <v>1</v>
+      </c>
+      <c r="C125" s="103" t="s">
+        <v>3129</v>
+      </c>
+      <c r="D125" s="122" t="s">
+        <v>3134</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>3138</v>
+      </c>
       <c r="AI125">
         <v>80001021</v>
       </c>
@@ -31657,7 +31878,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="2:36">
+    <row r="126" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="B126" s="13"/>
+      <c r="C126" s="13"/>
+      <c r="D126" s="15"/>
+      <c r="I126" s="51">
+        <v>10000131</v>
+      </c>
+      <c r="J126" s="52" t="s">
+        <v>3142</v>
+      </c>
       <c r="AI126">
         <v>80002006</v>
       </c>
@@ -31665,7 +31895,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="2:36">
+    <row r="127" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="B127" s="13">
+        <v>2</v>
+      </c>
+      <c r="C127" s="103" t="s">
+        <v>3130</v>
+      </c>
+      <c r="D127" s="122" t="s">
+        <v>3136</v>
+      </c>
+      <c r="I127" s="51">
+        <v>10000168</v>
+      </c>
+      <c r="J127" s="52" t="s">
+        <v>3140</v>
+      </c>
+      <c r="O127" s="105" t="s">
+        <v>3139</v>
+      </c>
       <c r="AI127">
         <v>80001022</v>
       </c>
@@ -31673,7 +31921,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="2:36">
+    <row r="128" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="B128" s="13"/>
+      <c r="C128" s="13"/>
+      <c r="D128" s="15"/>
+      <c r="I128" s="51">
+        <v>10000169</v>
+      </c>
+      <c r="J128" s="52" t="s">
+        <v>3141</v>
+      </c>
       <c r="AI128">
         <v>80001024</v>
       </c>
@@ -31681,7 +31938,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="35:36">
+    <row r="129" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="B129" s="13">
+        <v>3</v>
+      </c>
+      <c r="C129" s="103" t="s">
+        <v>3131</v>
+      </c>
+      <c r="D129" s="122" t="s">
+        <v>3137</v>
+      </c>
       <c r="AI129">
         <v>80001028</v>
       </c>
@@ -31689,7 +31955,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="35:36">
+    <row r="130" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="B130" s="13"/>
+      <c r="C130" s="13"/>
+      <c r="D130" s="15"/>
       <c r="AI130">
         <v>80001023</v>
       </c>
@@ -31697,7 +31966,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="35:36">
+    <row r="131" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="B131" s="13">
+        <v>4</v>
+      </c>
+      <c r="C131" s="103" t="s">
+        <v>3132</v>
+      </c>
+      <c r="D131" s="122" t="s">
+        <v>3137</v>
+      </c>
       <c r="AI131">
         <v>80001027</v>
       </c>
@@ -31705,7 +31983,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="35:36">
+    <row r="132" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="B132" s="13"/>
+      <c r="C132" s="13"/>
+      <c r="D132" s="15"/>
       <c r="AI132">
         <v>80001026</v>
       </c>
@@ -31713,7 +31994,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="35:36">
+    <row r="133" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="B133" s="13">
+        <v>5</v>
+      </c>
+      <c r="C133" s="103" t="s">
+        <v>3133</v>
+      </c>
+      <c r="D133" s="122" t="s">
+        <v>3135</v>
+      </c>
       <c r="AI133">
         <v>80001028</v>
       </c>
@@ -31721,7 +32011,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="35:36">
+    <row r="134" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="D134" s="15"/>
+      <c r="K134" s="1"/>
       <c r="AI134">
         <v>80001025</v>
       </c>
@@ -31729,7 +32021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="35:36">
+    <row r="135" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="AI135">
         <v>80002022</v>
       </c>
@@ -31737,7 +32029,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="35:36">
+    <row r="136" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="H136" s="1" t="s">
+        <v>3143</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J136" s="1">
+        <v>1</v>
+      </c>
+      <c r="K136" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M136" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N136" s="1">
+        <v>10</v>
+      </c>
+      <c r="O136" s="1"/>
+      <c r="P136" s="1"/>
+      <c r="Q136" s="1"/>
       <c r="AI136">
         <v>80002019</v>
       </c>
@@ -31745,7 +32061,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="35:36">
+    <row r="137" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="H137" s="1" t="s">
+        <v>3144</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J137" s="1">
+        <v>1</v>
+      </c>
+      <c r="K137" s="1">
+        <v>2000000</v>
+      </c>
+      <c r="L137" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M137" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N137" s="1">
+        <v>20</v>
+      </c>
+      <c r="O137" s="1"/>
+      <c r="P137" s="1"/>
+      <c r="Q137" s="1"/>
       <c r="AI137">
         <v>80002021</v>
       </c>
@@ -31753,7 +32093,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="35:36">
+    <row r="138" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="H138" s="1" t="s">
+        <v>3145</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J138" s="1">
+        <v>1</v>
+      </c>
+      <c r="K138" s="1">
+        <v>3000000</v>
+      </c>
+      <c r="L138" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M138" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N138" s="1">
+        <v>30</v>
+      </c>
+      <c r="O138" s="1"/>
+      <c r="P138" s="1"/>
+      <c r="Q138" s="1"/>
       <c r="AI138">
         <v>80002027</v>
       </c>
@@ -31761,7 +32125,31 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="35:36">
+    <row r="139" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="H139" s="1" t="s">
+        <v>3146</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J139" s="1">
+        <v>1</v>
+      </c>
+      <c r="K139" s="1">
+        <v>4000000</v>
+      </c>
+      <c r="L139" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M139" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N139" s="1">
+        <v>40</v>
+      </c>
+      <c r="O139" s="1"/>
+      <c r="P139" s="1"/>
+      <c r="Q139" s="1"/>
       <c r="AI139">
         <v>80002023</v>
       </c>
@@ -31769,7 +32157,37 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="35:36">
+    <row r="140" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="H140" s="1" t="s">
+        <v>3147</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J140" s="1">
+        <v>1</v>
+      </c>
+      <c r="K140" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="L140" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M140" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N140" s="1">
+        <v>50</v>
+      </c>
+      <c r="O140" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P140" s="1" t="s">
+        <v>3141</v>
+      </c>
+      <c r="Q140" s="1">
+        <v>3</v>
+      </c>
       <c r="AI140">
         <v>80002003</v>
       </c>
@@ -31777,6 +32195,420 @@
         <v>1</v>
       </c>
     </row>
+    <row r="141" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="H141" s="1" t="s">
+        <v>3148</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J141" s="1">
+        <v>1</v>
+      </c>
+      <c r="K141" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="L141" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M141" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N141" s="1">
+        <v>60</v>
+      </c>
+      <c r="O141" s="1"/>
+      <c r="P141" s="1"/>
+      <c r="Q141" s="1"/>
+    </row>
+    <row r="142" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="H142" s="1" t="s">
+        <v>3149</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J142" s="1">
+        <v>1</v>
+      </c>
+      <c r="K142" s="1">
+        <v>7000000</v>
+      </c>
+      <c r="L142" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M142" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N142" s="1">
+        <v>70</v>
+      </c>
+      <c r="O142" s="1"/>
+      <c r="P142" s="1"/>
+      <c r="Q142" s="1"/>
+    </row>
+    <row r="143" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="H143" s="1" t="s">
+        <v>3150</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J143" s="1">
+        <v>1</v>
+      </c>
+      <c r="K143" s="1">
+        <v>8000000</v>
+      </c>
+      <c r="L143" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M143" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N143" s="1">
+        <v>80</v>
+      </c>
+      <c r="O143" s="1"/>
+      <c r="P143" s="1"/>
+      <c r="Q143" s="1"/>
+    </row>
+    <row r="144" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="H144" s="1" t="s">
+        <v>3151</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J144" s="1">
+        <v>1</v>
+      </c>
+      <c r="K144" s="1">
+        <v>9000000</v>
+      </c>
+      <c r="L144" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M144" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N144" s="1">
+        <v>90</v>
+      </c>
+      <c r="O144" s="1"/>
+      <c r="P144" s="1"/>
+      <c r="Q144" s="1"/>
+    </row>
+    <row r="145" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="H145" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J145" s="1">
+        <v>1</v>
+      </c>
+      <c r="K145" s="1">
+        <v>10000000</v>
+      </c>
+      <c r="L145" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M145" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N145" s="1">
+        <v>100</v>
+      </c>
+      <c r="O145" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P145" s="1" t="s">
+        <v>3141</v>
+      </c>
+      <c r="Q145" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="H146" s="1" t="s">
+        <v>3153</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J146" s="1">
+        <v>1</v>
+      </c>
+      <c r="K146" s="1">
+        <v>12000000</v>
+      </c>
+      <c r="L146" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M146" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N146" s="1">
+        <v>120</v>
+      </c>
+      <c r="O146" s="1"/>
+      <c r="P146" s="1"/>
+      <c r="Q146" s="1"/>
+    </row>
+    <row r="147" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="H147" s="1" t="s">
+        <v>3154</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J147" s="1">
+        <v>1</v>
+      </c>
+      <c r="K147" s="1">
+        <v>14000000</v>
+      </c>
+      <c r="L147" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M147" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N147" s="1">
+        <v>140</v>
+      </c>
+      <c r="O147" s="1"/>
+      <c r="P147" s="1"/>
+      <c r="Q147" s="1"/>
+    </row>
+    <row r="148" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="H148" s="1" t="s">
+        <v>3155</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J148" s="1">
+        <v>1</v>
+      </c>
+      <c r="K148" s="1">
+        <v>16000000</v>
+      </c>
+      <c r="L148" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M148" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N148" s="1">
+        <v>160</v>
+      </c>
+      <c r="O148" s="1"/>
+      <c r="P148" s="1"/>
+      <c r="Q148" s="1"/>
+    </row>
+    <row r="149" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="H149" s="1" t="s">
+        <v>3156</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J149" s="1">
+        <v>1</v>
+      </c>
+      <c r="K149" s="1">
+        <v>18000000</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M149" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N149" s="1">
+        <v>180</v>
+      </c>
+      <c r="O149" s="1"/>
+      <c r="P149" s="1"/>
+      <c r="Q149" s="1"/>
+    </row>
+    <row r="150" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="H150" s="1" t="s">
+        <v>3157</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J150" s="1">
+        <v>1</v>
+      </c>
+      <c r="K150" s="1">
+        <v>20000000</v>
+      </c>
+      <c r="L150" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M150" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N150" s="1">
+        <v>200</v>
+      </c>
+      <c r="O150" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P150" s="1" t="s">
+        <v>3141</v>
+      </c>
+      <c r="Q150" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="H151" s="1" t="s">
+        <v>3158</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J151" s="1">
+        <v>1</v>
+      </c>
+      <c r="K151" s="1">
+        <v>22000000</v>
+      </c>
+      <c r="L151" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M151" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N151" s="1">
+        <v>220</v>
+      </c>
+      <c r="O151" s="1"/>
+      <c r="P151" s="1"/>
+      <c r="Q151" s="1"/>
+    </row>
+    <row r="152" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="H152" s="1" t="s">
+        <v>3159</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J152" s="1">
+        <v>1</v>
+      </c>
+      <c r="K152" s="1">
+        <v>24000000</v>
+      </c>
+      <c r="L152" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M152" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N152" s="1">
+        <v>240</v>
+      </c>
+      <c r="O152" s="1"/>
+      <c r="P152" s="1"/>
+      <c r="Q152" s="1"/>
+    </row>
+    <row r="153" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="H153" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J153" s="1">
+        <v>1</v>
+      </c>
+      <c r="K153" s="1">
+        <v>26000000</v>
+      </c>
+      <c r="L153" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M153" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N153" s="1">
+        <v>260</v>
+      </c>
+      <c r="O153" s="1"/>
+      <c r="P153" s="1"/>
+      <c r="Q153" s="1"/>
+    </row>
+    <row r="154" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="H154" s="1" t="s">
+        <v>3160</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J154" s="1">
+        <v>1</v>
+      </c>
+      <c r="K154" s="1">
+        <v>28000000</v>
+      </c>
+      <c r="L154" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M154" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N154" s="1">
+        <v>280</v>
+      </c>
+      <c r="O154" s="1"/>
+      <c r="P154" s="1"/>
+      <c r="Q154" s="1"/>
+    </row>
+    <row r="155" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="H155" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>3152</v>
+      </c>
+      <c r="J155" s="1">
+        <v>1</v>
+      </c>
+      <c r="K155" s="1">
+        <v>30000000</v>
+      </c>
+      <c r="L155" s="1" t="s">
+        <v>3140</v>
+      </c>
+      <c r="M155" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="N155" s="1">
+        <v>300</v>
+      </c>
+      <c r="O155" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P155" s="1" t="s">
+        <v>3141</v>
+      </c>
+      <c r="Q155" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156" spans="8:17" ht="20.100000000000001" customHeight="1"/>
+    <row r="157" spans="8:17" ht="20.100000000000001" customHeight="1"/>
+    <row r="158" spans="8:17" ht="20.100000000000001" customHeight="1"/>
+    <row r="159" spans="8:17" ht="20.100000000000001" customHeight="1"/>
+    <row r="160" spans="8:17" ht="20.100000000000001" customHeight="1"/>
+    <row r="161" ht="20.100000000000001" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -70022,6 +70854,13 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="CP23:CP25"/>
+    <mergeCell ref="CP26:CP28"/>
+    <mergeCell ref="CP8:CP10"/>
+    <mergeCell ref="CP11:CP13"/>
+    <mergeCell ref="CP14:CP16"/>
+    <mergeCell ref="CP17:CP19"/>
+    <mergeCell ref="CP20:CP22"/>
     <mergeCell ref="K18:K20"/>
     <mergeCell ref="K21:K23"/>
     <mergeCell ref="AX4:AX6"/>
@@ -70036,13 +70875,6 @@
     <mergeCell ref="K9:K11"/>
     <mergeCell ref="K12:K14"/>
     <mergeCell ref="K15:K17"/>
-    <mergeCell ref="CP23:CP25"/>
-    <mergeCell ref="CP26:CP28"/>
-    <mergeCell ref="CP8:CP10"/>
-    <mergeCell ref="CP11:CP13"/>
-    <mergeCell ref="CP14:CP16"/>
-    <mergeCell ref="CP17:CP19"/>
-    <mergeCell ref="CP20:CP22"/>
   </mergeCells>
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/WeiJingShuZhi/属性表.xlsx
+++ b/WeiJingShuZhi/属性表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\WeiJingShuZhi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A632C4C9-100E-4FA3-AAE0-5B0AE22D3422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C71F76B-3578-4957-A05F-1A322ED3788D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5628" uniqueCount="3161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5676" uniqueCount="3179">
   <si>
     <t>人物属性</t>
   </si>
@@ -9996,22 +9996,10 @@
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
   <si>
-    <t>攻击+百分比</t>
-    <phoneticPr fontId="35" type="noConversion"/>
-  </si>
-  <si>
     <t>生命百分比</t>
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
   <si>
-    <t>魔法+百分比</t>
-    <phoneticPr fontId="35" type="noConversion"/>
-  </si>
-  <si>
-    <t>对怪伤害+百分比  伤害减免+百分比</t>
-    <phoneticPr fontId="35" type="noConversion"/>
-  </si>
-  <si>
     <t>基础材料</t>
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
@@ -10086,6 +10074,88 @@
   </si>
   <si>
     <t>19级</t>
+  </si>
+  <si>
+    <t>130103;50</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物全体对怪伤害</t>
+  </si>
+  <si>
+    <t>魔法百分比</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害减免百分比</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害加成</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击百分比</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>NNZL 5级</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>231103;0.02</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Now_Res = 2004;          //当前韧性概率</t>
+  </si>
+  <si>
+    <t>加到</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>Now_PetAllDamgeAddPro = 2305;          //宠物全体伤害加成</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>Now_PetAllDamgeSubPro = 2306;          //宠物全体受到伤害减免</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>Now_PetAllActBossAddDamge = 2307;      //当前宠物BOSS普通攻击加成固定值</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Now_DamgeAddPro = 2009;          //当前伤害加成    </t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>Now_DamgeSubPro = 2010;          //当前伤害减免</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>Now_ActBossPro = 2030;      //当前BOSS普通攻击加成</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>Now_PetAllRes = 2304;         //宠物全体抗暴</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备材料</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>灿烂的结晶</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>原装备</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>平均1个宠物1个</t>
+    <phoneticPr fontId="35" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -10095,7 +10165,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10365,8 +10435,17 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10499,8 +10578,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="13"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -10635,12 +10720,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="12"/>
+      </left>
+      <right style="hair">
+        <color indexed="12"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="12"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10979,14 +11077,17 @@
     <xf numFmtId="0" fontId="1" fillId="22" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11200,8 +11301,8 @@
       <xdr:rowOff>64770</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>342265</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>2352040</xdr:colOff>
       <xdr:row>56</xdr:row>
       <xdr:rowOff>199390</xdr:rowOff>
     </xdr:to>
@@ -27512,20 +27613,30 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:AJ161"/>
+  <dimension ref="A1:AJ210"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="4" max="4" width="31.625" customWidth="1"/>
-    <col min="5" max="5" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="21.25" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="21.875" customWidth="1"/>
+    <col min="7" max="7" width="18.125" customWidth="1"/>
+    <col min="8" max="8" width="13.125" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
     <col min="10" max="10" width="13.125" customWidth="1"/>
     <col min="11" max="11" width="12.875" customWidth="1"/>
     <col min="12" max="13" width="10.625" customWidth="1"/>
     <col min="14" max="14" width="10.75" customWidth="1"/>
     <col min="15" max="16" width="11.375" customWidth="1"/>
     <col min="17" max="17" width="12.625" customWidth="1"/>
+    <col min="18" max="18" width="13.625" customWidth="1"/>
+    <col min="19" max="19" width="32.125" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
     <col min="21" max="21" width="13" customWidth="1"/>
+    <col min="22" max="22" width="13.375" customWidth="1"/>
     <col min="23" max="23" width="15" customWidth="1"/>
-    <col min="24" max="24" width="21.5" customWidth="1"/>
+    <col min="24" max="24" width="14.875" customWidth="1"/>
     <col min="25" max="25" width="14.375" customWidth="1"/>
     <col min="26" max="26" width="37.5" customWidth="1"/>
     <col min="29" max="29" width="27" customWidth="1"/>
@@ -31543,10 +31654,11 @@
       <c r="E112" s="1" t="s">
         <v>2388</v>
       </c>
-      <c r="J112" s="13"/>
-      <c r="K112" s="13" t="s">
+      <c r="J112" s="1"/>
+      <c r="K112" s="1" t="s">
         <v>2424</v>
       </c>
+      <c r="L112" s="1"/>
       <c r="AE112" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
@@ -31577,12 +31689,13 @@
       <c r="E113" s="1" t="s">
         <v>2382</v>
       </c>
-      <c r="J113" s="13">
-        <v>1</v>
-      </c>
-      <c r="K113" s="13">
-        <v>1</v>
-      </c>
+      <c r="J113" s="1">
+        <v>1</v>
+      </c>
+      <c r="K113" s="1">
+        <v>1</v>
+      </c>
+      <c r="L113" s="1"/>
       <c r="AE113" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -31613,13 +31726,13 @@
       <c r="E114" s="1" t="s">
         <v>2398</v>
       </c>
-      <c r="J114" s="13">
+      <c r="J114" s="1">
         <v>2</v>
       </c>
-      <c r="K114" s="13">
+      <c r="K114" s="1">
         <v>0.8</v>
       </c>
-      <c r="L114">
+      <c r="L114" s="1">
         <v>0.2</v>
       </c>
       <c r="AE114" s="13">
@@ -31652,13 +31765,13 @@
       <c r="E115" s="1" t="s">
         <v>2408</v>
       </c>
-      <c r="J115" s="13">
+      <c r="J115" s="1">
         <v>3</v>
       </c>
-      <c r="K115" s="13">
+      <c r="K115" s="1">
         <v>0.6</v>
       </c>
-      <c r="L115">
+      <c r="L115" s="1">
         <v>0.4</v>
       </c>
       <c r="AE115" s="13">
@@ -31840,7 +31953,7 @@
       </c>
     </row>
     <row r="123" spans="2:36" ht="20.100000000000001" customHeight="1">
-      <c r="B123" s="105" t="s">
+      <c r="B123" s="1" t="s">
         <v>3128</v>
       </c>
       <c r="AI123">
@@ -31851,6 +31964,9 @@
       </c>
     </row>
     <row r="124" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="B124" s="5"/>
+      <c r="C124" s="5"/>
+      <c r="D124" s="5"/>
       <c r="AI124">
         <v>80001023</v>
       </c>
@@ -31859,17 +31975,23 @@
       </c>
     </row>
     <row r="125" spans="2:36" ht="20.100000000000001" customHeight="1">
-      <c r="B125" s="13">
-        <v>1</v>
-      </c>
-      <c r="C125" s="103" t="s">
+      <c r="B125" s="1">
+        <v>1</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>3129</v>
       </c>
-      <c r="D125" s="122" t="s">
-        <v>3134</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>3138</v>
+      <c r="D125" s="1" t="s">
+        <v>3163</v>
+      </c>
+      <c r="F125" s="120" t="s">
+        <v>3158</v>
+      </c>
+      <c r="G125" s="120" t="s">
+        <v>3165</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>3135</v>
       </c>
       <c r="AI125">
         <v>80001021</v>
@@ -31879,15 +32001,18 @@
       </c>
     </row>
     <row r="126" spans="2:36" ht="20.100000000000001" customHeight="1">
-      <c r="B126" s="13"/>
-      <c r="C126" s="13"/>
-      <c r="D126" s="15"/>
-      <c r="I126" s="51">
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="J126" s="51">
         <v>10000131</v>
       </c>
-      <c r="J126" s="52" t="s">
-        <v>3142</v>
-      </c>
+      <c r="K126" s="52" t="s">
+        <v>3139</v>
+      </c>
+      <c r="N126" s="5"/>
+      <c r="O126" s="5"/>
+      <c r="P126" s="5"/>
       <c r="AI126">
         <v>80002006</v>
       </c>
@@ -31896,24 +32021,32 @@
       </c>
     </row>
     <row r="127" spans="2:36" ht="20.100000000000001" customHeight="1">
-      <c r="B127" s="13">
+      <c r="B127" s="1">
         <v>2</v>
       </c>
-      <c r="C127" s="103" t="s">
+      <c r="C127" s="1" t="s">
         <v>3130</v>
       </c>
-      <c r="D127" s="122" t="s">
+      <c r="D127" s="1" t="s">
+        <v>3160</v>
+      </c>
+      <c r="F127" s="120">
+        <v>130003</v>
+      </c>
+      <c r="G127" s="120">
+        <v>231003</v>
+      </c>
+      <c r="J127" s="51">
+        <v>10000168</v>
+      </c>
+      <c r="K127" s="52" t="s">
+        <v>3137</v>
+      </c>
+      <c r="N127" s="5"/>
+      <c r="O127" s="1" t="s">
         <v>3136</v>
       </c>
-      <c r="I127" s="51">
-        <v>10000168</v>
-      </c>
-      <c r="J127" s="52" t="s">
-        <v>3140</v>
-      </c>
-      <c r="O127" s="105" t="s">
-        <v>3139</v>
-      </c>
+      <c r="P127" s="5"/>
       <c r="AI127">
         <v>80001022</v>
       </c>
@@ -31922,15 +32055,20 @@
       </c>
     </row>
     <row r="128" spans="2:36" ht="20.100000000000001" customHeight="1">
-      <c r="B128" s="13"/>
-      <c r="C128" s="13"/>
-      <c r="D128" s="15"/>
-      <c r="I128" s="51">
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+      <c r="J128" s="51">
         <v>10000169</v>
       </c>
-      <c r="J128" s="52" t="s">
-        <v>3141</v>
-      </c>
+      <c r="K128" s="52" t="s">
+        <v>3138</v>
+      </c>
+      <c r="N128" s="5"/>
+      <c r="O128" s="1" t="s">
+        <v>3164</v>
+      </c>
+      <c r="P128" s="5"/>
       <c r="AI128">
         <v>80001024</v>
       </c>
@@ -31939,15 +32077,30 @@
       </c>
     </row>
     <row r="129" spans="2:36" ht="20.100000000000001" customHeight="1">
-      <c r="B129" s="13">
+      <c r="B129" s="1">
         <v>3</v>
       </c>
-      <c r="C129" s="103" t="s">
+      <c r="C129" s="1" t="s">
         <v>3131</v>
       </c>
-      <c r="D129" s="122" t="s">
-        <v>3137</v>
-      </c>
+      <c r="D129" s="1" t="s">
+        <v>3161</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>3162</v>
+      </c>
+      <c r="F129" s="120">
+        <v>130203</v>
+      </c>
+      <c r="G129" s="120">
+        <v>230503</v>
+      </c>
+      <c r="H129" s="1">
+        <v>230603</v>
+      </c>
+      <c r="N129" s="5"/>
+      <c r="O129" s="5"/>
+      <c r="P129" s="5"/>
       <c r="AI129">
         <v>80001028</v>
       </c>
@@ -31956,9 +32109,10 @@
       </c>
     </row>
     <row r="130" spans="2:36" ht="20.100000000000001" customHeight="1">
-      <c r="B130" s="13"/>
-      <c r="C130" s="13"/>
-      <c r="D130" s="15"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
+      <c r="H130" s="1"/>
       <c r="AI130">
         <v>80001023</v>
       </c>
@@ -31967,14 +32121,26 @@
       </c>
     </row>
     <row r="131" spans="2:36" ht="20.100000000000001" customHeight="1">
-      <c r="B131" s="13">
+      <c r="B131" s="1">
         <v>4</v>
       </c>
-      <c r="C131" s="103" t="s">
+      <c r="C131" s="1" t="s">
         <v>3132</v>
       </c>
-      <c r="D131" s="122" t="s">
-        <v>3137</v>
+      <c r="D131" s="1" t="s">
+        <v>3161</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>3162</v>
+      </c>
+      <c r="F131" s="120">
+        <v>130303</v>
+      </c>
+      <c r="G131" s="120">
+        <v>230503</v>
+      </c>
+      <c r="H131" s="1">
+        <v>230603</v>
       </c>
       <c r="AI131">
         <v>80001027</v>
@@ -31984,9 +32150,10 @@
       </c>
     </row>
     <row r="132" spans="2:36" ht="20.100000000000001" customHeight="1">
-      <c r="B132" s="13"/>
-      <c r="C132" s="13"/>
-      <c r="D132" s="15"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
+      <c r="H132" s="1"/>
       <c r="AI132">
         <v>80001026</v>
       </c>
@@ -31995,14 +32162,26 @@
       </c>
     </row>
     <row r="133" spans="2:36" ht="20.100000000000001" customHeight="1">
-      <c r="B133" s="13">
+      <c r="B133" s="1">
         <v>5</v>
       </c>
-      <c r="C133" s="103" t="s">
+      <c r="C133" s="1" t="s">
         <v>3133</v>
       </c>
-      <c r="D133" s="122" t="s">
-        <v>3135</v>
+      <c r="D133" s="1" t="s">
+        <v>3134</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>3159</v>
+      </c>
+      <c r="F133" s="120">
+        <v>130403</v>
+      </c>
+      <c r="G133" s="120">
+        <v>231403</v>
+      </c>
+      <c r="H133" s="1">
+        <v>230703</v>
       </c>
       <c r="AI133">
         <v>80001028</v>
@@ -32012,8 +32191,15 @@
       </c>
     </row>
     <row r="134" spans="2:36" ht="20.100000000000001" customHeight="1">
-      <c r="D134" s="15"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="5"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="13"/>
       <c r="K134" s="1"/>
+      <c r="U134" s="5"/>
+      <c r="V134" s="5"/>
+      <c r="W134" s="5"/>
+      <c r="X134" s="5"/>
       <c r="AI134">
         <v>80001025</v>
       </c>
@@ -32022,6 +32208,11 @@
       </c>
     </row>
     <row r="135" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="U135" s="5"/>
+      <c r="V135" s="1"/>
+      <c r="W135" s="1"/>
+      <c r="X135" s="1"/>
+      <c r="Y135" s="13"/>
       <c r="AI135">
         <v>80002022</v>
       </c>
@@ -32031,10 +32222,10 @@
     </row>
     <row r="136" spans="2:36" ht="20.100000000000001" customHeight="1">
       <c r="H136" s="1" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J136" s="1">
         <v>1</v>
@@ -32043,17 +32234,34 @@
         <v>1000000</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M136" s="1">
         <v>10000168</v>
       </c>
       <c r="N136" s="1">
-        <v>10</v>
-      </c>
-      <c r="O136" s="1"/>
-      <c r="P136" s="1"/>
-      <c r="Q136" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="O136" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P136" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q136" s="1">
+        <v>5</v>
+      </c>
+      <c r="S136" s="3" t="str">
+        <f>M136&amp;";"&amp;N136&amp;"@"&amp;O136&amp;";"&amp;Q136</f>
+        <v>10000168;20@10000169;5</v>
+      </c>
+      <c r="U136" s="5"/>
+      <c r="V136" s="1" t="s">
+        <v>3175</v>
+      </c>
+      <c r="W136" s="1"/>
+      <c r="X136" s="1"/>
+      <c r="Y136" s="13"/>
       <c r="AI136">
         <v>80002019</v>
       </c>
@@ -32062,11 +32270,17 @@
       </c>
     </row>
     <row r="137" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="D137" s="1" t="s">
+        <v>3162</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>3178</v>
+      </c>
       <c r="H137" s="1" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J137" s="1">
         <v>1</v>
@@ -32075,17 +32289,41 @@
         <v>2000000</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M137" s="1">
         <v>10000168</v>
       </c>
       <c r="N137" s="1">
-        <v>20</v>
-      </c>
-      <c r="O137" s="1"/>
-      <c r="P137" s="1"/>
-      <c r="Q137" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="O137" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P137" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q137" s="1">
+        <v>5</v>
+      </c>
+      <c r="S137" s="3" t="str">
+        <f t="shared" ref="S137:S155" si="8">M137&amp;";"&amp;N137&amp;"@"&amp;O137&amp;";"&amp;Q137</f>
+        <v>10000168;25@10000169;5</v>
+      </c>
+      <c r="U137" s="5"/>
+      <c r="V137" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="W137" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="X137" s="1">
+        <v>10</v>
+      </c>
+      <c r="Y137" s="13" t="str">
+        <f>V137&amp;";"&amp;X137</f>
+        <v>10000169;10</v>
+      </c>
       <c r="AI137">
         <v>80002021</v>
       </c>
@@ -32094,11 +32332,20 @@
       </c>
     </row>
     <row r="138" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="E138" s="1" t="s">
+        <v>3137</v>
+      </c>
+      <c r="F138" s="1">
+        <v>10000168</v>
+      </c>
+      <c r="G138" s="1">
+        <v>10</v>
+      </c>
       <c r="H138" s="1" t="s">
-        <v>3145</v>
+        <v>3142</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J138" s="1">
         <v>1</v>
@@ -32107,7 +32354,7 @@
         <v>3000000</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M138" s="1">
         <v>10000168</v>
@@ -32115,9 +32362,33 @@
       <c r="N138" s="1">
         <v>30</v>
       </c>
-      <c r="O138" s="1"/>
-      <c r="P138" s="1"/>
-      <c r="Q138" s="1"/>
+      <c r="O138" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P138" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q138" s="1">
+        <v>5</v>
+      </c>
+      <c r="S138" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;30@10000169;5</v>
+      </c>
+      <c r="U138" s="5"/>
+      <c r="V138" s="1">
+        <v>10000166</v>
+      </c>
+      <c r="W138" s="1" t="s">
+        <v>3136</v>
+      </c>
+      <c r="X138" s="1">
+        <v>120</v>
+      </c>
+      <c r="Y138" s="13" t="str">
+        <f t="shared" ref="Y138:Y141" si="9">V138&amp;";"&amp;X138</f>
+        <v>10000166;120</v>
+      </c>
       <c r="AI138">
         <v>80002027</v>
       </c>
@@ -32126,11 +32397,15 @@
       </c>
     </row>
     <row r="139" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="D139" s="1" t="s">
+        <v>3162</v>
+      </c>
+      <c r="F139" s="105"/>
       <c r="H139" s="1" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J139" s="1">
         <v>1</v>
@@ -32139,7 +32414,7 @@
         <v>4000000</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M139" s="1">
         <v>10000168</v>
@@ -32147,9 +32422,33 @@
       <c r="N139" s="1">
         <v>40</v>
       </c>
-      <c r="O139" s="1"/>
-      <c r="P139" s="1"/>
-      <c r="Q139" s="1"/>
+      <c r="O139" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P139" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q139" s="1">
+        <v>5</v>
+      </c>
+      <c r="S139" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;40@10000169;5</v>
+      </c>
+      <c r="U139" s="5"/>
+      <c r="V139" s="1">
+        <v>10000143</v>
+      </c>
+      <c r="W139" s="1" t="s">
+        <v>3176</v>
+      </c>
+      <c r="X139" s="1">
+        <v>50</v>
+      </c>
+      <c r="Y139" s="13" t="str">
+        <f t="shared" si="9"/>
+        <v>10000143;50</v>
+      </c>
       <c r="AI139">
         <v>80002023</v>
       </c>
@@ -32158,11 +32457,12 @@
       </c>
     </row>
     <row r="140" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="D140" s="13"/>
       <c r="H140" s="1" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J140" s="1">
         <v>1</v>
@@ -32171,7 +32471,7 @@
         <v>5000000</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M140" s="1">
         <v>10000168</v>
@@ -32183,10 +32483,28 @@
         <v>10000169</v>
       </c>
       <c r="P140" s="1" t="s">
-        <v>3141</v>
+        <v>3138</v>
       </c>
       <c r="Q140" s="1">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="S140" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;50@10000169;5</v>
+      </c>
+      <c r="U140" s="5"/>
+      <c r="V140" s="51">
+        <v>10000168</v>
+      </c>
+      <c r="W140" s="52" t="s">
+        <v>3137</v>
+      </c>
+      <c r="X140" s="1">
+        <v>100</v>
+      </c>
+      <c r="Y140" s="13" t="str">
+        <f t="shared" si="9"/>
+        <v>10000168;100</v>
       </c>
       <c r="AI140">
         <v>80002003</v>
@@ -32196,11 +32514,14 @@
       </c>
     </row>
     <row r="141" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="D141" s="1" t="s">
+        <v>3159</v>
+      </c>
       <c r="H141" s="1" t="s">
-        <v>3148</v>
+        <v>3145</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J141" s="1">
         <v>1</v>
@@ -32209,7 +32530,7 @@
         <v>6000000</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M141" s="1">
         <v>10000168</v>
@@ -32217,16 +32538,41 @@
       <c r="N141" s="1">
         <v>60</v>
       </c>
-      <c r="O141" s="1"/>
-      <c r="P141" s="1"/>
-      <c r="Q141" s="1"/>
+      <c r="O141" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P141" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q141" s="1">
+        <v>10</v>
+      </c>
+      <c r="S141" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;60@10000169;10</v>
+      </c>
+      <c r="U141" s="5"/>
+      <c r="V141" s="51">
+        <v>10010086</v>
+      </c>
+      <c r="W141" s="108" t="s">
+        <v>2845</v>
+      </c>
+      <c r="X141" s="13">
+        <v>30</v>
+      </c>
+      <c r="Y141" s="13" t="str">
+        <f t="shared" si="9"/>
+        <v>10010086;30</v>
+      </c>
     </row>
     <row r="142" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="D142" s="13"/>
       <c r="H142" s="1" t="s">
+        <v>3146</v>
+      </c>
+      <c r="I142" s="1" t="s">
         <v>3149</v>
-      </c>
-      <c r="I142" s="1" t="s">
-        <v>3152</v>
       </c>
       <c r="J142" s="1">
         <v>1</v>
@@ -32235,7 +32581,7 @@
         <v>7000000</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M142" s="1">
         <v>10000168</v>
@@ -32243,16 +32589,30 @@
       <c r="N142" s="1">
         <v>70</v>
       </c>
-      <c r="O142" s="1"/>
-      <c r="P142" s="1"/>
-      <c r="Q142" s="1"/>
+      <c r="O142" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P142" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q142" s="1">
+        <v>10</v>
+      </c>
+      <c r="S142" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;70@10000169;10</v>
+      </c>
+      <c r="U142" s="5"/>
     </row>
     <row r="143" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="D143" s="1" t="s">
+        <v>3159</v>
+      </c>
       <c r="H143" s="1" t="s">
-        <v>3150</v>
+        <v>3147</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J143" s="1">
         <v>1</v>
@@ -32261,7 +32621,7 @@
         <v>8000000</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M143" s="1">
         <v>10000168</v>
@@ -32269,16 +32629,39 @@
       <c r="N143" s="1">
         <v>80</v>
       </c>
-      <c r="O143" s="1"/>
-      <c r="P143" s="1"/>
-      <c r="Q143" s="1"/>
+      <c r="O143" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P143" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q143" s="1">
+        <v>10</v>
+      </c>
+      <c r="S143" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;80@10000169;10</v>
+      </c>
+      <c r="U143" s="5"/>
+      <c r="V143" s="1"/>
+      <c r="W143" s="1" t="s">
+        <v>3177</v>
+      </c>
+      <c r="X143" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y143" s="13" t="str">
+        <f>Y137&amp;"@"&amp;Y138&amp;"@"&amp;Y139&amp;"@"&amp;Y140&amp;"@"&amp;Y141</f>
+        <v>10000169;10@10000166;120@10000143;50@10000168;100@10010086;30</v>
+      </c>
     </row>
     <row r="144" spans="2:36" ht="20.100000000000001" customHeight="1">
+      <c r="D144" s="13"/>
       <c r="H144" s="1" t="s">
-        <v>3151</v>
+        <v>3148</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J144" s="1">
         <v>1</v>
@@ -32287,7 +32670,7 @@
         <v>9000000</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M144" s="1">
         <v>10000168</v>
@@ -32295,16 +32678,33 @@
       <c r="N144" s="1">
         <v>90</v>
       </c>
-      <c r="O144" s="1"/>
-      <c r="P144" s="1"/>
-      <c r="Q144" s="1"/>
-    </row>
-    <row r="145" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="O144" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P144" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q144" s="1">
+        <v>10</v>
+      </c>
+      <c r="S144" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;90@10000169;10</v>
+      </c>
+      <c r="U144" s="5"/>
+      <c r="V144" s="5"/>
+      <c r="W144" s="5"/>
+      <c r="X144" s="5"/>
+    </row>
+    <row r="145" spans="4:24" ht="20.100000000000001" customHeight="1">
+      <c r="D145" s="1" t="s">
+        <v>3159</v>
+      </c>
       <c r="H145" s="1" t="s">
         <v>1328</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J145" s="1">
         <v>1</v>
@@ -32313,7 +32713,7 @@
         <v>10000000</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M145" s="1">
         <v>10000168</v>
@@ -32325,18 +32725,26 @@
         <v>10000169</v>
       </c>
       <c r="P145" s="1" t="s">
-        <v>3141</v>
+        <v>3138</v>
       </c>
       <c r="Q145" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="146" spans="8:17" ht="20.100000000000001" customHeight="1">
+        <v>10</v>
+      </c>
+      <c r="S145" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;100@10000169;10</v>
+      </c>
+      <c r="U145" s="5"/>
+      <c r="V145" s="5"/>
+      <c r="W145" s="5"/>
+      <c r="X145" s="5"/>
+    </row>
+    <row r="146" spans="4:24" ht="20.100000000000001" customHeight="1">
       <c r="H146" s="1" t="s">
-        <v>3153</v>
+        <v>3150</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J146" s="1">
         <v>1</v>
@@ -32345,7 +32753,7 @@
         <v>12000000</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M146" s="1">
         <v>10000168</v>
@@ -32353,16 +32761,30 @@
       <c r="N146" s="1">
         <v>120</v>
       </c>
-      <c r="O146" s="1"/>
-      <c r="P146" s="1"/>
-      <c r="Q146" s="1"/>
-    </row>
-    <row r="147" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="O146" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P146" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q146" s="1">
+        <v>20</v>
+      </c>
+      <c r="S146" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;120@10000169;20</v>
+      </c>
+      <c r="U146" s="5"/>
+      <c r="V146" s="5"/>
+      <c r="W146" s="5"/>
+      <c r="X146" s="5"/>
+    </row>
+    <row r="147" spans="4:24" ht="20.100000000000001" customHeight="1">
       <c r="H147" s="1" t="s">
-        <v>3154</v>
+        <v>3151</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J147" s="1">
         <v>1</v>
@@ -32371,7 +32793,7 @@
         <v>14000000</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M147" s="1">
         <v>10000168</v>
@@ -32379,16 +32801,30 @@
       <c r="N147" s="1">
         <v>140</v>
       </c>
-      <c r="O147" s="1"/>
-      <c r="P147" s="1"/>
-      <c r="Q147" s="1"/>
-    </row>
-    <row r="148" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="O147" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P147" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q147" s="1">
+        <v>20</v>
+      </c>
+      <c r="S147" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;140@10000169;20</v>
+      </c>
+      <c r="U147" s="5"/>
+      <c r="V147" s="5"/>
+      <c r="W147" s="5"/>
+      <c r="X147" s="5"/>
+    </row>
+    <row r="148" spans="4:24" ht="20.100000000000001" customHeight="1">
       <c r="H148" s="1" t="s">
-        <v>3155</v>
+        <v>3152</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J148" s="1">
         <v>1</v>
@@ -32397,7 +32833,7 @@
         <v>16000000</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M148" s="1">
         <v>10000168</v>
@@ -32405,16 +32841,26 @@
       <c r="N148" s="1">
         <v>160</v>
       </c>
-      <c r="O148" s="1"/>
-      <c r="P148" s="1"/>
-      <c r="Q148" s="1"/>
-    </row>
-    <row r="149" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="O148" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P148" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q148" s="1">
+        <v>20</v>
+      </c>
+      <c r="S148" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;160@10000169;20</v>
+      </c>
+    </row>
+    <row r="149" spans="4:24" ht="20.100000000000001" customHeight="1">
       <c r="H149" s="1" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J149" s="1">
         <v>1</v>
@@ -32423,7 +32869,7 @@
         <v>18000000</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M149" s="1">
         <v>10000168</v>
@@ -32431,16 +32877,26 @@
       <c r="N149" s="1">
         <v>180</v>
       </c>
-      <c r="O149" s="1"/>
-      <c r="P149" s="1"/>
-      <c r="Q149" s="1"/>
-    </row>
-    <row r="150" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="O149" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P149" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q149" s="1">
+        <v>20</v>
+      </c>
+      <c r="S149" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;180@10000169;20</v>
+      </c>
+    </row>
+    <row r="150" spans="4:24" ht="20.100000000000001" customHeight="1">
       <c r="H150" s="1" t="s">
-        <v>3157</v>
+        <v>3154</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J150" s="1">
         <v>1</v>
@@ -32449,7 +32905,7 @@
         <v>20000000</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M150" s="1">
         <v>10000168</v>
@@ -32461,18 +32917,22 @@
         <v>10000169</v>
       </c>
       <c r="P150" s="1" t="s">
-        <v>3141</v>
+        <v>3138</v>
       </c>
       <c r="Q150" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="151" spans="8:17" ht="20.100000000000001" customHeight="1">
+        <v>20</v>
+      </c>
+      <c r="S150" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;200@10000169;20</v>
+      </c>
+    </row>
+    <row r="151" spans="4:24" ht="20.100000000000001" customHeight="1">
       <c r="H151" s="1" t="s">
-        <v>3158</v>
+        <v>3155</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J151" s="1">
         <v>1</v>
@@ -32481,7 +32941,7 @@
         <v>22000000</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M151" s="1">
         <v>10000168</v>
@@ -32489,16 +32949,26 @@
       <c r="N151" s="1">
         <v>220</v>
       </c>
-      <c r="O151" s="1"/>
-      <c r="P151" s="1"/>
-      <c r="Q151" s="1"/>
-    </row>
-    <row r="152" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="O151" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P151" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q151" s="1">
+        <v>30</v>
+      </c>
+      <c r="S151" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;220@10000169;30</v>
+      </c>
+    </row>
+    <row r="152" spans="4:24" ht="20.100000000000001" customHeight="1">
       <c r="H152" s="1" t="s">
-        <v>3159</v>
+        <v>3156</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J152" s="1">
         <v>1</v>
@@ -32507,7 +32977,7 @@
         <v>24000000</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M152" s="1">
         <v>10000168</v>
@@ -32515,16 +32985,26 @@
       <c r="N152" s="1">
         <v>240</v>
       </c>
-      <c r="O152" s="1"/>
-      <c r="P152" s="1"/>
-      <c r="Q152" s="1"/>
-    </row>
-    <row r="153" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="O152" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P152" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q152" s="1">
+        <v>30</v>
+      </c>
+      <c r="S152" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;240@10000169;30</v>
+      </c>
+    </row>
+    <row r="153" spans="4:24" ht="20.100000000000001" customHeight="1">
       <c r="H153" s="1" t="s">
         <v>50</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J153" s="1">
         <v>1</v>
@@ -32533,7 +33013,7 @@
         <v>26000000</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M153" s="1">
         <v>10000168</v>
@@ -32541,16 +33021,26 @@
       <c r="N153" s="1">
         <v>260</v>
       </c>
-      <c r="O153" s="1"/>
-      <c r="P153" s="1"/>
-      <c r="Q153" s="1"/>
-    </row>
-    <row r="154" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="O153" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P153" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q153" s="1">
+        <v>30</v>
+      </c>
+      <c r="S153" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;260@10000169;30</v>
+      </c>
+    </row>
+    <row r="154" spans="4:24" ht="20.100000000000001" customHeight="1">
       <c r="H154" s="1" t="s">
-        <v>3160</v>
+        <v>3157</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J154" s="1">
         <v>1</v>
@@ -32559,7 +33049,7 @@
         <v>28000000</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M154" s="1">
         <v>10000168</v>
@@ -32567,16 +33057,26 @@
       <c r="N154" s="1">
         <v>280</v>
       </c>
-      <c r="O154" s="1"/>
-      <c r="P154" s="1"/>
-      <c r="Q154" s="1"/>
-    </row>
-    <row r="155" spans="8:17" ht="20.100000000000001" customHeight="1">
+      <c r="O154" s="1">
+        <v>10000169</v>
+      </c>
+      <c r="P154" s="1" t="s">
+        <v>3138</v>
+      </c>
+      <c r="Q154" s="1">
+        <v>30</v>
+      </c>
+      <c r="S154" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;280@10000169;30</v>
+      </c>
+    </row>
+    <row r="155" spans="4:24" ht="20.100000000000001" customHeight="1">
       <c r="H155" s="1" t="s">
         <v>1333</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="J155" s="1">
         <v>1</v>
@@ -32585,7 +33085,7 @@
         <v>30000000</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="M155" s="1">
         <v>10000168</v>
@@ -32597,18 +33097,1471 @@
         <v>10000169</v>
       </c>
       <c r="P155" s="1" t="s">
-        <v>3141</v>
+        <v>3138</v>
       </c>
       <c r="Q155" s="1">
+        <v>30</v>
+      </c>
+      <c r="R155">
+        <f t="shared" ref="R137:R155" si="10">N155/Q155</f>
+        <v>10</v>
+      </c>
+      <c r="S155" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>10000168;300@10000169;30</v>
+      </c>
+    </row>
+    <row r="156" spans="4:24" ht="20.100000000000001" customHeight="1">
+      <c r="R156" s="1">
+        <f>500*5</f>
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="157" spans="4:24" ht="20.100000000000001" customHeight="1"/>
+    <row r="158" spans="4:24" ht="20.100000000000001" customHeight="1">
+      <c r="I158" s="13">
+        <v>130003</v>
+      </c>
+      <c r="J158" s="13"/>
+      <c r="K158" s="120">
+        <v>231003</v>
+      </c>
+    </row>
+    <row r="159" spans="4:24" ht="20.100000000000001" customHeight="1">
+      <c r="F159" s="1">
+        <f>H159*1.5</f>
+        <v>112.5</v>
+      </c>
+      <c r="G159" s="1">
+        <v>1</v>
+      </c>
+      <c r="H159" s="1">
+        <v>75</v>
+      </c>
+      <c r="I159" s="1">
+        <v>75</v>
+      </c>
+      <c r="J159" s="13" t="str">
+        <f>$I$158&amp;";"&amp;I159</f>
+        <v>130003;75</v>
+      </c>
+      <c r="K159" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="L159" t="str">
+        <f>$K$158&amp;";"&amp;K159</f>
+        <v>231003;0.01</v>
+      </c>
+      <c r="P159" t="str">
+        <f>J159&amp;"@"&amp;L159</f>
+        <v>130003;75@231003;0.01</v>
+      </c>
+    </row>
+    <row r="160" spans="4:24" ht="20.100000000000001" customHeight="1">
+      <c r="F160" s="1">
+        <f t="shared" ref="F160:F178" si="11">H160*1.5</f>
+        <v>112.5</v>
+      </c>
+      <c r="G160" s="1">
+        <v>2</v>
+      </c>
+      <c r="H160" s="1">
+        <v>75</v>
+      </c>
+      <c r="I160" s="1">
+        <f>I159+H159</f>
+        <v>150</v>
+      </c>
+      <c r="J160" s="13" t="str">
+        <f t="shared" ref="J160:J178" si="12">$I$158&amp;";"&amp;I160</f>
+        <v>130003;150</v>
+      </c>
+      <c r="K160" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="L160" t="str">
+        <f t="shared" ref="L160:L178" si="13">$K$158&amp;";"&amp;K160</f>
+        <v>231003;0.02</v>
+      </c>
+      <c r="P160" t="str">
+        <f t="shared" ref="P160:P178" si="14">J160&amp;"@"&amp;L160</f>
+        <v>130003;150@231003;0.02</v>
+      </c>
+    </row>
+    <row r="161" spans="6:16" ht="20.100000000000001" customHeight="1">
+      <c r="F161" s="1">
+        <f t="shared" si="11"/>
+        <v>112.5</v>
+      </c>
+      <c r="G161" s="1">
+        <v>3</v>
+      </c>
+      <c r="H161" s="1">
+        <v>75</v>
+      </c>
+      <c r="I161" s="1">
+        <f t="shared" ref="I161:I178" si="15">I160+H160</f>
+        <v>225</v>
+      </c>
+      <c r="J161" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;225</v>
+      </c>
+      <c r="K161" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="L161" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.03</v>
+      </c>
+      <c r="P161" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;225@231003;0.03</v>
+      </c>
+    </row>
+    <row r="162" spans="6:16">
+      <c r="F162" s="1">
+        <f t="shared" si="11"/>
+        <v>150</v>
+      </c>
+      <c r="G162" s="1">
+        <v>4</v>
+      </c>
+      <c r="H162" s="1">
+        <v>100</v>
+      </c>
+      <c r="I162" s="1">
+        <f t="shared" si="15"/>
+        <v>300</v>
+      </c>
+      <c r="J162" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;300</v>
+      </c>
+      <c r="K162" s="13">
+        <v>0.04</v>
+      </c>
+      <c r="L162" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.04</v>
+      </c>
+      <c r="P162" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;300@231003;0.04</v>
+      </c>
+    </row>
+    <row r="163" spans="6:16">
+      <c r="F163" s="1">
+        <f t="shared" si="11"/>
+        <v>150</v>
+      </c>
+      <c r="G163" s="1">
+        <v>5</v>
+      </c>
+      <c r="H163" s="1">
+        <v>100</v>
+      </c>
+      <c r="I163" s="1">
+        <f t="shared" si="15"/>
+        <v>400</v>
+      </c>
+      <c r="J163" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;400</v>
+      </c>
+      <c r="K163" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="L163" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.05</v>
+      </c>
+      <c r="P163" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;400@231003;0.05</v>
+      </c>
+    </row>
+    <row r="164" spans="6:16">
+      <c r="F164" s="1">
+        <f t="shared" si="11"/>
+        <v>225</v>
+      </c>
+      <c r="G164" s="1">
+        <v>6</v>
+      </c>
+      <c r="H164" s="1">
+        <v>150</v>
+      </c>
+      <c r="I164" s="1">
+        <f t="shared" si="15"/>
+        <v>500</v>
+      </c>
+      <c r="J164" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;500</v>
+      </c>
+      <c r="K164" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="L164" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.06</v>
+      </c>
+      <c r="P164" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;500@231003;0.06</v>
+      </c>
+    </row>
+    <row r="165" spans="6:16">
+      <c r="F165" s="1">
+        <f t="shared" si="11"/>
+        <v>225</v>
+      </c>
+      <c r="G165" s="1">
+        <v>7</v>
+      </c>
+      <c r="H165" s="1">
+        <v>150</v>
+      </c>
+      <c r="I165" s="1">
+        <f t="shared" si="15"/>
+        <v>650</v>
+      </c>
+      <c r="J165" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;650</v>
+      </c>
+      <c r="K165" s="13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L165" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.07</v>
+      </c>
+      <c r="P165" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;650@231003;0.07</v>
+      </c>
+    </row>
+    <row r="166" spans="6:16">
+      <c r="F166" s="1">
+        <f t="shared" si="11"/>
+        <v>300</v>
+      </c>
+      <c r="G166" s="1">
+        <v>8</v>
+      </c>
+      <c r="H166" s="1">
+        <v>200</v>
+      </c>
+      <c r="I166" s="1">
+        <f t="shared" si="15"/>
+        <v>800</v>
+      </c>
+      <c r="J166" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;800</v>
+      </c>
+      <c r="K166" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="L166" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.08</v>
+      </c>
+      <c r="P166" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;800@231003;0.08</v>
+      </c>
+    </row>
+    <row r="167" spans="6:16">
+      <c r="F167" s="1">
+        <f t="shared" si="11"/>
+        <v>300</v>
+      </c>
+      <c r="G167" s="1">
+        <v>9</v>
+      </c>
+      <c r="H167" s="1">
+        <v>200</v>
+      </c>
+      <c r="I167" s="1">
+        <f t="shared" si="15"/>
+        <v>1000</v>
+      </c>
+      <c r="J167" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;1000</v>
+      </c>
+      <c r="K167" s="13">
+        <v>0.09</v>
+      </c>
+      <c r="L167" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.09</v>
+      </c>
+      <c r="P167" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;1000@231003;0.09</v>
+      </c>
+    </row>
+    <row r="168" spans="6:16">
+      <c r="F168" s="1">
+        <f t="shared" si="11"/>
+        <v>375</v>
+      </c>
+      <c r="G168" s="1">
+        <v>10</v>
+      </c>
+      <c r="H168" s="1">
+        <v>250</v>
+      </c>
+      <c r="I168" s="1">
+        <f t="shared" si="15"/>
+        <v>1200</v>
+      </c>
+      <c r="J168" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;1200</v>
+      </c>
+      <c r="K168" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="L168" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.1</v>
+      </c>
+      <c r="P168" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;1200@231003;0.1</v>
+      </c>
+    </row>
+    <row r="169" spans="6:16">
+      <c r="F169" s="1">
+        <f t="shared" si="11"/>
+        <v>375</v>
+      </c>
+      <c r="G169" s="1">
+        <v>11</v>
+      </c>
+      <c r="H169" s="1">
+        <v>250</v>
+      </c>
+      <c r="I169" s="1">
+        <f t="shared" si="15"/>
+        <v>1450</v>
+      </c>
+      <c r="J169" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;1450</v>
+      </c>
+      <c r="K169" s="13">
+        <v>0.11</v>
+      </c>
+      <c r="L169" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.11</v>
+      </c>
+      <c r="P169" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;1450@231003;0.11</v>
+      </c>
+    </row>
+    <row r="170" spans="6:16">
+      <c r="F170" s="1">
+        <f t="shared" si="11"/>
+        <v>450</v>
+      </c>
+      <c r="G170" s="1">
+        <v>12</v>
+      </c>
+      <c r="H170" s="1">
+        <v>300</v>
+      </c>
+      <c r="I170" s="1">
+        <f t="shared" si="15"/>
+        <v>1700</v>
+      </c>
+      <c r="J170" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;1700</v>
+      </c>
+      <c r="K170" s="13">
+        <v>0.12</v>
+      </c>
+      <c r="L170" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.12</v>
+      </c>
+      <c r="P170" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;1700@231003;0.12</v>
+      </c>
+    </row>
+    <row r="171" spans="6:16">
+      <c r="F171" s="1">
+        <f t="shared" si="11"/>
+        <v>600</v>
+      </c>
+      <c r="G171" s="1">
+        <v>13</v>
+      </c>
+      <c r="H171" s="1">
+        <v>400</v>
+      </c>
+      <c r="I171" s="1">
+        <f t="shared" si="15"/>
+        <v>2000</v>
+      </c>
+      <c r="J171" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;2000</v>
+      </c>
+      <c r="K171" s="13">
+        <v>0.13</v>
+      </c>
+      <c r="L171" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.13</v>
+      </c>
+      <c r="P171" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;2000@231003;0.13</v>
+      </c>
+    </row>
+    <row r="172" spans="6:16">
+      <c r="F172" s="1">
+        <f t="shared" si="11"/>
+        <v>900</v>
+      </c>
+      <c r="G172" s="1">
+        <v>14</v>
+      </c>
+      <c r="H172" s="1">
+        <v>600</v>
+      </c>
+      <c r="I172" s="1">
+        <f t="shared" si="15"/>
+        <v>2400</v>
+      </c>
+      <c r="J172" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;2400</v>
+      </c>
+      <c r="K172" s="13">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L172" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.14</v>
+      </c>
+      <c r="P172" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;2400@231003;0.14</v>
+      </c>
+    </row>
+    <row r="173" spans="6:16">
+      <c r="F173" s="1">
+        <f t="shared" si="11"/>
+        <v>900</v>
+      </c>
+      <c r="G173" s="1">
+        <v>15</v>
+      </c>
+      <c r="H173" s="1">
+        <v>600</v>
+      </c>
+      <c r="I173" s="1">
+        <f t="shared" si="15"/>
+        <v>3000</v>
+      </c>
+      <c r="J173" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;3000</v>
+      </c>
+      <c r="K173" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="L173" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.15</v>
+      </c>
+      <c r="P173" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;3000@231003;0.15</v>
+      </c>
+    </row>
+    <row r="174" spans="6:16">
+      <c r="F174" s="1">
+        <f t="shared" si="11"/>
+        <v>1200</v>
+      </c>
+      <c r="G174" s="1">
+        <v>16</v>
+      </c>
+      <c r="H174" s="1">
+        <v>800</v>
+      </c>
+      <c r="I174" s="1">
+        <f t="shared" si="15"/>
+        <v>3600</v>
+      </c>
+      <c r="J174" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;3600</v>
+      </c>
+      <c r="K174" s="13">
+        <v>0.16</v>
+      </c>
+      <c r="L174" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.16</v>
+      </c>
+      <c r="P174" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;3600@231003;0.16</v>
+      </c>
+    </row>
+    <row r="175" spans="6:16">
+      <c r="F175" s="1">
+        <f t="shared" si="11"/>
+        <v>1200</v>
+      </c>
+      <c r="G175" s="1">
+        <v>17</v>
+      </c>
+      <c r="H175" s="1">
+        <v>800</v>
+      </c>
+      <c r="I175" s="1">
+        <f t="shared" si="15"/>
+        <v>4400</v>
+      </c>
+      <c r="J175" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;4400</v>
+      </c>
+      <c r="K175" s="13">
+        <v>0.17</v>
+      </c>
+      <c r="L175" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.17</v>
+      </c>
+      <c r="P175" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;4400@231003;0.17</v>
+      </c>
+    </row>
+    <row r="176" spans="6:16">
+      <c r="F176" s="1">
+        <f t="shared" si="11"/>
+        <v>1500</v>
+      </c>
+      <c r="G176" s="1">
+        <v>18</v>
+      </c>
+      <c r="H176" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I176" s="1">
+        <f t="shared" si="15"/>
+        <v>5200</v>
+      </c>
+      <c r="J176" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;5200</v>
+      </c>
+      <c r="K176" s="13">
+        <v>0.18</v>
+      </c>
+      <c r="L176" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.18</v>
+      </c>
+      <c r="P176" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;5200@231003;0.18</v>
+      </c>
+    </row>
+    <row r="177" spans="6:16">
+      <c r="F177" s="1">
+        <f t="shared" si="11"/>
+        <v>1500</v>
+      </c>
+      <c r="G177" s="1">
+        <v>19</v>
+      </c>
+      <c r="H177" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I177" s="1">
+        <f t="shared" si="15"/>
+        <v>6200</v>
+      </c>
+      <c r="J177" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;6200</v>
+      </c>
+      <c r="K177" s="13">
+        <v>0.19</v>
+      </c>
+      <c r="L177" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.19</v>
+      </c>
+      <c r="P177" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;6200@231003;0.19</v>
+      </c>
+    </row>
+    <row r="178" spans="6:16">
+      <c r="F178" s="1">
+        <f t="shared" si="11"/>
+        <v>1500</v>
+      </c>
+      <c r="G178" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="156" spans="8:17" ht="20.100000000000001" customHeight="1"/>
-    <row r="157" spans="8:17" ht="20.100000000000001" customHeight="1"/>
-    <row r="158" spans="8:17" ht="20.100000000000001" customHeight="1"/>
-    <row r="159" spans="8:17" ht="20.100000000000001" customHeight="1"/>
-    <row r="160" spans="8:17" ht="20.100000000000001" customHeight="1"/>
-    <row r="161" ht="20.100000000000001" customHeight="1"/>
+      <c r="H178" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I178" s="1">
+        <f t="shared" si="15"/>
+        <v>7200</v>
+      </c>
+      <c r="J178" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v>130003;7200</v>
+      </c>
+      <c r="K178" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="L178" t="str">
+        <f t="shared" si="13"/>
+        <v>231003;0.2</v>
+      </c>
+      <c r="P178" t="str">
+        <f t="shared" si="14"/>
+        <v>130003;7200@231003;0.2</v>
+      </c>
+    </row>
+    <row r="180" spans="6:16">
+      <c r="I180" s="120">
+        <v>130403</v>
+      </c>
+      <c r="J180" s="120"/>
+      <c r="K180" s="120">
+        <v>231403</v>
+      </c>
+      <c r="L180" s="1"/>
+      <c r="M180" s="1">
+        <v>230703</v>
+      </c>
+    </row>
+    <row r="181" spans="6:16">
+      <c r="F181">
+        <f>I181*5</f>
+        <v>375</v>
+      </c>
+      <c r="G181">
+        <v>1</v>
+      </c>
+      <c r="H181" s="1">
+        <v>75</v>
+      </c>
+      <c r="I181" s="1">
+        <v>75</v>
+      </c>
+      <c r="J181" s="13" t="str">
+        <f>$I$180&amp;";"&amp;F181</f>
+        <v>130403;375</v>
+      </c>
+      <c r="K181" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="L181" t="str">
+        <f>$K$180&amp;";"&amp;K181</f>
+        <v>231403;0.005</v>
+      </c>
+      <c r="M181" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="N181" t="str">
+        <f>$M$180&amp;";"&amp;M181</f>
+        <v>230703;0.01</v>
+      </c>
+      <c r="P181" t="str">
+        <f>J181&amp;"@"&amp;L181&amp;"@"&amp;N181</f>
+        <v>130403;375@231403;0.005@230703;0.01</v>
+      </c>
+    </row>
+    <row r="182" spans="6:16">
+      <c r="F182">
+        <f t="shared" ref="F182:F200" si="16">I182*5</f>
+        <v>750</v>
+      </c>
+      <c r="G182">
+        <v>2</v>
+      </c>
+      <c r="H182" s="1">
+        <v>75</v>
+      </c>
+      <c r="I182" s="1">
+        <f>I181+H181</f>
+        <v>150</v>
+      </c>
+      <c r="J182" s="13" t="str">
+        <f t="shared" ref="J182:J200" si="17">$I$180&amp;";"&amp;F182</f>
+        <v>130403;750</v>
+      </c>
+      <c r="K182" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="L182" t="str">
+        <f t="shared" ref="L182:L200" si="18">$K$180&amp;";"&amp;K182</f>
+        <v>231403;0.01</v>
+      </c>
+      <c r="M182" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="N182" t="str">
+        <f t="shared" ref="N182:N200" si="19">$M$180&amp;";"&amp;M182</f>
+        <v>230703;0.02</v>
+      </c>
+      <c r="P182" t="str">
+        <f t="shared" ref="P182:P200" si="20">J182&amp;"@"&amp;L182&amp;"@"&amp;N182</f>
+        <v>130403;750@231403;0.01@230703;0.02</v>
+      </c>
+    </row>
+    <row r="183" spans="6:16">
+      <c r="F183">
+        <f t="shared" si="16"/>
+        <v>1125</v>
+      </c>
+      <c r="G183">
+        <v>3</v>
+      </c>
+      <c r="H183" s="1">
+        <v>75</v>
+      </c>
+      <c r="I183" s="1">
+        <f t="shared" ref="I183:I200" si="21">I182+H182</f>
+        <v>225</v>
+      </c>
+      <c r="J183" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;1125</v>
+      </c>
+      <c r="K183" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="L183" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.015</v>
+      </c>
+      <c r="M183" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="N183" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.03</v>
+      </c>
+      <c r="P183" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;1125@231403;0.015@230703;0.03</v>
+      </c>
+    </row>
+    <row r="184" spans="6:16">
+      <c r="F184">
+        <f t="shared" si="16"/>
+        <v>1500</v>
+      </c>
+      <c r="G184">
+        <v>4</v>
+      </c>
+      <c r="H184" s="1">
+        <v>100</v>
+      </c>
+      <c r="I184" s="1">
+        <f t="shared" si="21"/>
+        <v>300</v>
+      </c>
+      <c r="J184" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;1500</v>
+      </c>
+      <c r="K184" s="13">
+        <v>0.02</v>
+      </c>
+      <c r="L184" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.02</v>
+      </c>
+      <c r="M184" s="13">
+        <v>0.04</v>
+      </c>
+      <c r="N184" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.04</v>
+      </c>
+      <c r="P184" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;1500@231403;0.02@230703;0.04</v>
+      </c>
+    </row>
+    <row r="185" spans="6:16">
+      <c r="F185">
+        <f t="shared" si="16"/>
+        <v>2000</v>
+      </c>
+      <c r="G185">
+        <v>5</v>
+      </c>
+      <c r="H185" s="1">
+        <v>100</v>
+      </c>
+      <c r="I185" s="1">
+        <f t="shared" si="21"/>
+        <v>400</v>
+      </c>
+      <c r="J185" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;2000</v>
+      </c>
+      <c r="K185" s="13">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L185" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.025</v>
+      </c>
+      <c r="M185" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="N185" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.05</v>
+      </c>
+      <c r="P185" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;2000@231403;0.025@230703;0.05</v>
+      </c>
+    </row>
+    <row r="186" spans="6:16">
+      <c r="F186">
+        <f t="shared" si="16"/>
+        <v>2500</v>
+      </c>
+      <c r="G186">
+        <v>6</v>
+      </c>
+      <c r="H186" s="1">
+        <v>150</v>
+      </c>
+      <c r="I186" s="1">
+        <f t="shared" si="21"/>
+        <v>500</v>
+      </c>
+      <c r="J186" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;2500</v>
+      </c>
+      <c r="K186" s="13">
+        <v>0.03</v>
+      </c>
+      <c r="L186" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.03</v>
+      </c>
+      <c r="M186" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="N186" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.06</v>
+      </c>
+      <c r="P186" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;2500@231403;0.03@230703;0.06</v>
+      </c>
+    </row>
+    <row r="187" spans="6:16">
+      <c r="F187">
+        <f t="shared" si="16"/>
+        <v>3250</v>
+      </c>
+      <c r="G187">
+        <v>7</v>
+      </c>
+      <c r="H187" s="1">
+        <v>150</v>
+      </c>
+      <c r="I187" s="1">
+        <f t="shared" si="21"/>
+        <v>650</v>
+      </c>
+      <c r="J187" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;3250</v>
+      </c>
+      <c r="K187" s="13">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="L187" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.035</v>
+      </c>
+      <c r="M187" s="13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N187" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.07</v>
+      </c>
+      <c r="P187" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;3250@231403;0.035@230703;0.07</v>
+      </c>
+    </row>
+    <row r="188" spans="6:16">
+      <c r="F188">
+        <f t="shared" si="16"/>
+        <v>4000</v>
+      </c>
+      <c r="G188">
+        <v>8</v>
+      </c>
+      <c r="H188" s="1">
+        <v>200</v>
+      </c>
+      <c r="I188" s="1">
+        <f t="shared" si="21"/>
+        <v>800</v>
+      </c>
+      <c r="J188" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;4000</v>
+      </c>
+      <c r="K188" s="13">
+        <v>0.04</v>
+      </c>
+      <c r="L188" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.04</v>
+      </c>
+      <c r="M188" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="N188" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.08</v>
+      </c>
+      <c r="P188" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;4000@231403;0.04@230703;0.08</v>
+      </c>
+    </row>
+    <row r="189" spans="6:16">
+      <c r="F189">
+        <f t="shared" si="16"/>
+        <v>5000</v>
+      </c>
+      <c r="G189">
+        <v>9</v>
+      </c>
+      <c r="H189" s="1">
+        <v>200</v>
+      </c>
+      <c r="I189" s="1">
+        <f t="shared" si="21"/>
+        <v>1000</v>
+      </c>
+      <c r="J189" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;5000</v>
+      </c>
+      <c r="K189" s="13">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="L189" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.045</v>
+      </c>
+      <c r="M189" s="13">
+        <v>0.09</v>
+      </c>
+      <c r="N189" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.09</v>
+      </c>
+      <c r="P189" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;5000@231403;0.045@230703;0.09</v>
+      </c>
+    </row>
+    <row r="190" spans="6:16">
+      <c r="F190">
+        <f t="shared" si="16"/>
+        <v>6000</v>
+      </c>
+      <c r="G190">
+        <v>10</v>
+      </c>
+      <c r="H190" s="1">
+        <v>250</v>
+      </c>
+      <c r="I190" s="1">
+        <f t="shared" si="21"/>
+        <v>1200</v>
+      </c>
+      <c r="J190" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;6000</v>
+      </c>
+      <c r="K190" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="L190" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.05</v>
+      </c>
+      <c r="M190" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="N190" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.1</v>
+      </c>
+      <c r="P190" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;6000@231403;0.05@230703;0.1</v>
+      </c>
+    </row>
+    <row r="191" spans="6:16">
+      <c r="F191">
+        <f t="shared" si="16"/>
+        <v>7250</v>
+      </c>
+      <c r="G191">
+        <v>11</v>
+      </c>
+      <c r="H191" s="1">
+        <v>250</v>
+      </c>
+      <c r="I191" s="1">
+        <f t="shared" si="21"/>
+        <v>1450</v>
+      </c>
+      <c r="J191" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;7250</v>
+      </c>
+      <c r="K191" s="13">
+        <v>5.5E-2</v>
+      </c>
+      <c r="L191" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.055</v>
+      </c>
+      <c r="M191" s="13">
+        <v>0.11</v>
+      </c>
+      <c r="N191" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.11</v>
+      </c>
+      <c r="P191" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;7250@231403;0.055@230703;0.11</v>
+      </c>
+    </row>
+    <row r="192" spans="6:16">
+      <c r="F192">
+        <f t="shared" si="16"/>
+        <v>8500</v>
+      </c>
+      <c r="G192">
+        <v>12</v>
+      </c>
+      <c r="H192" s="1">
+        <v>300</v>
+      </c>
+      <c r="I192" s="1">
+        <f t="shared" si="21"/>
+        <v>1700</v>
+      </c>
+      <c r="J192" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;8500</v>
+      </c>
+      <c r="K192" s="13">
+        <v>0.06</v>
+      </c>
+      <c r="L192" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.06</v>
+      </c>
+      <c r="M192" s="13">
+        <v>0.12</v>
+      </c>
+      <c r="N192" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.12</v>
+      </c>
+      <c r="P192" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;8500@231403;0.06@230703;0.12</v>
+      </c>
+    </row>
+    <row r="193" spans="4:16">
+      <c r="F193">
+        <f t="shared" si="16"/>
+        <v>10000</v>
+      </c>
+      <c r="G193">
+        <v>13</v>
+      </c>
+      <c r="H193" s="1">
+        <v>400</v>
+      </c>
+      <c r="I193" s="1">
+        <f t="shared" si="21"/>
+        <v>2000</v>
+      </c>
+      <c r="J193" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;10000</v>
+      </c>
+      <c r="K193" s="13">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="L193" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.065</v>
+      </c>
+      <c r="M193" s="13">
+        <v>0.13</v>
+      </c>
+      <c r="N193" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.13</v>
+      </c>
+      <c r="P193" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;10000@231403;0.065@230703;0.13</v>
+      </c>
+    </row>
+    <row r="194" spans="4:16">
+      <c r="F194">
+        <f t="shared" si="16"/>
+        <v>12000</v>
+      </c>
+      <c r="G194">
+        <v>14</v>
+      </c>
+      <c r="H194" s="1">
+        <v>600</v>
+      </c>
+      <c r="I194" s="1">
+        <f t="shared" si="21"/>
+        <v>2400</v>
+      </c>
+      <c r="J194" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;12000</v>
+      </c>
+      <c r="K194" s="13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L194" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.07</v>
+      </c>
+      <c r="M194" s="13">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="N194" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.14</v>
+      </c>
+      <c r="P194" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;12000@231403;0.07@230703;0.14</v>
+      </c>
+    </row>
+    <row r="195" spans="4:16">
+      <c r="F195">
+        <f t="shared" si="16"/>
+        <v>15000</v>
+      </c>
+      <c r="G195">
+        <v>15</v>
+      </c>
+      <c r="H195" s="1">
+        <v>600</v>
+      </c>
+      <c r="I195" s="1">
+        <f t="shared" si="21"/>
+        <v>3000</v>
+      </c>
+      <c r="J195" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;15000</v>
+      </c>
+      <c r="K195" s="13">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="L195" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.075</v>
+      </c>
+      <c r="M195" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="N195" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.15</v>
+      </c>
+      <c r="P195" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;15000@231403;0.075@230703;0.15</v>
+      </c>
+    </row>
+    <row r="196" spans="4:16">
+      <c r="F196">
+        <f t="shared" si="16"/>
+        <v>18000</v>
+      </c>
+      <c r="G196">
+        <v>16</v>
+      </c>
+      <c r="H196" s="1">
+        <v>800</v>
+      </c>
+      <c r="I196" s="1">
+        <f t="shared" si="21"/>
+        <v>3600</v>
+      </c>
+      <c r="J196" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;18000</v>
+      </c>
+      <c r="K196" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="L196" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.08</v>
+      </c>
+      <c r="M196" s="13">
+        <v>0.16</v>
+      </c>
+      <c r="N196" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.16</v>
+      </c>
+      <c r="P196" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;18000@231403;0.08@230703;0.16</v>
+      </c>
+    </row>
+    <row r="197" spans="4:16">
+      <c r="F197">
+        <f t="shared" si="16"/>
+        <v>22000</v>
+      </c>
+      <c r="G197">
+        <v>17</v>
+      </c>
+      <c r="H197" s="1">
+        <v>800</v>
+      </c>
+      <c r="I197" s="1">
+        <f t="shared" si="21"/>
+        <v>4400</v>
+      </c>
+      <c r="J197" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;22000</v>
+      </c>
+      <c r="K197" s="13">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="L197" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.085</v>
+      </c>
+      <c r="M197" s="13">
+        <v>0.17</v>
+      </c>
+      <c r="N197" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.17</v>
+      </c>
+      <c r="P197" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;22000@231403;0.085@230703;0.17</v>
+      </c>
+    </row>
+    <row r="198" spans="4:16">
+      <c r="F198">
+        <f t="shared" si="16"/>
+        <v>26000</v>
+      </c>
+      <c r="G198">
+        <v>18</v>
+      </c>
+      <c r="H198" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I198" s="1">
+        <f t="shared" si="21"/>
+        <v>5200</v>
+      </c>
+      <c r="J198" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;26000</v>
+      </c>
+      <c r="K198" s="13">
+        <v>0.09</v>
+      </c>
+      <c r="L198" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.09</v>
+      </c>
+      <c r="M198" s="13">
+        <v>0.18</v>
+      </c>
+      <c r="N198" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.18</v>
+      </c>
+      <c r="P198" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;26000@231403;0.09@230703;0.18</v>
+      </c>
+    </row>
+    <row r="199" spans="4:16">
+      <c r="F199">
+        <f t="shared" si="16"/>
+        <v>31000</v>
+      </c>
+      <c r="G199">
+        <v>19</v>
+      </c>
+      <c r="H199" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I199" s="1">
+        <f t="shared" si="21"/>
+        <v>6200</v>
+      </c>
+      <c r="J199" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;31000</v>
+      </c>
+      <c r="K199" s="13">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="L199" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.095</v>
+      </c>
+      <c r="M199" s="13">
+        <v>0.19</v>
+      </c>
+      <c r="N199" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.19</v>
+      </c>
+      <c r="P199" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;31000@231403;0.095@230703;0.19</v>
+      </c>
+    </row>
+    <row r="200" spans="4:16">
+      <c r="F200">
+        <f t="shared" si="16"/>
+        <v>36000</v>
+      </c>
+      <c r="G200">
+        <v>20</v>
+      </c>
+      <c r="H200" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I200" s="1">
+        <f t="shared" si="21"/>
+        <v>7200</v>
+      </c>
+      <c r="J200" s="13" t="str">
+        <f t="shared" si="17"/>
+        <v>130403;36000</v>
+      </c>
+      <c r="K200" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="L200" t="str">
+        <f t="shared" si="18"/>
+        <v>231403;0.1</v>
+      </c>
+      <c r="M200" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="N200" t="str">
+        <f t="shared" si="19"/>
+        <v>230703;0.2</v>
+      </c>
+      <c r="P200" t="str">
+        <f t="shared" si="20"/>
+        <v>130403;36000@231403;0.1@230703;0.2</v>
+      </c>
+    </row>
+    <row r="207" spans="4:16">
+      <c r="D207" s="105" t="s">
+        <v>3174</v>
+      </c>
+      <c r="E207" s="121" t="s">
+        <v>3167</v>
+      </c>
+      <c r="F207" t="s">
+        <v>3166</v>
+      </c>
+    </row>
+    <row r="208" spans="4:16">
+      <c r="D208" s="105" t="s">
+        <v>3168</v>
+      </c>
+      <c r="E208" s="121" t="s">
+        <v>3167</v>
+      </c>
+      <c r="F208" s="105" t="s">
+        <v>3171</v>
+      </c>
+    </row>
+    <row r="209" spans="4:6">
+      <c r="D209" s="105" t="s">
+        <v>3169</v>
+      </c>
+      <c r="E209" s="121" t="s">
+        <v>3167</v>
+      </c>
+      <c r="F209" s="105" t="s">
+        <v>3172</v>
+      </c>
+    </row>
+    <row r="210" spans="4:6">
+      <c r="D210" s="105" t="s">
+        <v>3170</v>
+      </c>
+      <c r="E210" s="121" t="s">
+        <v>3167</v>
+      </c>
+      <c r="F210" s="105" t="s">
+        <v>3173</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -66772,7 +68725,7 @@
       <c r="J3" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="120" t="s">
+      <c r="K3" s="122" t="s">
         <v>50</v>
       </c>
       <c r="L3" s="68" t="s">
@@ -66854,7 +68807,7 @@
       <c r="I4" s="78">
         <v>10002</v>
       </c>
-      <c r="K4" s="120"/>
+      <c r="K4" s="122"/>
       <c r="L4" s="68" t="s">
         <v>61</v>
       </c>
@@ -66909,7 +68862,7 @@
       <c r="AW4" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="AX4" s="120" t="s">
+      <c r="AX4" s="122" t="s">
         <v>50</v>
       </c>
       <c r="AY4" s="68" t="s">
@@ -66965,7 +68918,7 @@
       <c r="I5" s="78">
         <v>10003</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K5" s="122"/>
       <c r="L5" s="68" t="s">
         <v>81</v>
       </c>
@@ -67017,7 +68970,7 @@
       <c r="AV5" s="68">
         <v>10002</v>
       </c>
-      <c r="AX5" s="120"/>
+      <c r="AX5" s="122"/>
       <c r="AY5" s="68" t="s">
         <v>61</v>
       </c>
@@ -67063,7 +69016,7 @@
       <c r="I6" s="78">
         <v>10011</v>
       </c>
-      <c r="K6" s="120" t="s">
+      <c r="K6" s="122" t="s">
         <v>101</v>
       </c>
       <c r="L6" s="68" t="s">
@@ -67093,7 +69046,7 @@
       <c r="AV6" s="68">
         <v>10003</v>
       </c>
-      <c r="AX6" s="120"/>
+      <c r="AX6" s="122"/>
       <c r="AY6" s="68" t="s">
         <v>81</v>
       </c>
@@ -67123,7 +69076,7 @@
       <c r="I7" s="78">
         <v>10012</v>
       </c>
-      <c r="K7" s="120"/>
+      <c r="K7" s="122"/>
       <c r="L7" s="68" t="s">
         <v>61</v>
       </c>
@@ -67169,7 +69122,7 @@
       <c r="AV7" s="68">
         <v>10011</v>
       </c>
-      <c r="AX7" s="120" t="s">
+      <c r="AX7" s="122" t="s">
         <v>101</v>
       </c>
       <c r="AY7" s="68" t="s">
@@ -67216,7 +69169,7 @@
       <c r="I8" s="78">
         <v>10013</v>
       </c>
-      <c r="K8" s="120"/>
+      <c r="K8" s="122"/>
       <c r="L8" s="68" t="s">
         <v>81</v>
       </c>
@@ -67256,7 +69209,7 @@
       <c r="AV8" s="68">
         <v>10012</v>
       </c>
-      <c r="AX8" s="120"/>
+      <c r="AX8" s="122"/>
       <c r="AY8" s="68" t="s">
         <v>61</v>
       </c>
@@ -67290,7 +69243,7 @@
       <c r="CO8" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="CP8" s="120" t="s">
+      <c r="CP8" s="122" t="s">
         <v>50</v>
       </c>
       <c r="CQ8" s="68" t="s">
@@ -67309,7 +69262,7 @@
       <c r="I9" s="78">
         <v>10021</v>
       </c>
-      <c r="K9" s="120" t="s">
+      <c r="K9" s="122" t="s">
         <v>142</v>
       </c>
       <c r="L9" s="68" t="s">
@@ -67333,7 +69286,7 @@
       <c r="AV9" s="68">
         <v>10013</v>
       </c>
-      <c r="AX9" s="120"/>
+      <c r="AX9" s="122"/>
       <c r="AY9" s="68" t="s">
         <v>81</v>
       </c>
@@ -67352,7 +69305,7 @@
       <c r="CN9" s="78">
         <v>10002</v>
       </c>
-      <c r="CP9" s="120"/>
+      <c r="CP9" s="122"/>
       <c r="CQ9" s="68" t="s">
         <v>61</v>
       </c>
@@ -67380,7 +69333,7 @@
       <c r="I10" s="78">
         <v>10022</v>
       </c>
-      <c r="K10" s="120"/>
+      <c r="K10" s="122"/>
       <c r="L10" s="68" t="s">
         <v>61</v>
       </c>
@@ -67424,7 +69377,7 @@
       <c r="AV10" s="68">
         <v>10021</v>
       </c>
-      <c r="AX10" s="120" t="s">
+      <c r="AX10" s="122" t="s">
         <v>142</v>
       </c>
       <c r="AY10" s="68" t="s">
@@ -67440,7 +69393,7 @@
       <c r="CN10" s="78">
         <v>10003</v>
       </c>
-      <c r="CP10" s="120"/>
+      <c r="CP10" s="122"/>
       <c r="CQ10" s="68" t="s">
         <v>81</v>
       </c>
@@ -67467,7 +69420,7 @@
       <c r="I11" s="78">
         <v>10023</v>
       </c>
-      <c r="K11" s="120"/>
+      <c r="K11" s="122"/>
       <c r="L11" s="68" t="s">
         <v>81</v>
       </c>
@@ -67519,7 +69472,7 @@
       <c r="AV11" s="68">
         <v>10022</v>
       </c>
-      <c r="AX11" s="120"/>
+      <c r="AX11" s="122"/>
       <c r="AY11" s="68" t="s">
         <v>61</v>
       </c>
@@ -67557,7 +69510,7 @@
       <c r="CN11" s="78">
         <v>10011</v>
       </c>
-      <c r="CP11" s="120" t="s">
+      <c r="CP11" s="122" t="s">
         <v>101</v>
       </c>
       <c r="CQ11" s="68" t="s">
@@ -67577,7 +69530,7 @@
       <c r="I12" s="78">
         <v>10031</v>
       </c>
-      <c r="K12" s="120" t="s">
+      <c r="K12" s="122" t="s">
         <v>186</v>
       </c>
       <c r="L12" s="68" t="s">
@@ -67610,7 +69563,7 @@
       <c r="AV12" s="68">
         <v>10023</v>
       </c>
-      <c r="AX12" s="120"/>
+      <c r="AX12" s="122"/>
       <c r="AY12" s="68" t="s">
         <v>81</v>
       </c>
@@ -67659,7 +69612,7 @@
       <c r="CN12" s="78">
         <v>10012</v>
       </c>
-      <c r="CP12" s="120"/>
+      <c r="CP12" s="122"/>
       <c r="CQ12" s="68" t="s">
         <v>61</v>
       </c>
@@ -67680,7 +69633,7 @@
       <c r="I13" s="78">
         <v>10032</v>
       </c>
-      <c r="K13" s="120"/>
+      <c r="K13" s="122"/>
       <c r="L13" s="68" t="s">
         <v>61</v>
       </c>
@@ -67708,7 +69661,7 @@
       <c r="AV13" s="68">
         <v>10031</v>
       </c>
-      <c r="AX13" s="120" t="s">
+      <c r="AX13" s="122" t="s">
         <v>186</v>
       </c>
       <c r="AY13" s="68" t="s">
@@ -67744,7 +69697,7 @@
       <c r="CN13" s="78">
         <v>10013</v>
       </c>
-      <c r="CP13" s="120"/>
+      <c r="CP13" s="122"/>
       <c r="CQ13" s="68" t="s">
         <v>81</v>
       </c>
@@ -67776,7 +69729,7 @@
       <c r="I14" s="78">
         <v>10033</v>
       </c>
-      <c r="K14" s="120"/>
+      <c r="K14" s="122"/>
       <c r="L14" s="68" t="s">
         <v>81</v>
       </c>
@@ -67807,7 +69760,7 @@
       <c r="AV14" s="68">
         <v>10032</v>
       </c>
-      <c r="AX14" s="120"/>
+      <c r="AX14" s="122"/>
       <c r="AY14" s="68" t="s">
         <v>61</v>
       </c>
@@ -67842,7 +69795,7 @@
       <c r="CN14" s="78">
         <v>10021</v>
       </c>
-      <c r="CP14" s="120" t="s">
+      <c r="CP14" s="122" t="s">
         <v>142</v>
       </c>
       <c r="CQ14" s="68" t="s">
@@ -67870,7 +69823,7 @@
       <c r="I15" s="78">
         <v>10041</v>
       </c>
-      <c r="K15" s="120" t="s">
+      <c r="K15" s="122" t="s">
         <v>241</v>
       </c>
       <c r="L15" s="68" t="s">
@@ -67900,7 +69853,7 @@
       <c r="AV15" s="68">
         <v>10033</v>
       </c>
-      <c r="AX15" s="120"/>
+      <c r="AX15" s="122"/>
       <c r="AY15" s="68" t="s">
         <v>81</v>
       </c>
@@ -67925,7 +69878,7 @@
       <c r="CN15" s="78">
         <v>10022</v>
       </c>
-      <c r="CP15" s="120"/>
+      <c r="CP15" s="122"/>
       <c r="CQ15" s="68" t="s">
         <v>61</v>
       </c>
@@ -67951,7 +69904,7 @@
       <c r="I16" s="78">
         <v>10042</v>
       </c>
-      <c r="K16" s="120"/>
+      <c r="K16" s="122"/>
       <c r="L16" s="68" t="s">
         <v>61</v>
       </c>
@@ -67979,7 +69932,7 @@
       <c r="AV16" s="68">
         <v>10041</v>
       </c>
-      <c r="AX16" s="120" t="s">
+      <c r="AX16" s="122" t="s">
         <v>241</v>
       </c>
       <c r="AY16" s="68" t="s">
@@ -67997,7 +69950,7 @@
       <c r="CN16" s="78">
         <v>10023</v>
       </c>
-      <c r="CP16" s="120"/>
+      <c r="CP16" s="122"/>
       <c r="CQ16" s="68" t="s">
         <v>81</v>
       </c>
@@ -68023,7 +69976,7 @@
       <c r="I17" s="78">
         <v>10043</v>
       </c>
-      <c r="K17" s="120"/>
+      <c r="K17" s="122"/>
       <c r="L17" s="68" t="s">
         <v>81</v>
       </c>
@@ -68046,7 +69999,7 @@
       <c r="AV17" s="68">
         <v>10042</v>
       </c>
-      <c r="AX17" s="120"/>
+      <c r="AX17" s="122"/>
       <c r="AY17" s="68" t="s">
         <v>61</v>
       </c>
@@ -68071,7 +70024,7 @@
       <c r="CN17" s="78">
         <v>10031</v>
       </c>
-      <c r="CP17" s="120" t="s">
+      <c r="CP17" s="122" t="s">
         <v>186</v>
       </c>
       <c r="CQ17" s="68" t="s">
@@ -68099,7 +70052,7 @@
       <c r="I18" s="68">
         <v>10051</v>
       </c>
-      <c r="K18" s="120" t="s">
+      <c r="K18" s="122" t="s">
         <v>275</v>
       </c>
       <c r="L18" s="68" t="s">
@@ -68135,7 +70088,7 @@
       <c r="AV18" s="68">
         <v>10043</v>
       </c>
-      <c r="AX18" s="120"/>
+      <c r="AX18" s="122"/>
       <c r="AY18" s="68" t="s">
         <v>81</v>
       </c>
@@ -68151,7 +70104,7 @@
       <c r="CN18" s="78">
         <v>10032</v>
       </c>
-      <c r="CP18" s="120"/>
+      <c r="CP18" s="122"/>
       <c r="CQ18" s="68" t="s">
         <v>61</v>
       </c>
@@ -68174,7 +70127,7 @@
       <c r="I19" s="68">
         <v>10052</v>
       </c>
-      <c r="K19" s="120"/>
+      <c r="K19" s="122"/>
       <c r="L19" s="68" t="s">
         <v>61</v>
       </c>
@@ -68208,7 +70161,7 @@
       <c r="AV19" s="68">
         <v>10051</v>
       </c>
-      <c r="AX19" s="120" t="s">
+      <c r="AX19" s="122" t="s">
         <v>275</v>
       </c>
       <c r="AY19" s="68" t="s">
@@ -68232,7 +70185,7 @@
       <c r="CN19" s="78">
         <v>10033</v>
       </c>
-      <c r="CP19" s="120"/>
+      <c r="CP19" s="122"/>
       <c r="CQ19" s="68" t="s">
         <v>81</v>
       </c>
@@ -68248,7 +70201,7 @@
       <c r="I20" s="68">
         <v>10053</v>
       </c>
-      <c r="K20" s="120"/>
+      <c r="K20" s="122"/>
       <c r="L20" s="68" t="s">
         <v>81</v>
       </c>
@@ -68279,7 +70232,7 @@
       <c r="AV20" s="68">
         <v>10052</v>
       </c>
-      <c r="AX20" s="120"/>
+      <c r="AX20" s="122"/>
       <c r="AY20" s="68" t="s">
         <v>61</v>
       </c>
@@ -68304,7 +70257,7 @@
       <c r="CN20" s="78">
         <v>10041</v>
       </c>
-      <c r="CP20" s="120" t="s">
+      <c r="CP20" s="122" t="s">
         <v>241</v>
       </c>
       <c r="CQ20" s="68" t="s">
@@ -68336,7 +70289,7 @@
         <v>10051</v>
       </c>
       <c r="J21" s="70"/>
-      <c r="K21" s="121" t="s">
+      <c r="K21" s="123" t="s">
         <v>315</v>
       </c>
       <c r="L21" s="70" t="s">
@@ -68363,7 +70316,7 @@
       <c r="AV21" s="68">
         <v>10053</v>
       </c>
-      <c r="AX21" s="120"/>
+      <c r="AX21" s="122"/>
       <c r="AY21" s="68" t="s">
         <v>81</v>
       </c>
@@ -68379,7 +70332,7 @@
       <c r="CN21" s="78">
         <v>10042</v>
       </c>
-      <c r="CP21" s="120"/>
+      <c r="CP21" s="122"/>
       <c r="CQ21" s="68" t="s">
         <v>61</v>
       </c>
@@ -68406,7 +70359,7 @@
         <v>10052</v>
       </c>
       <c r="J22" s="70"/>
-      <c r="K22" s="121"/>
+      <c r="K22" s="123"/>
       <c r="L22" s="70" t="s">
         <v>61</v>
       </c>
@@ -68430,7 +70383,7 @@
         <v>10051</v>
       </c>
       <c r="AW22" s="70"/>
-      <c r="AX22" s="121" t="s">
+      <c r="AX22" s="123" t="s">
         <v>315</v>
       </c>
       <c r="AY22" s="70" t="s">
@@ -68455,7 +70408,7 @@
       <c r="CN22" s="78">
         <v>10043</v>
       </c>
-      <c r="CP22" s="120"/>
+      <c r="CP22" s="122"/>
       <c r="CQ22" s="68" t="s">
         <v>81</v>
       </c>
@@ -68482,7 +70435,7 @@
         <v>10053</v>
       </c>
       <c r="J23" s="70"/>
-      <c r="K23" s="121"/>
+      <c r="K23" s="123"/>
       <c r="L23" s="70" t="s">
         <v>81</v>
       </c>
@@ -68516,7 +70469,7 @@
         <v>10052</v>
       </c>
       <c r="AW23" s="70"/>
-      <c r="AX23" s="121"/>
+      <c r="AX23" s="123"/>
       <c r="AY23" s="70" t="s">
         <v>61</v>
       </c>
@@ -68539,7 +70492,7 @@
       <c r="CN23" s="68">
         <v>10051</v>
       </c>
-      <c r="CP23" s="120" t="s">
+      <c r="CP23" s="122" t="s">
         <v>275</v>
       </c>
       <c r="CQ23" s="68" t="s">
@@ -68605,7 +70558,7 @@
         <v>10053</v>
       </c>
       <c r="AW24" s="70"/>
-      <c r="AX24" s="121"/>
+      <c r="AX24" s="123"/>
       <c r="AY24" s="70" t="s">
         <v>81</v>
       </c>
@@ -68641,7 +70594,7 @@
       <c r="CN24" s="68">
         <v>10052</v>
       </c>
-      <c r="CP24" s="120"/>
+      <c r="CP24" s="122"/>
       <c r="CQ24" s="68" t="s">
         <v>61</v>
       </c>
@@ -68731,7 +70684,7 @@
       <c r="CN25" s="68">
         <v>10053</v>
       </c>
-      <c r="CP25" s="120"/>
+      <c r="CP25" s="122"/>
       <c r="CQ25" s="68" t="s">
         <v>81</v>
       </c>
@@ -68832,7 +70785,7 @@
         <v>10051</v>
       </c>
       <c r="CO26" s="70"/>
-      <c r="CP26" s="121" t="s">
+      <c r="CP26" s="123" t="s">
         <v>315</v>
       </c>
       <c r="CQ26" s="70" t="s">
@@ -68935,7 +70888,7 @@
         <v>10052</v>
       </c>
       <c r="CO27" s="70"/>
-      <c r="CP27" s="121"/>
+      <c r="CP27" s="123"/>
       <c r="CQ27" s="70" t="s">
         <v>61</v>
       </c>
@@ -69038,7 +70991,7 @@
         <v>10053</v>
       </c>
       <c r="CO28" s="70"/>
-      <c r="CP28" s="121"/>
+      <c r="CP28" s="123"/>
       <c r="CQ28" s="70" t="s">
         <v>81</v>
       </c>
